--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="1803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="1804">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48755359649658</t>
+    <t xml:space="preserve">7.48755407333374</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43893241882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23837566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0438928604126</t>
+    <t xml:space="preserve">7.43893337249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23837327957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04389238357544</t>
   </si>
   <si>
     <t xml:space="preserve">6.99527215957642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06212425231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25052928924561</t>
+    <t xml:space="preserve">7.06212615966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25053024291992</t>
   </si>
   <si>
     <t xml:space="preserve">7.22014188766479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17152070999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07428026199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84941053390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01350355148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75216960906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83725452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97096157073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09251260757446</t>
+    <t xml:space="preserve">7.17152166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07427978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84941101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0135064125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75216913223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83725547790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97096252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0925121307373</t>
   </si>
   <si>
     <t xml:space="preserve">7.00742721557617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00134944915771</t>
+    <t xml:space="preserve">7.00134897232056</t>
   </si>
   <si>
     <t xml:space="preserve">6.98919486999512</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">6.92841863632202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8615665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53337669372559</t>
+    <t xml:space="preserve">6.86156511306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53337717056274</t>
   </si>
   <si>
     <t xml:space="preserve">6.47867918014526</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">6.61238527297974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55160999298096</t>
+    <t xml:space="preserve">6.5516095161438</t>
   </si>
   <si>
     <t xml:space="preserve">6.77647972106934</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94057273864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8737211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63061809539795</t>
+    <t xml:space="preserve">6.94057416915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87372159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63061904907227</t>
   </si>
   <si>
     <t xml:space="preserve">6.78863573074341</t>
@@ -143,55 +143,55 @@
     <t xml:space="preserve">6.80686712265015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91626358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84333276748657</t>
+    <t xml:space="preserve">6.91626453399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84333372116089</t>
   </si>
   <si>
     <t xml:space="preserve">6.83117818832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.879798412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7096266746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74609231948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85548782348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86764287948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95272922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04997110366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27484035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35992622375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34777069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26876306533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22622013092041</t>
+    <t xml:space="preserve">6.87979745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70962619781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74609279632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85548734664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86764335632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95272874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04996919631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27483987808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35992479324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34777116775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26876258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22621965408325</t>
   </si>
   <si>
     <t xml:space="preserve">7.11074542999268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03173589706421</t>
+    <t xml:space="preserve">7.03173685073853</t>
   </si>
   <si>
     <t xml:space="preserve">7.08035802841187</t>
@@ -200,13 +200,13 @@
     <t xml:space="preserve">7.05604696273804</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18975400924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23229598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15328884124756</t>
+    <t xml:space="preserve">7.18975353240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23229694366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1532883644104</t>
   </si>
   <si>
     <t xml:space="preserve">7.11682319641113</t>
@@ -221,127 +221,127 @@
     <t xml:space="preserve">6.93449592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89803075790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90410852432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96488380432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79471254348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76432514190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14113330841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02565956115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15738725662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13741302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31052112579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25725793838501</t>
+    <t xml:space="preserve">6.89803123474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90410804748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96488475799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79471302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76432466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14113426208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02566003799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.157386302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1374135017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31052207946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25725698471069</t>
   </si>
   <si>
     <t xml:space="preserve">7.34381198883057</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38375997543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29720640182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25059938430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21730947494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062562942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23728370666504</t>
+    <t xml:space="preserve">7.38375902175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29720497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25059795379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21730995178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062610626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23728275299072</t>
   </si>
   <si>
     <t xml:space="preserve">7.27723217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22396802902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10412168502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85777521133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65803337097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60477066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.474937915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50822734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95764589309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93767213821411</t>
+    <t xml:space="preserve">7.22396659851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10412359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85777473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.658034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60476970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47493839263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50822877883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95764541625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93767166137695</t>
   </si>
   <si>
     <t xml:space="preserve">6.82448482513428</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88440799713135</t>
+    <t xml:space="preserve">6.88440656661987</t>
   </si>
   <si>
     <t xml:space="preserve">6.47826671600342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56149291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69132471084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81782579421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91769742965698</t>
+    <t xml:space="preserve">6.3218035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56149339675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69132423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81782674789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91769886016846</t>
   </si>
   <si>
     <t xml:space="preserve">7.03754138946533</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78453636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50490045547485</t>
+    <t xml:space="preserve">6.78453683853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50489950180054</t>
   </si>
   <si>
     <t xml:space="preserve">6.61808586120605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71795654296875</t>
+    <t xml:space="preserve">6.71795606613159</t>
   </si>
   <si>
     <t xml:space="preserve">6.6846661567688</t>
@@ -350,73 +350,73 @@
     <t xml:space="preserve">6.73793029785156</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87774848937988</t>
+    <t xml:space="preserve">6.87774801254272</t>
   </si>
   <si>
     <t xml:space="preserve">6.8111686706543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7512469291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79119491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76456260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86443328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77122116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89106512069702</t>
+    <t xml:space="preserve">6.75124645233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79119539260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76456308364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86443376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77122068405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89106607437134</t>
   </si>
   <si>
     <t xml:space="preserve">6.73127269744873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64471817016602</t>
+    <t xml:space="preserve">6.64471769332886</t>
   </si>
   <si>
     <t xml:space="preserve">6.63806056976318</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75790405273438</t>
+    <t xml:space="preserve">6.75790452957153</t>
   </si>
   <si>
     <t xml:space="preserve">6.83114242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80451154708862</t>
+    <t xml:space="preserve">6.80451202392578</t>
   </si>
   <si>
     <t xml:space="preserve">6.9310131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96430397033691</t>
+    <t xml:space="preserve">6.96430444717407</t>
   </si>
   <si>
     <t xml:space="preserve">6.74458885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71129941940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65137672424316</t>
+    <t xml:space="preserve">6.71129894256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65137529373169</t>
   </si>
   <si>
     <t xml:space="preserve">6.62807273864746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64139032363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62141513824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01756763458252</t>
+    <t xml:space="preserve">6.6413893699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62141418457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01756811141968</t>
   </si>
   <si>
     <t xml:space="preserve">6.98427724838257</t>
@@ -425,40 +425,40 @@
     <t xml:space="preserve">7.01090955734253</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04419994354248</t>
+    <t xml:space="preserve">7.04420042037964</t>
   </si>
   <si>
     <t xml:space="preserve">7.17070293426514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87109088897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92435455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97761964797974</t>
+    <t xml:space="preserve">6.87109136581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9243540763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97762012481689</t>
   </si>
   <si>
     <t xml:space="preserve">6.83780145645142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84445905685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79785251617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77787923812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59811210632324</t>
+    <t xml:space="preserve">6.84445953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79785346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7778787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5981125831604</t>
   </si>
   <si>
     <t xml:space="preserve">6.55150604248047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72461557388306</t>
+    <t xml:space="preserve">6.72461462020874</t>
   </si>
   <si>
     <t xml:space="preserve">6.67135000228882</t>
@@ -470,37 +470,37 @@
     <t xml:space="preserve">6.60809898376465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54484796524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45829391479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65470552444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67800807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46495151519775</t>
+    <t xml:space="preserve">6.54484844207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45829296112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65470504760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67800855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4649510383606</t>
   </si>
   <si>
     <t xml:space="preserve">6.13870763778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.228590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19197130203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17865514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24856472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13537883758545</t>
+    <t xml:space="preserve">6.22859144210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19197225570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17865467071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24856567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13537836074829</t>
   </si>
   <si>
     <t xml:space="preserve">6.06546926498413</t>
@@ -509,37 +509,37 @@
     <t xml:space="preserve">6.16866827011108</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15868139266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14203643798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06213998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03883600234985</t>
+    <t xml:space="preserve">6.15868234634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14203691482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0621395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03883647918701</t>
   </si>
   <si>
     <t xml:space="preserve">6.10874652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05881118774414</t>
+    <t xml:space="preserve">6.0588116645813</t>
   </si>
   <si>
     <t xml:space="preserve">6.02219200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0188627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11873245239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23191928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12206220626831</t>
+    <t xml:space="preserve">6.01886224746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11873340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23191976547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12206172943115</t>
   </si>
   <si>
     <t xml:space="preserve">6.22193288803101</t>
@@ -548,100 +548,100 @@
     <t xml:space="preserve">6.21860408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35842275619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37839698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62474393844604</t>
+    <t xml:space="preserve">6.35842227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37839555740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6247444152832</t>
   </si>
   <si>
     <t xml:space="preserve">6.70464038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85111808776855</t>
+    <t xml:space="preserve">6.8511176109314</t>
   </si>
   <si>
     <t xml:space="preserve">6.69798278808594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90438032150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89772272109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99093437194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07749032974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91103887557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07083129882812</t>
+    <t xml:space="preserve">6.90438079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89772367477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99093532562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07749080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91103982925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07083320617676</t>
   </si>
   <si>
     <t xml:space="preserve">7.1307544708252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15072822570801</t>
+    <t xml:space="preserve">7.15072870254517</t>
   </si>
   <si>
     <t xml:space="preserve">7.18402004241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0974645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05085802078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35047101974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27057361602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28388977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30386400222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53023672103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32383680343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31717967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3637866973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51692056655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59015989303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347461700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000337600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992607116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77658462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73663520812988</t>
+    <t xml:space="preserve">7.09746408462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05085849761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35046863555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27057313919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28388833999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30386352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53023719787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32383823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31717920303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36378479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51692008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59015846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347509384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71000385284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992464065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77658414840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73663711547852</t>
   </si>
   <si>
     <t xml:space="preserve">7.78990077972412</t>
@@ -650,73 +650,73 @@
     <t xml:space="preserve">7.75660991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8231897354126</t>
+    <t xml:space="preserve">7.82319116592407</t>
   </si>
   <si>
     <t xml:space="preserve">7.85648059844971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979579925537</t>
+    <t xml:space="preserve">7.86979675292969</t>
   </si>
   <si>
     <t xml:space="preserve">7.8764533996582</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90308475494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96966648101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94969272613525</t>
+    <t xml:space="preserve">7.90308713912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96966743469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94969320297241</t>
   </si>
   <si>
     <t xml:space="preserve">7.92306041717529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96300792694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72331953048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62344741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54355192184448</t>
+    <t xml:space="preserve">7.96300888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311243057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7233190536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62344884872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54355335235596</t>
   </si>
   <si>
     <t xml:space="preserve">7.47031497955322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63676452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56352663040161</t>
+    <t xml:space="preserve">7.6367654800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56352615356445</t>
   </si>
   <si>
     <t xml:space="preserve">7.57018518447876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74329280853271</t>
+    <t xml:space="preserve">7.74329376220703</t>
   </si>
   <si>
     <t xml:space="preserve">7.80321598052979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89642715454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94303417205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84982299804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06953811645508</t>
+    <t xml:space="preserve">7.89642810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94303512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84982204437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06953716278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.20842742919922</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">8.25009441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22926139831543</t>
+    <t xml:space="preserve">8.22926044464111</t>
   </si>
   <si>
     <t xml:space="preserve">8.31954002380371</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">8.35426235198975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28481960296631</t>
+    <t xml:space="preserve">8.28481769561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.29870700836182</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">8.37509632110596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34731960296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38898658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43759632110596</t>
+    <t xml:space="preserve">8.34731864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3889856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43759727478027</t>
   </si>
   <si>
     <t xml:space="preserve">8.4514856338501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68759918212891</t>
+    <t xml:space="preserve">8.68760013580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.7362117767334</t>
@@ -764,10 +764,10 @@
     <t xml:space="preserve">8.62509918212891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63898944854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6667652130127</t>
+    <t xml:space="preserve">8.63898849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66676712036133</t>
   </si>
   <si>
     <t xml:space="preserve">8.68065547943115</t>
@@ -776,22 +776,22 @@
     <t xml:space="preserve">8.59732151031494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7292652130127</t>
+    <t xml:space="preserve">8.72926616668701</t>
   </si>
   <si>
     <t xml:space="preserve">8.69454479217529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61121082305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50704193115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59037685394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52787590026855</t>
+    <t xml:space="preserve">8.61120986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50704288482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59037590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52787494659424</t>
   </si>
   <si>
     <t xml:space="preserve">8.54870986938477</t>
@@ -803,16 +803,16 @@
     <t xml:space="preserve">8.51398658752441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46537399291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47231864929199</t>
+    <t xml:space="preserve">8.46537494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47231960296631</t>
   </si>
   <si>
     <t xml:space="preserve">8.61815452575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65982151031494</t>
+    <t xml:space="preserve">8.65982246398926</t>
   </si>
   <si>
     <t xml:space="preserve">8.6459321975708</t>
@@ -821,58 +821,58 @@
     <t xml:space="preserve">8.40981864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43065357208252</t>
+    <t xml:space="preserve">8.4306526184082</t>
   </si>
   <si>
     <t xml:space="preserve">8.42370796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30565166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54176425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57648754119873</t>
+    <t xml:space="preserve">8.30565071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5417652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57648849487305</t>
   </si>
   <si>
     <t xml:space="preserve">8.60426712036133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88204479217529</t>
+    <t xml:space="preserve">8.71537780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88204669952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.00010299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1528844833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13204956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06954956054688</t>
+    <t xml:space="preserve">9.15288257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13204860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06954765319824</t>
   </si>
   <si>
     <t xml:space="preserve">9.09038257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00704765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95843696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06260395050049</t>
+    <t xml:space="preserve">9.00704860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95843505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0626049041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.1251049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20843982696533</t>
+    <t xml:space="preserve">9.20843887329102</t>
   </si>
   <si>
     <t xml:space="preserve">9.24316215515137</t>
@@ -890,34 +890,34 @@
     <t xml:space="preserve">9.41677570343018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32649707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29177474975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31260776519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45149612426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47233200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43760967254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44455146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4028844833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38899803161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38205146789551</t>
+    <t xml:space="preserve">9.32649612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29177379608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31260681152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45149707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47233104705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43760776519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44455432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40288639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38899707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38205242156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.3403844833374</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">9.34733009338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48622035980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75011157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79178047180176</t>
+    <t xml:space="preserve">9.31955242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48622131347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7501106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79177951812744</t>
   </si>
   <si>
     <t xml:space="preserve">9.77788925170898</t>
@@ -947,58 +947,58 @@
     <t xml:space="preserve">9.72927856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77094554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76400184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74316787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96539211273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0278921127319</t>
+    <t xml:space="preserve">9.77094459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76400279998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74316883087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96539306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0278930664062</t>
   </si>
   <si>
     <t xml:space="preserve">9.93761539459229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834503173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1181716918945</t>
+    <t xml:space="preserve">10.0834493637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1181697845459</t>
   </si>
   <si>
     <t xml:space="preserve">10.1876173019409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4445638656616</t>
+    <t xml:space="preserve">10.4445648193359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5001211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5695667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.229284286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3959541320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4237298965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5903997421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4931735992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5626220703125</t>
+    <t xml:space="preserve">10.5695657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2292833328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3959531784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.423731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5903987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4931764602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5626211166382</t>
   </si>
   <si>
     <t xml:space="preserve">10.6251230239868</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">10.7015113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7779006958008</t>
+    <t xml:space="preserve">10.7779026031494</t>
   </si>
   <si>
     <t xml:space="preserve">10.8542919158936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.833459854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9029026031494</t>
+    <t xml:space="preserve">10.8334579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9029035568237</t>
   </si>
   <si>
     <t xml:space="preserve">11.0904064178467</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">11.1042947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1112394332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9723472595215</t>
+    <t xml:space="preserve">11.1112384796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9723482131958</t>
   </si>
   <si>
     <t xml:space="preserve">10.9445705413818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0765161514282</t>
+    <t xml:space="preserve">11.0765151977539</t>
   </si>
   <si>
     <t xml:space="preserve">11.3473529815674</t>
@@ -1052,22 +1052,22 @@
     <t xml:space="preserve">11.1529064178467</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0626268386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2154054641724</t>
+    <t xml:space="preserve">11.0626287460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2154064178467</t>
   </si>
   <si>
     <t xml:space="preserve">11.3126316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2362403869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2084617614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9098472595215</t>
+    <t xml:space="preserve">11.2362413406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2084627151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9098482131958</t>
   </si>
   <si>
     <t xml:space="preserve">10.736234664917</t>
@@ -1076,49 +1076,49 @@
     <t xml:space="preserve">10.8751249313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6945667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5487337112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7848463058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.861234664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0695714950562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.187629699707</t>
+    <t xml:space="preserve">10.6945686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5487308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7848453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8612365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0695705413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876287460327</t>
   </si>
   <si>
     <t xml:space="preserve">10.9306812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1598510742188</t>
+    <t xml:space="preserve">11.1598501205444</t>
   </si>
   <si>
     <t xml:space="preserve">11.4515199661255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5001306533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4931869506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6251335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7223567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709693908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7015247344971</t>
+    <t xml:space="preserve">11.5001316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4931879043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.62513256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7223558425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709703445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7015237808228</t>
   </si>
   <si>
     <t xml:space="preserve">11.7293014526367</t>
@@ -1127,28 +1127,28 @@
     <t xml:space="preserve">11.7154130935669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6112442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4862442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5765218734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6806888580322</t>
+    <t xml:space="preserve">11.6112432479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4862432479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5765228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6806907653809</t>
   </si>
   <si>
     <t xml:space="preserve">11.3820753097534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8681802749634</t>
+    <t xml:space="preserve">10.8681812286377</t>
   </si>
   <si>
     <t xml:space="preserve">10.8959589004517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9862375259399</t>
+    <t xml:space="preserve">10.9862365722656</t>
   </si>
   <si>
     <t xml:space="preserve">11.0834608078003</t>
@@ -1160,31 +1160,31 @@
     <t xml:space="preserve">11.2848520278931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3265180587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.243185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5973567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7501354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6181898117065</t>
+    <t xml:space="preserve">11.3265171051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2431840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5973558425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7501344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6181888580322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7987470626831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6320791244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8334712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1251392364502</t>
+    <t xml:space="preserve">11.632080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8334703445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1251382827759</t>
   </si>
   <si>
     <t xml:space="preserve">11.9168033599854</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">12.6668119430542</t>
   </si>
   <si>
-    <t xml:space="preserve">13.152928352356</t>
+    <t xml:space="preserve">13.1529302597046</t>
   </si>
   <si>
     <t xml:space="preserve">13.3820991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.319598197937</t>
+    <t xml:space="preserve">13.3195991516113</t>
   </si>
   <si>
     <t xml:space="preserve">13.3682088851929</t>
@@ -1208,22 +1208,22 @@
     <t xml:space="preserve">13.5765438079834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5209875106812</t>
+    <t xml:space="preserve">13.5209884643555</t>
   </si>
   <si>
     <t xml:space="preserve">13.2362623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1668167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0487613677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4237651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0070943832397</t>
+    <t xml:space="preserve">13.1668176651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0487623214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4237661361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070924758911</t>
   </si>
   <si>
     <t xml:space="preserve">13.3543195724487</t>
@@ -1232,115 +1232,115 @@
     <t xml:space="preserve">13.4584875106812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154340744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918243408203</t>
+    <t xml:space="preserve">13.7154359817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918252944946</t>
   </si>
   <si>
     <t xml:space="preserve">13.6807136535645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9168281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9307146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.187650680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2987632751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3751554489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4168214797974</t>
+    <t xml:space="preserve">13.9168252944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9307155609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1876497268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2987642288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3751525878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.416820526123</t>
   </si>
   <si>
     <t xml:space="preserve">13.4723768234253</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4862670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6112689971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.736270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223796844482</t>
+    <t xml:space="preserve">13.4862651824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6112661361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7362689971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223815917969</t>
   </si>
   <si>
     <t xml:space="preserve">13.8196039199829</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8890466690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8543272018433</t>
+    <t xml:space="preserve">13.8890504837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8543243408203</t>
   </si>
   <si>
     <t xml:space="preserve">13.9029378890991</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0834951400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.798770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0279388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.305721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1945953369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1112604141235</t>
+    <t xml:space="preserve">14.0834941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7987689971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0279397964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.305718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1112623214722</t>
   </si>
   <si>
     <t xml:space="preserve">13.1807069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0200996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1486539840698</t>
+    <t xml:space="preserve">14.0201005935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1486530303955</t>
   </si>
   <si>
     <t xml:space="preserve">13.8083600997925</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6571187973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5361261367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2563285827637</t>
+    <t xml:space="preserve">13.6571178436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5361251831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2563276290894</t>
   </si>
   <si>
     <t xml:space="preserve">13.1277732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3092622756958</t>
+    <t xml:space="preserve">13.3092632293701</t>
   </si>
   <si>
     <t xml:space="preserve">13.4605045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4983148574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4680652618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5739364624023</t>
+    <t xml:space="preserve">13.4983139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4680671691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.573935508728</t>
   </si>
   <si>
     <t xml:space="preserve">13.7327394485474</t>
@@ -1352,49 +1352,49 @@
     <t xml:space="preserve">13.4075689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4889459609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.473822593689</t>
+    <t xml:space="preserve">14.4889469146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4738206863403</t>
   </si>
   <si>
     <t xml:space="preserve">14.6704368591309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7158098220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755168914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6175031661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.723370552063</t>
+    <t xml:space="preserve">14.7158088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755149841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6175022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7233715057373</t>
   </si>
   <si>
     <t xml:space="preserve">14.9351110458374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.746057510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292417526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167119979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2998962402344</t>
+    <t xml:space="preserve">14.7460584640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2998943328857</t>
   </si>
   <si>
     <t xml:space="preserve">14.2091512680054</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0654716491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1637783050537</t>
+    <t xml:space="preserve">14.0654706954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1637763977051</t>
   </si>
   <si>
     <t xml:space="preserve">14.0427846908569</t>
@@ -1403,94 +1403,94 @@
     <t xml:space="preserve">14.1713399887085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2847700119019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6250638961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536191940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.67799949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.791431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8443651199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8746128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.836802482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7611846923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6553115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5494441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099424362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6401891708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5721302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5191955566406</t>
+    <t xml:space="preserve">14.2847719192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6250648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6779975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7914304733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8443622589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8746156692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8368043899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7611827850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6553134918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5494451522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099405288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6401901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5721321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5191965103149</t>
   </si>
   <si>
     <t xml:space="preserve">14.2393999099731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0049743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9217910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9142303466797</t>
+    <t xml:space="preserve">14.0049724578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9217901229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9142284393311</t>
   </si>
   <si>
     <t xml:space="preserve">14.2696466445923</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3982048034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9898500442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.664680480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6722431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5814971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7705488204956</t>
+    <t xml:space="preserve">14.3982028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9898490905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6646814346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6722421646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5814952850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705497741699</t>
   </si>
   <si>
     <t xml:space="preserve">13.6268701553345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5210008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.551248550415</t>
+    <t xml:space="preserve">13.5209999084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495561599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5512495040894</t>
   </si>
   <si>
     <t xml:space="preserve">13.4907531738281</t>
@@ -1505,61 +1505,61 @@
     <t xml:space="preserve">13.3470726013184</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.483190536499</t>
+    <t xml:space="preserve">13.39244556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4831895828247</t>
   </si>
   <si>
     <t xml:space="preserve">13.8310470581055</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6344318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5663728713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5436859130859</t>
+    <t xml:space="preserve">13.6344327926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5663738250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5436868667603</t>
   </si>
   <si>
     <t xml:space="preserve">13.3773221969604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1958332061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2714519500732</t>
+    <t xml:space="preserve">13.1958322525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2714509963989</t>
   </si>
   <si>
     <t xml:space="preserve">13.3395099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3546352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2638912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4529447555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3319473266602</t>
+    <t xml:space="preserve">13.3546361923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2638902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4529428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3319492340088</t>
   </si>
   <si>
     <t xml:space="preserve">12.9311590194702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0219020843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8101654052734</t>
+    <t xml:space="preserve">13.0219030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8101663589478</t>
   </si>
   <si>
     <t xml:space="preserve">12.5530548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7421054840088</t>
+    <t xml:space="preserve">12.7421064376831</t>
   </si>
   <si>
     <t xml:space="preserve">12.6513614654541</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">13.3848838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">13.120210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9614057540894</t>
+    <t xml:space="preserve">13.1202116012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.961407661438</t>
   </si>
   <si>
     <t xml:space="preserve">12.5681791305542</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">12.6211128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4018135070801</t>
+    <t xml:space="preserve">12.4018125534058</t>
   </si>
   <si>
     <t xml:space="preserve">12.4925584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4698724746704</t>
+    <t xml:space="preserve">12.4698705673218</t>
   </si>
   <si>
     <t xml:space="preserve">12.1371393203735</t>
@@ -1598,85 +1598,85 @@
     <t xml:space="preserve">12.2883825302124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1522645950317</t>
+    <t xml:space="preserve">12.1522636413574</t>
   </si>
   <si>
     <t xml:space="preserve">12.6286754608154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6437997817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252878189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7723550796509</t>
+    <t xml:space="preserve">12.643798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252897262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7723541259766</t>
   </si>
   <si>
     <t xml:space="preserve">12.847975730896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7572298049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8177280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7799167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4471845626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4244985580444</t>
+    <t xml:space="preserve">12.7572317123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8177289962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7799158096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4471855163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4245004653931</t>
   </si>
   <si>
     <t xml:space="preserve">12.2581338882446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1673879623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.416937828064</t>
+    <t xml:space="preserve">12.1673889160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4169368743896</t>
   </si>
   <si>
     <t xml:space="preserve">12.1447019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0312700271606</t>
+    <t xml:space="preserve">12.031270980835</t>
   </si>
   <si>
     <t xml:space="preserve">12.2505722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1068916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2278842926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0463953018188</t>
+    <t xml:space="preserve">12.1068925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2278852462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0463962554932</t>
   </si>
   <si>
     <t xml:space="preserve">12.0993299484253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7968463897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8800296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5379304885864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2656946182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7950410842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2941408157349</t>
+    <t xml:space="preserve">11.7968454360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8800287246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5379295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2656955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7950401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2941389083862</t>
   </si>
   <si>
     <t xml:space="preserve">13.1126489639282</t>
@@ -1685,82 +1685,82 @@
     <t xml:space="preserve">12.9538440704346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5833015441895</t>
+    <t xml:space="preserve">12.5833024978638</t>
   </si>
   <si>
     <t xml:space="preserve">12.4774341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5757398605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8555383682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0143404006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8328523635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9084720611572</t>
+    <t xml:space="preserve">12.575740814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8555374145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0143413543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8328504562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9084730148315</t>
   </si>
   <si>
     <t xml:space="preserve">13.0521516799927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9160346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0975246429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0067796707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2260808944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2185163497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9009103775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0370283126831</t>
+    <t xml:space="preserve">12.916033744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.09752368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.006778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2260818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2185182571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9009094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0370273590088</t>
   </si>
   <si>
     <t xml:space="preserve">12.7647914886475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.029465675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.210955619812</t>
+    <t xml:space="preserve">13.0294647216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109546661377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2336416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9235973358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8706617355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8933458328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353349685669</t>
+    <t xml:space="preserve">12.9235963821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8706636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8933486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1882696151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353368759155</t>
   </si>
   <si>
     <t xml:space="preserve">12.9689683914185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1050863265991</t>
+    <t xml:space="preserve">13.1050853729248</t>
   </si>
   <si>
     <t xml:space="preserve">13.301700592041</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">12.8857860565186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6891717910767</t>
+    <t xml:space="preserve">12.689172744751</t>
   </si>
   <si>
     <t xml:space="preserve">12.6967344284058</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">12.6362371444702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.666485786438</t>
+    <t xml:space="preserve">12.6664876937866</t>
   </si>
   <si>
     <t xml:space="preserve">12.5152435302734</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3110675811768</t>
+    <t xml:space="preserve">12.3110685348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.2430086135864</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">12.6589241027832</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7269830703735</t>
+    <t xml:space="preserve">12.7269821166992</t>
   </si>
   <si>
     <t xml:space="preserve">12.7496700286865</t>
@@ -1826,64 +1826,64 @@
     <t xml:space="preserve">12.2808198928833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.303505897522</t>
+    <t xml:space="preserve">12.3035049438477</t>
   </si>
   <si>
     <t xml:space="preserve">12.8631000518799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2902870178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4485063552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5988121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146326065063</t>
+    <t xml:space="preserve">13.2902860641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.448504447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988140106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6146335601807</t>
   </si>
   <si>
     <t xml:space="preserve">13.9548015594482</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9785356521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8598728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7491188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7332973480225</t>
+    <t xml:space="preserve">13.978533744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8598709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7491178512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7332983016968</t>
   </si>
   <si>
     <t xml:space="preserve">13.7728519439697</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8124046325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.717474937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6383676528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6620998382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5750780105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1446628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2395944595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5085639953613</t>
+    <t xml:space="preserve">13.812406539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7174768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6383666992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6620988845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5750789642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1446619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2395935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.508563041687</t>
   </si>
   <si>
     <t xml:space="preserve">14.4690103530884</t>
@@ -1892,22 +1892,22 @@
     <t xml:space="preserve">14.5955858230591</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7221574783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.674690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.176305770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1604862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0813751220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0339097976685</t>
+    <t xml:space="preserve">14.7221593856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6746921539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1763067245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1604852676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0813760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0339107513428</t>
   </si>
   <si>
     <t xml:space="preserve">14.4373655319214</t>
@@ -1916,10 +1916,10 @@
     <t xml:space="preserve">14.6984243392944</t>
   </si>
   <si>
-    <t xml:space="preserve">14.611403465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4136323928833</t>
+    <t xml:space="preserve">14.6114053726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4136333465576</t>
   </si>
   <si>
     <t xml:space="preserve">14.6272268295288</t>
@@ -1931,43 +1931,43 @@
     <t xml:space="preserve">15.0939693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9911270141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.943660736084</t>
+    <t xml:space="preserve">14.9911289215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9436616897583</t>
   </si>
   <si>
     <t xml:space="preserve">14.9120187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8724641799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8645544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6430511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2870588302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3266134262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2158603668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2475032806396</t>
+    <t xml:space="preserve">14.8724660873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8645534515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6430501937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2870578765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3266143798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2158613204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.247504234314</t>
   </si>
   <si>
     <t xml:space="preserve">14.0259990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0576438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6067237854004</t>
+    <t xml:space="preserve">14.0576429367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6067228317261</t>
   </si>
   <si>
     <t xml:space="preserve">13.8677825927734</t>
@@ -1976,22 +1976,22 @@
     <t xml:space="preserve">14.2000398635864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2949705123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2079496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6304559707642</t>
+    <t xml:space="preserve">14.2949714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2079486846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6304550170898</t>
   </si>
   <si>
     <t xml:space="preserve">13.5671682357788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6700096130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5197038650513</t>
+    <t xml:space="preserve">13.6700115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.519702911377</t>
   </si>
   <si>
     <t xml:space="preserve">13.3693962097168</t>
@@ -2000,145 +2000,145 @@
     <t xml:space="preserve">13.8203172683716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9073390960693</t>
+    <t xml:space="preserve">13.9073362350464</t>
   </si>
   <si>
     <t xml:space="preserve">13.8440494537354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5592565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7886724472046</t>
+    <t xml:space="preserve">13.5592575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7886734008789</t>
   </si>
   <si>
     <t xml:space="preserve">13.7965850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1209306716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9310703277588</t>
+    <t xml:space="preserve">14.1209297180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9310693740845</t>
   </si>
   <si>
     <t xml:space="preserve">14.0892868041992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3028812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4848318099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6588706970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633256912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2316846847534</t>
+    <t xml:space="preserve">14.3028802871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4848299026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6588726043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633275985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2316827774048</t>
   </si>
   <si>
     <t xml:space="preserve">14.1130199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5876712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9753074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8566427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9990377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8329086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7458877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0227708816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7379779815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6905145645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6351385116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5402059555054</t>
+    <t xml:space="preserve">14.5876722335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9753046035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8566436767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9990367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8329095840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7458906173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7379808425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6905155181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5402088165283</t>
   </si>
   <si>
     <t xml:space="preserve">14.1525735855103</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5164747238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4294538497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1921281814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0971975326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2712373733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2791471481323</t>
+    <t xml:space="preserve">14.5164756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4294548034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1921291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0971984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2712383270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2791481018066</t>
   </si>
   <si>
     <t xml:space="preserve">14.4057216644287</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3899011611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3424348831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3582553863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4611005783081</t>
+    <t xml:space="preserve">14.3899021148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.342435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3582582473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4610986709595</t>
   </si>
   <si>
     <t xml:space="preserve">15.0069494247437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9515733718872</t>
+    <t xml:space="preserve">14.9515724182129</t>
   </si>
   <si>
     <t xml:space="preserve">14.5322971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3345232009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3740797042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3819894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6509609222412</t>
+    <t xml:space="preserve">14.3345251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.374077796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3819904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509590148926</t>
   </si>
   <si>
     <t xml:space="preserve">15.0860576629639</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8170881271362</t>
+    <t xml:space="preserve">14.8170871734619</t>
   </si>
   <si>
     <t xml:space="preserve">14.6193161010742</t>
@@ -2147,16 +2147,16 @@
     <t xml:space="preserve">15.0544166564941</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4895133972168</t>
+    <t xml:space="preserve">15.4895124435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.8692359924316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7189302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3075666427612</t>
+    <t xml:space="preserve">15.7189292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3075647354126</t>
   </si>
   <si>
     <t xml:space="preserve">15.3471174240112</t>
@@ -2165,40 +2165,40 @@
     <t xml:space="preserve">15.6081781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2284545898438</t>
+    <t xml:space="preserve">15.2284526824951</t>
   </si>
   <si>
     <t xml:space="preserve">15.1572551727295</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1889009475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1414346694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3866739273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2838325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3154735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7505722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7110185623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6160860061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4420509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2047214508057</t>
+    <t xml:space="preserve">15.1889019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.141432762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3866729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2838306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3154745101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7505741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7110176086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6160879135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4420471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2047204971313</t>
   </si>
   <si>
     <t xml:space="preserve">15.2363653182983</t>
@@ -2207,37 +2207,37 @@
     <t xml:space="preserve">15.1651668548584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4024925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6239995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7743072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2173137664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5179290771484</t>
+    <t xml:space="preserve">15.4024934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6239986419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7743053436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2173175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5179309844971</t>
   </si>
   <si>
     <t xml:space="preserve">16.296422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5653953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0400466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9292945861816</t>
+    <t xml:space="preserve">16.565393447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0400485992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9292964935303</t>
   </si>
   <si>
     <t xml:space="preserve">17.0875129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0558681488037</t>
+    <t xml:space="preserve">17.0558700561523</t>
   </si>
   <si>
     <t xml:space="preserve">16.9609394073486</t>
@@ -2246,28 +2246,28 @@
     <t xml:space="preserve">16.6919689178467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8976497650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1982650756836</t>
+    <t xml:space="preserve">16.8976516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.198263168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.8818302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">17.229907989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.356481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4514122009277</t>
+    <t xml:space="preserve">17.2299098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3564834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4514102935791</t>
   </si>
   <si>
     <t xml:space="preserve">17.6096305847168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4039478302002</t>
+    <t xml:space="preserve">17.4039459228516</t>
   </si>
   <si>
     <t xml:space="preserve">17.4355926513672</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">17.5305213928223</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8786010742188</t>
+    <t xml:space="preserve">17.8786029815674</t>
   </si>
   <si>
     <t xml:space="preserve">18.1792144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1317501068115</t>
+    <t xml:space="preserve">18.1317481994629</t>
   </si>
   <si>
     <t xml:space="preserve">18.2583236694336</t>
@@ -2291,58 +2291,58 @@
     <t xml:space="preserve">18.3690757751465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2899684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2108612060547</t>
+    <t xml:space="preserve">18.289966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2108592987061</t>
   </si>
   <si>
     <t xml:space="preserve">17.3723030090332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4830589294434</t>
+    <t xml:space="preserve">17.4830570220947</t>
   </si>
   <si>
     <t xml:space="preserve">17.7045612335205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3248386383057</t>
+    <t xml:space="preserve">17.324836730957</t>
   </si>
   <si>
     <t xml:space="preserve">16.5021076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4988803863525</t>
+    <t xml:space="preserve">17.4988784790039</t>
   </si>
   <si>
     <t xml:space="preserve">17.1507987976074</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1701707839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0213165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8267726898193</t>
+    <t xml:space="preserve">11.1701717376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0213174819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8267736434937</t>
   </si>
   <si>
     <t xml:space="preserve">11.6210899353027</t>
   </si>
   <si>
-    <t xml:space="preserve">11.629002571106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.360032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9882202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4470500946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0245456695557</t>
+    <t xml:space="preserve">11.6290016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3600301742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9882211685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4470520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.02454662323</t>
   </si>
   <si>
     <t xml:space="preserve">12.0641002655029</t>
@@ -2351,22 +2351,22 @@
     <t xml:space="preserve">12.4200897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1748533248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9026546478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6969699859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4722394943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3140211105347</t>
+    <t xml:space="preserve">12.1748523712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9026536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6969709396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2190885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4722385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3140201568604</t>
   </si>
   <si>
     <t xml:space="preserve">13.2349109649658</t>
@@ -2378,49 +2378,49 @@
     <t xml:space="preserve">13.4089517593384</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4564161300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1004266738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0925149917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3614864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4326829910278</t>
+    <t xml:space="preserve">13.4564170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1004257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0925140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2507343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687828063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3614835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4326839447021</t>
   </si>
   <si>
     <t xml:space="preserve">13.5038814544678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9738521575928</t>
+    <t xml:space="preserve">12.9738531112671</t>
   </si>
   <si>
     <t xml:space="preserve">12.9342975616455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0371389389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1795358657837</t>
+    <t xml:space="preserve">13.0371398925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1795339584351</t>
   </si>
   <si>
     <t xml:space="preserve">13.2111787796021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5434370040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6225433349609</t>
+    <t xml:space="preserve">13.5434350967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6225442886353</t>
   </si>
   <si>
     <t xml:space="preserve">13.7095642089844</t>
@@ -2429,37 +2429,37 @@
     <t xml:space="preserve">14.2056894302368</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8418636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1560773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2883768081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0491018295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2475481033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2971620559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1240348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4134407043457</t>
+    <t xml:space="preserve">13.8418645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1560754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966451644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2883777618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0490999221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2475490570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2971611022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1240367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4134426116943</t>
   </si>
   <si>
     <t xml:space="preserve">16.5043964385986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1405754089355</t>
+    <t xml:space="preserve">16.1405735015869</t>
   </si>
   <si>
     <t xml:space="preserve">16.0909595489502</t>
@@ -2468,37 +2468,37 @@
     <t xml:space="preserve">16.190185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5865659713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2144746780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2806253433228</t>
+    <t xml:space="preserve">15.5865678787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286874771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3467741012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2144727706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2806243896484</t>
   </si>
   <si>
     <t xml:space="preserve">15.8346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6527185440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692543029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5782985687256</t>
+    <t xml:space="preserve">15.6527166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5782995223999</t>
   </si>
   <si>
     <t xml:space="preserve">15.7932872772217</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8594379425049</t>
+    <t xml:space="preserve">15.8594369888306</t>
   </si>
   <si>
     <t xml:space="preserve">15.3633108139038</t>
@@ -2507,25 +2507,25 @@
     <t xml:space="preserve">15.4294605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5617609024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8677043914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3307552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0501365661621</t>
+    <t xml:space="preserve">15.5617599487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8677053451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.330753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0501346588135</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">16.868221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9509086608887</t>
+    <t xml:space="preserve">16.8682231903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9509105682373</t>
   </si>
   <si>
     <t xml:space="preserve">17.1162853240967</t>
@@ -2537,16 +2537,16 @@
     <t xml:space="preserve">17.51318359375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7777824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2981948852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2816600799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3147354125977</t>
+    <t xml:space="preserve">17.7777805328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2981967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2816581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.314733505249</t>
   </si>
   <si>
     <t xml:space="preserve">17.4304962158203</t>
@@ -2555,10 +2555,10 @@
     <t xml:space="preserve">17.3643455505371</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3808822631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9839859008789</t>
+    <t xml:space="preserve">17.3808841705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9839839935303</t>
   </si>
   <si>
     <t xml:space="preserve">16.8186092376709</t>
@@ -2570,16 +2570,16 @@
     <t xml:space="preserve">16.8516845703125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7524585723877</t>
+    <t xml:space="preserve">16.752462387085</t>
   </si>
   <si>
     <t xml:space="preserve">17.0170593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4635696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5958690643311</t>
+    <t xml:space="preserve">17.4635715484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5958709716797</t>
   </si>
   <si>
     <t xml:space="preserve">17.4801082611084</t>
@@ -2591,22 +2591,22 @@
     <t xml:space="preserve">17.9266204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.992769241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0919933319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4227428436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4723567962646</t>
+    <t xml:space="preserve">17.9927673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0919952392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4227466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4723587036133</t>
   </si>
   <si>
     <t xml:space="preserve">18.1581439971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.025842666626</t>
+    <t xml:space="preserve">18.0258445739746</t>
   </si>
   <si>
     <t xml:space="preserve">18.0754585266113</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">18.5054302215576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3896713256836</t>
+    <t xml:space="preserve">18.389669418335</t>
   </si>
   <si>
     <t xml:space="preserve">18.2739067077637</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">18.191219329834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0589218139648</t>
+    <t xml:space="preserve">18.0589199066162</t>
   </si>
   <si>
     <t xml:space="preserve">17.9100818634033</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">17.7943210601807</t>
   </si>
   <si>
-    <t xml:space="preserve">17.711633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5793323516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.347806930542</t>
+    <t xml:space="preserve">17.7116317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5793342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3478088378906</t>
   </si>
   <si>
     <t xml:space="preserve">17.4966449737549</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">17.3974208831787</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7447071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6046581268311</t>
+    <t xml:space="preserve">17.7447090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6046562194824</t>
   </si>
   <si>
     <t xml:space="preserve">18.7700328826904</t>
@@ -2684,19 +2684,19 @@
     <t xml:space="preserve">18.4062061309814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1416072845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9431591033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1085319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9596977233887</t>
+    <t xml:space="preserve">18.1416091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9431571960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1085300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7281703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.95969581604</t>
   </si>
   <si>
     <t xml:space="preserve">17.1989707946777</t>
@@ -2708,13 +2708,13 @@
     <t xml:space="preserve">16.2894115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9503927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0413494110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5374717712402</t>
+    <t xml:space="preserve">15.9503917694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0413475036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5374736785889</t>
   </si>
   <si>
     <t xml:space="preserve">17.0832099914551</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">17.5627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0666694641113</t>
+    <t xml:space="preserve">17.06667137146</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155094146729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1658973693848</t>
+    <t xml:space="preserve">17.1658954620361</t>
   </si>
   <si>
     <t xml:space="preserve">17.0005207061768</t>
@@ -2738,16 +2738,16 @@
     <t xml:space="preserve">16.9178352355957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7028484344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8847618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7855319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6201591491699</t>
+    <t xml:space="preserve">16.7028465270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8847599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7855339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6201610565186</t>
   </si>
   <si>
     <t xml:space="preserve">16.4795913696289</t>
@@ -2756,19 +2756,19 @@
     <t xml:space="preserve">17.0335960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1328201293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1824340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1746826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8692569732666</t>
+    <t xml:space="preserve">17.1328220367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1824359893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.546257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1746807098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.869255065918</t>
   </si>
   <si>
     <t xml:space="preserve">19.1669311523438</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">20.0599536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9607257843018</t>
+    <t xml:space="preserve">19.9607276916504</t>
   </si>
   <si>
     <t xml:space="preserve">20.5064640045166</t>
@@ -2789,40 +2789,40 @@
     <t xml:space="preserve">20.6883792877197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7049160003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6718406677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8206768035889</t>
+    <t xml:space="preserve">20.7049179077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.671838760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8206787109375</t>
   </si>
   <si>
     <t xml:space="preserve">20.7545280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9364376068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7214527130127</t>
+    <t xml:space="preserve">20.9364414215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7214508056641</t>
   </si>
   <si>
     <t xml:space="preserve">21.0025882720947</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1845016479492</t>
+    <t xml:space="preserve">21.1845035552979</t>
   </si>
   <si>
     <t xml:space="preserve">21.6806240081787</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1767520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.994836807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5571136474609</t>
+    <t xml:space="preserve">22.1767501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9948387145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5571117401123</t>
   </si>
   <si>
     <t xml:space="preserve">21.2175769805908</t>
@@ -2834,46 +2834,46 @@
     <t xml:space="preserve">20.9529781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3002662658691</t>
+    <t xml:space="preserve">21.3002643585205</t>
   </si>
   <si>
     <t xml:space="preserve">21.5979385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4160251617432</t>
+    <t xml:space="preserve">21.4160270690918</t>
   </si>
   <si>
     <t xml:space="preserve">21.8956127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.515251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8459987640381</t>
+    <t xml:space="preserve">21.5152530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8460006713867</t>
   </si>
   <si>
     <t xml:space="preserve">22.160213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5317916870117</t>
+    <t xml:space="preserve">21.5317897796631</t>
   </si>
   <si>
     <t xml:space="preserve">21.3664150238037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7379894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5726146697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2506523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7876033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2584056854248</t>
+    <t xml:space="preserve">20.7379913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5726165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2506561279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7876014709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2584037780762</t>
   </si>
   <si>
     <t xml:space="preserve">19.6134414672852</t>
@@ -2882,43 +2882,43 @@
     <t xml:space="preserve">20.192253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3323040008545</t>
+    <t xml:space="preserve">19.3323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">18.9354038238525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2749423980713</t>
+    <t xml:space="preserve">20.2749404907227</t>
   </si>
   <si>
     <t xml:space="preserve">21.2010402679443</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9860496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4656391143799</t>
+    <t xml:space="preserve">20.9860534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4656372070312</t>
   </si>
   <si>
     <t xml:space="preserve">20.0103416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2253284454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3410911560059</t>
+    <t xml:space="preserve">19.6465167999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2253265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3410892486572</t>
   </si>
   <si>
     <t xml:space="preserve">20.5560779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6387634277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0356636047363</t>
+    <t xml:space="preserve">20.638765335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.035665512085</t>
   </si>
   <si>
     <t xml:space="preserve">21.34987449646</t>
@@ -2927,16 +2927,16 @@
     <t xml:space="preserve">21.085277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0191287994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.870288848877</t>
+    <t xml:space="preserve">21.0191268920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8702907562256</t>
   </si>
   <si>
     <t xml:space="preserve">21.1018161773682</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8868293762207</t>
+    <t xml:space="preserve">20.8868274688721</t>
   </si>
   <si>
     <t xml:space="preserve">20.5230026245117</t>
@@ -2951,25 +2951,25 @@
     <t xml:space="preserve">20.1095676422119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1514263153076</t>
+    <t xml:space="preserve">21.1514282226562</t>
   </si>
   <si>
     <t xml:space="preserve">20.6222305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3080139160156</t>
+    <t xml:space="preserve">20.3080177307129</t>
   </si>
   <si>
     <t xml:space="preserve">20.4072399139404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9772663116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3907032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1261005401611</t>
+    <t xml:space="preserve">19.9772682189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3907012939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1261024475098</t>
   </si>
   <si>
     <t xml:space="preserve">20.0764923095703</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">21.3314075469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0756340026855</t>
+    <t xml:space="preserve">21.0756359100342</t>
   </si>
   <si>
     <t xml:space="preserve">21.2461490631104</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">21.229097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1779441833496</t>
+    <t xml:space="preserve">21.177942276001</t>
   </si>
   <si>
     <t xml:space="preserve">21.4337158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4848709106445</t>
+    <t xml:space="preserve">21.4848728179932</t>
   </si>
   <si>
     <t xml:space="preserve">21.6042308807373</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">21.3143558502197</t>
   </si>
   <si>
-    <t xml:space="preserve">21.570125579834</t>
+    <t xml:space="preserve">21.5701274871826</t>
   </si>
   <si>
     <t xml:space="preserve">22.388599395752</t>
@@ -3032,34 +3032,34 @@
     <t xml:space="preserve">22.0646190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.030517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7235908508301</t>
+    <t xml:space="preserve">22.0305194854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7235889434814</t>
   </si>
   <si>
     <t xml:space="preserve">21.6553840637207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7406425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3655090332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4507675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6724376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0987224578857</t>
+    <t xml:space="preserve">21.7406406402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3655071258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4507656097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.672435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0987243652344</t>
   </si>
   <si>
     <t xml:space="preserve">21.7917957305908</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9964141845703</t>
+    <t xml:space="preserve">21.9964122772217</t>
   </si>
   <si>
     <t xml:space="preserve">21.3825607299805</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">20.8369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8710155487061</t>
+    <t xml:space="preserve">20.8710174560547</t>
   </si>
   <si>
     <t xml:space="preserve">20.888069152832</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">22.1328258514404</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2351341247559</t>
+    <t xml:space="preserve">22.2351360321045</t>
   </si>
   <si>
     <t xml:space="preserve">22.47385597229</t>
@@ -3095,16 +3095,16 @@
     <t xml:space="preserve">20.7346057891846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5470390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2632026672363</t>
+    <t xml:space="preserve">20.5470371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2632007598877</t>
   </si>
   <si>
     <t xml:space="preserve">21.1097373962402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1608905792236</t>
+    <t xml:space="preserve">21.1608924865723</t>
   </si>
   <si>
     <t xml:space="preserve">21.5530776977539</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">21.2973022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0926876068115</t>
+    <t xml:space="preserve">21.0926837921143</t>
   </si>
   <si>
     <t xml:space="preserve">20.8539638519287</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">21.0074291229248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2802505493164</t>
+    <t xml:space="preserve">21.280252456665</t>
   </si>
   <si>
     <t xml:space="preserve">21.9282073974609</t>
@@ -3137,19 +3137,19 @@
     <t xml:space="preserve">21.8088474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8941078186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7576942443848</t>
+    <t xml:space="preserve">21.8941059112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7576961517334</t>
   </si>
   <si>
     <t xml:space="preserve">21.3996124267578</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9111576080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5079574584961</t>
+    <t xml:space="preserve">21.9111595153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5079593658447</t>
   </si>
   <si>
     <t xml:space="preserve">22.1669292449951</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">22.013463973999</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4909076690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4227027893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2521858215332</t>
+    <t xml:space="preserve">22.4909057617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.422700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2521877288818</t>
   </si>
   <si>
     <t xml:space="preserve">22.5761642456055</t>
@@ -3176,19 +3176,19 @@
     <t xml:space="preserve">22.6614227294922</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7296276092529</t>
+    <t xml:space="preserve">22.7296295166016</t>
   </si>
   <si>
     <t xml:space="preserve">23.172966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7697677612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4628429412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3775863647461</t>
+    <t xml:space="preserve">23.7697696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4628410339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3775844573975</t>
   </si>
   <si>
     <t xml:space="preserve">23.9232330322266</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">25.219144821167</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4749164581299</t>
+    <t xml:space="preserve">25.4749183654785</t>
   </si>
   <si>
     <t xml:space="preserve">25.8329982757568</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">26.6003150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6173648834229</t>
+    <t xml:space="preserve">26.6173667907715</t>
   </si>
   <si>
     <t xml:space="preserve">26.7708301544189</t>
@@ -3227,28 +3227,28 @@
     <t xml:space="preserve">25.969409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7196750640869</t>
+    <t xml:space="preserve">26.7196769714355</t>
   </si>
   <si>
     <t xml:space="preserve">26.3615951538086</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3104419708252</t>
+    <t xml:space="preserve">26.3104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">26.5491600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2251834869385</t>
+    <t xml:space="preserve">26.2251815795898</t>
   </si>
   <si>
     <t xml:space="preserve">25.5431232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0315799713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8269596099854</t>
+    <t xml:space="preserve">25.0315780639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.826961517334</t>
   </si>
   <si>
     <t xml:space="preserve">25.0145282745361</t>
@@ -3257,31 +3257,31 @@
     <t xml:space="preserve">25.1679916381836</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1168346405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8099117279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8440113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1338882446289</t>
+    <t xml:space="preserve">25.1168365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8099098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8440132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1338863372803</t>
   </si>
   <si>
     <t xml:space="preserve">24.7246532440186</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7587566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3896598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3836212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1790046691895</t>
+    <t xml:space="preserve">24.7587547302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3896617889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3836231231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1790065765381</t>
   </si>
   <si>
     <t xml:space="preserve">24.3324680328369</t>
@@ -3293,40 +3293,40 @@
     <t xml:space="preserve">24.1960563659668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3495197296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1449012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1107978820801</t>
+    <t xml:space="preserve">24.3495178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9402828216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1448993682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1107997894287</t>
   </si>
   <si>
     <t xml:space="preserve">23.8038711547852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.417724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4518280029297</t>
+    <t xml:space="preserve">24.4177227020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4518299102783</t>
   </si>
   <si>
     <t xml:space="preserve">24.2131061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3665733337402</t>
+    <t xml:space="preserve">24.3665714263916</t>
   </si>
   <si>
     <t xml:space="preserve">24.2472114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2813129425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0486278533936</t>
+    <t xml:space="preserve">24.2813110351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0486297607422</t>
   </si>
   <si>
     <t xml:space="preserve">24.4347763061523</t>
@@ -3338,13 +3338,13 @@
     <t xml:space="preserve">23.4969463348389</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9342460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7978324890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6443710327148</t>
+    <t xml:space="preserve">22.9342479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7978343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6443691253662</t>
   </si>
   <si>
     <t xml:space="preserve">22.3033409118652</t>
@@ -3356,25 +3356,25 @@
     <t xml:space="preserve">21.5189723968506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8429508209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1839809417725</t>
+    <t xml:space="preserve">21.8429527282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1839828491211</t>
   </si>
   <si>
     <t xml:space="preserve">21.1949939727783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6383304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2120456695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9051208496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6663990020752</t>
+    <t xml:space="preserve">21.638334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2120475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9051189422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6664009094238</t>
   </si>
   <si>
     <t xml:space="preserve">21.4678173065186</t>
@@ -3383,7 +3383,7 @@
     <t xml:space="preserve">21.0244789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5640926361084</t>
+    <t xml:space="preserve">20.5640907287598</t>
   </si>
   <si>
     <t xml:space="preserve">20.9221706390381</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">20.2912654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1378021240234</t>
+    <t xml:space="preserve">20.1378040313721</t>
   </si>
   <si>
     <t xml:space="preserve">22.6273193359375</t>
@@ -3404,37 +3404,37 @@
     <t xml:space="preserve">24.0937480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.616304397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7637329101562</t>
+    <t xml:space="preserve">23.6163063049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7637310028076</t>
   </si>
   <si>
     <t xml:space="preserve">22.8148860931396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6102695465088</t>
+    <t xml:space="preserve">22.6102676391602</t>
   </si>
   <si>
     <t xml:space="preserve">24.1619529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">25.560173034668</t>
+    <t xml:space="preserve">25.5601749420166</t>
   </si>
   <si>
     <t xml:space="preserve">24.9292697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8951683044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3154182434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2873497009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7136363983154</t>
+    <t xml:space="preserve">24.8951663970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3154163360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2873516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7136383056641</t>
   </si>
   <si>
     <t xml:space="preserve">24.6564464569092</t>
@@ -3443,37 +3443,37 @@
     <t xml:space="preserve">25.1850433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9804248809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6624851226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3786449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2933902740479</t>
+    <t xml:space="preserve">24.9804229736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.662483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3786468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2933883666992</t>
   </si>
   <si>
     <t xml:space="preserve">26.8049335479736</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7537803649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9413471221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0436515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0948085784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8219833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9924983978271</t>
+    <t xml:space="preserve">26.753776550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9413452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0436534881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0948104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.821985244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9925003051758</t>
   </si>
   <si>
     <t xml:space="preserve">27.1459617614746</t>
@@ -3485,43 +3485,43 @@
     <t xml:space="preserve">27.5040416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4699420928955</t>
+    <t xml:space="preserve">27.4699401855469</t>
   </si>
   <si>
     <t xml:space="preserve">27.6916103363037</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7939186096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8621234893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0496940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5893020629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1800670623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2823753356934</t>
+    <t xml:space="preserve">27.7939205169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8621273040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0496921539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5893039703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2823734283447</t>
   </si>
   <si>
     <t xml:space="preserve">26.856086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6514701843262</t>
+    <t xml:space="preserve">26.6514682769775</t>
   </si>
   <si>
     <t xml:space="preserve">25.3555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3214530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9864597320557</t>
+    <t xml:space="preserve">25.3214550018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9864616394043</t>
   </si>
   <si>
     <t xml:space="preserve">25.3385047912598</t>
@@ -3533,37 +3533,37 @@
     <t xml:space="preserve">27.7598171234131</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4759788513184</t>
+    <t xml:space="preserve">28.475980758667</t>
   </si>
   <si>
     <t xml:space="preserve">28.5100803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6976509094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9875240325928</t>
+    <t xml:space="preserve">28.6976490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9875221252441</t>
   </si>
   <si>
     <t xml:space="preserve">29.4604301452637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4954605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5655193328857</t>
+    <t xml:space="preserve">29.4954624176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5655212402344</t>
   </si>
   <si>
     <t xml:space="preserve">28.724796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6197052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3394641876221</t>
+    <t xml:space="preserve">28.6197071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3394660949707</t>
   </si>
   <si>
     <t xml:space="preserve">28.1993446350098</t>
@@ -3572,19 +3572,19 @@
     <t xml:space="preserve">28.3044338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9524936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8824329376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0575828552246</t>
+    <t xml:space="preserve">28.9524955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8824310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0575847625732</t>
   </si>
   <si>
     <t xml:space="preserve">29.1451568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">27.043342590332</t>
+    <t xml:space="preserve">27.0433444976807</t>
   </si>
   <si>
     <t xml:space="preserve">26.6229820251465</t>
@@ -3596,19 +3596,19 @@
     <t xml:space="preserve">26.8681926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">26.009952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9924392700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.957405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.607105255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5178928375244</t>
+    <t xml:space="preserve">26.0099544525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9924373626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9574069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6071033477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5178909301758</t>
   </si>
   <si>
     <t xml:space="preserve">26.255163192749</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">26.6054649353027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8873462677002</t>
+    <t xml:space="preserve">25.8873481750488</t>
   </si>
   <si>
     <t xml:space="preserve">26.4653453826904</t>
@@ -3629,10 +3629,10 @@
     <t xml:space="preserve">26.1675891876221</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9382553100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9732837677002</t>
+    <t xml:space="preserve">26.93825340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9732856750488</t>
   </si>
   <si>
     <t xml:space="preserve">27.1309204101562</t>
@@ -3641,10 +3641,10 @@
     <t xml:space="preserve">27.4286785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">27.341100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7455902099609</t>
+    <t xml:space="preserve">27.3411026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7455883026123</t>
   </si>
   <si>
     <t xml:space="preserve">26.9907989501953</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">27.6563739776611</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5687980651855</t>
+    <t xml:space="preserve">27.5687999725342</t>
   </si>
   <si>
     <t xml:space="preserve">26.7280731201172</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">25.7822570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3602561950684</t>
+    <t xml:space="preserve">26.3602542877197</t>
   </si>
   <si>
     <t xml:space="preserve">26.6930408477783</t>
@@ -3674,10 +3674,10 @@
     <t xml:space="preserve">27.1834678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5512828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.884069442749</t>
+    <t xml:space="preserve">27.5512847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8840713500977</t>
   </si>
   <si>
     <t xml:space="preserve">28.1467971801758</t>
@@ -3695,10 +3695,10 @@
     <t xml:space="preserve">29.6706123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6530990600586</t>
+    <t xml:space="preserve">29.7757015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.65309715271</t>
   </si>
   <si>
     <t xml:space="preserve">29.2327365875244</t>
@@ -3707,28 +3707,28 @@
     <t xml:space="preserve">30.4062480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1260070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3186702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8632755279541</t>
+    <t xml:space="preserve">30.1260051727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3186721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8632793426514</t>
   </si>
   <si>
     <t xml:space="preserve">29.950855255127</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4412784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.15940284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3361873626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1785526275635</t>
+    <t xml:space="preserve">30.4412746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1593990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3361854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1785488128662</t>
   </si>
   <si>
     <t xml:space="preserve">29.7406730651855</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">27.7089195251465</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4987373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0258312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1851024627686</t>
+    <t xml:space="preserve">27.4987392425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0258293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1851043701172</t>
   </si>
   <si>
     <t xml:space="preserve">26.4478321075439</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">27.8490409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2694034576416</t>
+    <t xml:space="preserve">28.269401550293</t>
   </si>
   <si>
     <t xml:space="preserve">28.1643142700195</t>
@@ -3770,19 +3770,19 @@
     <t xml:space="preserve">29.0926151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7598285675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8665542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.169225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.064136505127</t>
+    <t xml:space="preserve">28.7598266601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1801891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8665561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1692276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0641384124756</t>
   </si>
   <si>
     <t xml:space="preserve">24.5912284851074</t>
@@ -3791,10 +3791,10 @@
     <t xml:space="preserve">24.7488651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2726802825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1659507751465</t>
+    <t xml:space="preserve">26.2726783752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1659526824951</t>
   </si>
   <si>
     <t xml:space="preserve">25.0816516876221</t>
@@ -3806,22 +3806,22 @@
     <t xml:space="preserve">24.4335918426514</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1708660125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9781970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.838077545166</t>
+    <t xml:space="preserve">24.1708679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.978199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8380794525146</t>
   </si>
   <si>
     <t xml:space="preserve">24.9065017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5545616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7472267150879</t>
+    <t xml:space="preserve">25.5545597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7472248077393</t>
   </si>
   <si>
     <t xml:space="preserve">25.6946811676025</t>
@@ -3848,16 +3848,16 @@
     <t xml:space="preserve">27.2535285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.936616897583</t>
+    <t xml:space="preserve">27.48122215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9366149902344</t>
   </si>
   <si>
     <t xml:space="preserve">28.8649158477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7631034851074</t>
+    <t xml:space="preserve">26.7631015777588</t>
   </si>
   <si>
     <t xml:space="preserve">26.9032230377197</t>
@@ -3866,37 +3866,37 @@
     <t xml:space="preserve">26.0274677276611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3952865600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8331642150879</t>
+    <t xml:space="preserve">26.39528465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8331623077393</t>
   </si>
   <si>
     <t xml:space="preserve">26.307710647583</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9223785400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3777713775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5003757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1325569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0975284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5354061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8857097625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2376499176025</t>
+    <t xml:space="preserve">25.9223766326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3777694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5003776550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1325588226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.097526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5354042053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8857078552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2376480102539</t>
   </si>
   <si>
     <t xml:space="preserve">25.7647399902344</t>
@@ -3905,10 +3905,10 @@
     <t xml:space="preserve">25.8348026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2201347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4144382476807</t>
+    <t xml:space="preserve">26.2201328277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4144401550293</t>
   </si>
   <si>
     <t xml:space="preserve">25.466983795166</t>
@@ -3938,22 +3938,22 @@
     <t xml:space="preserve">24.2409267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3285007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7838935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8539562225342</t>
+    <t xml:space="preserve">24.3285026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7838954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8539543151855</t>
   </si>
   <si>
     <t xml:space="preserve">24.3109874725342</t>
   </si>
   <si>
-    <t xml:space="preserve">24.22340965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3460159301758</t>
+    <t xml:space="preserve">24.2234115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3460178375244</t>
   </si>
   <si>
     <t xml:space="preserve">24.4160766601562</t>
@@ -3962,22 +3962,22 @@
     <t xml:space="preserve">24.3985633850098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6788024902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9590454101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0466194152832</t>
+    <t xml:space="preserve">24.678804397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9590473175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0466213226318</t>
   </si>
   <si>
     <t xml:space="preserve">24.7138328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5036506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6612892150879</t>
+    <t xml:space="preserve">24.5036525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6612873077393</t>
   </si>
   <si>
     <t xml:space="preserve">24.2759552001953</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">24.2058944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.188383102417</t>
+    <t xml:space="preserve">24.1883811950684</t>
   </si>
   <si>
     <t xml:space="preserve">23.7329883575439</t>
@@ -3998,10 +3998,10 @@
     <t xml:space="preserve">23.9957141876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0307445526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8731079101562</t>
+    <t xml:space="preserve">24.0307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8731098175049</t>
   </si>
   <si>
     <t xml:space="preserve">23.3476543426514</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">23.5052909851074</t>
   </si>
   <si>
-    <t xml:space="preserve">23.049898147583</t>
+    <t xml:space="preserve">23.0498962402344</t>
   </si>
   <si>
     <t xml:space="preserve">22.8747463226318</t>
@@ -4028,13 +4028,13 @@
     <t xml:space="preserve">23.1900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2425632476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6979560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5578365325928</t>
+    <t xml:space="preserve">23.2425651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6979579925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5578384399414</t>
   </si>
   <si>
     <t xml:space="preserve">23.9256534576416</t>
@@ -4049,49 +4049,49 @@
     <t xml:space="preserve">23.0849285125732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3826866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5228061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9606838226318</t>
+    <t xml:space="preserve">23.3826847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5228080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9606857299805</t>
   </si>
   <si>
     <t xml:space="preserve">24.4861373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2584400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1166820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2217712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2042598724365</t>
+    <t xml:space="preserve">24.2584419250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1166839599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.221773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2042579650879</t>
   </si>
   <si>
     <t xml:space="preserve">25.1341972351074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6262588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3635330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7855319976807</t>
+    <t xml:space="preserve">24.6262607574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3635311126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7855339050293</t>
   </si>
   <si>
     <t xml:space="preserve">23.2250499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9798374176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2775955200195</t>
+    <t xml:space="preserve">22.9798355102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2775917053223</t>
   </si>
   <si>
     <t xml:space="preserve">23.295108795166</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">24.0657749176025</t>
   </si>
   <si>
-    <t xml:space="preserve">24.76637840271</t>
+    <t xml:space="preserve">24.7663803100586</t>
   </si>
   <si>
     <t xml:space="preserve">24.7313499450684</t>
@@ -5421,6 +5421,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.4200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1399993896484</t>
   </si>
 </sst>
 </file>
@@ -70421,7 +70424,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6504166667</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>193928</v>
@@ -70442,6 +70445,32 @@
         <v>1800</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493865741</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>353254</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>22.1399993896484</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1803</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="1805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="1806">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48755359649658</t>
+    <t xml:space="preserve">7.4875545501709</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">7.43893384933472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23837518692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0438928604126</t>
+    <t xml:space="preserve">7.23837471008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04389333724976</t>
   </si>
   <si>
     <t xml:space="preserve">6.99527215957642</t>
@@ -59,25 +59,25 @@
     <t xml:space="preserve">7.06212520599365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25053024291992</t>
+    <t xml:space="preserve">7.25052976608276</t>
   </si>
   <si>
     <t xml:space="preserve">7.22014188766479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17152309417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07428121566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84941101074219</t>
+    <t xml:space="preserve">7.17152214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07428073883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84941053390503</t>
   </si>
   <si>
     <t xml:space="preserve">7.01350450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75216865539551</t>
+    <t xml:space="preserve">6.75216960906982</t>
   </si>
   <si>
     <t xml:space="preserve">6.83725547790527</t>
@@ -86,64 +86,64 @@
     <t xml:space="preserve">6.9709620475769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09251260757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00742673873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00134992599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98919486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92841768264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8615665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53337669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47867965698242</t>
+    <t xml:space="preserve">7.09251308441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00742864608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00135040283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98919534683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92841863632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86156511306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5333776473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47867870330811</t>
   </si>
   <si>
     <t xml:space="preserve">6.61238527297974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55160999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77647972106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94057369232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87372255325317</t>
+    <t xml:space="preserve">6.55161046981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77647924423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94057416915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87372064590454</t>
   </si>
   <si>
     <t xml:space="preserve">6.63061857223511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78863525390625</t>
+    <t xml:space="preserve">6.78863382339478</t>
   </si>
   <si>
     <t xml:space="preserve">6.58199834823608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70354890823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71570444107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80686712265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91626405715942</t>
+    <t xml:space="preserve">6.70354843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71570491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8068675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91626310348511</t>
   </si>
   <si>
     <t xml:space="preserve">6.84333324432373</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">6.83117723464966</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70962619781494</t>
+    <t xml:space="preserve">6.879798412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70962572097778</t>
   </si>
   <si>
     <t xml:space="preserve">6.74609184265137</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85548877716064</t>
+    <t xml:space="preserve">6.85548782348633</t>
   </si>
   <si>
     <t xml:space="preserve">6.8676438331604</t>
@@ -170,115 +170,115 @@
     <t xml:space="preserve">6.95272922515869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04997062683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27484035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35992622375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34777069091797</t>
+    <t xml:space="preserve">7.0499701499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27484083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35992574691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34777021408081</t>
   </si>
   <si>
     <t xml:space="preserve">7.26876258850098</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22621965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11074542999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03173780441284</t>
+    <t xml:space="preserve">7.22622013092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11074590682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03173732757568</t>
   </si>
   <si>
     <t xml:space="preserve">7.08035850524902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0560474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975305557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23229646682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15328931808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11682271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16544485092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95880651473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93449544906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803075790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90410757064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96488428115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79471302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7643256187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14113330841064</t>
+    <t xml:space="preserve">7.05604696273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975353240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23229789733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15328884124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11682319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16544437408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95880603790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93449735641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803171157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90410947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96488523483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79471254348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76432418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14113426208496</t>
   </si>
   <si>
     <t xml:space="preserve">7.02566003799438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15738582611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13741254806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31052112579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25725603103638</t>
+    <t xml:space="preserve">7.15738677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1374135017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31052207946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25725650787354</t>
   </si>
   <si>
     <t xml:space="preserve">7.34381103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38376092910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29720497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25059938430786</t>
+    <t xml:space="preserve">7.38375997543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29720544815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25059986114502</t>
   </si>
   <si>
     <t xml:space="preserve">7.21730899810791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23062562942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23728322982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27723169326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22396850585938</t>
+    <t xml:space="preserve">7.23062515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23728275299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27723121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2239670753479</t>
   </si>
   <si>
     <t xml:space="preserve">7.10412263870239</t>
@@ -287,97 +287,97 @@
     <t xml:space="preserve">6.85777568817139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65803480148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60477066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47493886947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50822925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95764541625977</t>
+    <t xml:space="preserve">6.658034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60477018356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.474937915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50822734832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95764589309692</t>
   </si>
   <si>
     <t xml:space="preserve">6.93767166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82448530197144</t>
+    <t xml:space="preserve">6.82448577880859</t>
   </si>
   <si>
     <t xml:space="preserve">6.88440704345703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47826814651489</t>
+    <t xml:space="preserve">6.47826766967773</t>
   </si>
   <si>
     <t xml:space="preserve">6.32180309295654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56149244308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69132566452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81782722473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91769742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03754186630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78453636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50489950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61808490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71795701980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68466758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73793172836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87774896621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81116962432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7512469291687</t>
+    <t xml:space="preserve">6.56149291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69132471084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81782627105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91769886016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03754138946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78453683853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5048999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61808586120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71795606613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68466663360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73793077468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8777494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81116819381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75124740600586</t>
   </si>
   <si>
     <t xml:space="preserve">6.79119396209717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76456260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86443376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77122116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89106512069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73127317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64471817016602</t>
+    <t xml:space="preserve">6.76456308364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86443281173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77122068405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89106559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73127222061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64471769332886</t>
   </si>
   <si>
     <t xml:space="preserve">6.63806104660034</t>
@@ -386,34 +386,34 @@
     <t xml:space="preserve">6.75790452957153</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83114290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80451059341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101406097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96430397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74458885192871</t>
+    <t xml:space="preserve">6.83114242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80451202392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101358413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96430349349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74458837509155</t>
   </si>
   <si>
     <t xml:space="preserve">6.71129846572876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65137624740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62807273864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64139080047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62141418457031</t>
+    <t xml:space="preserve">6.65137577056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62807321548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64138889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62141370773315</t>
   </si>
   <si>
     <t xml:space="preserve">7.01756858825684</t>
@@ -422,46 +422,46 @@
     <t xml:space="preserve">6.98427772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01090955734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04420042037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17070245742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87109088897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92435550689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83780097961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84445905685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79785346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77787923812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59811115264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55150556564331</t>
+    <t xml:space="preserve">7.01090908050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04419994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17070293426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87109136581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92435503005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97762012481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83780193328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84445953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79785299301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7778787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59811210632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55150699615479</t>
   </si>
   <si>
     <t xml:space="preserve">6.7246150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67135047912598</t>
+    <t xml:space="preserve">6.67135000228882</t>
   </si>
   <si>
     <t xml:space="preserve">6.66469287872314</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">6.60809898376465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54484796524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45829343795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65470552444458</t>
+    <t xml:space="preserve">6.54484701156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45829296112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65470457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.67800807952881</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">6.13870716094971</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22859001159668</t>
+    <t xml:space="preserve">6.22859048843384</t>
   </si>
   <si>
     <t xml:space="preserve">6.19197177886963</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">6.17865562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24856472015381</t>
+    <t xml:space="preserve">6.24856567382812</t>
   </si>
   <si>
     <t xml:space="preserve">6.13537883758545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06546831130981</t>
+    <t xml:space="preserve">6.06546878814697</t>
   </si>
   <si>
     <t xml:space="preserve">6.16866827011108</t>
@@ -512,220 +512,220 @@
     <t xml:space="preserve">6.15868139266968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14203691482544</t>
+    <t xml:space="preserve">6.1420373916626</t>
   </si>
   <si>
     <t xml:space="preserve">6.0621395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03883647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10874700546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881023406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02219152450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01886224746704</t>
+    <t xml:space="preserve">6.03883600234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10874652862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881071090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02219200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0188627243042</t>
   </si>
   <si>
     <t xml:space="preserve">6.11873292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2319188117981</t>
+    <t xml:space="preserve">6.23191976547241</t>
   </si>
   <si>
     <t xml:space="preserve">6.12206220626831</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22193336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21860408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35842227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37839651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62474393844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70464086532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8511176109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69798278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90438175201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89772367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99093580245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07748937606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91103935241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07083225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13075399398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15072917938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18401908874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0974645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05085849761963</t>
+    <t xml:space="preserve">6.22193288803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21860361099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35842275619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37839698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62474489212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70463991165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85111713409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69798231124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.904381275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89772319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99093627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07749080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91103982925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07083177566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1307544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15072870254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1840181350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09746360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05085754394531</t>
   </si>
   <si>
     <t xml:space="preserve">7.35046911239624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27057266235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28388929367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30386352539062</t>
+    <t xml:space="preserve">7.27057313919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28388977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30386304855347</t>
   </si>
   <si>
     <t xml:space="preserve">7.53023672103882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32383728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31717872619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36378574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51691961288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59015798568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347318649292</t>
+    <t xml:space="preserve">7.3238377571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31717920303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36378526687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51692008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59015941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347461700439</t>
   </si>
   <si>
     <t xml:space="preserve">7.71000289916992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76992607116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77658367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7366361618042</t>
+    <t xml:space="preserve">7.76992559432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77658462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73663568496704</t>
   </si>
   <si>
     <t xml:space="preserve">7.7898998260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75660943984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8231897354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85647964477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86979579925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8764533996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96966648101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94969272613525</t>
+    <t xml:space="preserve">7.75660991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82319068908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85648059844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86979532241821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87645435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308713912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96966743469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9496922492981</t>
   </si>
   <si>
     <t xml:space="preserve">7.92306137084961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96300888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72331953048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62344789505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54355239868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47031497955322</t>
+    <t xml:space="preserve">7.96300935745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311243057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72332000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62344837188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5435528755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47031402587891</t>
   </si>
   <si>
     <t xml:space="preserve">7.63676595687866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56352615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018423080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74329423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80321598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89642810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94303512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84982299804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06953620910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20842742919922</t>
+    <t xml:space="preserve">7.56352758407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018566131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74329471588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80321741104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89642858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94303607940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84982252120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06953811645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2084264755249</t>
   </si>
   <si>
     <t xml:space="preserve">8.25009441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22926044464111</t>
+    <t xml:space="preserve">8.22926235198975</t>
   </si>
   <si>
     <t xml:space="preserve">8.31953907012939</t>
@@ -737,118 +737,118 @@
     <t xml:space="preserve">8.28481864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29870700836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37509536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34731960296631</t>
+    <t xml:space="preserve">8.29870510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37509632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34731864929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.3889856338501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43759727478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4514856338501</t>
+    <t xml:space="preserve">8.43759632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45148658752441</t>
   </si>
   <si>
     <t xml:space="preserve">8.68760013580322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73621082305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62509822845459</t>
+    <t xml:space="preserve">8.7362117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62509918212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.63898849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66676616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68065547943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59732151031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69454479217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61120891571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50704193115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59037685394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52787494659424</t>
+    <t xml:space="preserve">8.66676425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68065643310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59732246398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72926616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69454383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61120986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50704288482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59037494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52787590026855</t>
   </si>
   <si>
     <t xml:space="preserve">8.54870986938477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4931526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51398754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46537494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47231864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61815452575684</t>
+    <t xml:space="preserve">8.49315357208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51398658752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46537590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47231960296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61815357208252</t>
   </si>
   <si>
     <t xml:space="preserve">8.65982246398926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64593315124512</t>
+    <t xml:space="preserve">8.6459321975708</t>
   </si>
   <si>
     <t xml:space="preserve">8.40981864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43065166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42370700836182</t>
+    <t xml:space="preserve">8.4306526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42370891571045</t>
   </si>
   <si>
     <t xml:space="preserve">8.30565166473389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54176330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57648754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60426425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88204574584961</t>
+    <t xml:space="preserve">8.54176425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57648849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60426616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71537780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88204669952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.00010299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15288162231445</t>
+    <t xml:space="preserve">9.15288257598877</t>
   </si>
   <si>
     <t xml:space="preserve">9.13204860687256</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">9.06954956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09038257598877</t>
+    <t xml:space="preserve">9.09038162231445</t>
   </si>
   <si>
     <t xml:space="preserve">9.00704765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95843601226807</t>
+    <t xml:space="preserve">8.95843505859375</t>
   </si>
   <si>
     <t xml:space="preserve">9.06260395050049</t>
@@ -884,16 +884,16 @@
     <t xml:space="preserve">9.36816310882568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41677570343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32649612426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29177474975586</t>
+    <t xml:space="preserve">9.40983104705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41677665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32649707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29177379608154</t>
   </si>
   <si>
     <t xml:space="preserve">9.31260776519775</t>
@@ -905,37 +905,37 @@
     <t xml:space="preserve">9.47233200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43760871887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44455337524414</t>
+    <t xml:space="preserve">9.4376106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44455242156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.40288543701172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38899707794189</t>
+    <t xml:space="preserve">9.38899898529053</t>
   </si>
   <si>
     <t xml:space="preserve">9.38205242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3403844833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34732913970947</t>
+    <t xml:space="preserve">9.34038639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34733009338379</t>
   </si>
   <si>
     <t xml:space="preserve">9.31955146789551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48621940612793</t>
+    <t xml:space="preserve">9.48622035980225</t>
   </si>
   <si>
     <t xml:space="preserve">9.75011253356934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79178142547607</t>
+    <t xml:space="preserve">9.79177951812744</t>
   </si>
   <si>
     <t xml:space="preserve">9.7778902053833</t>
@@ -947,64 +947,64 @@
     <t xml:space="preserve">9.72927856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77094650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76400089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74316787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96539211273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0278921127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93761444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0834503173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1181707382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1876182556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4445648193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5001201629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5695667266846</t>
+    <t xml:space="preserve">9.77094554901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76400279998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74316692352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96539306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0278930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9376163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0834493637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1181726455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1876173019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4445638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5001211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5695648193359</t>
   </si>
   <si>
     <t xml:space="preserve">10.229284286499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3959541320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.423731803894</t>
+    <t xml:space="preserve">10.3959522247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4237298965454</t>
   </si>
   <si>
     <t xml:space="preserve">10.5903997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4931755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5626211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6251239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6042900085449</t>
+    <t xml:space="preserve">10.4931764602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5626220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6251220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6042890548706</t>
   </si>
   <si>
     <t xml:space="preserve">10.7015113830566</t>
@@ -1016,19 +1016,19 @@
     <t xml:space="preserve">10.8542919158936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8334589004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9029026031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0904054641724</t>
+    <t xml:space="preserve">10.8334579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9029035568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0904064178467</t>
   </si>
   <si>
     <t xml:space="preserve">11.1042947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1112394332886</t>
+    <t xml:space="preserve">11.1112384796143</t>
   </si>
   <si>
     <t xml:space="preserve">10.6667900085449</t>
@@ -1043,37 +1043,37 @@
     <t xml:space="preserve">11.0765161514282</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3473539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3959646224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1529054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0626268386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.215407371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3126316070557</t>
+    <t xml:space="preserve">11.3473529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3959636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1529064178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0626277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2154064178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3126306533813</t>
   </si>
   <si>
     <t xml:space="preserve">11.2362413406372</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2084617614746</t>
+    <t xml:space="preserve">11.2084608078003</t>
   </si>
   <si>
     <t xml:space="preserve">10.9098482131958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.736234664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8751258850098</t>
+    <t xml:space="preserve">10.7362337112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8751249313354</t>
   </si>
   <si>
     <t xml:space="preserve">10.6945667266846</t>
@@ -1082,34 +1082,34 @@
     <t xml:space="preserve">10.548731803894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7848472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8612356185913</t>
+    <t xml:space="preserve">10.7848463058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8612375259399</t>
   </si>
   <si>
     <t xml:space="preserve">11.0695714950562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.187629699707</t>
+    <t xml:space="preserve">11.1876287460327</t>
   </si>
   <si>
     <t xml:space="preserve">10.9306812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1598510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4515209197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5001335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4931869506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6251335144043</t>
+    <t xml:space="preserve">11.1598491668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4515190124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.50013256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4931859970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.62513256073</t>
   </si>
   <si>
     <t xml:space="preserve">11.7223558425903</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">11.7015237808228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.729302406311</t>
+    <t xml:space="preserve">11.7293014526367</t>
   </si>
   <si>
     <t xml:space="preserve">11.7154130935669</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">11.6112451553345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4862451553345</t>
+    <t xml:space="preserve">11.4862442016602</t>
   </si>
   <si>
     <t xml:space="preserve">11.5765218734741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6806898117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3820753097534</t>
+    <t xml:space="preserve">11.6806888580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3820762634277</t>
   </si>
   <si>
     <t xml:space="preserve">10.8681802749634</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">10.8959589004517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9862384796143</t>
+    <t xml:space="preserve">10.9862375259399</t>
   </si>
   <si>
     <t xml:space="preserve">11.0834608078003</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292957305908</t>
+    <t xml:space="preserve">11.2292966842651</t>
   </si>
   <si>
     <t xml:space="preserve">11.2848520278931</t>
@@ -1163,13 +1163,13 @@
     <t xml:space="preserve">11.3265190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2431840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5973567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7501363754272</t>
+    <t xml:space="preserve">11.243185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5973558425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7501354217529</t>
   </si>
   <si>
     <t xml:space="preserve">11.6181888580322</t>
@@ -1178,88 +1178,88 @@
     <t xml:space="preserve">11.7987470626831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.632080078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8334693908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1251392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9168043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6668109893799</t>
+    <t xml:space="preserve">11.6320781707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8334703445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1251382827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9168033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6668119430542</t>
   </si>
   <si>
     <t xml:space="preserve">13.1529302597046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3820991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3195972442627</t>
+    <t xml:space="preserve">13.3821001052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3196001052856</t>
   </si>
   <si>
     <t xml:space="preserve">13.3682088851929</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5765466690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5209884643555</t>
+    <t xml:space="preserve">13.5765428543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5209875106812</t>
   </si>
   <si>
     <t xml:space="preserve">13.2362632751465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1668167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0487604141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4237642288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0070934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3543195724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4584894180298</t>
+    <t xml:space="preserve">13.1668176651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0487613677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4237651824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070943832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.354320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4584884643555</t>
   </si>
   <si>
     <t xml:space="preserve">13.7154359817505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.791823387146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6807136535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9168281555176</t>
+    <t xml:space="preserve">13.7918262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6807146072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">13.9307155609131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1876516342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2987632751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3751525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.416820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4723777770996</t>
+    <t xml:space="preserve">13.187650680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2987651824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3751544952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4168214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4723768234253</t>
   </si>
   <si>
     <t xml:space="preserve">13.4862670898438</t>
@@ -1271,28 +1271,28 @@
     <t xml:space="preserve">13.7362689971924</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7223796844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8196039199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8890504837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8543281555176</t>
+    <t xml:space="preserve">13.7223815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8196048736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.889048576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8543252944946</t>
   </si>
   <si>
     <t xml:space="preserve">13.9029388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">14.08349609375</t>
+    <t xml:space="preserve">14.0834970474243</t>
   </si>
   <si>
     <t xml:space="preserve">13.7987699508667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0279397964478</t>
+    <t xml:space="preserve">14.0279407501221</t>
   </si>
   <si>
     <t xml:space="preserve">14.305721282959</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">13.1945972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1112613677979</t>
+    <t xml:space="preserve">13.1112623214722</t>
   </si>
   <si>
     <t xml:space="preserve">13.1807079315186</t>
@@ -1310,25 +1310,25 @@
     <t xml:space="preserve">14.0200996398926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1486539840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8083591461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6571178436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5361261367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2563285827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1277732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3092622756958</t>
+    <t xml:space="preserve">14.1486549377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8083581924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6571168899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5361232757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.256329536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1277742385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3092641830444</t>
   </si>
   <si>
     <t xml:space="preserve">13.4605045318604</t>
@@ -1340,52 +1340,52 @@
     <t xml:space="preserve">13.4680671691895</t>
   </si>
   <si>
-    <t xml:space="preserve">13.573935508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7327404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7478628158569</t>
+    <t xml:space="preserve">13.5739374160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.732738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7478637695312</t>
   </si>
   <si>
     <t xml:space="preserve">13.4075689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4889469146729</t>
+    <t xml:space="preserve">14.4889459609985</t>
   </si>
   <si>
     <t xml:space="preserve">14.473822593689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6704387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755168914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6175022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7233724594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9351119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7460584640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292417526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167119979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2998962402344</t>
+    <t xml:space="preserve">14.6704368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158079147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755140304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6175031661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.723370552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9351100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.746057510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292398452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2998943328857</t>
   </si>
   <si>
     <t xml:space="preserve">14.2091503143311</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">14.0654726028442</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1637754440308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0427837371826</t>
+    <t xml:space="preserve">14.1637783050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0427856445312</t>
   </si>
   <si>
     <t xml:space="preserve">14.1713399887085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2847719192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6250629425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536211013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6780004501343</t>
+    <t xml:space="preserve">14.2847700119019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6250638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536182403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.67799949646</t>
   </si>
   <si>
     <t xml:space="preserve">14.791431427002</t>
@@ -1427,88 +1427,88 @@
     <t xml:space="preserve">14.8368043899536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7611837387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6553134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5494422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099414825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6401882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5721311569214</t>
+    <t xml:space="preserve">14.7611827850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6553115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5494432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099405288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.640191078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5721292495728</t>
   </si>
   <si>
     <t xml:space="preserve">14.5191965103149</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2393970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0049753189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9217920303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9142293930054</t>
+    <t xml:space="preserve">14.2393989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0049734115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9217910766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9142274856567</t>
   </si>
   <si>
     <t xml:space="preserve">14.2696466445923</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3982038497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9898490905762</t>
+    <t xml:space="preserve">14.3982028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9898500442505</t>
   </si>
   <si>
     <t xml:space="preserve">13.664680480957</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6722421646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5814971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7705478668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6268711090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5210008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495561599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5512495040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907541275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4756298065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.505877494812</t>
+    <t xml:space="preserve">13.6722412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5814952850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705488204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6268692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5209999084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495542526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.551248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4756288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5058765411377</t>
   </si>
   <si>
     <t xml:space="preserve">13.3470726013184</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4831895828247</t>
+    <t xml:space="preserve">13.39244556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.483190536499</t>
   </si>
   <si>
     <t xml:space="preserve">13.8310461044312</t>
@@ -1517,16 +1517,16 @@
     <t xml:space="preserve">13.6344318389893</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5663738250732</t>
+    <t xml:space="preserve">13.5663719177246</t>
   </si>
   <si>
     <t xml:space="preserve">13.5436868667603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3773212432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1958322525024</t>
+    <t xml:space="preserve">13.3773231506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1958332061768</t>
   </si>
   <si>
     <t xml:space="preserve">13.2714519500732</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">13.3395099639893</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3546342849731</t>
+    <t xml:space="preserve">13.3546361923218</t>
   </si>
   <si>
     <t xml:space="preserve">13.2638902664185</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">13.4529438018799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3319473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9311599731445</t>
+    <t xml:space="preserve">13.3319482803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9311590194702</t>
   </si>
   <si>
     <t xml:space="preserve">13.0219030380249</t>
@@ -1559,19 +1559,19 @@
     <t xml:space="preserve">12.5530548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7421073913574</t>
+    <t xml:space="preserve">12.7421064376831</t>
   </si>
   <si>
     <t xml:space="preserve">12.6513614654541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3848838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1202125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.961404800415</t>
+    <t xml:space="preserve">13.3848829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1202096939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9614067077637</t>
   </si>
   <si>
     <t xml:space="preserve">12.5681791305542</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">12.4925575256348</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4698724746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1371393203735</t>
+    <t xml:space="preserve">12.4698705673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1371402740479</t>
   </si>
   <si>
     <t xml:space="preserve">12.2883825302124</t>
@@ -1607,55 +1607,55 @@
     <t xml:space="preserve">12.643798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8252878189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7723541259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.847975730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7572317123413</t>
+    <t xml:space="preserve">12.8252897262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7723531723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8479766845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.757230758667</t>
   </si>
   <si>
     <t xml:space="preserve">12.8177280426025</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7799158096313</t>
+    <t xml:space="preserve">12.7799167633057</t>
   </si>
   <si>
     <t xml:space="preserve">12.4471845626831</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4244995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2581329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1673879623413</t>
+    <t xml:space="preserve">12.4244985580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2581338882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1673889160156</t>
   </si>
   <si>
     <t xml:space="preserve">12.4169368743896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1447010040283</t>
+    <t xml:space="preserve">12.1447019577026</t>
   </si>
   <si>
     <t xml:space="preserve">12.031270980835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2505722045898</t>
+    <t xml:space="preserve">12.2505712509155</t>
   </si>
   <si>
     <t xml:space="preserve">12.1068925857544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2278842926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0463943481445</t>
+    <t xml:space="preserve">12.2278852462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0463953018188</t>
   </si>
   <si>
     <t xml:space="preserve">12.0993299484253</t>
@@ -1667,58 +1667,55 @@
     <t xml:space="preserve">11.8800296783447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5379314422607</t>
+    <t xml:space="preserve">12.5379295349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.2656946182251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7950420379639</t>
+    <t xml:space="preserve">12.7950410842896</t>
   </si>
   <si>
     <t xml:space="preserve">13.2941389083862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1126489639282</t>
+    <t xml:space="preserve">13.1126499176025</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538440704346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5833015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4774332046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.575740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8555374145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0143413543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8328523635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9084720611572</t>
+    <t xml:space="preserve">12.5833024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4774341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5757398605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8555364608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0143404006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8328504562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9084730148315</t>
   </si>
   <si>
     <t xml:space="preserve">13.0521516799927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1807069778442</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.9160346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0975246429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.006778717041</t>
+    <t xml:space="preserve">13.09752368927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0067796707153</t>
   </si>
   <si>
     <t xml:space="preserve">13.2260808944702</t>
@@ -1727,34 +1724,34 @@
     <t xml:space="preserve">13.2185163497925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9009103775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0370273590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7647914886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0294666290283</t>
+    <t xml:space="preserve">12.9009094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0370264053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7647924423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0294647216797</t>
   </si>
   <si>
     <t xml:space="preserve">13.210955619812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2336406707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9235973358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8706607818604</t>
+    <t xml:space="preserve">13.2336416244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9235963821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8706617355347</t>
   </si>
   <si>
     <t xml:space="preserve">12.8933477401733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1882705688477</t>
+    <t xml:space="preserve">13.188268661499</t>
   </si>
   <si>
     <t xml:space="preserve">13.1353349685669</t>
@@ -1766,13 +1763,13 @@
     <t xml:space="preserve">13.1050863265991</t>
   </si>
   <si>
-    <t xml:space="preserve">13.301700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8857870101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6891708374023</t>
+    <t xml:space="preserve">13.3017015457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8857860565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6891717910767</t>
   </si>
   <si>
     <t xml:space="preserve">12.6967344284058</t>
@@ -1784,37 +1781,37 @@
     <t xml:space="preserve">12.666485786438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5152444839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3110675811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2430095672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0388326644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6589241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7269830703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7496700286865</t>
+    <t xml:space="preserve">12.5152425765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3110685348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2430086135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0388336181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6589231491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7269821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7496690750122</t>
   </si>
   <si>
     <t xml:space="preserve">12.3186302185059</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1900749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1976366043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1749505996704</t>
+    <t xml:space="preserve">12.1900758743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1976356506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1749515533447</t>
   </si>
   <si>
     <t xml:space="preserve">12.2732572555542</t>
@@ -1829,64 +1826,64 @@
     <t xml:space="preserve">12.280818939209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3035078048706</t>
+    <t xml:space="preserve">12.303505897522</t>
   </si>
   <si>
     <t xml:space="preserve">12.8631000518799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2902879714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4485063552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5988130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9548015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9785356521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8598728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7491188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7332973480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7728519439697</t>
+    <t xml:space="preserve">13.2902860641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.448504447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.614631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9548006057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9785346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8598718643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7491178512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7332983016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7728509902954</t>
   </si>
   <si>
     <t xml:space="preserve">13.8124055862427</t>
   </si>
   <si>
-    <t xml:space="preserve">13.717474937439</t>
+    <t xml:space="preserve">13.7174758911133</t>
   </si>
   <si>
     <t xml:space="preserve">13.6383666992188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6620998382568</t>
+    <t xml:space="preserve">13.6620988845825</t>
   </si>
   <si>
     <t xml:space="preserve">13.5750789642334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1446628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2395944595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5085649490356</t>
+    <t xml:space="preserve">14.1446619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2395925521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5085620880127</t>
   </si>
   <si>
     <t xml:space="preserve">14.4690103530884</t>
@@ -1895,34 +1892,34 @@
     <t xml:space="preserve">14.5955858230591</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7221574783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.674690246582</t>
+    <t xml:space="preserve">14.7221584320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6746912002563</t>
   </si>
   <si>
     <t xml:space="preserve">14.176305770874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1604852676392</t>
+    <t xml:space="preserve">14.1604833602905</t>
   </si>
   <si>
     <t xml:space="preserve">14.0813751220703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0339097976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373655319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6984243392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.611403465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4136323928833</t>
+    <t xml:space="preserve">14.0339107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373664855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6984272003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6114053726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4136333465576</t>
   </si>
   <si>
     <t xml:space="preserve">14.6272268295288</t>
@@ -1931,28 +1928,28 @@
     <t xml:space="preserve">15.1097917556763</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0939683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911270141602</t>
+    <t xml:space="preserve">15.0939693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911279678345</t>
   </si>
   <si>
     <t xml:space="preserve">14.943660736084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9120178222656</t>
+    <t xml:space="preserve">14.9120197296143</t>
   </si>
   <si>
     <t xml:space="preserve">14.8724641799927</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8645544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6430501937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2870588302612</t>
+    <t xml:space="preserve">14.8645534515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6430511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2870578765869</t>
   </si>
   <si>
     <t xml:space="preserve">14.3266134262085</t>
@@ -1961,40 +1958,40 @@
     <t xml:space="preserve">14.2158603668213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2475023269653</t>
+    <t xml:space="preserve">14.2475061416626</t>
   </si>
   <si>
     <t xml:space="preserve">14.0259990692139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0576438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6067237854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8677825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000398635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2949705123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.207950592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6304559707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5671672821045</t>
+    <t xml:space="preserve">14.0576448440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6067228317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8677835464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000408172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2949695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2079477310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6304540634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5671682357788</t>
   </si>
   <si>
     <t xml:space="preserve">13.6700105667114</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5197048187256</t>
+    <t xml:space="preserve">13.519702911377</t>
   </si>
   <si>
     <t xml:space="preserve">13.3693962097168</t>
@@ -2003,76 +2000,76 @@
     <t xml:space="preserve">13.8203172683716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9073390960693</t>
+    <t xml:space="preserve">13.9073371887207</t>
   </si>
   <si>
     <t xml:space="preserve">13.8440494537354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5592565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7886724472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1209316253662</t>
+    <t xml:space="preserve">13.5592575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7886743545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965831756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1209306716919</t>
   </si>
   <si>
     <t xml:space="preserve">13.9310693740845</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0892868041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3028812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4848318099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6588706970215</t>
+    <t xml:space="preserve">14.0892887115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3028793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4848299026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6588716506958</t>
   </si>
   <si>
     <t xml:space="preserve">14.2633256912231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2316837310791</t>
+    <t xml:space="preserve">14.2316827774048</t>
   </si>
   <si>
     <t xml:space="preserve">14.1130199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5876712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9753074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8566417694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9990367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8329095840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7458877563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0227708816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7379779815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854452133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6905145645142</t>
+    <t xml:space="preserve">14.5876731872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9753046035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8566427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9990377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8329105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7458906173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7379808425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854461669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6905155181885</t>
   </si>
   <si>
     <t xml:space="preserve">14.6351375579834</t>
@@ -2084,70 +2081,70 @@
     <t xml:space="preserve">14.1525735855103</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5164747238159</t>
+    <t xml:space="preserve">14.5164756774902</t>
   </si>
   <si>
     <t xml:space="preserve">14.4294548034668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1921291351318</t>
+    <t xml:space="preserve">14.1921281814575</t>
   </si>
   <si>
     <t xml:space="preserve">14.0971975326538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2712373733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2791481018066</t>
+    <t xml:space="preserve">14.2712383270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.279146194458</t>
   </si>
   <si>
     <t xml:space="preserve">14.4057216644287</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3899021148682</t>
+    <t xml:space="preserve">14.3899011611938</t>
   </si>
   <si>
     <t xml:space="preserve">14.3424348831177</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3582553863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4611005783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0069494247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9515733718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5322971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3345232009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3740797042847</t>
+    <t xml:space="preserve">14.3582563400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4610977172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0069484710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9515724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5322961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3345241546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3740787506104</t>
   </si>
   <si>
     <t xml:space="preserve">14.3819894790649</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6509609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0860567092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8170890808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6193170547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0544176101685</t>
+    <t xml:space="preserve">14.6509599685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0860557556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8170881271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6193161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0544157028198</t>
   </si>
   <si>
     <t xml:space="preserve">15.4895133972168</t>
@@ -2156,55 +2153,55 @@
     <t xml:space="preserve">15.8692359924316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7189283370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3075647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3471183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081781387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2284545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572561264038</t>
+    <t xml:space="preserve">15.7189302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.307562828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3471174240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081762313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2284526824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572551727295</t>
   </si>
   <si>
     <t xml:space="preserve">15.1889009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1414356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3866729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2838325500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3154735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7505722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7110204696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6160860061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4420499801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2047204971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.236364364624</t>
+    <t xml:space="preserve">15.1414346694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3866720199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2838306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3154754638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7505741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7110185623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6160879135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4420490264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2047214508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.236367225647</t>
   </si>
   <si>
     <t xml:space="preserve">15.1651668548584</t>
@@ -2213,28 +2210,28 @@
     <t xml:space="preserve">15.4024925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6240015029907</t>
+    <t xml:space="preserve">15.6239976882935</t>
   </si>
   <si>
     <t xml:space="preserve">15.7743072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2173137664795</t>
+    <t xml:space="preserve">16.2173156738281</t>
   </si>
   <si>
     <t xml:space="preserve">16.5179290771484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2964248657227</t>
+    <t xml:space="preserve">16.296422958374</t>
   </si>
   <si>
     <t xml:space="preserve">16.5653953552246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0400447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9292964935303</t>
+    <t xml:space="preserve">17.0400485992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9292945861816</t>
   </si>
   <si>
     <t xml:space="preserve">17.0875129699707</t>
@@ -2243,22 +2240,22 @@
     <t xml:space="preserve">17.0558681488037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9609394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6919689178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8976497650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.198263168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8818283081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2299098968506</t>
+    <t xml:space="preserve">16.9609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.691967010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8976516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1982669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8818302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.229907989502</t>
   </si>
   <si>
     <t xml:space="preserve">17.356481552124</t>
@@ -2267,7 +2264,7 @@
     <t xml:space="preserve">17.4514122009277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6096305847168</t>
+    <t xml:space="preserve">17.6096286773682</t>
   </si>
   <si>
     <t xml:space="preserve">17.4039478302002</t>
@@ -2276,7 +2273,7 @@
     <t xml:space="preserve">17.4355926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305213928223</t>
+    <t xml:space="preserve">17.5305233001709</t>
   </si>
   <si>
     <t xml:space="preserve">17.8786010742188</t>
@@ -2285,10 +2282,10 @@
     <t xml:space="preserve">18.1792144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1317501068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2583236694336</t>
+    <t xml:space="preserve">18.1317520141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.258321762085</t>
   </si>
   <si>
     <t xml:space="preserve">18.3690757751465</t>
@@ -2303,10 +2300,10 @@
     <t xml:space="preserve">17.3723049163818</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4830570220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7045612335205</t>
+    <t xml:space="preserve">17.4830589294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7045593261719</t>
   </si>
   <si>
     <t xml:space="preserve">17.3248386383057</t>
@@ -2327,7 +2324,7 @@
     <t xml:space="preserve">13.0213165283203</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8267726898193</t>
+    <t xml:space="preserve">11.8267736434937</t>
   </si>
   <si>
     <t xml:space="preserve">11.6210899353027</t>
@@ -2348,10 +2345,13 @@
     <t xml:space="preserve">12.0245456695557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0641002655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4200897216797</t>
+    <t xml:space="preserve">12.0640993118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8630990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4200916290283</t>
   </si>
   <si>
     <t xml:space="preserve">12.1748533248901</t>
@@ -2360,16 +2360,16 @@
     <t xml:space="preserve">12.9026546478271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6969699859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.219090461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4722394943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.314022064209</t>
+    <t xml:space="preserve">12.6969709396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2190885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4722375869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3140201568604</t>
   </si>
   <si>
     <t xml:space="preserve">13.2349109649658</t>
@@ -2387,73 +2387,73 @@
     <t xml:space="preserve">13.1004266738892</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0925149917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3614864349365</t>
+    <t xml:space="preserve">13.0925140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2507333755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687828063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3614845275879</t>
   </si>
   <si>
     <t xml:space="preserve">13.4326829910278</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5038824081421</t>
+    <t xml:space="preserve">13.5038814544678</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738521575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9342975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0371379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1795358657837</t>
+    <t xml:space="preserve">12.9342966079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0371389389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1795349121094</t>
   </si>
   <si>
     <t xml:space="preserve">13.2111787796021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5434370040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6225433349609</t>
+    <t xml:space="preserve">13.543436050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6225442886353</t>
   </si>
   <si>
     <t xml:space="preserve">13.7095642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2056894302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1560773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966461181641</t>
+    <t xml:space="preserve">14.2056884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418626785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1560764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966442108154</t>
   </si>
   <si>
     <t xml:space="preserve">14.2883768081665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0491018295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2475481033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2971620559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1240348815918</t>
+    <t xml:space="preserve">15.0490999221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2475500106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2971611022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1240367889404</t>
   </si>
   <si>
     <t xml:space="preserve">16.4134407043457</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">16.5043964385986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1405754089355</t>
+    <t xml:space="preserve">16.1405735015869</t>
   </si>
   <si>
     <t xml:space="preserve">16.0909595489502</t>
@@ -2471,28 +2471,28 @@
     <t xml:space="preserve">16.190185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5865659713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2144746780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2806253433228</t>
+    <t xml:space="preserve">15.5865678787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286874771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3467750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2144727706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2806234359741</t>
   </si>
   <si>
     <t xml:space="preserve">15.8346290588379</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6527185440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692543029785</t>
+    <t xml:space="preserve">15.6527166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692562103271</t>
   </si>
   <si>
     <t xml:space="preserve">15.5782985687256</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">15.8594379425049</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3633108139038</t>
+    <t xml:space="preserve">15.3633127212524</t>
   </si>
   <si>
     <t xml:space="preserve">15.4294605255127</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">15.8677043914795</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3307552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0501365661621</t>
+    <t xml:space="preserve">16.330753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0501346588135</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651214599609</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">16.868221282959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9509086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1162853240967</t>
+    <t xml:space="preserve">16.9509105682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1162872314453</t>
   </si>
   <si>
     <t xml:space="preserve">17.3312702178955</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">17.51318359375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7777824401855</t>
+    <t xml:space="preserve">17.7777805328369</t>
   </si>
   <si>
     <t xml:space="preserve">17.2981948852539</t>
@@ -2549,16 +2549,16 @@
     <t xml:space="preserve">17.2816600799561</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3147354125977</t>
+    <t xml:space="preserve">17.314733505249</t>
   </si>
   <si>
     <t xml:space="preserve">17.4304962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3643455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3808822631836</t>
+    <t xml:space="preserve">17.3643436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3808841705322</t>
   </si>
   <si>
     <t xml:space="preserve">16.9839859008789</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">16.8186092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9012966156006</t>
+    <t xml:space="preserve">16.9012985229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.8516845703125</t>
@@ -2600,25 +2600,25 @@
     <t xml:space="preserve">18.0919933319092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4227428436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4723567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1581439971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.025842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0754585266113</t>
+    <t xml:space="preserve">18.4227447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.472354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.158145904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0258445739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0754566192627</t>
   </si>
   <si>
     <t xml:space="preserve">18.5054302215576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3896713256836</t>
+    <t xml:space="preserve">18.389669418335</t>
   </si>
   <si>
     <t xml:space="preserve">18.2739067077637</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">18.3235187530518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3400573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.191219329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0589218139648</t>
+    <t xml:space="preserve">18.3400554656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1912174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0589199066162</t>
   </si>
   <si>
     <t xml:space="preserve">17.9100818634033</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">17.711633682251</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5793323516846</t>
+    <t xml:space="preserve">17.5793342590332</t>
   </si>
   <si>
     <t xml:space="preserve">17.347806930542</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">18.3731307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6542682647705</t>
+    <t xml:space="preserve">18.6542663574219</t>
   </si>
   <si>
     <t xml:space="preserve">18.7534942626953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4062061309814</t>
+    <t xml:space="preserve">18.4062042236328</t>
   </si>
   <si>
     <t xml:space="preserve">18.1416072845459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9431591033936</t>
+    <t xml:space="preserve">17.9431571960449</t>
   </si>
   <si>
     <t xml:space="preserve">18.1085319519043</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">17.7281723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9596977233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1989707946777</t>
+    <t xml:space="preserve">17.95969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1989688873291</t>
   </si>
   <si>
     <t xml:space="preserve">16.636697769165</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">16.0413494110107</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5374717712402</t>
+    <t xml:space="preserve">16.5374736785889</t>
   </si>
   <si>
     <t xml:space="preserve">17.0832099914551</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">17.5627937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0666694641113</t>
+    <t xml:space="preserve">17.06667137146</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155094146729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1658973693848</t>
+    <t xml:space="preserve">17.1658954620361</t>
   </si>
   <si>
     <t xml:space="preserve">17.0005207061768</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">16.9178352355957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7028484344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8847618103027</t>
+    <t xml:space="preserve">16.7028503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8847599029541</t>
   </si>
   <si>
     <t xml:space="preserve">16.7855319976807</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">17.0335960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1328201293945</t>
+    <t xml:space="preserve">17.1328220367432</t>
   </si>
   <si>
     <t xml:space="preserve">17.1824340820312</t>
@@ -2768,22 +2768,22 @@
     <t xml:space="preserve">17.5462589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1746826171875</t>
+    <t xml:space="preserve">18.1746807098389</t>
   </si>
   <si>
     <t xml:space="preserve">18.8692569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1669311523438</t>
+    <t xml:space="preserve">19.1669330596924</t>
   </si>
   <si>
     <t xml:space="preserve">19.3488426208496</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0599536895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9607257843018</t>
+    <t xml:space="preserve">20.0599555969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9607276916504</t>
   </si>
   <si>
     <t xml:space="preserve">20.5064640045166</t>
@@ -2804,10 +2804,10 @@
     <t xml:space="preserve">20.7545280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9364376068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7214527130127</t>
+    <t xml:space="preserve">20.9364395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7214508056641</t>
   </si>
   <si>
     <t xml:space="preserve">21.0025882720947</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">21.994836807251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5571136474609</t>
+    <t xml:space="preserve">22.5571117401123</t>
   </si>
   <si>
     <t xml:space="preserve">21.2175769805908</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">20.9033660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9529781341553</t>
+    <t xml:space="preserve">20.9529762268066</t>
   </si>
   <si>
     <t xml:space="preserve">21.3002662658691</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">21.8956127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.515251159668</t>
+    <t xml:space="preserve">21.5152530670166</t>
   </si>
   <si>
     <t xml:space="preserve">21.8459987640381</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">22.160213470459</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5317916870117</t>
+    <t xml:space="preserve">21.5317897796631</t>
   </si>
   <si>
     <t xml:space="preserve">21.3664150238037</t>
@@ -2879,16 +2879,16 @@
     <t xml:space="preserve">20.2584056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6134414672852</t>
+    <t xml:space="preserve">19.6134433746338</t>
   </si>
   <si>
     <t xml:space="preserve">20.192253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3323040008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9354038238525</t>
+    <t xml:space="preserve">19.3323059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9354057312012</t>
   </si>
   <si>
     <t xml:space="preserve">20.2749423980713</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">21.2010402679443</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9860496520996</t>
+    <t xml:space="preserve">20.9860515594482</t>
   </si>
   <si>
     <t xml:space="preserve">21.4656391143799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0103416442871</t>
+    <t xml:space="preserve">20.0103435516357</t>
   </si>
   <si>
     <t xml:space="preserve">19.6465187072754</t>
@@ -2918,7 +2918,7 @@
     <t xml:space="preserve">20.5560779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6387634277344</t>
+    <t xml:space="preserve">20.638765335083</t>
   </si>
   <si>
     <t xml:space="preserve">21.0356636047363</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">21.085277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0191287994385</t>
+    <t xml:space="preserve">21.0191268920898</t>
   </si>
   <si>
     <t xml:space="preserve">20.870288848877</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">20.0268783569336</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1095676422119</t>
+    <t xml:space="preserve">20.1095657348633</t>
   </si>
   <si>
     <t xml:space="preserve">21.1514263153076</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">20.6222305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3080139160156</t>
+    <t xml:space="preserve">20.3080158233643</t>
   </si>
   <si>
     <t xml:space="preserve">20.4072399139404</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">20.3907032012939</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1261005401611</t>
+    <t xml:space="preserve">20.1261024475098</t>
   </si>
   <si>
     <t xml:space="preserve">20.0764923095703</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">21.229097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1779441833496</t>
+    <t xml:space="preserve">21.177942276001</t>
   </si>
   <si>
     <t xml:space="preserve">21.4337158203125</t>
@@ -3014,25 +3014,25 @@
     <t xml:space="preserve">21.4848709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6042308807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6212825775146</t>
+    <t xml:space="preserve">21.6042289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.621280670166</t>
   </si>
   <si>
     <t xml:space="preserve">21.3143558502197</t>
   </si>
   <si>
-    <t xml:space="preserve">21.570125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.388599395752</t>
+    <t xml:space="preserve">21.5701274871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3885974884033</t>
   </si>
   <si>
     <t xml:space="preserve">21.9793643951416</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0646190643311</t>
+    <t xml:space="preserve">22.0646171569824</t>
   </si>
   <si>
     <t xml:space="preserve">22.030517578125</t>
@@ -3047,19 +3047,19 @@
     <t xml:space="preserve">21.7406425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3655090332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4507675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6724376678467</t>
+    <t xml:space="preserve">21.3655071258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4507656097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.672435760498</t>
   </si>
   <si>
     <t xml:space="preserve">22.0987224578857</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7917957305908</t>
+    <t xml:space="preserve">21.7917938232422</t>
   </si>
   <si>
     <t xml:space="preserve">21.9964141845703</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">21.3825607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8369140625</t>
+    <t xml:space="preserve">20.8369159698486</t>
   </si>
   <si>
     <t xml:space="preserve">20.8710155487061</t>
@@ -3095,16 +3095,16 @@
     <t xml:space="preserve">22.2692375183105</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7346057891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5470390319824</t>
+    <t xml:space="preserve">20.7346038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5470371246338</t>
   </si>
   <si>
     <t xml:space="preserve">21.2632026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1097373962402</t>
+    <t xml:space="preserve">21.1097393035889</t>
   </si>
   <si>
     <t xml:space="preserve">21.1608905792236</t>
@@ -3113,22 +3113,22 @@
     <t xml:space="preserve">21.5530776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7747478485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2973022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0926876068115</t>
+    <t xml:space="preserve">21.7747459411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2973041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0926856994629</t>
   </si>
   <si>
     <t xml:space="preserve">20.8539638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0074291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2802505493164</t>
+    <t xml:space="preserve">21.0074272155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.280252456665</t>
   </si>
   <si>
     <t xml:space="preserve">21.9282073974609</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">21.8088474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8941078186035</t>
+    <t xml:space="preserve">21.8941059112549</t>
   </si>
   <si>
     <t xml:space="preserve">21.7576942443848</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">22.013463973999</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4909076690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4227027893066</t>
+    <t xml:space="preserve">22.4909057617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.422700881958</t>
   </si>
   <si>
     <t xml:space="preserve">22.2521858215332</t>
@@ -3176,13 +3176,13 @@
     <t xml:space="preserve">22.5761642456055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6614227294922</t>
+    <t xml:space="preserve">22.6614189147949</t>
   </si>
   <si>
     <t xml:space="preserve">22.7296276092529</t>
   </si>
   <si>
-    <t xml:space="preserve">23.172966003418</t>
+    <t xml:space="preserve">23.1729679107666</t>
   </si>
   <si>
     <t xml:space="preserve">23.7697677612305</t>
@@ -3203,55 +3203,55 @@
     <t xml:space="preserve">25.4749164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8329982757568</t>
+    <t xml:space="preserve">25.8329963684082</t>
   </si>
   <si>
     <t xml:space="preserve">25.7818431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1740283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3274898529053</t>
+    <t xml:space="preserve">26.1740264892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3274917602539</t>
   </si>
   <si>
     <t xml:space="preserve">26.6003150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6173648834229</t>
+    <t xml:space="preserve">26.6173667907715</t>
   </si>
   <si>
     <t xml:space="preserve">26.7708301544189</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6855716705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.969409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7196750640869</t>
+    <t xml:space="preserve">26.6855735778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9694080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7196769714355</t>
   </si>
   <si>
     <t xml:space="preserve">26.3615951538086</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3104419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5491600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2251834869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5431232452393</t>
+    <t xml:space="preserve">26.3104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5491619110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2251815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5431213378906</t>
   </si>
   <si>
     <t xml:space="preserve">25.0315799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8269596099854</t>
+    <t xml:space="preserve">24.826961517334</t>
   </si>
   <si>
     <t xml:space="preserve">25.0145282745361</t>
@@ -3263,25 +3263,25 @@
     <t xml:space="preserve">25.1168346405029</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8099117279053</t>
+    <t xml:space="preserve">24.8099098205566</t>
   </si>
   <si>
     <t xml:space="preserve">24.8440113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1338882446289</t>
+    <t xml:space="preserve">25.1338863372803</t>
   </si>
   <si>
     <t xml:space="preserve">24.7246532440186</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7587566375732</t>
+    <t xml:space="preserve">24.7587547302246</t>
   </si>
   <si>
     <t xml:space="preserve">25.3896598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3836212158203</t>
+    <t xml:space="preserve">24.3836231231689</t>
   </si>
   <si>
     <t xml:space="preserve">24.1790046691895</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">24.6223411560059</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1960563659668</t>
+    <t xml:space="preserve">24.1960544586182</t>
   </si>
   <si>
     <t xml:space="preserve">24.3495197296143</t>
@@ -3302,25 +3302,25 @@
     <t xml:space="preserve">23.9402847290039</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1449012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1107978820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8038711547852</t>
+    <t xml:space="preserve">24.1449031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1107997894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8038730621338</t>
   </si>
   <si>
     <t xml:space="preserve">24.417724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4518280029297</t>
+    <t xml:space="preserve">24.4518299102783</t>
   </si>
   <si>
     <t xml:space="preserve">24.2131061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3665733337402</t>
+    <t xml:space="preserve">24.3665714263916</t>
   </si>
   <si>
     <t xml:space="preserve">24.2472114562988</t>
@@ -3329,22 +3329,22 @@
     <t xml:space="preserve">24.2813129425049</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0486278533936</t>
+    <t xml:space="preserve">25.0486297607422</t>
   </si>
   <si>
     <t xml:space="preserve">24.4347763061523</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5481014251709</t>
+    <t xml:space="preserve">23.5480995178223</t>
   </si>
   <si>
     <t xml:space="preserve">23.4969463348389</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9342460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7978324890137</t>
+    <t xml:space="preserve">22.9342479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7978363037109</t>
   </si>
   <si>
     <t xml:space="preserve">22.6443710327148</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">21.8429508209229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1839809417725</t>
+    <t xml:space="preserve">22.1839828491211</t>
   </si>
   <si>
     <t xml:space="preserve">21.1949939727783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6383304595947</t>
+    <t xml:space="preserve">21.6383323669434</t>
   </si>
   <si>
     <t xml:space="preserve">21.2120456695557</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">20.9051208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6663990020752</t>
+    <t xml:space="preserve">20.6664009094238</t>
   </si>
   <si>
     <t xml:space="preserve">21.4678173065186</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">21.0244789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5640926361084</t>
+    <t xml:space="preserve">20.5640907287598</t>
   </si>
   <si>
     <t xml:space="preserve">20.9221706390381</t>
@@ -3398,19 +3398,19 @@
     <t xml:space="preserve">20.2912654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1378021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6273193359375</t>
+    <t xml:space="preserve">20.1378040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6273212432861</t>
   </si>
   <si>
     <t xml:space="preserve">24.0937480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.616304397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7637329101562</t>
+    <t xml:space="preserve">23.6163063049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7637310028076</t>
   </si>
   <si>
     <t xml:space="preserve">22.8148860931396</t>
@@ -3425,13 +3425,13 @@
     <t xml:space="preserve">25.560173034668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9292697906494</t>
+    <t xml:space="preserve">24.9292678833008</t>
   </si>
   <si>
     <t xml:space="preserve">24.8951683044434</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3154182434082</t>
+    <t xml:space="preserve">24.3154163360596</t>
   </si>
   <si>
     <t xml:space="preserve">25.2873497009277</t>
@@ -3440,46 +3440,46 @@
     <t xml:space="preserve">25.7136363983154</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6564464569092</t>
+    <t xml:space="preserve">24.6564445495605</t>
   </si>
   <si>
     <t xml:space="preserve">25.1850433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9804248809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6624851226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3786449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2933902740479</t>
+    <t xml:space="preserve">24.9804229736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.662483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3786468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2933883666992</t>
   </si>
   <si>
     <t xml:space="preserve">26.8049335479736</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7537803649902</t>
+    <t xml:space="preserve">26.7537784576416</t>
   </si>
   <si>
     <t xml:space="preserve">26.9413471221924</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0436515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0948085784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8219833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9924983978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1459617614746</t>
+    <t xml:space="preserve">27.0436534881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0948104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.821985244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9925003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1459636688232</t>
   </si>
   <si>
     <t xml:space="preserve">27.7086620330811</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">27.5040416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4699420928955</t>
+    <t xml:space="preserve">27.4699401855469</t>
   </si>
   <si>
     <t xml:space="preserve">27.6916103363037</t>
@@ -3497,22 +3497,22 @@
     <t xml:space="preserve">27.7939186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8621234893799</t>
+    <t xml:space="preserve">27.8621253967285</t>
   </si>
   <si>
     <t xml:space="preserve">28.0496940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5893020629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1800670623779</t>
+    <t xml:space="preserve">27.5893039703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1800651550293</t>
   </si>
   <si>
     <t xml:space="preserve">27.2823753356934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.856086730957</t>
+    <t xml:space="preserve">26.8560886383057</t>
   </si>
   <si>
     <t xml:space="preserve">26.6514701843262</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">25.3555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3214530944824</t>
+    <t xml:space="preserve">25.3214550018311</t>
   </si>
   <si>
     <t xml:space="preserve">25.9864597320557</t>
@@ -3533,40 +3533,40 @@
     <t xml:space="preserve">26.8901920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7598171234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4759788513184</t>
+    <t xml:space="preserve">27.7598190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.475980758667</t>
   </si>
   <si>
     <t xml:space="preserve">28.5100803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6976509094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9875240325928</t>
+    <t xml:space="preserve">28.6976470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9875202178955</t>
   </si>
   <si>
     <t xml:space="preserve">29.4604301452637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4954605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5655193328857</t>
+    <t xml:space="preserve">29.4954624176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5655212402344</t>
   </si>
   <si>
     <t xml:space="preserve">28.724796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6197052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3394641876221</t>
+    <t xml:space="preserve">28.6197071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3394660949707</t>
   </si>
   <si>
     <t xml:space="preserve">28.1993446350098</t>
@@ -3575,19 +3575,19 @@
     <t xml:space="preserve">28.3044338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9524936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8824329376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0575828552246</t>
+    <t xml:space="preserve">28.9524955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8824310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0575847625732</t>
   </si>
   <si>
     <t xml:space="preserve">29.1451568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">27.043342590332</t>
+    <t xml:space="preserve">27.0433444976807</t>
   </si>
   <si>
     <t xml:space="preserve">26.6229820251465</t>
@@ -3599,19 +3599,19 @@
     <t xml:space="preserve">26.8681926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">26.009952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9924392700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.957405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.607105255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5178928375244</t>
+    <t xml:space="preserve">26.0099544525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9924373626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9574069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6071033477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5178909301758</t>
   </si>
   <si>
     <t xml:space="preserve">26.255163192749</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">26.6054649353027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8873462677002</t>
+    <t xml:space="preserve">25.8873481750488</t>
   </si>
   <si>
     <t xml:space="preserve">26.4653453826904</t>
@@ -3632,10 +3632,10 @@
     <t xml:space="preserve">26.1675891876221</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9382553100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9732837677002</t>
+    <t xml:space="preserve">26.93825340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9732856750488</t>
   </si>
   <si>
     <t xml:space="preserve">27.1309204101562</t>
@@ -3644,10 +3644,10 @@
     <t xml:space="preserve">27.4286785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">27.341100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7455902099609</t>
+    <t xml:space="preserve">27.3411026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7455883026123</t>
   </si>
   <si>
     <t xml:space="preserve">26.9907989501953</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">27.6563739776611</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5687980651855</t>
+    <t xml:space="preserve">27.5687999725342</t>
   </si>
   <si>
     <t xml:space="preserve">26.7280731201172</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">25.7822570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3602561950684</t>
+    <t xml:space="preserve">26.3602542877197</t>
   </si>
   <si>
     <t xml:space="preserve">26.6930408477783</t>
@@ -3677,10 +3677,10 @@
     <t xml:space="preserve">27.1834678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5512828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.884069442749</t>
+    <t xml:space="preserve">27.5512847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8840713500977</t>
   </si>
   <si>
     <t xml:space="preserve">28.1467971801758</t>
@@ -3698,10 +3698,10 @@
     <t xml:space="preserve">29.6706123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6530990600586</t>
+    <t xml:space="preserve">29.7757015228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.65309715271</t>
   </si>
   <si>
     <t xml:space="preserve">29.2327365875244</t>
@@ -3710,28 +3710,28 @@
     <t xml:space="preserve">30.4062480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1260070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3186702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8632755279541</t>
+    <t xml:space="preserve">30.1260051727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3186721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8632793426514</t>
   </si>
   <si>
     <t xml:space="preserve">29.950855255127</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4412784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.15940284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3361873626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1785526275635</t>
+    <t xml:space="preserve">30.4412746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1593990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3361854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1785488128662</t>
   </si>
   <si>
     <t xml:space="preserve">29.7406730651855</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">27.7089195251465</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4987373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0258312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1851024627686</t>
+    <t xml:space="preserve">27.4987392425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0258293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1851043701172</t>
   </si>
   <si>
     <t xml:space="preserve">26.4478321075439</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">27.8490409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2694034576416</t>
+    <t xml:space="preserve">28.269401550293</t>
   </si>
   <si>
     <t xml:space="preserve">28.1643142700195</t>
@@ -3773,19 +3773,19 @@
     <t xml:space="preserve">29.0926151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7598285675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8665542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.169225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.064136505127</t>
+    <t xml:space="preserve">28.7598266601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1801891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8665561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1692276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0641384124756</t>
   </si>
   <si>
     <t xml:space="preserve">24.5912284851074</t>
@@ -3794,10 +3794,10 @@
     <t xml:space="preserve">24.7488651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2726802825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1659507751465</t>
+    <t xml:space="preserve">26.2726783752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1659526824951</t>
   </si>
   <si>
     <t xml:space="preserve">25.0816516876221</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">24.4335918426514</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1708660125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9781970977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.838077545166</t>
+    <t xml:space="preserve">24.1708679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.978199005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8380794525146</t>
   </si>
   <si>
     <t xml:space="preserve">24.9065017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5545616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7472267150879</t>
+    <t xml:space="preserve">25.5545597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7472248077393</t>
   </si>
   <si>
     <t xml:space="preserve">25.6946811676025</t>
@@ -3851,16 +3851,16 @@
     <t xml:space="preserve">27.2535285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.936616897583</t>
+    <t xml:space="preserve">27.48122215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9366149902344</t>
   </si>
   <si>
     <t xml:space="preserve">28.8649158477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7631034851074</t>
+    <t xml:space="preserve">26.7631015777588</t>
   </si>
   <si>
     <t xml:space="preserve">26.9032230377197</t>
@@ -3869,37 +3869,37 @@
     <t xml:space="preserve">26.0274677276611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3952865600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8331642150879</t>
+    <t xml:space="preserve">26.39528465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8331623077393</t>
   </si>
   <si>
     <t xml:space="preserve">26.307710647583</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9223785400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3777713775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5003757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1325569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0975284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5354061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8857097625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2376499176025</t>
+    <t xml:space="preserve">25.9223766326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3777694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5003776550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1325588226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.097526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5354042053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8857078552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2376480102539</t>
   </si>
   <si>
     <t xml:space="preserve">25.7647399902344</t>
@@ -3908,10 +3908,10 @@
     <t xml:space="preserve">25.8348026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2201347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4144382476807</t>
+    <t xml:space="preserve">26.2201328277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4144401550293</t>
   </si>
   <si>
     <t xml:space="preserve">25.466983795166</t>
@@ -3941,22 +3941,22 @@
     <t xml:space="preserve">24.2409267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3285007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7838935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8539562225342</t>
+    <t xml:space="preserve">24.3285026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7838954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8539543151855</t>
   </si>
   <si>
     <t xml:space="preserve">24.3109874725342</t>
   </si>
   <si>
-    <t xml:space="preserve">24.22340965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3460159301758</t>
+    <t xml:space="preserve">24.2234115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3460178375244</t>
   </si>
   <si>
     <t xml:space="preserve">24.4160766601562</t>
@@ -3965,22 +3965,22 @@
     <t xml:space="preserve">24.3985633850098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6788024902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9590454101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0466194152832</t>
+    <t xml:space="preserve">24.678804397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9590473175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0466213226318</t>
   </si>
   <si>
     <t xml:space="preserve">24.7138328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5036506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6612892150879</t>
+    <t xml:space="preserve">24.5036525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6612873077393</t>
   </si>
   <si>
     <t xml:space="preserve">24.2759552001953</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">24.2058944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.188383102417</t>
+    <t xml:space="preserve">24.1883811950684</t>
   </si>
   <si>
     <t xml:space="preserve">23.7329883575439</t>
@@ -4001,10 +4001,10 @@
     <t xml:space="preserve">23.9957141876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0307445526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8731079101562</t>
+    <t xml:space="preserve">24.0307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8731098175049</t>
   </si>
   <si>
     <t xml:space="preserve">23.3476543426514</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">23.5052909851074</t>
   </si>
   <si>
-    <t xml:space="preserve">23.049898147583</t>
+    <t xml:space="preserve">23.0498962402344</t>
   </si>
   <si>
     <t xml:space="preserve">22.8747463226318</t>
@@ -4031,13 +4031,13 @@
     <t xml:space="preserve">23.1900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2425632476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6979560852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5578365325928</t>
+    <t xml:space="preserve">23.2425651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6979579925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5578384399414</t>
   </si>
   <si>
     <t xml:space="preserve">23.9256534576416</t>
@@ -4052,49 +4052,49 @@
     <t xml:space="preserve">23.0849285125732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3826866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5228061676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9606838226318</t>
+    <t xml:space="preserve">23.3826847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5228080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9606857299805</t>
   </si>
   <si>
     <t xml:space="preserve">24.4861373901367</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2584400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1166820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2217712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2042598724365</t>
+    <t xml:space="preserve">24.2584419250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1166839599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.221773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2042579650879</t>
   </si>
   <si>
     <t xml:space="preserve">25.1341972351074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6262588500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3635330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7855319976807</t>
+    <t xml:space="preserve">24.6262607574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3635311126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7855339050293</t>
   </si>
   <si>
     <t xml:space="preserve">23.2250499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9798374176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2775955200195</t>
+    <t xml:space="preserve">22.9798355102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2775917053223</t>
   </si>
   <si>
     <t xml:space="preserve">23.295108795166</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">24.0657749176025</t>
   </si>
   <si>
-    <t xml:space="preserve">24.76637840271</t>
+    <t xml:space="preserve">24.7663803100586</t>
   </si>
   <si>
     <t xml:space="preserve">24.7313499450684</t>
@@ -5427,6 +5427,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.1399993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4799995422363</t>
   </si>
 </sst>
 </file>
@@ -25855,7 +25858,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G773" t="s">
-        <v>565</v>
+        <v>430</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25907,7 +25910,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G775" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25959,7 +25962,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G777" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25985,7 +25988,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G778" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -26011,7 +26014,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G779" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -26037,7 +26040,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G780" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -26089,7 +26092,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G782" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -26115,7 +26118,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G783" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -26141,7 +26144,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G784" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -26219,7 +26222,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G787" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26245,7 +26248,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G788" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -26271,7 +26274,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G789" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -26297,7 +26300,7 @@
         <v>17.5</v>
       </c>
       <c r="G790" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26401,7 +26404,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G794" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -26427,7 +26430,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G795" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26505,7 +26508,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G798" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26557,7 +26560,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G800" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -26583,7 +26586,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G801" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -26609,7 +26612,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26661,7 +26664,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G804" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26687,7 +26690,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G805" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26713,7 +26716,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G806" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26739,7 +26742,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G807" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26765,7 +26768,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G808" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26791,7 +26794,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G809" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26817,7 +26820,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G810" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26843,7 +26846,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G811" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26869,7 +26872,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G812" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26895,7 +26898,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G813" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26921,7 +26924,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G814" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26973,7 +26976,7 @@
         <v>16.75</v>
       </c>
       <c r="G816" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26999,7 +27002,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G817" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -27051,7 +27054,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G819" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -27077,7 +27080,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G820" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27129,7 +27132,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G822" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -27311,7 +27314,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G829" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -27363,7 +27366,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G831" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -27389,7 +27392,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G832" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27519,7 +27522,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G837" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -27623,7 +27626,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G841" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27675,7 +27678,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G843" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27701,7 +27704,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G844" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27727,7 +27730,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G845" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27779,7 +27782,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G847" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27857,7 +27860,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G850" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27883,7 +27886,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G851" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27935,7 +27938,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G853" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27961,7 +27964,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G854" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27987,7 +27990,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G855" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28013,7 +28016,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G856" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28039,7 +28042,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G857" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28065,7 +28068,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G858" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28091,7 +28094,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G859" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28117,7 +28120,7 @@
         <v>17</v>
       </c>
       <c r="G860" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28143,7 +28146,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G861" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28169,7 +28172,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G862" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28195,7 +28198,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G863" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28221,7 +28224,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G864" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28247,7 +28250,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G865" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28273,7 +28276,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G866" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28299,7 +28302,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G867" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28325,7 +28328,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G868" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28351,7 +28354,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G869" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28377,7 +28380,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G870" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28403,7 +28406,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G871" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28429,7 +28432,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G872" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28455,7 +28458,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G873" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28481,7 +28484,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G874" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28507,7 +28510,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G875" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28533,7 +28536,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G876" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28559,7 +28562,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G877" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -28585,7 +28588,7 @@
         <v>18</v>
       </c>
       <c r="G878" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28611,7 +28614,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G879" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28637,7 +28640,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G880" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -28663,7 +28666,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G881" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -28689,7 +28692,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G882" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -28715,7 +28718,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28741,7 +28744,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G884" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -28767,7 +28770,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G885" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28793,7 +28796,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G886" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28819,7 +28822,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G887" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28845,7 +28848,7 @@
         <v>18</v>
       </c>
       <c r="G888" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28871,7 +28874,7 @@
         <v>18</v>
       </c>
       <c r="G889" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28897,7 +28900,7 @@
         <v>18.25</v>
       </c>
       <c r="G890" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28923,7 +28926,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G891" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28949,7 +28952,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G892" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28975,7 +28978,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G893" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29001,7 +29004,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G894" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29027,7 +29030,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29053,7 +29056,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G896" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29079,7 +29082,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G897" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29105,7 +29108,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G898" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29131,7 +29134,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G899" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29157,7 +29160,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29183,7 +29186,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G901" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29209,7 +29212,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G902" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29235,7 +29238,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G903" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29261,7 +29264,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G904" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29287,7 +29290,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G905" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29313,7 +29316,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G906" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29339,7 +29342,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G907" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29365,7 +29368,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G908" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29391,7 +29394,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G909" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29417,7 +29420,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G910" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29443,7 +29446,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G911" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29469,7 +29472,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G912" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29495,7 +29498,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G913" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29521,7 +29524,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G914" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29547,7 +29550,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G915" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29573,7 +29576,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G916" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29599,7 +29602,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G917" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29625,7 +29628,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G918" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29651,7 +29654,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G919" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29677,7 +29680,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G920" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29703,7 +29706,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G921" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -29729,7 +29732,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -29755,7 +29758,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G923" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -29781,7 +29784,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G924" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -29807,7 +29810,7 @@
         <v>17.5</v>
       </c>
       <c r="G925" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29833,7 +29836,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G926" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29859,7 +29862,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G927" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29885,7 +29888,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G928" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29911,7 +29914,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G929" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29937,7 +29940,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G930" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -29963,7 +29966,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G931" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -29989,7 +29992,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G932" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30015,7 +30018,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G933" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30041,7 +30044,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G934" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30067,7 +30070,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G935" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30093,7 +30096,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G936" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30119,7 +30122,7 @@
         <v>18.25</v>
       </c>
       <c r="G937" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30145,7 +30148,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G938" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30171,7 +30174,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G939" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30197,7 +30200,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G940" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30223,7 +30226,7 @@
         <v>18</v>
       </c>
       <c r="G941" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30249,7 +30252,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G942" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30275,7 +30278,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G943" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30301,7 +30304,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G944" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30327,7 +30330,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G945" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30353,7 +30356,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G946" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30379,7 +30382,7 @@
         <v>18.75</v>
       </c>
       <c r="G947" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30405,7 +30408,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G948" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -30431,7 +30434,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G949" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -30457,7 +30460,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G950" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30483,7 +30486,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G951" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30509,7 +30512,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G952" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -30535,7 +30538,7 @@
         <v>18.5</v>
       </c>
       <c r="G953" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30561,7 +30564,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G954" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30587,7 +30590,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G955" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -30613,7 +30616,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G956" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -30639,7 +30642,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G957" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30665,7 +30668,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G958" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30691,7 +30694,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G959" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -30717,7 +30720,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G960" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -30743,7 +30746,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G961" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -30769,7 +30772,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G962" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -30795,7 +30798,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G963" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30821,7 +30824,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30847,7 +30850,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G965" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30873,7 +30876,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G966" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30899,7 +30902,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G967" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -30925,7 +30928,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G968" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30951,7 +30954,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G969" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -30977,7 +30980,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G970" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31003,7 +31006,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G971" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31029,7 +31032,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G972" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31055,7 +31058,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G973" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31081,7 +31084,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G974" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31107,7 +31110,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G975" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31133,7 +31136,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G976" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31159,7 +31162,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31185,7 +31188,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31211,7 +31214,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G979" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31237,7 +31240,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G980" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31263,7 +31266,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G981" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31289,7 +31292,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G982" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31315,7 +31318,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G983" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31341,7 +31344,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G984" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31367,7 +31370,7 @@
         <v>18.75</v>
       </c>
       <c r="G985" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -31393,7 +31396,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G986" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -31419,7 +31422,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G987" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -31445,7 +31448,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G988" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31471,7 +31474,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G989" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -31497,7 +31500,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G990" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -31523,7 +31526,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G991" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -31549,7 +31552,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G992" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31575,7 +31578,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -31601,7 +31604,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G994" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31627,7 +31630,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G995" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -31653,7 +31656,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G996" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -31679,7 +31682,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G997" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -31705,7 +31708,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -31731,7 +31734,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G999" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -31757,7 +31760,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1000" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -31783,7 +31786,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1001" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -31809,7 +31812,7 @@
         <v>19.25</v>
       </c>
       <c r="G1002" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -31835,7 +31838,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1003" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -31861,7 +31864,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -31887,7 +31890,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1005" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31913,7 +31916,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1006" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -31939,7 +31942,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1007" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -31965,7 +31968,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -31991,7 +31994,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32017,7 +32020,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1010" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32043,7 +32046,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G1011" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32069,7 +32072,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1012" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32095,7 +32098,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1013" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32121,7 +32124,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1014" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32147,7 +32150,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1015" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32173,7 +32176,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1016" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32199,7 +32202,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1017" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32225,7 +32228,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G1018" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32251,7 +32254,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1019" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32277,7 +32280,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1020" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32303,7 +32306,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1021" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32329,7 +32332,7 @@
         <v>19.75</v>
       </c>
       <c r="G1022" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32355,7 +32358,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1023" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32381,7 +32384,7 @@
         <v>20.5</v>
       </c>
       <c r="G1024" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -32407,7 +32410,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1025" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -32433,7 +32436,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -32459,7 +32462,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1027" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -32485,7 +32488,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1028" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -32511,7 +32514,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -32537,7 +32540,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -32563,7 +32566,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1031" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32589,7 +32592,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G1032" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -32615,7 +32618,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1033" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -32641,7 +32644,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1034" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -32667,7 +32670,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1035" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -32693,7 +32696,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G1036" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -32719,7 +32722,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G1037" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -32745,7 +32748,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1038" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -32771,7 +32774,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1039" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -32797,7 +32800,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1040" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -32823,7 +32826,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1041" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -32849,7 +32852,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1042" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -32875,7 +32878,7 @@
         <v>22</v>
       </c>
       <c r="G1043" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -32901,7 +32904,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1044" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -32927,7 +32930,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1045" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -32953,7 +32956,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1046" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -32979,7 +32982,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1047" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -33005,7 +33008,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1048" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -33031,7 +33034,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G1049" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -33057,7 +33060,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G1050" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -33083,7 +33086,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G1051" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -33109,7 +33112,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1052" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -33135,7 +33138,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1053" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -33161,7 +33164,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -33187,7 +33190,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G1055" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -33213,7 +33216,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1056" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -33239,7 +33242,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -33265,7 +33268,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1058" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -33291,7 +33294,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1059" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -33317,7 +33320,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G1060" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -33343,7 +33346,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1061" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -33369,7 +33372,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1062" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -33395,7 +33398,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1063" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33421,7 +33424,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1064" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -33447,7 +33450,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1065" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -33473,7 +33476,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1066" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -33499,7 +33502,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1067" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -33525,7 +33528,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -33551,7 +33554,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1069" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -33577,7 +33580,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1070" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -33603,7 +33606,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1071" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -33629,7 +33632,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1072" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -33655,7 +33658,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1073" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -33681,7 +33684,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1074" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -33707,7 +33710,7 @@
         <v>15.25</v>
       </c>
       <c r="G1075" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -33733,7 +33736,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1076" t="s">
-        <v>606</v>
+        <v>778</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -34071,7 +34074,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1089" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -34201,7 +34204,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1094" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -34279,7 +34282,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1097" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -34383,7 +34386,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1101" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34461,7 +34464,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -34565,7 +34568,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G1108" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -70479,7 +70482,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6495833333</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>187936</v>
@@ -70500,6 +70503,32 @@
         <v>1803</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6494328704</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>204843</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>22.5599994659424</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>22.2800006866455</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>22.2800006866455</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>22.4799995422363</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1805</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="1806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="1807">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48755407333374</t>
+    <t xml:space="preserve">7.4875545501709</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43893337249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23837375640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04389333724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99527263641357</t>
+    <t xml:space="preserve">7.43893384933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23837423324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04389381408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99527215957642</t>
   </si>
   <si>
     <t xml:space="preserve">7.06212425231934</t>
@@ -65,28 +65,28 @@
     <t xml:space="preserve">7.22014093399048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17152166366577</t>
+    <t xml:space="preserve">7.17152118682861</t>
   </si>
   <si>
     <t xml:space="preserve">7.07428073883057</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84941053390503</t>
+    <t xml:space="preserve">6.84940958023071</t>
   </si>
   <si>
     <t xml:space="preserve">7.01350498199463</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75216960906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83725452423096</t>
+    <t xml:space="preserve">6.75216913223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83725547790527</t>
   </si>
   <si>
     <t xml:space="preserve">6.9709620475769</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09251260757446</t>
+    <t xml:space="preserve">7.09251308441162</t>
   </si>
   <si>
     <t xml:space="preserve">7.00742673873901</t>
@@ -95,211 +95,211 @@
     <t xml:space="preserve">7.00135040283203</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98919486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9284200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86156511306763</t>
+    <t xml:space="preserve">6.9891939163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92841863632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86156558990479</t>
   </si>
   <si>
     <t xml:space="preserve">6.5333776473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47867870330811</t>
+    <t xml:space="preserve">6.47868013381958</t>
   </si>
   <si>
     <t xml:space="preserve">6.61238574981689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5516095161438</t>
+    <t xml:space="preserve">6.55160903930664</t>
   </si>
   <si>
     <t xml:space="preserve">6.77647972106934</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94057464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87372064590454</t>
+    <t xml:space="preserve">6.94057416915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87372016906738</t>
   </si>
   <si>
     <t xml:space="preserve">6.63061809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78863525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58199739456177</t>
+    <t xml:space="preserve">6.78863477706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58199834823608</t>
   </si>
   <si>
     <t xml:space="preserve">6.7035493850708</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71570539474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8068675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91626310348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84333276748657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83117914199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87979888916016</t>
+    <t xml:space="preserve">6.71570444107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80686712265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91626405715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84333229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83117866516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87979793548584</t>
   </si>
   <si>
     <t xml:space="preserve">6.70962619781494</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74609231948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85548734664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86764335632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95272827148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0499701499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27483987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35992574691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34776926040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26876211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22622108459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11074447631836</t>
+    <t xml:space="preserve">6.74609279632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85548830032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8676438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95272874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04997062683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27483940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35992527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34777116775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26876306533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22621965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11074590682983</t>
   </si>
   <si>
     <t xml:space="preserve">7.03173732757568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08035802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05604696273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975353240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23229694366455</t>
+    <t xml:space="preserve">7.08035755157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05604648590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975305557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23229742050171</t>
   </si>
   <si>
     <t xml:space="preserve">7.1532883644104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11682415008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16544437408447</t>
+    <t xml:space="preserve">7.11682319641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16544389724731</t>
   </si>
   <si>
     <t xml:space="preserve">6.95880651473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93449640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803171157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90410900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96488332748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79471254348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76432371139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14113330841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02566003799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.157386302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13741254806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3105206489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25725698471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34381103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38375997543335</t>
+    <t xml:space="preserve">6.93449687957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803123474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90410947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96488428115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79471302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76432466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14113283157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02565860748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15738677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13741302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31052160263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25725746154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34381198883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38376045227051</t>
   </si>
   <si>
     <t xml:space="preserve">7.29720544815063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2505989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21730947494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062562942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23728322982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27723169326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22396612167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10412216186523</t>
+    <t xml:space="preserve">7.25059938430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21730852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062610626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23728370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27723217010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2239670753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10412311553955</t>
   </si>
   <si>
     <t xml:space="preserve">6.85777616500854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.658034324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60477018356323</t>
+    <t xml:space="preserve">6.65803337097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60477066040039</t>
   </si>
   <si>
     <t xml:space="preserve">6.47493839263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50822782516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95764493942261</t>
+    <t xml:space="preserve">6.50822734832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95764589309692</t>
   </si>
   <si>
     <t xml:space="preserve">6.93767213821411</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">6.82448530197144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88440704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47826671600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3218035697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56149291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69132423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81782722473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91769742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03754138946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78453636169434</t>
+    <t xml:space="preserve">6.88440656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47826623916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32180404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56149244308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69132471084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81782817840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91769695281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03754186630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78453683853149</t>
   </si>
   <si>
     <t xml:space="preserve">6.50489950180054</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">6.61808586120605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71795701980591</t>
+    <t xml:space="preserve">6.71795654296875</t>
   </si>
   <si>
     <t xml:space="preserve">6.6846661567688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73793077468872</t>
+    <t xml:space="preserve">6.73792886734009</t>
   </si>
   <si>
     <t xml:space="preserve">6.87774991989136</t>
@@ -359,52 +359,52 @@
     <t xml:space="preserve">6.75124740600586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79119443893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76456260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86443185806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77122163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89106607437134</t>
+    <t xml:space="preserve">6.79119491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76456308364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86443328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77122068405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89106559753418</t>
   </si>
   <si>
     <t xml:space="preserve">6.73127222061157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64471817016602</t>
+    <t xml:space="preserve">6.64471864700317</t>
   </si>
   <si>
     <t xml:space="preserve">6.63805961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75790548324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83114337921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80451059341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101263046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9643030166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74458837509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7112979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65137672424316</t>
+    <t xml:space="preserve">6.75790500640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83114290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80451107025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101358413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96430444717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74458932876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71129846572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65137577056885</t>
   </si>
   <si>
     <t xml:space="preserve">6.62807369232178</t>
@@ -413,76 +413,76 @@
     <t xml:space="preserve">6.6413893699646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62141418457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01756763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98427772521973</t>
+    <t xml:space="preserve">6.62141370773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01756811141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98427724838257</t>
   </si>
   <si>
     <t xml:space="preserve">7.01090955734253</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04419994354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17070245742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87109088897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92435646057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97762060165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83780193328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84445858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79785346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77787828445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59811210632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55150604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72461414337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67135095596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66469240188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60809946060181</t>
+    <t xml:space="preserve">7.04420042037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17070341110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87109136581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92435503005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97761964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83780097961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84445905685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79785299301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77787923812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59811162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55150508880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7246150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67135143280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66469287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60809993743896</t>
   </si>
   <si>
     <t xml:space="preserve">6.54484796524048</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45829343795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65470552444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67800712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4649510383606</t>
+    <t xml:space="preserve">6.45829296112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65470457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67800855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46495151519775</t>
   </si>
   <si>
     <t xml:space="preserve">6.13870763778687</t>
@@ -497,22 +497,22 @@
     <t xml:space="preserve">6.17865514755249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24856519699097</t>
+    <t xml:space="preserve">6.24856472015381</t>
   </si>
   <si>
     <t xml:space="preserve">6.13537788391113</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06546974182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16866970062256</t>
+    <t xml:space="preserve">6.06546878814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1686692237854</t>
   </si>
   <si>
     <t xml:space="preserve">6.15868186950684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14203643798828</t>
+    <t xml:space="preserve">6.14203691482544</t>
   </si>
   <si>
     <t xml:space="preserve">6.06213998794556</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">6.10874700546265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05881118774414</t>
+    <t xml:space="preserve">6.0588116645813</t>
   </si>
   <si>
     <t xml:space="preserve">6.02219247817993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0188627243042</t>
+    <t xml:space="preserve">6.01886320114136</t>
   </si>
   <si>
     <t xml:space="preserve">6.11873292922974</t>
@@ -542,106 +542,106 @@
     <t xml:space="preserve">6.12206220626831</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22193288803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21860408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35842323303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37839603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6247444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70464086532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85111713409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69798278808594</t>
+    <t xml:space="preserve">6.22193336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21860361099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35842227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37839698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62474346160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70464134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85111665725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69798231124878</t>
   </si>
   <si>
     <t xml:space="preserve">6.904381275177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89772367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99093532562256</t>
+    <t xml:space="preserve">6.89772319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9909348487854</t>
   </si>
   <si>
     <t xml:space="preserve">7.07749128341675</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91103982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07083034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13075494766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15072870254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18401956558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0974645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05085754394531</t>
+    <t xml:space="preserve">6.91103887557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07083129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1307544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15072965621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18401861190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09746503829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05085897445679</t>
   </si>
   <si>
     <t xml:space="preserve">7.35046911239624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27057313919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28389024734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30386447906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53023719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32383728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31717967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36378479003906</t>
+    <t xml:space="preserve">7.27057361602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2838888168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30386352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53023624420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32383632659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31717920303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36378526687622</t>
   </si>
   <si>
     <t xml:space="preserve">7.51692056655884</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59015941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000337600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992559432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77658414840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73663473129272</t>
+    <t xml:space="preserve">7.59015893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347557067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71000480651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992607116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77658462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73663520812988</t>
   </si>
   <si>
     <t xml:space="preserve">7.78990030288696</t>
@@ -650,70 +650,70 @@
     <t xml:space="preserve">7.75660943984985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82319021224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85648059844971</t>
+    <t xml:space="preserve">7.82318925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85648012161255</t>
   </si>
   <si>
     <t xml:space="preserve">7.86979579925537</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87645435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9030876159668</t>
+    <t xml:space="preserve">7.8764533996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308666229248</t>
   </si>
   <si>
     <t xml:space="preserve">7.96966648101807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94969272613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92306137084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96300888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72331857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62344932556152</t>
+    <t xml:space="preserve">7.9496922492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92306089401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96300983428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311243057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72332048416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62344884872437</t>
   </si>
   <si>
     <t xml:space="preserve">7.54355239868164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47031450271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63676500320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56352615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5701847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74329328536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80321645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89642810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94303512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84982204437256</t>
+    <t xml:space="preserve">7.47031402587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6367654800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56352758407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018518447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74329376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80321598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89642906188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94303607940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84982252120972</t>
   </si>
   <si>
     <t xml:space="preserve">8.06953716278076</t>
@@ -725,19 +725,19 @@
     <t xml:space="preserve">8.25009441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22926330566406</t>
+    <t xml:space="preserve">8.22926235198975</t>
   </si>
   <si>
     <t xml:space="preserve">8.31953907012939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35426330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28481769561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29870510101318</t>
+    <t xml:space="preserve">8.35426235198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28481864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29870700836182</t>
   </si>
   <si>
     <t xml:space="preserve">8.37509727478027</t>
@@ -755,88 +755,88 @@
     <t xml:space="preserve">8.45148658752441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68759918212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73621082305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62509822845459</t>
+    <t xml:space="preserve">8.68760013580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7362117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62510013580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.63898849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66676616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59732151031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72926616668701</t>
+    <t xml:space="preserve">8.6667652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68065547943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59732055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72926712036133</t>
   </si>
   <si>
     <t xml:space="preserve">8.69454479217529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61120891571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50704193115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59037590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52787494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54871082305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49315357208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51398658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46537399291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47231960296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61815452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65982341766357</t>
+    <t xml:space="preserve">8.61120986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50704288482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59037685394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52787590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54870986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49315166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5139856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46537494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47232055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61815357208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65982246398926</t>
   </si>
   <si>
     <t xml:space="preserve">8.6459321975708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40981864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43065357208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42370796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30565166473389</t>
+    <t xml:space="preserve">8.40981769561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4306526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42370891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30565071105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.5417652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57648754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60426712036133</t>
+    <t xml:space="preserve">8.57648849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6042652130127</t>
   </si>
   <si>
     <t xml:space="preserve">8.71537780761719</t>
@@ -845,28 +845,28 @@
     <t xml:space="preserve">8.88204574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0001049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15288257598877</t>
+    <t xml:space="preserve">9.00010395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15288352966309</t>
   </si>
   <si>
     <t xml:space="preserve">9.13204956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06954956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09038162231445</t>
+    <t xml:space="preserve">9.06954860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09038257598877</t>
   </si>
   <si>
     <t xml:space="preserve">9.00704860687256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95843696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0626049041748</t>
+    <t xml:space="preserve">8.95843601226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06260395050049</t>
   </si>
   <si>
     <t xml:space="preserve">9.1251049041748</t>
@@ -878,40 +878,40 @@
     <t xml:space="preserve">9.24316215515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29871940612793</t>
+    <t xml:space="preserve">9.29871845245361</t>
   </si>
   <si>
     <t xml:space="preserve">9.36816310882568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40983104705811</t>
+    <t xml:space="preserve">9.40983009338379</t>
   </si>
   <si>
     <t xml:space="preserve">9.41677570343018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32649612426758</t>
+    <t xml:space="preserve">9.32649707794189</t>
   </si>
   <si>
     <t xml:space="preserve">9.29177474975586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31260681152344</t>
+    <t xml:space="preserve">9.31260776519775</t>
   </si>
   <si>
     <t xml:space="preserve">9.45149707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47233009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43760776519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44455337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40288639068604</t>
+    <t xml:space="preserve">9.47233104705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43760871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44455242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4028844833374</t>
   </si>
   <si>
     <t xml:space="preserve">9.38899707794189</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">9.38205242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34038543701172</t>
+    <t xml:space="preserve">9.3403844833374</t>
   </si>
   <si>
     <t xml:space="preserve">9.34733009338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31955242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48622035980225</t>
+    <t xml:space="preserve">9.31955146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48621940612793</t>
   </si>
   <si>
     <t xml:space="preserve">9.75011157989502</t>
@@ -938,16 +938,16 @@
     <t xml:space="preserve">9.79177856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77788925170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8056697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72927761077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77094554901123</t>
+    <t xml:space="preserve">9.7778902053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80566883087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72927856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77094650268555</t>
   </si>
   <si>
     <t xml:space="preserve">9.76400089263916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">9.74316787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96539306640625</t>
+    <t xml:space="preserve">9.96539402008057</t>
   </si>
   <si>
     <t xml:space="preserve">10.0278930664062</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">9.93761444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834493637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1181716918945</t>
+    <t xml:space="preserve">10.0834503173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1181726455688</t>
   </si>
   <si>
     <t xml:space="preserve">10.1876163482666</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">10.5001211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5695676803589</t>
+    <t xml:space="preserve">10.5695667266846</t>
   </si>
   <si>
     <t xml:space="preserve">10.2292852401733</t>
@@ -989,10 +989,10 @@
     <t xml:space="preserve">10.3959531784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.423731803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5903987884521</t>
+    <t xml:space="preserve">10.4237327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5903997421265</t>
   </si>
   <si>
     <t xml:space="preserve">10.4931755065918</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">10.5626211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6251220703125</t>
+    <t xml:space="preserve">10.6251230239868</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042890548706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7015113830566</t>
+    <t xml:space="preserve">10.701512336731</t>
   </si>
   <si>
     <t xml:space="preserve">10.7779016494751</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8542919158936</t>
+    <t xml:space="preserve">10.8542909622192</t>
   </si>
   <si>
     <t xml:space="preserve">10.8334589004517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9029026031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0904054641724</t>
+    <t xml:space="preserve">10.9029035568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0904064178467</t>
   </si>
   <si>
     <t xml:space="preserve">11.1042938232422</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">11.1112384796143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6667900085449</t>
+    <t xml:space="preserve">10.6667881011963</t>
   </si>
   <si>
     <t xml:space="preserve">10.9723482131958</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">11.3959646224976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1529054641724</t>
+    <t xml:space="preserve">11.1529064178467</t>
   </si>
   <si>
     <t xml:space="preserve">11.0626277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2154064178467</t>
+    <t xml:space="preserve">11.2154054641724</t>
   </si>
   <si>
     <t xml:space="preserve">11.3126316070557</t>
@@ -1070,31 +1070,31 @@
     <t xml:space="preserve">10.9098472595215</t>
   </si>
   <si>
-    <t xml:space="preserve">10.736234664917</t>
+    <t xml:space="preserve">10.7362356185913</t>
   </si>
   <si>
     <t xml:space="preserve">10.8751249313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6945667266846</t>
+    <t xml:space="preserve">10.6945676803589</t>
   </si>
   <si>
     <t xml:space="preserve">10.5487327575684</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7848463058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8612375259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0695714950562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.187629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9306802749634</t>
+    <t xml:space="preserve">10.7848472595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8612356185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0695695877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9306812286377</t>
   </si>
   <si>
     <t xml:space="preserve">11.1598510742188</t>
@@ -1103,58 +1103,58 @@
     <t xml:space="preserve">11.4515199661255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5001316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4931879043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.62513256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7223567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709703445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7015247344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7293004989624</t>
+    <t xml:space="preserve">11.50013256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4931869506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6251335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7223558425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709693908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7015228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7293014526367</t>
   </si>
   <si>
     <t xml:space="preserve">11.7154130935669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6112442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4862442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5765237808228</t>
+    <t xml:space="preserve">11.6112432479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4862451553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5765228271484</t>
   </si>
   <si>
     <t xml:space="preserve">11.6806898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820753097534</t>
+    <t xml:space="preserve">11.3820743560791</t>
   </si>
   <si>
     <t xml:space="preserve">10.8681793212891</t>
   </si>
   <si>
-    <t xml:space="preserve">10.895959854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9862375259399</t>
+    <t xml:space="preserve">10.8959589004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9862365722656</t>
   </si>
   <si>
     <t xml:space="preserve">11.0834608078003</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292947769165</t>
+    <t xml:space="preserve">11.2292957305908</t>
   </si>
   <si>
     <t xml:space="preserve">11.2848529815674</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">11.3265190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.243185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5973567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7501344680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6181888580322</t>
+    <t xml:space="preserve">11.2431859970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5973558425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7501354217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6181898117065</t>
   </si>
   <si>
     <t xml:space="preserve">11.7987451553345</t>
@@ -1181,46 +1181,46 @@
     <t xml:space="preserve">11.6320781707764</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334703445435</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">12.1251392364502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9168033599854</t>
+    <t xml:space="preserve">11.916802406311</t>
   </si>
   <si>
     <t xml:space="preserve">12.6668109893799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1529293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3820991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3195972442627</t>
+    <t xml:space="preserve">13.152928352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.382098197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.319598197937</t>
   </si>
   <si>
     <t xml:space="preserve">13.3682088851929</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5765428543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5209884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2362623214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1668186187744</t>
+    <t xml:space="preserve">13.5765438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5209875106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2362632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1668176651001</t>
   </si>
   <si>
     <t xml:space="preserve">13.0487623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4237661361694</t>
+    <t xml:space="preserve">13.4237651824951</t>
   </si>
   <si>
     <t xml:space="preserve">13.0070943832397</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">13.354320526123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4584875106812</t>
+    <t xml:space="preserve">13.4584865570068</t>
   </si>
   <si>
     <t xml:space="preserve">13.7154359817505</t>
@@ -1238,22 +1238,22 @@
     <t xml:space="preserve">13.7918252944946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6807126998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9168281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9307146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1876516342163</t>
+    <t xml:space="preserve">13.6807136535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9168300628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9307165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1876525878906</t>
   </si>
   <si>
     <t xml:space="preserve">13.2987651824951</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3751554489136</t>
+    <t xml:space="preserve">13.3751544952393</t>
   </si>
   <si>
     <t xml:space="preserve">13.416820526123</t>
@@ -1265,34 +1265,34 @@
     <t xml:space="preserve">13.4862661361694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6112680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7362680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223796844482</t>
+    <t xml:space="preserve">13.6112689971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7362699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223787307739</t>
   </si>
   <si>
     <t xml:space="preserve">13.8196029663086</t>
   </si>
   <si>
-    <t xml:space="preserve">13.889048576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8543262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9029388427734</t>
+    <t xml:space="preserve">13.8890466690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8543272018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9029378890991</t>
   </si>
   <si>
     <t xml:space="preserve">14.0834970474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7987689971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0279378890991</t>
+    <t xml:space="preserve">13.798770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0279397964478</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057222366333</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">13.1945953369141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1112613677979</t>
+    <t xml:space="preserve">13.1112623214722</t>
   </si>
   <si>
     <t xml:space="preserve">13.1807069778442</t>
@@ -1310,7 +1310,7 @@
     <t xml:space="preserve">14.0200986862183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1486520767212</t>
+    <t xml:space="preserve">14.1486539840698</t>
   </si>
   <si>
     <t xml:space="preserve">13.8083591461182</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">13.2563285827637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1277732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3092641830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4605045318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4983148574829</t>
+    <t xml:space="preserve">13.1277723312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3092632293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4605054855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4983139038086</t>
   </si>
   <si>
     <t xml:space="preserve">13.4680662155151</t>
@@ -1349,49 +1349,49 @@
     <t xml:space="preserve">13.7478618621826</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4075698852539</t>
+    <t xml:space="preserve">13.4075689315796</t>
   </si>
   <si>
     <t xml:space="preserve">14.4889469146729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.473822593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6704387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158069610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755159378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.617504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7233724594116</t>
+    <t xml:space="preserve">14.4738216400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6704378128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158079147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755178451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6175022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.723370552063</t>
   </si>
   <si>
     <t xml:space="preserve">14.9351081848145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7460594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292417526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167119979858</t>
+    <t xml:space="preserve">14.7460584640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292436599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167129516602</t>
   </si>
   <si>
     <t xml:space="preserve">14.2998952865601</t>
   </si>
   <si>
-    <t xml:space="preserve">14.209153175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0654697418213</t>
+    <t xml:space="preserve">14.2091522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0654706954956</t>
   </si>
   <si>
     <t xml:space="preserve">14.1637773513794</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">14.0427827835083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1713380813599</t>
+    <t xml:space="preserve">14.1713399887085</t>
   </si>
   <si>
     <t xml:space="preserve">14.2847709655762</t>
@@ -1409,37 +1409,37 @@
     <t xml:space="preserve">14.6250648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7536211013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.67799949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7914295196533</t>
+    <t xml:space="preserve">14.7536182403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6779985427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.791428565979</t>
   </si>
   <si>
     <t xml:space="preserve">14.8443641662598</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8746147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8368053436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7611808776855</t>
+    <t xml:space="preserve">14.8746137619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8368034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7611837387085</t>
   </si>
   <si>
     <t xml:space="preserve">14.6553134918213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5494432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6401891708374</t>
+    <t xml:space="preserve">14.5494441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099405288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6401882171631</t>
   </si>
   <si>
     <t xml:space="preserve">14.5721302032471</t>
@@ -1448,58 +1448,58 @@
     <t xml:space="preserve">14.5191965103149</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2393999099731</t>
+    <t xml:space="preserve">14.2393989562988</t>
   </si>
   <si>
     <t xml:space="preserve">14.0049743652344</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9217910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.914231300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.269645690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3982038497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9898509979248</t>
+    <t xml:space="preserve">13.9217920303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9142293930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2696475982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3982028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9898519515991</t>
   </si>
   <si>
     <t xml:space="preserve">13.6646795272827</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6722412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5814971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7705488204956</t>
+    <t xml:space="preserve">13.6722421646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5814962387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705497741699</t>
   </si>
   <si>
     <t xml:space="preserve">13.6268701553345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5210008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495561599731</t>
+    <t xml:space="preserve">13.5209999084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495542526245</t>
   </si>
   <si>
     <t xml:space="preserve">13.5512495040894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4907541275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4756269454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5058765411377</t>
+    <t xml:space="preserve">13.4907512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4756288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.505877494812</t>
   </si>
   <si>
     <t xml:space="preserve">13.3470726013184</t>
@@ -1514,37 +1514,37 @@
     <t xml:space="preserve">13.8310480117798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6344318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5663747787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5436878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3773221969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1958332061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2714519500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3395109176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3546352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2638902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4529428482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3319482803345</t>
+    <t xml:space="preserve">13.6344327926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5663738250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5436859130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3773231506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1958341598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2714500427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3395099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3546361923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2638912200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4529447555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3319473266602</t>
   </si>
   <si>
     <t xml:space="preserve">12.9311599731445</t>
@@ -1553,40 +1553,40 @@
     <t xml:space="preserve">13.0219030380249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8101644515991</t>
+    <t xml:space="preserve">12.8101654052734</t>
   </si>
   <si>
     <t xml:space="preserve">12.5530548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7421073913574</t>
+    <t xml:space="preserve">12.7421083450317</t>
   </si>
   <si>
     <t xml:space="preserve">12.6513614654541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3848857879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.120210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9614067077637</t>
+    <t xml:space="preserve">13.3848838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1202096939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9614057540894</t>
   </si>
   <si>
     <t xml:space="preserve">12.5681800842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.439624786377</t>
+    <t xml:space="preserve">12.4396228790283</t>
   </si>
   <si>
     <t xml:space="preserve">12.6211137771606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4018115997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4925575256348</t>
+    <t xml:space="preserve">12.4018106460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4925565719604</t>
   </si>
   <si>
     <t xml:space="preserve">12.4698715209961</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">12.1522636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6286773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643798828125</t>
+    <t xml:space="preserve">12.6286764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437997817993</t>
   </si>
   <si>
     <t xml:space="preserve">12.825288772583</t>
@@ -1616,19 +1616,19 @@
     <t xml:space="preserve">12.8479747772217</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7572317123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8177289962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7799167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4471845626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4244995117188</t>
+    <t xml:space="preserve">12.7572298049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8177270889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.77991771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4471836090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4245004653931</t>
   </si>
   <si>
     <t xml:space="preserve">12.2581329345703</t>
@@ -1646,25 +1646,25 @@
     <t xml:space="preserve">12.0312700271606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2505712509155</t>
+    <t xml:space="preserve">12.2505722045898</t>
   </si>
   <si>
     <t xml:space="preserve">12.1068925857544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2278861999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0463962554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.099328994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7968454360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8800296783447</t>
+    <t xml:space="preserve">12.2278852462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0463972091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0993309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7968463897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8800287246704</t>
   </si>
   <si>
     <t xml:space="preserve">12.5379295349121</t>
@@ -1673,22 +1673,22 @@
     <t xml:space="preserve">12.2656946182251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7950410842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2941370010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1126499176025</t>
+    <t xml:space="preserve">12.7950420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2941389083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1126480102539</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538440704346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5833024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4774332046509</t>
+    <t xml:space="preserve">12.5833034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4774341583252</t>
   </si>
   <si>
     <t xml:space="preserve">12.5757398605347</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">13.0143413543701</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8328504562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9084720611572</t>
+    <t xml:space="preserve">12.8328514099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9084711074829</t>
   </si>
   <si>
     <t xml:space="preserve">13.0521516799927</t>
@@ -1715,13 +1715,13 @@
     <t xml:space="preserve">13.0975246429443</t>
   </si>
   <si>
-    <t xml:space="preserve">13.006781578064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2260808944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2185173034668</t>
+    <t xml:space="preserve">13.0067806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2260799407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2185163497925</t>
   </si>
   <si>
     <t xml:space="preserve">12.9009103775024</t>
@@ -1730,49 +1730,49 @@
     <t xml:space="preserve">13.0370283126831</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7647914886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.029465675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109537124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2336416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9235963821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.870662689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8933477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882696151733</t>
+    <t xml:space="preserve">12.7647905349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0294647216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.233642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9235954284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8706617355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.893346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.188268661499</t>
   </si>
   <si>
     <t xml:space="preserve">13.1353349685669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9689674377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1050853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3017024993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8857870101929</t>
+    <t xml:space="preserve">12.9689683914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3017015457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8857879638672</t>
   </si>
   <si>
     <t xml:space="preserve">12.6891717910767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6967334747314</t>
+    <t xml:space="preserve">12.6967344284058</t>
   </si>
   <si>
     <t xml:space="preserve">12.6362361907959</t>
@@ -1781,46 +1781,46 @@
     <t xml:space="preserve">12.6664848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5152425765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3110675811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2430095672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0388326644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6589241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7269811630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7496681213379</t>
+    <t xml:space="preserve">12.5152454376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3110685348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2430086135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0388317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6589231491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7269830703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7496690750122</t>
   </si>
   <si>
     <t xml:space="preserve">12.3186311721802</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1900758743286</t>
+    <t xml:space="preserve">12.1900749206543</t>
   </si>
   <si>
     <t xml:space="preserve">12.1976366043091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1749515533447</t>
+    <t xml:space="preserve">12.1749505996704</t>
   </si>
   <si>
     <t xml:space="preserve">12.2732572555542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1598262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203226089478</t>
+    <t xml:space="preserve">12.1598281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203216552734</t>
   </si>
   <si>
     <t xml:space="preserve">12.280818939209</t>
@@ -1829,28 +1829,28 @@
     <t xml:space="preserve">12.303505897522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631010055542</t>
+    <t xml:space="preserve">12.8631000518799</t>
   </si>
   <si>
     <t xml:space="preserve">13.2902870178223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4485054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5988101959229</t>
+    <t xml:space="preserve">13.4485063552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988111495972</t>
   </si>
   <si>
     <t xml:space="preserve">13.6146335601807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9548015594482</t>
+    <t xml:space="preserve">13.9548025131226</t>
   </si>
   <si>
     <t xml:space="preserve">13.978533744812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8598718643188</t>
+    <t xml:space="preserve">13.8598709106445</t>
   </si>
   <si>
     <t xml:space="preserve">13.7491178512573</t>
@@ -1859,79 +1859,79 @@
     <t xml:space="preserve">13.7332973480225</t>
   </si>
   <si>
-    <t xml:space="preserve">13.772852897644</t>
+    <t xml:space="preserve">13.7728509902954</t>
   </si>
   <si>
     <t xml:space="preserve">13.8124046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7174768447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6383666992188</t>
+    <t xml:space="preserve">13.7174739837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6383657455444</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620988845825</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5750799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1446628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2395944595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5085649490356</t>
+    <t xml:space="preserve">13.5750780105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1446619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.239595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5085639953613</t>
   </si>
   <si>
     <t xml:space="preserve">14.4690113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5955839157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7221603393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.674693107605</t>
+    <t xml:space="preserve">14.5955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7221593856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.674690246582</t>
   </si>
   <si>
     <t xml:space="preserve">14.1763067245483</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1604852676392</t>
+    <t xml:space="preserve">14.1604862213135</t>
   </si>
   <si>
     <t xml:space="preserve">14.0813760757446</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0339107513428</t>
+    <t xml:space="preserve">14.0339117050171</t>
   </si>
   <si>
     <t xml:space="preserve">14.4373655319214</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6984252929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6114044189453</t>
+    <t xml:space="preserve">14.6984262466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.611403465271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4136333465576</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6272287368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.109790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0939702987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911289215088</t>
+    <t xml:space="preserve">14.6272277832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1097898483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0939693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911279678345</t>
   </si>
   <si>
     <t xml:space="preserve">14.9436626434326</t>
@@ -1940,43 +1940,43 @@
     <t xml:space="preserve">14.9120187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8724641799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.864556312561</t>
+    <t xml:space="preserve">14.8724632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8645553588867</t>
   </si>
   <si>
     <t xml:space="preserve">14.6430492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2870588302612</t>
+    <t xml:space="preserve">14.2870597839355</t>
   </si>
   <si>
     <t xml:space="preserve">14.3266143798828</t>
   </si>
   <si>
-    <t xml:space="preserve">14.215859413147</t>
+    <t xml:space="preserve">14.2158584594727</t>
   </si>
   <si>
     <t xml:space="preserve">14.2475051879883</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0260000228882</t>
+    <t xml:space="preserve">14.0259990692139</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576438903809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.606725692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8677825927734</t>
+    <t xml:space="preserve">13.6067237854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8677835464478</t>
   </si>
   <si>
     <t xml:space="preserve">14.2000408172607</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2949686050415</t>
+    <t xml:space="preserve">14.2949695587158</t>
   </si>
   <si>
     <t xml:space="preserve">14.2079496383667</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">13.5671672821045</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6700105667114</t>
+    <t xml:space="preserve">13.6700096130371</t>
   </si>
   <si>
     <t xml:space="preserve">13.519702911377</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">13.8203153610229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9073352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8440494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5592575073242</t>
+    <t xml:space="preserve">13.9073371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8440504074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5592565536499</t>
   </si>
   <si>
     <t xml:space="preserve">13.7886734008789</t>
@@ -2021,109 +2021,109 @@
     <t xml:space="preserve">13.9310703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0892868041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3028793334961</t>
+    <t xml:space="preserve">14.0892877578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3028812408447</t>
   </si>
   <si>
     <t xml:space="preserve">14.4848299026489</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6588697433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2316846847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1130208969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5876741409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.975305557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8566446304321</t>
+    <t xml:space="preserve">14.6588716506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633275985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2316827774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1130180358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5876722335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9753046035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8566427230835</t>
   </si>
   <si>
     <t xml:space="preserve">14.9990367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.832911491394</t>
+    <t xml:space="preserve">14.8329095840454</t>
   </si>
   <si>
     <t xml:space="preserve">14.745888710022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0227718353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7379789352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854471206665</t>
+    <t xml:space="preserve">15.0227708816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.737979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854461669922</t>
   </si>
   <si>
     <t xml:space="preserve">14.6905126571655</t>
   </si>
   <si>
-    <t xml:space="preserve">14.635139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.540207862854</t>
+    <t xml:space="preserve">14.6351375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5402069091797</t>
   </si>
   <si>
     <t xml:space="preserve">14.1525745391846</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5164747238159</t>
+    <t xml:space="preserve">14.5164756774902</t>
   </si>
   <si>
     <t xml:space="preserve">14.4294548034668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1921300888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0971965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2712364196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2791481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057216644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3899021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3424348831177</t>
+    <t xml:space="preserve">14.1921291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0971994400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2712383270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.279146194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057235717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3899030685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.342432975769</t>
   </si>
   <si>
     <t xml:space="preserve">14.3582563400269</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4610986709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0069484710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9515752792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5322952270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3345251083374</t>
+    <t xml:space="preserve">14.4610977172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0069465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9515743255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5322961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3345241546631</t>
   </si>
   <si>
     <t xml:space="preserve">14.3740787506104</t>
@@ -2132,19 +2132,19 @@
     <t xml:space="preserve">14.3819885253906</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6509599685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0860586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8170881271362</t>
+    <t xml:space="preserve">14.6509590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0860557556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8170871734619</t>
   </si>
   <si>
     <t xml:space="preserve">14.6193170547485</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0544147491455</t>
+    <t xml:space="preserve">15.0544157028198</t>
   </si>
   <si>
     <t xml:space="preserve">15.4895143508911</t>
@@ -2153,25 +2153,25 @@
     <t xml:space="preserve">15.8692350387573</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7189311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.307562828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3471193313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081781387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2284536361694</t>
+    <t xml:space="preserve">15.7189302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3075647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3471183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081762313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2284545898438</t>
   </si>
   <si>
     <t xml:space="preserve">15.1572561264038</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1889009475708</t>
+    <t xml:space="preserve">15.1888990402222</t>
   </si>
   <si>
     <t xml:space="preserve">15.1414337158203</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">15.3866729736328</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2838296890259</t>
+    <t xml:space="preserve">15.2838315963745</t>
   </si>
   <si>
     <t xml:space="preserve">15.3154745101929</t>
@@ -2189,43 +2189,43 @@
     <t xml:space="preserve">15.7505731582642</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7110185623169</t>
+    <t xml:space="preserve">15.7110176086426</t>
   </si>
   <si>
     <t xml:space="preserve">15.6160869598389</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4420471191406</t>
+    <t xml:space="preserve">15.4420490264893</t>
   </si>
   <si>
     <t xml:space="preserve">15.2047214508057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.236364364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1651659011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.402494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6239967346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7743072509766</t>
+    <t xml:space="preserve">15.2363662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1651678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4024934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6239986419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7743053436279</t>
   </si>
   <si>
     <t xml:space="preserve">16.2173156738281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5179271697998</t>
+    <t xml:space="preserve">16.5179290771484</t>
   </si>
   <si>
     <t xml:space="preserve">16.296422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5653953552246</t>
+    <t xml:space="preserve">16.5653915405273</t>
   </si>
   <si>
     <t xml:space="preserve">17.0400466918945</t>
@@ -2240,19 +2240,19 @@
     <t xml:space="preserve">17.0558700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9609394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6919689178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8976516723633</t>
+    <t xml:space="preserve">16.9609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.691967010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8976497650146</t>
   </si>
   <si>
     <t xml:space="preserve">17.1982650756836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8818302154541</t>
+    <t xml:space="preserve">16.8818283081055</t>
   </si>
   <si>
     <t xml:space="preserve">17.2299098968506</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">17.4514141082764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6096305847168</t>
+    <t xml:space="preserve">17.6096324920654</t>
   </si>
   <si>
     <t xml:space="preserve">17.4039478302002</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">17.5305233001709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8786010742188</t>
+    <t xml:space="preserve">17.8785991668701</t>
   </si>
   <si>
     <t xml:space="preserve">18.1792125701904</t>
@@ -2288,19 +2288,19 @@
     <t xml:space="preserve">18.2583236694336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3690776824951</t>
+    <t xml:space="preserve">18.3690738677979</t>
   </si>
   <si>
     <t xml:space="preserve">18.289966583252</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2108592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3723030090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4830570220947</t>
+    <t xml:space="preserve">18.2108573913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3723049163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4830589294434</t>
   </si>
   <si>
     <t xml:space="preserve">17.7045612335205</t>
@@ -2312,22 +2312,22 @@
     <t xml:space="preserve">16.5021076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4988784790039</t>
+    <t xml:space="preserve">17.4988803863525</t>
   </si>
   <si>
     <t xml:space="preserve">17.1508007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1701707839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0213165283203</t>
+    <t xml:space="preserve">11.1701698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0213174819946</t>
   </si>
   <si>
     <t xml:space="preserve">11.8267736434937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6210918426514</t>
+    <t xml:space="preserve">11.6210908889771</t>
   </si>
   <si>
     <t xml:space="preserve">11.6290016174316</t>
@@ -2339,25 +2339,25 @@
     <t xml:space="preserve">10.9882202148438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4470510482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0245456695557</t>
+    <t xml:space="preserve">11.4470520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0245447158813</t>
   </si>
   <si>
     <t xml:space="preserve">12.0641002655029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631000518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4200897216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1748523712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9026546478271</t>
+    <t xml:space="preserve">12.8630990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.420090675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1748533248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9026536941528</t>
   </si>
   <si>
     <t xml:space="preserve">12.6969699859619</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">13.4722385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">13.314019203186</t>
+    <t xml:space="preserve">13.3140211105347</t>
   </si>
   <si>
     <t xml:space="preserve">13.2349109649658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1241588592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4089527130127</t>
+    <t xml:space="preserve">13.1241598129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4089508056641</t>
   </si>
   <si>
     <t xml:space="preserve">13.4564170837402</t>
@@ -2387,28 +2387,28 @@
     <t xml:space="preserve">13.1004266738892</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0925140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687828063965</t>
+    <t xml:space="preserve">13.0925159454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2507333755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687818527222</t>
   </si>
   <si>
     <t xml:space="preserve">13.3614845275879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4326820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5038814544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9738512039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9342985153198</t>
+    <t xml:space="preserve">13.4326829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5038795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9738521575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9342975616455</t>
   </si>
   <si>
     <t xml:space="preserve">13.0371389389038</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">13.1795349121094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2111806869507</t>
+    <t xml:space="preserve">13.2111797332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.543436050415</t>
@@ -2429,40 +2429,40 @@
     <t xml:space="preserve">13.7095632553101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2056894302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1560764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2883768081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0490999221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2475509643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2971620559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1240348815918</t>
+    <t xml:space="preserve">14.2056884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418655395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1560773849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966470718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2883758544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0491018295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2475500106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2971611022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1240367889404</t>
   </si>
   <si>
     <t xml:space="preserve">16.4134407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5043983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1405754089355</t>
+    <t xml:space="preserve">16.5043964385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1405735015869</t>
   </si>
   <si>
     <t xml:space="preserve">16.0909614562988</t>
@@ -2471,70 +2471,70 @@
     <t xml:space="preserve">16.190185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286874771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3467750549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2144737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2806253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8346290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.652717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692571640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5782985687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932863235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8594369888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633108139038</t>
+    <t xml:space="preserve">15.5865659713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.346773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2144746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2806234359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8346300125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6527166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5782995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932844161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8594379425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633127212524</t>
   </si>
   <si>
     <t xml:space="preserve">15.429461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5617589950562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8677043914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.330753326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0501346588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2651233673096</t>
+    <t xml:space="preserve">15.5617599487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8677034378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3307552337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0501365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651214599609</t>
   </si>
   <si>
     <t xml:space="preserve">16.868221282959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9509086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1162872314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3312702178955</t>
+    <t xml:space="preserve">16.9509105682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.116283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3312683105469</t>
   </si>
   <si>
     <t xml:space="preserve">17.51318359375</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">17.2816562652588</t>
   </si>
   <si>
-    <t xml:space="preserve">17.314733505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4304943084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3643455505371</t>
+    <t xml:space="preserve">17.3147354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4304962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3643474578857</t>
   </si>
   <si>
     <t xml:space="preserve">17.3808841705322</t>
@@ -2564,46 +2564,46 @@
     <t xml:space="preserve">16.9839839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8186092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9012985229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8516845703125</t>
+    <t xml:space="preserve">16.8186111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012966156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8516826629639</t>
   </si>
   <si>
     <t xml:space="preserve">16.7524604797363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0170612335205</t>
+    <t xml:space="preserve">17.0170574188232</t>
   </si>
   <si>
     <t xml:space="preserve">17.4635715484619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5958728790283</t>
+    <t xml:space="preserve">17.5958709716797</t>
   </si>
   <si>
     <t xml:space="preserve">17.4801063537598</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8439331054688</t>
+    <t xml:space="preserve">17.8439311981201</t>
   </si>
   <si>
     <t xml:space="preserve">17.9266204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.992769241333</t>
+    <t xml:space="preserve">17.9927711486816</t>
   </si>
   <si>
     <t xml:space="preserve">18.0919933319092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4227466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4723587036133</t>
+    <t xml:space="preserve">18.4227447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4723567962646</t>
   </si>
   <si>
     <t xml:space="preserve">18.1581439971924</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">18.025842666626</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0754566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5054302215576</t>
+    <t xml:space="preserve">18.0754585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5054321289062</t>
   </si>
   <si>
     <t xml:space="preserve">18.389669418335</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">18.191219329834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0589218139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.910083770752</t>
+    <t xml:space="preserve">18.0589199066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9100818634033</t>
   </si>
   <si>
     <t xml:space="preserve">18.2408313751221</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">18.3069801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620216369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7943210601807</t>
+    <t xml:space="preserve">17.6620197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.794319152832</t>
   </si>
   <si>
     <t xml:space="preserve">17.7116317749023</t>
@@ -2669,25 +2669,25 @@
     <t xml:space="preserve">17.7447090148926</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6046581268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7700309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3731307983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6542701721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7534961700439</t>
+    <t xml:space="preserve">18.6046562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7700328826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3731327056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6542682647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7534942626953</t>
   </si>
   <si>
     <t xml:space="preserve">18.4062061309814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1416091918945</t>
+    <t xml:space="preserve">18.1416072845459</t>
   </si>
   <si>
     <t xml:space="preserve">17.9431571960449</t>
@@ -2705,46 +2705,46 @@
     <t xml:space="preserve">17.1989707946777</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6366958618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2894115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9503936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0413475036621</t>
+    <t xml:space="preserve">16.636697769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2894096374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9503927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0413494110107</t>
   </si>
   <si>
     <t xml:space="preserve">16.5374717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0832080841064</t>
+    <t xml:space="preserve">17.0832099914551</t>
   </si>
   <si>
     <t xml:space="preserve">17.5627956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.06667137146</t>
+    <t xml:space="preserve">17.0666694641113</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155094146729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1658973693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0005187988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178333282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7028484344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8847579956055</t>
+    <t xml:space="preserve">17.1658954620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0005226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178314208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7028465270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8847599029541</t>
   </si>
   <si>
     <t xml:space="preserve">16.7855339050293</t>
@@ -2756,142 +2756,142 @@
     <t xml:space="preserve">16.4795913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0335960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1328182220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1824340820312</t>
+    <t xml:space="preserve">17.033597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1328201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1824359893799</t>
   </si>
   <si>
     <t xml:space="preserve">17.546257019043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1746807098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.869255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1669311523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3488426208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0599555969238</t>
+    <t xml:space="preserve">18.1746845245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8692569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1669292449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.348840713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0599536895752</t>
   </si>
   <si>
     <t xml:space="preserve">19.960729598999</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5064640045166</t>
+    <t xml:space="preserve">20.5064659118652</t>
   </si>
   <si>
     <t xml:space="preserve">20.6883792877197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7049160003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6718425750732</t>
+    <t xml:space="preserve">20.7049140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.671838760376</t>
   </si>
   <si>
     <t xml:space="preserve">20.8206787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7545280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9364414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7214527130127</t>
+    <t xml:space="preserve">20.7545299530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9364395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7214508056641</t>
   </si>
   <si>
     <t xml:space="preserve">21.0025901794434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1845016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6806240081787</t>
+    <t xml:space="preserve">21.1845035552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6806259155273</t>
   </si>
   <si>
     <t xml:space="preserve">22.1767501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9948387145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5571117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2175788879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9033660888672</t>
+    <t xml:space="preserve">21.994836807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5571136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2175769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9033641815186</t>
   </si>
   <si>
     <t xml:space="preserve">20.9529781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3002662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5979385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4160270690918</t>
+    <t xml:space="preserve">21.3002643585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5979404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4160251617432</t>
   </si>
   <si>
     <t xml:space="preserve">21.8956127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5152530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8460025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.160213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5317878723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3664169311523</t>
+    <t xml:space="preserve">21.515251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8460006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1602115631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5317897796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3664150238037</t>
   </si>
   <si>
     <t xml:space="preserve">20.7379913330078</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5726165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2506523132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7876033782959</t>
+    <t xml:space="preserve">20.5726146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2506542205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7876014709473</t>
   </si>
   <si>
     <t xml:space="preserve">20.2584037780762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6134395599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1922550201416</t>
+    <t xml:space="preserve">19.6134433746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.192253112793</t>
   </si>
   <si>
     <t xml:space="preserve">19.3323040008545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9354057312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2749423980713</t>
+    <t xml:space="preserve">18.9354038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2749404907227</t>
   </si>
   <si>
     <t xml:space="preserve">21.2010383605957</t>
@@ -2906,43 +2906,43 @@
     <t xml:space="preserve">20.0103416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465187072754</t>
+    <t xml:space="preserve">19.6465167999268</t>
   </si>
   <si>
     <t xml:space="preserve">20.2253265380859</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3410930633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5560760498047</t>
+    <t xml:space="preserve">20.3410892486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5560779571533</t>
   </si>
   <si>
     <t xml:space="preserve">20.638765335083</t>
   </si>
   <si>
-    <t xml:space="preserve">21.035665512085</t>
+    <t xml:space="preserve">21.0356636047363</t>
   </si>
   <si>
     <t xml:space="preserve">21.34987449646</t>
   </si>
   <si>
-    <t xml:space="preserve">21.085277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0191268920898</t>
+    <t xml:space="preserve">21.0852756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0191287994385</t>
   </si>
   <si>
     <t xml:space="preserve">20.8702907562256</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1018142700195</t>
+    <t xml:space="preserve">21.1018161773682</t>
   </si>
   <si>
     <t xml:space="preserve">20.8868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5230045318604</t>
+    <t xml:space="preserve">20.5230026245117</t>
   </si>
   <si>
     <t xml:space="preserve">20.6056900024414</t>
@@ -2951,10 +2951,10 @@
     <t xml:space="preserve">20.0268783569336</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1095657348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1514282226562</t>
+    <t xml:space="preserve">20.1095676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1514263153076</t>
   </si>
   <si>
     <t xml:space="preserve">20.6222286224365</t>
@@ -2966,13 +2966,13 @@
     <t xml:space="preserve">20.4072399139404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9772663116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3907051086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1261043548584</t>
+    <t xml:space="preserve">19.9772644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3907032012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1261024475098</t>
   </si>
   <si>
     <t xml:space="preserve">20.0764904022217</t>
@@ -2981,34 +2981,34 @@
     <t xml:space="preserve">20.2914791107178</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2661552429199</t>
+    <t xml:space="preserve">19.2661533355713</t>
   </si>
   <si>
     <t xml:space="preserve">19.7622776031494</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8780422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3484592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3314075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0756340026855</t>
+    <t xml:space="preserve">19.878044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3484573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3314094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0756320953369</t>
   </si>
   <si>
     <t xml:space="preserve">21.2461490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.229097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1779441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4337158203125</t>
+    <t xml:space="preserve">21.2290992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.177942276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4337139129639</t>
   </si>
   <si>
     <t xml:space="preserve">21.4848709106445</t>
@@ -3017,10 +3017,10 @@
     <t xml:space="preserve">21.6042308807373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6212825775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3143558502197</t>
+    <t xml:space="preserve">21.621280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3143539428711</t>
   </si>
   <si>
     <t xml:space="preserve">21.570125579834</t>
@@ -3029,19 +3029,19 @@
     <t xml:space="preserve">22.388599395752</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9793643951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0646190643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.030517578125</t>
+    <t xml:space="preserve">21.979362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0646171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0305194854736</t>
   </si>
   <si>
     <t xml:space="preserve">21.7235908508301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6553840637207</t>
+    <t xml:space="preserve">21.6553859710693</t>
   </si>
   <si>
     <t xml:space="preserve">21.7406406402588</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">21.3655071258545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4507656097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.672435760498</t>
+    <t xml:space="preserve">21.4507675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6724376678467</t>
   </si>
   <si>
     <t xml:space="preserve">22.0987243652344</t>
@@ -3065,55 +3065,55 @@
     <t xml:space="preserve">21.9964141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3825607299805</t>
+    <t xml:space="preserve">21.3825626373291</t>
   </si>
   <si>
     <t xml:space="preserve">20.8369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8710155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.888069152832</t>
+    <t xml:space="preserve">20.8710174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8880672454834</t>
   </si>
   <si>
     <t xml:space="preserve">21.7065391540527</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9623146057129</t>
+    <t xml:space="preserve">21.9623126983643</t>
   </si>
   <si>
     <t xml:space="preserve">22.1328258514404</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2351341247559</t>
+    <t xml:space="preserve">22.2351360321045</t>
   </si>
   <si>
     <t xml:space="preserve">22.47385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2692375183105</t>
+    <t xml:space="preserve">22.2692394256592</t>
   </si>
   <si>
     <t xml:space="preserve">20.7346038818359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5470371246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2632026672363</t>
+    <t xml:space="preserve">20.5470390319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2632007598877</t>
   </si>
   <si>
     <t xml:space="preserve">21.1097373962402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1608924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5530776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7747459411621</t>
+    <t xml:space="preserve">21.1608905792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5530757904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7747478485107</t>
   </si>
   <si>
     <t xml:space="preserve">21.2973022460938</t>
@@ -3125,91 +3125,91 @@
     <t xml:space="preserve">20.8539638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0074272155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2802505493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9282093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8600006103516</t>
+    <t xml:space="preserve">21.0074291229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.280252456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9282073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8600025177002</t>
   </si>
   <si>
     <t xml:space="preserve">21.8088474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8941040039062</t>
+    <t xml:space="preserve">21.8941059112549</t>
   </si>
   <si>
     <t xml:space="preserve">21.7576942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3996124267578</t>
+    <t xml:space="preserve">21.3996143341064</t>
   </si>
   <si>
     <t xml:space="preserve">21.9111576080322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5079593658447</t>
+    <t xml:space="preserve">22.5079574584961</t>
   </si>
   <si>
     <t xml:space="preserve">22.1669292449951</t>
   </si>
   <si>
-    <t xml:space="preserve">22.081672668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0134658813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4909057617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4227027893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2521877288818</t>
+    <t xml:space="preserve">22.0816707611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.013463973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4909076690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.422700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2521858215332</t>
   </si>
   <si>
     <t xml:space="preserve">22.5761642456055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6614208221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7296276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1729679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7697677612305</t>
+    <t xml:space="preserve">22.6614227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7296257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.172966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7697696685791</t>
   </si>
   <si>
     <t xml:space="preserve">23.4628429412842</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3775863647461</t>
+    <t xml:space="preserve">23.3775844573975</t>
   </si>
   <si>
     <t xml:space="preserve">23.9232330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">25.219144821167</t>
+    <t xml:space="preserve">25.2191429138184</t>
   </si>
   <si>
     <t xml:space="preserve">25.4749164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8329982757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7818450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1740283966064</t>
+    <t xml:space="preserve">25.8329963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7818431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1740303039551</t>
   </si>
   <si>
     <t xml:space="preserve">26.3274898529053</t>
@@ -3218,52 +3218,52 @@
     <t xml:space="preserve">26.6003150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6173686981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7708301544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6855716705322</t>
+    <t xml:space="preserve">26.6173667907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7708282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6855735778809</t>
   </si>
   <si>
     <t xml:space="preserve">25.969409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7196769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3615951538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3104400634766</t>
+    <t xml:space="preserve">26.7196750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3615970611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3104419708252</t>
   </si>
   <si>
     <t xml:space="preserve">26.5491600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2251815795898</t>
+    <t xml:space="preserve">26.2251834869385</t>
   </si>
   <si>
     <t xml:space="preserve">25.5431232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0315799713135</t>
+    <t xml:space="preserve">25.0315780639648</t>
   </si>
   <si>
     <t xml:space="preserve">24.826961517334</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0145263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1679916381836</t>
+    <t xml:space="preserve">25.0145282745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.167989730835</t>
   </si>
   <si>
     <t xml:space="preserve">25.1168346405029</t>
   </si>
   <si>
-    <t xml:space="preserve">24.809907913208</t>
+    <t xml:space="preserve">24.8099117279053</t>
   </si>
   <si>
     <t xml:space="preserve">24.8440113067627</t>
@@ -3296,10 +3296,10 @@
     <t xml:space="preserve">24.1960563659668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3495178222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9402828216553</t>
+    <t xml:space="preserve">24.3495197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9402847290039</t>
   </si>
   <si>
     <t xml:space="preserve">24.1449012756348</t>
@@ -3320,19 +3320,19 @@
     <t xml:space="preserve">24.2131080627441</t>
   </si>
   <si>
-    <t xml:space="preserve">24.366569519043</t>
+    <t xml:space="preserve">24.3665714263916</t>
   </si>
   <si>
     <t xml:space="preserve">24.2472114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2813110351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0486316680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4347743988037</t>
+    <t xml:space="preserve">24.2813129425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0486278533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.434778213501</t>
   </si>
   <si>
     <t xml:space="preserve">23.5481014251709</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">23.4969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9342460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7978363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6443691253662</t>
+    <t xml:space="preserve">22.9342479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7978324890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6443710327148</t>
   </si>
   <si>
     <t xml:space="preserve">22.3033409118652</t>
@@ -3359,28 +3359,28 @@
     <t xml:space="preserve">21.5189723968506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8429508209229</t>
+    <t xml:space="preserve">21.8429527282715</t>
   </si>
   <si>
     <t xml:space="preserve">22.1839809417725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1949939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.638334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2120475769043</t>
+    <t xml:space="preserve">21.194995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6383323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2120456695557</t>
   </si>
   <si>
     <t xml:space="preserve">20.9051189422607</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6664009094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4678173065186</t>
+    <t xml:space="preserve">20.6663990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4678192138672</t>
   </si>
   <si>
     <t xml:space="preserve">21.0244789123535</t>
@@ -3398,16 +3398,16 @@
     <t xml:space="preserve">20.2912673950195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1378040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6273212432861</t>
+    <t xml:space="preserve">20.1378021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6273193359375</t>
   </si>
   <si>
     <t xml:space="preserve">24.0937480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6163063049316</t>
+    <t xml:space="preserve">23.616304397583</t>
   </si>
   <si>
     <t xml:space="preserve">22.7637329101562</t>
@@ -3422,28 +3422,28 @@
     <t xml:space="preserve">24.1619529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">25.560173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9292678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8951683044434</t>
+    <t xml:space="preserve">25.5601749420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9292697906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8951663970947</t>
   </si>
   <si>
     <t xml:space="preserve">24.3154163360596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2873497009277</t>
+    <t xml:space="preserve">25.2873516082764</t>
   </si>
   <si>
     <t xml:space="preserve">25.7136383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6564445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1850414276123</t>
+    <t xml:space="preserve">24.6564464569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1850433349609</t>
   </si>
   <si>
     <t xml:space="preserve">24.9804229736328</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">25.662483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3786468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2933902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8049335479736</t>
+    <t xml:space="preserve">26.3786449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2933883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8049354553223</t>
   </si>
   <si>
     <t xml:space="preserve">26.7537784576416</t>
@@ -3467,13 +3467,13 @@
     <t xml:space="preserve">26.9413452148438</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0436553955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0948104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.821985244751</t>
+    <t xml:space="preserve">27.0436515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0948066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8219833374023</t>
   </si>
   <si>
     <t xml:space="preserve">26.9925003051758</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">27.7086620330811</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5040435791016</t>
+    <t xml:space="preserve">27.5040416717529</t>
   </si>
   <si>
     <t xml:space="preserve">27.4699420928955</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">27.8621253967285</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0496921539307</t>
+    <t xml:space="preserve">28.0496940612793</t>
   </si>
   <si>
     <t xml:space="preserve">27.5893020629883</t>
@@ -3509,46 +3509,46 @@
     <t xml:space="preserve">27.1800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2823753356934</t>
+    <t xml:space="preserve">27.2823734283447</t>
   </si>
   <si>
     <t xml:space="preserve">26.856086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6514701843262</t>
+    <t xml:space="preserve">26.6514682769775</t>
   </si>
   <si>
     <t xml:space="preserve">25.3555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3214569091797</t>
+    <t xml:space="preserve">25.3214550018311</t>
   </si>
   <si>
     <t xml:space="preserve">25.9864616394043</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3385066986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8901901245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7598171234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4759788513184</t>
+    <t xml:space="preserve">25.3385047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8901920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7598152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.475980758667</t>
   </si>
   <si>
     <t xml:space="preserve">28.5100803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6976470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9875221252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4604320526123</t>
+    <t xml:space="preserve">28.6976490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9875240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4604301452637</t>
   </si>
   <si>
     <t xml:space="preserve">29.4954624176025</t>
@@ -3557,34 +3557,34 @@
     <t xml:space="preserve">30.0559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5655212402344</t>
+    <t xml:space="preserve">29.5655193328857</t>
   </si>
   <si>
     <t xml:space="preserve">28.724796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6197071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3394660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1993427276611</t>
+    <t xml:space="preserve">28.6197052001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3394641876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1993446350098</t>
   </si>
   <si>
     <t xml:space="preserve">28.3044338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9524936676025</t>
+    <t xml:space="preserve">28.9524955749512</t>
   </si>
   <si>
     <t xml:space="preserve">28.8824329376221</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0575847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1451568603516</t>
+    <t xml:space="preserve">29.0575828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1451587677002</t>
   </si>
   <si>
     <t xml:space="preserve">27.043342590332</t>
@@ -3596,19 +3596,19 @@
     <t xml:space="preserve">26.3427410125732</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8681945800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0099544525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9924373626709</t>
+    <t xml:space="preserve">26.8681926727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.009952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9924392700195</t>
   </si>
   <si>
     <t xml:space="preserve">25.9574069976807</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6071033477783</t>
+    <t xml:space="preserve">25.607105255127</t>
   </si>
   <si>
     <t xml:space="preserve">26.5178928375244</t>
@@ -3617,13 +3617,13 @@
     <t xml:space="preserve">26.255163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6054649353027</t>
+    <t xml:space="preserve">26.6054668426514</t>
   </si>
   <si>
     <t xml:space="preserve">25.8873462677002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4653453826904</t>
+    <t xml:space="preserve">26.4653434753418</t>
   </si>
   <si>
     <t xml:space="preserve">26.3252239227295</t>
@@ -3632,22 +3632,22 @@
     <t xml:space="preserve">26.1675891876221</t>
   </si>
   <si>
-    <t xml:space="preserve">26.93825340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9732837677002</t>
+    <t xml:space="preserve">26.9382553100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9732856750488</t>
   </si>
   <si>
     <t xml:space="preserve">27.1309204101562</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4286766052246</t>
+    <t xml:space="preserve">27.4286785125732</t>
   </si>
   <si>
     <t xml:space="preserve">27.3411026000977</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7455883026123</t>
+    <t xml:space="preserve">26.7455902099609</t>
   </si>
   <si>
     <t xml:space="preserve">26.9907989501953</t>
@@ -3668,25 +3668,25 @@
     <t xml:space="preserve">26.3602561950684</t>
   </si>
   <si>
-    <t xml:space="preserve">26.693042755127</t>
+    <t xml:space="preserve">26.6930408477783</t>
   </si>
   <si>
     <t xml:space="preserve">26.5879535675049</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1834678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.884069442749</t>
+    <t xml:space="preserve">27.1834659576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8840713500977</t>
   </si>
   <si>
     <t xml:space="preserve">28.1467971801758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4445552825928</t>
+    <t xml:space="preserve">28.4445533752441</t>
   </si>
   <si>
     <t xml:space="preserve">28.8999481201172</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">29.6706123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7757034301758</t>
+    <t xml:space="preserve">29.7757053375244</t>
   </si>
   <si>
     <t xml:space="preserve">29.6530990600586</t>
@@ -3707,43 +3707,43 @@
     <t xml:space="preserve">29.2327365875244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4062480926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1260070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3186740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8632793426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9508571624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.441276550293</t>
+    <t xml:space="preserve">30.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1260051727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3186721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8632774353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.950855255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4412784576416</t>
   </si>
   <si>
     <t xml:space="preserve">31.1593990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3361854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1785488128662</t>
+    <t xml:space="preserve">30.3361873626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1785526275635</t>
   </si>
   <si>
     <t xml:space="preserve">29.7406730651855</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7089176177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4987392425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0258293151855</t>
+    <t xml:space="preserve">27.7089214324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4987373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0258312225342</t>
   </si>
   <si>
     <t xml:space="preserve">26.1851024627686</t>
@@ -3776,37 +3776,37 @@
     <t xml:space="preserve">28.7598266601562</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8665542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1692276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0641384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5912284851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7488632202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2726783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1659526824951</t>
+    <t xml:space="preserve">29.1801891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8665561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.169225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.064136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5912303924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7488651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2726802825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1659507751465</t>
   </si>
   <si>
     <t xml:space="preserve">25.0816516876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9415283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4335918426514</t>
+    <t xml:space="preserve">24.9415302276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4335899353027</t>
   </si>
   <si>
     <t xml:space="preserve">24.1708660125732</t>
@@ -3824,13 +3824,13 @@
     <t xml:space="preserve">25.5545597076416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7472267150879</t>
+    <t xml:space="preserve">25.7472248077393</t>
   </si>
   <si>
     <t xml:space="preserve">25.6946811676025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9048633575439</t>
+    <t xml:space="preserve">25.9048614501953</t>
   </si>
   <si>
     <t xml:space="preserve">25.6771659851074</t>
@@ -3839,10 +3839,10 @@
     <t xml:space="preserve">27.0783767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7806205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6738910675049</t>
+    <t xml:space="preserve">26.7806186676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6738891601562</t>
   </si>
   <si>
     <t xml:space="preserve">27.7964954376221</t>
@@ -3851,19 +3851,19 @@
     <t xml:space="preserve">27.2535285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">27.48122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9366149902344</t>
+    <t xml:space="preserve">27.4812240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.936616897583</t>
   </si>
   <si>
     <t xml:space="preserve">28.8649158477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7631015777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9032230377197</t>
+    <t xml:space="preserve">26.7631034851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9032249450684</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274677276611</t>
@@ -3872,25 +3872,25 @@
     <t xml:space="preserve">26.3952865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8331642150879</t>
+    <t xml:space="preserve">26.8331623077393</t>
   </si>
   <si>
     <t xml:space="preserve">26.307710647583</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9223785400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3777694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5003776550293</t>
+    <t xml:space="preserve">25.9223766326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3777713775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5003757476807</t>
   </si>
   <si>
     <t xml:space="preserve">26.1325588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0975284576416</t>
+    <t xml:space="preserve">26.097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">26.5354061126709</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">26.2376499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7647399902344</t>
+    <t xml:space="preserve">25.764741897583</t>
   </si>
   <si>
     <t xml:space="preserve">25.8348026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2201347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4144382476807</t>
+    <t xml:space="preserve">26.2201366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4144401550293</t>
   </si>
   <si>
     <t xml:space="preserve">25.466983795166</t>
@@ -3923,10 +3923,10 @@
     <t xml:space="preserve">25.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5895881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8714694976807</t>
+    <t xml:space="preserve">25.5895900726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8714714050293</t>
   </si>
   <si>
     <t xml:space="preserve">24.4686241149902</t>
@@ -3935,22 +3935,22 @@
     <t xml:space="preserve">24.5737133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1183223724365</t>
+    <t xml:space="preserve">24.1183204650879</t>
   </si>
   <si>
     <t xml:space="preserve">24.2409267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3285007476807</t>
+    <t xml:space="preserve">24.3285026550293</t>
   </si>
   <si>
     <t xml:space="preserve">24.7838954925537</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8539562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3109874725342</t>
+    <t xml:space="preserve">24.8539543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3109855651855</t>
   </si>
   <si>
     <t xml:space="preserve">24.2234115600586</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">24.3460159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4160766601562</t>
+    <t xml:space="preserve">24.4160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">24.3985633850098</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">24.5036525726318</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6612892150879</t>
+    <t xml:space="preserve">24.6612873077393</t>
   </si>
   <si>
     <t xml:space="preserve">24.2759552001953</t>
@@ -4007,10 +4007,10 @@
     <t xml:space="preserve">23.8731079101562</t>
   </si>
   <si>
-    <t xml:space="preserve">23.34765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7154731750488</t>
+    <t xml:space="preserve">23.3476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7154712677002</t>
   </si>
   <si>
     <t xml:space="preserve">23.7680168151855</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">23.049898147583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8747463226318</t>
+    <t xml:space="preserve">22.8747482299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.1900177001953</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">23.9256534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7505035400391</t>
+    <t xml:space="preserve">23.7505016326904</t>
   </si>
   <si>
     <t xml:space="preserve">23.435230255127</t>
@@ -4052,16 +4052,16 @@
     <t xml:space="preserve">23.0849285125732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3826847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5228080749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9606838226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4861373901367</t>
+    <t xml:space="preserve">23.3826866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5228061676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9606857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4861354827881</t>
   </si>
   <si>
     <t xml:space="preserve">24.2584400177002</t>
@@ -4076,31 +4076,31 @@
     <t xml:space="preserve">25.2042579650879</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1341972351074</t>
+    <t xml:space="preserve">25.1341991424561</t>
   </si>
   <si>
     <t xml:space="preserve">24.6262588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3635311126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7855319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2250518798828</t>
+    <t xml:space="preserve">24.3635330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7855339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2250499725342</t>
   </si>
   <si>
     <t xml:space="preserve">22.9798374176025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2775936126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.295108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0657749176025</t>
+    <t xml:space="preserve">23.2775955200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2951107025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0657730102539</t>
   </si>
   <si>
     <t xml:space="preserve">24.7663803100586</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">23.6418628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4965953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334342956543</t>
+    <t xml:space="preserve">23.4965972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334362030029</t>
   </si>
   <si>
     <t xml:space="preserve">23.5329132080078</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">24.2955551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5679264068604</t>
+    <t xml:space="preserve">24.5679244995117</t>
   </si>
   <si>
     <t xml:space="preserve">24.4771347045898</t>
@@ -4163,13 +4163,13 @@
     <t xml:space="preserve">24.5134525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3318710327148</t>
+    <t xml:space="preserve">24.3318691253662</t>
   </si>
   <si>
     <t xml:space="preserve">23.9868659973145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5510711669922</t>
+    <t xml:space="preserve">23.5510730743408</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058074951172</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">23.4602813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8234424591064</t>
+    <t xml:space="preserve">23.8234443664551</t>
   </si>
   <si>
     <t xml:space="preserve">23.6237049102783</t>
@@ -4196,13 +4196,13 @@
     <t xml:space="preserve">24.8221397399902</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0413398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3863468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1321296691895</t>
+    <t xml:space="preserve">24.0413417816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.386344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1321315765381</t>
   </si>
   <si>
     <t xml:space="preserve">24.4589786529541</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">24.6768760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6042442321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5497703552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7858238220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2397766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8039817810059</t>
+    <t xml:space="preserve">24.6042423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.549768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7858219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2397747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8039798736572</t>
   </si>
   <si>
     <t xml:space="preserve">24.9674053192139</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">22.2618465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2981624603271</t>
+    <t xml:space="preserve">22.2981605529785</t>
   </si>
   <si>
     <t xml:space="preserve">22.388952255249</t>
@@ -4271,25 +4271,25 @@
     <t xml:space="preserve">22.2073707580566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0621070861816</t>
+    <t xml:space="preserve">22.062105178833</t>
   </si>
   <si>
     <t xml:space="preserve">21.6807861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6263122558594</t>
+    <t xml:space="preserve">21.6263103485107</t>
   </si>
   <si>
     <t xml:space="preserve">22.6431674957275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6794815063477</t>
+    <t xml:space="preserve">22.6794834136963</t>
   </si>
   <si>
     <t xml:space="preserve">22.5886917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1515922546387</t>
+    <t xml:space="preserve">23.1515941619873</t>
   </si>
   <si>
     <t xml:space="preserve">22.9700107574463</t>
@@ -4310,28 +4310,28 @@
     <t xml:space="preserve">23.024486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9155368804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.86106300354</t>
+    <t xml:space="preserve">22.9155387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8610649108887</t>
   </si>
   <si>
     <t xml:space="preserve">23.2060661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5342178344727</t>
+    <t xml:space="preserve">22.534215927124</t>
   </si>
   <si>
     <t xml:space="preserve">21.9349994659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8442096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2631511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8999881744385</t>
+    <t xml:space="preserve">21.8442077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2631492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8999862670898</t>
   </si>
   <si>
     <t xml:space="preserve">20.482349395752</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">20.7365646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1010284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6833934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7378673553467</t>
+    <t xml:space="preserve">20.1010303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6833953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7378692626953</t>
   </si>
   <si>
     <t xml:space="preserve">20.0102405548096</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">19.9376068115234</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3915576934814</t>
+    <t xml:space="preserve">20.3915596008301</t>
   </si>
   <si>
     <t xml:space="preserve">20.6094589233398</t>
@@ -4373,19 +4373,19 @@
     <t xml:space="preserve">20.6820907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1542015075684</t>
+    <t xml:space="preserve">21.1541996002197</t>
   </si>
   <si>
     <t xml:space="preserve">21.0997276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1723594665527</t>
+    <t xml:space="preserve">21.1723575592041</t>
   </si>
   <si>
     <t xml:space="preserve">21.0634117126465</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8091983795166</t>
+    <t xml:space="preserve">20.809196472168</t>
   </si>
   <si>
     <t xml:space="preserve">21.0089359283447</t>
@@ -4397,16 +4397,16 @@
     <t xml:space="preserve">21.0270938873291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.608154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7715759277344</t>
+    <t xml:space="preserve">21.6081523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.771577835083</t>
   </si>
   <si>
     <t xml:space="preserve">21.4628887176514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9181480407715</t>
+    <t xml:space="preserve">20.9181461334229</t>
   </si>
   <si>
     <t xml:space="preserve">21.2449913024902</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">22.7884311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0971183776855</t>
+    <t xml:space="preserve">23.0971202850342</t>
   </si>
   <si>
     <t xml:space="preserve">23.2605419158936</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">23.1152763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3694896697998</t>
+    <t xml:space="preserve">23.3694915771484</t>
   </si>
   <si>
     <t xml:space="preserve">23.8960742950439</t>
@@ -4445,13 +4445,13 @@
     <t xml:space="preserve">24.3681869506836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7689685821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4408206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2216186523438</t>
+    <t xml:space="preserve">23.768970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4408187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2216205596924</t>
   </si>
   <si>
     <t xml:space="preserve">25.493989944458</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">25.966100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">25.984260559082</t>
+    <t xml:space="preserve">25.9842586517334</t>
   </si>
   <si>
     <t xml:space="preserve">26.0932083129883</t>
@@ -4478,31 +4478,31 @@
     <t xml:space="preserve">26.2021560668945</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4758319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8947734832764</t>
+    <t xml:space="preserve">25.475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8947715759277</t>
   </si>
   <si>
     <t xml:space="preserve">25.0945110321045</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2942523956299</t>
+    <t xml:space="preserve">25.2942504882812</t>
   </si>
   <si>
     <t xml:space="preserve">24.9129314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">24.713191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0763549804688</t>
+    <t xml:space="preserve">24.7131900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0763530731201</t>
   </si>
   <si>
     <t xml:space="preserve">24.6405582427979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6587181091309</t>
+    <t xml:space="preserve">24.6587162017822</t>
   </si>
   <si>
     <t xml:space="preserve">24.3137130737305</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">21.5718383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4447326660156</t>
+    <t xml:space="preserve">21.444730758667</t>
   </si>
   <si>
     <t xml:space="preserve">21.1905174255371</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">21.136043548584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9363040924072</t>
+    <t xml:space="preserve">20.9363021850586</t>
   </si>
   <si>
     <t xml:space="preserve">21.3176250457764</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">22.6976413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7871265411377</t>
+    <t xml:space="preserve">23.7871284484863</t>
   </si>
   <si>
     <t xml:space="preserve">24.0231819152832</t>
@@ -5430,6 +5430,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.4799995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5</t>
   </si>
 </sst>
 </file>
@@ -70560,7 +70563,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6495717593</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>178369</v>
@@ -70581,6 +70584,32 @@
         <v>1802</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6494675926</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>452983</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>22.7600002288818</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>22.4799995422363</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>22.7000007629395</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1806</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -38,133 +38,133 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4875545501709</t>
+    <t xml:space="preserve">7.48755407333374</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43893384933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23837423324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04389381408691</t>
+    <t xml:space="preserve">7.43893480300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23837471008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04389238357544</t>
   </si>
   <si>
     <t xml:space="preserve">6.99527215957642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06212425231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25053071975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22014093399048</t>
+    <t xml:space="preserve">7.06212472915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25052976608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22014236450195</t>
   </si>
   <si>
     <t xml:space="preserve">7.17152118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07428073883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84940958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01350498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75216913223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83725547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9709620475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09251308441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00742673873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00135040283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9891939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92841863632202</t>
+    <t xml:space="preserve">7.07428169250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84941101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01350450515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75217008590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83725595474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97096252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09251403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00742721557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00134944915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98919343948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92841815948486</t>
   </si>
   <si>
     <t xml:space="preserve">6.86156558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5333776473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47868013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61238574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55160903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77647972106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94057416915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87372016906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63061809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78863477706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58199834823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7035493850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71570444107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80686712265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91626405715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84333229064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83117866516113</t>
+    <t xml:space="preserve">6.53337717056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47867918014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61238670349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55161046981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77647924423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94057464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8737211227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63061857223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78863573074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58199787139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70354890823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71570539474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80686807632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91626358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84333372116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83117723464966</t>
   </si>
   <si>
     <t xml:space="preserve">6.87979793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70962619781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74609279632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85548830032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8676438331604</t>
+    <t xml:space="preserve">6.70962715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74609231948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85548734664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86764287948608</t>
   </si>
   <si>
     <t xml:space="preserve">6.95272874832153</t>
@@ -173,43 +173,43 @@
     <t xml:space="preserve">7.04997062683105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27483940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35992527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34777116775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26876306533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22621965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11074590682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03173732757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08035755157471</t>
+    <t xml:space="preserve">7.27484035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35992431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34777164459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26876211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22621822357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1107439994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03173780441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08035802841187</t>
   </si>
   <si>
     <t xml:space="preserve">7.05604648590088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18975305557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23229742050171</t>
+    <t xml:space="preserve">7.18975496292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23229646682739</t>
   </si>
   <si>
     <t xml:space="preserve">7.1532883644104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11682319641113</t>
+    <t xml:space="preserve">7.11682224273682</t>
   </si>
   <si>
     <t xml:space="preserve">7.16544389724731</t>
@@ -218,127 +218,127 @@
     <t xml:space="preserve">6.95880651473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93449687957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803123474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90410947799683</t>
+    <t xml:space="preserve">6.93449640274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803075790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90410804748535</t>
   </si>
   <si>
     <t xml:space="preserve">6.96488428115845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79471302032471</t>
+    <t xml:space="preserve">6.79471206665039</t>
   </si>
   <si>
     <t xml:space="preserve">6.76432466506958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14113283157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02565860748291</t>
+    <t xml:space="preserve">7.14113426208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02566051483154</t>
   </si>
   <si>
     <t xml:space="preserve">7.15738677978516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13741302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31052160263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25725746154785</t>
+    <t xml:space="preserve">7.13741254806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3105206489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25725793838501</t>
   </si>
   <si>
     <t xml:space="preserve">7.34381198883057</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38376045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29720544815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25059938430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21730852127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062610626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23728370666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27723217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2239670753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10412311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85777616500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65803337097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60477066040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47493839263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50822734832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95764589309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93767213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82448530197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88440656661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47826623916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56149244308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69132471084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81782817840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91769695281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03754186630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78453683853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50489950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61808586120605</t>
+    <t xml:space="preserve">7.38375997543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29720449447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25059843063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21730947494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062467575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23728322982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27723169326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22396755218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10412263870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85777568817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.658034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60477018356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47493886947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50822877883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95764493942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93767261505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82448482513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88440752029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47826671600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3218035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56149291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69132423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81782627105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9176983833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03754281997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78453636169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50489902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61808490753174</t>
   </si>
   <si>
     <t xml:space="preserve">6.71795654296875</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">6.6846661567688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73792886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87774991989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81116819381714</t>
+    <t xml:space="preserve">6.73793029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87774896621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81116771697998</t>
   </si>
   <si>
     <t xml:space="preserve">6.75124740600586</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">6.79119491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76456308364868</t>
+    <t xml:space="preserve">6.76456212997437</t>
   </si>
   <si>
     <t xml:space="preserve">6.86443328857422</t>
@@ -371,16 +371,16 @@
     <t xml:space="preserve">6.77122068405151</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89106559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73127222061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64471864700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63805961608887</t>
+    <t xml:space="preserve">6.89106607437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73127126693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64471817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63806009292603</t>
   </si>
   <si>
     <t xml:space="preserve">6.75790500640869</t>
@@ -389,61 +389,61 @@
     <t xml:space="preserve">6.83114290237427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80451107025146</t>
+    <t xml:space="preserve">6.80451202392578</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101358413696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96430444717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74458932876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71129846572876</t>
+    <t xml:space="preserve">6.96430397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74458980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7112979888916</t>
   </si>
   <si>
     <t xml:space="preserve">6.65137577056885</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62807369232178</t>
+    <t xml:space="preserve">6.62807321548462</t>
   </si>
   <si>
     <t xml:space="preserve">6.6413893699646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62141370773315</t>
+    <t xml:space="preserve">6.62141466140747</t>
   </si>
   <si>
     <t xml:space="preserve">7.01756811141968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98427724838257</t>
+    <t xml:space="preserve">6.98427772521973</t>
   </si>
   <si>
     <t xml:space="preserve">7.01090955734253</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04420042037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17070341110229</t>
+    <t xml:space="preserve">7.0442008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17070293426514</t>
   </si>
   <si>
     <t xml:space="preserve">6.87109136581421</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92435503005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97761964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83780097961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84445905685425</t>
+    <t xml:space="preserve">6.92435598373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97762060165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83780145645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84446001052856</t>
   </si>
   <si>
     <t xml:space="preserve">6.79785299301147</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">6.59811162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55150508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7246150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67135143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66469287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60809993743896</t>
+    <t xml:space="preserve">6.55150556564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72461462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67135047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66469240188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60809898376465</t>
   </si>
   <si>
     <t xml:space="preserve">6.54484796524048</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">6.45829296112061</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65470457077026</t>
+    <t xml:space="preserve">6.65470409393311</t>
   </si>
   <si>
     <t xml:space="preserve">6.67800855636597</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">6.13870763778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22859048843384</t>
+    <t xml:space="preserve">6.22859144210815</t>
   </si>
   <si>
     <t xml:space="preserve">6.19197225570679</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17865514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24856472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13537788391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06546878814697</t>
+    <t xml:space="preserve">6.17865562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24856519699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13537836074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06546926498413</t>
   </si>
   <si>
     <t xml:space="preserve">6.1686692237854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15868186950684</t>
+    <t xml:space="preserve">6.15868091583252</t>
   </si>
   <si>
     <t xml:space="preserve">6.14203691482544</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">6.06213998794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03883695602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10874700546265</t>
+    <t xml:space="preserve">6.03883600234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10874652862549</t>
   </si>
   <si>
     <t xml:space="preserve">6.0588116645813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02219247817993</t>
+    <t xml:space="preserve">6.02219295501709</t>
   </si>
   <si>
     <t xml:space="preserve">6.01886320114136</t>
@@ -536,88 +536,88 @@
     <t xml:space="preserve">6.11873292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23192024230957</t>
+    <t xml:space="preserve">6.23191976547241</t>
   </si>
   <si>
     <t xml:space="preserve">6.12206220626831</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22193336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21860361099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35842227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37839698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62474346160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70464134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85111665725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69798231124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.904381275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89772319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9909348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07749128341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91103887557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07083129882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1307544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15072965621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18401861190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09746503829956</t>
+    <t xml:space="preserve">6.22193288803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21860408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35842275619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37839603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62474489212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70464086532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85111713409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69798278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90438175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89772272109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99093580245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07749032974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91103839874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07083225250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13075399398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15072774887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18401956558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0974645614624</t>
   </si>
   <si>
     <t xml:space="preserve">7.05085897445679</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35046911239624</t>
+    <t xml:space="preserve">7.35047006607056</t>
   </si>
   <si>
     <t xml:space="preserve">7.27057361602783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2838888168335</t>
+    <t xml:space="preserve">7.28389024734497</t>
   </si>
   <si>
     <t xml:space="preserve">7.30386352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53023624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32383632659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31717920303345</t>
+    <t xml:space="preserve">7.53023719787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32383728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31717967987061</t>
   </si>
   <si>
     <t xml:space="preserve">7.36378526687622</t>
@@ -626,43 +626,43 @@
     <t xml:space="preserve">7.51692056655884</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59015893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347557067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000480651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992607116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77658462524414</t>
+    <t xml:space="preserve">7.59015798568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347414016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71000385284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992559432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7765851020813</t>
   </si>
   <si>
     <t xml:space="preserve">7.73663520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78990030288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75660943984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82318925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85648012161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86979579925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8764533996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308666229248</t>
+    <t xml:space="preserve">7.7898998260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75660991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82319021224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85647869110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86979627609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87645530700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308570861816</t>
   </si>
   <si>
     <t xml:space="preserve">7.96966648101807</t>
@@ -671,34 +671,34 @@
     <t xml:space="preserve">7.9496922492981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92306089401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96300983428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311243057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72332048416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62344884872437</t>
+    <t xml:space="preserve">7.92306041717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96300888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311147689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72331953048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62344932556152</t>
   </si>
   <si>
     <t xml:space="preserve">7.54355239868164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47031402587891</t>
+    <t xml:space="preserve">7.47031497955322</t>
   </si>
   <si>
     <t xml:space="preserve">7.6367654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56352758407593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018518447876</t>
+    <t xml:space="preserve">7.56352615356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018566131592</t>
   </si>
   <si>
     <t xml:space="preserve">7.74329376220703</t>
@@ -707,67 +707,67 @@
     <t xml:space="preserve">7.80321598052979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89642906188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94303607940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84982252120972</t>
+    <t xml:space="preserve">7.89642810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94303417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84982204437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.06953716278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20842742919922</t>
+    <t xml:space="preserve">8.20842838287354</t>
   </si>
   <si>
     <t xml:space="preserve">8.25009441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22926235198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31953907012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35426235198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28481864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29870700836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37509727478027</t>
+    <t xml:space="preserve">8.22926139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31954002380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35426330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28481674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2987060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37509536743164</t>
   </si>
   <si>
     <t xml:space="preserve">8.34731864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38898658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43759727478027</t>
+    <t xml:space="preserve">8.3889856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43759536743164</t>
   </si>
   <si>
     <t xml:space="preserve">8.45148658752441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68760013580322</t>
+    <t xml:space="preserve">8.68760108947754</t>
   </si>
   <si>
     <t xml:space="preserve">8.7362117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62510013580322</t>
+    <t xml:space="preserve">8.62509918212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.63898849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6667652130127</t>
+    <t xml:space="preserve">8.66676616668701</t>
   </si>
   <si>
     <t xml:space="preserve">8.68065547943115</t>
@@ -797,34 +797,34 @@
     <t xml:space="preserve">8.54870986938477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49315166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5139856338501</t>
+    <t xml:space="preserve">8.4931526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51398754119873</t>
   </si>
   <si>
     <t xml:space="preserve">8.46537494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47232055664062</t>
+    <t xml:space="preserve">8.47231864929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.61815357208252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65982246398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6459321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40981769561768</t>
+    <t xml:space="preserve">8.65982151031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64593315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40981864929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.4306526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42370891571045</t>
+    <t xml:space="preserve">8.42370700836182</t>
   </si>
   <si>
     <t xml:space="preserve">8.30565071105957</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">8.5417652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57648849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6042652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71537780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88204574584961</t>
+    <t xml:space="preserve">8.57648754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60426616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7153787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88204669952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.00010395050049</t>
@@ -854,46 +854,46 @@
     <t xml:space="preserve">9.13204956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06954860687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09038257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00704860687256</t>
+    <t xml:space="preserve">9.06954956054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09038162231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00704765319824</t>
   </si>
   <si>
     <t xml:space="preserve">8.95843601226807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06260395050049</t>
+    <t xml:space="preserve">9.0626049041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.1251049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2084379196167</t>
+    <t xml:space="preserve">9.20843982696533</t>
   </si>
   <si>
     <t xml:space="preserve">9.24316215515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29871845245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36816310882568</t>
+    <t xml:space="preserve">9.2987174987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3681640625</t>
   </si>
   <si>
     <t xml:space="preserve">9.40983009338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41677570343018</t>
+    <t xml:space="preserve">9.41677474975586</t>
   </si>
   <si>
     <t xml:space="preserve">9.32649707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29177474975586</t>
+    <t xml:space="preserve">9.29177379608154</t>
   </si>
   <si>
     <t xml:space="preserve">9.31260776519775</t>
@@ -908,10 +908,10 @@
     <t xml:space="preserve">9.43760871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44455242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4028844833374</t>
+    <t xml:space="preserve">9.44455337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40288639068604</t>
   </si>
   <si>
     <t xml:space="preserve">9.38899707794189</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">9.3403844833374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34733009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48621940612793</t>
+    <t xml:space="preserve">9.34732913970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31955242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48622131347656</t>
   </si>
   <si>
     <t xml:space="preserve">9.75011157989502</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">9.7778902053833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80566883087158</t>
+    <t xml:space="preserve">9.8056697845459</t>
   </si>
   <si>
     <t xml:space="preserve">9.72927856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77094650268555</t>
+    <t xml:space="preserve">9.77094554901123</t>
   </si>
   <si>
     <t xml:space="preserve">9.76400089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74316787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96539402008057</t>
+    <t xml:space="preserve">9.74316692352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96539211273193</t>
   </si>
   <si>
     <t xml:space="preserve">10.0278930664062</t>
@@ -968,55 +968,55 @@
     <t xml:space="preserve">10.0834503173828</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1181726455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1876163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4445648193359</t>
+    <t xml:space="preserve">10.1181716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1876173019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4445638656616</t>
   </si>
   <si>
     <t xml:space="preserve">10.5001211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5695667266846</t>
+    <t xml:space="preserve">10.5695657730103</t>
   </si>
   <si>
     <t xml:space="preserve">10.2292852401733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3959531784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4237327575684</t>
+    <t xml:space="preserve">10.3959522247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4237308502197</t>
   </si>
   <si>
     <t xml:space="preserve">10.5903997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4931755065918</t>
+    <t xml:space="preserve">10.4931764602661</t>
   </si>
   <si>
     <t xml:space="preserve">10.5626211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6251230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6042890548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.701512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7779016494751</t>
+    <t xml:space="preserve">10.6251220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6042881011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7015104293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7779026031494</t>
   </si>
   <si>
     <t xml:space="preserve">10.8542909622192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8334589004517</t>
+    <t xml:space="preserve">10.8334579467773</t>
   </si>
   <si>
     <t xml:space="preserve">10.9029035568237</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">11.1112384796143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6667881011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9723482131958</t>
+    <t xml:space="preserve">10.6667890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9723491668701</t>
   </si>
   <si>
     <t xml:space="preserve">10.9445705413818</t>
@@ -1043,58 +1043,58 @@
     <t xml:space="preserve">11.0765171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3473529815674</t>
+    <t xml:space="preserve">11.3473539352417</t>
   </si>
   <si>
     <t xml:space="preserve">11.3959646224976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1529064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0626277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2154054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3126316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2362413406372</t>
+    <t xml:space="preserve">11.1529054641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0626268386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2154064178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3126306533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2362403869629</t>
   </si>
   <si>
     <t xml:space="preserve">11.2084617614746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9098472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7362356185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8751249313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6945676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5487327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7848472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8612356185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0695695877075</t>
+    <t xml:space="preserve">10.9098482131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.736234664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8751230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6945667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.548731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7848463058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8612365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0695714950562</t>
   </si>
   <si>
     <t xml:space="preserve">11.1876277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9306812286377</t>
+    <t xml:space="preserve">10.930682182312</t>
   </si>
   <si>
     <t xml:space="preserve">11.1598510742188</t>
@@ -1103,34 +1103,34 @@
     <t xml:space="preserve">11.4515199661255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.50013256073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4931869506836</t>
+    <t xml:space="preserve">11.5001316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4931879043579</t>
   </si>
   <si>
     <t xml:space="preserve">11.6251335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7223558425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709693908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7015228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7293014526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7154130935669</t>
+    <t xml:space="preserve">11.7223567962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709703445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7015237808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.729302406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7154121398926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6112432479858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4862451553345</t>
+    <t xml:space="preserve">11.4862442016602</t>
   </si>
   <si>
     <t xml:space="preserve">11.5765228271484</t>
@@ -1142,22 +1142,22 @@
     <t xml:space="preserve">11.3820743560791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8681793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8959589004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9862365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0834608078003</t>
+    <t xml:space="preserve">10.8681802749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8959579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9862375259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0834617614746</t>
   </si>
   <si>
     <t xml:space="preserve">11.2292957305908</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2848529815674</t>
+    <t xml:space="preserve">11.2848520278931</t>
   </si>
   <si>
     <t xml:space="preserve">11.3265190124512</t>
@@ -1166,49 +1166,49 @@
     <t xml:space="preserve">11.2431859970093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5973558425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7501354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6181898117065</t>
+    <t xml:space="preserve">11.597357749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7501363754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6181888580322</t>
   </si>
   <si>
     <t xml:space="preserve">11.7987451553345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6320781707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8334693908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1251392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.916802406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6668109893799</t>
+    <t xml:space="preserve">11.6320772171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8334712982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1251382827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9168043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6668100357056</t>
   </si>
   <si>
     <t xml:space="preserve">13.152928352356</t>
   </si>
   <si>
-    <t xml:space="preserve">13.382098197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.319598197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3682088851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5765438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5209875106812</t>
+    <t xml:space="preserve">13.3820991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3195972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3682107925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.576545715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5209884643555</t>
   </si>
   <si>
     <t xml:space="preserve">13.2362632751465</t>
@@ -1217,67 +1217,67 @@
     <t xml:space="preserve">13.1668176651001</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0487623214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4237651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0070943832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.354320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4584865570068</t>
+    <t xml:space="preserve">13.0487613677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4237642288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3543214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4584875106812</t>
   </si>
   <si>
     <t xml:space="preserve">13.7154359817505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7918252944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6807136535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9168300628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9307165145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1876525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2987651824951</t>
+    <t xml:space="preserve">13.7918243408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6807126998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9168272018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9307155609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1876516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2987623214722</t>
   </si>
   <si>
     <t xml:space="preserve">13.3751544952393</t>
   </si>
   <si>
-    <t xml:space="preserve">13.416820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4723768234253</t>
+    <t xml:space="preserve">13.4168186187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4723777770996</t>
   </si>
   <si>
     <t xml:space="preserve">13.4862661361694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6112689971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7362699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223787307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8196029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8890466690063</t>
+    <t xml:space="preserve">13.6112699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.736270904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8196048736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8890476226807</t>
   </si>
   <si>
     <t xml:space="preserve">13.8543272018433</t>
@@ -1289,16 +1289,16 @@
     <t xml:space="preserve">14.0834970474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.798770904541</t>
+    <t xml:space="preserve">13.7987699508667</t>
   </si>
   <si>
     <t xml:space="preserve">14.0279397964478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3057222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1945953369141</t>
+    <t xml:space="preserve">14.3057203292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1945972442627</t>
   </si>
   <si>
     <t xml:space="preserve">13.1112623214722</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">13.1807069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0200986862183</t>
+    <t xml:space="preserve">14.0200996398926</t>
   </si>
   <si>
     <t xml:space="preserve">14.1486539840698</t>
@@ -1325,19 +1325,19 @@
     <t xml:space="preserve">13.2563285827637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1277723312378</t>
+    <t xml:space="preserve">13.1277732849121</t>
   </si>
   <si>
     <t xml:space="preserve">13.3092632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4605054855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4983139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4680662155151</t>
+    <t xml:space="preserve">13.4605045318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4983129501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4680671691895</t>
   </si>
   <si>
     <t xml:space="preserve">13.5739364624023</t>
@@ -1346,16 +1346,16 @@
     <t xml:space="preserve">13.7327394485474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7478618621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4075689315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4889469146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4738216400146</t>
+    <t xml:space="preserve">13.7478628158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4075679779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4889478683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4738235473633</t>
   </si>
   <si>
     <t xml:space="preserve">14.6704378128052</t>
@@ -1367,91 +1367,91 @@
     <t xml:space="preserve">14.3755178451538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6175022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.723370552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9351081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7460584640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292436599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167129516602</t>
+    <t xml:space="preserve">14.6175031661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7233715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9351100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.746057510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167119979858</t>
   </si>
   <si>
     <t xml:space="preserve">14.2998952865601</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2091522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0654706954956</t>
+    <t xml:space="preserve">14.2091493606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0654697418213</t>
   </si>
   <si>
     <t xml:space="preserve">14.1637773513794</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0427827835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1713399887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2847709655762</t>
+    <t xml:space="preserve">14.0427837371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1713390350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2847700119019</t>
   </si>
   <si>
     <t xml:space="preserve">14.6250648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7536182403564</t>
+    <t xml:space="preserve">14.7536191940308</t>
   </si>
   <si>
     <t xml:space="preserve">14.6779985427856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.791428565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8443641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8746137619019</t>
+    <t xml:space="preserve">14.7914276123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8443651199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8746128082275</t>
   </si>
   <si>
     <t xml:space="preserve">14.8368034362793</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7611837387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6553134918213</t>
+    <t xml:space="preserve">14.7611818313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6553144454956</t>
   </si>
   <si>
     <t xml:space="preserve">14.5494441986084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6099405288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6401882171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5721302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5191965103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2393989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0049743652344</t>
+    <t xml:space="preserve">14.609938621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6401901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5721311569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5191946029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2393999099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0049734115601</t>
   </si>
   <si>
     <t xml:space="preserve">13.9217920303345</t>
@@ -1460,121 +1460,121 @@
     <t xml:space="preserve">13.9142293930054</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2696475982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3982028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9898519515991</t>
+    <t xml:space="preserve">14.2696485519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3982019424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9898490905762</t>
   </si>
   <si>
     <t xml:space="preserve">13.6646795272827</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6722421646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5814962387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7705497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6268701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5209999084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495542526245</t>
+    <t xml:space="preserve">13.6722431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5814971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705488204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6268711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5210008621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495561599731</t>
   </si>
   <si>
     <t xml:space="preserve">13.5512495040894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4907512664795</t>
+    <t xml:space="preserve">13.4907522201538</t>
   </si>
   <si>
     <t xml:space="preserve">13.4756288528442</t>
   </si>
   <si>
-    <t xml:space="preserve">13.505877494812</t>
+    <t xml:space="preserve">13.5058765411377</t>
   </si>
   <si>
     <t xml:space="preserve">13.3470726013184</t>
   </si>
   <si>
-    <t xml:space="preserve">13.39244556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.483190536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6344327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5663738250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5436859130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3773231506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1958341598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2714500427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3395099639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3546361923218</t>
+    <t xml:space="preserve">13.3924446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4831914901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8310470581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6344318389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5663728713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5436878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3773241043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1958322525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2714519500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3395118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3546352386475</t>
   </si>
   <si>
     <t xml:space="preserve">13.2638912200928</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4529447555542</t>
+    <t xml:space="preserve">13.4529438018799</t>
   </si>
   <si>
     <t xml:space="preserve">13.3319473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9311599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0219030380249</t>
+    <t xml:space="preserve">12.9311590194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0219039916992</t>
   </si>
   <si>
     <t xml:space="preserve">12.8101654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5530548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7421083450317</t>
+    <t xml:space="preserve">12.5530557632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7421073913574</t>
   </si>
   <si>
     <t xml:space="preserve">12.6513614654541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3848838806152</t>
+    <t xml:space="preserve">13.3848857879639</t>
   </si>
   <si>
     <t xml:space="preserve">13.1202096939087</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9614057540894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5681800842285</t>
+    <t xml:space="preserve">12.9614067077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5681791305542</t>
   </si>
   <si>
     <t xml:space="preserve">12.4396228790283</t>
@@ -1583,16 +1583,16 @@
     <t xml:space="preserve">12.6211137771606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4018106460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4925565719604</t>
+    <t xml:space="preserve">12.4018125534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4925584793091</t>
   </si>
   <si>
     <t xml:space="preserve">12.4698715209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1371393203735</t>
+    <t xml:space="preserve">12.1371383666992</t>
   </si>
   <si>
     <t xml:space="preserve">12.2883815765381</t>
@@ -1604,13 +1604,13 @@
     <t xml:space="preserve">12.6286764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6437997817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.825288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7723541259766</t>
+    <t xml:space="preserve">12.643798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252897262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7723550796509</t>
   </si>
   <si>
     <t xml:space="preserve">12.8479747772217</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">12.7572298049927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8177270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.77991771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4471836090088</t>
+    <t xml:space="preserve">12.8177280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7799167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4471855163574</t>
   </si>
   <si>
     <t xml:space="preserve">12.4245004653931</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">12.1673889160156</t>
   </si>
   <si>
-    <t xml:space="preserve">12.416937828064</t>
+    <t xml:space="preserve">12.4169387817383</t>
   </si>
   <si>
     <t xml:space="preserve">12.1447019577026</t>
@@ -1649,28 +1649,28 @@
     <t xml:space="preserve">12.2505722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1068925857544</t>
+    <t xml:space="preserve">12.1068935394287</t>
   </si>
   <si>
     <t xml:space="preserve">12.2278852462769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0463972091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0993309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7968463897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8800287246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5379295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2656946182251</t>
+    <t xml:space="preserve">12.0463943481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0993299484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7968454360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8800296783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5379304885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2656955718994</t>
   </si>
   <si>
     <t xml:space="preserve">12.7950420379639</t>
@@ -1679,16 +1679,16 @@
     <t xml:space="preserve">13.2941389083862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1126480102539</t>
+    <t xml:space="preserve">13.1126489639282</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538440704346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5833034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4774341583252</t>
+    <t xml:space="preserve">12.5833024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4774332046509</t>
   </si>
   <si>
     <t xml:space="preserve">12.5757398605347</t>
@@ -1697,49 +1697,52 @@
     <t xml:space="preserve">12.8555383682251</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0143413543701</t>
+    <t xml:space="preserve">13.0143404006958</t>
   </si>
   <si>
     <t xml:space="preserve">12.8328514099121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9084711074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0521516799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9160327911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0975246429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0067806243896</t>
+    <t xml:space="preserve">12.9084730148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.052152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1807079315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.916033744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0975227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0067796707153</t>
   </si>
   <si>
     <t xml:space="preserve">13.2260799407959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2185163497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9009103775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0370283126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7647905349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0294647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109546661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.233642578125</t>
+    <t xml:space="preserve">13.2185173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9009094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0370273590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7647914886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0294637680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109537124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2336416244507</t>
   </si>
   <si>
     <t xml:space="preserve">12.9235954284668</t>
@@ -1751,25 +1754,25 @@
     <t xml:space="preserve">12.893346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.188268661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9689683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3017015457153</t>
+    <t xml:space="preserve">13.1882705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9689702987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1050853729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3016996383667</t>
   </si>
   <si>
     <t xml:space="preserve">12.8857879638672</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6891717910767</t>
+    <t xml:space="preserve">12.689172744751</t>
   </si>
   <si>
     <t xml:space="preserve">12.6967344284058</t>
@@ -1778,55 +1781,55 @@
     <t xml:space="preserve">12.6362361907959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6664848327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5152454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3110685348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2430086135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0388317108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6589231491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7269830703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7496690750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3186311721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1900749206543</t>
+    <t xml:space="preserve">12.666485786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5152435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3110694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2430095672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0388326644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6589241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7269811630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7496700286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3186302185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1900758743286</t>
   </si>
   <si>
     <t xml:space="preserve">12.1976366043091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1749505996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2732572555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1598281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203216552734</t>
+    <t xml:space="preserve">12.1749515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2732582092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1598262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203235626221</t>
   </si>
   <si>
     <t xml:space="preserve">12.280818939209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.303505897522</t>
+    <t xml:space="preserve">12.3035068511963</t>
   </si>
   <si>
     <t xml:space="preserve">12.8631000518799</t>
@@ -1838,7 +1841,7 @@
     <t xml:space="preserve">13.4485063552856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5988111495972</t>
+    <t xml:space="preserve">13.5988130569458</t>
   </si>
   <si>
     <t xml:space="preserve">13.6146335601807</t>
@@ -1847,16 +1850,16 @@
     <t xml:space="preserve">13.9548025131226</t>
   </si>
   <si>
-    <t xml:space="preserve">13.978533744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8598709106445</t>
+    <t xml:space="preserve">13.9785346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8598728179932</t>
   </si>
   <si>
     <t xml:space="preserve">13.7491178512573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7332973480225</t>
+    <t xml:space="preserve">13.7332983016968</t>
   </si>
   <si>
     <t xml:space="preserve">13.7728509902954</t>
@@ -1865,7 +1868,7 @@
     <t xml:space="preserve">13.8124046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7174739837646</t>
+    <t xml:space="preserve">13.7174758911133</t>
   </si>
   <si>
     <t xml:space="preserve">13.6383657455444</t>
@@ -1874,46 +1877,46 @@
     <t xml:space="preserve">13.6620988845825</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5750780105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1446619033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.239595413208</t>
+    <t xml:space="preserve">13.5750789642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.14466381073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2395935058594</t>
   </si>
   <si>
     <t xml:space="preserve">14.5085639953613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4690113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7221593856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.674690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1763067245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1604862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0813760757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0339117050171</t>
+    <t xml:space="preserve">14.4690103530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955839157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7221584320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.674693107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1763076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1604852676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0813751220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0339107513428</t>
   </si>
   <si>
     <t xml:space="preserve">14.4373655319214</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6984262466431</t>
+    <t xml:space="preserve">14.6984252929688</t>
   </si>
   <si>
     <t xml:space="preserve">14.611403465271</t>
@@ -1925,34 +1928,34 @@
     <t xml:space="preserve">14.6272277832031</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1097898483276</t>
+    <t xml:space="preserve">15.1097927093506</t>
   </si>
   <si>
     <t xml:space="preserve">15.0939693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9911279678345</t>
+    <t xml:space="preserve">14.9911298751831</t>
   </si>
   <si>
     <t xml:space="preserve">14.9436626434326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9120187759399</t>
+    <t xml:space="preserve">14.9120168685913</t>
   </si>
   <si>
     <t xml:space="preserve">14.8724632263184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8645553588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6430492401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2870597839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3266143798828</t>
+    <t xml:space="preserve">14.8645515441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6430511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2870578765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3266153335571</t>
   </si>
   <si>
     <t xml:space="preserve">14.2158584594727</t>
@@ -1967,28 +1970,28 @@
     <t xml:space="preserve">14.0576438903809</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6067237854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8677835464478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000408172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2949695587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2079496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6304559707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5671672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6700096130371</t>
+    <t xml:space="preserve">13.6067247390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8677825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000398635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2949705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.207950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6304550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5671691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6700105667114</t>
   </si>
   <si>
     <t xml:space="preserve">13.519702911377</t>
@@ -1997,97 +2000,97 @@
     <t xml:space="preserve">13.3693962097168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8203153610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9073371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8440504074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5592565536499</t>
+    <t xml:space="preserve">13.8203163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9073362350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8440494537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5592575073242</t>
   </si>
   <si>
     <t xml:space="preserve">13.7886734008789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7965841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1209306716919</t>
+    <t xml:space="preserve">13.7965869903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1209325790405</t>
   </si>
   <si>
     <t xml:space="preserve">13.9310703277588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0892877578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3028812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4848299026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6588716506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633275985718</t>
+    <t xml:space="preserve">14.0892858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3028831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4848308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6588706970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633266448975</t>
   </si>
   <si>
     <t xml:space="preserve">14.2316827774048</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1130180358887</t>
+    <t xml:space="preserve">14.1130208969116</t>
   </si>
   <si>
     <t xml:space="preserve">14.5876722335815</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9753046035767</t>
+    <t xml:space="preserve">14.9753065109253</t>
   </si>
   <si>
     <t xml:space="preserve">14.8566427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9990367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8329095840454</t>
+    <t xml:space="preserve">14.9990386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.832911491394</t>
   </si>
   <si>
     <t xml:space="preserve">14.745888710022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0227708816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.737979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6905126571655</t>
+    <t xml:space="preserve">15.0227737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7379779815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6905145645142</t>
   </si>
   <si>
     <t xml:space="preserve">14.6351375579834</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1525745391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5164756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4294548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1921291351318</t>
+    <t xml:space="preserve">14.5402059555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1525735855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5164737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4294557571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1921272277832</t>
   </si>
   <si>
     <t xml:space="preserve">14.0971994400024</t>
@@ -2096,13 +2099,13 @@
     <t xml:space="preserve">14.2712383270264</t>
   </si>
   <si>
-    <t xml:space="preserve">14.279146194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3899030685425</t>
+    <t xml:space="preserve">14.2791481018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057207107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3899011611938</t>
   </si>
   <si>
     <t xml:space="preserve">14.342432975769</t>
@@ -2111,37 +2114,37 @@
     <t xml:space="preserve">14.3582563400269</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4610977172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0069465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9515743255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5322961807251</t>
+    <t xml:space="preserve">14.4610996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0069494247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9515733718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5322971343994</t>
   </si>
   <si>
     <t xml:space="preserve">14.3345241546631</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3740787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3819885253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6509590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0860557556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8170871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6193170547485</t>
+    <t xml:space="preserve">14.3740797042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3819894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509618759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0860586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8170900344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6193141937256</t>
   </si>
   <si>
     <t xml:space="preserve">15.0544157028198</t>
@@ -2150,19 +2153,19 @@
     <t xml:space="preserve">15.4895143508911</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8692350387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7189302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3075647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3471183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081762313843</t>
+    <t xml:space="preserve">15.8692378997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7189311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.307562828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3471193313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081743240356</t>
   </si>
   <si>
     <t xml:space="preserve">15.2284545898438</t>
@@ -2171,43 +2174,43 @@
     <t xml:space="preserve">15.1572561264038</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1888990402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1414337158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3866729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2838315963745</t>
+    <t xml:space="preserve">15.1888999938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1414346694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3866720199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2838306427002</t>
   </si>
   <si>
     <t xml:space="preserve">15.3154745101929</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7505731582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7110176086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6160869598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4420490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2047214508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2363662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1651678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4024934768677</t>
+    <t xml:space="preserve">15.7505722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7110195159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6160879135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4420471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.20472240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2363653182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.165168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4024925231934</t>
   </si>
   <si>
     <t xml:space="preserve">15.6239986419678</t>
@@ -2222,16 +2225,16 @@
     <t xml:space="preserve">16.5179290771484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.296422958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5653915405273</t>
+    <t xml:space="preserve">16.2964248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.565393447876</t>
   </si>
   <si>
     <t xml:space="preserve">17.0400466918945</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9292945861816</t>
+    <t xml:space="preserve">16.9292964935303</t>
   </si>
   <si>
     <t xml:space="preserve">17.0875129699707</t>
@@ -2240,19 +2243,19 @@
     <t xml:space="preserve">17.0558700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.691967010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8976497650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1982650756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8818283081055</t>
+    <t xml:space="preserve">16.9609394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6919689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8976516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.198263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8818321228027</t>
   </si>
   <si>
     <t xml:space="preserve">17.2299098968506</t>
@@ -2261,7 +2264,7 @@
     <t xml:space="preserve">17.3564834594727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4514141082764</t>
+    <t xml:space="preserve">17.4514122009277</t>
   </si>
   <si>
     <t xml:space="preserve">17.6096324920654</t>
@@ -2273,31 +2276,31 @@
     <t xml:space="preserve">17.4355907440186</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305233001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8785991668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1792125701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1317501068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2583236694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3690738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.289966583252</t>
+    <t xml:space="preserve">17.5305213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8786010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1792163848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1317481994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.258321762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3690776824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2899684906006</t>
   </si>
   <si>
     <t xml:space="preserve">18.2108573913574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3723049163818</t>
+    <t xml:space="preserve">17.3723030090332</t>
   </si>
   <si>
     <t xml:space="preserve">17.4830589294434</t>
@@ -2306,25 +2309,25 @@
     <t xml:space="preserve">17.7045612335205</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3248386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5021076202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4988803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1508007049561</t>
+    <t xml:space="preserve">17.324836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5021057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4988765716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1507987976074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1701698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0213174819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8267736434937</t>
+    <t xml:space="preserve">13.0213165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8267726898193</t>
   </si>
   <si>
     <t xml:space="preserve">11.6210908889771</t>
@@ -2333,25 +2336,22 @@
     <t xml:space="preserve">11.6290016174316</t>
   </si>
   <si>
-    <t xml:space="preserve">11.360032081604</t>
+    <t xml:space="preserve">11.3600311279297</t>
   </si>
   <si>
     <t xml:space="preserve">10.9882202148438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4470520019531</t>
+    <t xml:space="preserve">11.4470510482788</t>
   </si>
   <si>
     <t xml:space="preserve">12.0245447158813</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0641002655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8630990982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.420090675354</t>
+    <t xml:space="preserve">12.0641012191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4200897216797</t>
   </si>
   <si>
     <t xml:space="preserve">12.1748533248901</t>
@@ -2363,46 +2363,46 @@
     <t xml:space="preserve">12.6969699859619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2190885543823</t>
+    <t xml:space="preserve">13.2190895080566</t>
   </si>
   <si>
     <t xml:space="preserve">13.4722385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3140211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2349109649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241598129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4089508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4564170837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1004266738892</t>
+    <t xml:space="preserve">13.3140201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2349119186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241588592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4089517593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1004257202148</t>
   </si>
   <si>
     <t xml:space="preserve">13.0925159454346</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2507333755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687818527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3614845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4326829910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5038795471191</t>
+    <t xml:space="preserve">13.2507343292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3614854812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4326839447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5038814544678</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738521575928</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">12.9342975616455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0371389389038</t>
+    <t xml:space="preserve">13.0371398925781</t>
   </si>
   <si>
     <t xml:space="preserve">13.1795349121094</t>
@@ -2426,37 +2426,37 @@
     <t xml:space="preserve">13.6225442886353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7095632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2056884765625</t>
+    <t xml:space="preserve">13.7095651626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2056903839111</t>
   </si>
   <si>
     <t xml:space="preserve">13.8418655395508</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1560773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966470718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2883758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0491018295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2475500106812</t>
+    <t xml:space="preserve">14.1560764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966451644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2883777618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0491008758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2475490570068</t>
   </si>
   <si>
     <t xml:space="preserve">15.2971611022949</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1240367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4134407043457</t>
+    <t xml:space="preserve">16.1240348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4134426116943</t>
   </si>
   <si>
     <t xml:space="preserve">16.5043964385986</t>
@@ -2465,19 +2465,19 @@
     <t xml:space="preserve">16.1405735015869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0909614562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.190185546875</t>
+    <t xml:space="preserve">16.0909595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1901874542236</t>
   </si>
   <si>
     <t xml:space="preserve">15.5865659713745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5286884307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346773147583</t>
+    <t xml:space="preserve">15.5286874771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3467721939087</t>
   </si>
   <si>
     <t xml:space="preserve">15.2144746780396</t>
@@ -2486,25 +2486,25 @@
     <t xml:space="preserve">15.2806234359741</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8346300125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6527166366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692543029785</t>
+    <t xml:space="preserve">15.8346309661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6527185440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692562103271</t>
   </si>
   <si>
     <t xml:space="preserve">15.5782995223999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7932844161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8594379425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633127212524</t>
+    <t xml:space="preserve">15.7932872772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8594369888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633117675781</t>
   </si>
   <si>
     <t xml:space="preserve">15.429461479187</t>
@@ -2513,58 +2513,58 @@
     <t xml:space="preserve">15.5617599487305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8677034378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3307552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0501365661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2651214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.868221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9509105682373</t>
+    <t xml:space="preserve">15.8677053451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.330753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0501327514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8682231903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9509086608887</t>
   </si>
   <si>
     <t xml:space="preserve">17.116283416748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3312683105469</t>
+    <t xml:space="preserve">17.3312702178955</t>
   </si>
   <si>
     <t xml:space="preserve">17.51318359375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7777824401855</t>
+    <t xml:space="preserve">17.7777805328369</t>
   </si>
   <si>
     <t xml:space="preserve">17.2981967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2816562652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3147354125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4304962158203</t>
+    <t xml:space="preserve">17.2816600799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.314733505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4304943084717</t>
   </si>
   <si>
     <t xml:space="preserve">17.3643474578857</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3808841705322</t>
+    <t xml:space="preserve">17.380880355835</t>
   </si>
   <si>
     <t xml:space="preserve">16.9839839935303</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8186111450195</t>
+    <t xml:space="preserve">16.8186092376709</t>
   </si>
   <si>
     <t xml:space="preserve">16.9012966156006</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">17.5958709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4801063537598</t>
+    <t xml:space="preserve">17.4801082611084</t>
   </si>
   <si>
     <t xml:space="preserve">17.8439311981201</t>
@@ -2594,37 +2594,37 @@
     <t xml:space="preserve">17.9266204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9927711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0919933319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4227447509766</t>
+    <t xml:space="preserve">17.992769241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0919971466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4227466583252</t>
   </si>
   <si>
     <t xml:space="preserve">18.4723567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1581439971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.025842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0754585266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5054321289062</t>
+    <t xml:space="preserve">18.1581420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0258464813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.07546043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5054302215576</t>
   </si>
   <si>
     <t xml:space="preserve">18.389669418335</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2739067077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3235206604004</t>
+    <t xml:space="preserve">18.2739086151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3235187530518</t>
   </si>
   <si>
     <t xml:space="preserve">18.3400573730469</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">18.191219329834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0589199066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9100818634033</t>
+    <t xml:space="preserve">18.0589218139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.910083770752</t>
   </si>
   <si>
     <t xml:space="preserve">18.2408313751221</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">18.3069801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620197296143</t>
+    <t xml:space="preserve">17.6620216369629</t>
   </si>
   <si>
     <t xml:space="preserve">17.794319152832</t>
@@ -2654,25 +2654,25 @@
     <t xml:space="preserve">17.7116317749023</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5793342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.347806930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4966449737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3974227905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7447090148926</t>
+    <t xml:space="preserve">17.5793323516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3478088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4966468811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3974208831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7447052001953</t>
   </si>
   <si>
     <t xml:space="preserve">18.6046562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7700328826904</t>
+    <t xml:space="preserve">18.7700309753418</t>
   </si>
   <si>
     <t xml:space="preserve">18.3731327056885</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">18.7534942626953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4062061309814</t>
+    <t xml:space="preserve">18.4062080383301</t>
   </si>
   <si>
     <t xml:space="preserve">18.1416072845459</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">17.9431571960449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1085338592529</t>
+    <t xml:space="preserve">18.1085300445557</t>
   </si>
   <si>
     <t xml:space="preserve">17.7281703948975</t>
@@ -2711,13 +2711,13 @@
     <t xml:space="preserve">16.2894096374512</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9503927230835</t>
+    <t xml:space="preserve">15.9503917694092</t>
   </si>
   <si>
     <t xml:space="preserve">16.0413494110107</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5374717712402</t>
+    <t xml:space="preserve">16.5374698638916</t>
   </si>
   <si>
     <t xml:space="preserve">17.0832099914551</t>
@@ -2729,16 +2729,16 @@
     <t xml:space="preserve">17.0666694641113</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2155094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1658954620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0005226135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178314208984</t>
+    <t xml:space="preserve">17.2155075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1658973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0005187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178333282471</t>
   </si>
   <si>
     <t xml:space="preserve">16.7028465270996</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">16.7855339050293</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6201591491699</t>
+    <t xml:space="preserve">16.6201610565186</t>
   </si>
   <si>
     <t xml:space="preserve">16.4795913696289</t>
@@ -2759,22 +2759,22 @@
     <t xml:space="preserve">17.033597946167</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1328201293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1824359893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.546257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1746845245361</t>
+    <t xml:space="preserve">17.1328220367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1824340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1746807098389</t>
   </si>
   <si>
     <t xml:space="preserve">18.8692569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1669292449951</t>
+    <t xml:space="preserve">19.1669311523438</t>
   </si>
   <si>
     <t xml:space="preserve">19.348840713501</t>
@@ -2783,34 +2783,34 @@
     <t xml:space="preserve">20.0599536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.960729598999</t>
+    <t xml:space="preserve">19.9607276916504</t>
   </si>
   <si>
     <t xml:space="preserve">20.5064659118652</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6883792877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7049140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.671838760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8206787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7545299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9364395141602</t>
+    <t xml:space="preserve">20.6883773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7049160003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6718406677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8206806182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7545280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9364414215088</t>
   </si>
   <si>
     <t xml:space="preserve">20.7214508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0025901794434</t>
+    <t xml:space="preserve">21.0025882720947</t>
   </si>
   <si>
     <t xml:space="preserve">21.1845035552979</t>
@@ -2822,16 +2822,16 @@
     <t xml:space="preserve">22.1767501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.994836807251</t>
+    <t xml:space="preserve">21.9948387145996</t>
   </si>
   <si>
     <t xml:space="preserve">22.5571136474609</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2175769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9033641815186</t>
+    <t xml:space="preserve">21.2175788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9033660888672</t>
   </si>
   <si>
     <t xml:space="preserve">20.9529781341553</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">21.4160251617432</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8956127166748</t>
+    <t xml:space="preserve">21.8956108093262</t>
   </si>
   <si>
     <t xml:space="preserve">21.515251159668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8460006713867</t>
+    <t xml:space="preserve">21.8459987640381</t>
   </si>
   <si>
     <t xml:space="preserve">22.1602115631104</t>
@@ -2864,13 +2864,13 @@
     <t xml:space="preserve">21.3664150238037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7379913330078</t>
+    <t xml:space="preserve">20.7379894256592</t>
   </si>
   <si>
     <t xml:space="preserve">20.5726146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2506542205811</t>
+    <t xml:space="preserve">21.2506523132324</t>
   </si>
   <si>
     <t xml:space="preserve">20.7876014709473</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">20.2584037780762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6134433746338</t>
+    <t xml:space="preserve">19.6134395599365</t>
   </si>
   <si>
     <t xml:space="preserve">20.192253112793</t>
@@ -2894,19 +2894,19 @@
     <t xml:space="preserve">20.2749404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2010383605957</t>
+    <t xml:space="preserve">21.2010402679443</t>
   </si>
   <si>
     <t xml:space="preserve">20.9860515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4656391143799</t>
+    <t xml:space="preserve">21.4656372070312</t>
   </si>
   <si>
     <t xml:space="preserve">20.0103416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465167999268</t>
+    <t xml:space="preserve">19.6465187072754</t>
   </si>
   <si>
     <t xml:space="preserve">20.2253265380859</t>
@@ -2921,16 +2921,16 @@
     <t xml:space="preserve">20.638765335083</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0356636047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.34987449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0852756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0191287994385</t>
+    <t xml:space="preserve">21.035665512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3498783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.085277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0191268920898</t>
   </si>
   <si>
     <t xml:space="preserve">20.8702907562256</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">20.5230026245117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6056900024414</t>
+    <t xml:space="preserve">20.60569190979</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268783569336</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">20.1095676422119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1514263153076</t>
+    <t xml:space="preserve">21.1514282226562</t>
   </si>
   <si>
     <t xml:space="preserve">20.6222286224365</t>
@@ -2963,25 +2963,25 @@
     <t xml:space="preserve">20.3080158233643</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4072399139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9772644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3907032012939</t>
+    <t xml:space="preserve">20.4072418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9772663116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3907012939453</t>
   </si>
   <si>
     <t xml:space="preserve">20.1261024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0764904022217</t>
+    <t xml:space="preserve">20.0764923095703</t>
   </si>
   <si>
     <t xml:space="preserve">20.2914791107178</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2661533355713</t>
+    <t xml:space="preserve">19.2661571502686</t>
   </si>
   <si>
     <t xml:space="preserve">19.7622776031494</t>
@@ -2990,25 +2990,25 @@
     <t xml:space="preserve">19.878044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3484573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3314094543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0756320953369</t>
+    <t xml:space="preserve">21.3484592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3314075469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0756340026855</t>
   </si>
   <si>
     <t xml:space="preserve">21.2461490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2290992736816</t>
+    <t xml:space="preserve">21.229097366333</t>
   </si>
   <si>
     <t xml:space="preserve">21.177942276001</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4337139129639</t>
+    <t xml:space="preserve">21.4337158203125</t>
   </si>
   <si>
     <t xml:space="preserve">21.4848709106445</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">21.3143539428711</t>
   </si>
   <si>
-    <t xml:space="preserve">21.570125579834</t>
+    <t xml:space="preserve">21.5701274871826</t>
   </si>
   <si>
     <t xml:space="preserve">22.388599395752</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">21.979362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0646171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0305194854736</t>
+    <t xml:space="preserve">22.0646209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.030517578125</t>
   </si>
   <si>
     <t xml:space="preserve">21.7235908508301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6553859710693</t>
+    <t xml:space="preserve">21.6553840637207</t>
   </si>
   <si>
     <t xml:space="preserve">21.7406406402588</t>
@@ -3050,13 +3050,13 @@
     <t xml:space="preserve">21.3655071258545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4507675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6724376678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0987243652344</t>
+    <t xml:space="preserve">21.4507656097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.672435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0987224578857</t>
   </si>
   <si>
     <t xml:space="preserve">21.7917957305908</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">20.8710174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8880672454834</t>
+    <t xml:space="preserve">20.888069152832</t>
   </si>
   <si>
     <t xml:space="preserve">21.7065391540527</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">22.47385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2692394256592</t>
+    <t xml:space="preserve">22.2692375183105</t>
   </si>
   <si>
     <t xml:space="preserve">20.7346038818359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5470390319824</t>
+    <t xml:space="preserve">20.5470371246338</t>
   </si>
   <si>
     <t xml:space="preserve">21.2632007598877</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">21.1097373962402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1608905792236</t>
+    <t xml:space="preserve">21.1608924865723</t>
   </si>
   <si>
     <t xml:space="preserve">21.5530757904053</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">21.7747478485107</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2973022460938</t>
+    <t xml:space="preserve">21.2973041534424</t>
   </si>
   <si>
     <t xml:space="preserve">21.0926856994629</t>
@@ -3125,10 +3125,10 @@
     <t xml:space="preserve">20.8539638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0074291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.280252456665</t>
+    <t xml:space="preserve">21.0074272155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2802505493164</t>
   </si>
   <si>
     <t xml:space="preserve">21.9282073974609</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">21.8600025177002</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8088474273682</t>
+    <t xml:space="preserve">21.8088493347168</t>
   </si>
   <si>
     <t xml:space="preserve">21.8941059112549</t>
@@ -3146,43 +3146,43 @@
     <t xml:space="preserve">21.7576942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3996143341064</t>
+    <t xml:space="preserve">21.3996124267578</t>
   </si>
   <si>
     <t xml:space="preserve">21.9111576080322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5079574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1669292449951</t>
+    <t xml:space="preserve">22.5079593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1669273376465</t>
   </si>
   <si>
     <t xml:space="preserve">22.0816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">22.013463973999</t>
+    <t xml:space="preserve">22.0134658813477</t>
   </si>
   <si>
     <t xml:space="preserve">22.4909076690674</t>
   </si>
   <si>
-    <t xml:space="preserve">22.422700881958</t>
+    <t xml:space="preserve">22.4227027893066</t>
   </si>
   <si>
     <t xml:space="preserve">22.2521858215332</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5761642456055</t>
+    <t xml:space="preserve">22.5761661529541</t>
   </si>
   <si>
     <t xml:space="preserve">22.6614227294922</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7296257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.172966003418</t>
+    <t xml:space="preserve">22.7296276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1729679107666</t>
   </si>
   <si>
     <t xml:space="preserve">23.7697696685791</t>
@@ -3194,16 +3194,16 @@
     <t xml:space="preserve">23.3775844573975</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9232330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2191429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4749164581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8329963684082</t>
+    <t xml:space="preserve">23.9232311248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.219144821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4749183654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8329982757568</t>
   </si>
   <si>
     <t xml:space="preserve">25.7818431854248</t>
@@ -3212,40 +3212,40 @@
     <t xml:space="preserve">26.1740303039551</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3274898529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6003150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6173667907715</t>
+    <t xml:space="preserve">26.3274917602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6003170013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6173648834229</t>
   </si>
   <si>
     <t xml:space="preserve">26.7708282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6855735778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.969409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7196750640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3615970611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3104419708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5491600036621</t>
+    <t xml:space="preserve">26.6855716705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9694080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7196769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3615951538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5491619110107</t>
   </si>
   <si>
     <t xml:space="preserve">26.2251834869385</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5431232452393</t>
+    <t xml:space="preserve">25.5431213378906</t>
   </si>
   <si>
     <t xml:space="preserve">25.0315780639648</t>
@@ -3263,10 +3263,10 @@
     <t xml:space="preserve">25.1168346405029</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8099117279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8440113067627</t>
+    <t xml:space="preserve">24.8099098205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8440132141113</t>
   </si>
   <si>
     <t xml:space="preserve">25.1338882446289</t>
@@ -3278,16 +3278,16 @@
     <t xml:space="preserve">24.7587566375732</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3896598815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3836231231689</t>
+    <t xml:space="preserve">25.3896617889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3836250305176</t>
   </si>
   <si>
     <t xml:space="preserve">24.1790046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3324680328369</t>
+    <t xml:space="preserve">24.3324699401855</t>
   </si>
   <si>
     <t xml:space="preserve">24.6223430633545</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">24.1960563659668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3495197296143</t>
+    <t xml:space="preserve">24.3495178222656</t>
   </si>
   <si>
     <t xml:space="preserve">23.9402847290039</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">24.417724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4518280029297</t>
+    <t xml:space="preserve">24.4518299102783</t>
   </si>
   <si>
     <t xml:space="preserve">24.2131080627441</t>
@@ -3323,31 +3323,31 @@
     <t xml:space="preserve">24.3665714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2472114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2813129425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0486278533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.434778213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5481014251709</t>
+    <t xml:space="preserve">24.2472095489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2813148498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0486297607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5480995178223</t>
   </si>
   <si>
     <t xml:space="preserve">23.4969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9342479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7978324890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6443710327148</t>
+    <t xml:space="preserve">22.9342460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7978343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6443691253662</t>
   </si>
   <si>
     <t xml:space="preserve">22.3033409118652</t>
@@ -3356,10 +3356,10 @@
     <t xml:space="preserve">21.8770542144775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5189723968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8429527282715</t>
+    <t xml:space="preserve">21.5189743041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8429508209229</t>
   </si>
   <si>
     <t xml:space="preserve">22.1839809417725</t>
@@ -3386,28 +3386,28 @@
     <t xml:space="preserve">21.0244789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5640907287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9221706390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5129356384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2912673950195</t>
+    <t xml:space="preserve">20.5640888214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9221725463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5129337310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2912654876709</t>
   </si>
   <si>
     <t xml:space="preserve">20.1378021240234</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6273193359375</t>
+    <t xml:space="preserve">22.6273212432861</t>
   </si>
   <si>
     <t xml:space="preserve">24.0937480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.616304397583</t>
+    <t xml:space="preserve">23.6163063049316</t>
   </si>
   <si>
     <t xml:space="preserve">22.7637329101562</t>
@@ -3416,22 +3416,22 @@
     <t xml:space="preserve">22.8148860931396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6102695465088</t>
+    <t xml:space="preserve">22.6102676391602</t>
   </si>
   <si>
     <t xml:space="preserve">24.1619529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5601749420166</t>
+    <t xml:space="preserve">25.5601768493652</t>
   </si>
   <si>
     <t xml:space="preserve">24.9292697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8951663970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3154163360596</t>
+    <t xml:space="preserve">24.8951683044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3154144287109</t>
   </si>
   <si>
     <t xml:space="preserve">25.2873516082764</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">24.6564464569092</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1850433349609</t>
+    <t xml:space="preserve">25.1850452423096</t>
   </si>
   <si>
     <t xml:space="preserve">24.9804229736328</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">25.662483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3786449432373</t>
+    <t xml:space="preserve">26.3786468505859</t>
   </si>
   <si>
     <t xml:space="preserve">26.2933883666992</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8049354553223</t>
+    <t xml:space="preserve">26.8049335479736</t>
   </si>
   <si>
     <t xml:space="preserve">26.7537784576416</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">27.0436515808105</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0948066711426</t>
+    <t xml:space="preserve">27.0948104858398</t>
   </si>
   <si>
     <t xml:space="preserve">26.8219833374023</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">26.9925003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1459617614746</t>
+    <t xml:space="preserve">27.1459636688232</t>
   </si>
   <si>
     <t xml:space="preserve">27.7086620330811</t>
@@ -3488,7 +3488,7 @@
     <t xml:space="preserve">27.5040416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4699420928955</t>
+    <t xml:space="preserve">27.4699401855469</t>
   </si>
   <si>
     <t xml:space="preserve">27.6916103363037</t>
@@ -3500,13 +3500,13 @@
     <t xml:space="preserve">27.8621253967285</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0496940612793</t>
+    <t xml:space="preserve">28.0496921539307</t>
   </si>
   <si>
     <t xml:space="preserve">27.5893020629883</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1800651550293</t>
+    <t xml:space="preserve">27.1800670623779</t>
   </si>
   <si>
     <t xml:space="preserve">27.2823734283447</t>
@@ -3524,19 +3524,19 @@
     <t xml:space="preserve">25.3214550018311</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9864616394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3385047912598</t>
+    <t xml:space="preserve">25.9864635467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3385028839111</t>
   </si>
   <si>
     <t xml:space="preserve">26.8901920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7598152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.475980758667</t>
+    <t xml:space="preserve">27.7598171234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4759788513184</t>
   </si>
   <si>
     <t xml:space="preserve">28.5100803375244</t>
@@ -3545,10 +3545,10 @@
     <t xml:space="preserve">28.6976490020752</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9875240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4604301452637</t>
+    <t xml:space="preserve">28.9875221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.460428237915</t>
   </si>
   <si>
     <t xml:space="preserve">29.4954624176025</t>
@@ -3557,13 +3557,13 @@
     <t xml:space="preserve">30.0559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5655193328857</t>
+    <t xml:space="preserve">29.565523147583</t>
   </si>
   <si>
     <t xml:space="preserve">28.724796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6197052001953</t>
+    <t xml:space="preserve">28.6197071075439</t>
   </si>
   <si>
     <t xml:space="preserve">28.3394641876221</t>
@@ -3581,13 +3581,13 @@
     <t xml:space="preserve">28.8824329376221</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0575828552246</t>
+    <t xml:space="preserve">29.0575847625732</t>
   </si>
   <si>
     <t xml:space="preserve">29.1451587677002</t>
   </si>
   <si>
-    <t xml:space="preserve">27.043342590332</t>
+    <t xml:space="preserve">27.0433444976807</t>
   </si>
   <si>
     <t xml:space="preserve">26.6229820251465</t>
@@ -3596,10 +3596,10 @@
     <t xml:space="preserve">26.3427410125732</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8681926727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.009952545166</t>
+    <t xml:space="preserve">26.8681945800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0099544525146</t>
   </si>
   <si>
     <t xml:space="preserve">25.9924392700195</t>
@@ -3614,19 +3614,19 @@
     <t xml:space="preserve">26.5178928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">26.255163192749</t>
+    <t xml:space="preserve">26.2551651000977</t>
   </si>
   <si>
     <t xml:space="preserve">26.6054668426514</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8873462677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4653434753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3252239227295</t>
+    <t xml:space="preserve">25.8873481750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4653453826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3252258300781</t>
   </si>
   <si>
     <t xml:space="preserve">26.1675891876221</t>
@@ -3644,19 +3644,19 @@
     <t xml:space="preserve">27.4286785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3411026000977</t>
+    <t xml:space="preserve">27.341100692749</t>
   </si>
   <si>
     <t xml:space="preserve">26.7455902099609</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9907989501953</t>
+    <t xml:space="preserve">26.9907970428467</t>
   </si>
   <si>
     <t xml:space="preserve">27.6563739776611</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5687980651855</t>
+    <t xml:space="preserve">27.5687999725342</t>
   </si>
   <si>
     <t xml:space="preserve">26.7280731201172</t>
@@ -3665,19 +3665,19 @@
     <t xml:space="preserve">25.7822570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3602561950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6930408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5879535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1834659576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512809753418</t>
+    <t xml:space="preserve">26.3602542877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.693042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5879516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1834678649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512828826904</t>
   </si>
   <si>
     <t xml:space="preserve">27.8840713500977</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">28.1467971801758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4445533752441</t>
+    <t xml:space="preserve">28.4445552825928</t>
   </si>
   <si>
     <t xml:space="preserve">28.8999481201172</t>
@@ -3695,10 +3695,10 @@
     <t xml:space="preserve">29.0400676727295</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6706123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7757053375244</t>
+    <t xml:space="preserve">29.6706142425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7757034301758</t>
   </si>
   <si>
     <t xml:space="preserve">29.6530990600586</t>
@@ -3707,13 +3707,13 @@
     <t xml:space="preserve">29.2327365875244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1260051727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3186721801758</t>
+    <t xml:space="preserve">30.4062480926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1260070800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3186702728271</t>
   </si>
   <si>
     <t xml:space="preserve">29.8632774353027</t>
@@ -3728,25 +3728,25 @@
     <t xml:space="preserve">31.1593990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3361873626709</t>
+    <t xml:space="preserve">30.3361854553223</t>
   </si>
   <si>
     <t xml:space="preserve">30.1785526275635</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7406730651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7089214324951</t>
+    <t xml:space="preserve">29.7406749725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7089195251465</t>
   </si>
   <si>
     <t xml:space="preserve">27.4987373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0258312225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1851024627686</t>
+    <t xml:space="preserve">27.0258293151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1851043701172</t>
   </si>
   <si>
     <t xml:space="preserve">26.4478321075439</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">27.8490409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">28.269401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1643142700195</t>
+    <t xml:space="preserve">28.2694034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1643123626709</t>
   </si>
   <si>
     <t xml:space="preserve">28.6722526550293</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">27.8665561676025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.169225692749</t>
+    <t xml:space="preserve">25.1692276000977</t>
   </si>
   <si>
     <t xml:space="preserve">25.064136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5912303924561</t>
+    <t xml:space="preserve">24.5912284851074</t>
   </si>
   <si>
     <t xml:space="preserve">24.7488651275635</t>
@@ -3803,16 +3803,16 @@
     <t xml:space="preserve">25.0816516876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9415302276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4335899353027</t>
+    <t xml:space="preserve">24.9415321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4335918426514</t>
   </si>
   <si>
     <t xml:space="preserve">24.1708660125732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9781970977783</t>
+    <t xml:space="preserve">23.978199005127</t>
   </si>
   <si>
     <t xml:space="preserve">23.838077545166</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">24.9065017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5545597076416</t>
+    <t xml:space="preserve">25.5545616149902</t>
   </si>
   <si>
     <t xml:space="preserve">25.7472248077393</t>
@@ -3833,10 +3833,10 @@
     <t xml:space="preserve">25.9048614501953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6771659851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0783767700195</t>
+    <t xml:space="preserve">25.6771640777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0783748626709</t>
   </si>
   <si>
     <t xml:space="preserve">26.7806186676025</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">27.7964954376221</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2535285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.936616897583</t>
+    <t xml:space="preserve">27.2535266876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.48122215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9366149902344</t>
   </si>
   <si>
     <t xml:space="preserve">28.8649158477783</t>
@@ -3863,34 +3863,34 @@
     <t xml:space="preserve">26.7631034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9032249450684</t>
+    <t xml:space="preserve">26.9032230377197</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274677276611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3952865600586</t>
+    <t xml:space="preserve">26.39528465271</t>
   </si>
   <si>
     <t xml:space="preserve">26.8331623077393</t>
   </si>
   <si>
-    <t xml:space="preserve">26.307710647583</t>
+    <t xml:space="preserve">26.3077125549316</t>
   </si>
   <si>
     <t xml:space="preserve">25.9223766326904</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3777713775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5003757476807</t>
+    <t xml:space="preserve">26.3777694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5003776550293</t>
   </si>
   <si>
     <t xml:space="preserve">26.1325588226318</t>
   </si>
   <si>
-    <t xml:space="preserve">26.097526550293</t>
+    <t xml:space="preserve">26.0975284576416</t>
   </si>
   <si>
     <t xml:space="preserve">26.5354061126709</t>
@@ -3899,16 +3899,16 @@
     <t xml:space="preserve">26.8857097625732</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2376499176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.764741897583</t>
+    <t xml:space="preserve">26.2376480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7647399902344</t>
   </si>
   <si>
     <t xml:space="preserve">25.8348026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2201366424561</t>
+    <t xml:space="preserve">26.2201347351074</t>
   </si>
   <si>
     <t xml:space="preserve">25.4144401550293</t>
@@ -3923,16 +3923,16 @@
     <t xml:space="preserve">25.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5895900726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8714714050293</t>
+    <t xml:space="preserve">25.5895881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8714694976807</t>
   </si>
   <si>
     <t xml:space="preserve">24.4686241149902</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5737133026123</t>
+    <t xml:space="preserve">24.5737113952637</t>
   </si>
   <si>
     <t xml:space="preserve">24.1183204650879</t>
@@ -3941,7 +3941,7 @@
     <t xml:space="preserve">24.2409267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3285026550293</t>
+    <t xml:space="preserve">24.3285045623779</t>
   </si>
   <si>
     <t xml:space="preserve">24.7838954925537</t>
@@ -3950,19 +3950,19 @@
     <t xml:space="preserve">24.8539543151855</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3109855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2234115600586</t>
+    <t xml:space="preserve">24.3109874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.22340965271</t>
   </si>
   <si>
     <t xml:space="preserve">24.3460159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3985633850098</t>
+    <t xml:space="preserve">24.4160766601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3985614776611</t>
   </si>
   <si>
     <t xml:space="preserve">24.678804397583</t>
@@ -3989,10 +3989,10 @@
     <t xml:space="preserve">24.2058944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.188383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7329883575439</t>
+    <t xml:space="preserve">24.1883811950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7329864501953</t>
   </si>
   <si>
     <t xml:space="preserve">23.592866897583</t>
@@ -4001,34 +4001,34 @@
     <t xml:space="preserve">23.9957141876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0307445526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8731079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3476524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7154712677002</t>
+    <t xml:space="preserve">24.0307464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8731098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3476543426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7154731750488</t>
   </si>
   <si>
     <t xml:space="preserve">23.7680168151855</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4702606201172</t>
+    <t xml:space="preserve">23.4702587127686</t>
   </si>
   <si>
     <t xml:space="preserve">23.5052909851074</t>
   </si>
   <si>
-    <t xml:space="preserve">23.049898147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8747482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1900177001953</t>
+    <t xml:space="preserve">23.0498962402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8747463226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1900196075439</t>
   </si>
   <si>
     <t xml:space="preserve">23.2425651550293</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">23.5578365325928</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9256534576416</t>
+    <t xml:space="preserve">23.925651550293</t>
   </si>
   <si>
     <t xml:space="preserve">23.7505016326904</t>
@@ -4058,34 +4058,34 @@
     <t xml:space="preserve">23.5228061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9606857299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4861354827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2584400177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1166820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2217712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2042579650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1341991424561</t>
+    <t xml:space="preserve">23.9606838226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4861373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2584419250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1166839599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.221773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2042598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1341972351074</t>
   </si>
   <si>
     <t xml:space="preserve">24.6262588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3635330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7855339050293</t>
+    <t xml:space="preserve">24.3635292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7855319976807</t>
   </si>
   <si>
     <t xml:space="preserve">23.2250499725342</t>
@@ -4094,16 +4094,16 @@
     <t xml:space="preserve">22.9798374176025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2775955200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2951107025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0657730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7663803100586</t>
+    <t xml:space="preserve">23.2775936126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.295108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0657749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7663822174072</t>
   </si>
   <si>
     <t xml:space="preserve">24.7313499450684</t>
@@ -25861,7 +25861,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G773" t="s">
-        <v>430</v>
+        <v>565</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25913,7 +25913,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G775" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25965,7 +25965,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G777" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25991,7 +25991,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G778" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -26017,7 +26017,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G779" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -26043,7 +26043,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G780" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -26095,7 +26095,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G782" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -26121,7 +26121,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G783" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -26147,7 +26147,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G784" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -26225,7 +26225,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G787" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26251,7 +26251,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G788" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -26277,7 +26277,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G789" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -26303,7 +26303,7 @@
         <v>17.5</v>
       </c>
       <c r="G790" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26407,7 +26407,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G794" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -26433,7 +26433,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G795" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26511,7 +26511,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G798" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26563,7 +26563,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G800" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -26589,7 +26589,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G801" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -26615,7 +26615,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26667,7 +26667,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G804" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26693,7 +26693,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G805" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26719,7 +26719,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G806" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26745,7 +26745,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G807" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26771,7 +26771,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G808" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26797,7 +26797,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G809" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26823,7 +26823,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G810" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26849,7 +26849,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G811" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26875,7 +26875,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G812" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26901,7 +26901,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G813" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26927,7 +26927,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G814" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26979,7 +26979,7 @@
         <v>16.75</v>
       </c>
       <c r="G816" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -27005,7 +27005,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G817" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -27057,7 +27057,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G819" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -27083,7 +27083,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G820" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27135,7 +27135,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G822" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -27317,7 +27317,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G829" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -27369,7 +27369,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G831" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -27395,7 +27395,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G832" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27525,7 +27525,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G837" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -27629,7 +27629,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G841" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27681,7 +27681,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G843" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27707,7 +27707,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G844" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27733,7 +27733,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G845" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27785,7 +27785,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G847" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27863,7 +27863,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G850" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27889,7 +27889,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G851" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27941,7 +27941,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G853" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27967,7 +27967,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G854" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27993,7 +27993,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G855" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28019,7 +28019,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G856" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28045,7 +28045,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G857" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28071,7 +28071,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G858" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28097,7 +28097,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G859" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28123,7 +28123,7 @@
         <v>17</v>
       </c>
       <c r="G860" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28149,7 +28149,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G861" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28175,7 +28175,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G862" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28201,7 +28201,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G863" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28227,7 +28227,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G864" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28253,7 +28253,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G865" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28279,7 +28279,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G866" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28305,7 +28305,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G867" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28331,7 +28331,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G868" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28357,7 +28357,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G869" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28383,7 +28383,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G870" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28409,7 +28409,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G871" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28435,7 +28435,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G872" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28461,7 +28461,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G873" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28487,7 +28487,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G874" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28513,7 +28513,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G875" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28539,7 +28539,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G876" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28565,7 +28565,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G877" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -28591,7 +28591,7 @@
         <v>18</v>
       </c>
       <c r="G878" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28617,7 +28617,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G879" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28643,7 +28643,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G880" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -28669,7 +28669,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G881" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -28695,7 +28695,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G882" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -28721,7 +28721,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28747,7 +28747,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G884" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -28773,7 +28773,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G885" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28799,7 +28799,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G886" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28825,7 +28825,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G887" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28851,7 +28851,7 @@
         <v>18</v>
       </c>
       <c r="G888" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28877,7 +28877,7 @@
         <v>18</v>
       </c>
       <c r="G889" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28903,7 +28903,7 @@
         <v>18.25</v>
       </c>
       <c r="G890" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28929,7 +28929,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G891" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28955,7 +28955,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G892" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -28981,7 +28981,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G893" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29007,7 +29007,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G894" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29033,7 +29033,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29059,7 +29059,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G896" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29085,7 +29085,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G897" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29111,7 +29111,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G898" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29137,7 +29137,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G899" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29163,7 +29163,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29189,7 +29189,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G901" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29215,7 +29215,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G902" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29241,7 +29241,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G903" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29267,7 +29267,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G904" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29293,7 +29293,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G905" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29319,7 +29319,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G906" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29345,7 +29345,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G907" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29371,7 +29371,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G908" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29397,7 +29397,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G909" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29423,7 +29423,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G910" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29449,7 +29449,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G911" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29475,7 +29475,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G912" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29501,7 +29501,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G913" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29527,7 +29527,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G914" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29553,7 +29553,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G915" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29579,7 +29579,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G916" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29605,7 +29605,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G917" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29631,7 +29631,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G918" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29657,7 +29657,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G919" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29683,7 +29683,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G920" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29709,7 +29709,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G921" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -29735,7 +29735,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -29761,7 +29761,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G923" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -29787,7 +29787,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G924" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -29813,7 +29813,7 @@
         <v>17.5</v>
       </c>
       <c r="G925" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29839,7 +29839,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G926" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29865,7 +29865,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G927" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29891,7 +29891,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G928" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29917,7 +29917,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G929" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29943,7 +29943,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G930" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -29969,7 +29969,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G931" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -29995,7 +29995,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G932" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30021,7 +30021,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G933" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30047,7 +30047,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G934" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30073,7 +30073,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G935" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30099,7 +30099,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G936" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30125,7 +30125,7 @@
         <v>18.25</v>
       </c>
       <c r="G937" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30151,7 +30151,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G938" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30177,7 +30177,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G939" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30203,7 +30203,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G940" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30229,7 +30229,7 @@
         <v>18</v>
       </c>
       <c r="G941" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30255,7 +30255,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G942" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30281,7 +30281,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G943" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30307,7 +30307,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G944" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30333,7 +30333,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G945" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30359,7 +30359,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G946" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30385,7 +30385,7 @@
         <v>18.75</v>
       </c>
       <c r="G947" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30411,7 +30411,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G948" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -30437,7 +30437,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G949" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -30463,7 +30463,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G950" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30489,7 +30489,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G951" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30515,7 +30515,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G952" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -30541,7 +30541,7 @@
         <v>18.5</v>
       </c>
       <c r="G953" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30567,7 +30567,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G954" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30593,7 +30593,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G955" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -30619,7 +30619,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G956" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -30645,7 +30645,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G957" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30671,7 +30671,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G958" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30697,7 +30697,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G959" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -30723,7 +30723,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G960" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -30749,7 +30749,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G961" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -30775,7 +30775,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G962" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -30801,7 +30801,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G963" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30827,7 +30827,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30853,7 +30853,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G965" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30879,7 +30879,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G966" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30905,7 +30905,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G967" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -30931,7 +30931,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G968" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30957,7 +30957,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G969" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -30983,7 +30983,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G970" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31009,7 +31009,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G971" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31035,7 +31035,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G972" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31061,7 +31061,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G973" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31087,7 +31087,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G974" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31113,7 +31113,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G975" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31139,7 +31139,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G976" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31165,7 +31165,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31191,7 +31191,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31217,7 +31217,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G979" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31243,7 +31243,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G980" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31269,7 +31269,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G981" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31295,7 +31295,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G982" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31321,7 +31321,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G983" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31347,7 +31347,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G984" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31373,7 +31373,7 @@
         <v>18.75</v>
       </c>
       <c r="G985" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -31399,7 +31399,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G986" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -31425,7 +31425,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G987" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -31451,7 +31451,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G988" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31477,7 +31477,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G989" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -31503,7 +31503,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G990" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -31529,7 +31529,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G991" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -31555,7 +31555,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G992" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31581,7 +31581,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -31607,7 +31607,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G994" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31633,7 +31633,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G995" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -31659,7 +31659,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G996" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -31685,7 +31685,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G997" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -31711,7 +31711,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -31737,7 +31737,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G999" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -31763,7 +31763,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1000" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -31789,7 +31789,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1001" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -31815,7 +31815,7 @@
         <v>19.25</v>
       </c>
       <c r="G1002" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -31841,7 +31841,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1003" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -31867,7 +31867,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -31893,7 +31893,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1005" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31919,7 +31919,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1006" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -31945,7 +31945,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1007" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -31971,7 +31971,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -31997,7 +31997,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32023,7 +32023,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1010" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32049,7 +32049,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G1011" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32075,7 +32075,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1012" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32101,7 +32101,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1013" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32127,7 +32127,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1014" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32153,7 +32153,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1015" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32179,7 +32179,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1016" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32205,7 +32205,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1017" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32231,7 +32231,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G1018" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32257,7 +32257,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1019" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32283,7 +32283,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1020" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32309,7 +32309,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1021" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32335,7 +32335,7 @@
         <v>19.75</v>
       </c>
       <c r="G1022" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32361,7 +32361,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1023" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32387,7 +32387,7 @@
         <v>20.5</v>
       </c>
       <c r="G1024" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -32413,7 +32413,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1025" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -32439,7 +32439,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -32465,7 +32465,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1027" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -32491,7 +32491,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1028" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -32517,7 +32517,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -32543,7 +32543,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -32569,7 +32569,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1031" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32595,7 +32595,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G1032" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -32621,7 +32621,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1033" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -32647,7 +32647,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1034" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -32673,7 +32673,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1035" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -32699,7 +32699,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G1036" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -32725,7 +32725,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G1037" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -32751,7 +32751,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1038" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -32777,7 +32777,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1039" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -32803,7 +32803,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1040" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -32829,7 +32829,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1041" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -32855,7 +32855,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1042" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -32881,7 +32881,7 @@
         <v>22</v>
       </c>
       <c r="G1043" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -32907,7 +32907,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1044" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -32933,7 +32933,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1045" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -32959,7 +32959,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1046" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -32985,7 +32985,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1047" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -33011,7 +33011,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1048" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -33037,7 +33037,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G1049" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -33063,7 +33063,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G1050" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -33089,7 +33089,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G1051" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -33115,7 +33115,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1052" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -33141,7 +33141,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1053" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -33167,7 +33167,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -33193,7 +33193,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G1055" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -33219,7 +33219,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1056" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -33245,7 +33245,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -33271,7 +33271,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1058" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -33297,7 +33297,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1059" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -33323,7 +33323,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G1060" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -33349,7 +33349,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1061" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -33375,7 +33375,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1062" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -33401,7 +33401,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1063" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33427,7 +33427,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1064" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -33453,7 +33453,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1065" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -33479,7 +33479,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1066" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -33505,7 +33505,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1067" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -33531,7 +33531,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -33557,7 +33557,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1069" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -33583,7 +33583,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1070" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -33609,7 +33609,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1071" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -33635,7 +33635,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1072" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -33661,7 +33661,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1073" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -33687,7 +33687,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1074" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -33713,7 +33713,7 @@
         <v>15.25</v>
       </c>
       <c r="G1075" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -33739,7 +33739,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1076" t="s">
-        <v>778</v>
+        <v>606</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -34077,7 +34077,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1089" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -34207,7 +34207,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1094" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -34285,7 +34285,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1097" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -34389,7 +34389,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1101" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34467,7 +34467,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -34571,7 +34571,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G1108" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -70589,7 +70589,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6494675926</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>452983</v>
@@ -70610,6 +70610,32 @@
         <v>1806</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6495138889</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>346127</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>22.9799995422363</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1806</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="1809">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="1810">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48755502700806</t>
+    <t xml:space="preserve">7.48755407333374</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43893337249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23837327957153</t>
+    <t xml:space="preserve">7.43893432617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23837471008301</t>
   </si>
   <si>
     <t xml:space="preserve">7.04389238357544</t>
@@ -56,22 +56,22 @@
     <t xml:space="preserve">6.99527215957642</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06212520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25053071975708</t>
+    <t xml:space="preserve">7.06212472915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25052928924561</t>
   </si>
   <si>
     <t xml:space="preserve">7.22014236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17152261734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07427978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84941101074219</t>
+    <t xml:space="preserve">7.17152214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07428073883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84941005706787</t>
   </si>
   <si>
     <t xml:space="preserve">7.01350450515747</t>
@@ -80,52 +80,52 @@
     <t xml:space="preserve">6.75216913223267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83725595474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97096252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09251356124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00742721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00134992599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98919439315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92841911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86156558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5333776473999</t>
+    <t xml:space="preserve">6.83725643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9709620475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0925121307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00742673873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00134944915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98919486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92841815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86156463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53337717056274</t>
   </si>
   <si>
     <t xml:space="preserve">6.47867965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61238670349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55160903930664</t>
+    <t xml:space="preserve">6.61238527297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55160999298096</t>
   </si>
   <si>
     <t xml:space="preserve">6.77647924423218</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94057464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87372064590454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63061809539795</t>
+    <t xml:space="preserve">6.94057512283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8737211227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63061857223511</t>
   </si>
   <si>
     <t xml:space="preserve">6.78863477706909</t>
@@ -134,91 +134,91 @@
     <t xml:space="preserve">6.58199691772461</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70354795455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71570348739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8068675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91626405715942</t>
+    <t xml:space="preserve">6.7035493850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7157039642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80686712265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91626501083374</t>
   </si>
   <si>
     <t xml:space="preserve">6.84333372116089</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83117771148682</t>
+    <t xml:space="preserve">6.8311767578125</t>
   </si>
   <si>
     <t xml:space="preserve">6.879798412323</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70962619781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74609136581421</t>
+    <t xml:space="preserve">6.70962715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74609184265137</t>
   </si>
   <si>
     <t xml:space="preserve">6.85548830032349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86764287948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95272922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04996967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27483987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35992574691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34776973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26876163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22621965408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11074447631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03173685073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08035802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05604696273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975496292114</t>
+    <t xml:space="preserve">6.8676438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95272779464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04997110366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27483940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35992670059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34777069091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26876211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22621917724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11074495315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03173732757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08035755157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05604648590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975400924683</t>
   </si>
   <si>
     <t xml:space="preserve">7.23229646682739</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15328979492188</t>
+    <t xml:space="preserve">7.15328931808472</t>
   </si>
   <si>
     <t xml:space="preserve">7.11682319641113</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16544437408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95880651473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93449640274048</t>
+    <t xml:space="preserve">7.165442943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95880746841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93449687957764</t>
   </si>
   <si>
     <t xml:space="preserve">6.89803171157837</t>
@@ -230,157 +230,157 @@
     <t xml:space="preserve">6.96488428115845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79471254348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76432466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1411337852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02565956115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15738677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13741254806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31052160263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25725698471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34381055831909</t>
+    <t xml:space="preserve">6.79471206665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76432514190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14113283157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02566051483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.157386302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13741207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3105206489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25725650787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34381198883057</t>
   </si>
   <si>
     <t xml:space="preserve">7.38375949859619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29720544815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25060033798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21730899810791</t>
+    <t xml:space="preserve">7.29720640182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25059986114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21731042861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.23062467575073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23728322982788</t>
+    <t xml:space="preserve">7.23728370666504</t>
   </si>
   <si>
     <t xml:space="preserve">7.27723121643066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22396659851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10412311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85777425765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.658034324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60477018356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47493886947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50822973251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95764493942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93767261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82448482513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88440752029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47826623916626</t>
+    <t xml:space="preserve">7.22396755218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10412263870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85777521133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65803527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60476970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.474937915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50822830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95764541625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93767213821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82448530197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88440799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47826671600342</t>
   </si>
   <si>
     <t xml:space="preserve">6.32180404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56149291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69132471084595</t>
+    <t xml:space="preserve">6.56149244308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69132375717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.81782627105713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91769742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03754138946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78453636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5048999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61808633804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71795701980591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68466711044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73793077468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87774991989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81116914749146</t>
+    <t xml:space="preserve">6.9176983833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03754281997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78453683853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50490093231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61808490753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71795654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68466758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73793029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8777494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8111686706543</t>
   </si>
   <si>
     <t xml:space="preserve">6.7512469291687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79119348526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76456260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86443328857422</t>
+    <t xml:space="preserve">6.79119539260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76456356048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86443376541138</t>
   </si>
   <si>
     <t xml:space="preserve">6.7712197303772</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89106607437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73127222061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64471769332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63806009292603</t>
+    <t xml:space="preserve">6.89106559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73127269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64471864700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63805961608887</t>
   </si>
   <si>
     <t xml:space="preserve">6.75790452957153</t>
@@ -389,40 +389,40 @@
     <t xml:space="preserve">6.83114290237427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80451154708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101453781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96430397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74458980560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71129894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65137577056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62807273864746</t>
+    <t xml:space="preserve">6.80451059341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101263046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96430444717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74458932876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71129846572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65137434005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62807321548462</t>
   </si>
   <si>
     <t xml:space="preserve">6.6413893699646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62141466140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01756858825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98427867889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01090955734253</t>
+    <t xml:space="preserve">6.62141370773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01756811141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98427724838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01091003417969</t>
   </si>
   <si>
     <t xml:space="preserve">7.04419946670532</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">7.17070293426514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87109088897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92435503005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97761869430542</t>
+    <t xml:space="preserve">6.87109041213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92435550689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97762012481689</t>
   </si>
   <si>
     <t xml:space="preserve">6.83780145645142</t>
@@ -446,43 +446,43 @@
     <t xml:space="preserve">6.84445905685425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79785251617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77787828445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59811115264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55150556564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72461462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67135047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66469240188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60809946060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54484796524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45829343795776</t>
+    <t xml:space="preserve">6.79785299301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77787971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59811162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55150508880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7246150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67135000228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66469287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60809993743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54484748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45829296112061</t>
   </si>
   <si>
     <t xml:space="preserve">6.65470504760742</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67800903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46495056152344</t>
+    <t xml:space="preserve">6.67800760269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46495151519775</t>
   </si>
   <si>
     <t xml:space="preserve">6.13870763778687</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">6.19197130203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17865610122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24856519699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13537883758545</t>
+    <t xml:space="preserve">6.17865562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24856472015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13537836074829</t>
   </si>
   <si>
     <t xml:space="preserve">6.06546878814697</t>
@@ -512,85 +512,85 @@
     <t xml:space="preserve">6.15868139266968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14203643798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06213998794556</t>
+    <t xml:space="preserve">6.14203691482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0621395111084</t>
   </si>
   <si>
     <t xml:space="preserve">6.03883695602417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10874652862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881118774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02219247817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01886224746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11873340606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2319188117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12206268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22193336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21860408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35842227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37839651107788</t>
+    <t xml:space="preserve">6.10874700546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0588116645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02219200134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0188627243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11873292922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23191976547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12206220626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22193384170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21860361099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35842275619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37839603424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.6247444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70464038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85111713409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6979832649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90438175201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89772367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99093532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07749032974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91103887557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0708327293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13075542449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15072822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18401956558228</t>
+    <t xml:space="preserve">6.70463991165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85111665725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69798231124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.904381275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89772319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99093580245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07748937606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91103935241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07083177566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1307544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15072870254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18401861190796</t>
   </si>
   <si>
     <t xml:space="preserve">7.0974645614624</t>
@@ -599,121 +599,121 @@
     <t xml:space="preserve">7.05085849761963</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35046911239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27057361602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28389024734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30386400222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53023624420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32383728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31717967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36378574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51692056655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59015893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347557067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992654800415</t>
+    <t xml:space="preserve">7.35047006607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27057313919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28388977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30386257171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53023672103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32383871078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31718015670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3637843132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51691961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59015798568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347604751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71000289916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992511749268</t>
   </si>
   <si>
     <t xml:space="preserve">7.77658462524414</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73663568496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78989887237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75660991668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82319068908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85648155212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86979627609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87645530700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308618545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96966695785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94969272613525</t>
+    <t xml:space="preserve">7.73663520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78989934921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75660943984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82318925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85648107528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86979675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87645435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96966648101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94969320297241</t>
   </si>
   <si>
     <t xml:space="preserve">7.92305994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96300840377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7233190536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62344884872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54355192184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47031545639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63676595687866</t>
+    <t xml:space="preserve">7.96300888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311243057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72332048416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62344980239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54355239868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47031450271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6367654800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.56352567672729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57018423080444</t>
+    <t xml:space="preserve">7.5701847076416</t>
   </si>
   <si>
     <t xml:space="preserve">7.74329376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80321455001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89642858505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94303607940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84982299804688</t>
+    <t xml:space="preserve">7.80321598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89642810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94303417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8498215675354</t>
   </si>
   <si>
     <t xml:space="preserve">8.06953811645508</t>
@@ -722,22 +722,22 @@
     <t xml:space="preserve">8.20842742919922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25009441375732</t>
+    <t xml:space="preserve">8.25009536743164</t>
   </si>
   <si>
     <t xml:space="preserve">8.22926139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31954002380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35426235198975</t>
+    <t xml:space="preserve">8.31953907012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35426139831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.28481769561768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2987060546875</t>
+    <t xml:space="preserve">8.29870700836182</t>
   </si>
   <si>
     <t xml:space="preserve">8.37509632110596</t>
@@ -746,43 +746,43 @@
     <t xml:space="preserve">8.34731769561768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38898468017578</t>
+    <t xml:space="preserve">8.3889856338501</t>
   </si>
   <si>
     <t xml:space="preserve">8.43759632110596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4514856338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68760013580322</t>
+    <t xml:space="preserve">8.45148658752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68760108947754</t>
   </si>
   <si>
     <t xml:space="preserve">8.73621273040771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62509918212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63898754119873</t>
+    <t xml:space="preserve">8.62510013580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63898849487305</t>
   </si>
   <si>
     <t xml:space="preserve">8.66676616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68065547943115</t>
+    <t xml:space="preserve">8.68065357208252</t>
   </si>
   <si>
     <t xml:space="preserve">8.59732055664062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72926807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69454479217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61121082305908</t>
+    <t xml:space="preserve">8.72926712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69454383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61120986938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.50704288482666</t>
@@ -797,10 +797,10 @@
     <t xml:space="preserve">8.54870986938477</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4931526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5139856338501</t>
+    <t xml:space="preserve">8.49315166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51398658752441</t>
   </si>
   <si>
     <t xml:space="preserve">8.46537590026855</t>
@@ -809,43 +809,43 @@
     <t xml:space="preserve">8.47231960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61815452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65982151031494</t>
+    <t xml:space="preserve">8.61815357208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65982246398926</t>
   </si>
   <si>
     <t xml:space="preserve">8.64593315124512</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40981769561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4306526184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42370700836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30564975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5417652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57648754119873</t>
+    <t xml:space="preserve">8.40981864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43065166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42370986938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30565071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54176425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57648849487305</t>
   </si>
   <si>
     <t xml:space="preserve">8.6042652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71537780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88204574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00010395050049</t>
+    <t xml:space="preserve">8.7153787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88204669952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00010299682617</t>
   </si>
   <si>
     <t xml:space="preserve">9.15288352966309</t>
@@ -854,22 +854,22 @@
     <t xml:space="preserve">9.13204860687256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06954956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09038257598877</t>
+    <t xml:space="preserve">9.06954860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09038162231445</t>
   </si>
   <si>
     <t xml:space="preserve">9.00704765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95843696594238</t>
+    <t xml:space="preserve">8.95843601226807</t>
   </si>
   <si>
     <t xml:space="preserve">9.06260395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12510585784912</t>
+    <t xml:space="preserve">9.1251049041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.20843887329102</t>
@@ -884,28 +884,28 @@
     <t xml:space="preserve">9.3681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40983104705811</t>
+    <t xml:space="preserve">9.40982913970947</t>
   </si>
   <si>
     <t xml:space="preserve">9.41677570343018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32649707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29177379608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31260681152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45149803161621</t>
+    <t xml:space="preserve">9.32649612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29177474975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31260776519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45149707794189</t>
   </si>
   <si>
     <t xml:space="preserve">9.47233104705811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43760967254639</t>
+    <t xml:space="preserve">9.43760871887207</t>
   </si>
   <si>
     <t xml:space="preserve">9.44455337524414</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">9.48621940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75011253356934</t>
+    <t xml:space="preserve">9.75011157989502</t>
   </si>
   <si>
     <t xml:space="preserve">9.79177951812744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7778902053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80566787719727</t>
+    <t xml:space="preserve">9.77788925170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80566883087158</t>
   </si>
   <si>
     <t xml:space="preserve">9.72927856445312</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">9.77094554901123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76400089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74316596984863</t>
+    <t xml:space="preserve">9.76400184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74316692352295</t>
   </si>
   <si>
     <t xml:space="preserve">9.96539115905762</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">9.93761444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834503173828</t>
+    <t xml:space="preserve">10.0834512710571</t>
   </si>
   <si>
     <t xml:space="preserve">10.1181716918945</t>
@@ -977,22 +977,22 @@
     <t xml:space="preserve">10.4445648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5001201629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5695667266846</t>
+    <t xml:space="preserve">10.5001211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5695657730103</t>
   </si>
   <si>
     <t xml:space="preserve">10.229284286499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3959531784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4237308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5903987884521</t>
+    <t xml:space="preserve">10.3959522247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.423731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5903997421265</t>
   </si>
   <si>
     <t xml:space="preserve">10.4931764602661</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">10.5626220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6251220703125</t>
+    <t xml:space="preserve">10.6251230239868</t>
   </si>
   <si>
     <t xml:space="preserve">10.6042890548706</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">10.7779016494751</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8542909622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.833456993103</t>
+    <t xml:space="preserve">10.8542900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8334579467773</t>
   </si>
   <si>
     <t xml:space="preserve">10.9029035568237</t>
@@ -1031,40 +1031,40 @@
     <t xml:space="preserve">11.1112384796143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6667900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9723491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9445695877075</t>
+    <t xml:space="preserve">10.6667890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9723501205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9445705413818</t>
   </si>
   <si>
     <t xml:space="preserve">11.0765171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3473529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3959646224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1529054641724</t>
+    <t xml:space="preserve">11.3473520278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3959636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1529064178467</t>
   </si>
   <si>
     <t xml:space="preserve">11.0626268386841</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2154054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3126306533813</t>
+    <t xml:space="preserve">11.2154064178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3126316070557</t>
   </si>
   <si>
     <t xml:space="preserve">11.2362403869629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2084608078003</t>
+    <t xml:space="preserve">11.2084617614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.9098482131958</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">10.7362356185913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8751239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6945667266846</t>
+    <t xml:space="preserve">10.8751249313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6945657730103</t>
   </si>
   <si>
     <t xml:space="preserve">10.548731803894</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">11.0695714950562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.187629699707</t>
+    <t xml:space="preserve">11.1876287460327</t>
   </si>
   <si>
     <t xml:space="preserve">10.9306802749634</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1598491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4515199661255</t>
+    <t xml:space="preserve">11.1598510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4515209197998</t>
   </si>
   <si>
     <t xml:space="preserve">11.5001316070557</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">11.4931879043579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6251354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7223567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709703445435</t>
+    <t xml:space="preserve">11.6251344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7223558425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709684371948</t>
   </si>
   <si>
     <t xml:space="preserve">11.7015247344971</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">11.6112442016602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4862432479858</t>
+    <t xml:space="preserve">11.4862451553345</t>
   </si>
   <si>
     <t xml:space="preserve">11.5765218734741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6806888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3820753097534</t>
+    <t xml:space="preserve">11.6806898117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3820743560791</t>
   </si>
   <si>
     <t xml:space="preserve">10.8681793212891</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">10.8959579467773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9862365722656</t>
+    <t xml:space="preserve">10.9862375259399</t>
   </si>
   <si>
     <t xml:space="preserve">11.0834608078003</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292957305908</t>
+    <t xml:space="preserve">11.2292966842651</t>
   </si>
   <si>
     <t xml:space="preserve">11.2848520278931</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">11.2431859970093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5973567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7501344680786</t>
+    <t xml:space="preserve">11.5973558425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7501354217529</t>
   </si>
   <si>
     <t xml:space="preserve">11.6181888580322</t>
@@ -1181,82 +1181,82 @@
     <t xml:space="preserve">11.6320772171021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334712982178</t>
+    <t xml:space="preserve">11.8334693908691</t>
   </si>
   <si>
     <t xml:space="preserve">12.1251392364502</t>
   </si>
   <si>
-    <t xml:space="preserve">11.916805267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6668119430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1529293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3821001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3195991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3682107925415</t>
+    <t xml:space="preserve">11.9168033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6668109893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1529302597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3820962905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.319598197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3682098388672</t>
   </si>
   <si>
     <t xml:space="preserve">13.576545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5209875106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2362642288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1668176651001</t>
+    <t xml:space="preserve">13.5209884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2362632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1668167114258</t>
   </si>
   <si>
     <t xml:space="preserve">13.0487623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4237651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0070934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3543214797974</t>
+    <t xml:space="preserve">13.4237661361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070943832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.354320526123</t>
   </si>
   <si>
     <t xml:space="preserve">13.4584865570068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154359817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918243408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6807117462158</t>
+    <t xml:space="preserve">13.7154340744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918252944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6807136535645</t>
   </si>
   <si>
     <t xml:space="preserve">13.9168262481689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9307146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1876525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2987651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3751544952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4168195724487</t>
+    <t xml:space="preserve">13.9307155609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1876516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2987632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3751535415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.416820526123</t>
   </si>
   <si>
     <t xml:space="preserve">13.4723768234253</t>
@@ -1265,13 +1265,13 @@
     <t xml:space="preserve">13.4862661361694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6112661361694</t>
+    <t xml:space="preserve">13.6112680435181</t>
   </si>
   <si>
     <t xml:space="preserve">13.7362699508667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7223787307739</t>
+    <t xml:space="preserve">13.7223815917969</t>
   </si>
   <si>
     <t xml:space="preserve">13.8196048736572</t>
@@ -1280,22 +1280,22 @@
     <t xml:space="preserve">13.8890495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8543252944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9029369354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0834941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7987689971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0279417037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057193756104</t>
+    <t xml:space="preserve">13.8543262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9029388427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0834951400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7987718582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0279397964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057203292847</t>
   </si>
   <si>
     <t xml:space="preserve">13.1945962905884</t>
@@ -1304,22 +1304,22 @@
     <t xml:space="preserve">13.1112623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1807060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0200996398926</t>
+    <t xml:space="preserve">13.1807050704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0200986862183</t>
   </si>
   <si>
     <t xml:space="preserve">14.1486539840698</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8083591461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6571187973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5361251831055</t>
+    <t xml:space="preserve">13.8083581924438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6571197509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5361232757568</t>
   </si>
   <si>
     <t xml:space="preserve">13.2563285827637</t>
@@ -1328,82 +1328,82 @@
     <t xml:space="preserve">13.1277732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3092613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.460503578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4983148574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4680671691895</t>
+    <t xml:space="preserve">13.3092632293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4605045318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4983139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4680662155151</t>
   </si>
   <si>
     <t xml:space="preserve">13.5739345550537</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7327375411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7478618621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4075698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4889488220215</t>
+    <t xml:space="preserve">13.7327394485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7478647232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4075689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4889469146729</t>
   </si>
   <si>
     <t xml:space="preserve">14.4738235473633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6704368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755168914795</t>
+    <t xml:space="preserve">14.6704378128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158098220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755178451538</t>
   </si>
   <si>
     <t xml:space="preserve">14.6175022125244</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7233715057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9351100921631</t>
+    <t xml:space="preserve">14.723370552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9351081848145</t>
   </si>
   <si>
     <t xml:space="preserve">14.7460565567017</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8292398452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167119979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2998943328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2091512680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0654716491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1637773513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0427846908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1713390350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2847709655762</t>
+    <t xml:space="preserve">14.8292436599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2998933792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2091503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0654706954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1637763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0427856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1713380813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2847728729248</t>
   </si>
   <si>
     <t xml:space="preserve">14.6250648498535</t>
@@ -1412,49 +1412,49 @@
     <t xml:space="preserve">14.7536182403564</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6779975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7914304733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8443622589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8746137619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8368043899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7611827850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.655312538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5494451522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.609938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.640191078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5721321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5191946029663</t>
+    <t xml:space="preserve">14.6779985427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.791428565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8443641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8746156692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8368034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7611837387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6553115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5494441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099405288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6401901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5721302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5191965103149</t>
   </si>
   <si>
     <t xml:space="preserve">14.2393989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0049753189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9217920303345</t>
+    <t xml:space="preserve">14.0049743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9217910766602</t>
   </si>
   <si>
     <t xml:space="preserve">13.9142293930054</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">14.3982028961182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9898500442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6646785736084</t>
+    <t xml:space="preserve">13.9898490905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6646795272827</t>
   </si>
   <si>
     <t xml:space="preserve">13.6722412109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5814952850342</t>
+    <t xml:space="preserve">13.5814971923828</t>
   </si>
   <si>
     <t xml:space="preserve">13.7705488204956</t>
@@ -1484,13 +1484,13 @@
     <t xml:space="preserve">13.6268701553345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5210008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5512495040894</t>
+    <t xml:space="preserve">13.5210018157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495571136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5512504577637</t>
   </si>
   <si>
     <t xml:space="preserve">13.4907522201538</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">13.4756288528442</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5058765411377</t>
+    <t xml:space="preserve">13.505877494812</t>
   </si>
   <si>
     <t xml:space="preserve">13.3470726013184</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">13.3924446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4831895828247</t>
+    <t xml:space="preserve">13.483190536499</t>
   </si>
   <si>
     <t xml:space="preserve">13.8310470581055</t>
@@ -1517,22 +1517,22 @@
     <t xml:space="preserve">13.6344327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5663738250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5436878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3773212432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1958312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2714519500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3395118713379</t>
+    <t xml:space="preserve">13.5663747787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5436859130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3773221969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1958341598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2714500427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3395099639893</t>
   </si>
   <si>
     <t xml:space="preserve">13.3546342849731</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">12.9311599731445</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0219039916992</t>
+    <t xml:space="preserve">13.0219030380249</t>
   </si>
   <si>
     <t xml:space="preserve">12.8101654052734</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">12.5530557632446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7421073913574</t>
+    <t xml:space="preserve">12.7421083450317</t>
   </si>
   <si>
     <t xml:space="preserve">12.6513614654541</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">13.3848838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">13.120210647583</t>
+    <t xml:space="preserve">13.1202096939087</t>
   </si>
   <si>
     <t xml:space="preserve">12.9614067077637</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">12.4396238327026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6211137771606</t>
+    <t xml:space="preserve">12.621114730835</t>
   </si>
   <si>
     <t xml:space="preserve">12.4018125534058</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">12.4925584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4698715209961</t>
+    <t xml:space="preserve">12.4698724746704</t>
   </si>
   <si>
     <t xml:space="preserve">12.1371393203735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2883815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1522626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6286764144897</t>
+    <t xml:space="preserve">12.2883825302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1522645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6286754608154</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437997817993</t>
@@ -1610,31 +1610,31 @@
     <t xml:space="preserve">12.825288772583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7723550796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.847975730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.757230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8177289962769</t>
+    <t xml:space="preserve">12.7723541259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8479747772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7572298049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8177270889282</t>
   </si>
   <si>
     <t xml:space="preserve">12.77991771698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4471855163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4244995117188</t>
+    <t xml:space="preserve">12.4471845626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4245004653931</t>
   </si>
   <si>
     <t xml:space="preserve">12.2581329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1673889160156</t>
+    <t xml:space="preserve">12.1673879623413</t>
   </si>
   <si>
     <t xml:space="preserve">12.416937828064</t>
@@ -1643,19 +1643,19 @@
     <t xml:space="preserve">12.1447019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.031270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2505712509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1068916320801</t>
+    <t xml:space="preserve">12.0312700271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2505722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1068935394287</t>
   </si>
   <si>
     <t xml:space="preserve">12.2278852462769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0463943481445</t>
+    <t xml:space="preserve">12.0463953018188</t>
   </si>
   <si>
     <t xml:space="preserve">12.0993299484253</t>
@@ -1667,46 +1667,46 @@
     <t xml:space="preserve">11.8800296783447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5379314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2656955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7950410842896</t>
+    <t xml:space="preserve">12.5379304885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2656946182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7950420379639</t>
   </si>
   <si>
     <t xml:space="preserve">13.2941389083862</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1126489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9538440704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5833034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4774341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5757417678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8555383682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0143404006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8328504562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9084720611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0521516799927</t>
+    <t xml:space="preserve">13.1126499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9538431167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5833024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4774332046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5757398605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8555374145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0143413543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8328523635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9084711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.052152633667</t>
   </si>
   <si>
     <t xml:space="preserve">13.1807069778442</t>
@@ -1715,10 +1715,10 @@
     <t xml:space="preserve">12.9160346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0975246429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0067796707153</t>
+    <t xml:space="preserve">13.0975255966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.006781578064</t>
   </si>
   <si>
     <t xml:space="preserve">13.2260789871216</t>
@@ -1727,22 +1727,22 @@
     <t xml:space="preserve">13.2185163497925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9009094238281</t>
+    <t xml:space="preserve">12.9009103775024</t>
   </si>
   <si>
     <t xml:space="preserve">13.0370273590088</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7647924423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0294647216797</t>
+    <t xml:space="preserve">12.7647914886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.029465675354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2109546661377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2336416244507</t>
+    <t xml:space="preserve">13.233642578125</t>
   </si>
   <si>
     <t xml:space="preserve">12.9235973358154</t>
@@ -1754,19 +1754,19 @@
     <t xml:space="preserve">12.893346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.188268661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353359222412</t>
+    <t xml:space="preserve">13.1882696151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353349685669</t>
   </si>
   <si>
     <t xml:space="preserve">12.9689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1050863265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3016996383667</t>
+    <t xml:space="preserve">13.1050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.301700592041</t>
   </si>
   <si>
     <t xml:space="preserve">12.8857879638672</t>
@@ -1775,28 +1775,28 @@
     <t xml:space="preserve">12.689172744751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6967363357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6362371444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.666485786438</t>
+    <t xml:space="preserve">12.6967344284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6362361907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6664848327637</t>
   </si>
   <si>
     <t xml:space="preserve">12.5152444839478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3110675811768</t>
+    <t xml:space="preserve">12.3110685348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.2430095672607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0388326644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6589260101318</t>
+    <t xml:space="preserve">12.0388336181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6589241027832</t>
   </si>
   <si>
     <t xml:space="preserve">12.7269821166992</t>
@@ -1805,73 +1805,73 @@
     <t xml:space="preserve">12.7496700286865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3186302185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.19007396698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1976356506348</t>
+    <t xml:space="preserve">12.3186311721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1900749206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1976366043091</t>
   </si>
   <si>
     <t xml:space="preserve">12.1749505996704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2732563018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1598262786865</t>
+    <t xml:space="preserve">12.2732572555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1598272323608</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2808198928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3035068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8631000518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2902879714966</t>
+    <t xml:space="preserve">12.280818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.303505897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8630990982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2902870178223</t>
   </si>
   <si>
     <t xml:space="preserve">13.4485054016113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5988130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9548015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9785327911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8598709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.749116897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7332983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7728538513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.812406539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.717474937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6383666992188</t>
+    <t xml:space="preserve">13.5988121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6146326065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9548025131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.978533744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8598718643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7491188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7332973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7728509902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8124046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7174758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6383657455444</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620988845825</t>
@@ -1880,22 +1880,22 @@
     <t xml:space="preserve">13.5750789642334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.144660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.239595413208</t>
+    <t xml:space="preserve">14.1446619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2395935058594</t>
   </si>
   <si>
     <t xml:space="preserve">14.5085639953613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4690113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955829620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7221565246582</t>
+    <t xml:space="preserve">14.4690093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7221574783325</t>
   </si>
   <si>
     <t xml:space="preserve">14.674690246582</t>
@@ -1904,91 +1904,91 @@
     <t xml:space="preserve">14.1763067245483</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1604852676392</t>
+    <t xml:space="preserve">14.1604843139648</t>
   </si>
   <si>
     <t xml:space="preserve">14.0813770294189</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0339107513428</t>
+    <t xml:space="preserve">14.0339097976685</t>
   </si>
   <si>
     <t xml:space="preserve">14.4373664855957</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6984262466431</t>
+    <t xml:space="preserve">14.6984243392944</t>
   </si>
   <si>
     <t xml:space="preserve">14.611403465271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4136323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6272296905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1097927093506</t>
+    <t xml:space="preserve">14.4136333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6272277832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1097917556763</t>
   </si>
   <si>
     <t xml:space="preserve">15.0939693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9911279678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9436616897583</t>
+    <t xml:space="preserve">14.9911289215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.943660736084</t>
   </si>
   <si>
     <t xml:space="preserve">14.9120187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">14.872465133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8645544052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.643048286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2870578765869</t>
+    <t xml:space="preserve">14.8724632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8645553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6430492401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2870597839355</t>
   </si>
   <si>
     <t xml:space="preserve">14.3266143798828</t>
   </si>
   <si>
-    <t xml:space="preserve">14.215859413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2475051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0259990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0576419830322</t>
+    <t xml:space="preserve">14.2158603668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2475032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0260000228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0576438903809</t>
   </si>
   <si>
     <t xml:space="preserve">13.6067237854004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8677825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000389099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2949686050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2079486846924</t>
+    <t xml:space="preserve">13.8677835464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000408172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2949714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2079496383667</t>
   </si>
   <si>
     <t xml:space="preserve">13.6304550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5671682357788</t>
+    <t xml:space="preserve">13.5671691894531</t>
   </si>
   <si>
     <t xml:space="preserve">13.6700096130371</t>
@@ -1997,64 +1997,64 @@
     <t xml:space="preserve">13.519702911377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3693962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8203153610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9073352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.844051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5592575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7886724472046</t>
+    <t xml:space="preserve">13.3693952560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8203163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9073371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.844048500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5592565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7886734008789</t>
   </si>
   <si>
     <t xml:space="preserve">13.7965841293335</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1209316253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9310712814331</t>
+    <t xml:space="preserve">14.1209306716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9310703277588</t>
   </si>
   <si>
     <t xml:space="preserve">14.0892877578735</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3028793334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4848308563232</t>
+    <t xml:space="preserve">14.3028812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4848299026489</t>
   </si>
   <si>
     <t xml:space="preserve">14.6588726043701</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2633266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2316837310791</t>
+    <t xml:space="preserve">14.2633275985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2316827774048</t>
   </si>
   <si>
     <t xml:space="preserve">14.1130199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5876741409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9753084182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8566446304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9990377426147</t>
+    <t xml:space="preserve">14.5876722335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9753046035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8566427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9990386962891</t>
   </si>
   <si>
     <t xml:space="preserve">14.8329095840454</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">15.0227708816528</t>
   </si>
   <si>
-    <t xml:space="preserve">14.737979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6905136108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6351385116577</t>
+    <t xml:space="preserve">14.7379779815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6905126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351375579834</t>
   </si>
   <si>
     <t xml:space="preserve">14.5402069091797</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">14.1525745391846</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5164747238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4294557571411</t>
+    <t xml:space="preserve">14.5164756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4294548034668</t>
   </si>
   <si>
     <t xml:space="preserve">14.1921291351318</t>
@@ -2096,130 +2096,130 @@
     <t xml:space="preserve">14.0971975326538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2712392807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2791481018066</t>
+    <t xml:space="preserve">14.2712383270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.279146194458</t>
   </si>
   <si>
     <t xml:space="preserve">14.4057216644287</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3899030685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3424348831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3582572937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4610986709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0069494247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9515743255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5322961807251</t>
+    <t xml:space="preserve">14.3899011611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.342432975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3582563400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4610977172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0069465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9515724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5322980880737</t>
   </si>
   <si>
     <t xml:space="preserve">14.3345241546631</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3740768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3819894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6509599685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0860586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8170890808105</t>
+    <t xml:space="preserve">14.3740787506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3819904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0860576629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8170871734619</t>
   </si>
   <si>
     <t xml:space="preserve">14.6193151473999</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0544176101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4895143508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8692331314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7189292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.307562828064</t>
+    <t xml:space="preserve">15.0544137954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4895124435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.869236946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7189302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3075647354126</t>
   </si>
   <si>
     <t xml:space="preserve">15.3471174240112</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6081762313843</t>
+    <t xml:space="preserve">15.6081781387329</t>
   </si>
   <si>
     <t xml:space="preserve">15.2284545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1572551727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1889019012451</t>
+    <t xml:space="preserve">15.1572542190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1888990402222</t>
   </si>
   <si>
     <t xml:space="preserve">15.1414337158203</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3866710662842</t>
+    <t xml:space="preserve">15.3866748809814</t>
   </si>
   <si>
     <t xml:space="preserve">15.2838315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3154726028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7505712509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7110185623169</t>
+    <t xml:space="preserve">15.3154754638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7505750656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7110195159912</t>
   </si>
   <si>
     <t xml:space="preserve">15.6160869598389</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4420471191406</t>
+    <t xml:space="preserve">15.4420509338379</t>
   </si>
   <si>
     <t xml:space="preserve">15.2047214508057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.236364364624</t>
+    <t xml:space="preserve">15.2363662719727</t>
   </si>
   <si>
     <t xml:space="preserve">15.1651678085327</t>
   </si>
   <si>
-    <t xml:space="preserve">15.402494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6239986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7743072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2173137664795</t>
+    <t xml:space="preserve">15.4024934768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6240005493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7743053436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2173156738281</t>
   </si>
   <si>
     <t xml:space="preserve">16.5179290771484</t>
@@ -2234,25 +2234,25 @@
     <t xml:space="preserve">17.0400466918945</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0875129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9609413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.691967010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8976516723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.198263168335</t>
+    <t xml:space="preserve">16.929292678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0875148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6919689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8976497650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1982650756836</t>
   </si>
   <si>
     <t xml:space="preserve">16.8818302154541</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">17.3564834594727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4514141082764</t>
+    <t xml:space="preserve">17.451416015625</t>
   </si>
   <si>
     <t xml:space="preserve">17.6096305847168</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">17.4355926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305213928223</t>
+    <t xml:space="preserve">17.5305233001709</t>
   </si>
   <si>
     <t xml:space="preserve">17.8786010742188</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">18.1792125701904</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1317501068115</t>
+    <t xml:space="preserve">18.1317481994629</t>
   </si>
   <si>
     <t xml:space="preserve">18.2583236694336</t>
@@ -2303,10 +2303,10 @@
     <t xml:space="preserve">17.3723030090332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4830570220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7045612335205</t>
+    <t xml:space="preserve">17.4830589294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7045593261719</t>
   </si>
   <si>
     <t xml:space="preserve">17.3248386383057</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">17.1508007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1701707839966</t>
+    <t xml:space="preserve">11.1701698303223</t>
   </si>
   <si>
     <t xml:space="preserve">13.0213174819946</t>
@@ -2336,85 +2336,85 @@
     <t xml:space="preserve">11.6290016174316</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3600311279297</t>
+    <t xml:space="preserve">11.360032081604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9882202148438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4470500946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0245447158813</t>
+    <t xml:space="preserve">11.4470510482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.024543762207</t>
   </si>
   <si>
     <t xml:space="preserve">12.0641002655029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.420090675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1748533248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9026546478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6969709396362</t>
+    <t xml:space="preserve">12.4200897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1748523712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9026536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6969699859619</t>
   </si>
   <si>
     <t xml:space="preserve">13.2190885543823</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4722375869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.314019203186</t>
+    <t xml:space="preserve">13.4722385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3140211105347</t>
   </si>
   <si>
     <t xml:space="preserve">13.2349109649658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1241579055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4089517593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4564170837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1004257202148</t>
+    <t xml:space="preserve">13.1241598129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4089508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4564161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1004266738892</t>
   </si>
   <si>
     <t xml:space="preserve">13.0925149917603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2507343292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687828063965</t>
+    <t xml:space="preserve">13.2507333755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687837600708</t>
   </si>
   <si>
     <t xml:space="preserve">13.3614845275879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4326820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5038805007935</t>
+    <t xml:space="preserve">13.4326829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5038814544678</t>
   </si>
   <si>
     <t xml:space="preserve">12.9738521575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9342985153198</t>
+    <t xml:space="preserve">12.9342966079712</t>
   </si>
   <si>
     <t xml:space="preserve">13.0371389389038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1795349121094</t>
+    <t xml:space="preserve">13.1795358657837</t>
   </si>
   <si>
     <t xml:space="preserve">13.2111797332764</t>
@@ -2426,22 +2426,22 @@
     <t xml:space="preserve">13.6225442886353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7095642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2056903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418655395508</t>
+    <t xml:space="preserve">13.7095632553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2056884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418645858765</t>
   </si>
   <si>
     <t xml:space="preserve">14.1560773849487</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2966451644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2883768081665</t>
+    <t xml:space="preserve">14.2966470718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2883758544922</t>
   </si>
   <si>
     <t xml:space="preserve">15.0490999221802</t>
@@ -2450,13 +2450,13 @@
     <t xml:space="preserve">15.2475500106812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2971630096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1240348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4134426116943</t>
+    <t xml:space="preserve">15.2971611022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1240367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4134407043457</t>
   </si>
   <si>
     <t xml:space="preserve">16.5043964385986</t>
@@ -2465,61 +2465,61 @@
     <t xml:space="preserve">16.1405735015869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0909595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.190185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5865688323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2144737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2806253433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8346290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.652717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692552566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5782985687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932872772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8594388961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633108139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4294633865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5617589950562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8677043914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.330753326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0501365661621</t>
+    <t xml:space="preserve">16.0909614562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1901836395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5865678787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3467741012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2144746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2806234359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8346300125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6527166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5782995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932863235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8594379425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633127212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4294595718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5617599487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8677034378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3307552337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0501346588135</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651214599609</t>
@@ -2528,10 +2528,10 @@
     <t xml:space="preserve">16.868221282959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9509086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1162853240967</t>
+    <t xml:space="preserve">16.9509105682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.116283416748</t>
   </si>
   <si>
     <t xml:space="preserve">17.3312702178955</t>
@@ -2546,37 +2546,37 @@
     <t xml:space="preserve">17.2981967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2816581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3147315979004</t>
+    <t xml:space="preserve">17.2816562652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.314733505249</t>
   </si>
   <si>
     <t xml:space="preserve">17.4304943084717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3643474578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3808841705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9839839935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8186092376709</t>
+    <t xml:space="preserve">17.3643455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3808860778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9839820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8186111450195</t>
   </si>
   <si>
     <t xml:space="preserve">16.9012966156006</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8516826629639</t>
+    <t xml:space="preserve">16.8516845703125</t>
   </si>
   <si>
     <t xml:space="preserve">16.7524604797363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0170593261719</t>
+    <t xml:space="preserve">17.0170574188232</t>
   </si>
   <si>
     <t xml:space="preserve">17.4635715484619</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">17.4801063537598</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8439331054688</t>
+    <t xml:space="preserve">17.8439311981201</t>
   </si>
   <si>
     <t xml:space="preserve">17.9266204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.992769241333</t>
+    <t xml:space="preserve">17.9927711486816</t>
   </si>
   <si>
     <t xml:space="preserve">18.0919952392578</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4227447509766</t>
+    <t xml:space="preserve">18.4227428436279</t>
   </si>
   <si>
     <t xml:space="preserve">18.4723567962646</t>
@@ -2618,43 +2618,43 @@
     <t xml:space="preserve">18.5054302215576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.389669418335</t>
+    <t xml:space="preserve">18.3896675109863</t>
   </si>
   <si>
     <t xml:space="preserve">18.2739067077637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3235187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3400554656982</t>
+    <t xml:space="preserve">18.3235206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3400573730469</t>
   </si>
   <si>
     <t xml:space="preserve">18.191219329834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0589218139648</t>
+    <t xml:space="preserve">18.0589199066162</t>
   </si>
   <si>
     <t xml:space="preserve">17.9100818634033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2408313751221</t>
+    <t xml:space="preserve">18.2408332824707</t>
   </si>
   <si>
     <t xml:space="preserve">18.3069801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620216369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.794319152832</t>
+    <t xml:space="preserve">17.6620197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7943210601807</t>
   </si>
   <si>
     <t xml:space="preserve">17.711633682251</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5793323516846</t>
+    <t xml:space="preserve">17.5793342590332</t>
   </si>
   <si>
     <t xml:space="preserve">17.347806930542</t>
@@ -2663,19 +2663,19 @@
     <t xml:space="preserve">17.4966449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3974189758301</t>
+    <t xml:space="preserve">17.3974227905273</t>
   </si>
   <si>
     <t xml:space="preserve">17.7447071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6046581268311</t>
+    <t xml:space="preserve">18.6046562194824</t>
   </si>
   <si>
     <t xml:space="preserve">18.7700309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3731307983398</t>
+    <t xml:space="preserve">18.3731327056885</t>
   </si>
   <si>
     <t xml:space="preserve">18.6542682647705</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">18.7534942626953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4062061309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1416091918945</t>
+    <t xml:space="preserve">18.4062080383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1416072845459</t>
   </si>
   <si>
     <t xml:space="preserve">17.9431571960449</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">18.1085319519043</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7281723022461</t>
+    <t xml:space="preserve">17.7281703948975</t>
   </si>
   <si>
     <t xml:space="preserve">17.95969581604</t>
@@ -2708,64 +2708,64 @@
     <t xml:space="preserve">16.636697769165</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2894115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9503917694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0413475036621</t>
+    <t xml:space="preserve">16.2894096374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9503927230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0413494110107</t>
   </si>
   <si>
     <t xml:space="preserve">16.5374736785889</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0832080841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5627975463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0666694641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2155094146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1658973693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0005187988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7028484344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8847579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7855358123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6201610565186</t>
+    <t xml:space="preserve">17.0832099914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5627956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.06667137146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2155075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1658954620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0005226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178333282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7028465270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8847599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7855339050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6201591491699</t>
   </si>
   <si>
     <t xml:space="preserve">16.4795913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0335960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1328220367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1824340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462589263916</t>
+    <t xml:space="preserve">17.0335998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1328201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1824359893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.546257019043</t>
   </si>
   <si>
     <t xml:space="preserve">18.1746826171875</t>
@@ -2774,37 +2774,37 @@
     <t xml:space="preserve">18.869255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1669292449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3488426208496</t>
+    <t xml:space="preserve">19.1669311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.348840713501</t>
   </si>
   <si>
     <t xml:space="preserve">20.0599536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.960729598999</t>
+    <t xml:space="preserve">19.9607315063477</t>
   </si>
   <si>
     <t xml:space="preserve">20.5064659118652</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6883773803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7049160003662</t>
+    <t xml:space="preserve">20.6883792877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7049140930176</t>
   </si>
   <si>
     <t xml:space="preserve">20.6718406677246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8206806182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7545280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9364414215088</t>
+    <t xml:space="preserve">20.8206787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7545299530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9364395141602</t>
   </si>
   <si>
     <t xml:space="preserve">20.7214527130127</t>
@@ -2816,46 +2816,46 @@
     <t xml:space="preserve">21.1845035552979</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6806240081787</t>
+    <t xml:space="preserve">21.6806259155273</t>
   </si>
   <si>
     <t xml:space="preserve">22.1767501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9948387145996</t>
+    <t xml:space="preserve">21.994836807251</t>
   </si>
   <si>
     <t xml:space="preserve">22.5571117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2175788879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9033679962158</t>
+    <t xml:space="preserve">21.2175769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9033641815186</t>
   </si>
   <si>
     <t xml:space="preserve">20.9529781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3002662658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5979385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4160270690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8956127166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.515251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8460025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1602115631104</t>
+    <t xml:space="preserve">21.3002643585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5979404449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4160251617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8956146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5152530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8460006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.160213470459</t>
   </si>
   <si>
     <t xml:space="preserve">21.5317897796631</t>
@@ -2870,16 +2870,16 @@
     <t xml:space="preserve">20.5726146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2506504058838</t>
+    <t xml:space="preserve">21.2506542205811</t>
   </si>
   <si>
     <t xml:space="preserve">20.7876033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2584018707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6134395599365</t>
+    <t xml:space="preserve">20.2584037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6134433746338</t>
   </si>
   <si>
     <t xml:space="preserve">20.192253112793</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">19.3323040008545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9354057312012</t>
+    <t xml:space="preserve">18.9354038238525</t>
   </si>
   <si>
     <t xml:space="preserve">20.2749423980713</t>
@@ -2900,13 +2900,13 @@
     <t xml:space="preserve">20.9860515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4656372070312</t>
+    <t xml:space="preserve">21.4656391143799</t>
   </si>
   <si>
     <t xml:space="preserve">20.0103416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465167999268</t>
+    <t xml:space="preserve">19.6465187072754</t>
   </si>
   <si>
     <t xml:space="preserve">20.2253284454346</t>
@@ -2915,28 +2915,28 @@
     <t xml:space="preserve">20.3410911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5560779571533</t>
+    <t xml:space="preserve">20.5560760498047</t>
   </si>
   <si>
     <t xml:space="preserve">20.638765335083</t>
   </si>
   <si>
-    <t xml:space="preserve">21.035665512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3498764038086</t>
+    <t xml:space="preserve">21.0356636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.34987449646</t>
   </si>
   <si>
     <t xml:space="preserve">21.0852756500244</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0191268920898</t>
+    <t xml:space="preserve">21.0191287994385</t>
   </si>
   <si>
     <t xml:space="preserve">20.8702907562256</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1018142700195</t>
+    <t xml:space="preserve">21.1018180847168</t>
   </si>
   <si>
     <t xml:space="preserve">20.8868274688721</t>
@@ -2945,19 +2945,19 @@
     <t xml:space="preserve">20.5230026245117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6056900024414</t>
+    <t xml:space="preserve">20.60569190979</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268802642822</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1095657348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1514282226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6222286224365</t>
+    <t xml:space="preserve">20.1095676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1514263153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6222267150879</t>
   </si>
   <si>
     <t xml:space="preserve">20.3080158233643</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">20.4072418212891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9772663116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3907051086426</t>
+    <t xml:space="preserve">19.9772644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3907032012939</t>
   </si>
   <si>
     <t xml:space="preserve">20.1261024475098</t>
@@ -2990,22 +2990,22 @@
     <t xml:space="preserve">19.878044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3484592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3314075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0756340026855</t>
+    <t xml:space="preserve">21.3484573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3314094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0756320953369</t>
   </si>
   <si>
     <t xml:space="preserve">21.2461490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2290954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1779441833496</t>
+    <t xml:space="preserve">21.229097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.177942276001</t>
   </si>
   <si>
     <t xml:space="preserve">21.4337158203125</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">21.3143558502197</t>
   </si>
   <si>
-    <t xml:space="preserve">21.570125579834</t>
+    <t xml:space="preserve">21.5701274871826</t>
   </si>
   <si>
     <t xml:space="preserve">22.388599395752</t>
@@ -3035,13 +3035,13 @@
     <t xml:space="preserve">22.0646190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">22.030517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7235927581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6553821563721</t>
+    <t xml:space="preserve">22.0305194854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7235908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6553840637207</t>
   </si>
   <si>
     <t xml:space="preserve">21.7406406402588</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">22.0987243652344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7917976379395</t>
+    <t xml:space="preserve">21.7917957305908</t>
   </si>
   <si>
     <t xml:space="preserve">21.9964141845703</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">20.8710174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">20.888069152832</t>
+    <t xml:space="preserve">20.8880672454834</t>
   </si>
   <si>
     <t xml:space="preserve">21.7065391540527</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">22.1328258514404</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2351341247559</t>
+    <t xml:space="preserve">22.2351360321045</t>
   </si>
   <si>
     <t xml:space="preserve">22.47385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2692375183105</t>
+    <t xml:space="preserve">22.2692394256592</t>
   </si>
   <si>
     <t xml:space="preserve">20.7346038818359</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">20.5470390319824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2632007598877</t>
+    <t xml:space="preserve">21.2631988525391</t>
   </si>
   <si>
     <t xml:space="preserve">21.1097373962402</t>
@@ -3110,10 +3110,10 @@
     <t xml:space="preserve">21.1608905792236</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5530776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7747440338135</t>
+    <t xml:space="preserve">21.5530757904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7747459411621</t>
   </si>
   <si>
     <t xml:space="preserve">21.2973041534424</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">21.0926856994629</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8539638519287</t>
+    <t xml:space="preserve">20.8539657592773</t>
   </si>
   <si>
     <t xml:space="preserve">21.0074291229248</t>
@@ -3131,10 +3131,10 @@
     <t xml:space="preserve">21.280252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9282093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8600006103516</t>
+    <t xml:space="preserve">21.9282073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8600025177002</t>
   </si>
   <si>
     <t xml:space="preserve">21.8088474273682</t>
@@ -3152,25 +3152,25 @@
     <t xml:space="preserve">21.9111576080322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5079593658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1669292449951</t>
+    <t xml:space="preserve">22.5079574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1669273376465</t>
   </si>
   <si>
     <t xml:space="preserve">22.0816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0134658813477</t>
+    <t xml:space="preserve">22.013463973999</t>
   </si>
   <si>
     <t xml:space="preserve">22.4909076690674</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4227027893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2521877288818</t>
+    <t xml:space="preserve">22.422700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2521858215332</t>
   </si>
   <si>
     <t xml:space="preserve">22.5761661529541</t>
@@ -3203,19 +3203,19 @@
     <t xml:space="preserve">25.4749164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8329982757568</t>
+    <t xml:space="preserve">25.8329963684082</t>
   </si>
   <si>
     <t xml:space="preserve">25.7818431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1740283966064</t>
+    <t xml:space="preserve">26.1740303039551</t>
   </si>
   <si>
     <t xml:space="preserve">26.3274917602539</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6003150939941</t>
+    <t xml:space="preserve">26.6003170013428</t>
   </si>
   <si>
     <t xml:space="preserve">26.6173667907715</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">26.7708282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6855716705322</t>
+    <t xml:space="preserve">26.6855735778809</t>
   </si>
   <si>
     <t xml:space="preserve">25.9694080352783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7196750640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.36159324646</t>
+    <t xml:space="preserve">26.7196769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3615951538086</t>
   </si>
   <si>
     <t xml:space="preserve">26.3104400634766</t>
@@ -3248,22 +3248,22 @@
     <t xml:space="preserve">25.5431232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0315780639648</t>
+    <t xml:space="preserve">25.0315761566162</t>
   </si>
   <si>
     <t xml:space="preserve">24.826961517334</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0145263671875</t>
+    <t xml:space="preserve">25.0145282745361</t>
   </si>
   <si>
     <t xml:space="preserve">25.1679916381836</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1168365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8099098205566</t>
+    <t xml:space="preserve">25.1168346405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8099117279053</t>
   </si>
   <si>
     <t xml:space="preserve">24.8440113067627</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">25.1338882446289</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7246513366699</t>
+    <t xml:space="preserve">24.7246532440186</t>
   </si>
   <si>
     <t xml:space="preserve">24.7587566375732</t>
@@ -3287,31 +3287,31 @@
     <t xml:space="preserve">24.1790046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3324699401855</t>
+    <t xml:space="preserve">24.3324680328369</t>
   </si>
   <si>
     <t xml:space="preserve">24.6223430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1960544586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3495178222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9402828216553</t>
+    <t xml:space="preserve">24.1960563659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3495197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9402847290039</t>
   </si>
   <si>
     <t xml:space="preserve">24.1449012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1107978820801</t>
+    <t xml:space="preserve">24.1107997894287</t>
   </si>
   <si>
     <t xml:space="preserve">23.8038711547852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4177265167236</t>
+    <t xml:space="preserve">24.417724609375</t>
   </si>
   <si>
     <t xml:space="preserve">24.4518299102783</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">25.0486297607422</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4347743988037</t>
+    <t xml:space="preserve">24.4347763061523</t>
   </si>
   <si>
     <t xml:space="preserve">23.5481014251709</t>
@@ -3341,16 +3341,16 @@
     <t xml:space="preserve">23.4969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9342441558838</t>
+    <t xml:space="preserve">22.9342460632324</t>
   </si>
   <si>
     <t xml:space="preserve">22.7978324890137</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6443710327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3033428192139</t>
+    <t xml:space="preserve">22.6443729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3033409118652</t>
   </si>
   <si>
     <t xml:space="preserve">21.8770542144775</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">21.8429527282715</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1839809417725</t>
+    <t xml:space="preserve">22.1839828491211</t>
   </si>
   <si>
     <t xml:space="preserve">21.1949939727783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.638334274292</t>
+    <t xml:space="preserve">21.6383323669434</t>
   </si>
   <si>
     <t xml:space="preserve">21.2120456695557</t>
@@ -3398,10 +3398,10 @@
     <t xml:space="preserve">20.2912654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1378040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6273212432861</t>
+    <t xml:space="preserve">20.1378021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6273193359375</t>
   </si>
   <si>
     <t xml:space="preserve">24.0937480926514</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">25.5601749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9292678833008</t>
+    <t xml:space="preserve">24.9292697906494</t>
   </si>
   <si>
     <t xml:space="preserve">24.8951663970947</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">24.6564464569092</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1850414276123</t>
+    <t xml:space="preserve">25.1850433349609</t>
   </si>
   <si>
     <t xml:space="preserve">24.9804229736328</t>
@@ -3452,22 +3452,22 @@
     <t xml:space="preserve">25.6624851226807</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3786468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2933902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7537803649902</t>
+    <t xml:space="preserve">26.3786449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2933883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8049335479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7537784576416</t>
   </si>
   <si>
     <t xml:space="preserve">26.9413452148438</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0436553955078</t>
+    <t xml:space="preserve">27.0436534881592</t>
   </si>
   <si>
     <t xml:space="preserve">27.0948066711426</t>
@@ -3500,16 +3500,16 @@
     <t xml:space="preserve">27.8621273040771</t>
   </si>
   <si>
-    <t xml:space="preserve">28.049690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5893001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1800632476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2823753356934</t>
+    <t xml:space="preserve">28.0496921539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5893020629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2823734283447</t>
   </si>
   <si>
     <t xml:space="preserve">26.856086730957</t>
@@ -3524,13 +3524,13 @@
     <t xml:space="preserve">25.3214550018311</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9864616394043</t>
+    <t xml:space="preserve">25.9864635467529</t>
   </si>
   <si>
     <t xml:space="preserve">25.3385047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8901901245117</t>
+    <t xml:space="preserve">26.8901920318604</t>
   </si>
   <si>
     <t xml:space="preserve">27.7598171234131</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">29.4604301452637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4954605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.055944442749</t>
+    <t xml:space="preserve">29.4954624176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559463500977</t>
   </si>
   <si>
     <t xml:space="preserve">29.5655193328857</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">28.3044338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9524936676025</t>
+    <t xml:space="preserve">28.9524955749512</t>
   </si>
   <si>
     <t xml:space="preserve">28.8824329376221</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">29.0575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1451568603516</t>
+    <t xml:space="preserve">29.1451587677002</t>
   </si>
   <si>
     <t xml:space="preserve">27.043342590332</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">25.9924392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.957405090332</t>
+    <t xml:space="preserve">25.9574069976807</t>
   </si>
   <si>
     <t xml:space="preserve">25.607105255127</t>
@@ -3617,13 +3617,13 @@
     <t xml:space="preserve">26.255163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6054649353027</t>
+    <t xml:space="preserve">26.6054668426514</t>
   </si>
   <si>
     <t xml:space="preserve">25.8873462677002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4653453826904</t>
+    <t xml:space="preserve">26.4653434753418</t>
   </si>
   <si>
     <t xml:space="preserve">26.3252239227295</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">26.9382553100586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9732837677002</t>
+    <t xml:space="preserve">26.9732856750488</t>
   </si>
   <si>
     <t xml:space="preserve">27.1309204101562</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">27.4286785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">27.341100692749</t>
+    <t xml:space="preserve">27.3411026000977</t>
   </si>
   <si>
     <t xml:space="preserve">26.7455902099609</t>
@@ -3671,22 +3671,22 @@
     <t xml:space="preserve">26.6930408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5879516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1834678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.884069442749</t>
+    <t xml:space="preserve">26.5879535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1834659576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8840713500977</t>
   </si>
   <si>
     <t xml:space="preserve">28.1467971801758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4445552825928</t>
+    <t xml:space="preserve">28.4445533752441</t>
   </si>
   <si>
     <t xml:space="preserve">28.8999481201172</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">29.2327365875244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4062480926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1260070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3186702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8632755279541</t>
+    <t xml:space="preserve">30.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1260051727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3186721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8632774353027</t>
   </si>
   <si>
     <t xml:space="preserve">29.950855255127</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">30.4412784576416</t>
   </si>
   <si>
-    <t xml:space="preserve">31.15940284729</t>
+    <t xml:space="preserve">31.1593990325928</t>
   </si>
   <si>
     <t xml:space="preserve">30.3361873626709</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">29.7406730651855</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7089195251465</t>
+    <t xml:space="preserve">27.7089214324951</t>
   </si>
   <si>
     <t xml:space="preserve">27.4987373352051</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">27.8490409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2694034576416</t>
+    <t xml:space="preserve">28.269401550293</t>
   </si>
   <si>
     <t xml:space="preserve">28.1643142700195</t>
@@ -3773,13 +3773,13 @@
     <t xml:space="preserve">29.0926151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7598285675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8665542602539</t>
+    <t xml:space="preserve">28.7598266601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1801891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8665561676025</t>
   </si>
   <si>
     <t xml:space="preserve">25.169225692749</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">25.064136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5912284851074</t>
+    <t xml:space="preserve">24.5912303924561</t>
   </si>
   <si>
     <t xml:space="preserve">24.7488651275635</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">24.9415302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4335918426514</t>
+    <t xml:space="preserve">24.4335899353027</t>
   </si>
   <si>
     <t xml:space="preserve">24.1708660125732</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">24.9065017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5545616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7472267150879</t>
+    <t xml:space="preserve">25.5545597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7472248077393</t>
   </si>
   <si>
     <t xml:space="preserve">25.6946811676025</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">26.7806186676025</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6738910675049</t>
+    <t xml:space="preserve">27.6738891601562</t>
   </si>
   <si>
     <t xml:space="preserve">27.7964954376221</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">26.7631034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9032230377197</t>
+    <t xml:space="preserve">26.9032249450684</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274677276611</t>
@@ -3872,13 +3872,13 @@
     <t xml:space="preserve">26.3952865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8331642150879</t>
+    <t xml:space="preserve">26.8331623077393</t>
   </si>
   <si>
     <t xml:space="preserve">26.307710647583</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9223785400391</t>
+    <t xml:space="preserve">25.9223766326904</t>
   </si>
   <si>
     <t xml:space="preserve">26.3777713775635</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">26.5003757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1325569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0975284576416</t>
+    <t xml:space="preserve">26.1325588226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">26.5354061126709</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">26.2376499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7647399902344</t>
+    <t xml:space="preserve">25.764741897583</t>
   </si>
   <si>
     <t xml:space="preserve">25.8348026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2201347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4144382476807</t>
+    <t xml:space="preserve">26.2201366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4144401550293</t>
   </si>
   <si>
     <t xml:space="preserve">25.466983795166</t>
@@ -3923,10 +3923,10 @@
     <t xml:space="preserve">25.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5895881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8714694976807</t>
+    <t xml:space="preserve">25.5895900726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8714714050293</t>
   </si>
   <si>
     <t xml:space="preserve">24.4686241149902</t>
@@ -3935,52 +3935,52 @@
     <t xml:space="preserve">24.5737133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1183223724365</t>
+    <t xml:space="preserve">24.1183204650879</t>
   </si>
   <si>
     <t xml:space="preserve">24.2409267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3285007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7838935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8539562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3109874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.22340965271</t>
+    <t xml:space="preserve">24.3285026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7838954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8539543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3109855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2234115600586</t>
   </si>
   <si>
     <t xml:space="preserve">24.3460159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4160766601562</t>
+    <t xml:space="preserve">24.4160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">24.3985633850098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6788024902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9590454101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0466194152832</t>
+    <t xml:space="preserve">24.678804397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9590473175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0466213226318</t>
   </si>
   <si>
     <t xml:space="preserve">24.7138328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5036506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6612892150879</t>
+    <t xml:space="preserve">24.5036525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6612873077393</t>
   </si>
   <si>
     <t xml:space="preserve">24.2759552001953</t>
@@ -4007,10 +4007,10 @@
     <t xml:space="preserve">23.8731079101562</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3476543426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7154731750488</t>
+    <t xml:space="preserve">23.3476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7154712677002</t>
   </si>
   <si>
     <t xml:space="preserve">23.7680168151855</t>
@@ -4025,13 +4025,13 @@
     <t xml:space="preserve">23.049898147583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8747463226318</t>
+    <t xml:space="preserve">22.8747482299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.1900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2425632476807</t>
+    <t xml:space="preserve">23.2425651550293</t>
   </si>
   <si>
     <t xml:space="preserve">23.6979560852051</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">23.9256534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7505035400391</t>
+    <t xml:space="preserve">23.7505016326904</t>
   </si>
   <si>
     <t xml:space="preserve">23.435230255127</t>
@@ -4058,10 +4058,10 @@
     <t xml:space="preserve">23.5228061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9606838226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4861373901367</t>
+    <t xml:space="preserve">23.9606857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4861354827881</t>
   </si>
   <si>
     <t xml:space="preserve">24.2584400177002</t>
@@ -4073,10 +4073,10 @@
     <t xml:space="preserve">25.2217712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2042598724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1341972351074</t>
+    <t xml:space="preserve">25.2042579650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1341991424561</t>
   </si>
   <si>
     <t xml:space="preserve">24.6262588500977</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">24.3635330200195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7855319976807</t>
+    <t xml:space="preserve">23.7855339050293</t>
   </si>
   <si>
     <t xml:space="preserve">23.2250499725342</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">23.2775955200195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.295108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0657749176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.76637840271</t>
+    <t xml:space="preserve">23.2951107025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0657730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7663803100586</t>
   </si>
   <si>
     <t xml:space="preserve">24.7313499450684</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">23.6418628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4965953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334342956543</t>
+    <t xml:space="preserve">23.4965972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334362030029</t>
   </si>
   <si>
     <t xml:space="preserve">23.5329132080078</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">24.2955551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5679264068604</t>
+    <t xml:space="preserve">24.5679244995117</t>
   </si>
   <si>
     <t xml:space="preserve">24.4771347045898</t>
@@ -4163,13 +4163,13 @@
     <t xml:space="preserve">24.5134525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3318710327148</t>
+    <t xml:space="preserve">24.3318691253662</t>
   </si>
   <si>
     <t xml:space="preserve">23.9868659973145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5510711669922</t>
+    <t xml:space="preserve">23.5510730743408</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058074951172</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">23.4602813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8234424591064</t>
+    <t xml:space="preserve">23.8234443664551</t>
   </si>
   <si>
     <t xml:space="preserve">23.6237049102783</t>
@@ -4196,13 +4196,13 @@
     <t xml:space="preserve">24.8221397399902</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0413398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3863468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1321296691895</t>
+    <t xml:space="preserve">24.0413417816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.386344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1321315765381</t>
   </si>
   <si>
     <t xml:space="preserve">24.4589786529541</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">24.6768760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6042442321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5497703552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7858238220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2397766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8039817810059</t>
+    <t xml:space="preserve">24.6042423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.549768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7858219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2397747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8039798736572</t>
   </si>
   <si>
     <t xml:space="preserve">24.9674053192139</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">22.2618465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2981624603271</t>
+    <t xml:space="preserve">22.2981605529785</t>
   </si>
   <si>
     <t xml:space="preserve">22.388952255249</t>
@@ -4271,25 +4271,25 @@
     <t xml:space="preserve">22.2073707580566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0621070861816</t>
+    <t xml:space="preserve">22.062105178833</t>
   </si>
   <si>
     <t xml:space="preserve">21.6807861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6263122558594</t>
+    <t xml:space="preserve">21.6263103485107</t>
   </si>
   <si>
     <t xml:space="preserve">22.6431674957275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6794815063477</t>
+    <t xml:space="preserve">22.6794834136963</t>
   </si>
   <si>
     <t xml:space="preserve">22.5886917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1515922546387</t>
+    <t xml:space="preserve">23.1515941619873</t>
   </si>
   <si>
     <t xml:space="preserve">22.9700107574463</t>
@@ -4310,28 +4310,28 @@
     <t xml:space="preserve">23.024486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9155368804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.86106300354</t>
+    <t xml:space="preserve">22.9155387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8610649108887</t>
   </si>
   <si>
     <t xml:space="preserve">23.2060661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5342178344727</t>
+    <t xml:space="preserve">22.534215927124</t>
   </si>
   <si>
     <t xml:space="preserve">21.9349994659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8442096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2631511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8999881744385</t>
+    <t xml:space="preserve">21.8442077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2631492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8999862670898</t>
   </si>
   <si>
     <t xml:space="preserve">20.482349395752</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">20.7365646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1010284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6833934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7378673553467</t>
+    <t xml:space="preserve">20.1010303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6833953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7378692626953</t>
   </si>
   <si>
     <t xml:space="preserve">20.0102405548096</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">19.9376068115234</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3915576934814</t>
+    <t xml:space="preserve">20.3915596008301</t>
   </si>
   <si>
     <t xml:space="preserve">20.6094589233398</t>
@@ -4373,19 +4373,19 @@
     <t xml:space="preserve">20.6820907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1542015075684</t>
+    <t xml:space="preserve">21.1541996002197</t>
   </si>
   <si>
     <t xml:space="preserve">21.0997276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1723594665527</t>
+    <t xml:space="preserve">21.1723575592041</t>
   </si>
   <si>
     <t xml:space="preserve">21.0634117126465</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8091983795166</t>
+    <t xml:space="preserve">20.809196472168</t>
   </si>
   <si>
     <t xml:space="preserve">21.0089359283447</t>
@@ -4397,16 +4397,16 @@
     <t xml:space="preserve">21.0270938873291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.608154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7715759277344</t>
+    <t xml:space="preserve">21.6081523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.771577835083</t>
   </si>
   <si>
     <t xml:space="preserve">21.4628887176514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9181480407715</t>
+    <t xml:space="preserve">20.9181461334229</t>
   </si>
   <si>
     <t xml:space="preserve">21.2449913024902</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">22.7884311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0971183776855</t>
+    <t xml:space="preserve">23.0971202850342</t>
   </si>
   <si>
     <t xml:space="preserve">23.2605419158936</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">23.1152763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3694896697998</t>
+    <t xml:space="preserve">23.3694915771484</t>
   </si>
   <si>
     <t xml:space="preserve">23.8960742950439</t>
@@ -4445,13 +4445,13 @@
     <t xml:space="preserve">24.3681869506836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7689685821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4408206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2216186523438</t>
+    <t xml:space="preserve">23.768970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4408187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2216205596924</t>
   </si>
   <si>
     <t xml:space="preserve">25.493989944458</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">25.966100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">25.984260559082</t>
+    <t xml:space="preserve">25.9842586517334</t>
   </si>
   <si>
     <t xml:space="preserve">26.0932083129883</t>
@@ -4478,31 +4478,31 @@
     <t xml:space="preserve">26.2021560668945</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4758319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8947734832764</t>
+    <t xml:space="preserve">25.475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8947715759277</t>
   </si>
   <si>
     <t xml:space="preserve">25.0945110321045</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2942523956299</t>
+    <t xml:space="preserve">25.2942504882812</t>
   </si>
   <si>
     <t xml:space="preserve">24.9129314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">24.713191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0763549804688</t>
+    <t xml:space="preserve">24.7131900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0763530731201</t>
   </si>
   <si>
     <t xml:space="preserve">24.6405582427979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6587181091309</t>
+    <t xml:space="preserve">24.6587162017822</t>
   </si>
   <si>
     <t xml:space="preserve">24.3137130737305</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">21.5718383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4447326660156</t>
+    <t xml:space="preserve">21.444730758667</t>
   </si>
   <si>
     <t xml:space="preserve">21.1905174255371</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">21.136043548584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9363040924072</t>
+    <t xml:space="preserve">20.9363021850586</t>
   </si>
   <si>
     <t xml:space="preserve">21.3176250457764</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">22.6976413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7871265411377</t>
+    <t xml:space="preserve">23.7871284484863</t>
   </si>
   <si>
     <t xml:space="preserve">24.0231819152832</t>
@@ -5439,6 +5439,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.6000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3799991607666</t>
   </si>
 </sst>
 </file>
@@ -70673,7 +70676,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6495486111</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>291078</v>
@@ -70694,6 +70697,32 @@
         <v>1808</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912962963</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>177226</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>22.6000003814697</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>22.3600006103516</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>22.5799999237061</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>22.3799991607666</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1809</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="1814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="1815">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48755311965942</t>
+    <t xml:space="preserve">7.48755359649658</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
@@ -47,145 +47,145 @@
     <t xml:space="preserve">7.43893337249756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23837423324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0438928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99527168273926</t>
+    <t xml:space="preserve">7.23837375640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04389238357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99527215957642</t>
   </si>
   <si>
     <t xml:space="preserve">7.06212520599365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25052881240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22014093399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17152070999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07428121566772</t>
+    <t xml:space="preserve">7.25053071975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22014188766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17152166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07428026199341</t>
   </si>
   <si>
     <t xml:space="preserve">6.84941148757935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01350402832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75216913223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83725500106812</t>
+    <t xml:space="preserve">7.01350450515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75217008590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83725595474243</t>
   </si>
   <si>
     <t xml:space="preserve">6.97096252441406</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09251356124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00742721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00134992599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98919343948364</t>
+    <t xml:space="preserve">7.09251260757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00742673873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00135087966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98919439315796</t>
   </si>
   <si>
     <t xml:space="preserve">6.92841863632202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8615665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53337669372559</t>
+    <t xml:space="preserve">6.86156511306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53337717056274</t>
   </si>
   <si>
     <t xml:space="preserve">6.47868013381958</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61238574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55161094665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77647972106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94057416915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87372159957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63061952590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78863525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58199739456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7035493850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7157039642334</t>
+    <t xml:space="preserve">6.61238622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55160999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77648067474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94057321548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8737211227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63061809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78863573074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58199882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70354843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71570491790771</t>
   </si>
   <si>
     <t xml:space="preserve">6.8068675994873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91626453399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84333372116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83117818832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87979793548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70962762832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74609231948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85548877716064</t>
+    <t xml:space="preserve">6.91626405715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84333276748657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83117723464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70962715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74609136581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85548782348633</t>
   </si>
   <si>
     <t xml:space="preserve">6.86764335632324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95272922515869</t>
+    <t xml:space="preserve">6.95272827148438</t>
   </si>
   <si>
     <t xml:space="preserve">7.04996967315674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27483940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35992670059204</t>
+    <t xml:space="preserve">7.27484035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35992527008057</t>
   </si>
   <si>
     <t xml:space="preserve">7.34777164459229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26876306533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22621917724609</t>
+    <t xml:space="preserve">7.26876211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22621965408325</t>
   </si>
   <si>
     <t xml:space="preserve">7.11074590682983</t>
@@ -194,22 +194,22 @@
     <t xml:space="preserve">7.03173732757568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08035850524902</t>
+    <t xml:space="preserve">7.08035707473755</t>
   </si>
   <si>
     <t xml:space="preserve">7.0560474395752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18975400924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23229598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15328979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11682462692261</t>
+    <t xml:space="preserve">7.18975305557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23229789733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1532883644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11682319641113</t>
   </si>
   <si>
     <t xml:space="preserve">7.16544342041016</t>
@@ -218,124 +218,124 @@
     <t xml:space="preserve">6.95880603790283</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93449592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803218841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90410757064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96488428115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79471206665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76432418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1411337852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02565908432007</t>
+    <t xml:space="preserve">6.93449735641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803171157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90410852432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96488475799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79471254348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76432466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14113330841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02566051483154</t>
   </si>
   <si>
     <t xml:space="preserve">7.157386302948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13741397857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3105206489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25725793838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34381151199341</t>
+    <t xml:space="preserve">7.13741254806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31052207946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25725650787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34381103515625</t>
   </si>
   <si>
     <t xml:space="preserve">7.38376045227051</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29720544815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25059843063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21730947494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23728275299072</t>
+    <t xml:space="preserve">7.29720592498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25059986114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21730899810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062610626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23728322982788</t>
   </si>
   <si>
     <t xml:space="preserve">7.27723217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22396755218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10412263870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85777568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65803480148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60477018356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.474937915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50822877883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95764493942261</t>
+    <t xml:space="preserve">7.22396612167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10412311553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85777521133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.658034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60476970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47493839263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50822830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95764541625977</t>
   </si>
   <si>
     <t xml:space="preserve">6.93767166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82448625564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88440799713135</t>
+    <t xml:space="preserve">6.82448577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88440704345703</t>
   </si>
   <si>
     <t xml:space="preserve">6.47826719284058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3218035697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56149291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69132375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81782722473145</t>
+    <t xml:space="preserve">6.32180309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56149244308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69132471084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81782627105713</t>
   </si>
   <si>
     <t xml:space="preserve">6.9176983833313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03754281997681</t>
+    <t xml:space="preserve">7.03754234313965</t>
   </si>
   <si>
     <t xml:space="preserve">6.78453683853149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50490045547485</t>
+    <t xml:space="preserve">6.50489902496338</t>
   </si>
   <si>
     <t xml:space="preserve">6.61808586120605</t>
@@ -347,178 +347,178 @@
     <t xml:space="preserve">6.6846661567688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73793077468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8777494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81116771697998</t>
+    <t xml:space="preserve">6.73793029785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87774801254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8111686706543</t>
   </si>
   <si>
     <t xml:space="preserve">6.7512469291687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79119443893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76456308364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86443281173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77122020721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89106559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73127126693726</t>
+    <t xml:space="preserve">6.79119491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76456356048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86443376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77122116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89106607437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73127269744873</t>
   </si>
   <si>
     <t xml:space="preserve">6.64471769332886</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63806009292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75790452957153</t>
+    <t xml:space="preserve">6.63806056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75790500640869</t>
   </si>
   <si>
     <t xml:space="preserve">6.83114337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80451107025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9310131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96430349349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74458932876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71129846572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65137529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62807416915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64138984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62141370773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01756858825684</t>
+    <t xml:space="preserve">6.80451059341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101406097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96430397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74458885192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71129894256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65137672424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62807321548462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6413893699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62141466140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01756906509399</t>
   </si>
   <si>
     <t xml:space="preserve">6.98427772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01090860366821</t>
+    <t xml:space="preserve">7.01090908050537</t>
   </si>
   <si>
     <t xml:space="preserve">7.04419994354248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17070341110229</t>
+    <t xml:space="preserve">7.17070293426514</t>
   </si>
   <si>
     <t xml:space="preserve">6.87109041213989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92435455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97762012481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8378005027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84445858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79785299301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77787828445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59811162948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55150508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7246150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67135000228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66469287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60809993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54484844207764</t>
+    <t xml:space="preserve">6.92435503005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97761964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83780145645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84445905685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79785251617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77787923812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59811210632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55150556564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72461462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67135095596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66469144821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60809946060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54484748840332</t>
   </si>
   <si>
     <t xml:space="preserve">6.45829343795776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65470600128174</t>
+    <t xml:space="preserve">6.65470504760742</t>
   </si>
   <si>
     <t xml:space="preserve">6.67800807952881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46495151519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13870716094971</t>
+    <t xml:space="preserve">6.4649510383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13870763778687</t>
   </si>
   <si>
     <t xml:space="preserve">6.228590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19197177886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17865514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24856615066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13537788391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06546878814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1686692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15868139266968</t>
+    <t xml:space="preserve">6.19197225570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17865562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24856567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13537836074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06546974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16866827011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15868091583252</t>
   </si>
   <si>
     <t xml:space="preserve">6.14203691482544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06213998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03883647918701</t>
+    <t xml:space="preserve">6.06213903427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03883695602417</t>
   </si>
   <si>
     <t xml:space="preserve">6.10874652862549</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">6.02219200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01886224746704</t>
+    <t xml:space="preserve">6.0188627243042</t>
   </si>
   <si>
     <t xml:space="preserve">6.11873340606689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23191928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12206268310547</t>
+    <t xml:space="preserve">6.2319188117981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12206220626831</t>
   </si>
   <si>
     <t xml:space="preserve">6.22193288803101</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">6.21860408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35842227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37839651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62474489212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70464086532593</t>
+    <t xml:space="preserve">6.35842180252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37839603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62474346160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70464038848877</t>
   </si>
   <si>
     <t xml:space="preserve">6.85111665725708</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">6.99093580245972</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07749080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91103887557983</t>
+    <t xml:space="preserve">7.07749032974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91103982925415</t>
   </si>
   <si>
     <t xml:space="preserve">7.07083225250244</t>
@@ -587,91 +587,91 @@
     <t xml:space="preserve">7.1307544708252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15072822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18401908874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09746503829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05085802078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35047101974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27057361602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2838888168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30386400222778</t>
+    <t xml:space="preserve">7.15072917938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18401861190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0974645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05085706710815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35047006607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27057409286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28388977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30386352539062</t>
   </si>
   <si>
     <t xml:space="preserve">7.53023719787598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32383823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31717967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36378622055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51692008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59015893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347604751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000289916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992511749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77658367156982</t>
+    <t xml:space="preserve">7.32383728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31717920303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3637866973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51692056655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59015846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347414016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71000337600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992559432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77658414840698</t>
   </si>
   <si>
     <t xml:space="preserve">7.73663568496704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78990077972412</t>
+    <t xml:space="preserve">7.78990030288696</t>
   </si>
   <si>
     <t xml:space="preserve">7.75660943984985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82319068908691</t>
+    <t xml:space="preserve">7.82319021224976</t>
   </si>
   <si>
     <t xml:space="preserve">7.85648059844971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87645530700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9030876159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96966648101807</t>
+    <t xml:space="preserve">7.86979579925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8764533996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96966695785522</t>
   </si>
   <si>
     <t xml:space="preserve">7.94969272613525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92306041717529</t>
+    <t xml:space="preserve">7.92306137084961</t>
   </si>
   <si>
     <t xml:space="preserve">7.96300888061523</t>
@@ -689,37 +689,37 @@
     <t xml:space="preserve">7.5435528755188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47031402587891</t>
+    <t xml:space="preserve">7.47031450271606</t>
   </si>
   <si>
     <t xml:space="preserve">7.63676595687866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56352472305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018375396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74329423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80321598052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89642810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94303512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84982204437256</t>
+    <t xml:space="preserve">7.56352663040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018566131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74329328536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80321741104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89642906188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94303607940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84982109069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.06953716278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20842838287354</t>
+    <t xml:space="preserve">8.20842742919922</t>
   </si>
   <si>
     <t xml:space="preserve">8.25009441375732</t>
@@ -731,58 +731,58 @@
     <t xml:space="preserve">8.31954002380371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35426139831543</t>
+    <t xml:space="preserve">8.35426235198975</t>
   </si>
   <si>
     <t xml:space="preserve">8.28481769561768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29870700836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37509536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34731864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38898468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43759536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45148658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68759918212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7362117767334</t>
+    <t xml:space="preserve">8.2987060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37509727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34731769561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3889856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43759632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4514856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68760013580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73621082305908</t>
   </si>
   <si>
     <t xml:space="preserve">8.62509918212891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63898754119873</t>
+    <t xml:space="preserve">8.63898849487305</t>
   </si>
   <si>
     <t xml:space="preserve">8.66676616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68065452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59732151031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72926616668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69454574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61121082305908</t>
+    <t xml:space="preserve">8.68065547943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59732055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72926712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69454479217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61120986938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.50704288482666</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">8.52787494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54870986938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49315357208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51398754119873</t>
+    <t xml:space="preserve">8.54871082305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4931526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5139856338501</t>
   </si>
   <si>
     <t xml:space="preserve">8.46537494659424</t>
@@ -809,22 +809,22 @@
     <t xml:space="preserve">8.47231960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61815357208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65982246398926</t>
+    <t xml:space="preserve">8.61815452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65982151031494</t>
   </si>
   <si>
     <t xml:space="preserve">8.6459321975708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40981960296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43065357208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42370700836182</t>
+    <t xml:space="preserve">8.40981864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43065166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42370796203613</t>
   </si>
   <si>
     <t xml:space="preserve">8.30565166473389</t>
@@ -839,61 +839,61 @@
     <t xml:space="preserve">8.60426616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71537780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88204669952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0001049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15288257598877</t>
+    <t xml:space="preserve">8.71537971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88204765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00010299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15288352966309</t>
   </si>
   <si>
     <t xml:space="preserve">9.13204860687256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06954765319824</t>
+    <t xml:space="preserve">9.06954860687256</t>
   </si>
   <si>
     <t xml:space="preserve">9.09038257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00704765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95843601226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0626049041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12510585784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20843982696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24316215515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2987174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36816310882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40983009338379</t>
+    <t xml:space="preserve">9.00704956054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95843696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06260395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12510395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20843887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24316120147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29871940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40983104705811</t>
   </si>
   <si>
     <t xml:space="preserve">9.41677665710449</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32649707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29177474975586</t>
+    <t xml:space="preserve">9.32649517059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29177284240723</t>
   </si>
   <si>
     <t xml:space="preserve">9.31260681152344</t>
@@ -905,28 +905,28 @@
     <t xml:space="preserve">9.47233104705811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43760967254639</t>
+    <t xml:space="preserve">9.43760776519775</t>
   </si>
   <si>
     <t xml:space="preserve">9.44455242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40288352966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38899803161621</t>
+    <t xml:space="preserve">9.40288639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38899612426758</t>
   </si>
   <si>
     <t xml:space="preserve">9.38205242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3403844833374</t>
+    <t xml:space="preserve">9.34038639068604</t>
   </si>
   <si>
     <t xml:space="preserve">9.34733009338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31955051422119</t>
+    <t xml:space="preserve">9.31955242156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.48622035980225</t>
@@ -935,25 +935,25 @@
     <t xml:space="preserve">9.75011253356934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79177951812744</t>
+    <t xml:space="preserve">9.79178047180176</t>
   </si>
   <si>
     <t xml:space="preserve">9.7778902053833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80566787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72927951812744</t>
+    <t xml:space="preserve">9.80566883087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72927856445312</t>
   </si>
   <si>
     <t xml:space="preserve">9.77094554901123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76400184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74316596984863</t>
+    <t xml:space="preserve">9.76400089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74316787719727</t>
   </si>
   <si>
     <t xml:space="preserve">9.96539306640625</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">10.0278930664062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93761539459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0834493637085</t>
+    <t xml:space="preserve">9.93761444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0834503173828</t>
   </si>
   <si>
     <t xml:space="preserve">10.1181716918945</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">10.1876173019409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4445638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5001201629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5695657730103</t>
+    <t xml:space="preserve">10.4445648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5001211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5695667266846</t>
   </si>
   <si>
     <t xml:space="preserve">10.229284286499</t>
@@ -989,88 +989,88 @@
     <t xml:space="preserve">10.3959531784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4237308502197</t>
+    <t xml:space="preserve">10.423731803894</t>
   </si>
   <si>
     <t xml:space="preserve">10.5903997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4931755065918</t>
+    <t xml:space="preserve">10.4931764602661</t>
   </si>
   <si>
     <t xml:space="preserve">10.5626211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6251211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6042900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.701512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7779016494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8542928695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8334579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9029035568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0904054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1042947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1112384796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667890548706</t>
+    <t xml:space="preserve">10.6251230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6042890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7015113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7779026031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8542900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8334589004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9029026031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1042938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1112394332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667900085449</t>
   </si>
   <si>
     <t xml:space="preserve">10.9723491668701</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9445705413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0765161514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3473529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3959655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1529064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0626268386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2154064178467</t>
+    <t xml:space="preserve">10.9445695877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0765171051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3473520278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3959627151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0626277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2154054641724</t>
   </si>
   <si>
     <t xml:space="preserve">11.3126306533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2362413406372</t>
+    <t xml:space="preserve">11.2362403869629</t>
   </si>
   <si>
     <t xml:space="preserve">11.2084617614746</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9098472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7362337112427</t>
+    <t xml:space="preserve">10.9098482131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.736234664917</t>
   </si>
   <si>
     <t xml:space="preserve">10.8751249313354</t>
@@ -1079,40 +1079,40 @@
     <t xml:space="preserve">10.6945667266846</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5487327575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7848453521729</t>
+    <t xml:space="preserve">10.5487308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7848472595215</t>
   </si>
   <si>
     <t xml:space="preserve">10.8612356185913</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0695714950562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1876287460327</t>
+    <t xml:space="preserve">11.0695705413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.187629699707</t>
   </si>
   <si>
     <t xml:space="preserve">10.9306812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1598491668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4515199661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5001306533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4931879043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6251344680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7223567962646</t>
+    <t xml:space="preserve">11.1598510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4515209197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.50013256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4931869506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6251335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7223558425903</t>
   </si>
   <si>
     <t xml:space="preserve">11.7709693908691</t>
@@ -1121,55 +1121,55 @@
     <t xml:space="preserve">11.7015228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.729302406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7154121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6112442016602</t>
+    <t xml:space="preserve">11.7293014526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7154130935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6112432479858</t>
   </si>
   <si>
     <t xml:space="preserve">11.4862442016602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5765228271484</t>
+    <t xml:space="preserve">11.5765218734741</t>
   </si>
   <si>
     <t xml:space="preserve">11.6806888580322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820753097534</t>
+    <t xml:space="preserve">11.3820743560791</t>
   </si>
   <si>
     <t xml:space="preserve">10.8681802749634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8959579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9862375259399</t>
+    <t xml:space="preserve">10.895959854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9862365722656</t>
   </si>
   <si>
     <t xml:space="preserve">11.083459854126</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292966842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3265190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2431859970093</t>
+    <t xml:space="preserve">11.2292957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848520278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3265180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.243185043335</t>
   </si>
   <si>
     <t xml:space="preserve">11.5973567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7501354217529</t>
+    <t xml:space="preserve">11.7501344680786</t>
   </si>
   <si>
     <t xml:space="preserve">11.6181888580322</t>
@@ -1178,40 +1178,40 @@
     <t xml:space="preserve">11.7987461090088</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6320781707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8334712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1251392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9168033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6668119430542</t>
+    <t xml:space="preserve">11.6320772171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8334693908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1251382827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.916802406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6668109893799</t>
   </si>
   <si>
     <t xml:space="preserve">13.1529302597046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.382098197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.319598197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3682107925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.576545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5209875106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2362642288208</t>
+    <t xml:space="preserve">13.3820991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3195972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3682117462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5765447616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5209884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2362613677979</t>
   </si>
   <si>
     <t xml:space="preserve">13.1668176651001</t>
@@ -1220,43 +1220,43 @@
     <t xml:space="preserve">13.0487623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4237661361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0070934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3543195724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4584856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154359817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.791823387146</t>
+    <t xml:space="preserve">13.4237651824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070924758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3543214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4584884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918252944946</t>
   </si>
   <si>
     <t xml:space="preserve">13.6807126998901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9168262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9307155609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1876516342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2987651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3751525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4168186187744</t>
+    <t xml:space="preserve">13.9168281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9307136535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1876497268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2987642288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3751554489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.416820526123</t>
   </si>
   <si>
     <t xml:space="preserve">13.4723777770996</t>
@@ -1265,37 +1265,37 @@
     <t xml:space="preserve">13.4862661361694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6112670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7362699508667</t>
+    <t xml:space="preserve">13.6112661361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7362689971924</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223806381226</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8196048736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8890495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8543272018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9029388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0834951400757</t>
+    <t xml:space="preserve">13.8196029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.889048576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8543262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9029378890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.08349609375</t>
   </si>
   <si>
     <t xml:space="preserve">13.798770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0279407501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.305721282959</t>
+    <t xml:space="preserve">14.0279397964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057203292847</t>
   </si>
   <si>
     <t xml:space="preserve">13.1945972442627</t>
@@ -1304,445 +1304,445 @@
     <t xml:space="preserve">13.1112613677979</t>
   </si>
   <si>
+    <t xml:space="preserve">13.1807079315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0200996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1486558914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8083591461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6571178436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5361251831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.256329536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1277723312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3092641830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.460503578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4983139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4680652618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.573935508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7327404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7478637695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4075708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4889469146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4738235473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6704387664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755159378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6175012588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.723370552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9351091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7460594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292417526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2998962402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2091512680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0654716491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1637773513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0427837371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1713380813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2847719192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6250648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536191940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6779975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7914295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8443651199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8746156692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8368034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7611808776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6553134918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5494422912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099405288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6401901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5721311569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5191974639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2393980026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0049734115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9217901229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9142293930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2696475982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3982019424438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9898490905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6646814346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6722421646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5814962387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705478668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6268711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5210008621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5512475967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907541275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4756288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5058765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3470726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.39244556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4831895828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6344318389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5663738250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5436868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3773221969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1958312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2714519500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3395128250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3546342849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2638893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4529418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3319473266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9311580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0219039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8101644515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.553053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7421064376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6513614654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848848342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1202116012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9614057540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5681791305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4396238327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6211137771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4018125534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4925584793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4698724746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1371393203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2883815765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1522645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6286764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.643798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252897262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7723541259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.847975730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.757230758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8177289962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7799167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4471855163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4244995117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2581329345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1673889160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4169368743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1447019577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0312700271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2505712509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1068935394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2278861999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0463953018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.099328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7968463897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8800296783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5379304885864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2656946182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7950410842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2941398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1126470565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9538450241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5833015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4774341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5757389068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8555383682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0143413543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8328523635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9084711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0521535873413</t>
+  </si>
+  <si>
     <t xml:space="preserve">13.1807060241699</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0200977325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1486539840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8083581924438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6571187973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5361242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.256329536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1277732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3092622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4605045318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4983158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4680671691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.573935508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7327394485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7478618621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4075698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4889469146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4738216400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6704378128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755168914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6175031661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.723370552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9351110458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7460565567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292407989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2998952865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2091512680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0654706954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1637773513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0427846908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1713380813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2847709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6250648498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536201477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.67799949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7914304733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8443641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8746147155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8368034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7611827850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6553106307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5494432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.609938621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6401901245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5721302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5191955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2393999099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0049753189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9217920303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9142293930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2696475982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3982038497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9898500442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6646795272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6722412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5814962387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7705497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6268701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5210008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495561599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5512504577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907522201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4756288528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.505877494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.347071647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.39244556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4831895828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6344327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5663738250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5436868667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3773221969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1958332061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2714509963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3395109176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3546342849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2638902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4529428482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3319492340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9311599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0219039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8101654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5530557632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7421064376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6513614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1202096939087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9614067077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5681800842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4396238327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6211128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4018135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4925584793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4698715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1371402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2883815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1522626876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6286764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.825288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7723550796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8479747772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7572298049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8177289962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7799167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4471855163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4244985580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.258131980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1673879623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4169368743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1447019577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0312700271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2505712509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1068925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2278852462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0463943481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.099328994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7968463897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8800296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5379314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2656955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7950410842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2941398620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1126489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9538440704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5833024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4774341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5757389068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8555374145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0143404006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8328523635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9084720611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0521516799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1807079315186</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.9160346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0975255966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0067796707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2260799407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2185153961182</t>
+    <t xml:space="preserve">13.0975246429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0067806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2260808944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2185182571411</t>
   </si>
   <si>
     <t xml:space="preserve">12.9009103775024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0370273590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7647933959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0294647216797</t>
+    <t xml:space="preserve">13.0370292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7647924423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.029465675354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2109546661377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2336416244507</t>
+    <t xml:space="preserve">13.233642578125</t>
   </si>
   <si>
     <t xml:space="preserve">12.9235973358154</t>
@@ -1751,28 +1751,28 @@
     <t xml:space="preserve">12.870662689209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.893346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353359222412</t>
+    <t xml:space="preserve">12.8933477401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.188271522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353349685669</t>
   </si>
   <si>
     <t xml:space="preserve">12.9689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1050863265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3016996383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8857879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6891717910767</t>
+    <t xml:space="preserve">13.1050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.301700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8857870101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.689172744751</t>
   </si>
   <si>
     <t xml:space="preserve">12.6967353820801</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">12.666485786438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5152444839478</t>
+    <t xml:space="preserve">12.5152435302734</t>
   </si>
   <si>
     <t xml:space="preserve">12.3110685348511</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">12.2430105209351</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0388336181641</t>
+    <t xml:space="preserve">12.0388326644897</t>
   </si>
   <si>
     <t xml:space="preserve">12.6589241027832</t>
@@ -1805,25 +1805,25 @@
     <t xml:space="preserve">12.7496700286865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3186302185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1900758743286</t>
+    <t xml:space="preserve">12.3186311721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.19007396698</t>
   </si>
   <si>
     <t xml:space="preserve">12.1976366043091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.174952507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2732582092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1598262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203226089478</t>
+    <t xml:space="preserve">12.1749515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2732572555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1598272323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203216552734</t>
   </si>
   <si>
     <t xml:space="preserve">12.280818939209</t>
@@ -1838,133 +1838,133 @@
     <t xml:space="preserve">13.2902870178223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4485054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5988111495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146326065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9548025131226</t>
+    <t xml:space="preserve">13.4485063552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6146335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9548034667969</t>
   </si>
   <si>
     <t xml:space="preserve">13.978533744812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8598728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.749116897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7332973480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.772852897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8124055862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.717474937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6383666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6620979309082</t>
+    <t xml:space="preserve">13.8598718643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.749119758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7332963943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7728519439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8124046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7174739837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6383676528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6620988845825</t>
   </si>
   <si>
     <t xml:space="preserve">13.5750780105591</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1446619033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.239595413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5085649490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.469012260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955858230591</t>
+    <t xml:space="preserve">14.1446628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2395944595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5085620880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955829620361</t>
   </si>
   <si>
     <t xml:space="preserve">14.7221574783325</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6746912002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.176305770874</t>
+    <t xml:space="preserve">14.6746921539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1763048171997</t>
   </si>
   <si>
     <t xml:space="preserve">14.1604852676392</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0813760757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0339097976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6984262466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6114044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4136343002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6272287368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.109790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0939693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911279678345</t>
+    <t xml:space="preserve">14.0813751220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0339088439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373655319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6984243392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6114053726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4136323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6272277832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1097898483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0939674377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911289215088</t>
   </si>
   <si>
     <t xml:space="preserve">14.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9120197296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8724641799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8645534515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6430501937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2870578765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3266153335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2158584594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2475051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0260000228882</t>
+    <t xml:space="preserve">14.9120187759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.872465133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8645544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6430492401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2870588302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3266162872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2158603668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2475032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0260009765625</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576438903809</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">14.2000398635864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2949695587158</t>
+    <t xml:space="preserve">14.2949714660645</t>
   </si>
   <si>
     <t xml:space="preserve">14.2079486846924</t>
@@ -1988,52 +1988,52 @@
     <t xml:space="preserve">13.6304559707642</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5671682357788</t>
+    <t xml:space="preserve">13.5671691894531</t>
   </si>
   <si>
     <t xml:space="preserve">13.6700096130371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5197019577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3693971633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8203153610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9073362350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8440494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5592575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7886743545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965850830078</t>
+    <t xml:space="preserve">13.5197038650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3693962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8203163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.907338142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8440504074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5592565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7886724472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965860366821</t>
   </si>
   <si>
     <t xml:space="preserve">14.1209297180176</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9310703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0892868041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3028793334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4848308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6588706970215</t>
+    <t xml:space="preserve">13.9310693740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0892858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3028802871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4848327636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6588716506958</t>
   </si>
   <si>
     <t xml:space="preserve">14.2633256912231</t>
@@ -2042,43 +2042,43 @@
     <t xml:space="preserve">14.2316837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1130199432373</t>
+    <t xml:space="preserve">14.1130208969116</t>
   </si>
   <si>
     <t xml:space="preserve">14.5876731872559</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9753065109253</t>
+    <t xml:space="preserve">14.975305557251</t>
   </si>
   <si>
     <t xml:space="preserve">14.8566446304321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9990377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8329086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.745888710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0227699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.737979888916</t>
+    <t xml:space="preserve">14.9990396499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8329105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7458877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227689743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7379779815674</t>
   </si>
   <si>
     <t xml:space="preserve">14.7854461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6905126571655</t>
+    <t xml:space="preserve">14.6905136108398</t>
   </si>
   <si>
     <t xml:space="preserve">14.6351375579834</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402088165283</t>
+    <t xml:space="preserve">14.5402069091797</t>
   </si>
   <si>
     <t xml:space="preserve">14.1525745391846</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">14.1921291351318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0971975326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2712373733521</t>
+    <t xml:space="preserve">14.0971984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2712364196777</t>
   </si>
   <si>
     <t xml:space="preserve">14.2791471481323</t>
@@ -2105,70 +2105,70 @@
     <t xml:space="preserve">14.4057207107544</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3899011611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3424348831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3582553863525</t>
+    <t xml:space="preserve">14.3899021148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.342435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3582563400269</t>
   </si>
   <si>
     <t xml:space="preserve">14.4610986709595</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0069484710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9515733718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5322952270508</t>
+    <t xml:space="preserve">15.0069494247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9515724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5322971343994</t>
   </si>
   <si>
     <t xml:space="preserve">14.3345251083374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3740787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3819894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6509599685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0860567092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8170871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6193151473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0544157028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4895143508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.869234085083</t>
+    <t xml:space="preserve">14.3740797042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3819904327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0860595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8170881271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6193170547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0544147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4895133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8692331314087</t>
   </si>
   <si>
     <t xml:space="preserve">15.7189302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3075618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3471174240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081762313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2284526824951</t>
+    <t xml:space="preserve">15.307562828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3471193313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081771850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2284555435181</t>
   </si>
   <si>
     <t xml:space="preserve">15.1572561264038</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">15.1889019012451</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1414346694946</t>
+    <t xml:space="preserve">15.1414356231689</t>
   </si>
   <si>
     <t xml:space="preserve">15.3866729736328</t>
@@ -2186,49 +2186,49 @@
     <t xml:space="preserve">15.2838306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3154735565186</t>
+    <t xml:space="preserve">15.3154754638672</t>
   </si>
   <si>
     <t xml:space="preserve">15.7505722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7110166549683</t>
+    <t xml:space="preserve">15.7110195159912</t>
   </si>
   <si>
     <t xml:space="preserve">15.6160879135132</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4420480728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2047214508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2363634109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1651659011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.402494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6239957809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7743053436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2173175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5179290771484</t>
+    <t xml:space="preserve">15.4420471191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2047204971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2363662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1651678085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4024925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6239976882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7743072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2173156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5179309844971</t>
   </si>
   <si>
     <t xml:space="preserve">16.296422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5653953552246</t>
+    <t xml:space="preserve">16.565393447876</t>
   </si>
   <si>
     <t xml:space="preserve">17.0400466918945</t>
@@ -2237,37 +2237,37 @@
     <t xml:space="preserve">16.9292945861816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0875129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9609394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.691967010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8976497650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1982650756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8818283081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2299098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.356481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4514141082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6096305847168</t>
+    <t xml:space="preserve">17.0875148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558681488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6919689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8976516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.198263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8818321228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.229907989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3564834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4514122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6096324920654</t>
   </si>
   <si>
     <t xml:space="preserve">17.4039478302002</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">17.4355907440186</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305233001709</t>
+    <t xml:space="preserve">17.5305213928223</t>
   </si>
   <si>
     <t xml:space="preserve">17.8786010742188</t>
@@ -2285,28 +2285,28 @@
     <t xml:space="preserve">18.1792144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1317501068115</t>
+    <t xml:space="preserve">18.1317481994629</t>
   </si>
   <si>
     <t xml:space="preserve">18.2583236694336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3690757751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2899684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2108592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3723049163818</t>
+    <t xml:space="preserve">18.3690776824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.289966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2108612060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3723030090332</t>
   </si>
   <si>
     <t xml:space="preserve">17.4830570220947</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7045593261719</t>
+    <t xml:space="preserve">17.7045612335205</t>
   </si>
   <si>
     <t xml:space="preserve">17.3248386383057</t>
@@ -2315,25 +2315,25 @@
     <t xml:space="preserve">16.5021076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4988784790039</t>
+    <t xml:space="preserve">17.4988803863525</t>
   </si>
   <si>
     <t xml:space="preserve">17.1508007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1701707839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.021315574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8267736434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6210908889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.629002571106</t>
+    <t xml:space="preserve">11.1701698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0213174819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8267726898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6210899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6290006637573</t>
   </si>
   <si>
     <t xml:space="preserve">11.3600311279297</t>
@@ -2345,73 +2345,73 @@
     <t xml:space="preserve">11.4470510482788</t>
   </si>
   <si>
-    <t xml:space="preserve">12.02454662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0640993118286</t>
+    <t xml:space="preserve">12.0245456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0641002655029</t>
   </si>
   <si>
     <t xml:space="preserve">12.4200897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1748542785645</t>
+    <t xml:space="preserve">12.1748533248901</t>
   </si>
   <si>
     <t xml:space="preserve">12.9026536941528</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6969709396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2190885543823</t>
+    <t xml:space="preserve">12.6969699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2190895080566</t>
   </si>
   <si>
     <t xml:space="preserve">13.4722385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3140211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2349119186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241588592529</t>
+    <t xml:space="preserve">13.3140201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2349109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241579055786</t>
   </si>
   <si>
     <t xml:space="preserve">13.4089527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4564170837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1004257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0925140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687818527222</t>
+    <t xml:space="preserve">13.4564161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1004266738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0925149917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2507333755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687837600708</t>
   </si>
   <si>
     <t xml:space="preserve">13.3614845275879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4326820373535</t>
+    <t xml:space="preserve">13.4326829910278</t>
   </si>
   <si>
     <t xml:space="preserve">13.5038805007935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9738512039185</t>
+    <t xml:space="preserve">12.9738521575928</t>
   </si>
   <si>
     <t xml:space="preserve">12.9342975616455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0371398925781</t>
+    <t xml:space="preserve">13.0371389389038</t>
   </si>
   <si>
     <t xml:space="preserve">13.1795358657837</t>
@@ -2420,34 +2420,34 @@
     <t xml:space="preserve">13.2111797332764</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5434379577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6225442886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7095642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2056894302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1560764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966442108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2883768081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0490999221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2475490570068</t>
+    <t xml:space="preserve">13.5434370040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6225452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7095651626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2056884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1560773849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2883758544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0491008758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2475500106812</t>
   </si>
   <si>
     <t xml:space="preserve">15.2971611022949</t>
@@ -2459,13 +2459,13 @@
     <t xml:space="preserve">16.4134426116943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5043964385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1405754089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0909576416016</t>
+    <t xml:space="preserve">16.5043983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1405715942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0909614562988</t>
   </si>
   <si>
     <t xml:space="preserve">16.190185546875</t>
@@ -2474,19 +2474,19 @@
     <t xml:space="preserve">15.5865678787231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5286874771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2144727706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2806234359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8346290588379</t>
+    <t xml:space="preserve">15.5286884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3467741012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2144746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2806253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8346300125122</t>
   </si>
   <si>
     <t xml:space="preserve">15.6527166366577</t>
@@ -2495,46 +2495,46 @@
     <t xml:space="preserve">15.6692562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5782976150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932872772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8594379425049</t>
+    <t xml:space="preserve">15.5782995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932844161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8594360351562</t>
   </si>
   <si>
     <t xml:space="preserve">15.3633108139038</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4294595718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5617609024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8677043914795</t>
+    <t xml:space="preserve">15.429461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5617599487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8677053451538</t>
   </si>
   <si>
     <t xml:space="preserve">16.330753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0501346588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2651214599609</t>
+    <t xml:space="preserve">17.0501365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2651233673096</t>
   </si>
   <si>
     <t xml:space="preserve">16.868221282959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9509124755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1162872314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3312702178955</t>
+    <t xml:space="preserve">16.9509105682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1162853240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3312683105469</t>
   </si>
   <si>
     <t xml:space="preserve">17.51318359375</t>
@@ -2543,31 +2543,31 @@
     <t xml:space="preserve">17.7777824401855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2981948852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2816600799561</t>
+    <t xml:space="preserve">17.2981967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2816581726074</t>
   </si>
   <si>
     <t xml:space="preserve">17.314733505249</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4304943084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3643436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3808860778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9839859008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8186092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9012966156006</t>
+    <t xml:space="preserve">17.4304962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3643455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3808822631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9839839935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8186111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9012985229492</t>
   </si>
   <si>
     <t xml:space="preserve">16.8516845703125</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">16.7524604797363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0170612335205</t>
+    <t xml:space="preserve">17.0170574188232</t>
   </si>
   <si>
     <t xml:space="preserve">17.4635715484619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5958709716797</t>
+    <t xml:space="preserve">17.5958728790283</t>
   </si>
   <si>
     <t xml:space="preserve">17.4801082611084</t>
@@ -2600,16 +2600,16 @@
     <t xml:space="preserve">18.0919933319092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4227466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4723567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.158145904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0258445739746</t>
+    <t xml:space="preserve">18.4227447509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.472354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1581439971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.025842666626</t>
   </si>
   <si>
     <t xml:space="preserve">18.0754585266113</t>
@@ -2618,22 +2618,22 @@
     <t xml:space="preserve">18.5054302215576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.389669418335</t>
+    <t xml:space="preserve">18.3896713256836</t>
   </si>
   <si>
     <t xml:space="preserve">18.2739067077637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3235206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3400573730469</t>
+    <t xml:space="preserve">18.3235187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3400592803955</t>
   </si>
   <si>
     <t xml:space="preserve">18.191219329834</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0589218139648</t>
+    <t xml:space="preserve">18.0589199066162</t>
   </si>
   <si>
     <t xml:space="preserve">17.910083770752</t>
@@ -2645,37 +2645,37 @@
     <t xml:space="preserve">18.3069801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620197296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7943229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.711633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5793342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3478088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4966430664062</t>
+    <t xml:space="preserve">17.6620216369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7943210601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7116317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5793323516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.347806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4966449737549</t>
   </si>
   <si>
     <t xml:space="preserve">17.3974208831787</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7447071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6046581268311</t>
+    <t xml:space="preserve">17.7447090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6046562194824</t>
   </si>
   <si>
     <t xml:space="preserve">18.7700328826904</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3731288909912</t>
+    <t xml:space="preserve">18.3731307983398</t>
   </si>
   <si>
     <t xml:space="preserve">18.6542682647705</t>
@@ -2684,19 +2684,19 @@
     <t xml:space="preserve">18.7534942626953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4062061309814</t>
+    <t xml:space="preserve">18.4062080383301</t>
   </si>
   <si>
     <t xml:space="preserve">18.1416072845459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9431571960449</t>
+    <t xml:space="preserve">17.9431591033936</t>
   </si>
   <si>
     <t xml:space="preserve">18.1085319519043</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7281723022461</t>
+    <t xml:space="preserve">17.7281684875488</t>
   </si>
   <si>
     <t xml:space="preserve">17.95969581604</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">17.1989707946777</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6366958618164</t>
+    <t xml:space="preserve">16.636697769165</t>
   </si>
   <si>
     <t xml:space="preserve">16.2894096374512</t>
@@ -2714,40 +2714,40 @@
     <t xml:space="preserve">15.9503927230835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0413475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5374736785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0832099914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5627937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.06667137146</t>
+    <t xml:space="preserve">16.0413494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5374717712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0832080841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5627956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0666694641113</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155094146729</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1658954620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0005207061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7028465270996</t>
+    <t xml:space="preserve">17.1658973693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0005226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178333282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7028484344482</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847599029541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7855319976807</t>
+    <t xml:space="preserve">16.7855358123779</t>
   </si>
   <si>
     <t xml:space="preserve">16.6201591491699</t>
@@ -2762,28 +2762,28 @@
     <t xml:space="preserve">17.1328201293945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1824359893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462589263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1746826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8692569732666</t>
+    <t xml:space="preserve">17.1824340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.546257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1746807098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.869255065918</t>
   </si>
   <si>
     <t xml:space="preserve">19.1669311523438</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3488426208496</t>
+    <t xml:space="preserve">19.348840713501</t>
   </si>
   <si>
     <t xml:space="preserve">20.0599536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9607276916504</t>
+    <t xml:space="preserve">19.960729598999</t>
   </si>
   <si>
     <t xml:space="preserve">20.5064659118652</t>
@@ -2801,31 +2801,31 @@
     <t xml:space="preserve">20.8206768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7545280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9364395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7214508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0025882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1845035552979</t>
+    <t xml:space="preserve">20.7545299530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9364376068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7214527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0025901794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1844997406006</t>
   </si>
   <si>
     <t xml:space="preserve">21.6806240081787</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1767520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9948387145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5571098327637</t>
+    <t xml:space="preserve">22.1767501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.994836807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5571117401123</t>
   </si>
   <si>
     <t xml:space="preserve">21.2175769805908</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">20.9529781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3002662658691</t>
+    <t xml:space="preserve">21.3002643585205</t>
   </si>
   <si>
     <t xml:space="preserve">21.5979385375977</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">21.8956127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5152530670166</t>
+    <t xml:space="preserve">21.515251159668</t>
   </si>
   <si>
     <t xml:space="preserve">21.8460006713867</t>
@@ -2861,25 +2861,25 @@
     <t xml:space="preserve">21.5317897796631</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3664169311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7379894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5726165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2506542205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7876033782959</t>
+    <t xml:space="preserve">21.3664131164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7379913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5726146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2506523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7876014709473</t>
   </si>
   <si>
     <t xml:space="preserve">20.2584056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6134414672852</t>
+    <t xml:space="preserve">19.6134433746338</t>
   </si>
   <si>
     <t xml:space="preserve">20.192253112793</t>
@@ -2888,16 +2888,16 @@
     <t xml:space="preserve">19.3323040008545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9354057312012</t>
+    <t xml:space="preserve">18.9354038238525</t>
   </si>
   <si>
     <t xml:space="preserve">20.2749404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2010402679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9860534667969</t>
+    <t xml:space="preserve">21.2010383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9860515594482</t>
   </si>
   <si>
     <t xml:space="preserve">21.4656391143799</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">20.0103416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2253284454346</t>
+    <t xml:space="preserve">19.6465148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2253265380859</t>
   </si>
   <si>
     <t xml:space="preserve">20.3410911560059</t>
@@ -2921,16 +2921,16 @@
     <t xml:space="preserve">20.638765335083</t>
   </si>
   <si>
-    <t xml:space="preserve">21.035665512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.34987449646</t>
+    <t xml:space="preserve">21.0356636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3498764038086</t>
   </si>
   <si>
     <t xml:space="preserve">21.0852756500244</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0191268920898</t>
+    <t xml:space="preserve">21.0191287994385</t>
   </si>
   <si>
     <t xml:space="preserve">20.870288848877</t>
@@ -2942,31 +2942,31 @@
     <t xml:space="preserve">20.8868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5230045318604</t>
+    <t xml:space="preserve">20.5230026245117</t>
   </si>
   <si>
     <t xml:space="preserve">20.6056900024414</t>
   </si>
   <si>
-    <t xml:space="preserve">20.026876449585</t>
+    <t xml:space="preserve">20.0268783569336</t>
   </si>
   <si>
     <t xml:space="preserve">20.1095676422119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1514263153076</t>
+    <t xml:space="preserve">21.1514282226562</t>
   </si>
   <si>
     <t xml:space="preserve">20.6222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3080177307129</t>
+    <t xml:space="preserve">20.3080158233643</t>
   </si>
   <si>
     <t xml:space="preserve">20.4072399139404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9772682189941</t>
+    <t xml:space="preserve">19.9772663116455</t>
   </si>
   <si>
     <t xml:space="preserve">20.3907032012939</t>
@@ -2975,73 +2975,73 @@
     <t xml:space="preserve">20.1261024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0764923095703</t>
+    <t xml:space="preserve">20.0764904022217</t>
   </si>
   <si>
     <t xml:space="preserve">20.2914791107178</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2661552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7622776031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8780422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3484592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3314075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0756359100342</t>
+    <t xml:space="preserve">19.2661533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.762279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.878044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3484573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3314094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0756320953369</t>
   </si>
   <si>
     <t xml:space="preserve">21.2461490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.229097366333</t>
+    <t xml:space="preserve">21.2290992736816</t>
   </si>
   <si>
     <t xml:space="preserve">21.177942276001</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4337158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4848728179932</t>
+    <t xml:space="preserve">21.4337139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4848709106445</t>
   </si>
   <si>
     <t xml:space="preserve">21.6042308807373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6212825775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3143558502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5701274871826</t>
+    <t xml:space="preserve">21.621280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3143539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.570125579834</t>
   </si>
   <si>
     <t xml:space="preserve">22.388599395752</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9793643951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0646190643311</t>
+    <t xml:space="preserve">21.979362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0646171569824</t>
   </si>
   <si>
     <t xml:space="preserve">22.0305194854736</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7235889434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6553840637207</t>
+    <t xml:space="preserve">21.7235908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6553859710693</t>
   </si>
   <si>
     <t xml:space="preserve">21.7406406402588</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">21.3655071258545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4507656097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.672435760498</t>
+    <t xml:space="preserve">21.4507675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6724376678467</t>
   </si>
   <si>
     <t xml:space="preserve">22.0987243652344</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">21.7917957305908</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9964122772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3825607299805</t>
+    <t xml:space="preserve">21.9964141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3825626373291</t>
   </si>
   <si>
     <t xml:space="preserve">20.8369140625</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">20.8710174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">20.888069152832</t>
+    <t xml:space="preserve">20.8880672454834</t>
   </si>
   <si>
     <t xml:space="preserve">21.7065391540527</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">22.47385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2692375183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7346057891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5470371246338</t>
+    <t xml:space="preserve">22.2692394256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7346038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5470390319824</t>
   </si>
   <si>
     <t xml:space="preserve">21.2632007598877</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">21.1097373962402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1608924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5530776977539</t>
+    <t xml:space="preserve">21.1608905792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5530757904053</t>
   </si>
   <si>
     <t xml:space="preserve">21.7747478485107</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">21.2973022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0926837921143</t>
+    <t xml:space="preserve">21.0926856994629</t>
   </si>
   <si>
     <t xml:space="preserve">20.8539638519287</t>
@@ -3143,16 +3143,16 @@
     <t xml:space="preserve">21.8941059112549</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7576961517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3996124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9111595153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5079593658447</t>
+    <t xml:space="preserve">21.7576942443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3996143341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9111576080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5079574584961</t>
   </si>
   <si>
     <t xml:space="preserve">22.1669292449951</t>
@@ -3164,13 +3164,13 @@
     <t xml:space="preserve">22.013463973999</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4909057617188</t>
+    <t xml:space="preserve">22.4909076690674</t>
   </si>
   <si>
     <t xml:space="preserve">22.422700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2521877288818</t>
+    <t xml:space="preserve">22.2521858215332</t>
   </si>
   <si>
     <t xml:space="preserve">22.5761642456055</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">22.6614227294922</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7296295166016</t>
+    <t xml:space="preserve">22.7296257019043</t>
   </si>
   <si>
     <t xml:space="preserve">23.172966003418</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">23.7697696685791</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4628410339355</t>
+    <t xml:space="preserve">23.4628429412842</t>
   </si>
   <si>
     <t xml:space="preserve">23.3775844573975</t>
@@ -3197,19 +3197,19 @@
     <t xml:space="preserve">23.9232330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">25.219144821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4749183654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8329982757568</t>
+    <t xml:space="preserve">25.2191429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4749164581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8329963684082</t>
   </si>
   <si>
     <t xml:space="preserve">25.7818431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1740283966064</t>
+    <t xml:space="preserve">26.1740303039551</t>
   </si>
   <si>
     <t xml:space="preserve">26.3274898529053</t>
@@ -3221,28 +3221,28 @@
     <t xml:space="preserve">26.6173667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7708301544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6855716705322</t>
+    <t xml:space="preserve">26.7708282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6855735778809</t>
   </si>
   <si>
     <t xml:space="preserve">25.969409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7196769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3615951538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3104400634766</t>
+    <t xml:space="preserve">26.7196750640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3615970611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3104419708252</t>
   </si>
   <si>
     <t xml:space="preserve">26.5491600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2251815795898</t>
+    <t xml:space="preserve">26.2251834869385</t>
   </si>
   <si>
     <t xml:space="preserve">25.5431232452393</t>
@@ -3257,52 +3257,52 @@
     <t xml:space="preserve">25.0145282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1679916381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1168365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8099098205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8440132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1338863372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7246532440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7587547302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3896617889404</t>
+    <t xml:space="preserve">25.167989730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1168346405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8099117279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8440113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1338882446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7246513366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7587566375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3896598815918</t>
   </si>
   <si>
     <t xml:space="preserve">24.3836231231689</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1790065765381</t>
+    <t xml:space="preserve">24.1790046691895</t>
   </si>
   <si>
     <t xml:space="preserve">24.3324680328369</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6223411560059</t>
+    <t xml:space="preserve">24.6223430633545</t>
   </si>
   <si>
     <t xml:space="preserve">24.1960563659668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3495178222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9402828216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1448993682861</t>
+    <t xml:space="preserve">24.3495197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9402847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1449012756348</t>
   </si>
   <si>
     <t xml:space="preserve">24.1107997894287</t>
@@ -3311,13 +3311,13 @@
     <t xml:space="preserve">23.8038711547852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4177227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4518299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2131061553955</t>
+    <t xml:space="preserve">24.417724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4518280029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2131080627441</t>
   </si>
   <si>
     <t xml:space="preserve">24.3665714263916</t>
@@ -3326,28 +3326,28 @@
     <t xml:space="preserve">24.2472114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2813110351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0486297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4347763061523</t>
+    <t xml:space="preserve">24.2813129425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0486278533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.434778213501</t>
   </si>
   <si>
     <t xml:space="preserve">23.5481014251709</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4969463348389</t>
+    <t xml:space="preserve">23.4969444274902</t>
   </si>
   <si>
     <t xml:space="preserve">22.9342479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7978343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6443691253662</t>
+    <t xml:space="preserve">22.7978324890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6443710327148</t>
   </si>
   <si>
     <t xml:space="preserve">22.3033409118652</t>
@@ -3362,25 +3362,25 @@
     <t xml:space="preserve">21.8429527282715</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1839828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1949939727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.638334274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2120475769043</t>
+    <t xml:space="preserve">22.1839809417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.194995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6383323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2120456695557</t>
   </si>
   <si>
     <t xml:space="preserve">20.9051189422607</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6664009094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4678173065186</t>
+    <t xml:space="preserve">20.6663990020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4678192138672</t>
   </si>
   <si>
     <t xml:space="preserve">21.0244789123535</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">20.5129356384277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2912654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1378040313721</t>
+    <t xml:space="preserve">20.2912673950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1378021240234</t>
   </si>
   <si>
     <t xml:space="preserve">22.6273193359375</t>
@@ -3407,16 +3407,16 @@
     <t xml:space="preserve">24.0937480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6163063049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7637310028076</t>
+    <t xml:space="preserve">23.616304397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7637329101562</t>
   </si>
   <si>
     <t xml:space="preserve">22.8148860931396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6102676391602</t>
+    <t xml:space="preserve">22.6102695465088</t>
   </si>
   <si>
     <t xml:space="preserve">24.1619529724121</t>
@@ -3452,28 +3452,28 @@
     <t xml:space="preserve">25.662483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3786468505859</t>
+    <t xml:space="preserve">26.3786449432373</t>
   </si>
   <si>
     <t xml:space="preserve">26.2933883666992</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8049335479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.753776550293</t>
+    <t xml:space="preserve">26.8049354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7537784576416</t>
   </si>
   <si>
     <t xml:space="preserve">26.9413452148438</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0436534881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0948104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.821985244751</t>
+    <t xml:space="preserve">27.0436515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0948066711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8219833374023</t>
   </si>
   <si>
     <t xml:space="preserve">26.9925003051758</t>
@@ -3488,22 +3488,22 @@
     <t xml:space="preserve">27.5040416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4699401855469</t>
+    <t xml:space="preserve">27.4699420928955</t>
   </si>
   <si>
     <t xml:space="preserve">27.6916103363037</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7939205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8621273040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0496921539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5893039703369</t>
+    <t xml:space="preserve">27.7939186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8621253967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0496940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5893020629883</t>
   </si>
   <si>
     <t xml:space="preserve">27.1800651550293</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">26.8901920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7598171234131</t>
+    <t xml:space="preserve">27.7598152160645</t>
   </si>
   <si>
     <t xml:space="preserve">28.475980758667</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">28.6976490020752</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9875221252441</t>
+    <t xml:space="preserve">28.9875240325928</t>
   </si>
   <si>
     <t xml:space="preserve">29.4604301452637</t>
@@ -3557,16 +3557,16 @@
     <t xml:space="preserve">30.0559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5655212402344</t>
+    <t xml:space="preserve">29.5655193328857</t>
   </si>
   <si>
     <t xml:space="preserve">28.724796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6197071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3394660949707</t>
+    <t xml:space="preserve">28.6197052001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3394641876221</t>
   </si>
   <si>
     <t xml:space="preserve">28.1993446350098</t>
@@ -3578,16 +3578,16 @@
     <t xml:space="preserve">28.9524955749512</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8824310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0575847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1451568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0433444976807</t>
+    <t xml:space="preserve">28.8824329376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0575828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1451587677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.043342590332</t>
   </si>
   <si>
     <t xml:space="preserve">26.6229820251465</t>
@@ -3599,31 +3599,31 @@
     <t xml:space="preserve">26.8681926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0099544525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9924373626709</t>
+    <t xml:space="preserve">26.009952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9924392700195</t>
   </si>
   <si>
     <t xml:space="preserve">25.9574069976807</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6071033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5178909301758</t>
+    <t xml:space="preserve">25.607105255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5178928375244</t>
   </si>
   <si>
     <t xml:space="preserve">26.255163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6054649353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8873481750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4653453826904</t>
+    <t xml:space="preserve">26.6054668426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8873462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4653434753418</t>
   </si>
   <si>
     <t xml:space="preserve">26.3252239227295</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">26.1675891876221</t>
   </si>
   <si>
-    <t xml:space="preserve">26.93825340271</t>
+    <t xml:space="preserve">26.9382553100586</t>
   </si>
   <si>
     <t xml:space="preserve">26.9732856750488</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">27.3411026000977</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7455883026123</t>
+    <t xml:space="preserve">26.7455902099609</t>
   </si>
   <si>
     <t xml:space="preserve">26.9907989501953</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">27.6563739776611</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5687999725342</t>
+    <t xml:space="preserve">27.5687980651855</t>
   </si>
   <si>
     <t xml:space="preserve">26.7280731201172</t>
@@ -3665,19 +3665,19 @@
     <t xml:space="preserve">25.7822570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3602542877197</t>
+    <t xml:space="preserve">26.3602561950684</t>
   </si>
   <si>
     <t xml:space="preserve">26.6930408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5879516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1834678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512847900391</t>
+    <t xml:space="preserve">26.5879535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1834659576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512809753418</t>
   </si>
   <si>
     <t xml:space="preserve">27.8840713500977</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">28.1467971801758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4445552825928</t>
+    <t xml:space="preserve">28.4445533752441</t>
   </si>
   <si>
     <t xml:space="preserve">28.8999481201172</t>
@@ -3698,16 +3698,16 @@
     <t xml:space="preserve">29.6706123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7757015228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.65309715271</t>
+    <t xml:space="preserve">29.7757053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6530990600586</t>
   </si>
   <si>
     <t xml:space="preserve">29.2327365875244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4062480926514</t>
+    <t xml:space="preserve">30.40625</t>
   </si>
   <si>
     <t xml:space="preserve">30.1260051727295</t>
@@ -3716,37 +3716,37 @@
     <t xml:space="preserve">30.3186721801758</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8632793426514</t>
+    <t xml:space="preserve">29.8632774353027</t>
   </si>
   <si>
     <t xml:space="preserve">29.950855255127</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4412746429443</t>
+    <t xml:space="preserve">30.4412784576416</t>
   </si>
   <si>
     <t xml:space="preserve">31.1593990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3361854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1785488128662</t>
+    <t xml:space="preserve">30.3361873626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1785526275635</t>
   </si>
   <si>
     <t xml:space="preserve">29.7406730651855</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7089195251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4987392425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0258293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1851043701172</t>
+    <t xml:space="preserve">27.7089214324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4987373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0258312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1851024627686</t>
   </si>
   <si>
     <t xml:space="preserve">26.4478321075439</t>
@@ -3782,22 +3782,22 @@
     <t xml:space="preserve">27.8665561676025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1692276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0641384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5912284851074</t>
+    <t xml:space="preserve">25.169225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.064136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5912303924561</t>
   </si>
   <si>
     <t xml:space="preserve">24.7488651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2726783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1659526824951</t>
+    <t xml:space="preserve">26.2726802825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1659507751465</t>
   </si>
   <si>
     <t xml:space="preserve">25.0816516876221</t>
@@ -3806,16 +3806,16 @@
     <t xml:space="preserve">24.9415302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4335918426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1708679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.978199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8380794525146</t>
+    <t xml:space="preserve">24.4335899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1708660125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9781970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.838077545166</t>
   </si>
   <si>
     <t xml:space="preserve">24.9065017700195</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">26.7806186676025</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6738910675049</t>
+    <t xml:space="preserve">27.6738891601562</t>
   </si>
   <si>
     <t xml:space="preserve">27.7964954376221</t>
@@ -3851,25 +3851,25 @@
     <t xml:space="preserve">27.2535285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">27.48122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9366149902344</t>
+    <t xml:space="preserve">27.4812240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.936616897583</t>
   </si>
   <si>
     <t xml:space="preserve">28.8649158477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7631015777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9032230377197</t>
+    <t xml:space="preserve">26.7631034851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9032249450684</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274677276611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.39528465271</t>
+    <t xml:space="preserve">26.3952865600586</t>
   </si>
   <si>
     <t xml:space="preserve">26.8331623077393</t>
@@ -3881,10 +3881,10 @@
     <t xml:space="preserve">25.9223766326904</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3777694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5003776550293</t>
+    <t xml:space="preserve">26.3777713775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5003757476807</t>
   </si>
   <si>
     <t xml:space="preserve">26.1325588226318</t>
@@ -3893,22 +3893,22 @@
     <t xml:space="preserve">26.097526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5354042053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8857078552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2376480102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7647399902344</t>
+    <t xml:space="preserve">26.5354061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8857097625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2376499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.764741897583</t>
   </si>
   <si>
     <t xml:space="preserve">25.8348026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2201328277588</t>
+    <t xml:space="preserve">26.2201366424561</t>
   </si>
   <si>
     <t xml:space="preserve">25.4144401550293</t>
@@ -3923,10 +3923,10 @@
     <t xml:space="preserve">25.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5895881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8714694976807</t>
+    <t xml:space="preserve">25.5895900726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8714714050293</t>
   </si>
   <si>
     <t xml:space="preserve">24.4686241149902</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">24.5737133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1183223724365</t>
+    <t xml:space="preserve">24.1183204650879</t>
   </si>
   <si>
     <t xml:space="preserve">24.2409267425537</t>
@@ -3950,16 +3950,16 @@
     <t xml:space="preserve">24.8539543151855</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3109874725342</t>
+    <t xml:space="preserve">24.3109855651855</t>
   </si>
   <si>
     <t xml:space="preserve">24.2234115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3460178375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4160766601562</t>
+    <t xml:space="preserve">24.3460159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">24.3985633850098</t>
@@ -3989,7 +3989,7 @@
     <t xml:space="preserve">24.2058944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1883811950684</t>
+    <t xml:space="preserve">24.188383102417</t>
   </si>
   <si>
     <t xml:space="preserve">23.7329883575439</t>
@@ -4001,16 +4001,16 @@
     <t xml:space="preserve">23.9957141876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0307464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8731098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3476543426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7154731750488</t>
+    <t xml:space="preserve">24.0307445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8731079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7154712677002</t>
   </si>
   <si>
     <t xml:space="preserve">23.7680168151855</t>
@@ -4022,10 +4022,10 @@
     <t xml:space="preserve">23.5052909851074</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0498962402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8747463226318</t>
+    <t xml:space="preserve">23.049898147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8747482299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.1900177001953</t>
@@ -4034,16 +4034,16 @@
     <t xml:space="preserve">23.2425651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6979579925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5578384399414</t>
+    <t xml:space="preserve">23.6979560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5578365325928</t>
   </si>
   <si>
     <t xml:space="preserve">23.9256534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7505035400391</t>
+    <t xml:space="preserve">23.7505016326904</t>
   </si>
   <si>
     <t xml:space="preserve">23.435230255127</t>
@@ -4052,37 +4052,37 @@
     <t xml:space="preserve">23.0849285125732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3826847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5228080749512</t>
+    <t xml:space="preserve">23.3826866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5228061676025</t>
   </si>
   <si>
     <t xml:space="preserve">23.9606857299805</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4861373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2584419250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1166839599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.221773147583</t>
+    <t xml:space="preserve">24.4861354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2584400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1166820526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2217712402344</t>
   </si>
   <si>
     <t xml:space="preserve">25.2042579650879</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1341972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6262607574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3635311126709</t>
+    <t xml:space="preserve">25.1341991424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6262588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3635330200195</t>
   </si>
   <si>
     <t xml:space="preserve">23.7855339050293</t>
@@ -4091,16 +4091,16 @@
     <t xml:space="preserve">23.2250499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9798355102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2775917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.295108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0657749176025</t>
+    <t xml:space="preserve">22.9798374176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2775955200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2951107025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0657730102539</t>
   </si>
   <si>
     <t xml:space="preserve">24.7663803100586</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">23.6418628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4965953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334342956543</t>
+    <t xml:space="preserve">23.4965972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334362030029</t>
   </si>
   <si>
     <t xml:space="preserve">23.5329132080078</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">24.2955551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5679264068604</t>
+    <t xml:space="preserve">24.5679244995117</t>
   </si>
   <si>
     <t xml:space="preserve">24.4771347045898</t>
@@ -4163,13 +4163,13 @@
     <t xml:space="preserve">24.5134525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3318710327148</t>
+    <t xml:space="preserve">24.3318691253662</t>
   </si>
   <si>
     <t xml:space="preserve">23.9868659973145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5510711669922</t>
+    <t xml:space="preserve">23.5510730743408</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058074951172</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">23.4602813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8234424591064</t>
+    <t xml:space="preserve">23.8234443664551</t>
   </si>
   <si>
     <t xml:space="preserve">23.6237049102783</t>
@@ -4196,13 +4196,13 @@
     <t xml:space="preserve">24.8221397399902</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0413398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3863468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1321296691895</t>
+    <t xml:space="preserve">24.0413417816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.386344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1321315765381</t>
   </si>
   <si>
     <t xml:space="preserve">24.4589786529541</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">24.6768760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6042442321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5497703552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7858238220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2397766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8039817810059</t>
+    <t xml:space="preserve">24.6042423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.549768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7858219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2397747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8039798736572</t>
   </si>
   <si>
     <t xml:space="preserve">24.9674053192139</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">22.2618465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2981624603271</t>
+    <t xml:space="preserve">22.2981605529785</t>
   </si>
   <si>
     <t xml:space="preserve">22.388952255249</t>
@@ -4271,25 +4271,25 @@
     <t xml:space="preserve">22.2073707580566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0621070861816</t>
+    <t xml:space="preserve">22.062105178833</t>
   </si>
   <si>
     <t xml:space="preserve">21.6807861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6263122558594</t>
+    <t xml:space="preserve">21.6263103485107</t>
   </si>
   <si>
     <t xml:space="preserve">22.6431674957275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6794815063477</t>
+    <t xml:space="preserve">22.6794834136963</t>
   </si>
   <si>
     <t xml:space="preserve">22.5886917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1515922546387</t>
+    <t xml:space="preserve">23.1515941619873</t>
   </si>
   <si>
     <t xml:space="preserve">22.9700107574463</t>
@@ -4310,28 +4310,28 @@
     <t xml:space="preserve">23.024486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9155368804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.86106300354</t>
+    <t xml:space="preserve">22.9155387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8610649108887</t>
   </si>
   <si>
     <t xml:space="preserve">23.2060661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5342178344727</t>
+    <t xml:space="preserve">22.534215927124</t>
   </si>
   <si>
     <t xml:space="preserve">21.9349994659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8442096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2631511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8999881744385</t>
+    <t xml:space="preserve">21.8442077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2631492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8999862670898</t>
   </si>
   <si>
     <t xml:space="preserve">20.482349395752</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">20.7365646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1010284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6833934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7378673553467</t>
+    <t xml:space="preserve">20.1010303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6833953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7378692626953</t>
   </si>
   <si>
     <t xml:space="preserve">20.0102405548096</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">19.9376068115234</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3915576934814</t>
+    <t xml:space="preserve">20.3915596008301</t>
   </si>
   <si>
     <t xml:space="preserve">20.6094589233398</t>
@@ -4373,19 +4373,19 @@
     <t xml:space="preserve">20.6820907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1542015075684</t>
+    <t xml:space="preserve">21.1541996002197</t>
   </si>
   <si>
     <t xml:space="preserve">21.0997276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1723594665527</t>
+    <t xml:space="preserve">21.1723575592041</t>
   </si>
   <si>
     <t xml:space="preserve">21.0634117126465</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8091983795166</t>
+    <t xml:space="preserve">20.809196472168</t>
   </si>
   <si>
     <t xml:space="preserve">21.0089359283447</t>
@@ -4397,16 +4397,16 @@
     <t xml:space="preserve">21.0270938873291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.608154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7715759277344</t>
+    <t xml:space="preserve">21.6081523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.771577835083</t>
   </si>
   <si>
     <t xml:space="preserve">21.4628887176514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9181480407715</t>
+    <t xml:space="preserve">20.9181461334229</t>
   </si>
   <si>
     <t xml:space="preserve">21.2449913024902</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">22.7884311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0971183776855</t>
+    <t xml:space="preserve">23.0971202850342</t>
   </si>
   <si>
     <t xml:space="preserve">23.2605419158936</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">23.1152763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3694896697998</t>
+    <t xml:space="preserve">23.3694915771484</t>
   </si>
   <si>
     <t xml:space="preserve">23.8960742950439</t>
@@ -4445,13 +4445,13 @@
     <t xml:space="preserve">24.3681869506836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7689685821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4408206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2216186523438</t>
+    <t xml:space="preserve">23.768970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4408187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2216205596924</t>
   </si>
   <si>
     <t xml:space="preserve">25.493989944458</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">25.966100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">25.984260559082</t>
+    <t xml:space="preserve">25.9842586517334</t>
   </si>
   <si>
     <t xml:space="preserve">26.0932083129883</t>
@@ -4478,31 +4478,31 @@
     <t xml:space="preserve">26.2021560668945</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4758319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8947734832764</t>
+    <t xml:space="preserve">25.475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8947715759277</t>
   </si>
   <si>
     <t xml:space="preserve">25.0945110321045</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2942523956299</t>
+    <t xml:space="preserve">25.2942504882812</t>
   </si>
   <si>
     <t xml:space="preserve">24.9129314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">24.713191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0763549804688</t>
+    <t xml:space="preserve">24.7131900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0763530731201</t>
   </si>
   <si>
     <t xml:space="preserve">24.6405582427979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6587181091309</t>
+    <t xml:space="preserve">24.6587162017822</t>
   </si>
   <si>
     <t xml:space="preserve">24.3137130737305</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">21.5718383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4447326660156</t>
+    <t xml:space="preserve">21.444730758667</t>
   </si>
   <si>
     <t xml:space="preserve">21.1905174255371</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">21.136043548584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9363040924072</t>
+    <t xml:space="preserve">20.9363021850586</t>
   </si>
   <si>
     <t xml:space="preserve">21.3176250457764</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">22.6976413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7871265411377</t>
+    <t xml:space="preserve">23.7871284484863</t>
   </si>
   <si>
     <t xml:space="preserve">24.0231819152832</t>
@@ -5454,6 +5454,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.4400005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7999992370605</t>
   </si>
 </sst>
 </file>
@@ -70844,7 +70847,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6913078704</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>212460</v>
@@ -70865,6 +70868,32 @@
         <v>1813</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6909953704</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>325430</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>22.8199996948242</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>22.2199993133545</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>22.3400001525879</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>22.7999992370605</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1814</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48755311965942</t>
+    <t xml:space="preserve">7.48755407333374</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
@@ -53,58 +53,58 @@
     <t xml:space="preserve">7.04389238357544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99527215957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06212568283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25053071975708</t>
+    <t xml:space="preserve">6.99527168273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06212520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25052976608276</t>
   </si>
   <si>
     <t xml:space="preserve">7.22014141082764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17152214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07428073883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8494119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01350450515747</t>
+    <t xml:space="preserve">7.17152166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07428121566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84941053390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01350545883179</t>
   </si>
   <si>
     <t xml:space="preserve">6.75216913223267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83725595474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97096109390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09251308441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00742673873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00135040283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9891939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92841911315918</t>
+    <t xml:space="preserve">6.83725547790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9709620475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09251260757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00742769241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00134944915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98919439315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92841958999634</t>
   </si>
   <si>
     <t xml:space="preserve">6.86156511306763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53337717056274</t>
+    <t xml:space="preserve">6.5333776473999</t>
   </si>
   <si>
     <t xml:space="preserve">6.47867918014526</t>
@@ -113,61 +113,61 @@
     <t xml:space="preserve">6.61238622665405</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55160903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77648019790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94057369232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8737211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63061857223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78863525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58199834823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70354986190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7157039642334</t>
+    <t xml:space="preserve">6.55160999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77647972106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94057416915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87372159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63061761856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78863573074341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58199882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70354890823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71570491790771</t>
   </si>
   <si>
     <t xml:space="preserve">6.80686712265015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91626405715942</t>
+    <t xml:space="preserve">6.91626310348511</t>
   </si>
   <si>
     <t xml:space="preserve">6.84333276748657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83117866516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87979698181152</t>
+    <t xml:space="preserve">6.83117771148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87979984283447</t>
   </si>
   <si>
     <t xml:space="preserve">6.7096266746521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74609327316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85548830032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86764430999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95272874832153</t>
+    <t xml:space="preserve">6.74609184265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85548734664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8676438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95272922515869</t>
   </si>
   <si>
     <t xml:space="preserve">7.04996919631958</t>
@@ -176,31 +176,31 @@
     <t xml:space="preserve">7.27483940124512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35992574691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34777069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26876211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22622013092041</t>
+    <t xml:space="preserve">7.35992527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34777116775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26876258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22621965408325</t>
   </si>
   <si>
     <t xml:space="preserve">7.11074590682983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03173732757568</t>
+    <t xml:space="preserve">7.03173780441284</t>
   </si>
   <si>
     <t xml:space="preserve">7.08035755157471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05604696273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975400924683</t>
+    <t xml:space="preserve">7.0560474395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975496292114</t>
   </si>
   <si>
     <t xml:space="preserve">7.23229646682739</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">7.15328931808472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11682319641113</t>
+    <t xml:space="preserve">7.11682415008545</t>
   </si>
   <si>
     <t xml:space="preserve">7.16544389724731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95880746841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.934494972229</t>
+    <t xml:space="preserve">6.95880651473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93449687957764</t>
   </si>
   <si>
     <t xml:space="preserve">6.89803123474121</t>
@@ -227,43 +227,43 @@
     <t xml:space="preserve">6.90410852432251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96488428115845</t>
+    <t xml:space="preserve">6.96488475799561</t>
   </si>
   <si>
     <t xml:space="preserve">6.79471397399902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76432514190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1411337852478</t>
+    <t xml:space="preserve">6.76432418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14113235473633</t>
   </si>
   <si>
     <t xml:space="preserve">7.02565956115723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.157386302948</t>
+    <t xml:space="preserve">7.15738677978516</t>
   </si>
   <si>
     <t xml:space="preserve">7.13741254806519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31052160263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25725698471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34381246566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38376092910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29720497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25060033798218</t>
+    <t xml:space="preserve">7.31052112579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25725650787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34381151199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38375997543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29720544815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2505989074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.21730804443359</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">7.23062467575073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23728227615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27723121643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2239670753479</t>
+    <t xml:space="preserve">7.23728370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27723264694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22396755218506</t>
   </si>
   <si>
     <t xml:space="preserve">7.10412311553955</t>
@@ -287,37 +287,37 @@
     <t xml:space="preserve">6.85777521133423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65803384780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60476922988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.474937915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50822782516479</t>
+    <t xml:space="preserve">6.65803337097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60477018356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47493839263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50822877883911</t>
   </si>
   <si>
     <t xml:space="preserve">6.95764493942261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93767118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82448482513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88440704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47826671600342</t>
+    <t xml:space="preserve">6.93767166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82448577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88440752029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47826766967773</t>
   </si>
   <si>
     <t xml:space="preserve">6.32180309295654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56149196624756</t>
+    <t xml:space="preserve">6.56149244308472</t>
   </si>
   <si>
     <t xml:space="preserve">6.69132471084595</t>
@@ -326,28 +326,28 @@
     <t xml:space="preserve">6.81782674789429</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91769695281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03754138946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78453540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50490045547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61808586120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71795558929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68466567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73792934417725</t>
+    <t xml:space="preserve">6.9176983833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03754281997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78453636169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50489950180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6180853843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71795654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68466520309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73793029785156</t>
   </si>
   <si>
     <t xml:space="preserve">6.87774991989136</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">6.81116819381714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75124645233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79119443893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76456117630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8644323348999</t>
+    <t xml:space="preserve">6.75124740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79119539260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76456260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86443328857422</t>
   </si>
   <si>
     <t xml:space="preserve">6.77122020721436</t>
@@ -374,151 +374,151 @@
     <t xml:space="preserve">6.89106559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73127174377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64471769332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63806009292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75790452957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83114385604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80451011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101406097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96430397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74458837509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7112979888916</t>
+    <t xml:space="preserve">6.73127317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64471817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63806104660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75790500640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83114290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80451059341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101358413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9643030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74458789825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71129846572876</t>
   </si>
   <si>
     <t xml:space="preserve">6.65137624740601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62807369232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64138889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62141513824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01756811141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98427724838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01091051101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04420042037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17070293426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87109136581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92435550689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97761869430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83780193328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84445810317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79785299301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77787828445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59811162948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55150508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72461366653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67135000228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66469144821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60809898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54484701156616</t>
+    <t xml:space="preserve">6.6280722618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64138984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62141370773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01756763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98427772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01090955734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04419898986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17070198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87109041213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92435503005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97761964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83780145645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84445905685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79785346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77787923812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59811210632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55150651931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7246150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67135143280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66469287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60809993743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54484796524048</t>
   </si>
   <si>
     <t xml:space="preserve">6.45829343795776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65470457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67800712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46495056152344</t>
+    <t xml:space="preserve">6.65470552444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67800807952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46495151519775</t>
   </si>
   <si>
     <t xml:space="preserve">6.13870763778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.228590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19197225570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17865562438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24856472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13537836074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06546878814697</t>
+    <t xml:space="preserve">6.22859048843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19197273254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17865514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24856615066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13537788391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06546974182129</t>
   </si>
   <si>
     <t xml:space="preserve">6.16866874694824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15868186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1420373916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0621395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03883647918701</t>
+    <t xml:space="preserve">6.15868091583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14203691482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06213998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03883695602417</t>
   </si>
   <si>
     <t xml:space="preserve">6.10874652862549</t>
@@ -530,118 +530,118 @@
     <t xml:space="preserve">6.02219200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01886320114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11873292922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23192024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12206220626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22193336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21860361099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35842275619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37839698791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62474346160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70463943481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85111665725708</t>
+    <t xml:space="preserve">6.01886415481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11873245239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23191976547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12206268310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22193288803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21860456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35842227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37839603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6247444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70464086532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85111713409424</t>
   </si>
   <si>
     <t xml:space="preserve">6.69798278808594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90438079833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89772272109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99093580245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07748985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91103935241699</t>
+    <t xml:space="preserve">6.90438175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89772319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9909348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07749080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91104030609131</t>
   </si>
   <si>
     <t xml:space="preserve">7.0708327293396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13075494766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15072917938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18401956558228</t>
+    <t xml:space="preserve">7.13075399398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15072774887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18402004241943</t>
   </si>
   <si>
     <t xml:space="preserve">7.09746408462524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085849761963</t>
+    <t xml:space="preserve">7.05085754394531</t>
   </si>
   <si>
     <t xml:space="preserve">7.3504695892334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27057313919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28388977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30386352539062</t>
+    <t xml:space="preserve">7.27057361602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28389024734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30386257171631</t>
   </si>
   <si>
     <t xml:space="preserve">7.53023719787598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32383823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31717967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36378622055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51692008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59015893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347461700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992607116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77658462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7366361618042</t>
+    <t xml:space="preserve">7.32383728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31717920303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36378717422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51692056655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59015941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347509384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71000337600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992559432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77658319473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73663568496704</t>
   </si>
   <si>
     <t xml:space="preserve">7.78990030288696</t>
@@ -650,16 +650,16 @@
     <t xml:space="preserve">7.75660943984985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82319021224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85648107528687</t>
+    <t xml:space="preserve">7.82318925857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85648059844971</t>
   </si>
   <si>
     <t xml:space="preserve">7.86979675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87645435333252</t>
+    <t xml:space="preserve">7.87645530700684</t>
   </si>
   <si>
     <t xml:space="preserve">7.90308666229248</t>
@@ -668,52 +668,52 @@
     <t xml:space="preserve">7.96966648101807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94969320297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96300888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311338424683</t>
+    <t xml:space="preserve">7.94969177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92306041717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96300983428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311195373535</t>
   </si>
   <si>
     <t xml:space="preserve">7.72331857681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62344980239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54355335235596</t>
+    <t xml:space="preserve">7.62344884872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54355192184448</t>
   </si>
   <si>
     <t xml:space="preserve">7.47031450271606</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63676452636719</t>
+    <t xml:space="preserve">7.6367654800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.56352663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57018518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74329376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8032169342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89642906188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94303607940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84982252120972</t>
+    <t xml:space="preserve">7.57018375396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74329423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80321645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89642810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94303512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84982204437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.06953716278076</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">8.20842742919922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25009441375732</t>
+    <t xml:space="preserve">8.25009632110596</t>
   </si>
   <si>
     <t xml:space="preserve">8.22926235198975</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">8.31954002380371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35426330566406</t>
+    <t xml:space="preserve">8.35426235198975</t>
   </si>
   <si>
     <t xml:space="preserve">8.28481864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29870700836182</t>
+    <t xml:space="preserve">8.2987060546875</t>
   </si>
   <si>
     <t xml:space="preserve">8.37509727478027</t>
@@ -746,31 +746,31 @@
     <t xml:space="preserve">8.34731864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38898372650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43759632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4514856338501</t>
+    <t xml:space="preserve">8.3889856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43759727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45148658752441</t>
   </si>
   <si>
     <t xml:space="preserve">8.68760108947754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73621082305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62510013580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63898849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66676712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68065547943115</t>
+    <t xml:space="preserve">8.7362117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62509918212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63898754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66676616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68065452575684</t>
   </si>
   <si>
     <t xml:space="preserve">8.59732151031494</t>
@@ -779,85 +779,85 @@
     <t xml:space="preserve">8.72926712036133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69454479217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61120986938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50704288482666</t>
+    <t xml:space="preserve">8.69454383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61120891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50704193115234</t>
   </si>
   <si>
     <t xml:space="preserve">8.59037685394287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52787590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54870986938477</t>
+    <t xml:space="preserve">8.52787494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54871082305908</t>
   </si>
   <si>
     <t xml:space="preserve">8.4931526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5139856338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46537590026855</t>
+    <t xml:space="preserve">8.51398754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46537399291992</t>
   </si>
   <si>
     <t xml:space="preserve">8.47231960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61815547943115</t>
+    <t xml:space="preserve">8.61815643310547</t>
   </si>
   <si>
     <t xml:space="preserve">8.65982246398926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40981864929199</t>
+    <t xml:space="preserve">8.6459321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40981960296631</t>
   </si>
   <si>
     <t xml:space="preserve">8.4306526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42370891571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30565071105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5417652130127</t>
+    <t xml:space="preserve">8.42370796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30565166473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54176425933838</t>
   </si>
   <si>
     <t xml:space="preserve">8.57648754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60426712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88204574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00010299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15288352966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13205051422119</t>
+    <t xml:space="preserve">8.6042652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71537780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88204669952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00010395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15288257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13204956054688</t>
   </si>
   <si>
     <t xml:space="preserve">9.06954860687256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09038352966309</t>
+    <t xml:space="preserve">9.09038257598877</t>
   </si>
   <si>
     <t xml:space="preserve">9.00704860687256</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">8.95843601226807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06260395050049</t>
+    <t xml:space="preserve">9.0626049041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.1251049041748</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">9.20843887329102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24316310882568</t>
+    <t xml:space="preserve">9.24316215515137</t>
   </si>
   <si>
     <t xml:space="preserve">9.29871845245361</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">9.36816310882568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40983009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41677474975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32649612426758</t>
+    <t xml:space="preserve">9.40983104705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41677570343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32649517059326</t>
   </si>
   <si>
     <t xml:space="preserve">9.29177379608154</t>
@@ -902,49 +902,49 @@
     <t xml:space="preserve">9.45149707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47233009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43760967254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44455242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4028844833374</t>
+    <t xml:space="preserve">9.47233200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43760776519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44455337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40288734436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.38899707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38205242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3403844833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34732913970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48621940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7501106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79177856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7778902053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80566787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72927856445312</t>
+    <t xml:space="preserve">9.38205337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34038639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34733104705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31955242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48622035980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75011253356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79177951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77788925170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80566883087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72927761077881</t>
   </si>
   <si>
     <t xml:space="preserve">9.77094554901123</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">9.74316692352295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96539306640625</t>
+    <t xml:space="preserve">9.96539211273193</t>
   </si>
   <si>
     <t xml:space="preserve">10.0278930664062</t>
@@ -965,34 +965,34 @@
     <t xml:space="preserve">9.93761348724365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834503173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1181716918945</t>
+    <t xml:space="preserve">10.0834493637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1181707382202</t>
   </si>
   <si>
     <t xml:space="preserve">10.1876163482666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4445657730103</t>
+    <t xml:space="preserve">10.4445648193359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5001211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5695676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.229284286499</t>
+    <t xml:space="preserve">10.5695667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2292852401733</t>
   </si>
   <si>
     <t xml:space="preserve">10.3959531784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.423731803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5904006958008</t>
+    <t xml:space="preserve">10.4237308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5903987884521</t>
   </si>
   <si>
     <t xml:space="preserve">10.4931764602661</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">10.6251230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6042890548706</t>
+    <t xml:space="preserve">10.6042900085449</t>
   </si>
   <si>
     <t xml:space="preserve">10.7015113830566</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">10.7779026031494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8542909622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.833459854126</t>
+    <t xml:space="preserve">10.8542919158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8334579467773</t>
   </si>
   <si>
     <t xml:space="preserve">10.9029026031494</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0904054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1042938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1112394332886</t>
+    <t xml:space="preserve">11.090404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1042947769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1112375259399</t>
   </si>
   <si>
     <t xml:space="preserve">10.6667900085449</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">10.9723482131958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9445705413818</t>
+    <t xml:space="preserve">10.9445695877075</t>
   </si>
   <si>
     <t xml:space="preserve">11.0765171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3473529815674</t>
+    <t xml:space="preserve">11.3473520278931</t>
   </si>
   <si>
     <t xml:space="preserve">11.3959636688232</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">11.0626277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2154064178467</t>
+    <t xml:space="preserve">11.2154054641724</t>
   </si>
   <si>
     <t xml:space="preserve">11.3126306533813</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">10.9098472595215</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7362365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8751258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6945676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5487337112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7848463058472</t>
+    <t xml:space="preserve">10.736234664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8751249313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6945667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5487327575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7848472595215</t>
   </si>
   <si>
     <t xml:space="preserve">10.8612365722656</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">11.0695724487305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1876287460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.930682182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1598510742188</t>
+    <t xml:space="preserve">11.1876306533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9306812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1598501205444</t>
   </si>
   <si>
     <t xml:space="preserve">11.4515199661255</t>
@@ -1106,13 +1106,13 @@
     <t xml:space="preserve">11.5001316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4931859970093</t>
+    <t xml:space="preserve">11.4931879043579</t>
   </si>
   <si>
     <t xml:space="preserve">11.6251335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7223567962646</t>
+    <t xml:space="preserve">11.7223558425903</t>
   </si>
   <si>
     <t xml:space="preserve">11.7709703445435</t>
@@ -1124,13 +1124,13 @@
     <t xml:space="preserve">11.7293014526367</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7154121398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6112442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4862442016602</t>
+    <t xml:space="preserve">11.7154130935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6112451553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4862432479858</t>
   </si>
   <si>
     <t xml:space="preserve">11.5765228271484</t>
@@ -1139,37 +1139,37 @@
     <t xml:space="preserve">11.6806898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820753097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8681802749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8959579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9862365722656</t>
+    <t xml:space="preserve">11.3820743560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8681793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.895959854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9862375259399</t>
   </si>
   <si>
     <t xml:space="preserve">11.0834608078003</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292957305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848520278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3265190124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.243185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.597357749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7501363754272</t>
+    <t xml:space="preserve">11.2292947769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3265199661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2431859970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5973558425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7501354217529</t>
   </si>
   <si>
     <t xml:space="preserve">11.6181879043579</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">11.6320772171021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334693908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1251392364502</t>
+    <t xml:space="preserve">11.8334703445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1251373291016</t>
   </si>
   <si>
     <t xml:space="preserve">11.9168033599854</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">12.6668109893799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.152928352356</t>
+    <t xml:space="preserve">13.1529293060303</t>
   </si>
   <si>
     <t xml:space="preserve">13.382098197937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3195962905884</t>
+    <t xml:space="preserve">13.319598197937</t>
   </si>
   <si>
     <t xml:space="preserve">13.3682088851929</t>
@@ -1208,70 +1208,70 @@
     <t xml:space="preserve">13.5765438079834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5209875106812</t>
+    <t xml:space="preserve">13.5209884643555</t>
   </si>
   <si>
     <t xml:space="preserve">13.2362623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1668157577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0487613677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4237651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0070953369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.354320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4584865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918243408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6807126998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9168262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9307126998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.187650680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2987632751465</t>
+    <t xml:space="preserve">13.1668167114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0487623214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4237670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070943832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3543214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4584875106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154359817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6807117462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9168281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9307155609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1876516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2987623214722</t>
   </si>
   <si>
     <t xml:space="preserve">13.3751535415649</t>
   </si>
   <si>
-    <t xml:space="preserve">13.416820526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4723777770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4862642288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6112680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7362689971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223796844482</t>
+    <t xml:space="preserve">13.4168214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.472375869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4862670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6112661361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7362680435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223815917969</t>
   </si>
   <si>
     <t xml:space="preserve">13.8196029663086</t>
@@ -1280,28 +1280,28 @@
     <t xml:space="preserve">13.889048576355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8543262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9029369354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.08349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7987699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0279378890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057203292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1945943832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1112594604492</t>
+    <t xml:space="preserve">13.8543272018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9029378890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0834970474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.798770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0279397964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.305721282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1112623214722</t>
   </si>
   <si>
     <t xml:space="preserve">13.1807060241699</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">14.0200986862183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1486530303955</t>
+    <t xml:space="preserve">14.1486549377441</t>
   </si>
   <si>
     <t xml:space="preserve">13.8083591461182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6571168899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5361251831055</t>
+    <t xml:space="preserve">13.6571187973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5361261367798</t>
   </si>
   <si>
     <t xml:space="preserve">13.2563285827637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1277723312378</t>
+    <t xml:space="preserve">13.1277732849121</t>
   </si>
   <si>
     <t xml:space="preserve">13.3092622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.460503578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4983148574829</t>
+    <t xml:space="preserve">13.4605054855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4983158111572</t>
   </si>
   <si>
     <t xml:space="preserve">13.4680662155151</t>
@@ -1343,16 +1343,16 @@
     <t xml:space="preserve">13.573935508728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7327404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7478637695312</t>
+    <t xml:space="preserve">13.7327394485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7478628158569</t>
   </si>
   <si>
     <t xml:space="preserve">13.4075698852539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4889469146729</t>
+    <t xml:space="preserve">14.4889450073242</t>
   </si>
   <si>
     <t xml:space="preserve">14.4738235473633</t>
@@ -1364,31 +1364,31 @@
     <t xml:space="preserve">14.7158088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3755168914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6175012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7233724594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9351091384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7460565567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292407989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167119979858</t>
+    <t xml:space="preserve">14.3755149841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6175022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.723370552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9351119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7460594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292417526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167139053345</t>
   </si>
   <si>
     <t xml:space="preserve">14.2998952865601</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2091484069824</t>
+    <t xml:space="preserve">14.2091522216797</t>
   </si>
   <si>
     <t xml:space="preserve">14.0654716491699</t>
@@ -1403,37 +1403,37 @@
     <t xml:space="preserve">14.1713390350342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2847719192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6250638961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536201477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.677996635437</t>
+    <t xml:space="preserve">14.2847709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6250648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536191940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.67799949646</t>
   </si>
   <si>
     <t xml:space="preserve">14.791431427002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8443651199341</t>
+    <t xml:space="preserve">14.8443660736084</t>
   </si>
   <si>
     <t xml:space="preserve">14.8746128082275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8368034362793</t>
+    <t xml:space="preserve">14.8368043899536</t>
   </si>
   <si>
     <t xml:space="preserve">14.7611827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6553134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5494422912598</t>
+    <t xml:space="preserve">14.655312538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5494441986084</t>
   </si>
   <si>
     <t xml:space="preserve">14.6099414825439</t>
@@ -1442,52 +1442,52 @@
     <t xml:space="preserve">14.6401891708374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5721311569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5191965103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2393989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0049734115601</t>
+    <t xml:space="preserve">14.5721302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5191955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2393999099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0049753189087</t>
   </si>
   <si>
     <t xml:space="preserve">13.9217901229858</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9142284393311</t>
+    <t xml:space="preserve">13.9142293930054</t>
   </si>
   <si>
     <t xml:space="preserve">14.2696466445923</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3982009887695</t>
+    <t xml:space="preserve">14.3982038497925</t>
   </si>
   <si>
     <t xml:space="preserve">13.9898490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6646814346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6722421646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5814952850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.770546913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6268720626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5209999084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495552062988</t>
+    <t xml:space="preserve">13.664680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6722440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5814981460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705488204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6268701553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5210008621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495561599731</t>
   </si>
   <si>
     <t xml:space="preserve">13.551248550415</t>
@@ -1496,52 +1496,52 @@
     <t xml:space="preserve">13.4907531738281</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4756298065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5058765411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.347071647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3924446105957</t>
+    <t xml:space="preserve">13.4756269454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.505877494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3470726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3924436569214</t>
   </si>
   <si>
     <t xml:space="preserve">13.4831895828247</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8310480117798</t>
+    <t xml:space="preserve">13.8310470581055</t>
   </si>
   <si>
     <t xml:space="preserve">13.6344318389893</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5663728713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5436878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3773212432861</t>
+    <t xml:space="preserve">13.5663738250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5436868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3773221969604</t>
   </si>
   <si>
     <t xml:space="preserve">13.1958322525024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2714529037476</t>
+    <t xml:space="preserve">13.2714519500732</t>
   </si>
   <si>
     <t xml:space="preserve">13.3395118713379</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3546342849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2638893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4529428482056</t>
+    <t xml:space="preserve">13.3546352386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2638902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4529438018799</t>
   </si>
   <si>
     <t xml:space="preserve">13.3319473266602</t>
@@ -1550,49 +1550,49 @@
     <t xml:space="preserve">12.9311590194702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0219039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8101634979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5530557632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7421073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6513605117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848848342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1202116012573</t>
+    <t xml:space="preserve">13.0219030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8101654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5530548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7421064376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6513614654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.120210647583</t>
   </si>
   <si>
     <t xml:space="preserve">12.9614057540894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5681781768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4396228790283</t>
+    <t xml:space="preserve">12.5681791305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.439624786377</t>
   </si>
   <si>
     <t xml:space="preserve">12.6211137771606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4018125534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4925575256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4698724746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1371393203735</t>
+    <t xml:space="preserve">12.4018135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4925584793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4698715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1371402740479</t>
   </si>
   <si>
     <t xml:space="preserve">12.2883815765381</t>
@@ -1604,40 +1604,40 @@
     <t xml:space="preserve">12.6286754608154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6437997817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.825288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7723541259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8479747772217</t>
+    <t xml:space="preserve">12.643798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252897262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7723560333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.847975730896</t>
   </si>
   <si>
     <t xml:space="preserve">12.7572317123413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8177289962769</t>
+    <t xml:space="preserve">12.8177280426025</t>
   </si>
   <si>
     <t xml:space="preserve">12.7799158096313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4471845626831</t>
+    <t xml:space="preserve">12.4471855163574</t>
   </si>
   <si>
     <t xml:space="preserve">12.4244995117188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2581329345703</t>
+    <t xml:space="preserve">12.2581338882446</t>
   </si>
   <si>
     <t xml:space="preserve">12.1673879623413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4169368743896</t>
+    <t xml:space="preserve">12.416937828064</t>
   </si>
   <si>
     <t xml:space="preserve">12.1447019577026</t>
@@ -1652,34 +1652,34 @@
     <t xml:space="preserve">12.1068925857544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2278852462769</t>
+    <t xml:space="preserve">12.2278861999512</t>
   </si>
   <si>
     <t xml:space="preserve">12.0463953018188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0993299484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7968473434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8800296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5379304885864</t>
+    <t xml:space="preserve">12.099328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7968454360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8800287246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5379285812378</t>
   </si>
   <si>
     <t xml:space="preserve">12.2656946182251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7950420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2941398620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1126470565796</t>
+    <t xml:space="preserve">12.7950410842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2941389083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1126480102539</t>
   </si>
   <si>
     <t xml:space="preserve">12.9538440704346</t>
@@ -1688,16 +1688,16 @@
     <t xml:space="preserve">12.5833015441895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4774351119995</t>
+    <t xml:space="preserve">12.4774341583252</t>
   </si>
   <si>
     <t xml:space="preserve">12.5757398605347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8555374145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0143404006958</t>
+    <t xml:space="preserve">12.8555383682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0143413543701</t>
   </si>
   <si>
     <t xml:space="preserve">12.8328523635864</t>
@@ -1709,25 +1709,25 @@
     <t xml:space="preserve">13.052152633667</t>
   </si>
   <si>
-    <t xml:space="preserve">12.916033744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0975246429443</t>
+    <t xml:space="preserve">12.9160346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.09752368927</t>
   </si>
   <si>
     <t xml:space="preserve">13.0067806243896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2260818481445</t>
+    <t xml:space="preserve">13.2260799407959</t>
   </si>
   <si>
     <t xml:space="preserve">13.2185163497925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9009094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0370283126831</t>
+    <t xml:space="preserve">12.9009103775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0370292663574</t>
   </si>
   <si>
     <t xml:space="preserve">12.7647914886475</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">13.029465675354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2109546661377</t>
+    <t xml:space="preserve">13.2109537124634</t>
   </si>
   <si>
     <t xml:space="preserve">13.233642578125</t>
@@ -1754,37 +1754,37 @@
     <t xml:space="preserve">13.1882705688477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1353349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9689683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1050863265991</t>
+    <t xml:space="preserve">13.1353340148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9689693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1050853729248</t>
   </si>
   <si>
     <t xml:space="preserve">13.3016996383667</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8857879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6891736984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6967344284058</t>
+    <t xml:space="preserve">12.8857870101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.689172744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6967334747314</t>
   </si>
   <si>
     <t xml:space="preserve">12.6362371444702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6664848327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5152435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3110685348511</t>
+    <t xml:space="preserve">12.666485786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5152425765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3110666275024</t>
   </si>
   <si>
     <t xml:space="preserve">12.2430095672607</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">12.0388326644897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6589241027832</t>
+    <t xml:space="preserve">12.6589231491089</t>
   </si>
   <si>
     <t xml:space="preserve">12.7269821166992</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">12.7496700286865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3186302185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1900758743286</t>
+    <t xml:space="preserve">12.3186311721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1900749206543</t>
   </si>
   <si>
     <t xml:space="preserve">12.1976366043091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1749505996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2732572555542</t>
+    <t xml:space="preserve">12.1749515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2732563018799</t>
   </si>
   <si>
     <t xml:space="preserve">12.1598262786865</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">12.2808198928833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.303505897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8631000518799</t>
+    <t xml:space="preserve">12.3035068511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8631010055542</t>
   </si>
   <si>
     <t xml:space="preserve">13.2902870178223</t>
@@ -1841,19 +1841,19 @@
     <t xml:space="preserve">13.5988121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6146326065063</t>
+    <t xml:space="preserve">13.6146335601807</t>
   </si>
   <si>
     <t xml:space="preserve">13.9548025131226</t>
   </si>
   <si>
-    <t xml:space="preserve">13.978533744812</t>
+    <t xml:space="preserve">13.9785356521606</t>
   </si>
   <si>
     <t xml:space="preserve">13.8598718643188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.749119758606</t>
+    <t xml:space="preserve">13.7491188049316</t>
   </si>
   <si>
     <t xml:space="preserve">13.7332973480225</t>
@@ -1865,64 +1865,64 @@
     <t xml:space="preserve">13.8124046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7174739837646</t>
+    <t xml:space="preserve">13.717474937439</t>
   </si>
   <si>
     <t xml:space="preserve">13.6383676528931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6620988845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5750780105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1446619033813</t>
+    <t xml:space="preserve">13.6620998382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5750789642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1446628570557</t>
   </si>
   <si>
     <t xml:space="preserve">14.2395944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5085649490356</t>
+    <t xml:space="preserve">14.5085639953613</t>
   </si>
   <si>
     <t xml:space="preserve">14.4690103530884</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5955829620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7221574783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6746921539307</t>
+    <t xml:space="preserve">14.5955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7221593856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6746912002563</t>
   </si>
   <si>
     <t xml:space="preserve">14.176305770874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1604852676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0813751220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0339107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373655319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6984233856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6114053726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4136343002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6272277832031</t>
+    <t xml:space="preserve">14.1604862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0813770294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0339097976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373664855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6984252929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6114044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4136323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6272268295288</t>
   </si>
   <si>
     <t xml:space="preserve">15.1097917556763</t>
@@ -1931,34 +1931,34 @@
     <t xml:space="preserve">15.0939683914185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9911289215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9436635971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9120187759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8724641799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8645524978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6430511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2870578765869</t>
+    <t xml:space="preserve">14.9911279678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9436626434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9120178222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8724660873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8645553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6430492401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2870597839355</t>
   </si>
   <si>
     <t xml:space="preserve">14.3266143798828</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2158613204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2475032806396</t>
+    <t xml:space="preserve">14.2158603668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.247504234314</t>
   </si>
   <si>
     <t xml:space="preserve">14.0260000228882</t>
@@ -1970,22 +1970,22 @@
     <t xml:space="preserve">13.6067237854004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8677835464478</t>
+    <t xml:space="preserve">13.8677825927734</t>
   </si>
   <si>
     <t xml:space="preserve">14.2000398635864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2949714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2079486846924</t>
+    <t xml:space="preserve">14.2949705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.207950592041</t>
   </si>
   <si>
     <t xml:space="preserve">13.6304559707642</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5671682357788</t>
+    <t xml:space="preserve">13.5671691894531</t>
   </si>
   <si>
     <t xml:space="preserve">13.6700105667114</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">13.3693952560425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8203163146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.907338142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8440494537354</t>
+    <t xml:space="preserve">13.8203153610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9073371887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8440504074097</t>
   </si>
   <si>
     <t xml:space="preserve">13.5592565536499</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">13.7965850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1209306716919</t>
+    <t xml:space="preserve">14.1209316253662</t>
   </si>
   <si>
     <t xml:space="preserve">13.9310693740845</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">14.0892868041992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3028812408447</t>
+    <t xml:space="preserve">14.302882194519</t>
   </si>
   <si>
     <t xml:space="preserve">14.4848308563232</t>
@@ -2033,40 +2033,40 @@
     <t xml:space="preserve">14.6588697433472</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2633256912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2316818237305</t>
+    <t xml:space="preserve">14.2633266448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2316846847534</t>
   </si>
   <si>
     <t xml:space="preserve">14.1130199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5876731872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9753065109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8566436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9990377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8329086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7458906173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0227689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.737979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854461669922</t>
+    <t xml:space="preserve">14.5876722335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.975305557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8566427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9990358352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8329105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.745888710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227708816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7379779815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854452133179</t>
   </si>
   <si>
     <t xml:space="preserve">14.6905145645142</t>
@@ -2084,55 +2084,55 @@
     <t xml:space="preserve">14.5164747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4294557571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1921272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0971984863281</t>
+    <t xml:space="preserve">14.4294538497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1921291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0971965789795</t>
   </si>
   <si>
     <t xml:space="preserve">14.2712373733521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2791471481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057197570801</t>
+    <t xml:space="preserve">14.2791481018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057216644287</t>
   </si>
   <si>
     <t xml:space="preserve">14.3899021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3424348831177</t>
+    <t xml:space="preserve">14.3424339294434</t>
   </si>
   <si>
     <t xml:space="preserve">14.3582563400269</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4610986709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0069494247437</t>
+    <t xml:space="preserve">14.4610996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0069484710693</t>
   </si>
   <si>
     <t xml:space="preserve">14.9515733718872</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5322971343994</t>
+    <t xml:space="preserve">14.5322961807251</t>
   </si>
   <si>
     <t xml:space="preserve">14.3345241546631</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3740797042847</t>
+    <t xml:space="preserve">14.374077796936</t>
   </si>
   <si>
     <t xml:space="preserve">14.3819894790649</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6509590148926</t>
+    <t xml:space="preserve">14.6509609222412</t>
   </si>
   <si>
     <t xml:space="preserve">15.0860576629639</t>
@@ -2141,37 +2141,37 @@
     <t xml:space="preserve">14.8170881271362</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6193151473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0544157028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4895143508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8692350387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7189302444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3075647354126</t>
+    <t xml:space="preserve">14.6193170547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0544176101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4895124435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.869236946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7189311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3075637817383</t>
   </si>
   <si>
     <t xml:space="preserve">15.3471183776855</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6081762313843</t>
+    <t xml:space="preserve">15.6081781387329</t>
   </si>
   <si>
     <t xml:space="preserve">15.2284545898438</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1572561264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1889009475708</t>
+    <t xml:space="preserve">15.1572542190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1888999938965</t>
   </si>
   <si>
     <t xml:space="preserve">15.1414356231689</t>
@@ -2189,10 +2189,10 @@
     <t xml:space="preserve">15.7505731582642</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7110195159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6160869598389</t>
+    <t xml:space="preserve">15.7110185623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6160888671875</t>
   </si>
   <si>
     <t xml:space="preserve">15.4420490264893</t>
@@ -2207,22 +2207,22 @@
     <t xml:space="preserve">15.1651678085327</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4024953842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6239986419678</t>
+    <t xml:space="preserve">15.4024925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6240005493164</t>
   </si>
   <si>
     <t xml:space="preserve">15.7743072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2173175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5179290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2964248657227</t>
+    <t xml:space="preserve">16.2173137664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5179271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.296422958374</t>
   </si>
   <si>
     <t xml:space="preserve">16.5653953552246</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">16.9292945861816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0875129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558700561523</t>
+    <t xml:space="preserve">17.0875148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558681488037</t>
   </si>
   <si>
     <t xml:space="preserve">16.9609394073486</t>
@@ -2249,28 +2249,28 @@
     <t xml:space="preserve">16.8976516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">17.198263168335</t>
+    <t xml:space="preserve">17.1982650756836</t>
   </si>
   <si>
     <t xml:space="preserve">16.8818302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2299098968506</t>
+    <t xml:space="preserve">17.229907989502</t>
   </si>
   <si>
     <t xml:space="preserve">17.3564834594727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4514141082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6096286773682</t>
+    <t xml:space="preserve">17.4514102935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6096305847168</t>
   </si>
   <si>
     <t xml:space="preserve">17.4039459228516</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4355907440186</t>
+    <t xml:space="preserve">17.4355926513672</t>
   </si>
   <si>
     <t xml:space="preserve">17.5305213928223</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">18.1792144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1317481994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2583255767822</t>
+    <t xml:space="preserve">18.1317501068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2583236694336</t>
   </si>
   <si>
     <t xml:space="preserve">18.3690757751465</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">18.2899684906006</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2108612060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3723030090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4830589294434</t>
+    <t xml:space="preserve">18.2108592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3723011016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4830570220947</t>
   </si>
   <si>
     <t xml:space="preserve">17.7045593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3248405456543</t>
+    <t xml:space="preserve">17.3248386383057</t>
   </si>
   <si>
     <t xml:space="preserve">16.5021076202393</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">17.4988803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1508026123047</t>
+    <t xml:space="preserve">17.1507987976074</t>
   </si>
   <si>
     <t xml:space="preserve">11.1701698303223</t>
@@ -2327,10 +2327,10 @@
     <t xml:space="preserve">11.8267726898193</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6210889816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6290006637573</t>
+    <t xml:space="preserve">11.6210899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6290016174316</t>
   </si>
   <si>
     <t xml:space="preserve">11.3600311279297</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">11.4470510482788</t>
   </si>
   <si>
-    <t xml:space="preserve">12.02454662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0641002655029</t>
+    <t xml:space="preserve">12.0245456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0640993118286</t>
   </si>
   <si>
     <t xml:space="preserve">12.4200897216797</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">12.1748523712158</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9026536941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6969699859619</t>
+    <t xml:space="preserve">12.9026546478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6969709396362</t>
   </si>
   <si>
     <t xml:space="preserve">13.2190895080566</t>
@@ -2369,43 +2369,43 @@
     <t xml:space="preserve">13.3140201568604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2349100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241598129272</t>
+    <t xml:space="preserve">13.2349109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241579055786</t>
   </si>
   <si>
     <t xml:space="preserve">13.4089517593384</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4564161300659</t>
+    <t xml:space="preserve">13.4564170837402</t>
   </si>
   <si>
     <t xml:space="preserve">13.1004257202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0925149917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.250732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687828063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3614854812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4326839447021</t>
+    <t xml:space="preserve">13.0925140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2507333755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3614864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4326829910278</t>
   </si>
   <si>
     <t xml:space="preserve">13.5038814544678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9738521575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9342966079712</t>
+    <t xml:space="preserve">12.9738531112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9342975616455</t>
   </si>
   <si>
     <t xml:space="preserve">13.0371379852295</t>
@@ -2414,91 +2414,91 @@
     <t xml:space="preserve">13.1795358657837</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2111797332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.543436050415</t>
+    <t xml:space="preserve">13.2111787796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5434370040894</t>
   </si>
   <si>
     <t xml:space="preserve">13.6225442886353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7095642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2056884765625</t>
+    <t xml:space="preserve">13.7095632553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2056894302368</t>
   </si>
   <si>
     <t xml:space="preserve">13.8418645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1560773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966470718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2883768081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0491018295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2475500106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2971611022949</t>
+    <t xml:space="preserve">14.156078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2883758544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0490999221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2475490570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2971620559692</t>
   </si>
   <si>
     <t xml:space="preserve">16.1240348815918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4134426116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5043964385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1405735015869</t>
+    <t xml:space="preserve">16.4134407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5043983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1405754089355</t>
   </si>
   <si>
     <t xml:space="preserve">16.0909595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">16.190185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5865678787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286884307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3467741012573</t>
+    <t xml:space="preserve">16.1901836395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5865669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286874771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3467721939087</t>
   </si>
   <si>
     <t xml:space="preserve">15.2144746780396</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2806234359741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8346300125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6527185440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5782995223999</t>
+    <t xml:space="preserve">15.2806253433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8346290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.652717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692533493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5782985687256</t>
   </si>
   <si>
     <t xml:space="preserve">15.7932863235474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8594379425049</t>
+    <t xml:space="preserve">15.8594350814819</t>
   </si>
   <si>
     <t xml:space="preserve">15.3633108139038</t>
@@ -2507,16 +2507,16 @@
     <t xml:space="preserve">15.429461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5617599487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8677034378052</t>
+    <t xml:space="preserve">15.5617609024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8677043914795</t>
   </si>
   <si>
     <t xml:space="preserve">16.330753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0501365661621</t>
+    <t xml:space="preserve">17.0501346588135</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651214599609</t>
@@ -2525,37 +2525,37 @@
     <t xml:space="preserve">16.868221282959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9509105682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1162853240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3312683105469</t>
+    <t xml:space="preserve">16.9509086608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.116283416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3312702178955</t>
   </si>
   <si>
     <t xml:space="preserve">17.51318359375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7777824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2981967926025</t>
+    <t xml:space="preserve">17.7777843475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2981948852539</t>
   </si>
   <si>
     <t xml:space="preserve">17.2816581726074</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3147354125977</t>
+    <t xml:space="preserve">17.314733505249</t>
   </si>
   <si>
     <t xml:space="preserve">17.4304962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3643455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3808841705322</t>
+    <t xml:space="preserve">17.3643474578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3808822631836</t>
   </si>
   <si>
     <t xml:space="preserve">16.9839839935303</t>
@@ -2573,25 +2573,25 @@
     <t xml:space="preserve">16.7524604797363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0170574188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4635715484619</t>
+    <t xml:space="preserve">17.0170593261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4635696411133</t>
   </si>
   <si>
     <t xml:space="preserve">17.5958709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">17.480110168457</t>
+    <t xml:space="preserve">17.4801082611084</t>
   </si>
   <si>
     <t xml:space="preserve">17.8439331054688</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9266223907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.992769241333</t>
+    <t xml:space="preserve">17.9266204833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9927711486816</t>
   </si>
   <si>
     <t xml:space="preserve">18.0919933319092</t>
@@ -2600,43 +2600,43 @@
     <t xml:space="preserve">18.4227447509766</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4723567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1581439971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.025842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.07546043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5054302215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.389669418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2739086151123</t>
+    <t xml:space="preserve">18.4723587036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1581420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0258445739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0754585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5054321289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3896713256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2739067077637</t>
   </si>
   <si>
     <t xml:space="preserve">18.3235187530518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3400573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.191219329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0589179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.910083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2408313751221</t>
+    <t xml:space="preserve">18.3400554656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1912174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0589218139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9100818634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2408294677734</t>
   </si>
   <si>
     <t xml:space="preserve">18.3069801330566</t>
@@ -2651,28 +2651,28 @@
     <t xml:space="preserve">17.7116317749023</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5793323516846</t>
+    <t xml:space="preserve">17.5793342590332</t>
   </si>
   <si>
     <t xml:space="preserve">17.347806930542</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4966449737549</t>
+    <t xml:space="preserve">17.4966430664062</t>
   </si>
   <si>
     <t xml:space="preserve">17.3974208831787</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7447090148926</t>
+    <t xml:space="preserve">17.7447071075439</t>
   </si>
   <si>
     <t xml:space="preserve">18.6046562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7700328826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3731307983398</t>
+    <t xml:space="preserve">18.7700309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3731327056885</t>
   </si>
   <si>
     <t xml:space="preserve">18.6542701721191</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">18.7534923553467</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4062061309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1416072845459</t>
+    <t xml:space="preserve">18.4062080383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1416091918945</t>
   </si>
   <si>
     <t xml:space="preserve">17.9431571960449</t>
@@ -2696,22 +2696,22 @@
     <t xml:space="preserve">17.7281703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9596939086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1989707946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.636697769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2894096374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9503927230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0413494110107</t>
+    <t xml:space="preserve">17.9596977233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1989727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6366958618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2894115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9503936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0413475036621</t>
   </si>
   <si>
     <t xml:space="preserve">16.5374717712402</t>
@@ -2732,37 +2732,37 @@
     <t xml:space="preserve">17.1658973693848</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0005226135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178314208984</t>
+    <t xml:space="preserve">17.0005207061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178333282471</t>
   </si>
   <si>
     <t xml:space="preserve">16.7028465270996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8847579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7855358123779</t>
+    <t xml:space="preserve">16.8847599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7855339050293</t>
   </si>
   <si>
     <t xml:space="preserve">16.6201591491699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4795913696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.033597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1328220367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1824340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.546257019043</t>
+    <t xml:space="preserve">16.4795894622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0335960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1328201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1824359893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5462589263916</t>
   </si>
   <si>
     <t xml:space="preserve">18.1746826171875</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">20.6883792877197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7049140930176</t>
+    <t xml:space="preserve">20.7049160003662</t>
   </si>
   <si>
     <t xml:space="preserve">20.6718406677246</t>
@@ -2801,10 +2801,10 @@
     <t xml:space="preserve">20.7545280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9364395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7214508056641</t>
+    <t xml:space="preserve">20.9364414215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7214527130127</t>
   </si>
   <si>
     <t xml:space="preserve">21.0025901794434</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">21.6806259155273</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1767501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.994836807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5571117401123</t>
+    <t xml:space="preserve">22.1767520904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9948387145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5571136474609</t>
   </si>
   <si>
     <t xml:space="preserve">21.2175769805908</t>
@@ -2834,34 +2834,34 @@
     <t xml:space="preserve">20.9529781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3002643585205</t>
+    <t xml:space="preserve">21.3002662658691</t>
   </si>
   <si>
     <t xml:space="preserve">21.5979385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4160251617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8956108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5152492523193</t>
+    <t xml:space="preserve">21.4160270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8956127166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.515251159668</t>
   </si>
   <si>
     <t xml:space="preserve">21.8460006713867</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1602115631104</t>
+    <t xml:space="preserve">22.160213470459</t>
   </si>
   <si>
     <t xml:space="preserve">21.5317897796631</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3664131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7379913330078</t>
+    <t xml:space="preserve">21.3664150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7379894256592</t>
   </si>
   <si>
     <t xml:space="preserve">20.5726146697998</t>
@@ -2870,40 +2870,40 @@
     <t xml:space="preserve">21.2506523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7876014709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2584056854248</t>
+    <t xml:space="preserve">20.7876033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2584037780762</t>
   </si>
   <si>
     <t xml:space="preserve">19.6134414672852</t>
   </si>
   <si>
-    <t xml:space="preserve">20.192253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3323040008545</t>
+    <t xml:space="preserve">20.1922550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3323059082031</t>
   </si>
   <si>
     <t xml:space="preserve">18.9354038238525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.274938583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2010383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9860515594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4656391143799</t>
+    <t xml:space="preserve">20.2749404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2010364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9860496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4656372070312</t>
   </si>
   <si>
     <t xml:space="preserve">20.0103416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465148925781</t>
+    <t xml:space="preserve">19.6465167999268</t>
   </si>
   <si>
     <t xml:space="preserve">20.2253265380859</t>
@@ -2918,16 +2918,16 @@
     <t xml:space="preserve">20.638765335083</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0356636047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3498764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0852756500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0191287994385</t>
+    <t xml:space="preserve">21.035665512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.34987449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.085277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0191268920898</t>
   </si>
   <si>
     <t xml:space="preserve">20.8702907562256</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">21.1018142700195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8868274688721</t>
+    <t xml:space="preserve">20.8868293762207</t>
   </si>
   <si>
     <t xml:space="preserve">20.5230045318604</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">20.6056900024414</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0268783569336</t>
+    <t xml:space="preserve">20.0268802642822</t>
   </si>
   <si>
     <t xml:space="preserve">20.1095676422119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1514263153076</t>
+    <t xml:space="preserve">21.1514282226562</t>
   </si>
   <si>
     <t xml:space="preserve">20.6222286224365</t>
@@ -2963,10 +2963,10 @@
     <t xml:space="preserve">20.4072399139404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9772663116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3907032012939</t>
+    <t xml:space="preserve">19.9772644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3907012939453</t>
   </si>
   <si>
     <t xml:space="preserve">20.1261024475098</t>
@@ -2978,31 +2978,31 @@
     <t xml:space="preserve">20.2914791107178</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2661533355713</t>
+    <t xml:space="preserve">19.2661552429199</t>
   </si>
   <si>
     <t xml:space="preserve">19.762279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.878044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3484573364258</t>
+    <t xml:space="preserve">19.8780422210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3484592437744</t>
   </si>
   <si>
     <t xml:space="preserve">21.3314075469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0756320953369</t>
+    <t xml:space="preserve">21.0756340026855</t>
   </si>
   <si>
     <t xml:space="preserve">21.2461490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2290992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1779441833496</t>
+    <t xml:space="preserve">21.229097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1779460906982</t>
   </si>
   <si>
     <t xml:space="preserve">21.4337158203125</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">21.6212825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3143558502197</t>
+    <t xml:space="preserve">21.3143539428711</t>
   </si>
   <si>
     <t xml:space="preserve">21.570125579834</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">21.9793643951416</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0646171569824</t>
+    <t xml:space="preserve">22.0646190643311</t>
   </si>
   <si>
     <t xml:space="preserve">22.030517578125</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">21.6553840637207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7406425476074</t>
+    <t xml:space="preserve">21.7406406402588</t>
   </si>
   <si>
     <t xml:space="preserve">21.3655090332031</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">21.7917957305908</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9964122772217</t>
+    <t xml:space="preserve">21.9964141845703</t>
   </si>
   <si>
     <t xml:space="preserve">21.3825607299805</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">20.8369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8710174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8880672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7065372467041</t>
+    <t xml:space="preserve">20.8710155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.888069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7065391540527</t>
   </si>
   <si>
     <t xml:space="preserve">21.9623126983643</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">22.1328258514404</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2351360321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4738578796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2692394256592</t>
+    <t xml:space="preserve">22.2351341247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.47385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2692375183105</t>
   </si>
   <si>
     <t xml:space="preserve">20.7346057891846</t>
@@ -3098,40 +3098,40 @@
     <t xml:space="preserve">20.5470390319824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2632007598877</t>
+    <t xml:space="preserve">21.2632026672363</t>
   </si>
   <si>
     <t xml:space="preserve">21.1097373962402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1608905792236</t>
+    <t xml:space="preserve">21.1608924865723</t>
   </si>
   <si>
     <t xml:space="preserve">21.5530776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7747478485107</t>
+    <t xml:space="preserve">21.7747459411621</t>
   </si>
   <si>
     <t xml:space="preserve">21.2973022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0926856994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8539638519287</t>
+    <t xml:space="preserve">21.0926876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8539619445801</t>
   </si>
   <si>
     <t xml:space="preserve">21.0074291229248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.280252456665</t>
+    <t xml:space="preserve">21.2802505493164</t>
   </si>
   <si>
     <t xml:space="preserve">21.9282093048096</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8600025177002</t>
+    <t xml:space="preserve">21.8600006103516</t>
   </si>
   <si>
     <t xml:space="preserve">21.8088474273682</t>
@@ -3143,28 +3143,28 @@
     <t xml:space="preserve">21.7576942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3996143341064</t>
+    <t xml:space="preserve">21.3996124267578</t>
   </si>
   <si>
     <t xml:space="preserve">21.9111576080322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5079574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1669311523438</t>
+    <t xml:space="preserve">22.5079593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1669292449951</t>
   </si>
   <si>
     <t xml:space="preserve">22.0816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">22.013463973999</t>
+    <t xml:space="preserve">22.0134658813477</t>
   </si>
   <si>
     <t xml:space="preserve">22.4909076690674</t>
   </si>
   <si>
-    <t xml:space="preserve">22.422700881958</t>
+    <t xml:space="preserve">22.4227027893066</t>
   </si>
   <si>
     <t xml:space="preserve">22.2521858215332</t>
@@ -3173,16 +3173,16 @@
     <t xml:space="preserve">22.5761642456055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6614246368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7296276092529</t>
+    <t xml:space="preserve">22.6614227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7296257019043</t>
   </si>
   <si>
     <t xml:space="preserve">23.172966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7697696685791</t>
+    <t xml:space="preserve">23.7697677612305</t>
   </si>
   <si>
     <t xml:space="preserve">23.4628429412842</t>
@@ -3200,25 +3200,25 @@
     <t xml:space="preserve">25.4749164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8329963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7818431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1740303039551</t>
+    <t xml:space="preserve">25.8329982757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7818450927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1740283966064</t>
   </si>
   <si>
     <t xml:space="preserve">26.3274898529053</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6003170013428</t>
+    <t xml:space="preserve">26.6003150939941</t>
   </si>
   <si>
     <t xml:space="preserve">26.6173667907715</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7708301544189</t>
+    <t xml:space="preserve">26.7708282470703</t>
   </si>
   <si>
     <t xml:space="preserve">26.6855716705322</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">25.969409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7196769714355</t>
+    <t xml:space="preserve">26.7196750640869</t>
   </si>
   <si>
     <t xml:space="preserve">26.3615951538086</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3104400634766</t>
+    <t xml:space="preserve">26.3104419708252</t>
   </si>
   <si>
     <t xml:space="preserve">26.5491600036621</t>
@@ -3242,16 +3242,16 @@
     <t xml:space="preserve">26.2251834869385</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5431251525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0315780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.826961517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0145282745361</t>
+    <t xml:space="preserve">25.5431232452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0315799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8269596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0145263671875</t>
   </si>
   <si>
     <t xml:space="preserve">25.1679916381836</t>
@@ -3260,13 +3260,13 @@
     <t xml:space="preserve">25.1168346405029</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8099117279053</t>
+    <t xml:space="preserve">24.8099098205566</t>
   </si>
   <si>
     <t xml:space="preserve">24.8440113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1338863372803</t>
+    <t xml:space="preserve">25.1338882446289</t>
   </si>
   <si>
     <t xml:space="preserve">24.7246513366699</t>
@@ -3275,16 +3275,16 @@
     <t xml:space="preserve">24.7587566375732</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3896579742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3836231231689</t>
+    <t xml:space="preserve">25.3896598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3836212158203</t>
   </si>
   <si>
     <t xml:space="preserve">24.1790046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3324661254883</t>
+    <t xml:space="preserve">24.3324680328369</t>
   </si>
   <si>
     <t xml:space="preserve">24.6223430633545</t>
@@ -3296,13 +3296,13 @@
     <t xml:space="preserve">24.3495178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9402847290039</t>
+    <t xml:space="preserve">23.9402828216553</t>
   </si>
   <si>
     <t xml:space="preserve">24.1449012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1107997894287</t>
+    <t xml:space="preserve">24.1107978820801</t>
   </si>
   <si>
     <t xml:space="preserve">23.8038711547852</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">24.417724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4518299102783</t>
+    <t xml:space="preserve">24.4518280029297</t>
   </si>
   <si>
     <t xml:space="preserve">24.2131080627441</t>
@@ -3326,10 +3326,10 @@
     <t xml:space="preserve">24.2813129425049</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0486278533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.434778213501</t>
+    <t xml:space="preserve">25.0486297607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4347763061523</t>
   </si>
   <si>
     <t xml:space="preserve">23.5481014251709</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">22.9342460632324</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7978324890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6443710327148</t>
+    <t xml:space="preserve">22.7978343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6443691253662</t>
   </si>
   <si>
     <t xml:space="preserve">22.3033409118652</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">21.4678173065186</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0244789123535</t>
+    <t xml:space="preserve">21.0244770050049</t>
   </si>
   <si>
     <t xml:space="preserve">20.5640907287598</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">20.9221725463867</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5129375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2912654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1378040313721</t>
+    <t xml:space="preserve">20.5129356384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2912673950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1378021240234</t>
   </si>
   <si>
     <t xml:space="preserve">22.6273193359375</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">24.0937480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.616304397583</t>
+    <t xml:space="preserve">23.6163063049316</t>
   </si>
   <si>
     <t xml:space="preserve">22.7637329101562</t>
@@ -3416,31 +3416,31 @@
     <t xml:space="preserve">22.6102676391602</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1619510650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5601749420166</t>
+    <t xml:space="preserve">24.1619529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.560173034668</t>
   </si>
   <si>
     <t xml:space="preserve">24.9292697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8951663970947</t>
+    <t xml:space="preserve">24.8951683044434</t>
   </si>
   <si>
     <t xml:space="preserve">24.3154163360596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2873516082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7136383056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6564483642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1850452423096</t>
+    <t xml:space="preserve">25.2873497009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7136363983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6564464569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1850414276123</t>
   </si>
   <si>
     <t xml:space="preserve">24.9804248809814</t>
@@ -3449,22 +3449,22 @@
     <t xml:space="preserve">25.662483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3786449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2933883666992</t>
+    <t xml:space="preserve">26.3786468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2933902740479</t>
   </si>
   <si>
     <t xml:space="preserve">26.8049335479736</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7537784576416</t>
+    <t xml:space="preserve">26.7537803649902</t>
   </si>
   <si>
     <t xml:space="preserve">26.9413452148438</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0436515808105</t>
+    <t xml:space="preserve">27.0436534881592</t>
   </si>
   <si>
     <t xml:space="preserve">27.0948085784912</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">26.9924983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1459636688232</t>
+    <t xml:space="preserve">27.1459617614746</t>
   </si>
   <si>
     <t xml:space="preserve">27.7086620330811</t>
@@ -3500,43 +3500,43 @@
     <t xml:space="preserve">28.0496921539307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5893020629883</t>
+    <t xml:space="preserve">27.5893001556396</t>
   </si>
   <si>
     <t xml:space="preserve">27.1800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2823734283447</t>
+    <t xml:space="preserve">27.2823753356934</t>
   </si>
   <si>
     <t xml:space="preserve">26.856086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6514682769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3555583953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3214530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9864616394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3385047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8901920318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7598171234131</t>
+    <t xml:space="preserve">26.6514701843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3555564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3214550018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9864597320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3385066986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8901901245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7598152160645</t>
   </si>
   <si>
     <t xml:space="preserve">28.4759788513184</t>
   </si>
   <si>
-    <t xml:space="preserve">28.510082244873</t>
+    <t xml:space="preserve">28.5100803375244</t>
   </si>
   <si>
     <t xml:space="preserve">28.6976490020752</t>
@@ -3548,10 +3548,10 @@
     <t xml:space="preserve">29.4604301452637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4954624176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0559463500977</t>
+    <t xml:space="preserve">29.4954605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.055944442749</t>
   </si>
   <si>
     <t xml:space="preserve">29.5655193328857</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">28.3044338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9524955749512</t>
+    <t xml:space="preserve">28.9524936676025</t>
   </si>
   <si>
     <t xml:space="preserve">28.8824329376221</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">29.0575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1451587677002</t>
+    <t xml:space="preserve">29.1451568603516</t>
   </si>
   <si>
     <t xml:space="preserve">27.043342590332</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">25.9924392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9574069976807</t>
+    <t xml:space="preserve">25.957405090332</t>
   </si>
   <si>
     <t xml:space="preserve">25.607105255127</t>
@@ -3614,13 +3614,13 @@
     <t xml:space="preserve">26.255163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6054668426514</t>
+    <t xml:space="preserve">26.6054649353027</t>
   </si>
   <si>
     <t xml:space="preserve">25.8873462677002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4653434753418</t>
+    <t xml:space="preserve">26.4653453826904</t>
   </si>
   <si>
     <t xml:space="preserve">26.3252239227295</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">26.9382553100586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9732856750488</t>
+    <t xml:space="preserve">26.9732837677002</t>
   </si>
   <si>
     <t xml:space="preserve">27.1309204101562</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">27.4286785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3411026000977</t>
+    <t xml:space="preserve">27.341100692749</t>
   </si>
   <si>
     <t xml:space="preserve">26.7455902099609</t>
@@ -3668,22 +3668,22 @@
     <t xml:space="preserve">26.6930408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5879535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1834659576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8840713500977</t>
+    <t xml:space="preserve">26.5879516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1834678649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512828826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.884069442749</t>
   </si>
   <si>
     <t xml:space="preserve">28.1467971801758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4445533752441</t>
+    <t xml:space="preserve">28.4445552825928</t>
   </si>
   <si>
     <t xml:space="preserve">28.8999481201172</t>
@@ -3704,16 +3704,16 @@
     <t xml:space="preserve">29.2327365875244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1260051727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3186721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8632774353027</t>
+    <t xml:space="preserve">30.4062480926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1260070800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3186702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8632755279541</t>
   </si>
   <si>
     <t xml:space="preserve">29.950855255127</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">30.4412784576416</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1593990325928</t>
+    <t xml:space="preserve">31.15940284729</t>
   </si>
   <si>
     <t xml:space="preserve">30.3361873626709</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">29.7406730651855</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7089214324951</t>
+    <t xml:space="preserve">27.7089195251465</t>
   </si>
   <si>
     <t xml:space="preserve">27.4987373352051</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">27.8490409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">28.269401550293</t>
+    <t xml:space="preserve">28.2694034576416</t>
   </si>
   <si>
     <t xml:space="preserve">28.1643142700195</t>
@@ -3770,13 +3770,13 @@
     <t xml:space="preserve">29.0926151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7598266601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1801891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8665561676025</t>
+    <t xml:space="preserve">28.7598285675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1801910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8665542602539</t>
   </si>
   <si>
     <t xml:space="preserve">25.169225692749</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">25.064136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5912303924561</t>
+    <t xml:space="preserve">24.5912284851074</t>
   </si>
   <si>
     <t xml:space="preserve">24.7488651275635</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">24.9415302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4335899353027</t>
+    <t xml:space="preserve">24.4335918426514</t>
   </si>
   <si>
     <t xml:space="preserve">24.1708660125732</t>
@@ -3818,10 +3818,10 @@
     <t xml:space="preserve">24.9065017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5545597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7472248077393</t>
+    <t xml:space="preserve">25.5545616149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7472267150879</t>
   </si>
   <si>
     <t xml:space="preserve">25.6946811676025</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">26.7806186676025</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6738891601562</t>
+    <t xml:space="preserve">27.6738910675049</t>
   </si>
   <si>
     <t xml:space="preserve">27.7964954376221</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">26.7631034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9032249450684</t>
+    <t xml:space="preserve">26.9032230377197</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274677276611</t>
@@ -3869,13 +3869,13 @@
     <t xml:space="preserve">26.3952865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8331623077393</t>
+    <t xml:space="preserve">26.8331642150879</t>
   </si>
   <si>
     <t xml:space="preserve">26.307710647583</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9223766326904</t>
+    <t xml:space="preserve">25.9223785400391</t>
   </si>
   <si>
     <t xml:space="preserve">26.3777713775635</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">26.5003757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1325588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.097526550293</t>
+    <t xml:space="preserve">26.1325569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0975284576416</t>
   </si>
   <si>
     <t xml:space="preserve">26.5354061126709</t>
@@ -3899,16 +3899,16 @@
     <t xml:space="preserve">26.2376499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.764741897583</t>
+    <t xml:space="preserve">25.7647399902344</t>
   </si>
   <si>
     <t xml:space="preserve">25.8348026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2201366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4144401550293</t>
+    <t xml:space="preserve">26.2201347351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4144382476807</t>
   </si>
   <si>
     <t xml:space="preserve">25.466983795166</t>
@@ -3920,10 +3920,10 @@
     <t xml:space="preserve">25.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5895900726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8714714050293</t>
+    <t xml:space="preserve">25.5895881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8714694976807</t>
   </si>
   <si>
     <t xml:space="preserve">24.4686241149902</t>
@@ -3932,52 +3932,52 @@
     <t xml:space="preserve">24.5737133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1183204650879</t>
+    <t xml:space="preserve">24.1183223724365</t>
   </si>
   <si>
     <t xml:space="preserve">24.2409267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3285026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7838954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8539543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3109855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2234115600586</t>
+    <t xml:space="preserve">24.3285007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7838935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8539562225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3109874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.22340965271</t>
   </si>
   <si>
     <t xml:space="preserve">24.3460159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4160785675049</t>
+    <t xml:space="preserve">24.4160766601562</t>
   </si>
   <si>
     <t xml:space="preserve">24.3985633850098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.678804397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9590473175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0466213226318</t>
+    <t xml:space="preserve">24.6788024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9590454101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0466194152832</t>
   </si>
   <si>
     <t xml:space="preserve">24.7138328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5036525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6612873077393</t>
+    <t xml:space="preserve">24.5036506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6612892150879</t>
   </si>
   <si>
     <t xml:space="preserve">24.2759552001953</t>
@@ -4004,10 +4004,10 @@
     <t xml:space="preserve">23.8731079101562</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3476524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7154712677002</t>
+    <t xml:space="preserve">23.3476543426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7154731750488</t>
   </si>
   <si>
     <t xml:space="preserve">23.7680168151855</t>
@@ -4022,13 +4022,13 @@
     <t xml:space="preserve">23.049898147583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8747482299805</t>
+    <t xml:space="preserve">22.8747463226318</t>
   </si>
   <si>
     <t xml:space="preserve">23.1900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2425651550293</t>
+    <t xml:space="preserve">23.2425632476807</t>
   </si>
   <si>
     <t xml:space="preserve">23.6979560852051</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">23.9256534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7505016326904</t>
+    <t xml:space="preserve">23.7505035400391</t>
   </si>
   <si>
     <t xml:space="preserve">23.435230255127</t>
@@ -4055,10 +4055,10 @@
     <t xml:space="preserve">23.5228061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9606857299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4861354827881</t>
+    <t xml:space="preserve">23.9606838226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4861373901367</t>
   </si>
   <si>
     <t xml:space="preserve">24.2584400177002</t>
@@ -4070,10 +4070,10 @@
     <t xml:space="preserve">25.2217712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2042579650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1341991424561</t>
+    <t xml:space="preserve">25.2042598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1341972351074</t>
   </si>
   <si>
     <t xml:space="preserve">24.6262588500977</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">24.3635330200195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7855339050293</t>
+    <t xml:space="preserve">23.7855319976807</t>
   </si>
   <si>
     <t xml:space="preserve">23.2250499725342</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">23.2775955200195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2951107025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0657730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7663803100586</t>
+    <t xml:space="preserve">23.295108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0657749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.76637840271</t>
   </si>
   <si>
     <t xml:space="preserve">24.7313499450684</t>
@@ -4118,10 +4118,10 @@
     <t xml:space="preserve">23.6418628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4965972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334362030029</t>
+    <t xml:space="preserve">23.4965953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334342956543</t>
   </si>
   <si>
     <t xml:space="preserve">23.5329132080078</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">24.2955551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5679244995117</t>
+    <t xml:space="preserve">24.5679264068604</t>
   </si>
   <si>
     <t xml:space="preserve">24.4771347045898</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">24.5134525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3318691253662</t>
+    <t xml:space="preserve">24.3318710327148</t>
   </si>
   <si>
     <t xml:space="preserve">23.9868659973145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5510730743408</t>
+    <t xml:space="preserve">23.5510711669922</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058074951172</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">23.4602813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8234443664551</t>
+    <t xml:space="preserve">23.8234424591064</t>
   </si>
   <si>
     <t xml:space="preserve">23.6237049102783</t>
@@ -4193,13 +4193,13 @@
     <t xml:space="preserve">24.8221397399902</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0413417816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.386344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1321315765381</t>
+    <t xml:space="preserve">24.0413398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3863468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1321296691895</t>
   </si>
   <si>
     <t xml:space="preserve">24.4589786529541</t>
@@ -4208,19 +4208,19 @@
     <t xml:space="preserve">24.6768760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6042423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.549768447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7858219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2397747039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8039798736572</t>
+    <t xml:space="preserve">24.6042442321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5497703552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7858238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2397766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8039817810059</t>
   </si>
   <si>
     <t xml:space="preserve">24.9674053192139</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">22.2618465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2981605529785</t>
+    <t xml:space="preserve">22.2981624603271</t>
   </si>
   <si>
     <t xml:space="preserve">22.388952255249</t>
@@ -4268,25 +4268,25 @@
     <t xml:space="preserve">22.2073707580566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.062105178833</t>
+    <t xml:space="preserve">22.0621070861816</t>
   </si>
   <si>
     <t xml:space="preserve">21.6807861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6263103485107</t>
+    <t xml:space="preserve">21.6263122558594</t>
   </si>
   <si>
     <t xml:space="preserve">22.6431674957275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6794834136963</t>
+    <t xml:space="preserve">22.6794815063477</t>
   </si>
   <si>
     <t xml:space="preserve">22.5886917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1515941619873</t>
+    <t xml:space="preserve">23.1515922546387</t>
   </si>
   <si>
     <t xml:space="preserve">22.9700107574463</t>
@@ -4307,28 +4307,28 @@
     <t xml:space="preserve">23.024486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9155387878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8610649108887</t>
+    <t xml:space="preserve">22.9155368804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.86106300354</t>
   </si>
   <si>
     <t xml:space="preserve">23.2060661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">22.534215927124</t>
+    <t xml:space="preserve">22.5342178344727</t>
   </si>
   <si>
     <t xml:space="preserve">21.9349994659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8442077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2631492614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8999862670898</t>
+    <t xml:space="preserve">21.8442096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2631511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8999881744385</t>
   </si>
   <si>
     <t xml:space="preserve">20.482349395752</t>
@@ -4340,13 +4340,13 @@
     <t xml:space="preserve">20.7365646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1010303497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6833953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7378692626953</t>
+    <t xml:space="preserve">20.1010284423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6833934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7378673553467</t>
   </si>
   <si>
     <t xml:space="preserve">20.0102405548096</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">19.9376068115234</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3915596008301</t>
+    <t xml:space="preserve">20.3915576934814</t>
   </si>
   <si>
     <t xml:space="preserve">20.6094589233398</t>
@@ -4370,19 +4370,19 @@
     <t xml:space="preserve">20.6820907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1541996002197</t>
+    <t xml:space="preserve">21.1542015075684</t>
   </si>
   <si>
     <t xml:space="preserve">21.0997276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1723575592041</t>
+    <t xml:space="preserve">21.1723594665527</t>
   </si>
   <si>
     <t xml:space="preserve">21.0634117126465</t>
   </si>
   <si>
-    <t xml:space="preserve">20.809196472168</t>
+    <t xml:space="preserve">20.8091983795166</t>
   </si>
   <si>
     <t xml:space="preserve">21.0089359283447</t>
@@ -4394,16 +4394,16 @@
     <t xml:space="preserve">21.0270938873291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6081523895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.771577835083</t>
+    <t xml:space="preserve">21.608154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7715759277344</t>
   </si>
   <si>
     <t xml:space="preserve">21.4628887176514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9181461334229</t>
+    <t xml:space="preserve">20.9181480407715</t>
   </si>
   <si>
     <t xml:space="preserve">21.2449913024902</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">22.7884311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0971202850342</t>
+    <t xml:space="preserve">23.0971183776855</t>
   </si>
   <si>
     <t xml:space="preserve">23.2605419158936</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">23.1152763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3694915771484</t>
+    <t xml:space="preserve">23.3694896697998</t>
   </si>
   <si>
     <t xml:space="preserve">23.8960742950439</t>
@@ -4442,13 +4442,13 @@
     <t xml:space="preserve">24.3681869506836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.768970489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4408187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2216205596924</t>
+    <t xml:space="preserve">23.7689685821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4408206939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2216186523438</t>
   </si>
   <si>
     <t xml:space="preserve">25.493989944458</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">25.966100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9842586517334</t>
+    <t xml:space="preserve">25.984260559082</t>
   </si>
   <si>
     <t xml:space="preserve">26.0932083129883</t>
@@ -4475,31 +4475,31 @@
     <t xml:space="preserve">26.2021560668945</t>
   </si>
   <si>
-    <t xml:space="preserve">25.475830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8947715759277</t>
+    <t xml:space="preserve">25.4758319854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8947734832764</t>
   </si>
   <si>
     <t xml:space="preserve">25.0945110321045</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2942504882812</t>
+    <t xml:space="preserve">25.2942523956299</t>
   </si>
   <si>
     <t xml:space="preserve">24.9129314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7131900787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0763530731201</t>
+    <t xml:space="preserve">24.713191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0763549804688</t>
   </si>
   <si>
     <t xml:space="preserve">24.6405582427979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6587162017822</t>
+    <t xml:space="preserve">24.6587181091309</t>
   </si>
   <si>
     <t xml:space="preserve">24.3137130737305</t>
@@ -4547,7 +4547,7 @@
     <t xml:space="preserve">21.5718383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.444730758667</t>
+    <t xml:space="preserve">21.4447326660156</t>
   </si>
   <si>
     <t xml:space="preserve">21.1905174255371</t>
@@ -4562,7 +4562,7 @@
     <t xml:space="preserve">21.136043548584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9363021850586</t>
+    <t xml:space="preserve">20.9363040924072</t>
   </si>
   <si>
     <t xml:space="preserve">21.3176250457764</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">22.6976413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7871284484863</t>
+    <t xml:space="preserve">23.7871265411377</t>
   </si>
   <si>
     <t xml:space="preserve">24.0231819152832</t>
@@ -5456,7 +5456,7 @@
     <t xml:space="preserve">22.7999992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7600002288818</t>
+    <t xml:space="preserve">22.5599994659424</t>
   </si>
 </sst>
 </file>
@@ -70899,22 +70899,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6911458333</v>
+        <v>45967.6912847222</v>
       </c>
       <c r="B2505" t="n">
-        <v>294824</v>
+        <v>235782</v>
       </c>
       <c r="C2505" t="n">
-        <v>22.9400005340576</v>
+        <v>22.8400001525879</v>
       </c>
       <c r="D2505" t="n">
-        <v>22.6599998474121</v>
+        <v>22.5599994659424</v>
       </c>
       <c r="E2505" t="n">
-        <v>22.8999996185303</v>
+        <v>22.8400001525879</v>
       </c>
       <c r="F2505" t="n">
-        <v>22.7600002288818</v>
+        <v>22.5599994659424</v>
       </c>
       <c r="G2505" t="s">
         <v>1814</v>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="1815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="1814">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,112 +38,112 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48755407333374</t>
+    <t xml:space="preserve">7.4875545501709</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43893337249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23837471008301</t>
+    <t xml:space="preserve">7.43893384933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23837423324585</t>
   </si>
   <si>
     <t xml:space="preserve">7.04389238357544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99527168273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06212520599365</t>
+    <t xml:space="preserve">6.99527215957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06212568283081</t>
   </si>
   <si>
     <t xml:space="preserve">7.25052976608276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22014141082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17152166366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07428121566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84941053390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01350545883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75216913223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83725547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9709620475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09251260757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00742769241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00134944915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98919439315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92841958999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86156511306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5333776473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47867918014526</t>
+    <t xml:space="preserve">7.22014188766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17152214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07427978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84941101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01350498199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75217008590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83725595474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97096300125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09251403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00742673873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00134992599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98919534683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92841863632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86156606674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53337717056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47867965698242</t>
   </si>
   <si>
     <t xml:space="preserve">6.61238622665405</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55160999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77647972106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94057416915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87372159957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63061761856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78863573074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58199882507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70354890823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71570491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80686712265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91626310348511</t>
+    <t xml:space="preserve">6.55160903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77648019790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94057512283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8737211227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63061857223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78863430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58199787139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7035493850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7157039642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8068675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91626501083374</t>
   </si>
   <si>
     <t xml:space="preserve">6.84333276748657</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">6.83117771148682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87979984283447</t>
+    <t xml:space="preserve">6.87979793548584</t>
   </si>
   <si>
     <t xml:space="preserve">6.7096266746521</t>
@@ -164,28 +164,28 @@
     <t xml:space="preserve">6.85548734664917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8676438331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95272922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04996919631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27483940124512</t>
+    <t xml:space="preserve">6.86764335632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95272827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04997062683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27483987808228</t>
   </si>
   <si>
     <t xml:space="preserve">7.35992527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34777116775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26876258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22621965408325</t>
+    <t xml:space="preserve">7.34776973724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26876163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22622013092041</t>
   </si>
   <si>
     <t xml:space="preserve">7.11074590682983</t>
@@ -197,154 +197,154 @@
     <t xml:space="preserve">7.08035755157471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0560474395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975496292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23229646682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15328931808472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11682415008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16544389724731</t>
+    <t xml:space="preserve">7.05604696273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975305557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23229694366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15328979492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11682224273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16544342041016</t>
   </si>
   <si>
     <t xml:space="preserve">6.95880651473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93449687957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803123474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90410852432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96488475799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79471397399902</t>
+    <t xml:space="preserve">6.93449592590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803075790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90410804748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96488428115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79471302032471</t>
   </si>
   <si>
     <t xml:space="preserve">6.76432418823242</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14113235473633</t>
+    <t xml:space="preserve">7.14113283157349</t>
   </si>
   <si>
     <t xml:space="preserve">7.02565956115723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15738677978516</t>
+    <t xml:space="preserve">7.15738582611084</t>
   </si>
   <si>
     <t xml:space="preserve">7.13741254806519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31052112579346</t>
+    <t xml:space="preserve">7.3105206489563</t>
   </si>
   <si>
     <t xml:space="preserve">7.25725650787354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34381151199341</t>
+    <t xml:space="preserve">7.34381246566772</t>
   </si>
   <si>
     <t xml:space="preserve">7.38375997543335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29720544815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2505989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21730804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062467575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23728370666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27723264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22396755218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10412311553955</t>
+    <t xml:space="preserve">7.29720592498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25060033798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21730947494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23728227615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27723073959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22396802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10412263870239</t>
   </si>
   <si>
     <t xml:space="preserve">6.85777521133423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65803337097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60477018356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47493839263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50822877883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95764493942261</t>
+    <t xml:space="preserve">6.658034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60476970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47493743896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50822734832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95764541625977</t>
   </si>
   <si>
     <t xml:space="preserve">6.93767166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82448577880859</t>
+    <t xml:space="preserve">6.82448434829712</t>
   </si>
   <si>
     <t xml:space="preserve">6.88440752029419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47826766967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32180309295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56149244308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69132471084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81782674789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9176983833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03754281997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78453636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50489950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6180853843689</t>
+    <t xml:space="preserve">6.47826623916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3218035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56149291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69132375717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81782722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91769742965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03754186630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78453683853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5048999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61808586120605</t>
   </si>
   <si>
     <t xml:space="preserve">6.71795654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68466520309448</t>
+    <t xml:space="preserve">6.68466663360596</t>
   </si>
   <si>
     <t xml:space="preserve">6.73793029785156</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">6.87774991989136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81116819381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75124740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79119539260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76456260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86443328857422</t>
+    <t xml:space="preserve">6.81117010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75124645233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79119491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76456356048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86443376541138</t>
   </si>
   <si>
     <t xml:space="preserve">6.77122020721436</t>
@@ -374,82 +374,82 @@
     <t xml:space="preserve">6.89106559753418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73127317428589</t>
+    <t xml:space="preserve">6.73127269744873</t>
   </si>
   <si>
     <t xml:space="preserve">6.64471817016602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63806104660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75790500640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83114290237427</t>
+    <t xml:space="preserve">6.63806009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75790452957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83114337921143</t>
   </si>
   <si>
     <t xml:space="preserve">6.80451059341431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101358413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9643030166626</t>
+    <t xml:space="preserve">6.93101406097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96430397033691</t>
   </si>
   <si>
     <t xml:space="preserve">6.74458789825439</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71129846572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65137624740601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6280722618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64138984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62141370773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01756763458252</t>
+    <t xml:space="preserve">6.7112979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65137529373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62807273864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6413893699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62141513824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01756858825684</t>
   </si>
   <si>
     <t xml:space="preserve">6.98427772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01090955734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04419898986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17070198059082</t>
+    <t xml:space="preserve">7.010910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04420042037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17070341110229</t>
   </si>
   <si>
     <t xml:space="preserve">6.87109041213989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92435503005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97761964797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83780145645142</t>
+    <t xml:space="preserve">6.9243540763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97762012481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83780097961426</t>
   </si>
   <si>
     <t xml:space="preserve">6.84445905685425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79785346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77787923812866</t>
+    <t xml:space="preserve">6.79785251617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7778787612915</t>
   </si>
   <si>
     <t xml:space="preserve">6.59811210632324</t>
@@ -461,25 +461,25 @@
     <t xml:space="preserve">6.7246150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67135143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66469287872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60809993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54484796524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45829343795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65470552444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67800807952881</t>
+    <t xml:space="preserve">6.67135000228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66469240188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54484748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45829248428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65470457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67800855636597</t>
   </si>
   <si>
     <t xml:space="preserve">6.46495151519775</t>
@@ -491,28 +491,28 @@
     <t xml:space="preserve">6.22859048843384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19197273254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17865514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24856615066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13537788391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06546974182129</t>
+    <t xml:space="preserve">6.19197225570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17865467071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24856519699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13537836074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06546926498413</t>
   </si>
   <si>
     <t xml:space="preserve">6.16866874694824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15868091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14203691482544</t>
+    <t xml:space="preserve">6.15868186950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14203643798828</t>
   </si>
   <si>
     <t xml:space="preserve">6.06213998794556</t>
@@ -524,133 +524,133 @@
     <t xml:space="preserve">6.10874652862549</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0588116645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02219200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01886415481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11873245239258</t>
+    <t xml:space="preserve">6.05881261825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02219247817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01886224746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11873388290405</t>
   </si>
   <si>
     <t xml:space="preserve">6.23191976547241</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12206268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22193288803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21860456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35842227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37839603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6247444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70464086532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85111713409424</t>
+    <t xml:space="preserve">6.12206220626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22193336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21860504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35842180252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3783974647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62474393844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70464038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85111808776855</t>
   </si>
   <si>
     <t xml:space="preserve">6.69798278808594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90438175201416</t>
+    <t xml:space="preserve">6.90438079833984</t>
   </si>
   <si>
     <t xml:space="preserve">6.89772319793701</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9909348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07749080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91104030609131</t>
+    <t xml:space="preserve">6.99093675613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07749032974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91103982925415</t>
   </si>
   <si>
     <t xml:space="preserve">7.0708327293396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13075399398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15072774887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18402004241943</t>
+    <t xml:space="preserve">7.1307544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15072822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18401908874512</t>
   </si>
   <si>
     <t xml:space="preserve">7.09746408462524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3504695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27057361602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28389024734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30386257171631</t>
+    <t xml:space="preserve">7.05085897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35046911239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27057313919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28388977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30386304855347</t>
   </si>
   <si>
     <t xml:space="preserve">7.53023719787598</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32383728027344</t>
+    <t xml:space="preserve">7.3238377571106</t>
   </si>
   <si>
     <t xml:space="preserve">7.31717920303345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36378717422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51692056655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59015941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347509384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000337600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992559432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77658319473267</t>
+    <t xml:space="preserve">7.36378622055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51692199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59015893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347604751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7100043296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992607116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77658462524414</t>
   </si>
   <si>
     <t xml:space="preserve">7.73663568496704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78990030288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75660943984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82318925857544</t>
+    <t xml:space="preserve">7.78990077972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7566089630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82319068908691</t>
   </si>
   <si>
     <t xml:space="preserve">7.85648059844971</t>
@@ -659,79 +659,79 @@
     <t xml:space="preserve">7.86979675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87645530700684</t>
+    <t xml:space="preserve">7.87645387649536</t>
   </si>
   <si>
     <t xml:space="preserve">7.90308666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96966648101807</t>
+    <t xml:space="preserve">7.96966600418091</t>
   </si>
   <si>
     <t xml:space="preserve">7.94969177246094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92306041717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96300983428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72331857681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62344884872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54355192184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47031450271606</t>
+    <t xml:space="preserve">7.92306089401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96300840377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311243057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72332000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62344837188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54355239868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47031402587891</t>
   </si>
   <si>
     <t xml:space="preserve">7.6367654800415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56352663040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018375396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74329423904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80321645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89642810821533</t>
+    <t xml:space="preserve">7.56352519989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018613815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74329471588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80321741104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89642715454102</t>
   </si>
   <si>
     <t xml:space="preserve">7.94303512573242</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84982204437256</t>
+    <t xml:space="preserve">7.84982252120972</t>
   </si>
   <si>
     <t xml:space="preserve">8.06953716278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20842742919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25009632110596</t>
+    <t xml:space="preserve">8.2084264755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25009441375732</t>
   </si>
   <si>
     <t xml:space="preserve">8.22926235198975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31954002380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35426235198975</t>
+    <t xml:space="preserve">8.31953907012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35426330566406</t>
   </si>
   <si>
     <t xml:space="preserve">8.28481864929199</t>
@@ -740,28 +740,28 @@
     <t xml:space="preserve">8.2987060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37509727478027</t>
+    <t xml:space="preserve">8.37509536743164</t>
   </si>
   <si>
     <t xml:space="preserve">8.34731864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3889856338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43759727478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45148658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68760108947754</t>
+    <t xml:space="preserve">8.38898658752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43759536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45148468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68760013580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.7362117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62509918212891</t>
+    <t xml:space="preserve">8.62510013580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.63898754119873</t>
@@ -770,19 +770,19 @@
     <t xml:space="preserve">8.66676616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68065452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59732151031494</t>
+    <t xml:space="preserve">8.68065547943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59732246398926</t>
   </si>
   <si>
     <t xml:space="preserve">8.72926712036133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69454383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61120891571045</t>
+    <t xml:space="preserve">8.69454574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61120986938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.50704193115234</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">8.59037685394287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52787494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54871082305908</t>
+    <t xml:space="preserve">8.52787590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54870891571045</t>
   </si>
   <si>
     <t xml:space="preserve">8.4931526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51398754119873</t>
+    <t xml:space="preserve">8.51398658752441</t>
   </si>
   <si>
     <t xml:space="preserve">8.46537399291992</t>
@@ -809,37 +809,37 @@
     <t xml:space="preserve">8.47231960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61815643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65982246398926</t>
+    <t xml:space="preserve">8.61815547943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65982341766357</t>
   </si>
   <si>
     <t xml:space="preserve">8.6459321975708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40981960296631</t>
+    <t xml:space="preserve">8.40981769561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.4306526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42370796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30565166473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54176425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57648754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6042652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71537780761719</t>
+    <t xml:space="preserve">8.42370700836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30564975738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5417652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57648849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60426616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7153787612915</t>
   </si>
   <si>
     <t xml:space="preserve">8.88204669952393</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">9.00010395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15288257598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13204956054688</t>
+    <t xml:space="preserve">9.15288352966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13204860687256</t>
   </si>
   <si>
     <t xml:space="preserve">9.06954860687256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09038257598877</t>
+    <t xml:space="preserve">9.09038352966309</t>
   </si>
   <si>
     <t xml:space="preserve">9.00704860687256</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">8.95843601226807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0626049041748</t>
+    <t xml:space="preserve">9.06260395050049</t>
   </si>
   <si>
     <t xml:space="preserve">9.1251049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20843887329102</t>
+    <t xml:space="preserve">9.20843982696533</t>
   </si>
   <si>
     <t xml:space="preserve">9.24316215515137</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">9.29871845245361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36816310882568</t>
+    <t xml:space="preserve">9.36816215515137</t>
   </si>
   <si>
     <t xml:space="preserve">9.40983104705811</t>
@@ -890,88 +890,88 @@
     <t xml:space="preserve">9.41677570343018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32649517059326</t>
+    <t xml:space="preserve">9.32649707794189</t>
   </si>
   <si>
     <t xml:space="preserve">9.29177379608154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31260776519775</t>
+    <t xml:space="preserve">9.31260681152344</t>
   </si>
   <si>
     <t xml:space="preserve">9.45149707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47233200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43760776519775</t>
+    <t xml:space="preserve">9.47233104705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43760871887207</t>
   </si>
   <si>
     <t xml:space="preserve">9.44455337524414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40288734436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38899707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38205337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34038639068604</t>
+    <t xml:space="preserve">9.40288639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38899803161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38205242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3403844833374</t>
   </si>
   <si>
     <t xml:space="preserve">9.34733104705811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31955242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48622035980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75011253356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79177951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77788925170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80566883087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72927761077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77094554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76400184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74316692352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96539211273193</t>
+    <t xml:space="preserve">9.31955146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48621940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75011157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79177856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7778902053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80566787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72927951812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77094650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76399993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74316787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96539306640625</t>
   </si>
   <si>
     <t xml:space="preserve">10.0278930664062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93761348724365</t>
+    <t xml:space="preserve">9.93761444091797</t>
   </si>
   <si>
     <t xml:space="preserve">10.0834493637085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1181707382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1876163482666</t>
+    <t xml:space="preserve">10.1181716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1876173019409</t>
   </si>
   <si>
     <t xml:space="preserve">10.4445648193359</t>
@@ -983,28 +983,28 @@
     <t xml:space="preserve">10.5695667266846</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2292852401733</t>
+    <t xml:space="preserve">10.229284286499</t>
   </si>
   <si>
     <t xml:space="preserve">10.3959531784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4237308502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5903987884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4931764602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5626220703125</t>
+    <t xml:space="preserve">10.423731803894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5903997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4931755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5626211166382</t>
   </si>
   <si>
     <t xml:space="preserve">10.6251230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6042900085449</t>
+    <t xml:space="preserve">10.6042890548706</t>
   </si>
   <si>
     <t xml:space="preserve">10.7015113830566</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">10.7779026031494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8542919158936</t>
+    <t xml:space="preserve">10.8542928695679</t>
   </si>
   <si>
     <t xml:space="preserve">10.8334579467773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9029026031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090404510498</t>
+    <t xml:space="preserve">10.9029035568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0904054641724</t>
   </si>
   <si>
     <t xml:space="preserve">11.1042947769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1112375259399</t>
+    <t xml:space="preserve">11.1112384796143</t>
   </si>
   <si>
     <t xml:space="preserve">10.6667900085449</t>
@@ -1040,34 +1040,34 @@
     <t xml:space="preserve">10.9445695877075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0765171051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3473520278931</t>
+    <t xml:space="preserve">11.0765161514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3473529815674</t>
   </si>
   <si>
     <t xml:space="preserve">11.3959636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1529064178467</t>
+    <t xml:space="preserve">11.1529054641724</t>
   </si>
   <si>
     <t xml:space="preserve">11.0626277923584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2154054641724</t>
+    <t xml:space="preserve">11.2154064178467</t>
   </si>
   <si>
     <t xml:space="preserve">11.3126306533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2362403869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2084627151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9098472595215</t>
+    <t xml:space="preserve">11.2362413406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2084617614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9098482131958</t>
   </si>
   <si>
     <t xml:space="preserve">10.736234664917</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">10.8751249313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6945667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5487327575684</t>
+    <t xml:space="preserve">10.6945686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.548731803894</t>
   </si>
   <si>
     <t xml:space="preserve">10.7848472595215</t>
@@ -1088,52 +1088,52 @@
     <t xml:space="preserve">10.8612365722656</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0695724487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1876306533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9306812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1598501205444</t>
+    <t xml:space="preserve">11.0695714950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876287460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.930682182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1598510742188</t>
   </si>
   <si>
     <t xml:space="preserve">11.4515199661255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5001316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4931879043579</t>
+    <t xml:space="preserve">11.50013256073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4931859970093</t>
   </si>
   <si>
     <t xml:space="preserve">11.6251335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7223558425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709703445435</t>
+    <t xml:space="preserve">11.722354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.7015237808228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7293014526367</t>
+    <t xml:space="preserve">11.7293004989624</t>
   </si>
   <si>
     <t xml:space="preserve">11.7154130935669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6112451553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4862432479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5765228271484</t>
+    <t xml:space="preserve">11.6112432479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4862451553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5765218734741</t>
   </si>
   <si>
     <t xml:space="preserve">11.6806898117065</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">11.3820743560791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8681793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.895959854126</t>
+    <t xml:space="preserve">10.8681802749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8959589004517</t>
   </si>
   <si>
     <t xml:space="preserve">10.9862375259399</t>
@@ -1154,13 +1154,13 @@
     <t xml:space="preserve">11.0834608078003</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3265199661255</t>
+    <t xml:space="preserve">11.2292957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848520278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3265180587769</t>
   </si>
   <si>
     <t xml:space="preserve">11.2431859970093</t>
@@ -1169,43 +1169,43 @@
     <t xml:space="preserve">11.5973558425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7501354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6181879043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7987461090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6320772171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8334703445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1251373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9168033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6668109893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1529293060303</t>
+    <t xml:space="preserve">11.7501344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6181898117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7987451553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6320791244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8334693908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1251382827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.916802406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6668119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1529273986816</t>
   </si>
   <si>
     <t xml:space="preserve">13.382098197937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.319598197937</t>
+    <t xml:space="preserve">13.3195991516113</t>
   </si>
   <si>
     <t xml:space="preserve">13.3682088851929</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5765438079834</t>
+    <t xml:space="preserve">13.5765419006348</t>
   </si>
   <si>
     <t xml:space="preserve">13.5209884643555</t>
@@ -1214,31 +1214,31 @@
     <t xml:space="preserve">13.2362623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1668167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0487623214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4237670898438</t>
+    <t xml:space="preserve">13.1668157577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0487632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4237651824951</t>
   </si>
   <si>
     <t xml:space="preserve">13.0070943832397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3543214797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4584875106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154359817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6807117462158</t>
+    <t xml:space="preserve">13.3543195724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4584884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154340744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.791823387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6807126998901</t>
   </si>
   <si>
     <t xml:space="preserve">13.9168281555176</t>
@@ -1247,34 +1247,34 @@
     <t xml:space="preserve">13.9307155609131</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1876516342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2987623214722</t>
+    <t xml:space="preserve">13.1876525878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2987632751465</t>
   </si>
   <si>
     <t xml:space="preserve">13.3751535415649</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4168214797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.472375869751</t>
+    <t xml:space="preserve">13.416820526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4723768234253</t>
   </si>
   <si>
     <t xml:space="preserve">13.4862670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6112661361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7362680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223815917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8196029663086</t>
+    <t xml:space="preserve">13.6112689971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7362689971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223787307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.81960105896</t>
   </si>
   <si>
     <t xml:space="preserve">13.889048576355</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">13.8543272018433</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9029378890991</t>
+    <t xml:space="preserve">13.9029369354248</t>
   </si>
   <si>
     <t xml:space="preserve">14.0834970474243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.798770904541</t>
+    <t xml:space="preserve">13.7987718582153</t>
   </si>
   <si>
     <t xml:space="preserve">14.0279397964478</t>
@@ -1301,88 +1301,88 @@
     <t xml:space="preserve">13.1945972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1112623214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1807060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0200986862183</t>
+    <t xml:space="preserve">13.1112613677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1807079315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0200977325439</t>
   </si>
   <si>
     <t xml:space="preserve">14.1486549377441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8083591461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6571187973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5361261367798</t>
+    <t xml:space="preserve">13.8083600997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6571178436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5361270904541</t>
   </si>
   <si>
     <t xml:space="preserve">13.2563285827637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1277732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3092622756958</t>
+    <t xml:space="preserve">13.1277723312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3092632293701</t>
   </si>
   <si>
     <t xml:space="preserve">13.4605054855347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4983158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4680662155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.573935508728</t>
+    <t xml:space="preserve">13.4983148574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4680652618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5739374160767</t>
   </si>
   <si>
     <t xml:space="preserve">13.7327394485474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7478628158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4075698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4889450073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4738235473633</t>
+    <t xml:space="preserve">13.7478618621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4075689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4889478683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.473822593689</t>
   </si>
   <si>
     <t xml:space="preserve">14.6704378128052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755149841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6175022125244</t>
+    <t xml:space="preserve">14.7158079147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755178451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6175012588501</t>
   </si>
   <si>
     <t xml:space="preserve">14.723370552063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9351119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7460594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292417526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167139053345</t>
+    <t xml:space="preserve">14.9351091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7460584640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167129516602</t>
   </si>
   <si>
     <t xml:space="preserve">14.2998952865601</t>
@@ -1391,70 +1391,70 @@
     <t xml:space="preserve">14.2091522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0654716491699</t>
+    <t xml:space="preserve">14.0654706954956</t>
   </si>
   <si>
     <t xml:space="preserve">14.1637773513794</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0427846908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1713390350342</t>
+    <t xml:space="preserve">14.0427827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1713409423828</t>
   </si>
   <si>
     <t xml:space="preserve">14.2847709655762</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6250648498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536191940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.67799949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.791431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8443660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8746128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8368043899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7611827850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.655312538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5494441986084</t>
+    <t xml:space="preserve">14.6250638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6779975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.791428565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8443641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8746147155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.836802482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7611837387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6553115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5494451522827</t>
   </si>
   <si>
     <t xml:space="preserve">14.6099414825439</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6401891708374</t>
+    <t xml:space="preserve">14.6401882171631</t>
   </si>
   <si>
     <t xml:space="preserve">14.5721302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5191955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2393999099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0049753189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9217901229858</t>
+    <t xml:space="preserve">14.5191965103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2393989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0049743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9217920303345</t>
   </si>
   <si>
     <t xml:space="preserve">13.9142293930054</t>
@@ -1463,79 +1463,79 @@
     <t xml:space="preserve">14.2696466445923</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3982038497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9898490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.664680480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6722440719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5814981460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7705488204956</t>
+    <t xml:space="preserve">14.3982028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9898509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6646795272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6722431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5814971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705507278442</t>
   </si>
   <si>
     <t xml:space="preserve">13.6268701553345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5210008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495561599731</t>
+    <t xml:space="preserve">13.5209999084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495552062988</t>
   </si>
   <si>
     <t xml:space="preserve">13.551248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4907531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4756269454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.505877494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3470726013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3924436569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4831895828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8310470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6344318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5663738250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5436868667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3773221969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1958322525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2714519500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3395118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3546352386475</t>
+    <t xml:space="preserve">13.4907522201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4756288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5058765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3470735549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3924465179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4831914901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6344327926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5663728713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5436859130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3773231506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1958332061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2714509963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3395099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3546342849731</t>
   </si>
   <si>
     <t xml:space="preserve">13.2638902664185</t>
@@ -1547,25 +1547,25 @@
     <t xml:space="preserve">13.3319473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9311590194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0219030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8101654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5530548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7421064376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6513614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848838806152</t>
+    <t xml:space="preserve">12.9311599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0219039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8101663589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.553053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7421073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6513605117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848848342896</t>
   </si>
   <si>
     <t xml:space="preserve">13.120210647583</t>
@@ -1577,70 +1577,70 @@
     <t xml:space="preserve">12.5681791305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.439624786377</t>
+    <t xml:space="preserve">12.4396238327026</t>
   </si>
   <si>
     <t xml:space="preserve">12.6211137771606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4018135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4925584793091</t>
+    <t xml:space="preserve">12.4018115997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4925575256348</t>
   </si>
   <si>
     <t xml:space="preserve">12.4698715209961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1371402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2883815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1522645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6286754608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252897262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7723560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.847975730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7572317123413</t>
+    <t xml:space="preserve">12.1371393203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2883806228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1522626876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6286764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437997817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.825288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7723541259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8479738235474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.757230758667</t>
   </si>
   <si>
     <t xml:space="preserve">12.8177280426025</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7799158096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4471855163574</t>
+    <t xml:space="preserve">12.77991771698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4471845626831</t>
   </si>
   <si>
     <t xml:space="preserve">12.4244995117188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2581338882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1673879623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.416937828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1447019577026</t>
+    <t xml:space="preserve">12.2581329345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1673889160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4169368743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.144702911377</t>
   </si>
   <si>
     <t xml:space="preserve">12.031270980835</t>
@@ -1649,34 +1649,34 @@
     <t xml:space="preserve">12.2505722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1068925857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2278861999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0463953018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.099328994751</t>
+    <t xml:space="preserve">12.1068916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2278842926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0463962554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0993299484253</t>
   </si>
   <si>
     <t xml:space="preserve">11.7968454360962</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8800287246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5379285812378</t>
+    <t xml:space="preserve">11.8800296783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5379295349121</t>
   </si>
   <si>
     <t xml:space="preserve">12.2656946182251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7950410842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2941389083862</t>
+    <t xml:space="preserve">12.7950420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2941379547119</t>
   </si>
   <si>
     <t xml:space="preserve">13.1126480102539</t>
@@ -1685,31 +1685,31 @@
     <t xml:space="preserve">12.9538440704346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5833015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4774341583252</t>
+    <t xml:space="preserve">12.5833034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4774332046509</t>
   </si>
   <si>
     <t xml:space="preserve">12.5757398605347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8555383682251</t>
+    <t xml:space="preserve">12.8555393218994</t>
   </si>
   <si>
     <t xml:space="preserve">13.0143413543701</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8328523635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9084720611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.052152633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9160346984863</t>
+    <t xml:space="preserve">12.8328514099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9084711074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0521516799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.916033744812</t>
   </si>
   <si>
     <t xml:space="preserve">13.09752368927</t>
@@ -1727,67 +1727,67 @@
     <t xml:space="preserve">12.9009103775024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0370292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7647914886475</t>
+    <t xml:space="preserve">13.0370273590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7647924423218</t>
   </si>
   <si>
     <t xml:space="preserve">13.029465675354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2109537124634</t>
+    <t xml:space="preserve">13.210955619812</t>
   </si>
   <si>
     <t xml:space="preserve">13.233642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9235973358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8706617355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8933477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353340148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9689693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1050853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3016996383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8857870101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.689172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6967334747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6362371444702</t>
+    <t xml:space="preserve">12.9235954284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.870662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.893346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.188268661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9689683914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3017015457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8857860565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6891717910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6967344284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6362361907959</t>
   </si>
   <si>
     <t xml:space="preserve">12.666485786438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5152425765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3110666275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2430095672607</t>
+    <t xml:space="preserve">12.5152435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3110685348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2430086135864</t>
   </si>
   <si>
     <t xml:space="preserve">12.0388326644897</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">12.6589231491089</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7269821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7496700286865</t>
+    <t xml:space="preserve">12.7269830703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7496681213379</t>
   </si>
   <si>
     <t xml:space="preserve">12.3186311721802</t>
@@ -1808,52 +1808,52 @@
     <t xml:space="preserve">12.1900749206543</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1976366043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1749515533447</t>
+    <t xml:space="preserve">12.1976356506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1749505996704</t>
   </si>
   <si>
     <t xml:space="preserve">12.2732563018799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1598262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203226089478</t>
+    <t xml:space="preserve">12.1598272323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203235626221</t>
   </si>
   <si>
     <t xml:space="preserve">12.2808198928833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3035068511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8631010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2902870178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4485054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5988121032715</t>
+    <t xml:space="preserve">12.3035049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8631000518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2902879714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4485063552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988111495972</t>
   </si>
   <si>
     <t xml:space="preserve">13.6146335601807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9548025131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9785356521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8598718643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7491188049316</t>
+    <t xml:space="preserve">13.9548015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.978533744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8598709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.749116897583</t>
   </si>
   <si>
     <t xml:space="preserve">13.7332973480225</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">13.8124046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">13.717474937439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6383676528931</t>
+    <t xml:space="preserve">13.7174739837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6383666992188</t>
   </si>
   <si>
     <t xml:space="preserve">13.6620998382568</t>
@@ -1877,49 +1877,49 @@
     <t xml:space="preserve">13.5750789642334</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1446628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2395944595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5085639953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690103530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7221593856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6746912002563</t>
+    <t xml:space="preserve">14.1446619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.239595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.508563041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.469012260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955839157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7221584320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.674690246582</t>
   </si>
   <si>
     <t xml:space="preserve">14.176305770874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1604862213135</t>
+    <t xml:space="preserve">14.1604843139648</t>
   </si>
   <si>
     <t xml:space="preserve">14.0813770294189</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0339097976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6984252929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6114044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4136323928833</t>
+    <t xml:space="preserve">14.0339107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4373645782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6984262466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.611403465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4136333465576</t>
   </si>
   <si>
     <t xml:space="preserve">14.6272268295288</t>
@@ -1928,73 +1928,73 @@
     <t xml:space="preserve">15.1097917556763</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0939683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911279678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9436626434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9120178222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8724660873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8645553588867</t>
+    <t xml:space="preserve">15.0939712524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911289215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9436616897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9120197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.872465133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.864556312561</t>
   </si>
   <si>
     <t xml:space="preserve">14.6430492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2870597839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3266143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2158603668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.247504234314</t>
+    <t xml:space="preserve">14.2870588302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3266153335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.215859413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2475051879883</t>
   </si>
   <si>
     <t xml:space="preserve">14.0260000228882</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0576438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6067237854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8677825927734</t>
+    <t xml:space="preserve">14.0576429367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6067247390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8677835464478</t>
   </si>
   <si>
     <t xml:space="preserve">14.2000398635864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2949705123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.207950592041</t>
+    <t xml:space="preserve">14.2949686050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2079486846924</t>
   </si>
   <si>
     <t xml:space="preserve">13.6304559707642</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5671691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6700105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5197038650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3693952560425</t>
+    <t xml:space="preserve">13.5671672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6700096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5197019577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3693962097168</t>
   </si>
   <si>
     <t xml:space="preserve">13.8203153610229</t>
@@ -2003,40 +2003,40 @@
     <t xml:space="preserve">13.9073371887207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8440504074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5592565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7886724472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965850830078</t>
+    <t xml:space="preserve">13.844051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5592575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7886743545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965841293335</t>
   </si>
   <si>
     <t xml:space="preserve">14.1209316253662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9310693740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0892868041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.302882194519</t>
+    <t xml:space="preserve">13.9310703277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0892858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3028802871704</t>
   </si>
   <si>
     <t xml:space="preserve">14.4848308563232</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6588697433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2316846847534</t>
+    <t xml:space="preserve">14.6588726043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633275985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2316827774048</t>
   </si>
   <si>
     <t xml:space="preserve">14.1130199432373</t>
@@ -2048,31 +2048,31 @@
     <t xml:space="preserve">14.975305557251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8566427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9990358352661</t>
+    <t xml:space="preserve">14.8566446304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9990367889404</t>
   </si>
   <si>
     <t xml:space="preserve">14.8329105377197</t>
   </si>
   <si>
-    <t xml:space="preserve">14.745888710022</t>
+    <t xml:space="preserve">14.7458906173706</t>
   </si>
   <si>
     <t xml:space="preserve">15.0227708816528</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7379779815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854452133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6905145645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6351375579834</t>
+    <t xml:space="preserve">14.7379789352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854461669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6905126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351385116577</t>
   </si>
   <si>
     <t xml:space="preserve">14.5402069091797</t>
@@ -2081,61 +2081,61 @@
     <t xml:space="preserve">14.1525735855103</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5164747238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4294538497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1921291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0971965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2712373733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2791481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057216644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3899021148682</t>
+    <t xml:space="preserve">14.5164756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4294557571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1921281814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0971984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2712383270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.279146194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.405722618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3899011611938</t>
   </si>
   <si>
     <t xml:space="preserve">14.3424339294434</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3582563400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4610996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0069484710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9515733718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5322961807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3345241546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.374077796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3819894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6509609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0860576629639</t>
+    <t xml:space="preserve">14.3582572937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4610986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.006947517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9515743255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5322971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3345251083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3740797042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3819885253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509599685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0860567092896</t>
   </si>
   <si>
     <t xml:space="preserve">14.8170881271362</t>
@@ -2144,46 +2144,46 @@
     <t xml:space="preserve">14.6193170547485</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0544176101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4895124435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.869236946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7189311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3075637817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3471183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081781387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2284545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572542190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1888999938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1414356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3866729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2838315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3154745101929</t>
+    <t xml:space="preserve">15.0544157028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4895153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.869234085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7189321517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3075647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3471193313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081762313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2284526824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1889009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1414346694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3866720199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2838306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3154735565186</t>
   </si>
   <si>
     <t xml:space="preserve">15.7505731582642</t>
@@ -2192,31 +2192,31 @@
     <t xml:space="preserve">15.7110185623169</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6160888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4420490264893</t>
+    <t xml:space="preserve">15.6160879135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4420480728149</t>
   </si>
   <si>
     <t xml:space="preserve">15.2047214508057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2363662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1651678085327</t>
+    <t xml:space="preserve">15.2363653182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1651668548584</t>
   </si>
   <si>
     <t xml:space="preserve">15.4024925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6240005493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7743072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2173137664795</t>
+    <t xml:space="preserve">15.6239986419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7743053436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2173156738281</t>
   </si>
   <si>
     <t xml:space="preserve">16.5179271697998</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">16.296422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5653953552246</t>
+    <t xml:space="preserve">16.565393447876</t>
   </si>
   <si>
     <t xml:space="preserve">17.0400466918945</t>
@@ -2234,49 +2234,49 @@
     <t xml:space="preserve">16.9292945861816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0875148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9609394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6919689178467</t>
+    <t xml:space="preserve">17.0875129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.691967010498</t>
   </si>
   <si>
     <t xml:space="preserve">16.8976516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1982650756836</t>
+    <t xml:space="preserve">17.198263168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.8818302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">17.229907989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3564834594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4514102935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6096305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4039459228516</t>
+    <t xml:space="preserve">17.2299098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.356481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4514141082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6096324920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4039497375488</t>
   </si>
   <si>
     <t xml:space="preserve">17.4355926513672</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5305213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8786010742188</t>
+    <t xml:space="preserve">17.5305233001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8785991668701</t>
   </si>
   <si>
     <t xml:space="preserve">18.1792144775391</t>
@@ -2288,22 +2288,22 @@
     <t xml:space="preserve">18.2583236694336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3690757751465</t>
+    <t xml:space="preserve">18.3690738677979</t>
   </si>
   <si>
     <t xml:space="preserve">18.2899684906006</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2108592987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3723011016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4830570220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7045593261719</t>
+    <t xml:space="preserve">18.2108573913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3723030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4830551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7045612335205</t>
   </si>
   <si>
     <t xml:space="preserve">17.3248386383057</t>
@@ -2312,70 +2312,70 @@
     <t xml:space="preserve">16.5021076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4988803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1507987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1701698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0213174819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8267726898193</t>
+    <t xml:space="preserve">17.4988765716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1508007049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1701707839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0213165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8267736434937</t>
   </si>
   <si>
     <t xml:space="preserve">11.6210899353027</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6290016174316</t>
+    <t xml:space="preserve">11.629002571106</t>
   </si>
   <si>
     <t xml:space="preserve">11.3600311279297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9882202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4470510482788</t>
+    <t xml:space="preserve">10.9882192611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4470520019531</t>
   </si>
   <si>
     <t xml:space="preserve">12.0245456695557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0640993118286</t>
+    <t xml:space="preserve">12.0641002655029</t>
   </si>
   <si>
     <t xml:space="preserve">12.4200897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1748523712158</t>
+    <t xml:space="preserve">12.1748533248901</t>
   </si>
   <si>
     <t xml:space="preserve">12.9026546478271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6969709396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4722394943237</t>
+    <t xml:space="preserve">12.6969699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2190885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4722385406494</t>
   </si>
   <si>
     <t xml:space="preserve">13.3140201568604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2349109649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241579055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4089517593384</t>
+    <t xml:space="preserve">13.2349119186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241588592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4089508056641</t>
   </si>
   <si>
     <t xml:space="preserve">13.4564170837402</t>
@@ -2384,34 +2384,34 @@
     <t xml:space="preserve">13.1004257202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0925140380859</t>
+    <t xml:space="preserve">13.0925149917603</t>
   </si>
   <si>
     <t xml:space="preserve">13.2507333755493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0687837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3614864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4326829910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5038814544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9738531112671</t>
+    <t xml:space="preserve">13.0687818527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3614845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4326839447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5038805007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9738521575928</t>
   </si>
   <si>
     <t xml:space="preserve">12.9342975616455</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0371379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1795358657837</t>
+    <t xml:space="preserve">13.0371389389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1795339584351</t>
   </si>
   <si>
     <t xml:space="preserve">13.2111787796021</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">13.6225442886353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7095632553101</t>
+    <t xml:space="preserve">13.7095642089844</t>
   </si>
   <si>
     <t xml:space="preserve">14.2056894302368</t>
@@ -2432,31 +2432,31 @@
     <t xml:space="preserve">13.8418645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">14.156078338623</t>
+    <t xml:space="preserve">14.1560773849487</t>
   </si>
   <si>
     <t xml:space="preserve">14.2966461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2883758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0490999221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2475490570068</t>
+    <t xml:space="preserve">14.2883768081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0491018295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2475481033325</t>
   </si>
   <si>
     <t xml:space="preserve">15.2971620559692</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1240348815918</t>
+    <t xml:space="preserve">16.1240367889404</t>
   </si>
   <si>
     <t xml:space="preserve">16.4134407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5043983459473</t>
+    <t xml:space="preserve">16.5043964385986</t>
   </si>
   <si>
     <t xml:space="preserve">16.1405754089355</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">16.0909595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1901836395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286874771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3467721939087</t>
+    <t xml:space="preserve">16.190185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5865659713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.346773147583</t>
   </si>
   <si>
     <t xml:space="preserve">15.2144746780396</t>
@@ -2483,28 +2483,28 @@
     <t xml:space="preserve">15.2806253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8346290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.652717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692533493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5782985687256</t>
+    <t xml:space="preserve">15.8346300125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6527185440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5782995223999</t>
   </si>
   <si>
     <t xml:space="preserve">15.7932863235474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8594350814819</t>
+    <t xml:space="preserve">15.8594369888306</t>
   </si>
   <si>
     <t xml:space="preserve">15.3633108139038</t>
   </si>
   <si>
-    <t xml:space="preserve">15.429461479187</t>
+    <t xml:space="preserve">15.4294605255127</t>
   </si>
   <si>
     <t xml:space="preserve">15.5617609024048</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">15.8677043914795</t>
   </si>
   <si>
-    <t xml:space="preserve">16.330753326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0501346588135</t>
+    <t xml:space="preserve">16.3307552337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0501365661621</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651214599609</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">16.9509086608887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.116283416748</t>
+    <t xml:space="preserve">17.1162853240967</t>
   </si>
   <si>
     <t xml:space="preserve">17.3312702178955</t>
@@ -2546,28 +2546,28 @@
     <t xml:space="preserve">17.2816581726074</t>
   </si>
   <si>
-    <t xml:space="preserve">17.314733505249</t>
+    <t xml:space="preserve">17.3147354125977</t>
   </si>
   <si>
     <t xml:space="preserve">17.4304962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3643474578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3808822631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9839839935303</t>
+    <t xml:space="preserve">17.3643455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3808841705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9839859008789</t>
   </si>
   <si>
     <t xml:space="preserve">16.8186092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9012966156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8516826629639</t>
+    <t xml:space="preserve">16.901294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8516845703125</t>
   </si>
   <si>
     <t xml:space="preserve">16.7524604797363</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">17.0170593261719</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4635696411133</t>
+    <t xml:space="preserve">17.4635715484619</t>
   </si>
   <si>
     <t xml:space="preserve">17.5958709716797</t>
@@ -2585,19 +2585,19 @@
     <t xml:space="preserve">17.4801082611084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8439331054688</t>
+    <t xml:space="preserve">17.8439350128174</t>
   </si>
   <si>
     <t xml:space="preserve">17.9266204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9927711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0919933319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4227447509766</t>
+    <t xml:space="preserve">17.992769241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0919914245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4227428436279</t>
   </si>
   <si>
     <t xml:space="preserve">18.4723587036133</t>
@@ -2606,13 +2606,13 @@
     <t xml:space="preserve">18.1581420898438</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0258445739746</t>
+    <t xml:space="preserve">18.025842666626</t>
   </si>
   <si>
     <t xml:space="preserve">18.0754585266113</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5054321289062</t>
+    <t xml:space="preserve">18.5054302215576</t>
   </si>
   <si>
     <t xml:space="preserve">18.3896713256836</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">18.3235187530518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3400554656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1912174224854</t>
+    <t xml:space="preserve">18.3400573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1912212371826</t>
   </si>
   <si>
     <t xml:space="preserve">18.0589218139648</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">17.9100818634033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2408294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3069801330566</t>
+    <t xml:space="preserve">18.2408313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3069820404053</t>
   </si>
   <si>
     <t xml:space="preserve">17.6620216369629</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">17.7943210601807</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7116317749023</t>
+    <t xml:space="preserve">17.711633682251</t>
   </si>
   <si>
     <t xml:space="preserve">17.5793342590332</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">17.347806930542</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4966430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3974208831787</t>
+    <t xml:space="preserve">17.4966449737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3974227905273</t>
   </si>
   <si>
     <t xml:space="preserve">17.7447071075439</t>
@@ -2672,31 +2672,31 @@
     <t xml:space="preserve">18.7700309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3731327056885</t>
+    <t xml:space="preserve">18.3731307983398</t>
   </si>
   <si>
     <t xml:space="preserve">18.6542701721191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7534923553467</t>
+    <t xml:space="preserve">18.7534942626953</t>
   </si>
   <si>
     <t xml:space="preserve">18.4062080383301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1416091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9431571960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1085338592529</t>
+    <t xml:space="preserve">18.1416072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9431591033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1085319519043</t>
   </si>
   <si>
     <t xml:space="preserve">17.7281703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9596977233887</t>
+    <t xml:space="preserve">17.95969581604</t>
   </si>
   <si>
     <t xml:space="preserve">17.1989727020264</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">16.2894115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9503936767578</t>
+    <t xml:space="preserve">15.9503917694092</t>
   </si>
   <si>
     <t xml:space="preserve">16.0413475036621</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">16.6201591491699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4795894622803</t>
+    <t xml:space="preserve">16.4795913696289</t>
   </si>
   <si>
     <t xml:space="preserve">17.0335960388184</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">17.1328201293945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1824359893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462589263916</t>
+    <t xml:space="preserve">17.1824340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.546257019043</t>
   </si>
   <si>
     <t xml:space="preserve">18.1746826171875</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">20.0599536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9607276916504</t>
+    <t xml:space="preserve">19.9607257843018</t>
   </si>
   <si>
     <t xml:space="preserve">20.5064659118652</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6883792877197</t>
+    <t xml:space="preserve">20.6883773803711</t>
   </si>
   <si>
     <t xml:space="preserve">20.7049160003662</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">20.7545280456543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9364414215088</t>
+    <t xml:space="preserve">20.9364395141602</t>
   </si>
   <si>
     <t xml:space="preserve">20.7214527130127</t>
@@ -2810,16 +2810,16 @@
     <t xml:space="preserve">21.0025901794434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1845016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6806259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1767520904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9948387145996</t>
+    <t xml:space="preserve">21.1845035552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6806240081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1767501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.994836807251</t>
   </si>
   <si>
     <t xml:space="preserve">22.5571136474609</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">21.5979385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4160270690918</t>
+    <t xml:space="preserve">21.4160251617432</t>
   </si>
   <si>
     <t xml:space="preserve">21.8956127166748</t>
@@ -2852,19 +2852,19 @@
     <t xml:space="preserve">21.8460006713867</t>
   </si>
   <si>
-    <t xml:space="preserve">22.160213470459</t>
+    <t xml:space="preserve">22.1602115631104</t>
   </si>
   <si>
     <t xml:space="preserve">21.5317897796631</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3664150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7379894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5726146697998</t>
+    <t xml:space="preserve">21.3664169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7379913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5726165771484</t>
   </si>
   <si>
     <t xml:space="preserve">21.2506523132324</t>
@@ -2876,13 +2876,13 @@
     <t xml:space="preserve">20.2584037780762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6134414672852</t>
+    <t xml:space="preserve">19.6134395599365</t>
   </si>
   <si>
     <t xml:space="preserve">20.1922550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3323059082031</t>
+    <t xml:space="preserve">19.3323040008545</t>
   </si>
   <si>
     <t xml:space="preserve">18.9354038238525</t>
@@ -2891,19 +2891,19 @@
     <t xml:space="preserve">20.2749404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2010364532471</t>
+    <t xml:space="preserve">21.2010402679443</t>
   </si>
   <si>
     <t xml:space="preserve">20.9860496520996</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4656372070312</t>
+    <t xml:space="preserve">21.4656391143799</t>
   </si>
   <si>
     <t xml:space="preserve">20.0103416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465167999268</t>
+    <t xml:space="preserve">19.6465187072754</t>
   </si>
   <si>
     <t xml:space="preserve">20.2253265380859</t>
@@ -2924,55 +2924,55 @@
     <t xml:space="preserve">21.34987449646</t>
   </si>
   <si>
-    <t xml:space="preserve">21.085277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0191268920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8702907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1018142700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8868293762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5230045318604</t>
+    <t xml:space="preserve">21.0852756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0191287994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.870288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1018161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8868274688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5230026245117</t>
   </si>
   <si>
     <t xml:space="preserve">20.6056900024414</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0268802642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1095676422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1514282226562</t>
+    <t xml:space="preserve">20.0268783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1095695495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1514263153076</t>
   </si>
   <si>
     <t xml:space="preserve">20.6222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3080139160156</t>
+    <t xml:space="preserve">20.3080158233643</t>
   </si>
   <si>
     <t xml:space="preserve">20.4072399139404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9772644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3907012939453</t>
+    <t xml:space="preserve">19.9772663116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3907032012939</t>
   </si>
   <si>
     <t xml:space="preserve">20.1261024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0764923095703</t>
+    <t xml:space="preserve">20.0764904022217</t>
   </si>
   <si>
     <t xml:space="preserve">20.2914791107178</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">21.229097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1779460906982</t>
+    <t xml:space="preserve">21.1779441833496</t>
   </si>
   <si>
     <t xml:space="preserve">21.4337158203125</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">21.6212825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3143539428711</t>
+    <t xml:space="preserve">21.3143558502197</t>
   </si>
   <si>
     <t xml:space="preserve">21.570125579834</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">21.6553840637207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7406406402588</t>
+    <t xml:space="preserve">21.7406425476074</t>
   </si>
   <si>
     <t xml:space="preserve">21.3655090332031</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">21.6724376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0987243652344</t>
+    <t xml:space="preserve">22.0987224578857</t>
   </si>
   <si>
     <t xml:space="preserve">21.7917957305908</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">21.1097373962402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1608924865723</t>
+    <t xml:space="preserve">21.1608905792236</t>
   </si>
   <si>
     <t xml:space="preserve">21.5530776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7747459411621</t>
+    <t xml:space="preserve">21.7747478485107</t>
   </si>
   <si>
     <t xml:space="preserve">21.2973022460938</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">21.0926876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8539619445801</t>
+    <t xml:space="preserve">20.8539638519287</t>
   </si>
   <si>
     <t xml:space="preserve">21.0074291229248</t>
@@ -3128,16 +3128,16 @@
     <t xml:space="preserve">21.2802505493164</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9282093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8600006103516</t>
+    <t xml:space="preserve">21.9282073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8600025177002</t>
   </si>
   <si>
     <t xml:space="preserve">21.8088474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8941059112549</t>
+    <t xml:space="preserve">21.8941078186035</t>
   </si>
   <si>
     <t xml:space="preserve">21.7576942443848</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">21.9111576080322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5079593658447</t>
+    <t xml:space="preserve">22.5079574584961</t>
   </si>
   <si>
     <t xml:space="preserve">22.1669292449951</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">22.0816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0134658813477</t>
+    <t xml:space="preserve">22.013463973999</t>
   </si>
   <si>
     <t xml:space="preserve">22.4909076690674</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">22.6614227294922</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7296257019043</t>
+    <t xml:space="preserve">22.7296276092529</t>
   </si>
   <si>
     <t xml:space="preserve">23.172966003418</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">23.9232330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2191429138184</t>
+    <t xml:space="preserve">25.219144821167</t>
   </si>
   <si>
     <t xml:space="preserve">25.4749164581299</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">25.8329982757568</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7818450927734</t>
+    <t xml:space="preserve">25.7818431854248</t>
   </si>
   <si>
     <t xml:space="preserve">26.1740283966064</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">26.6003150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6173667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7708282470703</t>
+    <t xml:space="preserve">26.6173648834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7708301544189</t>
   </si>
   <si>
     <t xml:space="preserve">26.6855716705322</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">24.8269596099854</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0145263671875</t>
+    <t xml:space="preserve">25.0145282745361</t>
   </si>
   <si>
     <t xml:space="preserve">25.1679916381836</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">25.1168346405029</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8099098205566</t>
+    <t xml:space="preserve">24.8099117279053</t>
   </si>
   <si>
     <t xml:space="preserve">24.8440113067627</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">25.1338882446289</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7246513366699</t>
+    <t xml:space="preserve">24.7246532440186</t>
   </si>
   <si>
     <t xml:space="preserve">24.7587566375732</t>
@@ -3287,16 +3287,16 @@
     <t xml:space="preserve">24.3324680328369</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6223430633545</t>
+    <t xml:space="preserve">24.6223411560059</t>
   </si>
   <si>
     <t xml:space="preserve">24.1960563659668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3495178222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9402828216553</t>
+    <t xml:space="preserve">24.3495197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9402847290039</t>
   </si>
   <si>
     <t xml:space="preserve">24.1449012756348</t>
@@ -3314,10 +3314,10 @@
     <t xml:space="preserve">24.4518280029297</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2131080627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3665714263916</t>
+    <t xml:space="preserve">24.2131061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3665733337402</t>
   </si>
   <si>
     <t xml:space="preserve">24.2472114562988</t>
@@ -3326,7 +3326,7 @@
     <t xml:space="preserve">24.2813129425049</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0486297607422</t>
+    <t xml:space="preserve">25.0486278533936</t>
   </si>
   <si>
     <t xml:space="preserve">24.4347763061523</t>
@@ -3335,16 +3335,16 @@
     <t xml:space="preserve">23.5481014251709</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4969444274902</t>
+    <t xml:space="preserve">23.4969463348389</t>
   </si>
   <si>
     <t xml:space="preserve">22.9342460632324</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7978343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6443691253662</t>
+    <t xml:space="preserve">22.7978324890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6443710327148</t>
   </si>
   <si>
     <t xml:space="preserve">22.3033409118652</t>
@@ -3359,19 +3359,19 @@
     <t xml:space="preserve">21.8429508209229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1839790344238</t>
+    <t xml:space="preserve">22.1839809417725</t>
   </si>
   <si>
     <t xml:space="preserve">21.1949939727783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6383323669434</t>
+    <t xml:space="preserve">21.6383304595947</t>
   </si>
   <si>
     <t xml:space="preserve">21.2120456695557</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9051189422607</t>
+    <t xml:space="preserve">20.9051208496094</t>
   </si>
   <si>
     <t xml:space="preserve">20.6663990020752</t>
@@ -3380,19 +3380,19 @@
     <t xml:space="preserve">21.4678173065186</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0244770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5640907287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9221725463867</t>
+    <t xml:space="preserve">21.0244789123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5640926361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9221706390381</t>
   </si>
   <si>
     <t xml:space="preserve">20.5129356384277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2912673950195</t>
+    <t xml:space="preserve">20.2912654876709</t>
   </si>
   <si>
     <t xml:space="preserve">20.1378021240234</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">24.0937480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6163063049316</t>
+    <t xml:space="preserve">23.616304397583</t>
   </si>
   <si>
     <t xml:space="preserve">22.7637329101562</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">22.8148860931396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6102676391602</t>
+    <t xml:space="preserve">22.6102695465088</t>
   </si>
   <si>
     <t xml:space="preserve">24.1619529724121</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">24.8951683044434</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3154163360596</t>
+    <t xml:space="preserve">24.3154182434082</t>
   </si>
   <si>
     <t xml:space="preserve">25.2873497009277</t>
@@ -3440,16 +3440,16 @@
     <t xml:space="preserve">24.6564464569092</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1850414276123</t>
+    <t xml:space="preserve">25.1850433349609</t>
   </si>
   <si>
     <t xml:space="preserve">24.9804248809814</t>
   </si>
   <si>
-    <t xml:space="preserve">25.662483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3786468505859</t>
+    <t xml:space="preserve">25.6624851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3786449432373</t>
   </si>
   <si>
     <t xml:space="preserve">26.2933902740479</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">26.7537803649902</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9413452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0436534881592</t>
+    <t xml:space="preserve">26.9413471221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0436515808105</t>
   </si>
   <si>
     <t xml:space="preserve">27.0948085784912</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">27.7086620330811</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5040435791016</t>
+    <t xml:space="preserve">27.5040416717529</t>
   </si>
   <si>
     <t xml:space="preserve">27.4699420928955</t>
@@ -3494,16 +3494,16 @@
     <t xml:space="preserve">27.7939186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8621253967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0496921539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5893001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1800651550293</t>
+    <t xml:space="preserve">27.8621234893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0496940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5893020629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1800670623779</t>
   </si>
   <si>
     <t xml:space="preserve">27.2823753356934</t>
@@ -3518,19 +3518,19 @@
     <t xml:space="preserve">25.3555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3214550018311</t>
+    <t xml:space="preserve">25.3214530944824</t>
   </si>
   <si>
     <t xml:space="preserve">25.9864597320557</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3385066986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8901901245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7598152160645</t>
+    <t xml:space="preserve">25.3385047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8901920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7598171234131</t>
   </si>
   <si>
     <t xml:space="preserve">28.4759788513184</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">28.5100803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6976490020752</t>
+    <t xml:space="preserve">28.6976509094238</t>
   </si>
   <si>
     <t xml:space="preserve">28.9875240325928</t>
@@ -5454,9 +5454,6 @@
   </si>
   <si>
     <t xml:space="preserve">22.7999992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5599994659424</t>
   </si>
 </sst>
 </file>
@@ -70899,25 +70896,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6912847222</v>
+        <v>45968.6911689815</v>
       </c>
       <c r="B2505" t="n">
-        <v>235782</v>
+        <v>340991</v>
       </c>
       <c r="C2505" t="n">
-        <v>22.8400001525879</v>
+        <v>22.7000007629395</v>
       </c>
       <c r="D2505" t="n">
-        <v>22.5599994659424</v>
+        <v>22.2999992370605</v>
       </c>
       <c r="E2505" t="n">
-        <v>22.8400001525879</v>
+        <v>22.5400009155273</v>
       </c>
       <c r="F2505" t="n">
-        <v>22.5599994659424</v>
+        <v>22.4400005340576</v>
       </c>
       <c r="G2505" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -38,316 +38,316 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48755502700806</t>
+    <t xml:space="preserve">7.4875545501709</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43893337249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23837375640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04389333724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99527215957642</t>
+    <t xml:space="preserve">7.43893432617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23837423324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0438928604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9952712059021</t>
   </si>
   <si>
     <t xml:space="preserve">7.06212520599365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25053024291992</t>
+    <t xml:space="preserve">7.25052833557129</t>
   </si>
   <si>
     <t xml:space="preserve">7.22014188766479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17152261734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07428121566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8494119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0135064125061</t>
+    <t xml:space="preserve">7.17152118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07428073883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84941101074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01350450515747</t>
   </si>
   <si>
     <t xml:space="preserve">6.75216960906982</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83725547790527</t>
+    <t xml:space="preserve">6.83725500106812</t>
   </si>
   <si>
     <t xml:space="preserve">6.97096252441406</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09251260757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00742721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00134897232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98919343948364</t>
+    <t xml:space="preserve">7.09251356124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00742673873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00135040283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98919439315796</t>
   </si>
   <si>
     <t xml:space="preserve">6.92841863632202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86156463623047</t>
+    <t xml:space="preserve">6.86156558990479</t>
   </si>
   <si>
     <t xml:space="preserve">6.5333776473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47868013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61238527297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5516095161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77647972106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94057321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8737211227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63061857223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78863573074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58199882507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70354890823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71570444107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80686712265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91626501083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84333324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83117818832397</t>
+    <t xml:space="preserve">6.47867965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61238622665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55161046981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77647924423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94057369232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87372064590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63061809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78863430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58199834823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7035493850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71570301055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80686855316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91626405715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84333229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83117866516113</t>
   </si>
   <si>
     <t xml:space="preserve">6.879798412323</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70962619781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74609327316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85548877716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86764287948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95272922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04996967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27483940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35992574691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34776973724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26876306533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22622013092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11074542999268</t>
+    <t xml:space="preserve">6.7096266746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74609136581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85548734664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86764240264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95272874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04997110366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27483987808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35992431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34777021408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26876258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22621965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11074590682983</t>
   </si>
   <si>
     <t xml:space="preserve">7.03173685073853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08035707473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05604839324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1897554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23229646682739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15328979492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11682367324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16544389724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95880603790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93449735641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803075790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90410900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96488428115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79471302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7643256187439</t>
+    <t xml:space="preserve">7.08035755157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05604791641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23229694366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15328884124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11682271957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16544485092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95880556106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93449640274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803171157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90410947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96488332748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79471206665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76432514190674</t>
   </si>
   <si>
     <t xml:space="preserve">7.1411337852478</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02566003799438</t>
+    <t xml:space="preserve">7.02566146850586</t>
   </si>
   <si>
     <t xml:space="preserve">7.15738677978516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13741111755371</t>
+    <t xml:space="preserve">7.1374135017395</t>
   </si>
   <si>
     <t xml:space="preserve">7.31052112579346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25725746154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34381151199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38376045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29720592498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2505989074707</t>
+    <t xml:space="preserve">7.25725793838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34381198883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38375902175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29720640182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25059938430786</t>
   </si>
   <si>
     <t xml:space="preserve">7.21730995178223</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23062515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23728227615356</t>
+    <t xml:space="preserve">7.23062467575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23728322982788</t>
   </si>
   <si>
     <t xml:space="preserve">7.27723169326782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22396802902222</t>
+    <t xml:space="preserve">7.2239670753479</t>
   </si>
   <si>
     <t xml:space="preserve">7.10412311553955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85777521133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.658034324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60476970672607</t>
+    <t xml:space="preserve">6.85777568817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65803480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60477066040039</t>
   </si>
   <si>
     <t xml:space="preserve">6.47493839263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50822830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95764541625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93767118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82448482513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88440799713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47826671600342</t>
+    <t xml:space="preserve">6.50822782516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95764493942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93767166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82448530197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88440752029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4782657623291</t>
   </si>
   <si>
     <t xml:space="preserve">6.32180309295654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56149196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69132423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81782817840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9176983833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03754234313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78453636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50489950180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6180853843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71795654296875</t>
+    <t xml:space="preserve">6.56149387359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69132471084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8178277015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91769742965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03754186630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78453683853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5048999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61808586120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71795606613159</t>
   </si>
   <si>
     <t xml:space="preserve">6.68466663360596</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73793077468872</t>
+    <t xml:space="preserve">6.73793125152588</t>
   </si>
   <si>
     <t xml:space="preserve">6.87774896621704</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">6.81116914749146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75124788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79119443893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76456165313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86443376541138</t>
+    <t xml:space="preserve">6.75124645233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79119348526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76456260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86443424224854</t>
   </si>
   <si>
     <t xml:space="preserve">6.77122068405151</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">6.89106607437134</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73127174377441</t>
+    <t xml:space="preserve">6.73127269744873</t>
   </si>
   <si>
     <t xml:space="preserve">6.64471817016602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63806009292603</t>
+    <t xml:space="preserve">6.63805913925171</t>
   </si>
   <si>
     <t xml:space="preserve">6.75790357589722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83114290237427</t>
+    <t xml:space="preserve">6.83114337921143</t>
   </si>
   <si>
     <t xml:space="preserve">6.80451107025146</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">6.74458932876587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71129894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65137577056885</t>
+    <t xml:space="preserve">6.7112979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65137529373169</t>
   </si>
   <si>
     <t xml:space="preserve">6.62807273864746</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">7.01756858825684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98427724838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01090955734253</t>
+    <t xml:space="preserve">6.98427867889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01091003417969</t>
   </si>
   <si>
     <t xml:space="preserve">7.04419994354248</t>
@@ -431,40 +431,40 @@
     <t xml:space="preserve">7.17070245742798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87109041213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92435598373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83780097961426</t>
+    <t xml:space="preserve">6.87109088897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92435503005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97761964797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83780145645142</t>
   </si>
   <si>
     <t xml:space="preserve">6.84445905685425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79785346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7778787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59811162948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55150604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72461414337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67135095596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66469240188599</t>
+    <t xml:space="preserve">6.79785299301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77787971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59811115264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55150651931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7246150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67134952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66469383239746</t>
   </si>
   <si>
     <t xml:space="preserve">6.60809993743896</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">6.54484844207764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45829343795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65470552444458</t>
+    <t xml:space="preserve">6.45829391479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65470457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.67800807952881</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">6.46495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13870716094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.228590965271</t>
+    <t xml:space="preserve">6.13870763778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22859048843384</t>
   </si>
   <si>
     <t xml:space="preserve">6.19197177886963</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">6.17865562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24856567382812</t>
+    <t xml:space="preserve">6.24856615066528</t>
   </si>
   <si>
     <t xml:space="preserve">6.13537836074829</t>
@@ -506,37 +506,37 @@
     <t xml:space="preserve">6.06546878814697</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16866874694824</t>
+    <t xml:space="preserve">6.1686692237854</t>
   </si>
   <si>
     <t xml:space="preserve">6.15868139266968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1420373916626</t>
+    <t xml:space="preserve">6.14203691482544</t>
   </si>
   <si>
     <t xml:space="preserve">6.0621395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03883647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10874605178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881214141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02219247817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01886320114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11873245239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23191976547241</t>
+    <t xml:space="preserve">6.03883695602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10874700546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0588116645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02219152450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0188627243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11873292922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23191928863525</t>
   </si>
   <si>
     <t xml:space="preserve">6.12206268310547</t>
@@ -545,97 +545,97 @@
     <t xml:space="preserve">6.22193241119385</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21860456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35842275619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37839603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6247444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70464038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85111808776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69798278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.904381275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8977222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99093675613403</t>
+    <t xml:space="preserve">6.21860361099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35842180252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37839698791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62474536895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70464086532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8511176109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6979832649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90438222885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89772319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99093580245972</t>
   </si>
   <si>
     <t xml:space="preserve">7.07748985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91103935241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07083177566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13075542449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15072774887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18401861190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09746503829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05085754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35046911239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27057409286499</t>
+    <t xml:space="preserve">6.91103887557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07083129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1307544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15072727203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1840181350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0974645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05085849761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35047006607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27057313919067</t>
   </si>
   <si>
     <t xml:space="preserve">7.2838888168335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30386400222778</t>
+    <t xml:space="preserve">7.30386352539062</t>
   </si>
   <si>
     <t xml:space="preserve">7.53023672103882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32383823394775</t>
+    <t xml:space="preserve">7.3238377571106</t>
   </si>
   <si>
     <t xml:space="preserve">7.31717920303345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36378622055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51691961288452</t>
+    <t xml:space="preserve">7.36378526687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51692008972168</t>
   </si>
   <si>
     <t xml:space="preserve">7.59015846252441</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60347414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000242233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992559432983</t>
+    <t xml:space="preserve">7.60347509384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71000337600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992654800415</t>
   </si>
   <si>
     <t xml:space="preserve">7.77658414840698</t>
@@ -653,67 +653,67 @@
     <t xml:space="preserve">7.82319068908691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85648155212402</t>
+    <t xml:space="preserve">7.85648059844971</t>
   </si>
   <si>
     <t xml:space="preserve">7.86979627609253</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87645578384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308666229248</t>
+    <t xml:space="preserve">7.87645483016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308618545532</t>
   </si>
   <si>
     <t xml:space="preserve">7.96966648101807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9496922492981</t>
+    <t xml:space="preserve">7.94969129562378</t>
   </si>
   <si>
     <t xml:space="preserve">7.92306041717529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96300983428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311243057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7233190536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62344837188721</t>
+    <t xml:space="preserve">7.96300888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72332096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62344741821289</t>
   </si>
   <si>
     <t xml:space="preserve">7.54355239868164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47031593322754</t>
+    <t xml:space="preserve">7.47031402587891</t>
   </si>
   <si>
     <t xml:space="preserve">7.63676595687866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56352710723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5701847076416</t>
+    <t xml:space="preserve">7.56352758407593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018518447876</t>
   </si>
   <si>
     <t xml:space="preserve">7.74329328536987</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80321550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8964262008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94303560256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84982252120972</t>
+    <t xml:space="preserve">7.80321645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89642810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94303369522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84982347488403</t>
   </si>
   <si>
     <t xml:space="preserve">8.06953716278076</t>
@@ -725,43 +725,43 @@
     <t xml:space="preserve">8.25009536743164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22926139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31954097747803</t>
+    <t xml:space="preserve">8.22926044464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31954002380371</t>
   </si>
   <si>
     <t xml:space="preserve">8.35426235198975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28481769561768</t>
+    <t xml:space="preserve">8.28481674194336</t>
   </si>
   <si>
     <t xml:space="preserve">8.2987060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37509822845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34731864929199</t>
+    <t xml:space="preserve">8.37509727478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34731960296631</t>
   </si>
   <si>
     <t xml:space="preserve">8.3889856338501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43759727478027</t>
+    <t xml:space="preserve">8.43759632110596</t>
   </si>
   <si>
     <t xml:space="preserve">8.4514856338501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68760108947754</t>
+    <t xml:space="preserve">8.68760013580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.7362117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62510013580322</t>
+    <t xml:space="preserve">8.62509918212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.63898849487305</t>
@@ -770,22 +770,22 @@
     <t xml:space="preserve">8.66676616668701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68065547943115</t>
+    <t xml:space="preserve">8.68065643310547</t>
   </si>
   <si>
     <t xml:space="preserve">8.59732151031494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69454479217529</t>
+    <t xml:space="preserve">8.7292652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69454383850098</t>
   </si>
   <si>
     <t xml:space="preserve">8.61121082305908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50704288482666</t>
+    <t xml:space="preserve">8.50704193115234</t>
   </si>
   <si>
     <t xml:space="preserve">8.59037590026855</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">8.52787590026855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54870891571045</t>
+    <t xml:space="preserve">8.54870986938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.4931526184082</t>
@@ -803,22 +803,22 @@
     <t xml:space="preserve">8.51398754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46537399291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47231864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61815547943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65982055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6459321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40981960296631</t>
+    <t xml:space="preserve">8.46537590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47232055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61815452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65982151031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64593315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40981769561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.4306526184082</t>
@@ -836,37 +836,37 @@
     <t xml:space="preserve">8.57648754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6042652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88204669952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00010395050049</t>
+    <t xml:space="preserve">8.60426616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71537780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88204765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00010299682617</t>
   </si>
   <si>
     <t xml:space="preserve">9.15288257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13204765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06954956054688</t>
+    <t xml:space="preserve">9.13204956054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06954860687256</t>
   </si>
   <si>
     <t xml:space="preserve">9.09038257598877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00704860687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95843505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06260299682617</t>
+    <t xml:space="preserve">9.00704765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95843601226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0626049041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.1251049041748</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">9.20843982696533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24316120147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29871940612793</t>
+    <t xml:space="preserve">9.24316215515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29871845245361</t>
   </si>
   <si>
     <t xml:space="preserve">9.36816310882568</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">9.40983009338379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41677474975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32649421691895</t>
+    <t xml:space="preserve">9.41677570343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32649612426758</t>
   </si>
   <si>
     <t xml:space="preserve">9.29177379608154</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">9.45149707794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47233200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43760776519775</t>
+    <t xml:space="preserve">9.47233104705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43760967254639</t>
   </si>
   <si>
     <t xml:space="preserve">9.44455242156982</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">9.40288639068604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38899803161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38205242156982</t>
+    <t xml:space="preserve">9.38899707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38205337524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.3403844833374</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">9.48622035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75011157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79177951812744</t>
+    <t xml:space="preserve">9.7501106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79178047180176</t>
   </si>
   <si>
     <t xml:space="preserve">9.7778902053833</t>
@@ -947,43 +947,43 @@
     <t xml:space="preserve">9.72927856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77094745635986</t>
+    <t xml:space="preserve">9.77094554901123</t>
   </si>
   <si>
     <t xml:space="preserve">9.76400089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74316787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96539402008057</t>
+    <t xml:space="preserve">9.74316692352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96539306640625</t>
   </si>
   <si>
     <t xml:space="preserve">10.0278921127319</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93761444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0834503173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1181707382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1876163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4445648193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5001201629639</t>
+    <t xml:space="preserve">9.93761539459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0834493637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1181716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1876173019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4445638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5001192092896</t>
   </si>
   <si>
     <t xml:space="preserve">10.5695657730103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.229284286499</t>
+    <t xml:space="preserve">10.2292852401733</t>
   </si>
   <si>
     <t xml:space="preserve">10.3959531784058</t>
@@ -995,52 +995,52 @@
     <t xml:space="preserve">10.5903997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4931774139404</t>
+    <t xml:space="preserve">10.4931755065918</t>
   </si>
   <si>
     <t xml:space="preserve">10.5626220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6251230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6042890548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.701512336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7779016494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8542909622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8334579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9029016494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1042947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1112394332886</t>
+    <t xml:space="preserve">10.6251220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6042881011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7015113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7779006958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8542919158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8334589004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9029026031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0904054641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1042938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1112384796143</t>
   </si>
   <si>
     <t xml:space="preserve">10.6667890548706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9723482131958</t>
+    <t xml:space="preserve">10.9723491668701</t>
   </si>
   <si>
     <t xml:space="preserve">10.9445695877075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0765171051025</t>
+    <t xml:space="preserve">11.0765142440796</t>
   </si>
   <si>
     <t xml:space="preserve">11.3473529815674</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">11.3959636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1529054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0626277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2154064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3126316070557</t>
+    <t xml:space="preserve">11.1529064178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0626268386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2154054641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3126306533813</t>
   </si>
   <si>
     <t xml:space="preserve">11.2362394332886</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2084617614746</t>
+    <t xml:space="preserve">11.2084627151489</t>
   </si>
   <si>
     <t xml:space="preserve">10.9098472595215</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">10.548731803894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7848472595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8612365722656</t>
+    <t xml:space="preserve">10.7848453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8612356185913</t>
   </si>
   <si>
     <t xml:space="preserve">11.0695714950562</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">10.930682182312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1598501205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4515199661255</t>
+    <t xml:space="preserve">11.1598510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4515218734741</t>
   </si>
   <si>
     <t xml:space="preserve">11.5001316070557</t>
@@ -1109,19 +1109,19 @@
     <t xml:space="preserve">11.4931869506836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6251335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7223558425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7709703445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7015228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.729302406311</t>
+    <t xml:space="preserve">11.6251344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.722354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7709684371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7015247344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7293014526367</t>
   </si>
   <si>
     <t xml:space="preserve">11.7154130935669</t>
@@ -1139,55 +1139,55 @@
     <t xml:space="preserve">11.6806898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820753097534</t>
+    <t xml:space="preserve">11.3820743560791</t>
   </si>
   <si>
     <t xml:space="preserve">10.8681802749634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8959589004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9862375259399</t>
+    <t xml:space="preserve">10.8959579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9862365722656</t>
   </si>
   <si>
     <t xml:space="preserve">11.0834608078003</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292966842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848520278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3265180587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2431859970093</t>
+    <t xml:space="preserve">11.2292957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3265190124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.243185043335</t>
   </si>
   <si>
     <t xml:space="preserve">11.5973558425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7501354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6181879043579</t>
+    <t xml:space="preserve">11.7501363754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6181898117065</t>
   </si>
   <si>
     <t xml:space="preserve">11.7987461090088</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6320781707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8334693908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1251382827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9168033599854</t>
+    <t xml:space="preserve">11.6320772171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8334703445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1251392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9168043136597</t>
   </si>
   <si>
     <t xml:space="preserve">12.6668109893799</t>
@@ -1196,31 +1196,31 @@
     <t xml:space="preserve">13.1529293060303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.382098197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3195972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3682088851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5765447616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5209875106812</t>
+    <t xml:space="preserve">13.3820972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.319598197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3682107925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5765438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5209903717041</t>
   </si>
   <si>
     <t xml:space="preserve">13.2362632751465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1668167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0487613677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4237651824951</t>
+    <t xml:space="preserve">13.1668176651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0487632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4237642288208</t>
   </si>
   <si>
     <t xml:space="preserve">13.0070943832397</t>
@@ -1232,109 +1232,109 @@
     <t xml:space="preserve">13.4584875106812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7154350280762</t>
+    <t xml:space="preserve">13.7154340744019</t>
   </si>
   <si>
     <t xml:space="preserve">13.7918252944946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6807146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9168272018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9307155609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.187650680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2987642288208</t>
+    <t xml:space="preserve">13.6807126998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9168252944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9307146072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1876516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2987632751465</t>
   </si>
   <si>
     <t xml:space="preserve">13.3751544952393</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4168224334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4723777770996</t>
+    <t xml:space="preserve">13.4168214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4723787307739</t>
   </si>
   <si>
     <t xml:space="preserve">13.4862680435181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6112670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7362689971924</t>
+    <t xml:space="preserve">13.6112680435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7362699508667</t>
   </si>
   <si>
     <t xml:space="preserve">13.7223806381226</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8196039199829</t>
+    <t xml:space="preserve">13.8196048736572</t>
   </si>
   <si>
     <t xml:space="preserve">13.8890495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8543281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9029369354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0834970474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7987699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0279388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057193756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1945972442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1112613677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1807069778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0200986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1486539840698</t>
+    <t xml:space="preserve">13.8543272018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9029407501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0834951400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.798770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0279407501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.305721282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1945962905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1112623214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1807060241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0200996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1486530303955</t>
   </si>
   <si>
     <t xml:space="preserve">13.8083610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6571178436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5361261367798</t>
+    <t xml:space="preserve">13.6571187973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5361251831055</t>
   </si>
   <si>
     <t xml:space="preserve">13.2563276290894</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1277732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3092613220215</t>
+    <t xml:space="preserve">13.1277723312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3092622756958</t>
   </si>
   <si>
     <t xml:space="preserve">13.4605045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4983148574829</t>
+    <t xml:space="preserve">13.4983139038086</t>
   </si>
   <si>
     <t xml:space="preserve">13.4680662155151</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">13.5739364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7327404022217</t>
+    <t xml:space="preserve">13.7327394485474</t>
   </si>
   <si>
     <t xml:space="preserve">13.7478628158569</t>
@@ -1352,58 +1352,58 @@
     <t xml:space="preserve">13.4075689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4889469146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4738245010376</t>
+    <t xml:space="preserve">14.4889488220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.473822593689</t>
   </si>
   <si>
     <t xml:space="preserve">14.6704378128052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7158069610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755159378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6175031661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7233686447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9351110458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7460565567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292417526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2998952865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2091503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0654706954956</t>
+    <t xml:space="preserve">14.7158060073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755178451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6175022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7233724594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9351081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7460584640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167119979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2998962402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2091512680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0654697418213</t>
   </si>
   <si>
     <t xml:space="preserve">14.1637773513794</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0427846908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1713399887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2847700119019</t>
+    <t xml:space="preserve">14.0427827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1713390350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2847719192505</t>
   </si>
   <si>
     <t xml:space="preserve">14.6250648498535</t>
@@ -1412,124 +1412,124 @@
     <t xml:space="preserve">14.7536191940308</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6780004501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7914295196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8443641662598</t>
+    <t xml:space="preserve">14.6779985427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7914304733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8443632125854</t>
   </si>
   <si>
     <t xml:space="preserve">14.8746137619019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8368034362793</t>
+    <t xml:space="preserve">14.8368053436279</t>
   </si>
   <si>
     <t xml:space="preserve">14.7611827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6553134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5494441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099424362183</t>
+    <t xml:space="preserve">14.655312538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5494422912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099405288696</t>
   </si>
   <si>
     <t xml:space="preserve">14.6401891708374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5721302032471</t>
+    <t xml:space="preserve">14.5721282958984</t>
   </si>
   <si>
     <t xml:space="preserve">14.5191965103149</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2394008636475</t>
+    <t xml:space="preserve">14.2393999099731</t>
   </si>
   <si>
     <t xml:space="preserve">14.0049753189087</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9217910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9142293930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2696495056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3982038497925</t>
+    <t xml:space="preserve">13.9217920303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9142284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2696466445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3982028961182</t>
   </si>
   <si>
     <t xml:space="preserve">13.9898500442505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6646814346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6722431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5814971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7705488204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6268692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5210008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.551248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4756278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5058755874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3470735549927</t>
+    <t xml:space="preserve">13.664680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6722421646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5814962387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705478668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6268711090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5210018157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495571136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5512495040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907522201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4756288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5058765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.347071647644</t>
   </si>
   <si>
     <t xml:space="preserve">13.3924446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4831895828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6344318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5663738250732</t>
+    <t xml:space="preserve">13.483190536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8310489654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6344327926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5663728713989</t>
   </si>
   <si>
     <t xml:space="preserve">13.5436868667603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3773212432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1958322525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2714519500732</t>
+    <t xml:space="preserve">13.3773231506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1958332061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2714509963989</t>
   </si>
   <si>
     <t xml:space="preserve">13.3395118713379</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">13.2638902664185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4529438018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3319473266602</t>
+    <t xml:space="preserve">13.4529428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3319492340088</t>
   </si>
   <si>
     <t xml:space="preserve">12.9311599731445</t>
@@ -1553,22 +1553,22 @@
     <t xml:space="preserve">13.0219039916992</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8101663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5530548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7421054840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6513605117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848829269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1202125549316</t>
+    <t xml:space="preserve">12.8101654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.553053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7421073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6513624191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1202116012573</t>
   </si>
   <si>
     <t xml:space="preserve">12.9614057540894</t>
@@ -1577,25 +1577,25 @@
     <t xml:space="preserve">12.5681800842285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4396238327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6211137771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4018125534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4925594329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4698715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1371383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2883806228638</t>
+    <t xml:space="preserve">12.439624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.621114730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4018135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4925575256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4698724746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1371393203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2883825302124</t>
   </si>
   <si>
     <t xml:space="preserve">12.1522645950317</t>
@@ -1607,10 +1607,10 @@
     <t xml:space="preserve">12.643798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.825288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7723550796509</t>
+    <t xml:space="preserve">12.8252878189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7723541259766</t>
   </si>
   <si>
     <t xml:space="preserve">12.8479747772217</t>
@@ -1619,19 +1619,19 @@
     <t xml:space="preserve">12.7572317123413</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8177289962769</t>
+    <t xml:space="preserve">12.8177270889282</t>
   </si>
   <si>
     <t xml:space="preserve">12.7799167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4471845626831</t>
+    <t xml:space="preserve">12.4471855163574</t>
   </si>
   <si>
     <t xml:space="preserve">12.4244995117188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2581329345703</t>
+    <t xml:space="preserve">12.258131980896</t>
   </si>
   <si>
     <t xml:space="preserve">12.1673879623413</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">12.1447019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.031270980835</t>
+    <t xml:space="preserve">12.0312719345093</t>
   </si>
   <si>
     <t xml:space="preserve">12.2505722045898</t>
@@ -1661,28 +1661,28 @@
     <t xml:space="preserve">12.0993299484253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7968463897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8800287246704</t>
+    <t xml:space="preserve">11.7968473434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8800296783447</t>
   </si>
   <si>
     <t xml:space="preserve">12.5379304885864</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2656936645508</t>
+    <t xml:space="preserve">12.2656955718994</t>
   </si>
   <si>
     <t xml:space="preserve">12.7950420379639</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2941398620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1126489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9538440704346</t>
+    <t xml:space="preserve">13.2941389083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1126499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9538431167603</t>
   </si>
   <si>
     <t xml:space="preserve">12.5833024978638</t>
@@ -1694,21 +1694,24 @@
     <t xml:space="preserve">12.575740814209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8555383682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0143404006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8328514099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9084730148315</t>
+    <t xml:space="preserve">12.8555374145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0143413543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8328523635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9084720611572</t>
   </si>
   <si>
     <t xml:space="preserve">13.052152633667</t>
   </si>
   <si>
+    <t xml:space="preserve">13.1807079315186</t>
+  </si>
+  <si>
     <t xml:space="preserve">12.916033744812</t>
   </si>
   <si>
@@ -1721,25 +1724,25 @@
     <t xml:space="preserve">13.2260799407959</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2185182571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9009113311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0370283126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7647914886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0294666290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.210955619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.233642578125</t>
+    <t xml:space="preserve">13.2185173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9009094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0370264053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7647905349731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.029465675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2336406707764</t>
   </si>
   <si>
     <t xml:space="preserve">12.9235973358154</t>
@@ -1748,58 +1751,58 @@
     <t xml:space="preserve">12.8706617355347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8933458328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882705688477</t>
+    <t xml:space="preserve">12.893346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.188268661499</t>
   </si>
   <si>
     <t xml:space="preserve">13.1353349685669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9689683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1050863265991</t>
+    <t xml:space="preserve">12.9689702987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1050872802734</t>
   </si>
   <si>
     <t xml:space="preserve">13.3016996383667</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8857870101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6891736984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6967344284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6362380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.666485786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5152435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3110675811768</t>
+    <t xml:space="preserve">12.8857879638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6891717910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6362361907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6664848327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5152444839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3110685348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.2430095672607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0388326644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6589241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7269830703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7496700286865</t>
+    <t xml:space="preserve">12.0388336181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6589250564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7269811630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7496709823608</t>
   </si>
   <si>
     <t xml:space="preserve">12.3186302185059</t>
@@ -1808,13 +1811,13 @@
     <t xml:space="preserve">12.19007396698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1976356506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.174952507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2732572555542</t>
+    <t xml:space="preserve">12.1976366043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1749515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2732563018799</t>
   </si>
   <si>
     <t xml:space="preserve">12.1598262786865</t>
@@ -1823,58 +1826,58 @@
     <t xml:space="preserve">12.2203235626221</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2808198928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.303505897522</t>
+    <t xml:space="preserve">12.280818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3035068511963</t>
   </si>
   <si>
     <t xml:space="preserve">12.8630990982056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2902870178223</t>
+    <t xml:space="preserve">13.2902860641479</t>
   </si>
   <si>
     <t xml:space="preserve">13.4485054016113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5988130569458</t>
+    <t xml:space="preserve">13.5988121032715</t>
   </si>
   <si>
     <t xml:space="preserve">13.6146335601807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9548025131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9785356521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8598728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.749119758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7332973480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7728509902954</t>
+    <t xml:space="preserve">13.9548006057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.978533744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8598709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7491188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7332963943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7728500366211</t>
   </si>
   <si>
     <t xml:space="preserve">13.8124055862427</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7174758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6383666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6620988845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5750789642334</t>
+    <t xml:space="preserve">13.7174768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6383657455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6620998382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5750799179077</t>
   </si>
   <si>
     <t xml:space="preserve">14.1446628570557</t>
@@ -1883,10 +1886,10 @@
     <t xml:space="preserve">14.2395944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5085620880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690113067627</t>
+    <t xml:space="preserve">14.508563041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690103530884</t>
   </si>
   <si>
     <t xml:space="preserve">14.5955848693848</t>
@@ -1895,34 +1898,34 @@
     <t xml:space="preserve">14.7221574783325</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6746921539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.176305770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1604862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0813760757446</t>
+    <t xml:space="preserve">14.6746912002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1763076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1604843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0813751220703</t>
   </si>
   <si>
     <t xml:space="preserve">14.0339097976685</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4373664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6984252929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6114044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4136323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6272277832031</t>
+    <t xml:space="preserve">14.4373655319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6984243392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.611403465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4136333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6272268295288</t>
   </si>
   <si>
     <t xml:space="preserve">15.1097917556763</t>
@@ -1931,7 +1934,7 @@
     <t xml:space="preserve">15.0939683914185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9911270141602</t>
+    <t xml:space="preserve">14.9911289215088</t>
   </si>
   <si>
     <t xml:space="preserve">14.9436626434326</t>
@@ -1958,10 +1961,10 @@
     <t xml:space="preserve">14.2158603668213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2475032806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0260000228882</t>
+    <t xml:space="preserve">14.247504234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0259990692139</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576438903809</t>
@@ -1970,49 +1973,49 @@
     <t xml:space="preserve">13.6067237854004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8677816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000398635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2949714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2079496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6304559707642</t>
+    <t xml:space="preserve">13.8677825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000408172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2949705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2079477310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6304540634155</t>
   </si>
   <si>
     <t xml:space="preserve">13.5671682357788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6700096130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5197048187256</t>
+    <t xml:space="preserve">13.6700105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5197038650513</t>
   </si>
   <si>
     <t xml:space="preserve">13.3693962097168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8203172683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9073371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8440504074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5592565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7886734008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965850830078</t>
+    <t xml:space="preserve">13.8203163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9073362350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8440494537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5592575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7886753082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965841293335</t>
   </si>
   <si>
     <t xml:space="preserve">14.1209306716919</t>
@@ -2024,49 +2027,49 @@
     <t xml:space="preserve">14.0892868041992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3028812408447</t>
+    <t xml:space="preserve">14.3028802871704</t>
   </si>
   <si>
     <t xml:space="preserve">14.4848308563232</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6588697433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633266448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2316846847534</t>
+    <t xml:space="preserve">14.6588726043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633275985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2316827774048</t>
   </si>
   <si>
     <t xml:space="preserve">14.1130199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5876722335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.975305557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8566427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9990358352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8329105377197</t>
+    <t xml:space="preserve">14.5876731872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9753074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8566417694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9990377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8329095840454</t>
   </si>
   <si>
     <t xml:space="preserve">14.7458877563477</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0227699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7379779815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854452133179</t>
+    <t xml:space="preserve">15.0227718353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7379808425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854433059692</t>
   </si>
   <si>
     <t xml:space="preserve">14.6905145645142</t>
@@ -2081,37 +2084,37 @@
     <t xml:space="preserve">14.1525735855103</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5164737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4294548034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1921291351318</t>
+    <t xml:space="preserve">14.5164747238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4294557571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1921281814575</t>
   </si>
   <si>
     <t xml:space="preserve">14.0971975326538</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2712364196777</t>
+    <t xml:space="preserve">14.2712383270264</t>
   </si>
   <si>
     <t xml:space="preserve">14.2791471481323</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4057216644287</t>
+    <t xml:space="preserve">14.4057207107544</t>
   </si>
   <si>
     <t xml:space="preserve">14.3899030685425</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3424339294434</t>
+    <t xml:space="preserve">14.3424348831177</t>
   </si>
   <si>
     <t xml:space="preserve">14.3582563400269</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4611005783081</t>
+    <t xml:space="preserve">14.4610986709595</t>
   </si>
   <si>
     <t xml:space="preserve">15.0069484710693</t>
@@ -2120,19 +2123,19 @@
     <t xml:space="preserve">14.9515724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5322971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3345241546631</t>
+    <t xml:space="preserve">14.5322961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3345251083374</t>
   </si>
   <si>
     <t xml:space="preserve">14.3740787506104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3819894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6509609222412</t>
+    <t xml:space="preserve">14.3819885253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509590148926</t>
   </si>
   <si>
     <t xml:space="preserve">15.0860576629639</t>
@@ -2150,16 +2153,16 @@
     <t xml:space="preserve">15.4895133972168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8692350387573</t>
+    <t xml:space="preserve">15.869236946106</t>
   </si>
   <si>
     <t xml:space="preserve">15.7189302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3075666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3471193313599</t>
+    <t xml:space="preserve">15.3075647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3471155166626</t>
   </si>
   <si>
     <t xml:space="preserve">15.6081771850586</t>
@@ -2174,7 +2177,7 @@
     <t xml:space="preserve">15.1889009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1414365768433</t>
+    <t xml:space="preserve">15.141432762146</t>
   </si>
   <si>
     <t xml:space="preserve">15.3866710662842</t>
@@ -2192,10 +2195,10 @@
     <t xml:space="preserve">15.7110195159912</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6160879135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4420490264893</t>
+    <t xml:space="preserve">15.6160898208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4420509338379</t>
   </si>
   <si>
     <t xml:space="preserve">15.2047204971313</t>
@@ -2207,7 +2210,7 @@
     <t xml:space="preserve">15.1651668548584</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4024906158447</t>
+    <t xml:space="preserve">15.402494430542</t>
   </si>
   <si>
     <t xml:space="preserve">15.6239995956421</t>
@@ -2222,22 +2225,22 @@
     <t xml:space="preserve">16.5179290771484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2964210510254</t>
+    <t xml:space="preserve">16.296422958374</t>
   </si>
   <si>
     <t xml:space="preserve">16.5653953552246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0400447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9292964935303</t>
+    <t xml:space="preserve">17.0400466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9292945861816</t>
   </si>
   <si>
     <t xml:space="preserve">17.0875148773193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0558662414551</t>
+    <t xml:space="preserve">17.0558681488037</t>
   </si>
   <si>
     <t xml:space="preserve">16.9609375</t>
@@ -2258,10 +2261,10 @@
     <t xml:space="preserve">17.229907989502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3564853668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4514102935791</t>
+    <t xml:space="preserve">17.3564834594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4514122009277</t>
   </si>
   <si>
     <t xml:space="preserve">17.6096324920654</t>
@@ -2270,22 +2273,22 @@
     <t xml:space="preserve">17.4039497375488</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4355907440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5305213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8785991668701</t>
+    <t xml:space="preserve">17.4355926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305233001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8786029815674</t>
   </si>
   <si>
     <t xml:space="preserve">18.1792144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1317481994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2583236694336</t>
+    <t xml:space="preserve">18.1317501068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.258321762085</t>
   </si>
   <si>
     <t xml:space="preserve">18.3690757751465</t>
@@ -2327,10 +2330,10 @@
     <t xml:space="preserve">11.8267736434937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6210908889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6290006637573</t>
+    <t xml:space="preserve">11.6210918426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6290016174316</t>
   </si>
   <si>
     <t xml:space="preserve">11.3600311279297</t>
@@ -2339,7 +2342,7 @@
     <t xml:space="preserve">10.9882192611694</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4470510482788</t>
+    <t xml:space="preserve">11.4470520019531</t>
   </si>
   <si>
     <t xml:space="preserve">12.0245456695557</t>
@@ -2348,10 +2351,7 @@
     <t xml:space="preserve">12.0641012191772</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631000518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4200887680054</t>
+    <t xml:space="preserve">12.420090675354</t>
   </si>
   <si>
     <t xml:space="preserve">12.1748533248901</t>
@@ -2360,46 +2360,46 @@
     <t xml:space="preserve">12.9026536941528</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6969699859619</t>
+    <t xml:space="preserve">12.6969709396362</t>
   </si>
   <si>
     <t xml:space="preserve">13.2190895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4722394943237</t>
+    <t xml:space="preserve">13.4722375869751</t>
   </si>
   <si>
     <t xml:space="preserve">13.3140211105347</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2349100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241579055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4089527130127</t>
+    <t xml:space="preserve">13.2349109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241588592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4089517593384</t>
   </si>
   <si>
     <t xml:space="preserve">13.4564161300659</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1004257202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0925140380859</t>
+    <t xml:space="preserve">13.1004266738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0925149917603</t>
   </si>
   <si>
     <t xml:space="preserve">13.2507333755493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0687837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3614854812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4326829910278</t>
+    <t xml:space="preserve">13.0687828063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3614845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4326839447021</t>
   </si>
   <si>
     <t xml:space="preserve">13.5038814544678</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">13.179536819458</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2111797332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5434370040894</t>
+    <t xml:space="preserve">13.2111787796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.543436050415</t>
   </si>
   <si>
     <t xml:space="preserve">13.6225452423096</t>
@@ -2429,43 +2429,43 @@
     <t xml:space="preserve">13.7095642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2056903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1560773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2883758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0491018295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2475490570068</t>
+    <t xml:space="preserve">14.2056884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1560764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966442108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2883768081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0490999221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2475500106812</t>
   </si>
   <si>
     <t xml:space="preserve">15.2971620559692</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1240348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4134426116943</t>
+    <t xml:space="preserve">16.1240367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4134407043457</t>
   </si>
   <si>
     <t xml:space="preserve">16.5043964385986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1405735015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0909576416016</t>
+    <t xml:space="preserve">16.1405754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0909595489502</t>
   </si>
   <si>
     <t xml:space="preserve">16.190185546875</t>
@@ -2474,25 +2474,25 @@
     <t xml:space="preserve">15.5865678787231</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5286865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2144746780396</t>
+    <t xml:space="preserve">15.5286855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3467750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2144727706909</t>
   </si>
   <si>
     <t xml:space="preserve">15.2806253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8346300125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6527166366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692543029785</t>
+    <t xml:space="preserve">15.8346319198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6527185440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692562103271</t>
   </si>
   <si>
     <t xml:space="preserve">15.5782995223999</t>
@@ -2501,10 +2501,10 @@
     <t xml:space="preserve">15.7932863235474</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8594350814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633117675781</t>
+    <t xml:space="preserve">15.8594369888306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633108139038</t>
   </si>
   <si>
     <t xml:space="preserve">15.4294605255127</t>
@@ -2519,13 +2519,13 @@
     <t xml:space="preserve">16.3307552337646</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0501346588135</t>
+    <t xml:space="preserve">17.0501365661621</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">16.868221282959</t>
+    <t xml:space="preserve">16.8682231903076</t>
   </si>
   <si>
     <t xml:space="preserve">16.9509086608887</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">17.1162853240967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3312702178955</t>
+    <t xml:space="preserve">17.3312721252441</t>
   </si>
   <si>
     <t xml:space="preserve">17.51318359375</t>
@@ -2555,10 +2555,10 @@
     <t xml:space="preserve">17.4304962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3643455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3808822631836</t>
+    <t xml:space="preserve">17.3643436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3808860778809</t>
   </si>
   <si>
     <t xml:space="preserve">16.9839859008789</t>
@@ -2576,19 +2576,19 @@
     <t xml:space="preserve">16.7524604797363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0170574188232</t>
+    <t xml:space="preserve">17.0170593261719</t>
   </si>
   <si>
     <t xml:space="preserve">17.4635715484619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5958709716797</t>
+    <t xml:space="preserve">17.5958728790283</t>
   </si>
   <si>
     <t xml:space="preserve">17.4801082611084</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8439331054688</t>
+    <t xml:space="preserve">17.8439350128174</t>
   </si>
   <si>
     <t xml:space="preserve">17.9266204833984</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">17.992769241333</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0919933319092</t>
+    <t xml:space="preserve">18.0919914245605</t>
   </si>
   <si>
     <t xml:space="preserve">18.4227447509766</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4723567962646</t>
+    <t xml:space="preserve">18.4723587036133</t>
   </si>
   <si>
     <t xml:space="preserve">18.1581439971924</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">18.5054302215576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3896713256836</t>
+    <t xml:space="preserve">18.389669418335</t>
   </si>
   <si>
     <t xml:space="preserve">18.2739067077637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3235187530518</t>
+    <t xml:space="preserve">18.3235206604004</t>
   </si>
   <si>
     <t xml:space="preserve">18.3400573730469</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">18.0589218139648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.910083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2408294677734</t>
+    <t xml:space="preserve">17.9100818634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2408313751221</t>
   </si>
   <si>
     <t xml:space="preserve">18.3069820404053</t>
@@ -2651,25 +2651,25 @@
     <t xml:space="preserve">17.7943210601807</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7116355895996</t>
+    <t xml:space="preserve">17.711633682251</t>
   </si>
   <si>
     <t xml:space="preserve">17.5793342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3478088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4966430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3974208831787</t>
+    <t xml:space="preserve">17.347806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4966468811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3974227905273</t>
   </si>
   <si>
     <t xml:space="preserve">17.7447071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6046581268311</t>
+    <t xml:space="preserve">18.6046562194824</t>
   </si>
   <si>
     <t xml:space="preserve">18.7700309753418</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">18.3731307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6542701721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7534923553467</t>
+    <t xml:space="preserve">18.6542682647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7534942626953</t>
   </si>
   <si>
     <t xml:space="preserve">18.4062080383301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1416091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9431591033936</t>
+    <t xml:space="preserve">18.1416072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9431571960449</t>
   </si>
   <si>
     <t xml:space="preserve">18.1085319519043</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">17.7281703948975</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9596939086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1989727020264</t>
+    <t xml:space="preserve">17.95969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1989707946777</t>
   </si>
   <si>
     <t xml:space="preserve">16.6366958618164</t>
@@ -2711,22 +2711,22 @@
     <t xml:space="preserve">16.2894115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9503936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0413494110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5374717712402</t>
+    <t xml:space="preserve">15.9503917694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0413455963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5374736785889</t>
   </si>
   <si>
     <t xml:space="preserve">17.0832080841064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5627937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0666694641113</t>
+    <t xml:space="preserve">17.5627956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.06667137146</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155094146729</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">17.1658973693848</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0005226135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7028465270996</t>
+    <t xml:space="preserve">17.0005207061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178333282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7028484344482</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847599029541</t>
@@ -2753,16 +2753,16 @@
     <t xml:space="preserve">16.6201591491699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4795932769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0335941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1328201293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1824359893799</t>
+    <t xml:space="preserve">16.4795913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0335960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1328220367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1824340820312</t>
   </si>
   <si>
     <t xml:space="preserve">17.546257019043</t>
@@ -2777,37 +2777,37 @@
     <t xml:space="preserve">19.1669292449951</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3488445281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0599536895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9607257843018</t>
+    <t xml:space="preserve">19.348840713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0599555969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9607276916504</t>
   </si>
   <si>
     <t xml:space="preserve">20.5064659118652</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6883792877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7049179077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6718406677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8206748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7545299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9364395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7214546203613</t>
+    <t xml:space="preserve">20.6883773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7049160003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6718425750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8206768035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7545280456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9364414215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7214508056641</t>
   </si>
   <si>
     <t xml:space="preserve">21.0025901794434</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">21.1845035552979</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6806240081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1767501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9948387145996</t>
+    <t xml:space="preserve">21.6806259155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1767482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.994836807251</t>
   </si>
   <si>
     <t xml:space="preserve">22.5571117401123</t>
@@ -2837,22 +2837,22 @@
     <t xml:space="preserve">20.9529781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3002643585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5979404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4160251617432</t>
+    <t xml:space="preserve">21.3002681732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5979385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4160270690918</t>
   </si>
   <si>
     <t xml:space="preserve">21.8956127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.515251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8460006713867</t>
+    <t xml:space="preserve">21.5152530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8460025787354</t>
   </si>
   <si>
     <t xml:space="preserve">22.1602115631104</t>
@@ -2861,37 +2861,37 @@
     <t xml:space="preserve">21.5317897796631</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3664150238037</t>
+    <t xml:space="preserve">21.3664169311523</t>
   </si>
   <si>
     <t xml:space="preserve">20.7379913330078</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5726146697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2506504058838</t>
+    <t xml:space="preserve">20.5726184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2506542205811</t>
   </si>
   <si>
     <t xml:space="preserve">20.7876033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2584056854248</t>
+    <t xml:space="preserve">20.2584037780762</t>
   </si>
   <si>
     <t xml:space="preserve">19.6134395599365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1922550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3323059082031</t>
+    <t xml:space="preserve">20.192253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3323040008545</t>
   </si>
   <si>
     <t xml:space="preserve">18.9354038238525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2749423980713</t>
+    <t xml:space="preserve">20.2749404907227</t>
   </si>
   <si>
     <t xml:space="preserve">21.2010402679443</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">20.0103416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465167999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2253265380859</t>
+    <t xml:space="preserve">19.6465187072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2253284454346</t>
   </si>
   <si>
     <t xml:space="preserve">20.3410911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5560760498047</t>
+    <t xml:space="preserve">20.5560779571533</t>
   </si>
   <si>
     <t xml:space="preserve">20.638765335083</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">20.8868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5230045318604</t>
+    <t xml:space="preserve">20.5230026245117</t>
   </si>
   <si>
     <t xml:space="preserve">20.6056900024414</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">20.1095676422119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1514282226562</t>
+    <t xml:space="preserve">21.1514263153076</t>
   </si>
   <si>
     <t xml:space="preserve">20.6222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3080158233643</t>
+    <t xml:space="preserve">20.3080177307129</t>
   </si>
   <si>
     <t xml:space="preserve">20.4072399139404</t>
@@ -2969,16 +2969,16 @@
     <t xml:space="preserve">19.9772663116455</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3907012939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1261024475098</t>
+    <t xml:space="preserve">20.3907051086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1261043548584</t>
   </si>
   <si>
     <t xml:space="preserve">20.0764904022217</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2914810180664</t>
+    <t xml:space="preserve">20.2914791107178</t>
   </si>
   <si>
     <t xml:space="preserve">19.2661552429199</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">21.229097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1779441833496</t>
+    <t xml:space="preserve">21.177942276001</t>
   </si>
   <si>
     <t xml:space="preserve">21.4337158203125</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">21.6212825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3143558502197</t>
+    <t xml:space="preserve">21.3143577575684</t>
   </si>
   <si>
     <t xml:space="preserve">21.570125579834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.388599395752</t>
+    <t xml:space="preserve">22.3885974884033</t>
   </si>
   <si>
     <t xml:space="preserve">21.9793643951416</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">21.7406425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3655090332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4507675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6724376678467</t>
+    <t xml:space="preserve">21.3655071258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4507656097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.672435760498</t>
   </si>
   <si>
     <t xml:space="preserve">22.0987224578857</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">21.7065391540527</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9623126983643</t>
+    <t xml:space="preserve">21.9623146057129</t>
   </si>
   <si>
     <t xml:space="preserve">22.1328258514404</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">22.2692375183105</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7346057891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5470390319824</t>
+    <t xml:space="preserve">20.7346038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5470371246338</t>
   </si>
   <si>
     <t xml:space="preserve">21.2632026672363</t>
@@ -3119,13 +3119,13 @@
     <t xml:space="preserve">21.2973022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0926876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8539638519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0074291229248</t>
+    <t xml:space="preserve">21.0926856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8539657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0074272155762</t>
   </si>
   <si>
     <t xml:space="preserve">21.2802505493164</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">21.8088474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8941078186035</t>
+    <t xml:space="preserve">21.8941059112549</t>
   </si>
   <si>
     <t xml:space="preserve">21.7576942443848</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">21.3996124267578</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9111576080322</t>
+    <t xml:space="preserve">21.9111595153809</t>
   </si>
   <si>
     <t xml:space="preserve">22.5079574584961</t>
@@ -3158,31 +3158,31 @@
     <t xml:space="preserve">22.1669292449951</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0816707611084</t>
+    <t xml:space="preserve">22.081672668457</t>
   </si>
   <si>
     <t xml:space="preserve">22.013463973999</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4909076690674</t>
+    <t xml:space="preserve">22.4909057617188</t>
   </si>
   <si>
     <t xml:space="preserve">22.4227027893066</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2521858215332</t>
+    <t xml:space="preserve">22.2521877288818</t>
   </si>
   <si>
     <t xml:space="preserve">22.5761642456055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6614227294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7296276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.172966003418</t>
+    <t xml:space="preserve">22.6614208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7296295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1729679107666</t>
   </si>
   <si>
     <t xml:space="preserve">23.7697677612305</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">23.9232330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">25.219144821167</t>
+    <t xml:space="preserve">25.2191467285156</t>
   </si>
   <si>
     <t xml:space="preserve">25.4749164581299</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">26.6003150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6173648834229</t>
+    <t xml:space="preserve">26.6173667907715</t>
   </si>
   <si>
     <t xml:space="preserve">26.7708301544189</t>
@@ -3230,19 +3230,19 @@
     <t xml:space="preserve">25.969409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7196750640869</t>
+    <t xml:space="preserve">26.7196769714355</t>
   </si>
   <si>
     <t xml:space="preserve">26.3615951538086</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3104419708252</t>
+    <t xml:space="preserve">26.3104400634766</t>
   </si>
   <si>
     <t xml:space="preserve">26.5491600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2251834869385</t>
+    <t xml:space="preserve">26.2251815795898</t>
   </si>
   <si>
     <t xml:space="preserve">25.5431232452393</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">25.0315799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8269596099854</t>
+    <t xml:space="preserve">24.826961517334</t>
   </si>
   <si>
     <t xml:space="preserve">25.0145282745361</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">25.1168346405029</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8099117279053</t>
+    <t xml:space="preserve">24.8099098205566</t>
   </si>
   <si>
     <t xml:space="preserve">24.8440113067627</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">25.3896598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3836212158203</t>
+    <t xml:space="preserve">24.3836231231689</t>
   </si>
   <si>
     <t xml:space="preserve">24.1790046691895</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">24.1449012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1107978820801</t>
+    <t xml:space="preserve">24.1107997894287</t>
   </si>
   <si>
     <t xml:space="preserve">23.8038711547852</t>
@@ -3320,16 +3320,16 @@
     <t xml:space="preserve">24.2131061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3665733337402</t>
+    <t xml:space="preserve">24.3665714263916</t>
   </si>
   <si>
     <t xml:space="preserve">24.2472114562988</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2813129425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0486278533936</t>
+    <t xml:space="preserve">24.2813110351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0486297607422</t>
   </si>
   <si>
     <t xml:space="preserve">24.4347763061523</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">22.9342460632324</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7978324890137</t>
+    <t xml:space="preserve">22.7978343963623</t>
   </si>
   <si>
     <t xml:space="preserve">22.6443710327148</t>
@@ -3362,28 +3362,28 @@
     <t xml:space="preserve">21.8429508209229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1839809417725</t>
+    <t xml:space="preserve">22.1839828491211</t>
   </si>
   <si>
     <t xml:space="preserve">21.1949939727783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6383304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2120456695557</t>
+    <t xml:space="preserve">21.6383323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2120475769043</t>
   </si>
   <si>
     <t xml:space="preserve">20.9051208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6663990020752</t>
+    <t xml:space="preserve">20.6664009094238</t>
   </si>
   <si>
     <t xml:space="preserve">21.4678173065186</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0244789123535</t>
+    <t xml:space="preserve">21.0244808197021</t>
   </si>
   <si>
     <t xml:space="preserve">20.5640926361084</t>
@@ -3398,25 +3398,25 @@
     <t xml:space="preserve">20.2912654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1378021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6273193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0937480926514</t>
+    <t xml:space="preserve">20.1378040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6273212432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0937461853027</t>
   </si>
   <si>
     <t xml:space="preserve">23.616304397583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7637329101562</t>
+    <t xml:space="preserve">22.7637310028076</t>
   </si>
   <si>
     <t xml:space="preserve">22.8148860931396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6102695465088</t>
+    <t xml:space="preserve">22.6102714538574</t>
   </si>
   <si>
     <t xml:space="preserve">24.1619529724121</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">25.560173034668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9292697906494</t>
+    <t xml:space="preserve">24.9292678833008</t>
   </si>
   <si>
     <t xml:space="preserve">24.8951683044434</t>
@@ -3437,16 +3437,16 @@
     <t xml:space="preserve">25.2873497009277</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7136363983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6564464569092</t>
+    <t xml:space="preserve">25.7136383056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6564445495605</t>
   </si>
   <si>
     <t xml:space="preserve">25.1850433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9804248809814</t>
+    <t xml:space="preserve">24.9804229736328</t>
   </si>
   <si>
     <t xml:space="preserve">25.6624851226807</t>
@@ -3461,22 +3461,22 @@
     <t xml:space="preserve">26.8049335479736</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7537803649902</t>
+    <t xml:space="preserve">26.7537784576416</t>
   </si>
   <si>
     <t xml:space="preserve">26.9413471221924</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0436515808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0948085784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8219833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9924983978271</t>
+    <t xml:space="preserve">27.0436534881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0948104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.821985244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9925003051758</t>
   </si>
   <si>
     <t xml:space="preserve">27.1459617614746</t>
@@ -3497,13 +3497,13 @@
     <t xml:space="preserve">27.7939186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8621234893799</t>
+    <t xml:space="preserve">27.8621253967285</t>
   </si>
   <si>
     <t xml:space="preserve">28.0496940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5893020629883</t>
+    <t xml:space="preserve">27.5893039703369</t>
   </si>
   <si>
     <t xml:space="preserve">27.1800670623779</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">25.3555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3214530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9864597320557</t>
+    <t xml:space="preserve">25.3214550018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9864616394043</t>
   </si>
   <si>
     <t xml:space="preserve">25.3385047912598</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">26.8901920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7598171234131</t>
+    <t xml:space="preserve">27.7598190307617</t>
   </si>
   <si>
     <t xml:space="preserve">28.4759788513184</t>
@@ -3542,34 +3542,34 @@
     <t xml:space="preserve">28.5100803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6976509094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9875240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4604301452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4954605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.055944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5655193328857</t>
+    <t xml:space="preserve">28.6976490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9875221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4604320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4954624176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5655212402344</t>
   </si>
   <si>
     <t xml:space="preserve">28.724796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6197052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3394641876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1993446350098</t>
+    <t xml:space="preserve">28.6197071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3394660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1993427276611</t>
   </si>
   <si>
     <t xml:space="preserve">28.3044338226318</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">28.8824329376221</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0575828552246</t>
+    <t xml:space="preserve">29.0575847625732</t>
   </si>
   <si>
     <t xml:space="preserve">29.1451568603516</t>
@@ -3596,19 +3596,19 @@
     <t xml:space="preserve">26.3427410125732</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8681926727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.009952545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9924392700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.957405090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.607105255127</t>
+    <t xml:space="preserve">26.8681945800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0099544525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9924373626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9574069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6071033477783</t>
   </si>
   <si>
     <t xml:space="preserve">26.5178928375244</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">26.1675891876221</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9382553100586</t>
+    <t xml:space="preserve">26.93825340271</t>
   </si>
   <si>
     <t xml:space="preserve">26.9732837677002</t>
@@ -3641,13 +3641,13 @@
     <t xml:space="preserve">27.1309204101562</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4286785125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.341100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7455902099609</t>
+    <t xml:space="preserve">27.4286766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3411026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7455883026123</t>
   </si>
   <si>
     <t xml:space="preserve">26.9907989501953</t>
@@ -3668,16 +3668,16 @@
     <t xml:space="preserve">26.3602561950684</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6930408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5879516601562</t>
+    <t xml:space="preserve">26.693042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5879535675049</t>
   </si>
   <si>
     <t xml:space="preserve">27.1834678649902</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5512828826904</t>
+    <t xml:space="preserve">27.5512847900391</t>
   </si>
   <si>
     <t xml:space="preserve">27.884069442749</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">29.6706123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7757053375244</t>
+    <t xml:space="preserve">29.7757034301758</t>
   </si>
   <si>
     <t xml:space="preserve">29.6530990600586</t>
@@ -3713,37 +3713,37 @@
     <t xml:space="preserve">30.1260070800781</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3186702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8632755279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.950855255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4412784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.15940284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3361873626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1785526275635</t>
+    <t xml:space="preserve">30.3186740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8632793426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9508571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.441276550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1593990325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3361854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1785488128662</t>
   </si>
   <si>
     <t xml:space="preserve">29.7406730651855</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7089195251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4987373352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0258312225342</t>
+    <t xml:space="preserve">27.7089176177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4987392425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0258293151855</t>
   </si>
   <si>
     <t xml:space="preserve">26.1851024627686</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">27.8490409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2694034576416</t>
+    <t xml:space="preserve">28.269401550293</t>
   </si>
   <si>
     <t xml:space="preserve">28.1643142700195</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">29.0926151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7598285675049</t>
+    <t xml:space="preserve">28.7598266601562</t>
   </si>
   <si>
     <t xml:space="preserve">29.1801910400391</t>
@@ -3782,28 +3782,28 @@
     <t xml:space="preserve">27.8665542602539</t>
   </si>
   <si>
-    <t xml:space="preserve">25.169225692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.064136505127</t>
+    <t xml:space="preserve">25.1692276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0641384124756</t>
   </si>
   <si>
     <t xml:space="preserve">24.5912284851074</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7488651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2726802825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1659507751465</t>
+    <t xml:space="preserve">24.7488632202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2726783752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1659526824951</t>
   </si>
   <si>
     <t xml:space="preserve">25.0816516876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9415302276611</t>
+    <t xml:space="preserve">24.9415283203125</t>
   </si>
   <si>
     <t xml:space="preserve">24.4335918426514</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">24.9065017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5545616149902</t>
+    <t xml:space="preserve">25.5545597076416</t>
   </si>
   <si>
     <t xml:space="preserve">25.7472267150879</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">25.6946811676025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9048614501953</t>
+    <t xml:space="preserve">25.9048633575439</t>
   </si>
   <si>
     <t xml:space="preserve">25.6771659851074</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">27.0783767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7806186676025</t>
+    <t xml:space="preserve">26.7806205749512</t>
   </si>
   <si>
     <t xml:space="preserve">27.6738910675049</t>
@@ -3851,16 +3851,16 @@
     <t xml:space="preserve">27.2535285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4812240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.936616897583</t>
+    <t xml:space="preserve">27.48122215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9366149902344</t>
   </si>
   <si>
     <t xml:space="preserve">28.8649158477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7631034851074</t>
+    <t xml:space="preserve">26.7631015777588</t>
   </si>
   <si>
     <t xml:space="preserve">26.9032230377197</t>
@@ -3881,13 +3881,13 @@
     <t xml:space="preserve">25.9223785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3777713775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5003757476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1325569152832</t>
+    <t xml:space="preserve">26.3777694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5003776550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1325588226318</t>
   </si>
   <si>
     <t xml:space="preserve">26.0975284576416</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">24.3285007476807</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7838935852051</t>
+    <t xml:space="preserve">24.7838954925537</t>
   </si>
   <si>
     <t xml:space="preserve">24.8539562225342</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">24.3109874725342</t>
   </si>
   <si>
-    <t xml:space="preserve">24.22340965271</t>
+    <t xml:space="preserve">24.2234115600586</t>
   </si>
   <si>
     <t xml:space="preserve">24.3460159301758</t>
@@ -3965,19 +3965,19 @@
     <t xml:space="preserve">24.3985633850098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6788024902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9590454101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0466194152832</t>
+    <t xml:space="preserve">24.678804397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9590473175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0466213226318</t>
   </si>
   <si>
     <t xml:space="preserve">24.7138328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5036506652832</t>
+    <t xml:space="preserve">24.5036525726318</t>
   </si>
   <si>
     <t xml:space="preserve">24.6612892150879</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">23.8731079101562</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3476543426514</t>
+    <t xml:space="preserve">23.34765625</t>
   </si>
   <si>
     <t xml:space="preserve">23.7154731750488</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">23.1900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2425632476807</t>
+    <t xml:space="preserve">23.2425651550293</t>
   </si>
   <si>
     <t xml:space="preserve">23.6979560852051</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">23.0849285125732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3826866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5228061676025</t>
+    <t xml:space="preserve">23.3826847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5228080749512</t>
   </si>
   <si>
     <t xml:space="preserve">23.9606838226318</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">25.2217712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2042598724365</t>
+    <t xml:space="preserve">25.2042579650879</t>
   </si>
   <si>
     <t xml:space="preserve">25.1341972351074</t>
@@ -4082,19 +4082,19 @@
     <t xml:space="preserve">24.6262588500977</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3635330200195</t>
+    <t xml:space="preserve">24.3635311126709</t>
   </si>
   <si>
     <t xml:space="preserve">23.7855319976807</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2250499725342</t>
+    <t xml:space="preserve">23.2250518798828</t>
   </si>
   <si>
     <t xml:space="preserve">22.9798374176025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2775955200195</t>
+    <t xml:space="preserve">23.2775936126709</t>
   </si>
   <si>
     <t xml:space="preserve">23.295108795166</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">24.0657749176025</t>
   </si>
   <si>
-    <t xml:space="preserve">24.76637840271</t>
+    <t xml:space="preserve">24.7663803100586</t>
   </si>
   <si>
     <t xml:space="preserve">24.7313499450684</t>
@@ -25891,7 +25891,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G773" t="s">
-        <v>430</v>
+        <v>565</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25943,7 +25943,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G775" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25995,7 +25995,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G777" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -26021,7 +26021,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G778" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -26047,7 +26047,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G779" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -26073,7 +26073,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G780" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -26125,7 +26125,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G782" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -26151,7 +26151,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G783" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -26177,7 +26177,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G784" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -26255,7 +26255,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G787" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26281,7 +26281,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G788" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -26307,7 +26307,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G789" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -26333,7 +26333,7 @@
         <v>17.5</v>
       </c>
       <c r="G790" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26437,7 +26437,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G794" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -26463,7 +26463,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G795" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26541,7 +26541,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G798" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26593,7 +26593,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G800" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -26619,7 +26619,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G801" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -26645,7 +26645,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26697,7 +26697,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G804" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26723,7 +26723,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G805" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26749,7 +26749,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G806" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26775,7 +26775,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G807" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26801,7 +26801,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G808" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26827,7 +26827,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G809" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26853,7 +26853,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G810" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26879,7 +26879,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G811" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26905,7 +26905,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G812" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26931,7 +26931,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G813" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26957,7 +26957,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G814" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -27009,7 +27009,7 @@
         <v>16.75</v>
       </c>
       <c r="G816" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -27035,7 +27035,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G817" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -27087,7 +27087,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G819" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -27113,7 +27113,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G820" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27165,7 +27165,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G822" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -27347,7 +27347,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G829" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -27399,7 +27399,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G831" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -27425,7 +27425,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G832" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27555,7 +27555,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G837" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -27659,7 +27659,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G841" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27711,7 +27711,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G843" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27737,7 +27737,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G844" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27763,7 +27763,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G845" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27815,7 +27815,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G847" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27893,7 +27893,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G850" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27919,7 +27919,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G851" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27971,7 +27971,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G853" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27997,7 +27997,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G854" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28023,7 +28023,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G855" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28049,7 +28049,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G856" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28075,7 +28075,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G857" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28101,7 +28101,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G858" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28127,7 +28127,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G859" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28153,7 +28153,7 @@
         <v>17</v>
       </c>
       <c r="G860" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28179,7 +28179,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G861" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28205,7 +28205,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G862" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28231,7 +28231,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G863" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28257,7 +28257,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G864" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28283,7 +28283,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G865" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28309,7 +28309,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G866" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28335,7 +28335,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G867" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28361,7 +28361,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G868" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28387,7 +28387,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G869" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28413,7 +28413,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G870" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28439,7 +28439,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G871" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28465,7 +28465,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G872" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28491,7 +28491,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G873" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28517,7 +28517,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G874" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28543,7 +28543,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G875" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28569,7 +28569,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G876" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28595,7 +28595,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G877" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -28621,7 +28621,7 @@
         <v>18</v>
       </c>
       <c r="G878" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28647,7 +28647,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G879" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28673,7 +28673,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G880" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -28699,7 +28699,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G881" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -28725,7 +28725,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G882" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -28751,7 +28751,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28777,7 +28777,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G884" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -28803,7 +28803,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G885" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28829,7 +28829,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G886" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28855,7 +28855,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G887" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28881,7 +28881,7 @@
         <v>18</v>
       </c>
       <c r="G888" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28907,7 +28907,7 @@
         <v>18</v>
       </c>
       <c r="G889" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28933,7 +28933,7 @@
         <v>18.25</v>
       </c>
       <c r="G890" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28959,7 +28959,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G891" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -28985,7 +28985,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G892" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -29011,7 +29011,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G893" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29037,7 +29037,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G894" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29063,7 +29063,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29089,7 +29089,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G896" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29115,7 +29115,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G897" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29141,7 +29141,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G898" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29167,7 +29167,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G899" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29193,7 +29193,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29219,7 +29219,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G901" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29245,7 +29245,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G902" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29271,7 +29271,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G903" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29297,7 +29297,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G904" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29323,7 +29323,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G905" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29349,7 +29349,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G906" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29375,7 +29375,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G907" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29401,7 +29401,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G908" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29427,7 +29427,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G909" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29453,7 +29453,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G910" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29479,7 +29479,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G911" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29505,7 +29505,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G912" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29531,7 +29531,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G913" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29557,7 +29557,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G914" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29583,7 +29583,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G915" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29609,7 +29609,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G916" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29635,7 +29635,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G917" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29661,7 +29661,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G918" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29687,7 +29687,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G919" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29713,7 +29713,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G920" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29739,7 +29739,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G921" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -29765,7 +29765,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -29791,7 +29791,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G923" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -29817,7 +29817,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G924" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -29843,7 +29843,7 @@
         <v>17.5</v>
       </c>
       <c r="G925" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29869,7 +29869,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G926" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29895,7 +29895,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G927" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29921,7 +29921,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G928" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29947,7 +29947,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G929" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29973,7 +29973,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G930" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -29999,7 +29999,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G931" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30025,7 +30025,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G932" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30051,7 +30051,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G933" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30077,7 +30077,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G934" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30103,7 +30103,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G935" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30129,7 +30129,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G936" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30155,7 +30155,7 @@
         <v>18.25</v>
       </c>
       <c r="G937" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30181,7 +30181,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G938" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30207,7 +30207,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G939" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30233,7 +30233,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G940" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30259,7 +30259,7 @@
         <v>18</v>
       </c>
       <c r="G941" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30285,7 +30285,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G942" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30311,7 +30311,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G943" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30337,7 +30337,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G944" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30363,7 +30363,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G945" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30389,7 +30389,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G946" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30415,7 +30415,7 @@
         <v>18.75</v>
       </c>
       <c r="G947" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30441,7 +30441,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G948" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -30467,7 +30467,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G949" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -30493,7 +30493,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G950" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30519,7 +30519,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G951" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30545,7 +30545,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G952" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -30571,7 +30571,7 @@
         <v>18.5</v>
       </c>
       <c r="G953" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30597,7 +30597,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G954" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30623,7 +30623,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G955" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -30649,7 +30649,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G956" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -30675,7 +30675,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G957" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30701,7 +30701,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G958" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30727,7 +30727,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G959" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -30753,7 +30753,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G960" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -30779,7 +30779,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G961" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -30805,7 +30805,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G962" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -30831,7 +30831,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G963" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30857,7 +30857,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30883,7 +30883,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G965" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30909,7 +30909,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G966" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30935,7 +30935,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G967" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -30961,7 +30961,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G968" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -30987,7 +30987,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G969" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31013,7 +31013,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G970" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31039,7 +31039,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G971" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31065,7 +31065,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G972" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31091,7 +31091,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G973" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31117,7 +31117,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G974" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31143,7 +31143,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G975" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31169,7 +31169,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G976" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31195,7 +31195,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31221,7 +31221,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31247,7 +31247,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G979" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31273,7 +31273,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G980" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31299,7 +31299,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G981" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31325,7 +31325,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G982" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31351,7 +31351,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G983" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31377,7 +31377,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G984" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31403,7 +31403,7 @@
         <v>18.75</v>
       </c>
       <c r="G985" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -31429,7 +31429,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G986" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -31455,7 +31455,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G987" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -31481,7 +31481,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G988" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31507,7 +31507,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G989" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -31533,7 +31533,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G990" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -31559,7 +31559,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G991" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -31585,7 +31585,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G992" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31611,7 +31611,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -31637,7 +31637,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G994" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31663,7 +31663,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G995" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -31689,7 +31689,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G996" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -31715,7 +31715,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G997" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -31741,7 +31741,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -31767,7 +31767,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G999" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -31793,7 +31793,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1000" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -31819,7 +31819,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1001" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -31845,7 +31845,7 @@
         <v>19.25</v>
       </c>
       <c r="G1002" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -31871,7 +31871,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1003" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -31897,7 +31897,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -31923,7 +31923,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1005" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31949,7 +31949,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1006" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -31975,7 +31975,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1007" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32001,7 +32001,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32027,7 +32027,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32053,7 +32053,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1010" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32079,7 +32079,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G1011" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32105,7 +32105,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1012" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32131,7 +32131,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1013" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32157,7 +32157,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1014" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32183,7 +32183,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1015" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32209,7 +32209,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1016" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32235,7 +32235,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1017" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32261,7 +32261,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G1018" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32287,7 +32287,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1019" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32313,7 +32313,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1020" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32339,7 +32339,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1021" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32365,7 +32365,7 @@
         <v>19.75</v>
       </c>
       <c r="G1022" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32391,7 +32391,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1023" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32417,7 +32417,7 @@
         <v>20.5</v>
       </c>
       <c r="G1024" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -32443,7 +32443,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1025" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -32469,7 +32469,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -32495,7 +32495,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1027" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -32521,7 +32521,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1028" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -32547,7 +32547,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -32573,7 +32573,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -32599,7 +32599,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1031" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32625,7 +32625,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G1032" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -32651,7 +32651,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1033" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -32677,7 +32677,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1034" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -32703,7 +32703,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1035" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -32729,7 +32729,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G1036" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -32755,7 +32755,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G1037" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -32781,7 +32781,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1038" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -32807,7 +32807,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1039" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -32833,7 +32833,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1040" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -32859,7 +32859,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1041" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -32885,7 +32885,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1042" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -32911,7 +32911,7 @@
         <v>22</v>
       </c>
       <c r="G1043" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -32937,7 +32937,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1044" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -32963,7 +32963,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1045" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -32989,7 +32989,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1046" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -33015,7 +33015,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1047" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -33041,7 +33041,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1048" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -33067,7 +33067,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G1049" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -33093,7 +33093,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G1050" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -33119,7 +33119,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G1051" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -33145,7 +33145,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1052" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -33171,7 +33171,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1053" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -33197,7 +33197,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -33223,7 +33223,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G1055" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -33249,7 +33249,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1056" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -33275,7 +33275,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -33301,7 +33301,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1058" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -33327,7 +33327,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1059" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -33353,7 +33353,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G1060" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -33379,7 +33379,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1061" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -33405,7 +33405,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1062" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -33431,7 +33431,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1063" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33457,7 +33457,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1064" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -33483,7 +33483,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1065" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -33509,7 +33509,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1066" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -33535,7 +33535,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1067" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -33561,7 +33561,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -33587,7 +33587,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1069" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -33613,7 +33613,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1070" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -33639,7 +33639,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1071" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -33665,7 +33665,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1072" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -33691,7 +33691,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1073" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -33717,7 +33717,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1074" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -33743,7 +33743,7 @@
         <v>15.25</v>
       </c>
       <c r="G1075" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -33769,7 +33769,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1076" t="s">
-        <v>778</v>
+        <v>606</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -34107,7 +34107,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1089" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -34237,7 +34237,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1094" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -34315,7 +34315,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1097" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -34419,7 +34419,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1101" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34497,7 +34497,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -34601,7 +34601,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G1108" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -70983,7 +70983,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6914699074</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>239080</v>
@@ -71004,6 +71004,32 @@
         <v>1800</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6910532407</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>317304</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>22.5400009155273</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>22.2999992370605</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>22.4799995422363</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>22.3600006103516</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1812</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="1823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="1824">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,142 +38,142 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48755550384521</t>
+    <t xml:space="preserve">7.4875545501709</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43893337249756</t>
+    <t xml:space="preserve">7.43893480300903</t>
   </si>
   <si>
     <t xml:space="preserve">7.23837471008301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0438928604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99527168273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06212520599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25053024291992</t>
+    <t xml:space="preserve">7.04389238357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99527215957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06212568283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25052976608276</t>
   </si>
   <si>
     <t xml:space="preserve">7.22014188766479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1715202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07428026199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84941148757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01350450515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75217008590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83725595474243</t>
+    <t xml:space="preserve">7.17152118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07428073883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84941053390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01350498199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75217056274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83725500106812</t>
   </si>
   <si>
     <t xml:space="preserve">6.97096157073975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09251260757446</t>
+    <t xml:space="preserve">7.09251356124878</t>
   </si>
   <si>
     <t xml:space="preserve">7.00742721557617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00135087966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98919534683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92841768264771</t>
+    <t xml:space="preserve">7.00135040283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98919486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92841863632202</t>
   </si>
   <si>
     <t xml:space="preserve">6.86156511306763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53337717056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47867918014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61238622665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5516095161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77647972106934</t>
+    <t xml:space="preserve">6.5333776473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47868013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61238527297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55160856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77648019790649</t>
   </si>
   <si>
     <t xml:space="preserve">6.94057464599609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87372159957886</t>
+    <t xml:space="preserve">6.87372255325317</t>
   </si>
   <si>
     <t xml:space="preserve">6.63061857223511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78863573074341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58199787139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70354843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71570491790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80686855316162</t>
+    <t xml:space="preserve">6.78863525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58199691772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70354795455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71570444107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80686712265015</t>
   </si>
   <si>
     <t xml:space="preserve">6.91626453399658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84333229064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83117771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87979698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70962715148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74609136581421</t>
+    <t xml:space="preserve">6.84333324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83117723464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.879798412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7096266746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74609184265137</t>
   </si>
   <si>
     <t xml:space="preserve">6.85548782348633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8676438331604</t>
+    <t xml:space="preserve">6.86764335632324</t>
   </si>
   <si>
     <t xml:space="preserve">6.95272874832153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04996967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27483987808228</t>
+    <t xml:space="preserve">7.04997062683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27483940124512</t>
   </si>
   <si>
     <t xml:space="preserve">7.35992527008057</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">7.34777164459229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26876211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22621870040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11074590682983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03173732757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08035802841187</t>
+    <t xml:space="preserve">7.26876306533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22621965408325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11074495315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03173780441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08035755157471</t>
   </si>
   <si>
     <t xml:space="preserve">7.05604791641235</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">7.18975448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23229789733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15328884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11682319641113</t>
+    <t xml:space="preserve">7.23229694366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1532883644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11682224273682</t>
   </si>
   <si>
     <t xml:space="preserve">7.16544389724731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95880746841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93449640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89803075790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90410900115967</t>
+    <t xml:space="preserve">6.95880603790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93449687957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89803171157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90410804748535</t>
   </si>
   <si>
     <t xml:space="preserve">6.96488332748413</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">6.79471302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76432466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14113330841064</t>
+    <t xml:space="preserve">6.76432418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14113283157349</t>
   </si>
   <si>
     <t xml:space="preserve">7.02566003799438</t>
@@ -248,49 +248,49 @@
     <t xml:space="preserve">7.13741254806519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3105206489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25725603103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34381151199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38376045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29720640182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25059986114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21730947494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062467575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23728275299072</t>
+    <t xml:space="preserve">7.31052112579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25725746154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34381103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38376092910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29720592498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25060033798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21730899810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23728370666504</t>
   </si>
   <si>
     <t xml:space="preserve">7.27723217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22396755218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10412359237671</t>
+    <t xml:space="preserve">7.2239670753479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10412311553955</t>
   </si>
   <si>
     <t xml:space="preserve">6.85777521133423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65803527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60477018356323</t>
+    <t xml:space="preserve">6.658034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60477066040039</t>
   </si>
   <si>
     <t xml:space="preserve">6.474937915802</t>
@@ -299,73 +299,73 @@
     <t xml:space="preserve">6.50822830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95764636993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93767166137695</t>
+    <t xml:space="preserve">6.95764493942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93767070770264</t>
   </si>
   <si>
     <t xml:space="preserve">6.82448530197144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88440656661987</t>
+    <t xml:space="preserve">6.88440799713135</t>
   </si>
   <si>
     <t xml:space="preserve">6.47826671600342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3218035697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56149244308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69132328033447</t>
+    <t xml:space="preserve">6.32180309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5614914894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69132518768311</t>
   </si>
   <si>
     <t xml:space="preserve">6.81782722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91769742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03754281997681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78453683853149</t>
+    <t xml:space="preserve">6.9176983833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03754186630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78453588485718</t>
   </si>
   <si>
     <t xml:space="preserve">6.50489950180054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61808586120605</t>
+    <t xml:space="preserve">6.61808633804321</t>
   </si>
   <si>
     <t xml:space="preserve">6.71795606613159</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6846661567688</t>
+    <t xml:space="preserve">6.68466663360596</t>
   </si>
   <si>
     <t xml:space="preserve">6.73793029785156</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8777494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81116962432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75124645233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79119539260864</t>
+    <t xml:space="preserve">6.87774848937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81116914749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7512469291687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79119443893433</t>
   </si>
   <si>
     <t xml:space="preserve">6.76456308364868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86443328857422</t>
+    <t xml:space="preserve">6.86443376541138</t>
   </si>
   <si>
     <t xml:space="preserve">6.77122068405151</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">6.73127222061157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64471769332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63806056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75790452957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83114290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80451154708862</t>
+    <t xml:space="preserve">6.64471817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63806009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75790405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83114337921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80451011657715</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101453781128</t>
@@ -398,28 +398,28 @@
     <t xml:space="preserve">6.96430349349976</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74458837509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71129751205444</t>
+    <t xml:space="preserve">6.74458885192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7112979888916</t>
   </si>
   <si>
     <t xml:space="preserve">6.65137624740601</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62807321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64138984680176</t>
+    <t xml:space="preserve">6.6280722618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64139032363892</t>
   </si>
   <si>
     <t xml:space="preserve">6.62141466140747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01756811141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98427772521973</t>
+    <t xml:space="preserve">7.01756858825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98427820205688</t>
   </si>
   <si>
     <t xml:space="preserve">7.01091003417969</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">7.17070341110229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87109136581421</t>
+    <t xml:space="preserve">6.87108993530273</t>
   </si>
   <si>
     <t xml:space="preserve">6.92435455322266</t>
@@ -443,22 +443,22 @@
     <t xml:space="preserve">6.83780145645142</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84445858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79785299301147</t>
+    <t xml:space="preserve">6.84446001052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79785346984863</t>
   </si>
   <si>
     <t xml:space="preserve">6.77787923812866</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5981125831604</t>
+    <t xml:space="preserve">6.59811162948608</t>
   </si>
   <si>
     <t xml:space="preserve">6.55150604248047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72461462020874</t>
+    <t xml:space="preserve">6.7246150970459</t>
   </si>
   <si>
     <t xml:space="preserve">6.67135047912598</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">6.66469192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60809993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54484748840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45829296112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65470504760742</t>
+    <t xml:space="preserve">6.60809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54484796524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45829248428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65470457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.67800807952881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46495151519775</t>
+    <t xml:space="preserve">6.4649510383606</t>
   </si>
   <si>
     <t xml:space="preserve">6.13870763778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22859048843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1919732093811</t>
+    <t xml:space="preserve">6.228590965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19197273254395</t>
   </si>
   <si>
     <t xml:space="preserve">6.17865562438965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24856519699097</t>
+    <t xml:space="preserve">6.24856567382812</t>
   </si>
   <si>
     <t xml:space="preserve">6.13537836074829</t>
@@ -509,43 +509,43 @@
     <t xml:space="preserve">6.16866874694824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15868091583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14203643798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0621395111084</t>
+    <t xml:space="preserve">6.15868139266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14203691482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06213903427124</t>
   </si>
   <si>
     <t xml:space="preserve">6.03883695602417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10874557495117</t>
+    <t xml:space="preserve">6.10874700546265</t>
   </si>
   <si>
     <t xml:space="preserve">6.0588116645813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02219200134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01886224746704</t>
+    <t xml:space="preserve">6.02219152450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0188627243042</t>
   </si>
   <si>
     <t xml:space="preserve">6.11873292922974</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23191928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12206268310547</t>
+    <t xml:space="preserve">6.23191976547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12206220626831</t>
   </si>
   <si>
     <t xml:space="preserve">6.22193288803101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21860456466675</t>
+    <t xml:space="preserve">6.21860408782959</t>
   </si>
   <si>
     <t xml:space="preserve">6.35842227935791</t>
@@ -554,16 +554,16 @@
     <t xml:space="preserve">6.37839603424072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62474393844604</t>
+    <t xml:space="preserve">6.6247444152832</t>
   </si>
   <si>
     <t xml:space="preserve">6.70464038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8511176109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69798135757446</t>
+    <t xml:space="preserve">6.85111713409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69798278808594</t>
   </si>
   <si>
     <t xml:space="preserve">6.904381275177</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">6.99093532562256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07749080657959</t>
+    <t xml:space="preserve">7.07748985290527</t>
   </si>
   <si>
     <t xml:space="preserve">6.91104030609131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07083225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13075399398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15072774887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18401861190796</t>
+    <t xml:space="preserve">7.07083177566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1307544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15072822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18401956558228</t>
   </si>
   <si>
     <t xml:space="preserve">7.0974645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3504695892334</t>
+    <t xml:space="preserve">7.05085945129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35046911239624</t>
   </si>
   <si>
     <t xml:space="preserve">7.27057313919067</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">7.28388786315918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30386352539062</t>
+    <t xml:space="preserve">7.30386400222778</t>
   </si>
   <si>
     <t xml:space="preserve">7.53023815155029</t>
@@ -617,115 +617,115 @@
     <t xml:space="preserve">7.3238377571106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31717920303345</t>
+    <t xml:space="preserve">7.31717967987061</t>
   </si>
   <si>
     <t xml:space="preserve">7.36378622055054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.516921043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59015893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347461700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000337600708</t>
+    <t xml:space="preserve">7.51692008972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59015798568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347509384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71000242233276</t>
   </si>
   <si>
     <t xml:space="preserve">7.76992607116699</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77658367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73663568496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7898998260498</t>
+    <t xml:space="preserve">7.77658271789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73663663864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78990077972412</t>
   </si>
   <si>
     <t xml:space="preserve">7.75660991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82319164276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85647964477539</t>
+    <t xml:space="preserve">7.82319068908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85648107528687</t>
   </si>
   <si>
     <t xml:space="preserve">7.86979675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87645387649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96966695785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94969272613525</t>
+    <t xml:space="preserve">7.87645483016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9030876159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96966600418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94969177246094</t>
   </si>
   <si>
     <t xml:space="preserve">7.92306089401245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96300935745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311147689819</t>
+    <t xml:space="preserve">7.96300840377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311243057251</t>
   </si>
   <si>
     <t xml:space="preserve">7.72332000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62344932556152</t>
+    <t xml:space="preserve">7.62344884872437</t>
   </si>
   <si>
     <t xml:space="preserve">7.5435528755188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47031450271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6367654800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56352663040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5701847076416</t>
+    <t xml:space="preserve">7.47031545639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56352567672729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57018566131592</t>
   </si>
   <si>
     <t xml:space="preserve">7.74329423904419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80321550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89642906188965</t>
+    <t xml:space="preserve">7.80321645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89642810821533</t>
   </si>
   <si>
     <t xml:space="preserve">7.94303512573242</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8498215675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06953811645508</t>
+    <t xml:space="preserve">7.84982252120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06953716278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.20842742919922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22926044464111</t>
+    <t xml:space="preserve">8.25009536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22926235198975</t>
   </si>
   <si>
     <t xml:space="preserve">8.31953907012939</t>
@@ -737,37 +737,37 @@
     <t xml:space="preserve">8.28481769561768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2987060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37509727478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34731864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38898468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43759727478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45148658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68760108947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73621082305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62509822845459</t>
+    <t xml:space="preserve">8.29870700836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37509632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34731769561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3889856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43759632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4514856338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68760013580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7362117767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62510013580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.63898849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66676712036133</t>
+    <t xml:space="preserve">8.66676616668701</t>
   </si>
   <si>
     <t xml:space="preserve">8.68065547943115</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">8.59732151031494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69454574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61121082305908</t>
+    <t xml:space="preserve">8.72926807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69454383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61120986938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.50704193115234</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">8.52787590026855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54870986938477</t>
+    <t xml:space="preserve">8.54870891571045</t>
   </si>
   <si>
     <t xml:space="preserve">8.4931526184082</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">8.47231864929199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61815547943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65982341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40981864929199</t>
+    <t xml:space="preserve">8.61815452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65982246398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64593410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40981960296631</t>
   </si>
   <si>
     <t xml:space="preserve">8.4306526184082</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">8.7153787612915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88204765319824</t>
+    <t xml:space="preserve">8.88204669952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.00010395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15288352966309</t>
+    <t xml:space="preserve">9.15288257598877</t>
   </si>
   <si>
     <t xml:space="preserve">9.13204860687256</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">9.06954956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09038257598877</t>
+    <t xml:space="preserve">9.09038352966309</t>
   </si>
   <si>
     <t xml:space="preserve">9.00704860687256</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">8.95843601226807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0626049041748</t>
+    <t xml:space="preserve">9.06260395050049</t>
   </si>
   <si>
     <t xml:space="preserve">9.1251049041748</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">9.29871845245361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3681640625</t>
+    <t xml:space="preserve">9.36816310882568</t>
   </si>
   <si>
     <t xml:space="preserve">9.40983009338379</t>
@@ -896,79 +896,79 @@
     <t xml:space="preserve">9.29177379608154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31260776519775</t>
+    <t xml:space="preserve">9.31260681152344</t>
   </si>
   <si>
     <t xml:space="preserve">9.45149803161621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47233104705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43760776519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44455242156982</t>
+    <t xml:space="preserve">9.47233200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43760871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44455432891846</t>
   </si>
   <si>
     <t xml:space="preserve">9.40288543701172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38899612426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38205146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34038639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34733104705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31955337524414</t>
+    <t xml:space="preserve">9.38899707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38205242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34038543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34732818603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31955242156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.48622035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75011157989502</t>
+    <t xml:space="preserve">9.75011253356934</t>
   </si>
   <si>
     <t xml:space="preserve">9.79177951812744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77788925170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80566883087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72927856445312</t>
+    <t xml:space="preserve">9.7778902053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80566787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72927761077881</t>
   </si>
   <si>
     <t xml:space="preserve">9.77094554901123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76400184631348</t>
+    <t xml:space="preserve">9.76400089263916</t>
   </si>
   <si>
     <t xml:space="preserve">9.74316692352295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96539306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0278930664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93761539459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0834484100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1181707382202</t>
+    <t xml:space="preserve">9.96539402008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0278921127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93761444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0834493637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1181726455688</t>
   </si>
   <si>
     <t xml:space="preserve">10.1876173019409</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">10.5001211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5695667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2292833328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3959522247314</t>
+    <t xml:space="preserve">10.5695657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.229284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3959531784058</t>
   </si>
   <si>
     <t xml:space="preserve">10.4237308502197</t>
@@ -995,22 +995,22 @@
     <t xml:space="preserve">10.5903997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4931764602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5626220703125</t>
+    <t xml:space="preserve">10.4931755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5626201629639</t>
   </si>
   <si>
     <t xml:space="preserve">10.6251230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6042900085449</t>
+    <t xml:space="preserve">10.6042890548706</t>
   </si>
   <si>
     <t xml:space="preserve">10.701512336731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7779035568237</t>
+    <t xml:space="preserve">10.7779016494751</t>
   </si>
   <si>
     <t xml:space="preserve">10.8542919158936</t>
@@ -1025,22 +1025,22 @@
     <t xml:space="preserve">11.0904054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1042947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1112384796143</t>
+    <t xml:space="preserve">11.1042928695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1112394332886</t>
   </si>
   <si>
     <t xml:space="preserve">10.6667900085449</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9723501205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9445705413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0765161514282</t>
+    <t xml:space="preserve">10.9723482131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9445695877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0765171051025</t>
   </si>
   <si>
     <t xml:space="preserve">11.3473529815674</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">11.3959646224976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1529064178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0626277923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.215407371521</t>
+    <t xml:space="preserve">11.1529054641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0626258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2154054641724</t>
   </si>
   <si>
     <t xml:space="preserve">11.3126306533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2362413406372</t>
+    <t xml:space="preserve">11.2362403869629</t>
   </si>
   <si>
     <t xml:space="preserve">11.2084617614746</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">10.9098472595215</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7362337112427</t>
+    <t xml:space="preserve">10.7362356185913</t>
   </si>
   <si>
     <t xml:space="preserve">10.8751249313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6945676803589</t>
+    <t xml:space="preserve">10.6945686340332</t>
   </si>
   <si>
     <t xml:space="preserve">10.5487327575684</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">11.0695714950562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1876287460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9306812286377</t>
+    <t xml:space="preserve">11.187629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9306802749634</t>
   </si>
   <si>
     <t xml:space="preserve">11.1598510742188</t>
@@ -1103,16 +1103,16 @@
     <t xml:space="preserve">11.4515209197998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5001306533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4931859970093</t>
+    <t xml:space="preserve">11.5001316070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4931869506836</t>
   </si>
   <si>
     <t xml:space="preserve">11.6251335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7223567962646</t>
+    <t xml:space="preserve">11.7223558425903</t>
   </si>
   <si>
     <t xml:space="preserve">11.7709693908691</t>
@@ -1139,52 +1139,52 @@
     <t xml:space="preserve">11.6806898117065</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820753097534</t>
+    <t xml:space="preserve">11.3820762634277</t>
   </si>
   <si>
     <t xml:space="preserve">10.8681802749634</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8959579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9862365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0834608078003</t>
+    <t xml:space="preserve">10.8959589004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9862384796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.083459854126</t>
   </si>
   <si>
     <t xml:space="preserve">11.2292966842651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2848520278931</t>
+    <t xml:space="preserve">11.2848510742188</t>
   </si>
   <si>
     <t xml:space="preserve">11.3265190124512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2431859970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5973558425903</t>
+    <t xml:space="preserve">11.243185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.597354888916</t>
   </si>
   <si>
     <t xml:space="preserve">11.7501354217529</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6181888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7987470626831</t>
+    <t xml:space="preserve">11.6181879043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7987451553345</t>
   </si>
   <si>
     <t xml:space="preserve">11.6320781707764</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8334712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1251382827759</t>
+    <t xml:space="preserve">11.8334703445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1251363754272</t>
   </si>
   <si>
     <t xml:space="preserve">11.9168043136597</t>
@@ -1196,67 +1196,67 @@
     <t xml:space="preserve">13.1529302597046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3820991516113</t>
+    <t xml:space="preserve">13.3820972442627</t>
   </si>
   <si>
     <t xml:space="preserve">13.319598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3682079315186</t>
+    <t xml:space="preserve">13.3682069778442</t>
   </si>
   <si>
     <t xml:space="preserve">13.5765447616577</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5209884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2362632751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1668176651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0487632751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4237651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0070934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3543195724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4584865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154340744019</t>
+    <t xml:space="preserve">13.5209875106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2362642288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1668167114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0487623214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4237661361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070924758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.354320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4584884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154359817505</t>
   </si>
   <si>
     <t xml:space="preserve">13.7918252944946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6807136535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9168262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9307146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1876525878906</t>
+    <t xml:space="preserve">13.6807146072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9168281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9307155609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1876516342163</t>
   </si>
   <si>
     <t xml:space="preserve">13.2987632751465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3751544952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.416820526123</t>
+    <t xml:space="preserve">13.3751554489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4168224334717</t>
   </si>
   <si>
     <t xml:space="preserve">13.4723768234253</t>
@@ -1265,25 +1265,25 @@
     <t xml:space="preserve">13.4862661361694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6112680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7362689971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223806381226</t>
+    <t xml:space="preserve">13.6112670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7362699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223787307739</t>
   </si>
   <si>
     <t xml:space="preserve">13.8196029663086</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8890495300293</t>
+    <t xml:space="preserve">13.8890466690063</t>
   </si>
   <si>
     <t xml:space="preserve">13.8543262481689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9029369354248</t>
+    <t xml:space="preserve">13.9029359817505</t>
   </si>
   <si>
     <t xml:space="preserve">14.0834951400757</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">14.3057203292847</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1945972442627</t>
+    <t xml:space="preserve">13.1945962905884</t>
   </si>
   <si>
     <t xml:space="preserve">13.1112623214722</t>
@@ -1307,28 +1307,28 @@
     <t xml:space="preserve">13.1807079315186</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0201005935669</t>
+    <t xml:space="preserve">14.0200996398926</t>
   </si>
   <si>
     <t xml:space="preserve">14.1486539840698</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8083600997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6571178436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5361232757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2563285827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1277732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3092632293701</t>
+    <t xml:space="preserve">13.8083610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6571187973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5361251831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2563304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1277723312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3092641830444</t>
   </si>
   <si>
     <t xml:space="preserve">13.460503578186</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">13.4983148574829</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4680652618408</t>
+    <t xml:space="preserve">13.4680662155151</t>
   </si>
   <si>
     <t xml:space="preserve">13.5739364624023</t>
@@ -1346,34 +1346,34 @@
     <t xml:space="preserve">13.7327394485474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7478656768799</t>
+    <t xml:space="preserve">13.7478637695312</t>
   </si>
   <si>
     <t xml:space="preserve">13.4075698852539</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4889459609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.473822593689</t>
+    <t xml:space="preserve">14.4889478683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4738216400146</t>
   </si>
   <si>
     <t xml:space="preserve">14.6704368591309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7158079147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755149841309</t>
+    <t xml:space="preserve">14.7158088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755159378052</t>
   </si>
   <si>
     <t xml:space="preserve">14.6175031661987</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7233724594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9351100921631</t>
+    <t xml:space="preserve">14.723370552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9351119995117</t>
   </si>
   <si>
     <t xml:space="preserve">14.7460584640503</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">14.8292417526245</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2167119979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2998962402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2091522216797</t>
+    <t xml:space="preserve">14.2167129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2998971939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2091503143311</t>
   </si>
   <si>
     <t xml:space="preserve">14.0654706954956</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">14.1637773513794</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0427865982056</t>
+    <t xml:space="preserve">14.0427856445312</t>
   </si>
   <si>
     <t xml:space="preserve">14.1713399887085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2847719192505</t>
+    <t xml:space="preserve">14.2847709655762</t>
   </si>
   <si>
     <t xml:space="preserve">14.6250638961792</t>
@@ -1412,145 +1412,145 @@
     <t xml:space="preserve">14.7536191940308</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6779975891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7914295196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8443641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8746128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8368053436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7611827850342</t>
+    <t xml:space="preserve">14.6779985427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7914276123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8443632125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8746137619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8368043899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7611846923828</t>
   </si>
   <si>
     <t xml:space="preserve">14.655312538147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5494441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099414825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6401901245117</t>
+    <t xml:space="preserve">14.5494422912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099424362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6401872634888</t>
   </si>
   <si>
     <t xml:space="preserve">14.5721302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5191955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2393980026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0049743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9217910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9142265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2696485519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3982028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9898490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6646814346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6722421646118</t>
+    <t xml:space="preserve">14.5191965103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2393970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0049734115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9217920303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9142284393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2696466445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3982038497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9898481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6646795272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6722431182861</t>
   </si>
   <si>
     <t xml:space="preserve">13.5814971923828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7705488204956</t>
+    <t xml:space="preserve">13.7705478668213</t>
   </si>
   <si>
     <t xml:space="preserve">13.6268711090088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5210008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495542526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5512495040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907522201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4756278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5058784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.347071647644</t>
+    <t xml:space="preserve">13.5209999084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495561599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.551248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4756288528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.505877494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3470735549927</t>
   </si>
   <si>
     <t xml:space="preserve">13.3924446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4831914901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8310461044312</t>
+    <t xml:space="preserve">13.483190536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8310470581055</t>
   </si>
   <si>
     <t xml:space="preserve">13.6344327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5663738250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5436878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3773221969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1958322525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2714509963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3395090103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3546361923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2638912200928</t>
+    <t xml:space="preserve">13.5663728713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5436868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3773212432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1958312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2714519500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3395118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3546333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2638902664185</t>
   </si>
   <si>
     <t xml:space="preserve">13.4529428482056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3319501876831</t>
+    <t xml:space="preserve">13.3319473266602</t>
   </si>
   <si>
     <t xml:space="preserve">12.9311590194702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0219039916992</t>
+    <t xml:space="preserve">13.0219030380249</t>
   </si>
   <si>
     <t xml:space="preserve">12.8101663589478</t>
@@ -1565,22 +1565,22 @@
     <t xml:space="preserve">12.6513605117798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3848838806152</t>
+    <t xml:space="preserve">13.3848848342896</t>
   </si>
   <si>
     <t xml:space="preserve">13.120210647583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9614067077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5681810379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.439624786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6211137771606</t>
+    <t xml:space="preserve">12.961404800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5681800842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4396228790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.621114730835</t>
   </si>
   <si>
     <t xml:space="preserve">12.4018125534058</t>
@@ -1589,40 +1589,40 @@
     <t xml:space="preserve">12.4925584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4698715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1371402740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2883825302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1522636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6286764144897</t>
+    <t xml:space="preserve">12.4698724746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1371393203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2883806228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1522645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6286745071411</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437997817993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.825288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7723541259766</t>
+    <t xml:space="preserve">12.8252878189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7723550796509</t>
   </si>
   <si>
     <t xml:space="preserve">12.847975730896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.757230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8177280426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7799167633057</t>
+    <t xml:space="preserve">12.7572317123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8177289962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7799158096313</t>
   </si>
   <si>
     <t xml:space="preserve">12.4471855163574</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">12.2581338882446</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1673889160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.416937828064</t>
+    <t xml:space="preserve">12.1673879623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4169368743896</t>
   </si>
   <si>
     <t xml:space="preserve">12.1447019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.031270980835</t>
+    <t xml:space="preserve">12.0312719345093</t>
   </si>
   <si>
     <t xml:space="preserve">12.2505722045898</t>
@@ -1655,49 +1655,49 @@
     <t xml:space="preserve">12.2278852462769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0463953018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0993299484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7968463897705</t>
+    <t xml:space="preserve">12.0463943481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0993309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7968454360962</t>
   </si>
   <si>
     <t xml:space="preserve">11.8800296783447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5379295349121</t>
+    <t xml:space="preserve">12.5379285812378</t>
   </si>
   <si>
     <t xml:space="preserve">12.2656946182251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7950410842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2941370010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1126489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9538440704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5833015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4774351119995</t>
+    <t xml:space="preserve">12.7950420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2941389083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1126480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9538431167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5833024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4774341583252</t>
   </si>
   <si>
     <t xml:space="preserve">12.5757398605347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8555374145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0143404006958</t>
+    <t xml:space="preserve">12.8555383682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0143413543701</t>
   </si>
   <si>
     <t xml:space="preserve">12.8328504562378</t>
@@ -1706,37 +1706,37 @@
     <t xml:space="preserve">12.9084730148315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0521507263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1807088851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9160346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.09752368927</t>
+    <t xml:space="preserve">13.0521535873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1807069778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.916033744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0975246429443</t>
   </si>
   <si>
     <t xml:space="preserve">13.0067796707153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2260789871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2185173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9009094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0370264053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7647924423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0294647216797</t>
+    <t xml:space="preserve">13.2260808944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2185163497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9009103775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0370283126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7647914886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.029465675354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2109565734863</t>
@@ -1745,46 +1745,46 @@
     <t xml:space="preserve">13.2336416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9235954284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8706645965576</t>
+    <t xml:space="preserve">12.9235963821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8706617355347</t>
   </si>
   <si>
     <t xml:space="preserve">12.8933477401733</t>
   </si>
   <si>
-    <t xml:space="preserve">13.188268661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353368759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9689683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1050863265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.301700592041</t>
+    <t xml:space="preserve">13.1882696151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9689693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3016996383667</t>
   </si>
   <si>
     <t xml:space="preserve">12.8857870101929</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6891736984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6967353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6362361907959</t>
+    <t xml:space="preserve">12.689172744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6967344284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6362371444702</t>
   </si>
   <si>
     <t xml:space="preserve">12.6664867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5152435302734</t>
+    <t xml:space="preserve">12.5152444839478</t>
   </si>
   <si>
     <t xml:space="preserve">12.3110675811768</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">12.0388326644897</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6589231491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7269811630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7496700286865</t>
+    <t xml:space="preserve">12.6589241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7269821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7496690750122</t>
   </si>
   <si>
     <t xml:space="preserve">12.3186311721802</t>
@@ -1817,70 +1817,70 @@
     <t xml:space="preserve">12.1749505996704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2732563018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1598253250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203235626221</t>
+    <t xml:space="preserve">12.2732582092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1598262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203245162964</t>
   </si>
   <si>
     <t xml:space="preserve">12.280818939209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.303505897522</t>
+    <t xml:space="preserve">12.3035068511963</t>
   </si>
   <si>
     <t xml:space="preserve">12.8631000518799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2902870178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4485054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5988121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146326065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9548006057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9785346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8598709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7491178512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7332983016968</t>
+    <t xml:space="preserve">13.2902879714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4485063552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988111495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6146335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9548034667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9785356521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8598718643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7491188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7332973480225</t>
   </si>
   <si>
     <t xml:space="preserve">13.7728509902954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8124055862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7174758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6383657455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6621007919312</t>
+    <t xml:space="preserve">13.812403678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.717474937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6383676528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6620998382568</t>
   </si>
   <si>
     <t xml:space="preserve">13.5750799179077</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1446628570557</t>
+    <t xml:space="preserve">14.1446619033813</t>
   </si>
   <si>
     <t xml:space="preserve">14.2395935058594</t>
@@ -1889,22 +1889,22 @@
     <t xml:space="preserve">14.5085639953613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4690093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955839157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7221565246582</t>
+    <t xml:space="preserve">14.4690103530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7221574783325</t>
   </si>
   <si>
     <t xml:space="preserve">14.6746921539307</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1763067245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1604824066162</t>
+    <t xml:space="preserve">14.176305770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1604843139648</t>
   </si>
   <si>
     <t xml:space="preserve">14.0813751220703</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">14.6984243392944</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6114053726196</t>
+    <t xml:space="preserve">14.611403465271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4136333465576</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">14.6272268295288</t>
   </si>
   <si>
-    <t xml:space="preserve">15.109790802002</t>
+    <t xml:space="preserve">15.1097917556763</t>
   </si>
   <si>
     <t xml:space="preserve">15.0939702987671</t>
@@ -1937,94 +1937,94 @@
     <t xml:space="preserve">14.9911289215088</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9436635971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9120178222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8724641799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8645553588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.643048286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2870588302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3266143798828</t>
+    <t xml:space="preserve">14.9436626434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9120168685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.872465133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8645544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6430501937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2870597839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3266153335571</t>
   </si>
   <si>
     <t xml:space="preserve">14.2158603668213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2475051879883</t>
+    <t xml:space="preserve">14.2475032806396</t>
   </si>
   <si>
     <t xml:space="preserve">14.0260000228882</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0576438903809</t>
+    <t xml:space="preserve">14.0576429367065</t>
   </si>
   <si>
     <t xml:space="preserve">13.6067228317261</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8677825927734</t>
+    <t xml:space="preserve">13.8677845001221</t>
   </si>
   <si>
     <t xml:space="preserve">14.2000408172607</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2949714660645</t>
+    <t xml:space="preserve">14.2949695587158</t>
   </si>
   <si>
     <t xml:space="preserve">14.2079496383667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6304550170898</t>
+    <t xml:space="preserve">13.6304559707642</t>
   </si>
   <si>
     <t xml:space="preserve">13.5671682357788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6700105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.519702911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3693962097168</t>
+    <t xml:space="preserve">13.6700096130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5197038650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3693952560425</t>
   </si>
   <si>
     <t xml:space="preserve">13.8203172683716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9073352813721</t>
+    <t xml:space="preserve">13.9073371887207</t>
   </si>
   <si>
     <t xml:space="preserve">13.844048500061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5592575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7886753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1209297180176</t>
+    <t xml:space="preserve">13.5592555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7886724472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1209306716919</t>
   </si>
   <si>
     <t xml:space="preserve">13.9310693740845</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0892858505249</t>
+    <t xml:space="preserve">14.0892868041992</t>
   </si>
   <si>
     <t xml:space="preserve">14.3028802871704</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">14.2316818237305</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1130199432373</t>
+    <t xml:space="preserve">14.1130208969116</t>
   </si>
   <si>
     <t xml:space="preserve">14.5876731872559</t>
@@ -2051,142 +2051,142 @@
     <t xml:space="preserve">14.975305557251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8566427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9990367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8329105377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7458896636963</t>
+    <t xml:space="preserve">14.8566417694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9990377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.832911491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7458906173706</t>
   </si>
   <si>
     <t xml:space="preserve">15.0227718353271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7379808425903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6905164718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6351375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5402069091797</t>
+    <t xml:space="preserve">14.7379779815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854452133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6905155181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6351366043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5402059555054</t>
   </si>
   <si>
     <t xml:space="preserve">14.1525726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5164747238159</t>
+    <t xml:space="preserve">14.5164756774902</t>
   </si>
   <si>
     <t xml:space="preserve">14.4294548034668</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1921291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0971975326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2712392807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2791452407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057207107544</t>
+    <t xml:space="preserve">14.1921281814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0971984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2712383270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2791471481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057197570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.3899011611938</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3424348831177</t>
+    <t xml:space="preserve">14.342435836792</t>
   </si>
   <si>
     <t xml:space="preserve">14.3582572937012</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4610996246338</t>
+    <t xml:space="preserve">14.4610986709595</t>
   </si>
   <si>
     <t xml:space="preserve">15.006950378418</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9515724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5322961807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3345251083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3740787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3819913864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6509599685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0860586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8170890808105</t>
+    <t xml:space="preserve">14.9515733718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5322980880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3345232009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3740797042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3819894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0860576629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8170871734619</t>
   </si>
   <si>
     <t xml:space="preserve">14.6193170547485</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0544147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4895143508911</t>
+    <t xml:space="preserve">15.0544157028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4895124435425</t>
   </si>
   <si>
     <t xml:space="preserve">15.8692359924316</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7189321517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.307562828064</t>
+    <t xml:space="preserve">15.7189302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3075637817383</t>
   </si>
   <si>
     <t xml:space="preserve">15.3471174240112</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6081743240356</t>
+    <t xml:space="preserve">15.6081762313843</t>
   </si>
   <si>
     <t xml:space="preserve">15.2284526824951</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1572542190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1888999938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1414337158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3866720199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2838306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3154754638672</t>
+    <t xml:space="preserve">15.1572561264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1889009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.141432762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3866710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2838315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3154726028442</t>
   </si>
   <si>
     <t xml:space="preserve">15.7505712509155</t>
@@ -2198,28 +2198,28 @@
     <t xml:space="preserve">15.6160879135132</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4420490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2047214508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2363662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1651668548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.402494430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6239986419678</t>
+    <t xml:space="preserve">15.4420499801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2047204971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.236367225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.165168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4024925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6240005493164</t>
   </si>
   <si>
     <t xml:space="preserve">15.7743072509766</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2173156738281</t>
+    <t xml:space="preserve">16.2173175811768</t>
   </si>
   <si>
     <t xml:space="preserve">16.5179271697998</t>
@@ -2228,25 +2228,25 @@
     <t xml:space="preserve">16.296422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.565393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0400485992432</t>
+    <t xml:space="preserve">16.5653953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0400466918945</t>
   </si>
   <si>
     <t xml:space="preserve">16.9292945861816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0875129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9609394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6919651031494</t>
+    <t xml:space="preserve">17.087516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.691967010498</t>
   </si>
   <si>
     <t xml:space="preserve">16.8976516723633</t>
@@ -2261,22 +2261,22 @@
     <t xml:space="preserve">17.2299098968506</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3564834594727</t>
+    <t xml:space="preserve">17.356481552124</t>
   </si>
   <si>
     <t xml:space="preserve">17.4514122009277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6096324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4039478302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4355945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5305194854736</t>
+    <t xml:space="preserve">17.6096305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4039497375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4355926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305213928223</t>
   </si>
   <si>
     <t xml:space="preserve">17.8786010742188</t>
@@ -2288,16 +2288,16 @@
     <t xml:space="preserve">18.1317501068115</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2583236694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3690738677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2899684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2108592987061</t>
+    <t xml:space="preserve">18.258321762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3690757751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.289966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2108612060547</t>
   </si>
   <si>
     <t xml:space="preserve">17.3723049163818</t>
@@ -2306,34 +2306,34 @@
     <t xml:space="preserve">17.4830570220947</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7045593261719</t>
+    <t xml:space="preserve">17.7045612335205</t>
   </si>
   <si>
     <t xml:space="preserve">17.3248386383057</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5021057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4988803863525</t>
+    <t xml:space="preserve">16.5021076202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4988784790039</t>
   </si>
   <si>
     <t xml:space="preserve">17.1508007049561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1701698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0213174819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.826774597168</t>
+    <t xml:space="preserve">11.1701707839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0213165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8267736434937</t>
   </si>
   <si>
     <t xml:space="preserve">11.6210899353027</t>
   </si>
   <si>
-    <t xml:space="preserve">11.629002571106</t>
+    <t xml:space="preserve">11.6290006637573</t>
   </si>
   <si>
     <t xml:space="preserve">11.3600311279297</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">10.9882202148438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4470520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.02454662323</t>
+    <t xml:space="preserve">11.4470500946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0245456695557</t>
   </si>
   <si>
     <t xml:space="preserve">12.0641002655029</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">12.8630990982056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.420090675354</t>
+    <t xml:space="preserve">12.4200897216797</t>
   </si>
   <si>
     <t xml:space="preserve">12.1748533248901</t>
@@ -2363,25 +2363,25 @@
     <t xml:space="preserve">12.9026536941528</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6969718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2190885543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4722375869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.314019203186</t>
+    <t xml:space="preserve">12.6969709396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.219090461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4722394943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3140201568604</t>
   </si>
   <si>
     <t xml:space="preserve">13.2349109649658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1241588592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4089508056641</t>
+    <t xml:space="preserve">13.1241579055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4089517593384</t>
   </si>
   <si>
     <t xml:space="preserve">13.4564161300659</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">13.1004257202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0925140380859</t>
+    <t xml:space="preserve">13.0925149917603</t>
   </si>
   <si>
     <t xml:space="preserve">13.2507333755493</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">13.0687828063965</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3614845275879</t>
+    <t xml:space="preserve">13.3614854812622</t>
   </si>
   <si>
     <t xml:space="preserve">13.4326839447021</t>
@@ -2411,52 +2411,52 @@
     <t xml:space="preserve">12.9738521575928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9342975616455</t>
+    <t xml:space="preserve">12.9342966079712</t>
   </si>
   <si>
     <t xml:space="preserve">13.0371379852295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1795358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2111797332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.543436050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6225452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7095642089844</t>
+    <t xml:space="preserve">13.1795349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2111778259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5434370040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6225442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.709566116333</t>
   </si>
   <si>
     <t xml:space="preserve">14.2056894302368</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8418645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1560764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966451644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2883768081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0490989685059</t>
+    <t xml:space="preserve">13.8418655395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1560773849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2883758544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0491008758545</t>
   </si>
   <si>
     <t xml:space="preserve">15.2475500106812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2971611022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1240386962891</t>
+    <t xml:space="preserve">15.2971601486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1240367889404</t>
   </si>
   <si>
     <t xml:space="preserve">16.4134407043457</t>
@@ -2468,34 +2468,34 @@
     <t xml:space="preserve">16.1405754089355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0909614562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1901874542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5865678787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286874771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346776008606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2144737243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2806243896484</t>
+    <t xml:space="preserve">16.0909595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.190185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5865659713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.346773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2144746780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2806253433228</t>
   </si>
   <si>
     <t xml:space="preserve">15.8346300125122</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6527185440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692581176758</t>
+    <t xml:space="preserve">15.6527166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692562103271</t>
   </si>
   <si>
     <t xml:space="preserve">15.5782995223999</t>
@@ -2507,52 +2507,52 @@
     <t xml:space="preserve">15.8594369888306</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3633127212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.429461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5617618560791</t>
+    <t xml:space="preserve">15.3633108139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4294624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5617609024048</t>
   </si>
   <si>
     <t xml:space="preserve">15.8677043914795</t>
   </si>
   <si>
-    <t xml:space="preserve">16.330753326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0501346588135</t>
+    <t xml:space="preserve">16.3307552337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0501365661621</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8682231903076</t>
+    <t xml:space="preserve">16.868221282959</t>
   </si>
   <si>
     <t xml:space="preserve">16.9509105682373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1162872314453</t>
+    <t xml:space="preserve">17.1162853240967</t>
   </si>
   <si>
     <t xml:space="preserve">17.3312702178955</t>
   </si>
   <si>
-    <t xml:space="preserve">17.51318359375</t>
+    <t xml:space="preserve">17.5131855010986</t>
   </si>
   <si>
     <t xml:space="preserve">17.7777843475342</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2981948852539</t>
+    <t xml:space="preserve">17.2981967926025</t>
   </si>
   <si>
     <t xml:space="preserve">17.2816581726074</t>
   </si>
   <si>
-    <t xml:space="preserve">17.314733505249</t>
+    <t xml:space="preserve">17.3147354125977</t>
   </si>
   <si>
     <t xml:space="preserve">17.4304962158203</t>
@@ -2570,16 +2570,16 @@
     <t xml:space="preserve">16.8186092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9012985229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8516845703125</t>
+    <t xml:space="preserve">16.901294708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8516826629639</t>
   </si>
   <si>
     <t xml:space="preserve">16.7524604797363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0170593261719</t>
+    <t xml:space="preserve">17.0170574188232</t>
   </si>
   <si>
     <t xml:space="preserve">17.4635715484619</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">17.5958709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4801082611084</t>
+    <t xml:space="preserve">17.480110168457</t>
   </si>
   <si>
     <t xml:space="preserve">17.8439350128174</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">17.992769241333</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0919933319092</t>
+    <t xml:space="preserve">18.0919914245605</t>
   </si>
   <si>
     <t xml:space="preserve">18.4227428436279</t>
@@ -2612,55 +2612,55 @@
     <t xml:space="preserve">18.1581439971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.025842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0754566192627</t>
+    <t xml:space="preserve">18.0258445739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0754585266113</t>
   </si>
   <si>
     <t xml:space="preserve">18.5054302215576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3896675109863</t>
+    <t xml:space="preserve">18.3896713256836</t>
   </si>
   <si>
     <t xml:space="preserve">18.2739067077637</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3235187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3400554656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.191219329834</t>
+    <t xml:space="preserve">18.3235206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3400573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1912212371826</t>
   </si>
   <si>
     <t xml:space="preserve">18.0589199066162</t>
   </si>
   <si>
-    <t xml:space="preserve">17.910083770752</t>
+    <t xml:space="preserve">17.9100818634033</t>
   </si>
   <si>
     <t xml:space="preserve">18.2408313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3069801330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6620197296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7943229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.711633682251</t>
+    <t xml:space="preserve">18.3069820404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6620216369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7943210601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7116317749023</t>
   </si>
   <si>
     <t xml:space="preserve">17.5793342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">17.347806930542</t>
+    <t xml:space="preserve">17.3478088378906</t>
   </si>
   <si>
     <t xml:space="preserve">17.4966449737549</t>
@@ -2678,22 +2678,22 @@
     <t xml:space="preserve">18.7700309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3731307983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6542682647705</t>
+    <t xml:space="preserve">18.3731327056885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6542701721191</t>
   </si>
   <si>
     <t xml:space="preserve">18.7534942626953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4062042236328</t>
+    <t xml:space="preserve">18.4062061309814</t>
   </si>
   <si>
     <t xml:space="preserve">18.1416072845459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9431571960449</t>
+    <t xml:space="preserve">17.9431591033936</t>
   </si>
   <si>
     <t xml:space="preserve">18.1085319519043</t>
@@ -2714,22 +2714,22 @@
     <t xml:space="preserve">16.2894115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9503936767578</t>
+    <t xml:space="preserve">15.9503917694092</t>
   </si>
   <si>
     <t xml:space="preserve">16.0413475036621</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5374736785889</t>
+    <t xml:space="preserve">16.5374717712402</t>
   </si>
   <si>
     <t xml:space="preserve">17.0832080841064</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5627937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.06667137146</t>
+    <t xml:space="preserve">17.5627956390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0666694641113</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155094146729</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">17.1658973693848</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0005207061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9178352355957</t>
+    <t xml:space="preserve">17.0005226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9178333282471</t>
   </si>
   <si>
     <t xml:space="preserve">16.7028465270996</t>
@@ -2750,10 +2750,10 @@
     <t xml:space="preserve">16.8847599029541</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7855339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6201591491699</t>
+    <t xml:space="preserve">16.7855358123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6201610565186</t>
   </si>
   <si>
     <t xml:space="preserve">16.4795913696289</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">17.1824359893799</t>
   </si>
   <si>
-    <t xml:space="preserve">17.546257019043</t>
+    <t xml:space="preserve">17.5462551116943</t>
   </si>
   <si>
     <t xml:space="preserve">18.1746826171875</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">18.8692569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1669311523438</t>
+    <t xml:space="preserve">19.1669292449951</t>
   </si>
   <si>
     <t xml:space="preserve">19.3488426208496</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">20.0599536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9607276916504</t>
+    <t xml:space="preserve">19.9607257843018</t>
   </si>
   <si>
     <t xml:space="preserve">20.5064659118652</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">20.8206768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7545261383057</t>
+    <t xml:space="preserve">20.7545299530029</t>
   </si>
   <si>
     <t xml:space="preserve">20.9364395141602</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">21.6806240081787</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1767520904541</t>
+    <t xml:space="preserve">22.1767501831055</t>
   </si>
   <si>
     <t xml:space="preserve">21.9948387145996</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">20.9033660888672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9529762268066</t>
+    <t xml:space="preserve">20.9529781341553</t>
   </si>
   <si>
     <t xml:space="preserve">21.3002662658691</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5979385375977</t>
+    <t xml:space="preserve">21.5979404449463</t>
   </si>
   <si>
     <t xml:space="preserve">21.4160251617432</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">21.8956127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5152530670166</t>
+    <t xml:space="preserve">21.515251159668</t>
   </si>
   <si>
     <t xml:space="preserve">21.8460025787354</t>
@@ -2861,49 +2861,49 @@
     <t xml:space="preserve">22.1602115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5317897796631</t>
+    <t xml:space="preserve">21.5317878723145</t>
   </si>
   <si>
     <t xml:space="preserve">21.3664150238037</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7379894256592</t>
+    <t xml:space="preserve">20.7379913330078</t>
   </si>
   <si>
     <t xml:space="preserve">20.5726165771484</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2506542205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7876014709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2584056854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6134414672852</t>
+    <t xml:space="preserve">21.2506523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7876033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2584037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6134395599365</t>
   </si>
   <si>
     <t xml:space="preserve">20.1922550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3323059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9354057312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2749423980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2010402679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9860534667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4656372070312</t>
+    <t xml:space="preserve">19.3323040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9354038238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2749404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2010383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9860515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4656391143799</t>
   </si>
   <si>
     <t xml:space="preserve">20.0103416442871</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">19.6465187072754</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2253284454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3410911560059</t>
+    <t xml:space="preserve">20.2253265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3410892486572</t>
   </si>
   <si>
     <t xml:space="preserve">20.5560779571533</t>
@@ -2945,16 +2945,16 @@
     <t xml:space="preserve">20.8868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5230045318604</t>
+    <t xml:space="preserve">20.5230026245117</t>
   </si>
   <si>
     <t xml:space="preserve">20.6056900024414</t>
   </si>
   <si>
-    <t xml:space="preserve">20.026876449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1095657348633</t>
+    <t xml:space="preserve">20.0268783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1095695495605</t>
   </si>
   <si>
     <t xml:space="preserve">21.1514263153076</t>
@@ -2963,10 +2963,10 @@
     <t xml:space="preserve">20.6222286224365</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3080177307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4072399139404</t>
+    <t xml:space="preserve">20.3080158233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4072418212891</t>
   </si>
   <si>
     <t xml:space="preserve">19.9772663116455</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">20.1261024475098</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0764904022217</t>
+    <t xml:space="preserve">20.0764923095703</t>
   </si>
   <si>
     <t xml:space="preserve">20.2914791107178</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2661552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7622776031494</t>
+    <t xml:space="preserve">19.2661533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">19.8780422210693</t>
@@ -3005,10 +3005,10 @@
     <t xml:space="preserve">21.2461490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.229097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.177942276001</t>
+    <t xml:space="preserve">21.2290992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1779441833496</t>
   </si>
   <si>
     <t xml:space="preserve">21.4337158203125</t>
@@ -3017,10 +3017,10 @@
     <t xml:space="preserve">21.4848709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6042289733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.621280670166</t>
+    <t xml:space="preserve">21.6042308807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6212825775146</t>
   </si>
   <si>
     <t xml:space="preserve">21.3143558502197</t>
@@ -3029,16 +3029,16 @@
     <t xml:space="preserve">21.5701274871826</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3885974884033</t>
+    <t xml:space="preserve">22.388599395752</t>
   </si>
   <si>
     <t xml:space="preserve">21.9793643951416</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0646171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.030517578125</t>
+    <t xml:space="preserve">22.0646190643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0305156707764</t>
   </si>
   <si>
     <t xml:space="preserve">21.7235908508301</t>
@@ -3053,16 +3053,16 @@
     <t xml:space="preserve">21.3655071258545</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4507656097412</t>
+    <t xml:space="preserve">21.4507675170898</t>
   </si>
   <si>
     <t xml:space="preserve">21.672435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0987224578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7917938232422</t>
+    <t xml:space="preserve">22.0987243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7917957305908</t>
   </si>
   <si>
     <t xml:space="preserve">21.9964141845703</t>
@@ -3071,10 +3071,10 @@
     <t xml:space="preserve">21.3825607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8369159698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8710155487061</t>
+    <t xml:space="preserve">20.8369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8710174560547</t>
   </si>
   <si>
     <t xml:space="preserve">20.888069152832</t>
@@ -3095,19 +3095,19 @@
     <t xml:space="preserve">22.47385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2692375183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7346038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5470371246338</t>
+    <t xml:space="preserve">22.2692394256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7346057891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5470390319824</t>
   </si>
   <si>
     <t xml:space="preserve">21.2632026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1097393035889</t>
+    <t xml:space="preserve">21.1097373962402</t>
   </si>
   <si>
     <t xml:space="preserve">21.1608905792236</t>
@@ -3116,28 +3116,28 @@
     <t xml:space="preserve">21.5530776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7747459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2973041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0926856994629</t>
+    <t xml:space="preserve">21.7747478485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2973022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0926876068115</t>
   </si>
   <si>
     <t xml:space="preserve">20.8539638519287</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0074272155762</t>
+    <t xml:space="preserve">21.0074291229248</t>
   </si>
   <si>
     <t xml:space="preserve">21.280252456665</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9282073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8600025177002</t>
+    <t xml:space="preserve">21.9282093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8600006103516</t>
   </si>
   <si>
     <t xml:space="preserve">21.8088474273682</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">21.7576942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3996124267578</t>
+    <t xml:space="preserve">21.3996143341064</t>
   </si>
   <si>
     <t xml:space="preserve">21.9111576080322</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">22.5079574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1669292449951</t>
+    <t xml:space="preserve">22.1669311523438</t>
   </si>
   <si>
     <t xml:space="preserve">22.0816707611084</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">22.013463973999</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4909057617188</t>
+    <t xml:space="preserve">22.4909076690674</t>
   </si>
   <si>
     <t xml:space="preserve">22.422700881958</t>
@@ -3179,16 +3179,16 @@
     <t xml:space="preserve">22.5761642456055</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6614189147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7296276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1729679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7697677612305</t>
+    <t xml:space="preserve">22.6614227294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7296257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.172966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7697696685791</t>
   </si>
   <si>
     <t xml:space="preserve">23.4628429412842</t>
@@ -3206,16 +3206,16 @@
     <t xml:space="preserve">25.4749164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8329963684082</t>
+    <t xml:space="preserve">25.8329982757568</t>
   </si>
   <si>
     <t xml:space="preserve">25.7818431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1740264892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3274917602539</t>
+    <t xml:space="preserve">26.1740283966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3274898529053</t>
   </si>
   <si>
     <t xml:space="preserve">26.6003150939941</t>
@@ -3227,10 +3227,10 @@
     <t xml:space="preserve">26.7708301544189</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6855735778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9694080352783</t>
+    <t xml:space="preserve">26.6855716705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.969409942627</t>
   </si>
   <si>
     <t xml:space="preserve">26.7196769714355</t>
@@ -3239,16 +3239,16 @@
     <t xml:space="preserve">26.3615951538086</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3104400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5491619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2251815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5431213378906</t>
+    <t xml:space="preserve">26.3104419708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5491600036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2251834869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5431232452393</t>
   </si>
   <si>
     <t xml:space="preserve">25.0315799713135</t>
@@ -3266,19 +3266,19 @@
     <t xml:space="preserve">25.1168346405029</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8099098205566</t>
+    <t xml:space="preserve">24.8099117279053</t>
   </si>
   <si>
     <t xml:space="preserve">24.8440113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1338863372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7246532440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7587547302246</t>
+    <t xml:space="preserve">25.1338882446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7246513366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7587566375732</t>
   </si>
   <si>
     <t xml:space="preserve">25.3896598815918</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">24.3836231231689</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1790046691895</t>
+    <t xml:space="preserve">24.1790027618408</t>
   </si>
   <si>
     <t xml:space="preserve">24.3324680328369</t>
@@ -3302,25 +3302,25 @@
     <t xml:space="preserve">24.3495197296143</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9402847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1449031829834</t>
+    <t xml:space="preserve">23.9402866363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1449012756348</t>
   </si>
   <si>
     <t xml:space="preserve">24.1107997894287</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8038730621338</t>
+    <t xml:space="preserve">23.8038711547852</t>
   </si>
   <si>
     <t xml:space="preserve">24.417724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4518299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2131061553955</t>
+    <t xml:space="preserve">24.4518280029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2131080627441</t>
   </si>
   <si>
     <t xml:space="preserve">24.3665714263916</t>
@@ -3332,22 +3332,22 @@
     <t xml:space="preserve">24.2813129425049</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0486297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4347763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5480995178223</t>
+    <t xml:space="preserve">25.0486278533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.434778213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5481014251709</t>
   </si>
   <si>
     <t xml:space="preserve">23.4969463348389</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9342479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7978363037109</t>
+    <t xml:space="preserve">22.9342460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7978343963623</t>
   </si>
   <si>
     <t xml:space="preserve">22.6443710327148</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">21.8429508209229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1839828491211</t>
+    <t xml:space="preserve">22.1839809417725</t>
   </si>
   <si>
     <t xml:space="preserve">21.1949939727783</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">20.9051208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6664009094238</t>
+    <t xml:space="preserve">20.6663990020752</t>
   </si>
   <si>
     <t xml:space="preserve">21.4678173065186</t>
@@ -3401,7 +3401,7 @@
     <t xml:space="preserve">20.2912654876709</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1378040313721</t>
+    <t xml:space="preserve">20.1378021240234</t>
   </si>
   <si>
     <t xml:space="preserve">22.6273212432861</t>
@@ -3410,10 +3410,10 @@
     <t xml:space="preserve">24.0937480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6163063049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7637310028076</t>
+    <t xml:space="preserve">23.616304397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7637329101562</t>
   </si>
   <si>
     <t xml:space="preserve">22.8148860931396</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">25.560173034668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9292678833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8951683044434</t>
+    <t xml:space="preserve">24.9292697906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8951663970947</t>
   </si>
   <si>
     <t xml:space="preserve">24.3154163360596</t>
@@ -3443,19 +3443,19 @@
     <t xml:space="preserve">25.7136363983154</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6564445495605</t>
+    <t xml:space="preserve">24.6564464569092</t>
   </si>
   <si>
     <t xml:space="preserve">25.1850433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9804229736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.662483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3786468505859</t>
+    <t xml:space="preserve">24.9804248809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6624851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3786449432373</t>
   </si>
   <si>
     <t xml:space="preserve">26.2933883666992</t>
@@ -3464,49 +3464,49 @@
     <t xml:space="preserve">26.8049335479736</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7537784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9413471221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0436534881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0948104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.821985244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9925003051758</t>
+    <t xml:space="preserve">26.7537803649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9413452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0436515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0948085784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8219814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9924983978271</t>
   </si>
   <si>
     <t xml:space="preserve">27.1459636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7086620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5040416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4699401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6916103363037</t>
+    <t xml:space="preserve">27.7086601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5040435791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4699420928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6916084289551</t>
   </si>
   <si>
     <t xml:space="preserve">27.7939186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8621253967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0496940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5893039703369</t>
+    <t xml:space="preserve">27.8621234893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0496921539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5893020629883</t>
   </si>
   <si>
     <t xml:space="preserve">27.1800651550293</t>
@@ -3515,16 +3515,16 @@
     <t xml:space="preserve">27.2823753356934</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8560886383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6514701843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3555564880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3214550018311</t>
+    <t xml:space="preserve">26.856086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6514682769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3555583953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3214530944824</t>
   </si>
   <si>
     <t xml:space="preserve">25.9864597320557</t>
@@ -3536,19 +3536,19 @@
     <t xml:space="preserve">26.8901920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7598190307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.475980758667</t>
+    <t xml:space="preserve">27.7598171234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4759788513184</t>
   </si>
   <si>
     <t xml:space="preserve">28.5100803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6976470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9875202178955</t>
+    <t xml:space="preserve">28.6976490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9875240325928</t>
   </si>
   <si>
     <t xml:space="preserve">29.4604301452637</t>
@@ -3560,16 +3560,16 @@
     <t xml:space="preserve">30.0559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5655212402344</t>
+    <t xml:space="preserve">29.5655193328857</t>
   </si>
   <si>
     <t xml:space="preserve">28.724796295166</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6197071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3394660949707</t>
+    <t xml:space="preserve">28.6197052001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3394641876221</t>
   </si>
   <si>
     <t xml:space="preserve">28.1993446350098</t>
@@ -3581,16 +3581,16 @@
     <t xml:space="preserve">28.9524955749512</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8824310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0575847625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1451568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0433444976807</t>
+    <t xml:space="preserve">28.8824329376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0575828552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1451587677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.043342590332</t>
   </si>
   <si>
     <t xml:space="preserve">26.6229820251465</t>
@@ -3602,31 +3602,31 @@
     <t xml:space="preserve">26.8681926727295</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0099544525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9924373626709</t>
+    <t xml:space="preserve">26.009952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9924392700195</t>
   </si>
   <si>
     <t xml:space="preserve">25.9574069976807</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6071033477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5178909301758</t>
+    <t xml:space="preserve">25.607105255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5178928375244</t>
   </si>
   <si>
     <t xml:space="preserve">26.255163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6054649353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8873481750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4653453826904</t>
+    <t xml:space="preserve">26.6054668426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8873462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4653434753418</t>
   </si>
   <si>
     <t xml:space="preserve">26.3252239227295</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">26.1675891876221</t>
   </si>
   <si>
-    <t xml:space="preserve">26.93825340271</t>
+    <t xml:space="preserve">26.9382553100586</t>
   </si>
   <si>
     <t xml:space="preserve">26.9732856750488</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">27.3411026000977</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7455883026123</t>
+    <t xml:space="preserve">26.7455902099609</t>
   </si>
   <si>
     <t xml:space="preserve">26.9907989501953</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">27.6563739776611</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5687999725342</t>
+    <t xml:space="preserve">27.5687980651855</t>
   </si>
   <si>
     <t xml:space="preserve">26.7280731201172</t>
@@ -3668,19 +3668,19 @@
     <t xml:space="preserve">25.7822570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3602542877197</t>
+    <t xml:space="preserve">26.3602561950684</t>
   </si>
   <si>
     <t xml:space="preserve">26.6930408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5879516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1834678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512847900391</t>
+    <t xml:space="preserve">26.5879535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1834659576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512809753418</t>
   </si>
   <si>
     <t xml:space="preserve">27.8840713500977</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">28.1467971801758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4445552825928</t>
+    <t xml:space="preserve">28.4445533752441</t>
   </si>
   <si>
     <t xml:space="preserve">28.8999481201172</t>
@@ -3701,16 +3701,16 @@
     <t xml:space="preserve">29.6706123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7757015228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.65309715271</t>
+    <t xml:space="preserve">29.7757053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6530990600586</t>
   </si>
   <si>
     <t xml:space="preserve">29.2327365875244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4062480926514</t>
+    <t xml:space="preserve">30.40625</t>
   </si>
   <si>
     <t xml:space="preserve">30.1260051727295</t>
@@ -3719,37 +3719,37 @@
     <t xml:space="preserve">30.3186721801758</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8632793426514</t>
+    <t xml:space="preserve">29.8632774353027</t>
   </si>
   <si>
     <t xml:space="preserve">29.950855255127</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4412746429443</t>
+    <t xml:space="preserve">30.4412784576416</t>
   </si>
   <si>
     <t xml:space="preserve">31.1593990325928</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3361854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1785488128662</t>
+    <t xml:space="preserve">30.3361873626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1785526275635</t>
   </si>
   <si>
     <t xml:space="preserve">29.7406730651855</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7089195251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4987392425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0258293151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1851043701172</t>
+    <t xml:space="preserve">27.7089214324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4987373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0258312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1851024627686</t>
   </si>
   <si>
     <t xml:space="preserve">26.4478321075439</t>
@@ -3785,22 +3785,22 @@
     <t xml:space="preserve">27.8665561676025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1692276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0641384124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5912284851074</t>
+    <t xml:space="preserve">25.169225692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.064136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5912303924561</t>
   </si>
   <si>
     <t xml:space="preserve">24.7488651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2726783752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1659526824951</t>
+    <t xml:space="preserve">26.2726802825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1659507751465</t>
   </si>
   <si>
     <t xml:space="preserve">25.0816516876221</t>
@@ -3809,16 +3809,16 @@
     <t xml:space="preserve">24.9415302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4335918426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1708679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.978199005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8380794525146</t>
+    <t xml:space="preserve">24.4335899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1708660125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9781970977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.838077545166</t>
   </si>
   <si>
     <t xml:space="preserve">24.9065017700195</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">26.7806186676025</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6738910675049</t>
+    <t xml:space="preserve">27.6738891601562</t>
   </si>
   <si>
     <t xml:space="preserve">27.7964954376221</t>
@@ -3854,25 +3854,25 @@
     <t xml:space="preserve">27.2535285949707</t>
   </si>
   <si>
-    <t xml:space="preserve">27.48122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9366149902344</t>
+    <t xml:space="preserve">27.4812240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.936616897583</t>
   </si>
   <si>
     <t xml:space="preserve">28.8649158477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7631015777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9032230377197</t>
+    <t xml:space="preserve">26.7631034851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9032249450684</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274677276611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.39528465271</t>
+    <t xml:space="preserve">26.3952865600586</t>
   </si>
   <si>
     <t xml:space="preserve">26.8331623077393</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">25.9223766326904</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3777694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5003776550293</t>
+    <t xml:space="preserve">26.3777713775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5003757476807</t>
   </si>
   <si>
     <t xml:space="preserve">26.1325588226318</t>
@@ -3896,22 +3896,22 @@
     <t xml:space="preserve">26.097526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5354042053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8857078552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2376480102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7647399902344</t>
+    <t xml:space="preserve">26.5354061126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8857097625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2376499176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.764741897583</t>
   </si>
   <si>
     <t xml:space="preserve">25.8348026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2201328277588</t>
+    <t xml:space="preserve">26.2201366424561</t>
   </si>
   <si>
     <t xml:space="preserve">25.4144401550293</t>
@@ -3926,10 +3926,10 @@
     <t xml:space="preserve">25.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5895881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8714694976807</t>
+    <t xml:space="preserve">25.5895900726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8714714050293</t>
   </si>
   <si>
     <t xml:space="preserve">24.4686241149902</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">24.5737133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1183223724365</t>
+    <t xml:space="preserve">24.1183204650879</t>
   </si>
   <si>
     <t xml:space="preserve">24.2409267425537</t>
@@ -3953,16 +3953,16 @@
     <t xml:space="preserve">24.8539543151855</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3109874725342</t>
+    <t xml:space="preserve">24.3109855651855</t>
   </si>
   <si>
     <t xml:space="preserve">24.2234115600586</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3460178375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4160766601562</t>
+    <t xml:space="preserve">24.3460159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">24.3985633850098</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">24.2058944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1883811950684</t>
+    <t xml:space="preserve">24.188383102417</t>
   </si>
   <si>
     <t xml:space="preserve">23.7329883575439</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">23.9957141876221</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0307464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8731098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3476543426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7154731750488</t>
+    <t xml:space="preserve">24.0307445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8731079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7154712677002</t>
   </si>
   <si>
     <t xml:space="preserve">23.7680168151855</t>
@@ -4025,10 +4025,10 @@
     <t xml:space="preserve">23.5052909851074</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0498962402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8747463226318</t>
+    <t xml:space="preserve">23.049898147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8747482299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.1900177001953</t>
@@ -4037,16 +4037,16 @@
     <t xml:space="preserve">23.2425651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6979579925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5578384399414</t>
+    <t xml:space="preserve">23.6979560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5578365325928</t>
   </si>
   <si>
     <t xml:space="preserve">23.9256534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7505035400391</t>
+    <t xml:space="preserve">23.7505016326904</t>
   </si>
   <si>
     <t xml:space="preserve">23.435230255127</t>
@@ -4055,37 +4055,37 @@
     <t xml:space="preserve">23.0849285125732</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3826847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5228080749512</t>
+    <t xml:space="preserve">23.3826866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5228061676025</t>
   </si>
   <si>
     <t xml:space="preserve">23.9606857299805</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4861373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2584419250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1166839599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.221773147583</t>
+    <t xml:space="preserve">24.4861354827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2584400177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1166820526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2217712402344</t>
   </si>
   <si>
     <t xml:space="preserve">25.2042579650879</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1341972351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6262607574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3635311126709</t>
+    <t xml:space="preserve">25.1341991424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6262588500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3635330200195</t>
   </si>
   <si>
     <t xml:space="preserve">23.7855339050293</t>
@@ -4094,16 +4094,16 @@
     <t xml:space="preserve">23.2250499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9798355102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2775917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.295108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0657749176025</t>
+    <t xml:space="preserve">22.9798374176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2775955200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2951107025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0657730102539</t>
   </si>
   <si>
     <t xml:space="preserve">24.7663803100586</t>
@@ -4124,10 +4124,10 @@
     <t xml:space="preserve">23.6418628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4965953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334342956543</t>
+    <t xml:space="preserve">23.4965972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334362030029</t>
   </si>
   <si>
     <t xml:space="preserve">23.5329132080078</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">24.2955551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5679264068604</t>
+    <t xml:space="preserve">24.5679244995117</t>
   </si>
   <si>
     <t xml:space="preserve">24.4771347045898</t>
@@ -4166,13 +4166,13 @@
     <t xml:space="preserve">24.5134525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3318710327148</t>
+    <t xml:space="preserve">24.3318691253662</t>
   </si>
   <si>
     <t xml:space="preserve">23.9868659973145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5510711669922</t>
+    <t xml:space="preserve">23.5510730743408</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058074951172</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">23.4602813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8234424591064</t>
+    <t xml:space="preserve">23.8234443664551</t>
   </si>
   <si>
     <t xml:space="preserve">23.6237049102783</t>
@@ -4199,13 +4199,13 @@
     <t xml:space="preserve">24.8221397399902</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0413398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3863468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1321296691895</t>
+    <t xml:space="preserve">24.0413417816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.386344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1321315765381</t>
   </si>
   <si>
     <t xml:space="preserve">24.4589786529541</t>
@@ -4214,19 +4214,19 @@
     <t xml:space="preserve">24.6768760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6042442321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5497703552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7858238220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2397766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8039817810059</t>
+    <t xml:space="preserve">24.6042423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.549768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7858219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2397747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8039798736572</t>
   </si>
   <si>
     <t xml:space="preserve">24.9674053192139</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">22.2618465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2981624603271</t>
+    <t xml:space="preserve">22.2981605529785</t>
   </si>
   <si>
     <t xml:space="preserve">22.388952255249</t>
@@ -4274,25 +4274,25 @@
     <t xml:space="preserve">22.2073707580566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0621070861816</t>
+    <t xml:space="preserve">22.062105178833</t>
   </si>
   <si>
     <t xml:space="preserve">21.6807861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6263122558594</t>
+    <t xml:space="preserve">21.6263103485107</t>
   </si>
   <si>
     <t xml:space="preserve">22.6431674957275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6794815063477</t>
+    <t xml:space="preserve">22.6794834136963</t>
   </si>
   <si>
     <t xml:space="preserve">22.5886917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1515922546387</t>
+    <t xml:space="preserve">23.1515941619873</t>
   </si>
   <si>
     <t xml:space="preserve">22.9700107574463</t>
@@ -4313,28 +4313,28 @@
     <t xml:space="preserve">23.024486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9155368804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.86106300354</t>
+    <t xml:space="preserve">22.9155387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8610649108887</t>
   </si>
   <si>
     <t xml:space="preserve">23.2060661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5342178344727</t>
+    <t xml:space="preserve">22.534215927124</t>
   </si>
   <si>
     <t xml:space="preserve">21.9349994659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8442096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2631511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8999881744385</t>
+    <t xml:space="preserve">21.8442077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2631492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8999862670898</t>
   </si>
   <si>
     <t xml:space="preserve">20.482349395752</t>
@@ -4346,13 +4346,13 @@
     <t xml:space="preserve">20.7365646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1010284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6833934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7378673553467</t>
+    <t xml:space="preserve">20.1010303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6833953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7378692626953</t>
   </si>
   <si>
     <t xml:space="preserve">20.0102405548096</t>
@@ -4364,7 +4364,7 @@
     <t xml:space="preserve">19.9376068115234</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3915576934814</t>
+    <t xml:space="preserve">20.3915596008301</t>
   </si>
   <si>
     <t xml:space="preserve">20.6094589233398</t>
@@ -4376,19 +4376,19 @@
     <t xml:space="preserve">20.6820907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1542015075684</t>
+    <t xml:space="preserve">21.1541996002197</t>
   </si>
   <si>
     <t xml:space="preserve">21.0997276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1723594665527</t>
+    <t xml:space="preserve">21.1723575592041</t>
   </si>
   <si>
     <t xml:space="preserve">21.0634117126465</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8091983795166</t>
+    <t xml:space="preserve">20.809196472168</t>
   </si>
   <si>
     <t xml:space="preserve">21.0089359283447</t>
@@ -4400,16 +4400,16 @@
     <t xml:space="preserve">21.0270938873291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.608154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7715759277344</t>
+    <t xml:space="preserve">21.6081523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.771577835083</t>
   </si>
   <si>
     <t xml:space="preserve">21.4628887176514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9181480407715</t>
+    <t xml:space="preserve">20.9181461334229</t>
   </si>
   <si>
     <t xml:space="preserve">21.2449913024902</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">22.7884311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0971183776855</t>
+    <t xml:space="preserve">23.0971202850342</t>
   </si>
   <si>
     <t xml:space="preserve">23.2605419158936</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">23.1152763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3694896697998</t>
+    <t xml:space="preserve">23.3694915771484</t>
   </si>
   <si>
     <t xml:space="preserve">23.8960742950439</t>
@@ -4448,13 +4448,13 @@
     <t xml:space="preserve">24.3681869506836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7689685821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4408206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2216186523438</t>
+    <t xml:space="preserve">23.768970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4408187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2216205596924</t>
   </si>
   <si>
     <t xml:space="preserve">25.493989944458</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">25.966100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">25.984260559082</t>
+    <t xml:space="preserve">25.9842586517334</t>
   </si>
   <si>
     <t xml:space="preserve">26.0932083129883</t>
@@ -4481,31 +4481,31 @@
     <t xml:space="preserve">26.2021560668945</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4758319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8947734832764</t>
+    <t xml:space="preserve">25.475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8947715759277</t>
   </si>
   <si>
     <t xml:space="preserve">25.0945110321045</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2942523956299</t>
+    <t xml:space="preserve">25.2942504882812</t>
   </si>
   <si>
     <t xml:space="preserve">24.9129314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">24.713191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0763549804688</t>
+    <t xml:space="preserve">24.7131900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0763530731201</t>
   </si>
   <si>
     <t xml:space="preserve">24.6405582427979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6587181091309</t>
+    <t xml:space="preserve">24.6587162017822</t>
   </si>
   <si>
     <t xml:space="preserve">24.3137130737305</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">21.5718383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4447326660156</t>
+    <t xml:space="preserve">21.444730758667</t>
   </si>
   <si>
     <t xml:space="preserve">21.1905174255371</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">21.136043548584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9363040924072</t>
+    <t xml:space="preserve">20.9363021850586</t>
   </si>
   <si>
     <t xml:space="preserve">21.3176250457764</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">22.6976413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7871265411377</t>
+    <t xml:space="preserve">23.7871284484863</t>
   </si>
   <si>
     <t xml:space="preserve">24.0231819152832</t>
@@ -5481,6 +5481,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.0200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5599994659424</t>
   </si>
 </sst>
 </file>
@@ -71209,7 +71212,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6911458333</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>258142</v>
@@ -71230,6 +71233,32 @@
         <v>1822</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6911342593</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>160615</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>21.8799991607666</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>21.4599990844727</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>21.7999992370605</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>21.5599994659424</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1823</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="1825">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="1826">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">7.43893432617188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23837471008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0438928604126</t>
+    <t xml:space="preserve">7.23837423324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04389381408691</t>
   </si>
   <si>
     <t xml:space="preserve">6.99527168273926</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">7.06212472915649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25053071975708</t>
+    <t xml:space="preserve">7.25052976608276</t>
   </si>
   <si>
     <t xml:space="preserve">7.22014141082764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1715202331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07427978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8494119644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01350355148315</t>
+    <t xml:space="preserve">7.17152070999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07428121566772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84941053390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01350450515747</t>
   </si>
   <si>
     <t xml:space="preserve">6.75216960906982</t>
@@ -83,139 +83,139 @@
     <t xml:space="preserve">6.83725547790527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97096252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09251356124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00742816925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00134944915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98919486999512</t>
+    <t xml:space="preserve">6.97096157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09251403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00742673873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00135040283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98919439315796</t>
   </si>
   <si>
     <t xml:space="preserve">6.92841863632202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86156463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53337669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47867965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61238574981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55161046981812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77647972106934</t>
+    <t xml:space="preserve">6.86156606674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53337717056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47867870330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61238670349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55160999298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77647924423218</t>
   </si>
   <si>
     <t xml:space="preserve">6.94057416915894</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8737211227417</t>
+    <t xml:space="preserve">6.87372064590454</t>
   </si>
   <si>
     <t xml:space="preserve">6.63061809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78863382339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58199691772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7035493850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71570587158203</t>
+    <t xml:space="preserve">6.78863477706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58199834823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70354890823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7157039642334</t>
   </si>
   <si>
     <t xml:space="preserve">6.80686712265015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91626405715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84333324432373</t>
+    <t xml:space="preserve">6.91626358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84333276748657</t>
   </si>
   <si>
     <t xml:space="preserve">6.83117818832397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70962715148926</t>
+    <t xml:space="preserve">6.879798412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70962619781494</t>
   </si>
   <si>
     <t xml:space="preserve">6.74609231948853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85548686981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8676438331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95272922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0499701499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27484035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35992527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34777116775513</t>
+    <t xml:space="preserve">6.85548782348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86764335632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95272874832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04997062683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27483987808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35992574691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34777069091797</t>
   </si>
   <si>
     <t xml:space="preserve">7.26876163482666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22621870040894</t>
+    <t xml:space="preserve">7.22621965408325</t>
   </si>
   <si>
     <t xml:space="preserve">7.11074590682983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08035755157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05604791641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975400924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23229646682739</t>
+    <t xml:space="preserve">7.03173780441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08035802841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05604696273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23229694366455</t>
   </si>
   <si>
     <t xml:space="preserve">7.15328931808472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11682319641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16544389724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95880603790283</t>
+    <t xml:space="preserve">7.11682415008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16544342041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95880556106567</t>
   </si>
   <si>
     <t xml:space="preserve">6.93449640274048</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">6.90410900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96488380432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79471302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76432514190674</t>
+    <t xml:space="preserve">6.96488428115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79471397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7643256187439</t>
   </si>
   <si>
     <t xml:space="preserve">7.14113330841064</t>
@@ -242,22 +242,22 @@
     <t xml:space="preserve">7.02566003799438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15738582611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1374135017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31052112579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25725698471069</t>
+    <t xml:space="preserve">7.15738677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13741302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31052160263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25725650787354</t>
   </si>
   <si>
     <t xml:space="preserve">7.34381103515625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38375949859619</t>
+    <t xml:space="preserve">7.38376045227051</t>
   </si>
   <si>
     <t xml:space="preserve">7.29720497131348</t>
@@ -266,46 +266,46 @@
     <t xml:space="preserve">7.25059938430786</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21730899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062372207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2372841835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27723217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22396755218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10412216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85777616500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65803480148315</t>
+    <t xml:space="preserve">7.21730852127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23728275299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27723121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22396659851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10412263870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85777473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65803384780884</t>
   </si>
   <si>
     <t xml:space="preserve">6.60476970672607</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47493886947632</t>
+    <t xml:space="preserve">6.474937915802</t>
   </si>
   <si>
     <t xml:space="preserve">6.50822830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95764589309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93767070770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82448625564575</t>
+    <t xml:space="preserve">6.95764493942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93767213821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82448530197144</t>
   </si>
   <si>
     <t xml:space="preserve">6.88440704345703</t>
@@ -314,85 +314,85 @@
     <t xml:space="preserve">6.47826671600342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32180404663086</t>
+    <t xml:space="preserve">6.3218035697937</t>
   </si>
   <si>
     <t xml:space="preserve">6.56149244308472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69132423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8178277015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91769647598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03754091262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78453683853149</t>
+    <t xml:space="preserve">6.69132471084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81782722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91769742965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03754138946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78453731536865</t>
   </si>
   <si>
     <t xml:space="preserve">6.50489950180054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61808681488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71795654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68466758728027</t>
+    <t xml:space="preserve">6.6180853843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71795606613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68466663360596</t>
   </si>
   <si>
     <t xml:space="preserve">6.73793077468872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8777494430542</t>
+    <t xml:space="preserve">6.87774896621704</t>
   </si>
   <si>
     <t xml:space="preserve">6.81116819381714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7512469291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79119491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76456308364868</t>
+    <t xml:space="preserve">6.75124645233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79119396209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76456260681152</t>
   </si>
   <si>
     <t xml:space="preserve">6.86443328857422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77122163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89106607437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73127317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64471769332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63805866241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75790452957153</t>
+    <t xml:space="preserve">6.77122020721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8910665512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73127222061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64471864700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63806056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75790500640869</t>
   </si>
   <si>
     <t xml:space="preserve">6.83114290237427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80451059341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101406097412</t>
+    <t xml:space="preserve">6.80451202392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101358413696</t>
   </si>
   <si>
     <t xml:space="preserve">6.96430397033691</t>
@@ -401,100 +401,100 @@
     <t xml:space="preserve">6.74458885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7112979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65137672424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6280722618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64138984680176</t>
+    <t xml:space="preserve">6.71129846572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65137624740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62807369232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6413893699646</t>
   </si>
   <si>
     <t xml:space="preserve">6.62141466140747</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01756906509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98427772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01090955734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04420042037964</t>
+    <t xml:space="preserve">7.01756763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98427820205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01090860366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04419946670532</t>
   </si>
   <si>
     <t xml:space="preserve">7.17070293426514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87109088897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92435455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97762012481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83780193328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84445810317993</t>
+    <t xml:space="preserve">6.87109136581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9243540763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97761869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83780097961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84445858001709</t>
   </si>
   <si>
     <t xml:space="preserve">6.79785299301147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77787780761719</t>
+    <t xml:space="preserve">6.77787923812866</t>
   </si>
   <si>
     <t xml:space="preserve">6.59811162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55150508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72461414337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67135000228882</t>
+    <t xml:space="preserve">6.55150651931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72461462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67135047912598</t>
   </si>
   <si>
     <t xml:space="preserve">6.66469192504883</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60809993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54484796524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45829391479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65470409393311</t>
+    <t xml:space="preserve">6.60809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54484701156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45829296112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65470504760742</t>
   </si>
   <si>
     <t xml:space="preserve">6.67800760269165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46495008468628</t>
+    <t xml:space="preserve">6.46495056152344</t>
   </si>
   <si>
     <t xml:space="preserve">6.13870811462402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.228590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19197177886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17865514755249</t>
+    <t xml:space="preserve">6.22859048843384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19197225570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17865610122681</t>
   </si>
   <si>
     <t xml:space="preserve">6.24856567382812</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">6.13537836074829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06546831130981</t>
+    <t xml:space="preserve">6.06546878814697</t>
   </si>
   <si>
     <t xml:space="preserve">6.16866874694824</t>
@@ -515,55 +515,55 @@
     <t xml:space="preserve">6.14203691482544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06213998794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03883647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10874557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881118774414</t>
+    <t xml:space="preserve">6.0621395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03883695602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10874700546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881071090698</t>
   </si>
   <si>
     <t xml:space="preserve">6.02219247817993</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0188627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11873292922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23191928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12206172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22193384170532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21860456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35842275619507</t>
+    <t xml:space="preserve">6.01886224746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11873340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23192024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12206220626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22193336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21860408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35842227935791</t>
   </si>
   <si>
     <t xml:space="preserve">6.37839603424072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62474346160889</t>
+    <t xml:space="preserve">6.62474393844604</t>
   </si>
   <si>
     <t xml:space="preserve">6.70464038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85111713409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69798231124878</t>
+    <t xml:space="preserve">6.85111808776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69798183441162</t>
   </si>
   <si>
     <t xml:space="preserve">6.904381275177</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">6.89772319793701</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99093627929688</t>
+    <t xml:space="preserve">6.99093437194824</t>
   </si>
   <si>
     <t xml:space="preserve">7.07749032974243</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">6.91103982925415</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07083177566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13075542449951</t>
+    <t xml:space="preserve">7.07083225250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1307544708252</t>
   </si>
   <si>
     <t xml:space="preserve">7.15072822570801</t>
@@ -593,55 +593,55 @@
     <t xml:space="preserve">7.18401861190796</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09746551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05085897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35046911239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27057456970215</t>
+    <t xml:space="preserve">7.09746360778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05085802078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3504695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27057409286499</t>
   </si>
   <si>
     <t xml:space="preserve">7.28388833999634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3038649559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53023815155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32383823394775</t>
+    <t xml:space="preserve">7.30386304855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53023767471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32383728027344</t>
   </si>
   <si>
     <t xml:space="preserve">7.31717872619629</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3637866973877</t>
+    <t xml:space="preserve">7.36378622055054</t>
   </si>
   <si>
     <t xml:space="preserve">7.51691961288452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59015893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347557067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992654800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77658462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73663568496704</t>
+    <t xml:space="preserve">7.59015941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347604751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7100043296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992559432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7765851020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73663663864136</t>
   </si>
   <si>
     <t xml:space="preserve">7.7898998260498</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">7.75660991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8231897354126</t>
+    <t xml:space="preserve">7.82319068908691</t>
   </si>
   <si>
     <t xml:space="preserve">7.85647964477539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86979532241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87645530700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308618545532</t>
+    <t xml:space="preserve">7.86979627609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8764533996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308713912964</t>
   </si>
   <si>
     <t xml:space="preserve">7.96966695785522</t>
@@ -671,31 +671,31 @@
     <t xml:space="preserve">7.94969272613525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92305994033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96300745010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72332000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62344884872437</t>
+    <t xml:space="preserve">7.92306137084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96300840377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311290740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7233190536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62344932556152</t>
   </si>
   <si>
     <t xml:space="preserve">7.54355192184448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47031354904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63676595687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56352758407593</t>
+    <t xml:space="preserve">7.47031545639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63676452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56352663040161</t>
   </si>
   <si>
     <t xml:space="preserve">7.57018518447876</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">7.74329376220703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80321550369263</t>
+    <t xml:space="preserve">7.80321645736694</t>
   </si>
   <si>
     <t xml:space="preserve">7.89642858505249</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94303607940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84982299804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06953907012939</t>
+    <t xml:space="preserve">7.94303512573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84982204437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06953811645508</t>
   </si>
   <si>
     <t xml:space="preserve">8.20842742919922</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">8.25009441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22926044464111</t>
+    <t xml:space="preserve">8.22926139831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.31953907012939</t>
@@ -734,16 +734,16 @@
     <t xml:space="preserve">8.35426235198975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28481769561768</t>
+    <t xml:space="preserve">8.28481864929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.29870510101318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37509536743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34731864929199</t>
+    <t xml:space="preserve">8.37509632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34731769561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.3889856338501</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">8.43759727478027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45148658752441</t>
+    <t xml:space="preserve">8.4514856338501</t>
   </si>
   <si>
     <t xml:space="preserve">8.68760108947754</t>
@@ -761,34 +761,34 @@
     <t xml:space="preserve">8.7362117767334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62509918212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63898849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66676712036133</t>
+    <t xml:space="preserve">8.62510013580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63898754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66676616668701</t>
   </si>
   <si>
     <t xml:space="preserve">8.68065547943115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59732246398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72926807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69454479217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61120986938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50704288482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59037590026855</t>
+    <t xml:space="preserve">8.59732151031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72926712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69454574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61120796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50704193115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59037685394287</t>
   </si>
   <si>
     <t xml:space="preserve">8.52787590026855</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">8.51398658752441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46537399291992</t>
+    <t xml:space="preserve">8.46537590026855</t>
   </si>
   <si>
     <t xml:space="preserve">8.47231960296631</t>
@@ -812,49 +812,49 @@
     <t xml:space="preserve">8.61815547943115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65982151031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6459321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40981769561768</t>
+    <t xml:space="preserve">8.65982246398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64593315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40981864929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.4306526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42370700836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30564975738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54176425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57648754119873</t>
+    <t xml:space="preserve">8.42370796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30565071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5417652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57648658752441</t>
   </si>
   <si>
     <t xml:space="preserve">8.6042652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71537780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88204574584961</t>
+    <t xml:space="preserve">8.71537971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88204669952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.00010299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15288257598877</t>
+    <t xml:space="preserve">9.15288352966309</t>
   </si>
   <si>
     <t xml:space="preserve">9.13204860687256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06954956054688</t>
+    <t xml:space="preserve">9.06954860687256</t>
   </si>
   <si>
     <t xml:space="preserve">9.09038257598877</t>
@@ -866,22 +866,22 @@
     <t xml:space="preserve">8.95843696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06260395050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12510585784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20843982696533</t>
+    <t xml:space="preserve">9.06260299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12510395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20844078063965</t>
   </si>
   <si>
     <t xml:space="preserve">9.24316215515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29871940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36816310882568</t>
+    <t xml:space="preserve">9.29871845245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3681640625</t>
   </si>
   <si>
     <t xml:space="preserve">9.40983104705811</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">9.29177379608154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31260585784912</t>
+    <t xml:space="preserve">9.31260681152344</t>
   </si>
   <si>
     <t xml:space="preserve">9.45149803161621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47233200073242</t>
+    <t xml:space="preserve">9.47233104705811</t>
   </si>
   <si>
     <t xml:space="preserve">9.43760871887207</t>
@@ -911,34 +911,34 @@
     <t xml:space="preserve">9.44455432891846</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40288543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38899707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38205242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34038543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34732913970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31955146789551</t>
+    <t xml:space="preserve">9.40288639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38899803161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38205337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34038639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34733009338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31955242156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.48622035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75011253356934</t>
+    <t xml:space="preserve">9.75011157989502</t>
   </si>
   <si>
     <t xml:space="preserve">9.79177951812744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7778902053833</t>
+    <t xml:space="preserve">9.77788925170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.80566787719727</t>
@@ -947,19 +947,19 @@
     <t xml:space="preserve">9.72927856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77094554901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76400089263916</t>
+    <t xml:space="preserve">9.77094459533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76400184631348</t>
   </si>
   <si>
     <t xml:space="preserve">9.74316787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96539211273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0278930664062</t>
+    <t xml:space="preserve">9.96539306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0278940200806</t>
   </si>
   <si>
     <t xml:space="preserve">9.93761539459229</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">10.4445648193359</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5001211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5695676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2292833328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3959541320801</t>
+    <t xml:space="preserve">10.5001201629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5695657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.229284286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3959522247314</t>
   </si>
   <si>
     <t xml:space="preserve">10.423731803894</t>
@@ -995,49 +995,49 @@
     <t xml:space="preserve">10.5903997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4931764602661</t>
+    <t xml:space="preserve">10.4931755065918</t>
   </si>
   <si>
     <t xml:space="preserve">10.5626211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6251230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6042890548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7015113830566</t>
+    <t xml:space="preserve">10.6251220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6042900085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.701512336731</t>
   </si>
   <si>
     <t xml:space="preserve">10.7779016494751</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8542919158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.833456993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9029026031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0904054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1042938232422</t>
+    <t xml:space="preserve">10.8542909622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8334579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9029016494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1042947769165</t>
   </si>
   <si>
     <t xml:space="preserve">11.1112384796143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6667900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9723482131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9445695877075</t>
+    <t xml:space="preserve">10.6667890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9723501205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9445705413818</t>
   </si>
   <si>
     <t xml:space="preserve">11.0765161514282</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">11.3959646224976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1529054641724</t>
+    <t xml:space="preserve">11.152904510498</t>
   </si>
   <si>
     <t xml:space="preserve">11.0626277923584</t>
@@ -1064,109 +1064,109 @@
     <t xml:space="preserve">11.2362403869629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2084627151489</t>
+    <t xml:space="preserve">11.2084617614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.9098482131958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7362356185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8751239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6945667266846</t>
+    <t xml:space="preserve">10.7362365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8751249313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6945676803589</t>
   </si>
   <si>
     <t xml:space="preserve">10.548731803894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7848463058472</t>
+    <t xml:space="preserve">10.7848453521729</t>
   </si>
   <si>
     <t xml:space="preserve">10.8612356185913</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0695724487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.187629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9306793212891</t>
+    <t xml:space="preserve">11.0695714950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876287460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9306812286377</t>
   </si>
   <si>
     <t xml:space="preserve">11.1598501205444</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4515209197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.500129699707</t>
+    <t xml:space="preserve">11.4515199661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.50013256073</t>
   </si>
   <si>
     <t xml:space="preserve">11.4931869506836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6251344680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7223567962646</t>
+    <t xml:space="preserve">11.6251335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7223558425903</t>
   </si>
   <si>
     <t xml:space="preserve">11.7709693908691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7015237808228</t>
+    <t xml:space="preserve">11.7015228271484</t>
   </si>
   <si>
     <t xml:space="preserve">11.7293004989624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7154130935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6112442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4862451553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5765218734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6806888580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3820762634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8681793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8959589004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9862375259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0834608078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2292947769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3265190124512</t>
+    <t xml:space="preserve">11.7154140472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6112432479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4862442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5765209197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6806898117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3820753097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8681802749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8959579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9862365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.083459854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2292966842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3265199661255</t>
   </si>
   <si>
     <t xml:space="preserve">11.2431859970093</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5973567962646</t>
+    <t xml:space="preserve">11.5973558425903</t>
   </si>
   <si>
     <t xml:space="preserve">11.7501354217529</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">11.7987470626831</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6320791244507</t>
+    <t xml:space="preserve">11.6320781707764</t>
   </si>
   <si>
     <t xml:space="preserve">11.8334703445435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1251382827759</t>
+    <t xml:space="preserve">12.1251392364502</t>
   </si>
   <si>
     <t xml:space="preserve">11.9168033599854</t>
@@ -1193,97 +1193,97 @@
     <t xml:space="preserve">12.6668128967285</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1529302597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.382098197937</t>
+    <t xml:space="preserve">13.1529293060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3820991516113</t>
   </si>
   <si>
     <t xml:space="preserve">13.3195991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3682098388672</t>
+    <t xml:space="preserve">13.3682088851929</t>
   </si>
   <si>
     <t xml:space="preserve">13.5765438079834</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5209856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2362632751465</t>
+    <t xml:space="preserve">13.5209875106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2362642288208</t>
   </si>
   <si>
     <t xml:space="preserve">13.1668176651001</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0487594604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4237651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0070953369141</t>
+    <t xml:space="preserve">13.0487613677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4237670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070924758911</t>
   </si>
   <si>
     <t xml:space="preserve">13.3543195724487</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4584875106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154359817505</t>
+    <t xml:space="preserve">13.4584865570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154340744019</t>
   </si>
   <si>
     <t xml:space="preserve">13.7918252944946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6807126998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9168262481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9307155609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1876525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2987651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3751525878906</t>
+    <t xml:space="preserve">13.6807136535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9168272018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9307146072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1876516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2987661361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3751544952393</t>
   </si>
   <si>
     <t xml:space="preserve">13.416820526123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4723777770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4862642288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6112689971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7362680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223796844482</t>
+    <t xml:space="preserve">13.472375869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4862651824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6112680435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7362699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223787307739</t>
   </si>
   <si>
     <t xml:space="preserve">13.8196029663086</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8890504837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8543272018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9029378890991</t>
+    <t xml:space="preserve">13.8890476226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8543262481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9029388427734</t>
   </si>
   <si>
     <t xml:space="preserve">14.0834951400757</t>
@@ -1292,28 +1292,28 @@
     <t xml:space="preserve">13.798770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0279388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.305721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1945953369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1112623214722</t>
+    <t xml:space="preserve">14.0279407501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1945972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1112613677979</t>
   </si>
   <si>
     <t xml:space="preserve">13.1807079315186</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0200996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1486530303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8083610534668</t>
+    <t xml:space="preserve">14.0201005935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1486539840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8083581924438</t>
   </si>
   <si>
     <t xml:space="preserve">13.6571178436279</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">13.5361232757568</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2563285827637</t>
+    <t xml:space="preserve">13.2563276290894</t>
   </si>
   <si>
     <t xml:space="preserve">13.1277732849121</t>
@@ -1334,22 +1334,22 @@
     <t xml:space="preserve">13.460503578186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4983158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4680662155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.573935508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.732738494873</t>
+    <t xml:space="preserve">13.4983148574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4680671691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5739364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7327404022217</t>
   </si>
   <si>
     <t xml:space="preserve">13.7478637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4075698852539</t>
+    <t xml:space="preserve">13.4075708389282</t>
   </si>
   <si>
     <t xml:space="preserve">14.4889459609985</t>
@@ -1358,121 +1358,121 @@
     <t xml:space="preserve">14.4738235473633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6704387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755159378052</t>
+    <t xml:space="preserve">14.6704368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158098220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755149841309</t>
   </si>
   <si>
     <t xml:space="preserve">14.6175022125244</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7233686447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9351100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.746057510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292427062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2998952865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2091484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0654716491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.163779258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0427837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1713380813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2847709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6250638961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536211013794</t>
+    <t xml:space="preserve">14.7233715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9351081848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7460584640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292417526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167119979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2998943328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2091512680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0654726028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1637773513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0427846908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1713399887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2847719192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6250648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536191940308</t>
   </si>
   <si>
     <t xml:space="preserve">14.6780004501343</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7914323806763</t>
+    <t xml:space="preserve">14.791428565979</t>
   </si>
   <si>
     <t xml:space="preserve">14.8443632125854</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8746128082275</t>
+    <t xml:space="preserve">14.8746137619019</t>
   </si>
   <si>
     <t xml:space="preserve">14.8368043899536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7611808776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6553134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5494432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099395751953</t>
+    <t xml:space="preserve">14.7611818313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6553115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5494451522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099414825439</t>
   </si>
   <si>
     <t xml:space="preserve">14.6401901245117</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5721292495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5191993713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2393999099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0049753189087</t>
+    <t xml:space="preserve">14.5721321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5191955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2393989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0049734115601</t>
   </si>
   <si>
     <t xml:space="preserve">13.9217910766602</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9142293930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2696466445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3982038497925</t>
+    <t xml:space="preserve">13.9142274856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2696475982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3982000350952</t>
   </si>
   <si>
     <t xml:space="preserve">13.9898509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6646795272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6722431182861</t>
+    <t xml:space="preserve">13.664680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6722412109375</t>
   </si>
   <si>
     <t xml:space="preserve">13.5814952850342</t>
@@ -1481,25 +1481,25 @@
     <t xml:space="preserve">13.7705497741699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6268692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5210018157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495561599731</t>
+    <t xml:space="preserve">13.6268701553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5210008621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495552062988</t>
   </si>
   <si>
     <t xml:space="preserve">13.551248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4907531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4756288528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.505877494812</t>
+    <t xml:space="preserve">13.4907541275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4756278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5058765411377</t>
   </si>
   <si>
     <t xml:space="preserve">13.3470726013184</t>
@@ -1508,55 +1508,55 @@
     <t xml:space="preserve">13.3924446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">13.483190536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8310470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6344337463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5663738250732</t>
+    <t xml:space="preserve">13.4831895828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8310451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6344327926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5663747787476</t>
   </si>
   <si>
     <t xml:space="preserve">13.5436868667603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3773212432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1958303451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2714509963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3395118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3546361923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2638912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4529428482056</t>
+    <t xml:space="preserve">13.3773231506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1958312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2714500427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3395099639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3546342849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2638921737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4529438018799</t>
   </si>
   <si>
     <t xml:space="preserve">13.3319482803345</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9311580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0219039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8101663589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5530548095703</t>
+    <t xml:space="preserve">12.9311599731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0219030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8101654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5530557632446</t>
   </si>
   <si>
     <t xml:space="preserve">12.7421064376831</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">12.6513614654541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3848829269409</t>
+    <t xml:space="preserve">13.3848848342896</t>
   </si>
   <si>
     <t xml:space="preserve">13.120210647583</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">12.9614067077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5681791305542</t>
+    <t xml:space="preserve">12.5681800842285</t>
   </si>
   <si>
     <t xml:space="preserve">12.439624786377</t>
@@ -1583,16 +1583,16 @@
     <t xml:space="preserve">12.6211137771606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4018115997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4925584793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4698724746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1371393203735</t>
+    <t xml:space="preserve">12.4018125534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4925575256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4698705673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1371412277222</t>
   </si>
   <si>
     <t xml:space="preserve">12.2883806228638</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">12.6437997817993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8252897262573</t>
+    <t xml:space="preserve">12.825288772583</t>
   </si>
   <si>
     <t xml:space="preserve">12.7723541259766</t>
@@ -1625,13 +1625,13 @@
     <t xml:space="preserve">12.7799167633057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4471845626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4244985580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.258131980896</t>
+    <t xml:space="preserve">12.4471855163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4245004653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2581338882446</t>
   </si>
   <si>
     <t xml:space="preserve">12.1673889160156</t>
@@ -1640,22 +1640,22 @@
     <t xml:space="preserve">12.4169368743896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1447019577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0312700271606</t>
+    <t xml:space="preserve">12.144702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0312728881836</t>
   </si>
   <si>
     <t xml:space="preserve">12.2505722045898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1068916320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2278833389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0463962554932</t>
+    <t xml:space="preserve">12.1068906784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2278852462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0463943481445</t>
   </si>
   <si>
     <t xml:space="preserve">12.0993299484253</t>
@@ -1673,31 +1673,31 @@
     <t xml:space="preserve">12.2656946182251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7950420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2941398620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1126489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9538459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5833015441895</t>
+    <t xml:space="preserve">12.7950410842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2941370010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1126480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9538450241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5833024978638</t>
   </si>
   <si>
     <t xml:space="preserve">12.4774341583252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.575740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8555383682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0143423080444</t>
+    <t xml:space="preserve">12.5757398605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8555374145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0143413543701</t>
   </si>
   <si>
     <t xml:space="preserve">12.8328504562378</t>
@@ -1709,19 +1709,16 @@
     <t xml:space="preserve">13.0521516799927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1807098388672</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.9160346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">13.09752368927</t>
+    <t xml:space="preserve">13.0975246429443</t>
   </si>
   <si>
     <t xml:space="preserve">13.0067796707153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2260789871216</t>
+    <t xml:space="preserve">13.2260808944702</t>
   </si>
   <si>
     <t xml:space="preserve">13.2185182571411</t>
@@ -1730,13 +1727,13 @@
     <t xml:space="preserve">12.9009094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0370264053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7647924423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.029465675354</t>
+    <t xml:space="preserve">13.0370283126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7647914886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0294647216797</t>
   </si>
   <si>
     <t xml:space="preserve">13.2109546661377</t>
@@ -1745,16 +1742,16 @@
     <t xml:space="preserve">13.2336416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9235973358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8706617355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8933477401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882696151733</t>
+    <t xml:space="preserve">12.9235963821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8706636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8933486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.188268661499</t>
   </si>
   <si>
     <t xml:space="preserve">13.1353349685669</t>
@@ -1763,10 +1760,10 @@
     <t xml:space="preserve">12.9689683914185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.301700592041</t>
+    <t xml:space="preserve">13.1050863265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3016996383667</t>
   </si>
   <si>
     <t xml:space="preserve">12.8857870101929</t>
@@ -1778,13 +1775,13 @@
     <t xml:space="preserve">12.6967344284058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6362371444702</t>
+    <t xml:space="preserve">12.6362361907959</t>
   </si>
   <si>
     <t xml:space="preserve">12.6664867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5152435302734</t>
+    <t xml:space="preserve">12.5152425765991</t>
   </si>
   <si>
     <t xml:space="preserve">12.3110685348511</t>
@@ -1793,22 +1790,22 @@
     <t xml:space="preserve">12.2430095672607</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0388336181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6589250564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7269821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7496690750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3186302185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1900749206543</t>
+    <t xml:space="preserve">12.0388317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6589231491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7269830703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7496700286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3186311721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1900758743286</t>
   </si>
   <si>
     <t xml:space="preserve">12.1976356506348</t>
@@ -1820,553 +1817,556 @@
     <t xml:space="preserve">12.2732572555542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1598262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2203235626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2808208465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3035068511963</t>
+    <t xml:space="preserve">12.1598272323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2203216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2808198928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.303505897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8631010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2902870178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.448504447937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5988130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6146335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9548006057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9785327911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8598709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7491178512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7332973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7728509902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.812406539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7174758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6383657455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6620988845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5750799179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1446619033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2395935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.508563041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690084457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955839157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7221574783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6746912002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.176305770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1604843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0813751220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0339097976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.43736743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6984243392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6114044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4136333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6272268295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1097898483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0939693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911289215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9436626434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9120206832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8724660873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8645544052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6430473327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2870588302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3266134262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2158613204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2475061416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0260000228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0576429367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6067228317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8677816390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2000398635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2949714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2079486846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6304540634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5671682357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6700105667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.519702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3693962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8203153610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9073352813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8440494537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5592575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7886743545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965841293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1209316253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9310684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0892877578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3028793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4848308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6588716506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633275985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2316818237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1130208969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5876750946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9753065109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8566436767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9990377426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8329105377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7458896636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0227708816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7379779815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7854461669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6905126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.635139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.540207862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1525735855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5164756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4294557571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1921291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0971975326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2712383270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.279146194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.405722618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3899030685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.342435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3582582473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4610986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.006950378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9515743255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5322971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3345241546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3740768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3819894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0860567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8170881271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6193161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0544166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4895143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8692350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7189292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.307562828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3471174240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6081762313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2284536361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572551727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1889009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1414356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3866710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2838315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3154754638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7505731582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7110166549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6160888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4420490264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.204719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2363653182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1651668548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4024925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6239967346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7743053436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2173175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5179271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2964248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5653953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0400485992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9292945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0875148773193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558681488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9609413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6919689178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8976516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1982650756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8818302154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2299098968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3564853668213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4514122009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6096305847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4039478302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4355926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5305213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8786029815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1792144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1317501068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2583236694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3690757751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2899703979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2108592987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3723049163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4830570220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7045612335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3248405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5021057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4988803863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1507987976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1701707839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0213174819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8267736434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6210899353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6290016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3600311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9882192611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4470520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0245456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0640993118286</t>
   </si>
   <si>
     <t xml:space="preserve">12.8631000518799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2902870178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4485063552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5988130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6146354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9548025131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9785327911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8598718643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7491188049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7332983016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.772852897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8124055862427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7174758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6383647918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6620979309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5750799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.14466381073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2395935058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.508563041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690103530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955839157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7221574783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.674693107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1763048171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1604833602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0813751220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0339097976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4373655319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6984262466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6114044189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.413631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6272268295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1097917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0939693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911289215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9436626434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9120206832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8724641799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8645524978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6430492401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2870588302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3266143798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.215859413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2475051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0260000228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0576429367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6067237854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8677825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2000398635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2949695587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2079486846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6304550170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5671682357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6700105667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5197038650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3693962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8203153610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9073371887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8440494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5592575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7886753082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1209316253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9310703277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0892877578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3028812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4848318099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6588716506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633275985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2316827774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1130199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5876731872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9753084182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8566436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9990377426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8329124450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7458896636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0227727890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.737979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7854461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6905126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.635139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5402059555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1525745391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5164737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4294557571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1921291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0971975326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2712383270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2791481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.405722618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3899011611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3424339294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3582563400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4611005783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0069484710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9515743255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5322971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3345222473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3740768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3819894790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6509609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0860567092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8170900344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6193161010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0544147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4895143508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8692350387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7189311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3075647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3471193313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6081762313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2284545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572551727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1889028549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1414356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3866729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2838296890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3154754638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7505712509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7110185623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6160869598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4420471191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2047214508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2363634109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1651668548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4024906158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6239986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7743034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2173175811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5179271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2964248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5653953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0400485992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0875148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558662414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9609413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6919689178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8976516723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1982669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8818302154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2299098968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3564853668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4514122009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6096305847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4039478302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4355945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5305194854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8786010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1792144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1317501068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.258321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3690757751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2899684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2108573913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3723030090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4830589294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7045612335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3248386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5021076202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4988803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1507987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1701698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0213165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8267726898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6210899353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6290016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.360032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9882202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4470520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0245456695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0641002655029</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.4200897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1748514175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9026536941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6969699859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2190895080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4722375869751</t>
+    <t xml:space="preserve">12.1748523712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9026546478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6969709396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2190885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4722366333008</t>
   </si>
   <si>
     <t xml:space="preserve">13.314019203186</t>
@@ -2375,43 +2375,43 @@
     <t xml:space="preserve">13.2349109649658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1241579055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4089517593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4564161300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1004247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0925149917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2507343292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0687837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3614845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4326839447021</t>
+    <t xml:space="preserve">13.1241588592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4089508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4564170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1004257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0925140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2507333755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0687828063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3614835739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4326829910278</t>
   </si>
   <si>
     <t xml:space="preserve">13.5038814544678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9738512039185</t>
+    <t xml:space="preserve">12.9738521575928</t>
   </si>
   <si>
     <t xml:space="preserve">12.9342985153198</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0371389389038</t>
+    <t xml:space="preserve">13.0371379852295</t>
   </si>
   <si>
     <t xml:space="preserve">13.1795349121094</t>
@@ -2426,19 +2426,19 @@
     <t xml:space="preserve">13.6225442886353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7095651626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2056903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1560773849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2966451644897</t>
+    <t xml:space="preserve">13.7095642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2056894302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1560764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2966461181641</t>
   </si>
   <si>
     <t xml:space="preserve">14.2883768081665</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">15.0490999221802</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2475500106812</t>
+    <t xml:space="preserve">15.2475509643555</t>
   </si>
   <si>
     <t xml:space="preserve">15.2971630096436</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">16.4134426116943</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5043964385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1405715942383</t>
+    <t xml:space="preserve">16.5043983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1405735015869</t>
   </si>
   <si>
     <t xml:space="preserve">16.0909595489502</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">15.5286874771118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2144746780396</t>
+    <t xml:space="preserve">15.3467750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2144727706909</t>
   </si>
   <si>
     <t xml:space="preserve">15.2806243896484</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">15.8346309661865</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6527194976807</t>
+    <t xml:space="preserve">15.652717590332</t>
   </si>
   <si>
     <t xml:space="preserve">15.6692552566528</t>
@@ -2498,13 +2498,13 @@
     <t xml:space="preserve">15.5782985687256</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7932863235474</t>
+    <t xml:space="preserve">15.7932844161987</t>
   </si>
   <si>
     <t xml:space="preserve">15.8594369888306</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3633127212524</t>
+    <t xml:space="preserve">15.3633108139038</t>
   </si>
   <si>
     <t xml:space="preserve">15.429461479187</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">15.5617589950562</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8677062988281</t>
+    <t xml:space="preserve">15.8677043914795</t>
   </si>
   <si>
     <t xml:space="preserve">16.330753326416</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">17.0501346588135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2651195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8682231903076</t>
+    <t xml:space="preserve">17.2651214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.868221282959</t>
   </si>
   <si>
     <t xml:space="preserve">16.9509105682373</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">17.3312702178955</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5131855010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7777824401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2981986999512</t>
+    <t xml:space="preserve">17.51318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7777843475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2981967926025</t>
   </si>
   <si>
     <t xml:space="preserve">17.2816581726074</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">17.4304962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3643474578857</t>
+    <t xml:space="preserve">17.3643455505371</t>
   </si>
   <si>
     <t xml:space="preserve">17.3808860778809</t>
@@ -2567,25 +2567,25 @@
     <t xml:space="preserve">16.8186092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9012966156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8516826629639</t>
+    <t xml:space="preserve">16.9012985229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8516845703125</t>
   </si>
   <si>
     <t xml:space="preserve">16.7524604797363</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0170593261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4635715484619</t>
+    <t xml:space="preserve">17.0170612335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4635696411133</t>
   </si>
   <si>
     <t xml:space="preserve">17.5958728790283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4801063537598</t>
+    <t xml:space="preserve">17.4801082611084</t>
   </si>
   <si>
     <t xml:space="preserve">17.8439331054688</t>
@@ -2600,19 +2600,19 @@
     <t xml:space="preserve">18.0919933319092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4227447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4723567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1581439971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0258445739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0754585266113</t>
+    <t xml:space="preserve">18.4227466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4723587036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.158145904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.025842666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0754566192627</t>
   </si>
   <si>
     <t xml:space="preserve">18.5054321289062</t>
@@ -2621,13 +2621,13 @@
     <t xml:space="preserve">18.389669418335</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2739086151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3235187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3400554656982</t>
+    <t xml:space="preserve">18.2739067077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3235206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3400573730469</t>
   </si>
   <si>
     <t xml:space="preserve">18.191219329834</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">18.0589218139648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9100818634033</t>
+    <t xml:space="preserve">17.910083770752</t>
   </si>
   <si>
     <t xml:space="preserve">18.2408313751221</t>
@@ -2651,10 +2651,10 @@
     <t xml:space="preserve">17.7943210601807</t>
   </si>
   <si>
-    <t xml:space="preserve">17.711633682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5793323516846</t>
+    <t xml:space="preserve">17.7116317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5793361663818</t>
   </si>
   <si>
     <t xml:space="preserve">17.347806930542</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">17.4966449737549</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3974189758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7447052001953</t>
+    <t xml:space="preserve">17.3974208831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7447071075439</t>
   </si>
   <si>
     <t xml:space="preserve">18.6046562194824</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">18.3731307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6542663574219</t>
+    <t xml:space="preserve">18.6542682647705</t>
   </si>
   <si>
     <t xml:space="preserve">18.7534942626953</t>
@@ -2690,22 +2690,22 @@
     <t xml:space="preserve">18.1416091918945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9431591033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1085319519043</t>
+    <t xml:space="preserve">17.9431571960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1085338592529</t>
   </si>
   <si>
     <t xml:space="preserve">17.7281723022461</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9596939086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1989707946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.636697769165</t>
+    <t xml:space="preserve">17.95969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1989688873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6366958618164</t>
   </si>
   <si>
     <t xml:space="preserve">16.2894115447998</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">15.9503917694092</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0413494110107</t>
+    <t xml:space="preserve">16.0413475036621</t>
   </si>
   <si>
     <t xml:space="preserve">16.5374736785889</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">17.5627956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0666694641113</t>
+    <t xml:space="preserve">17.06667137146</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155094146729</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">16.9178314208984</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7028465270996</t>
+    <t xml:space="preserve">16.7028484344482</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847599029541</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">17.1328201293945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1824321746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462589263916</t>
+    <t xml:space="preserve">17.1824340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.546257019043</t>
   </si>
   <si>
     <t xml:space="preserve">18.1746807098389</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">18.869255065918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1669292449951</t>
+    <t xml:space="preserve">19.1669311523438</t>
   </si>
   <si>
     <t xml:space="preserve">19.3488426208496</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">20.0599536895752</t>
   </si>
   <si>
-    <t xml:space="preserve">19.960729598999</t>
+    <t xml:space="preserve">19.9607315063477</t>
   </si>
   <si>
     <t xml:space="preserve">20.5064640045166</t>
@@ -2795,13 +2795,13 @@
     <t xml:space="preserve">20.7049160003662</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6718406677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8206806182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7545280456543</t>
+    <t xml:space="preserve">20.6718425750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8206787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7545299530029</t>
   </si>
   <si>
     <t xml:space="preserve">20.9364395141602</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">21.6806240081787</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1767482757568</t>
+    <t xml:space="preserve">22.1767501831055</t>
   </si>
   <si>
     <t xml:space="preserve">21.9948406219482</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5571136474609</t>
+    <t xml:space="preserve">22.5571117401123</t>
   </si>
   <si>
     <t xml:space="preserve">21.2175788879395</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">21.3002662658691</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5979385375977</t>
+    <t xml:space="preserve">21.5979404449463</t>
   </si>
   <si>
     <t xml:space="preserve">21.4160270690918</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">21.5152530670166</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8460006713867</t>
+    <t xml:space="preserve">21.8460025787354</t>
   </si>
   <si>
     <t xml:space="preserve">22.160213470459</t>
@@ -2861,10 +2861,10 @@
     <t xml:space="preserve">21.5317878723145</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3664150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7379913330078</t>
+    <t xml:space="preserve">21.3664169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7379894256592</t>
   </si>
   <si>
     <t xml:space="preserve">20.5726165771484</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">21.2506523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7876033782959</t>
+    <t xml:space="preserve">20.7876014709473</t>
   </si>
   <si>
     <t xml:space="preserve">20.2584037780762</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">19.6134414672852</t>
   </si>
   <si>
-    <t xml:space="preserve">20.192253112793</t>
+    <t xml:space="preserve">20.1922550201416</t>
   </si>
   <si>
     <t xml:space="preserve">19.3323040008545</t>
@@ -2909,22 +2909,22 @@
     <t xml:space="preserve">19.6465167999268</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2253284454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3410892486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5560779571533</t>
+    <t xml:space="preserve">20.2253265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3410911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5560760498047</t>
   </si>
   <si>
     <t xml:space="preserve">20.638765335083</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0356674194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3498764038086</t>
+    <t xml:space="preserve">21.035665512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.34987449646</t>
   </si>
   <si>
     <t xml:space="preserve">21.085277557373</t>
@@ -2936,16 +2936,16 @@
     <t xml:space="preserve">20.8702907562256</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1018142700195</t>
+    <t xml:space="preserve">21.1018161773682</t>
   </si>
   <si>
     <t xml:space="preserve">20.8868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5230026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.60569190979</t>
+    <t xml:space="preserve">20.5230045318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6056900024414</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268783569336</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">21.1514282226562</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6222267150879</t>
+    <t xml:space="preserve">20.6222286224365</t>
   </si>
   <si>
     <t xml:space="preserve">20.3080158233643</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">20.2914791107178</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2661552429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7622776031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.878044128418</t>
+    <t xml:space="preserve">19.2661571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.762279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8780422210693</t>
   </si>
   <si>
     <t xml:space="preserve">21.3484592437744</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">21.3314075469971</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0756320953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.246150970459</t>
+    <t xml:space="preserve">21.0756340026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2461490631104</t>
   </si>
   <si>
     <t xml:space="preserve">21.2290954589844</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">21.4337158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4848690032959</t>
+    <t xml:space="preserve">21.4848709106445</t>
   </si>
   <si>
     <t xml:space="preserve">21.6042308807373</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">21.9793643951416</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0646190643311</t>
+    <t xml:space="preserve">22.0646171569824</t>
   </si>
   <si>
     <t xml:space="preserve">22.030517578125</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">21.7406406402588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3655090332031</t>
+    <t xml:space="preserve">21.3655071258545</t>
   </si>
   <si>
     <t xml:space="preserve">21.4507656097412</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">22.0987243652344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7917976379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9964141845703</t>
+    <t xml:space="preserve">21.7917957305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9964122772217</t>
   </si>
   <si>
     <t xml:space="preserve">21.3825607299805</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8369121551514</t>
+    <t xml:space="preserve">20.8369140625</t>
   </si>
   <si>
     <t xml:space="preserve">20.8710155487061</t>
@@ -3080,28 +3080,28 @@
     <t xml:space="preserve">21.7065391540527</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9623107910156</t>
+    <t xml:space="preserve">21.9623126983643</t>
   </si>
   <si>
     <t xml:space="preserve">22.1328258514404</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2351341247559</t>
+    <t xml:space="preserve">22.2351360321045</t>
   </si>
   <si>
     <t xml:space="preserve">22.47385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2692394256592</t>
+    <t xml:space="preserve">22.2692375183105</t>
   </si>
   <si>
     <t xml:space="preserve">20.7346057891846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5470390319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2632007598877</t>
+    <t xml:space="preserve">20.5470371246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2632026672363</t>
   </si>
   <si>
     <t xml:space="preserve">21.1097373962402</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">21.5530776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7747440338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2973041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0926856994629</t>
+    <t xml:space="preserve">21.7747459411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2973022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0926837921143</t>
   </si>
   <si>
     <t xml:space="preserve">20.8539638519287</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">21.3996124267578</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9111576080322</t>
+    <t xml:space="preserve">21.9111595153809</t>
   </si>
   <si>
     <t xml:space="preserve">22.5079593658447</t>
@@ -3164,13 +3164,13 @@
     <t xml:space="preserve">22.0134658813477</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4909076690674</t>
+    <t xml:space="preserve">22.4909057617188</t>
   </si>
   <si>
     <t xml:space="preserve">22.422700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2521858215332</t>
+    <t xml:space="preserve">22.2521877288818</t>
   </si>
   <si>
     <t xml:space="preserve">22.5761642456055</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">23.1729679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7697658538818</t>
+    <t xml:space="preserve">23.7697677612305</t>
   </si>
   <si>
     <t xml:space="preserve">23.4628429412842</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">23.3775844573975</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9232311248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2191429138184</t>
+    <t xml:space="preserve">23.9232330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.219144821167</t>
   </si>
   <si>
     <t xml:space="preserve">25.4749164581299</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">26.3274917602539</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6003170013428</t>
+    <t xml:space="preserve">26.6003150939941</t>
   </si>
   <si>
     <t xml:space="preserve">26.6173667907715</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">26.6855716705322</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9694080352783</t>
+    <t xml:space="preserve">25.969409942627</t>
   </si>
   <si>
     <t xml:space="preserve">26.7196750640869</t>
@@ -3242,13 +3242,13 @@
     <t xml:space="preserve">26.5491600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2251834869385</t>
+    <t xml:space="preserve">26.2251815795898</t>
   </si>
   <si>
     <t xml:space="preserve">25.5431232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0315780639648</t>
+    <t xml:space="preserve">25.0315799713135</t>
   </si>
   <si>
     <t xml:space="preserve">24.826961517334</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">25.0145263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1679916381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1168365478516</t>
+    <t xml:space="preserve">25.1679935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1168346405029</t>
   </si>
   <si>
     <t xml:space="preserve">24.8099098205566</t>
@@ -3275,10 +3275,10 @@
     <t xml:space="preserve">24.7246513366699</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7587566375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3896617889404</t>
+    <t xml:space="preserve">24.7587547302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3896598815918</t>
   </si>
   <si>
     <t xml:space="preserve">24.3836231231689</t>
@@ -3293,13 +3293,13 @@
     <t xml:space="preserve">24.6223430633545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1960544586182</t>
+    <t xml:space="preserve">24.1960563659668</t>
   </si>
   <si>
     <t xml:space="preserve">24.3495178222656</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9402847290039</t>
+    <t xml:space="preserve">23.9402828216553</t>
   </si>
   <si>
     <t xml:space="preserve">24.1448993682861</t>
@@ -3311,19 +3311,19 @@
     <t xml:space="preserve">23.8038711547852</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4177265167236</t>
+    <t xml:space="preserve">24.417724609375</t>
   </si>
   <si>
     <t xml:space="preserve">24.4518299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2131080627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3665733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2472095489502</t>
+    <t xml:space="preserve">24.2131061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3665714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2472114562988</t>
   </si>
   <si>
     <t xml:space="preserve">24.2813110351562</t>
@@ -3338,16 +3338,16 @@
     <t xml:space="preserve">23.5481014251709</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4969444274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9342441558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7978324890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6443710327148</t>
+    <t xml:space="preserve">23.4969463348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9342460632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7978343963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6443691253662</t>
   </si>
   <si>
     <t xml:space="preserve">22.3033428192139</t>
@@ -3356,28 +3356,28 @@
     <t xml:space="preserve">21.8770542144775</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5189723968506</t>
+    <t xml:space="preserve">21.518970489502</t>
   </si>
   <si>
     <t xml:space="preserve">21.8429527282715</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1839790344238</t>
+    <t xml:space="preserve">22.1839809417725</t>
   </si>
   <si>
     <t xml:space="preserve">21.1949939727783</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6383323669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2120456695557</t>
+    <t xml:space="preserve">21.638334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2120475769043</t>
   </si>
   <si>
     <t xml:space="preserve">20.9051189422607</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6663990020752</t>
+    <t xml:space="preserve">20.6664009094238</t>
   </si>
   <si>
     <t xml:space="preserve">21.4678192138672</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">21.0244789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5640888214111</t>
+    <t xml:space="preserve">20.5640907287598</t>
   </si>
   <si>
     <t xml:space="preserve">20.9221725463867</t>
@@ -3395,10 +3395,10 @@
     <t xml:space="preserve">20.5129356384277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2912635803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1378021240234</t>
+    <t xml:space="preserve">20.2912654876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1378040313721</t>
   </si>
   <si>
     <t xml:space="preserve">22.6273212432861</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">23.6163063049316</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7637329101562</t>
+    <t xml:space="preserve">22.7637310028076</t>
   </si>
   <si>
     <t xml:space="preserve">22.8148860931396</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">25.560173034668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9292697906494</t>
+    <t xml:space="preserve">24.9292678833008</t>
   </si>
   <si>
     <t xml:space="preserve">24.8951663970947</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">24.9804210662842</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6624851226807</t>
+    <t xml:space="preserve">25.662483215332</t>
   </si>
   <si>
     <t xml:space="preserve">26.3786468505859</t>
@@ -3464,22 +3464,22 @@
     <t xml:space="preserve">26.7537784576416</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9413433074951</t>
+    <t xml:space="preserve">26.9413452148438</t>
   </si>
   <si>
     <t xml:space="preserve">27.0436534881592</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0948085784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8219833374023</t>
+    <t xml:space="preserve">27.0948104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.821985244751</t>
   </si>
   <si>
     <t xml:space="preserve">26.9925003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1459636688232</t>
+    <t xml:space="preserve">27.1459617614746</t>
   </si>
   <si>
     <t xml:space="preserve">27.7086639404297</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">27.5040435791016</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4699420928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6916084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7939186096191</t>
+    <t xml:space="preserve">27.4699401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6916103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7939205169678</t>
   </si>
   <si>
     <t xml:space="preserve">27.8621273040771</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">28.0496921539307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5893001556396</t>
+    <t xml:space="preserve">27.5893020629883</t>
   </si>
   <si>
     <t xml:space="preserve">27.1800632476807</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">26.856086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6514701843262</t>
+    <t xml:space="preserve">26.6514682769775</t>
   </si>
   <si>
     <t xml:space="preserve">25.3555564880371</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">25.3385047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8901901245117</t>
+    <t xml:space="preserve">26.8901920318604</t>
   </si>
   <si>
     <t xml:space="preserve">27.7598171234131</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">28.5100803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6976509094238</t>
+    <t xml:space="preserve">28.6976490020752</t>
   </si>
   <si>
     <t xml:space="preserve">28.9875221252441</t>
@@ -5487,6 +5487,9 @@
   </si>
   <si>
     <t xml:space="preserve">21.8400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8999996185303</t>
   </si>
 </sst>
 </file>
@@ -25915,7 +25918,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G773" t="s">
-        <v>565</v>
+        <v>430</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25967,7 +25970,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G775" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -26019,7 +26022,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G777" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -26045,7 +26048,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G778" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -26071,7 +26074,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G779" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -26097,7 +26100,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G780" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -26149,7 +26152,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G782" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -26175,7 +26178,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G783" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -26201,7 +26204,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G784" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -26279,7 +26282,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G787" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26305,7 +26308,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G788" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -26331,7 +26334,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G789" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -26357,7 +26360,7 @@
         <v>17.5</v>
       </c>
       <c r="G790" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26461,7 +26464,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G794" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -26487,7 +26490,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G795" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26565,7 +26568,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G798" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26617,7 +26620,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G800" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -26643,7 +26646,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G801" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -26669,7 +26672,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26721,7 +26724,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G804" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26747,7 +26750,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G805" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26773,7 +26776,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G806" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26799,7 +26802,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G807" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26825,7 +26828,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G808" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26851,7 +26854,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G809" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26877,7 +26880,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G810" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26903,7 +26906,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G811" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26929,7 +26932,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G812" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26955,7 +26958,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G813" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26981,7 +26984,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G814" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -27033,7 +27036,7 @@
         <v>16.75</v>
       </c>
       <c r="G816" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -27059,7 +27062,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G817" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -27111,7 +27114,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G819" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -27137,7 +27140,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G820" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27189,7 +27192,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G822" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -27371,7 +27374,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G829" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -27423,7 +27426,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G831" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -27449,7 +27452,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G832" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27579,7 +27582,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G837" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -27683,7 +27686,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G841" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27735,7 +27738,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G843" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27761,7 +27764,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G844" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27787,7 +27790,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G845" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27839,7 +27842,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G847" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27917,7 +27920,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G850" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27943,7 +27946,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G851" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27995,7 +27998,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G853" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -28021,7 +28024,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G854" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28047,7 +28050,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G855" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28073,7 +28076,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G856" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28099,7 +28102,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G857" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28125,7 +28128,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G858" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28151,7 +28154,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G859" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28177,7 +28180,7 @@
         <v>17</v>
       </c>
       <c r="G860" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28203,7 +28206,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G861" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28229,7 +28232,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G862" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28255,7 +28258,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G863" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28281,7 +28284,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G864" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28307,7 +28310,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G865" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28333,7 +28336,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G866" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28359,7 +28362,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G867" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28385,7 +28388,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G868" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28411,7 +28414,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G869" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28437,7 +28440,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G870" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28463,7 +28466,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G871" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28489,7 +28492,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G872" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28515,7 +28518,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G873" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28541,7 +28544,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G874" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28567,7 +28570,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G875" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28593,7 +28596,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G876" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28619,7 +28622,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G877" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -28645,7 +28648,7 @@
         <v>18</v>
       </c>
       <c r="G878" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28671,7 +28674,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G879" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28697,7 +28700,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G880" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -28723,7 +28726,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G881" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -28749,7 +28752,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G882" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -28775,7 +28778,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28801,7 +28804,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G884" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -28827,7 +28830,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G885" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28853,7 +28856,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G886" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28879,7 +28882,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G887" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28905,7 +28908,7 @@
         <v>18</v>
       </c>
       <c r="G888" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28931,7 +28934,7 @@
         <v>18</v>
       </c>
       <c r="G889" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28957,7 +28960,7 @@
         <v>18.25</v>
       </c>
       <c r="G890" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28983,7 +28986,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G891" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -29009,7 +29012,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G892" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -29035,7 +29038,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G893" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29061,7 +29064,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G894" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29087,7 +29090,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29113,7 +29116,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G896" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29139,7 +29142,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G897" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29165,7 +29168,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G898" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29191,7 +29194,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G899" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29217,7 +29220,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29243,7 +29246,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G901" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29269,7 +29272,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G902" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29295,7 +29298,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G903" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29321,7 +29324,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G904" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29347,7 +29350,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G905" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29373,7 +29376,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G906" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29399,7 +29402,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G907" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29425,7 +29428,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G908" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29451,7 +29454,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G909" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29477,7 +29480,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G910" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29503,7 +29506,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G911" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29529,7 +29532,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G912" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29555,7 +29558,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G913" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29581,7 +29584,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G914" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29607,7 +29610,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G915" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29633,7 +29636,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G916" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29659,7 +29662,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G917" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29685,7 +29688,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G918" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29711,7 +29714,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G919" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29737,7 +29740,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G920" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29763,7 +29766,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G921" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -29789,7 +29792,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -29815,7 +29818,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G923" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -29841,7 +29844,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G924" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -29867,7 +29870,7 @@
         <v>17.5</v>
       </c>
       <c r="G925" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29893,7 +29896,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G926" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29919,7 +29922,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G927" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29945,7 +29948,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G928" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29971,7 +29974,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G929" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -29997,7 +30000,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G930" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30023,7 +30026,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G931" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30049,7 +30052,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G932" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30075,7 +30078,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G933" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30101,7 +30104,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G934" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30127,7 +30130,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G935" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30153,7 +30156,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G936" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30179,7 +30182,7 @@
         <v>18.25</v>
       </c>
       <c r="G937" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30205,7 +30208,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G938" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30231,7 +30234,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G939" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30257,7 +30260,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G940" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30283,7 +30286,7 @@
         <v>18</v>
       </c>
       <c r="G941" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30309,7 +30312,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G942" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30335,7 +30338,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G943" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30361,7 +30364,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G944" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30387,7 +30390,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G945" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30413,7 +30416,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G946" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30439,7 +30442,7 @@
         <v>18.75</v>
       </c>
       <c r="G947" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30465,7 +30468,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G948" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -30491,7 +30494,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G949" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -30517,7 +30520,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G950" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30543,7 +30546,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G951" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30569,7 +30572,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G952" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -30595,7 +30598,7 @@
         <v>18.5</v>
       </c>
       <c r="G953" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30621,7 +30624,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G954" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30647,7 +30650,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G955" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -30673,7 +30676,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G956" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -30699,7 +30702,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G957" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30725,7 +30728,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G958" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30751,7 +30754,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G959" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -30777,7 +30780,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G960" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -30803,7 +30806,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G961" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -30829,7 +30832,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G962" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -30855,7 +30858,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G963" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30881,7 +30884,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30907,7 +30910,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G965" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30933,7 +30936,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G966" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30959,7 +30962,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G967" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -30985,7 +30988,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G968" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31011,7 +31014,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G969" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31037,7 +31040,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G970" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31063,7 +31066,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G971" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31089,7 +31092,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G972" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31115,7 +31118,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G973" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31141,7 +31144,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G974" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31167,7 +31170,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G975" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31193,7 +31196,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G976" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31219,7 +31222,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31245,7 +31248,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31271,7 +31274,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G979" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31297,7 +31300,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G980" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31323,7 +31326,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G981" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31349,7 +31352,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G982" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31375,7 +31378,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G983" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31401,7 +31404,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G984" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31427,7 +31430,7 @@
         <v>18.75</v>
       </c>
       <c r="G985" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -31453,7 +31456,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G986" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -31479,7 +31482,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G987" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -31505,7 +31508,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G988" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31531,7 +31534,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G989" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -31557,7 +31560,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G990" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -31583,7 +31586,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G991" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -31609,7 +31612,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G992" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31635,7 +31638,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -31661,7 +31664,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G994" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31687,7 +31690,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G995" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -31713,7 +31716,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G996" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -31739,7 +31742,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G997" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -31765,7 +31768,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -31791,7 +31794,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G999" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -31817,7 +31820,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1000" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -31843,7 +31846,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1001" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -31869,7 +31872,7 @@
         <v>19.25</v>
       </c>
       <c r="G1002" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -31895,7 +31898,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1003" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -31921,7 +31924,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -31947,7 +31950,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1005" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31973,7 +31976,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1006" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -31999,7 +32002,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1007" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32025,7 +32028,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32051,7 +32054,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32077,7 +32080,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1010" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32103,7 +32106,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G1011" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32129,7 +32132,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1012" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32155,7 +32158,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1013" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32181,7 +32184,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1014" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32207,7 +32210,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1015" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32233,7 +32236,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1016" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32259,7 +32262,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1017" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32285,7 +32288,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G1018" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32311,7 +32314,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1019" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32337,7 +32340,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1020" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32363,7 +32366,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1021" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32389,7 +32392,7 @@
         <v>19.75</v>
       </c>
       <c r="G1022" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32415,7 +32418,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1023" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32441,7 +32444,7 @@
         <v>20.5</v>
       </c>
       <c r="G1024" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -32467,7 +32470,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1025" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -32493,7 +32496,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -32519,7 +32522,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1027" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -32545,7 +32548,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1028" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -32571,7 +32574,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -32597,7 +32600,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -32623,7 +32626,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1031" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32649,7 +32652,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G1032" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -32675,7 +32678,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1033" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -32701,7 +32704,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1034" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -32727,7 +32730,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1035" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -32753,7 +32756,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G1036" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -32779,7 +32782,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G1037" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -32805,7 +32808,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1038" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -32831,7 +32834,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1039" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -32857,7 +32860,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1040" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -32883,7 +32886,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1041" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -32909,7 +32912,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1042" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -32935,7 +32938,7 @@
         <v>22</v>
       </c>
       <c r="G1043" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -32961,7 +32964,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1044" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -32987,7 +32990,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1045" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -33013,7 +33016,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1046" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -33039,7 +33042,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1047" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -33065,7 +33068,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1048" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -33091,7 +33094,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G1049" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -33117,7 +33120,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G1050" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -33143,7 +33146,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G1051" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -33169,7 +33172,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1052" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -33195,7 +33198,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1053" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -33221,7 +33224,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -33247,7 +33250,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G1055" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -33273,7 +33276,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1056" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -33299,7 +33302,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -33325,7 +33328,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1058" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -33351,7 +33354,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1059" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -33377,7 +33380,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G1060" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -33403,7 +33406,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1061" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -33429,7 +33432,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1062" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -33455,7 +33458,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1063" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33481,7 +33484,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1064" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -33507,7 +33510,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1065" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -33533,7 +33536,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1066" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -33559,7 +33562,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1067" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -33585,7 +33588,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -33611,7 +33614,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1069" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -33637,7 +33640,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1070" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -33663,7 +33666,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1071" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -33689,7 +33692,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1072" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -33715,7 +33718,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1073" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -33741,7 +33744,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1074" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -33767,7 +33770,7 @@
         <v>15.25</v>
       </c>
       <c r="G1075" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -33793,7 +33796,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1076" t="s">
-        <v>606</v>
+        <v>778</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -34131,7 +34134,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1089" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -34261,7 +34264,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1094" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -34339,7 +34342,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1097" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -34443,7 +34446,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1101" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34521,7 +34524,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -34625,7 +34628,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G1108" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -71293,7 +71296,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6912962963</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>218894</v>
@@ -71314,6 +71317,32 @@
         <v>1824</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6909722222</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>107024</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>21.7000007629395</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>21.9599990844727</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1825</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ERG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43893194198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23837280273438</t>
+    <t xml:space="preserve">7.43893384933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23837471008301</t>
   </si>
   <si>
     <t xml:space="preserve">7.04389333724976</t>
@@ -59,79 +59,79 @@
     <t xml:space="preserve">7.06212472915649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25053024291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22014188766479</t>
+    <t xml:space="preserve">7.25053071975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22014284133911</t>
   </si>
   <si>
     <t xml:space="preserve">7.17152214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07428169250488</t>
+    <t xml:space="preserve">7.07428026199341</t>
   </si>
   <si>
     <t xml:space="preserve">6.84941101074219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01350498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75216913223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83725547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97096157073975</t>
+    <t xml:space="preserve">7.01350450515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75216960906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83725500106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97096252441406</t>
   </si>
   <si>
     <t xml:space="preserve">7.09251356124878</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00742721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00134992599487</t>
+    <t xml:space="preserve">7.00742673873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00134944915771</t>
   </si>
   <si>
     <t xml:space="preserve">6.98919486999512</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92841815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86156463623047</t>
+    <t xml:space="preserve">6.92841911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86156558990479</t>
   </si>
   <si>
     <t xml:space="preserve">6.5333776473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47868061065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61238527297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55160903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77648019790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94057416915894</t>
+    <t xml:space="preserve">6.47867918014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61238574981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5516095161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77647876739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94057369232178</t>
   </si>
   <si>
     <t xml:space="preserve">6.8737211227417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63061857223511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78863477706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58199739456177</t>
+    <t xml:space="preserve">6.63061809539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78863525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58199834823608</t>
   </si>
   <si>
     <t xml:space="preserve">6.70354843139648</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">6.71570491790771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8068675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91626453399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84333229064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83117771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.879798412323</t>
+    <t xml:space="preserve">6.80686712265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91626358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84333324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83117723464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">6.70962619781494</t>
@@ -164,148 +164,148 @@
     <t xml:space="preserve">6.85548830032349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86764430999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95272970199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04997062683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27483987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35992670059204</t>
+    <t xml:space="preserve">6.8676438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95272922515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0499701499939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27484035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35992574691772</t>
   </si>
   <si>
     <t xml:space="preserve">7.34777069091797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26876163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22621870040894</t>
+    <t xml:space="preserve">7.26876211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22621965408325</t>
   </si>
   <si>
     <t xml:space="preserve">7.11074590682983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03173732757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08035898208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05604696273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975496292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23229742050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15328884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11682224273682</t>
+    <t xml:space="preserve">7.03173685073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08035755157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05604648590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23229598999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1532883644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11682367324829</t>
   </si>
   <si>
     <t xml:space="preserve">7.16544389724731</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95880651473999</t>
+    <t xml:space="preserve">6.95880746841431</t>
   </si>
   <si>
     <t xml:space="preserve">6.93449687957764</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89803171157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90410709381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96488380432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79471302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76432514190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14113330841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02565908432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15738677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13741159439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3105206489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25725603103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34381103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38376092910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29720687866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25059938430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21730899810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2372841835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27723073959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2239670753479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10412263870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85777378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65803384780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60477018356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47493934631348</t>
+    <t xml:space="preserve">6.89803123474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90410900115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96488428115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79471254348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76432371139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14113283157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02566051483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15738725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13741207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31052160263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25725698471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34381151199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38375854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29720544815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2505989074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21730947494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062562942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23728275299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27723169326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22396802902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10412311553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85777425765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.658034324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60476970672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47493839263916</t>
   </si>
   <si>
     <t xml:space="preserve">6.50822877883911</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95764636993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93767070770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82448434829712</t>
+    <t xml:space="preserve">6.95764541625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93767166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82448625564575</t>
   </si>
   <si>
     <t xml:space="preserve">6.88440799713135</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">6.47826671600342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32180404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5614914894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69132375717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8178277015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91769742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03754186630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78453683853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50489950180054</t>
+    <t xml:space="preserve">6.3218035697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56149244308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69132423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.81782722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9176983833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03754234313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78453636169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50490045547485</t>
   </si>
   <si>
     <t xml:space="preserve">6.6180853843689</t>
@@ -344,22 +344,22 @@
     <t xml:space="preserve">6.71795654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68466663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73793077468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87774991989136</t>
+    <t xml:space="preserve">6.68466711044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73793172836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87774896621704</t>
   </si>
   <si>
     <t xml:space="preserve">6.81116819381714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7512469291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79119443893433</t>
+    <t xml:space="preserve">6.75124597549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79119396209717</t>
   </si>
   <si>
     <t xml:space="preserve">6.76456260681152</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">6.86443376541138</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77122116088867</t>
+    <t xml:space="preserve">6.77122020721436</t>
   </si>
   <si>
     <t xml:space="preserve">6.89106512069702</t>
@@ -377,16 +377,16 @@
     <t xml:space="preserve">6.73127222061157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64471817016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63805961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75790405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83114290237427</t>
+    <t xml:space="preserve">6.64471769332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63806056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75790452957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83114337921143</t>
   </si>
   <si>
     <t xml:space="preserve">6.80451059341431</t>
@@ -395,49 +395,49 @@
     <t xml:space="preserve">6.93101406097412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96430349349976</t>
+    <t xml:space="preserve">6.96430397033691</t>
   </si>
   <si>
     <t xml:space="preserve">6.74458885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71129894256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65137672424316</t>
+    <t xml:space="preserve">6.7112979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65137577056885</t>
   </si>
   <si>
     <t xml:space="preserve">6.62807321548462</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64138984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62141370773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01756906509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98427772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01091051101685</t>
+    <t xml:space="preserve">6.64138889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62141418457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01756811141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98427820205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.010910987854</t>
   </si>
   <si>
     <t xml:space="preserve">7.04419994354248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17070245742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87109088897705</t>
+    <t xml:space="preserve">7.17070341110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87109041213989</t>
   </si>
   <si>
     <t xml:space="preserve">6.92435598373413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97761964797974</t>
+    <t xml:space="preserve">6.97761917114258</t>
   </si>
   <si>
     <t xml:space="preserve">6.83780193328857</t>
@@ -449,112 +449,112 @@
     <t xml:space="preserve">6.79785251617432</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77787923812866</t>
+    <t xml:space="preserve">6.7778787612915</t>
   </si>
   <si>
     <t xml:space="preserve">6.59811162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55150508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72461414337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67135095596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66469192504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60809946060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54484796524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45829343795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65470409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67800903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4649510383606</t>
+    <t xml:space="preserve">6.55150556564331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72461462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67135143280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66469287872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60809993743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54484748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45829296112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65470457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67800855636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46495151519775</t>
   </si>
   <si>
     <t xml:space="preserve">6.13870763778687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.228590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19197225570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17865467071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24856472015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13537836074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06546831130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16866827011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15868139266968</t>
+    <t xml:space="preserve">6.22859144210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19197177886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17865610122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24856519699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13537883758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06546878814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16866874694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15868186950684</t>
   </si>
   <si>
     <t xml:space="preserve">6.14203691482544</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0621395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03883600234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10874605178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881214141846</t>
+    <t xml:space="preserve">6.06214046478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03883695602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10874700546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05881118774414</t>
   </si>
   <si>
     <t xml:space="preserve">6.02219200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01886320114136</t>
+    <t xml:space="preserve">6.0188627243042</t>
   </si>
   <si>
     <t xml:space="preserve">6.11873340606689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23191976547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12206268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22193288803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21860456466675</t>
+    <t xml:space="preserve">6.23191928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12206220626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22193336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21860313415527</t>
   </si>
   <si>
     <t xml:space="preserve">6.35842275619507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37839555740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6247444152832</t>
+    <t xml:space="preserve">6.37839651107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62474346160889</t>
   </si>
   <si>
     <t xml:space="preserve">6.70463991165161</t>
@@ -563,43 +563,43 @@
     <t xml:space="preserve">6.85111713409424</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69798231124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.904381275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89772319793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99093580245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07748985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91104078292847</t>
+    <t xml:space="preserve">6.69798278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90438175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89772272109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99093532562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07749128341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91103982925415</t>
   </si>
   <si>
     <t xml:space="preserve">7.07083225250244</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13075542449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15072870254517</t>
+    <t xml:space="preserve">7.13075494766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15072822570801</t>
   </si>
   <si>
     <t xml:space="preserve">7.18401908874512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09746599197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05085897445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35046911239624</t>
+    <t xml:space="preserve">7.0974645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05085849761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35046863555908</t>
   </si>
   <si>
     <t xml:space="preserve">7.27057409286499</t>
@@ -608,118 +608,118 @@
     <t xml:space="preserve">7.28388929367065</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30386352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53023719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32383680343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31717967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36378717422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51692008972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59015846252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347509384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000385284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992559432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77658462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73663568496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78990077972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75660991668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8231897354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85648059844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86979532241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87645530700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308713912964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96966695785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94969272613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92306041717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96300840377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72332000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62344837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5435528755188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47031450271606</t>
+    <t xml:space="preserve">7.30386304855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53023672103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32383823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31718015670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36378574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51692056655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59015893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347557067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71000289916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992607116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77658367156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73663520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78989934921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75660943984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82319021224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85648107528687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86979675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87645435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308570861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96966648101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9496922492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92305898666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96300983428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311243057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72331953048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62344980239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54355192184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47031497955322</t>
   </si>
   <si>
     <t xml:space="preserve">7.63676595687866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56352615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57018518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74329376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80321550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89642858505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94303512573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84982204437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06953811645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2084264755249</t>
+    <t xml:space="preserve">7.56352663040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5701847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74329280853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8032169342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89642810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94303417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84982347488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06953716278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20842838287354</t>
   </si>
   <si>
     <t xml:space="preserve">8.25009441375732</t>
@@ -728,37 +728,37 @@
     <t xml:space="preserve">8.22926139831543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31953907012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35426139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28481769561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2987060546875</t>
+    <t xml:space="preserve">8.31954097747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35426235198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28481674194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29870700836182</t>
   </si>
   <si>
     <t xml:space="preserve">8.37509632110596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34731864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3889856338501</t>
+    <t xml:space="preserve">8.34731769561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38898372650146</t>
   </si>
   <si>
     <t xml:space="preserve">8.43759727478027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4514856338501</t>
+    <t xml:space="preserve">8.45148658752441</t>
   </si>
   <si>
     <t xml:space="preserve">8.68760108947754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73621273040771</t>
+    <t xml:space="preserve">8.73621082305908</t>
   </si>
   <si>
     <t xml:space="preserve">8.62509918212891</t>
@@ -767,34 +767,34 @@
     <t xml:space="preserve">8.63898754119873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66676712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68065643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59732055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72926807403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69454383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61121082305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50704383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59037590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52787494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54870986938477</t>
+    <t xml:space="preserve">8.6667652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68065547943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59732151031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72926712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69454479217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61120891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50704193115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59037780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52787590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54870891571045</t>
   </si>
   <si>
     <t xml:space="preserve">8.4931526184082</t>
@@ -803,31 +803,31 @@
     <t xml:space="preserve">8.51398658752441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46537399291992</t>
+    <t xml:space="preserve">8.46537494659424</t>
   </si>
   <si>
     <t xml:space="preserve">8.47231960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61815547943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65982151031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6459321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40981864929199</t>
+    <t xml:space="preserve">8.61815357208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65982055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64593315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40981769561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.4306526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42370700836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30564975738525</t>
+    <t xml:space="preserve">8.42370796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30565071105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.5417652130127</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">8.57648849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6042652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88204574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00010299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15288352966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13204860687256</t>
+    <t xml:space="preserve">8.60426712036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71537780761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88204669952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00010395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15288257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13204956054688</t>
   </si>
   <si>
     <t xml:space="preserve">9.06954956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09038257598877</t>
+    <t xml:space="preserve">9.09038352966309</t>
   </si>
   <si>
     <t xml:space="preserve">9.00704765319824</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">9.24316215515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29871940612793</t>
+    <t xml:space="preserve">9.2987174987793</t>
   </si>
   <si>
     <t xml:space="preserve">9.3681640625</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">9.40983104705811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41677665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32649612426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29177379608154</t>
+    <t xml:space="preserve">9.41677474975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32649517059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29177284240723</t>
   </si>
   <si>
     <t xml:space="preserve">9.31260776519775</t>
@@ -902,34 +902,34 @@
     <t xml:space="preserve">9.45149803161621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47233104705811</t>
+    <t xml:space="preserve">9.47233200073242</t>
   </si>
   <si>
     <t xml:space="preserve">9.43760871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44455432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40288543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38899803161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38205337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34038543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34733009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31955242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48622035980225</t>
+    <t xml:space="preserve">9.44455242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4028844833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38899707794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38205146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3403844833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34732913970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31955146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48622131347656</t>
   </si>
   <si>
     <t xml:space="preserve">9.75011253356934</t>
@@ -938,55 +938,55 @@
     <t xml:space="preserve">9.79177951812744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77788925170898</t>
+    <t xml:space="preserve">9.7778902053833</t>
   </si>
   <si>
     <t xml:space="preserve">9.80566883087158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72927761077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77094650268555</t>
+    <t xml:space="preserve">9.72927856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77094554901123</t>
   </si>
   <si>
     <t xml:space="preserve">9.76400184631348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74316692352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96539211273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0278940200806</t>
+    <t xml:space="preserve">9.74316787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96539306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0278930664062</t>
   </si>
   <si>
     <t xml:space="preserve">9.93761444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0834503173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1181716918945</t>
+    <t xml:space="preserve">10.0834512710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1181726455688</t>
   </si>
   <si>
     <t xml:space="preserve">10.1876173019409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4445648193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5001220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5695667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2292833328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3959531784058</t>
+    <t xml:space="preserve">10.4445638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5001211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5695657730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2292852401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3959522247314</t>
   </si>
   <si>
     <t xml:space="preserve">10.423731803894</t>
@@ -998,19 +998,19 @@
     <t xml:space="preserve">10.4931764602661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5626211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6251230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6042890548706</t>
+    <t xml:space="preserve">10.5626201629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6251220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6042881011963</t>
   </si>
   <si>
     <t xml:space="preserve">10.7015113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7779016494751</t>
+    <t xml:space="preserve">10.7779026031494</t>
   </si>
   <si>
     <t xml:space="preserve">10.8542919158936</t>
@@ -1019,22 +1019,22 @@
     <t xml:space="preserve">10.833456993103</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9029026031494</t>
+    <t xml:space="preserve">10.9029035568237</t>
   </si>
   <si>
     <t xml:space="preserve">11.0904054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1042928695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1112384796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9723482131958</t>
+    <t xml:space="preserve">11.1042938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1112394332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667881011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9723491668701</t>
   </si>
   <si>
     <t xml:space="preserve">10.9445695877075</t>
@@ -1043,10 +1043,10 @@
     <t xml:space="preserve">11.0765161514282</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3473520278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3959646224976</t>
+    <t xml:space="preserve">11.3473529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3959636688232</t>
   </si>
   <si>
     <t xml:space="preserve">11.1529054641724</t>
@@ -1058,25 +1058,25 @@
     <t xml:space="preserve">11.2154064178467</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3126316070557</t>
+    <t xml:space="preserve">11.3126306533813</t>
   </si>
   <si>
     <t xml:space="preserve">11.2362403869629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2084627151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9098482131958</t>
+    <t xml:space="preserve">11.2084608078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9098491668701</t>
   </si>
   <si>
     <t xml:space="preserve">10.736234664917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8751249313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6945686340332</t>
+    <t xml:space="preserve">10.8751239776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6945667266846</t>
   </si>
   <si>
     <t xml:space="preserve">10.548731803894</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">10.8612365722656</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0695724487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.187629699707</t>
+    <t xml:space="preserve">11.0695705413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876287460327</t>
   </si>
   <si>
     <t xml:space="preserve">10.9306802749634</t>
@@ -1106,16 +1106,16 @@
     <t xml:space="preserve">11.5001316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4931859970093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6251335144043</t>
+    <t xml:space="preserve">11.4931879043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6251344680786</t>
   </si>
   <si>
     <t xml:space="preserve">11.7223558425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709693908691</t>
+    <t xml:space="preserve">11.7709703445435</t>
   </si>
   <si>
     <t xml:space="preserve">11.7015237808228</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">11.729302406311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7154130935669</t>
+    <t xml:space="preserve">11.7154121398926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6112442016602</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">11.6806888580322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3820753097534</t>
+    <t xml:space="preserve">11.3820743560791</t>
   </si>
   <si>
     <t xml:space="preserve">10.8681802749634</t>
@@ -1148,19 +1148,19 @@
     <t xml:space="preserve">10.8959589004517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9862375259399</t>
+    <t xml:space="preserve">10.9862365722656</t>
   </si>
   <si>
     <t xml:space="preserve">11.0834608078003</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292957305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3265199661255</t>
+    <t xml:space="preserve">11.2292966842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3265190124512</t>
   </si>
   <si>
     <t xml:space="preserve">11.2431859970093</t>
@@ -1169,28 +1169,28 @@
     <t xml:space="preserve">11.5973558425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7501354217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6181879043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7987470626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6320781707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8334712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1251382827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.916802406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6668119430542</t>
+    <t xml:space="preserve">11.7501363754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6181888580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7987461090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6320772171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8334703445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1251392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9168043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6668109893799</t>
   </si>
   <si>
     <t xml:space="preserve">13.1529293060303</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">13.3820991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">13.319598197937</t>
+    <t xml:space="preserve">13.3195962905884</t>
   </si>
   <si>
     <t xml:space="preserve">13.3682098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.576545715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5209875106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2362623214722</t>
+    <t xml:space="preserve">13.5765447616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5209884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2362632751465</t>
   </si>
   <si>
     <t xml:space="preserve">13.1668167114258</t>
@@ -1220,43 +1220,43 @@
     <t xml:space="preserve">13.0487623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4237651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0070934295654</t>
+    <t xml:space="preserve">13.4237632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070953369141</t>
   </si>
   <si>
     <t xml:space="preserve">13.354320526123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4584865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154378890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918252944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6807146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9168281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9307174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1876525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2987642288208</t>
+    <t xml:space="preserve">13.4584875106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154359817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918243408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6807117462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9168272018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9307155609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1876516342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2987623214722</t>
   </si>
   <si>
     <t xml:space="preserve">13.3751544952393</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4168214797974</t>
+    <t xml:space="preserve">13.416820526123</t>
   </si>
   <si>
     <t xml:space="preserve">13.4723777770996</t>
@@ -1265,13 +1265,13 @@
     <t xml:space="preserve">13.4862661361694</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6112670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7362699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223815917969</t>
+    <t xml:space="preserve">13.6112680435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7362718582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223806381226</t>
   </si>
   <si>
     <t xml:space="preserve">13.8196048736572</t>
@@ -1280,37 +1280,37 @@
     <t xml:space="preserve">13.889048576355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8543281555176</t>
+    <t xml:space="preserve">13.8543272018433</t>
   </si>
   <si>
     <t xml:space="preserve">13.9029378890991</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0834951400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.798770904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0279388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.194598197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1112613677979</t>
+    <t xml:space="preserve">14.0834970474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7987699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0279378890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057203292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1945962905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1112623214722</t>
   </si>
   <si>
     <t xml:space="preserve">13.1807069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0200986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1486539840698</t>
+    <t xml:space="preserve">14.0200996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1486549377441</t>
   </si>
   <si>
     <t xml:space="preserve">13.8083600997925</t>
@@ -1319,166 +1319,166 @@
     <t xml:space="preserve">13.6571178436279</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5361261367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2563285827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1277723312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3092613220215</t>
+    <t xml:space="preserve">13.5361242294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2563276290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1277713775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3092622756958</t>
   </si>
   <si>
     <t xml:space="preserve">13.4605045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4983158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4680652618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.573935508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7327394485474</t>
+    <t xml:space="preserve">13.4983148574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4680671691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5739364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.732738494873</t>
   </si>
   <si>
     <t xml:space="preserve">13.7478637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4075698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4889450073242</t>
+    <t xml:space="preserve">13.4075689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4889459609985</t>
   </si>
   <si>
     <t xml:space="preserve">14.4738235473633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6704387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755159378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6175022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.723370552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9351119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7460594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292427062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167119979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2998962402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2091512680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0654716491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1637773513794</t>
+    <t xml:space="preserve">14.6704368591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158098220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755178451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6175012588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7233715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9351091384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.746057510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292417526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2998933792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2091503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0654706954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1637763977051</t>
   </si>
   <si>
     <t xml:space="preserve">14.0427846908569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1713380813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2847719192505</t>
+    <t xml:space="preserve">14.1713399887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2847709655762</t>
   </si>
   <si>
     <t xml:space="preserve">14.6250629425049</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7536211013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6780004501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7914323806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8443632125854</t>
+    <t xml:space="preserve">14.7536201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6779985427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7914304733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8443651199341</t>
   </si>
   <si>
     <t xml:space="preserve">14.8746128082275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8368043899536</t>
+    <t xml:space="preserve">14.8368034362793</t>
   </si>
   <si>
     <t xml:space="preserve">14.7611827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6553115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5494422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099414825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6401891708374</t>
+    <t xml:space="preserve">14.6553134918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5494432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099405288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.640191078186</t>
   </si>
   <si>
     <t xml:space="preserve">14.5721302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5191974639893</t>
+    <t xml:space="preserve">14.5191955566406</t>
   </si>
   <si>
     <t xml:space="preserve">14.2393999099731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0049753189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9217901229858</t>
+    <t xml:space="preserve">14.0049743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9217910766602</t>
   </si>
   <si>
     <t xml:space="preserve">13.9142293930054</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2696466445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3982038497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9898490905762</t>
+    <t xml:space="preserve">14.2696475982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3982028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9898471832275</t>
   </si>
   <si>
     <t xml:space="preserve">13.6646795272827</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6722440719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5814962387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7705488204956</t>
+    <t xml:space="preserve">13.6722421646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5814981460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705497741699</t>
   </si>
   <si>
     <t xml:space="preserve">13.6268701553345</t>
@@ -1487,25 +1487,25 @@
     <t xml:space="preserve">13.5210008621216</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6495561599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.551248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907531738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4756278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5058755874634</t>
+    <t xml:space="preserve">13.6495580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5512495040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4756298065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.505877494812</t>
   </si>
   <si>
     <t xml:space="preserve">13.3470726013184</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924446105957</t>
+    <t xml:space="preserve">13.3924436569214</t>
   </si>
   <si>
     <t xml:space="preserve">13.4831895828247</t>
@@ -1514,40 +1514,40 @@
     <t xml:space="preserve">13.8310480117798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6344318389893</t>
+    <t xml:space="preserve">13.6344327926636</t>
   </si>
   <si>
     <t xml:space="preserve">13.5663738250732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5436859130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3773221969604</t>
+    <t xml:space="preserve">13.5436868667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3773231506348</t>
   </si>
   <si>
     <t xml:space="preserve">13.1958322525024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2714529037476</t>
+    <t xml:space="preserve">13.2714519500732</t>
   </si>
   <si>
     <t xml:space="preserve">13.3395109176636</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3546352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2638893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4529438018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3319473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9311590194702</t>
+    <t xml:space="preserve">13.3546342849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2638912200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4529428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3319492340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9311599731445</t>
   </si>
   <si>
     <t xml:space="preserve">13.0219030380249</t>
@@ -1556,28 +1556,28 @@
     <t xml:space="preserve">12.8101654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5530557632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7421064376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6513605117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1202116012573</t>
+    <t xml:space="preserve">12.5530548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7421073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6513614654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848848342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.120210647583</t>
   </si>
   <si>
     <t xml:space="preserve">12.9614067077637</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5681791305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4396238327026</t>
+    <t xml:space="preserve">12.5681800842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4396228790283</t>
   </si>
   <si>
     <t xml:space="preserve">12.6211137771606</t>
@@ -1589,13 +1589,13 @@
     <t xml:space="preserve">12.4925584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4698715209961</t>
+    <t xml:space="preserve">12.4698724746704</t>
   </si>
   <si>
     <t xml:space="preserve">12.1371393203735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2883806228638</t>
+    <t xml:space="preserve">12.2883815765381</t>
   </si>
   <si>
     <t xml:space="preserve">12.1522645950317</t>
@@ -1604,22 +1604,22 @@
     <t xml:space="preserve">12.6286754608154</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6437997817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252897262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7723560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.847975730896</t>
+    <t xml:space="preserve">12.643798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.825288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7723550796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8479747772217</t>
   </si>
   <si>
     <t xml:space="preserve">12.757230758667</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8177280426025</t>
+    <t xml:space="preserve">12.8177270889282</t>
   </si>
   <si>
     <t xml:space="preserve">12.7799158096313</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">12.4471855163574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4244985580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2581338882446</t>
+    <t xml:space="preserve">12.4245004653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2581329345703</t>
   </si>
   <si>
     <t xml:space="preserve">12.1673879623413</t>
@@ -1640,43 +1640,43 @@
     <t xml:space="preserve">12.416937828064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1447019577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.031270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2505722045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1068916320801</t>
+    <t xml:space="preserve">12.1447010040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0312700271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2505712509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1068935394287</t>
   </si>
   <si>
     <t xml:space="preserve">12.2278852462769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0463953018188</t>
+    <t xml:space="preserve">12.0463943481445</t>
   </si>
   <si>
     <t xml:space="preserve">12.0993299484253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7968454360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8800296783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5379285812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2656936645508</t>
+    <t xml:space="preserve">11.7968463897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.880030632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5379295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2656955718994</t>
   </si>
   <si>
     <t xml:space="preserve">12.7950420379639</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2941398620605</t>
+    <t xml:space="preserve">13.2941389083862</t>
   </si>
   <si>
     <t xml:space="preserve">13.1126489639282</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">12.9538440704346</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5833015441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4774341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.575740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8555374145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0143394470215</t>
+    <t xml:space="preserve">12.5833024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4774332046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5757398605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8555364608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0143423080444</t>
   </si>
   <si>
     <t xml:space="preserve">12.8328514099121</t>
@@ -1706,34 +1706,37 @@
     <t xml:space="preserve">12.9084720611572</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0521516799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.916033744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0975246429443</t>
+    <t xml:space="preserve">13.052152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1807088851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9160356521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0975227355957</t>
   </si>
   <si>
     <t xml:space="preserve">13.0067796707153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2260808944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2185173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9009103775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0370283126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7647914886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.029465675354</t>
+    <t xml:space="preserve">13.2260789871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2185163497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9009094238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0370264053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7647924423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0294647216797</t>
   </si>
   <si>
     <t xml:space="preserve">13.2109546661377</t>
@@ -1742,7 +1745,7 @@
     <t xml:space="preserve">13.2336416244507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9235982894897</t>
+    <t xml:space="preserve">12.9235963821411</t>
   </si>
   <si>
     <t xml:space="preserve">12.870662689209</t>
@@ -1751,16 +1754,16 @@
     <t xml:space="preserve">12.893346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1882696151733</t>
+    <t xml:space="preserve">13.1882705688477</t>
   </si>
   <si>
     <t xml:space="preserve">13.1353349685669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9689683914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1050853729248</t>
+    <t xml:space="preserve">12.9689693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1050863265991</t>
   </si>
   <si>
     <t xml:space="preserve">13.3016996383667</t>
@@ -1769,46 +1772,46 @@
     <t xml:space="preserve">12.8857879638672</t>
   </si>
   <si>
-    <t xml:space="preserve">12.689172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6967334747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6362380981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6664867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5152425765991</t>
+    <t xml:space="preserve">12.6891717910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6967363357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6362371444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6664848327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5152444839478</t>
   </si>
   <si>
     <t xml:space="preserve">12.3110685348511</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2430095672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0388326644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6589241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7269830703735</t>
+    <t xml:space="preserve">12.2430105209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0388336181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6589250564575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7269821166992</t>
   </si>
   <si>
     <t xml:space="preserve">12.7496700286865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3186311721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1900749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1976356506348</t>
+    <t xml:space="preserve">12.3186321258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1900758743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1976366043091</t>
   </si>
   <si>
     <t xml:space="preserve">12.1749515533447</t>
@@ -1817,46 +1820,46 @@
     <t xml:space="preserve">12.2732572555542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1598272323608</t>
+    <t xml:space="preserve">12.1598262786865</t>
   </si>
   <si>
     <t xml:space="preserve">12.2203226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2808208465576</t>
+    <t xml:space="preserve">12.2808198928833</t>
   </si>
   <si>
     <t xml:space="preserve">12.303505897522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631000518799</t>
+    <t xml:space="preserve">12.8631010055542</t>
   </si>
   <si>
     <t xml:space="preserve">13.2902870178223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4485054016113</t>
+    <t xml:space="preserve">13.4485063552856</t>
   </si>
   <si>
     <t xml:space="preserve">13.5988121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6146326065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9548015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9785356521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8598728179932</t>
+    <t xml:space="preserve">13.6146335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9548034667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.978533744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8598709106445</t>
   </si>
   <si>
     <t xml:space="preserve">13.7491188049316</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7332973480225</t>
+    <t xml:space="preserve">13.7332992553711</t>
   </si>
   <si>
     <t xml:space="preserve">13.7728519439697</t>
@@ -1868,67 +1871,67 @@
     <t xml:space="preserve">13.7174758911133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6383676528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6620998382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5750789642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1446628570557</t>
+    <t xml:space="preserve">13.6383657455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6620988845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5750799179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1446647644043</t>
   </si>
   <si>
     <t xml:space="preserve">14.2395944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5085639953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4690113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7221593856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6746912002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.176305770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1604862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0813770294189</t>
+    <t xml:space="preserve">14.508563041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.469012260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955829620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7221574783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6746940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1763048171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1604833602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.081374168396</t>
   </si>
   <si>
     <t xml:space="preserve">14.0339097976685</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4373664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6984252929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6114044189453</t>
+    <t xml:space="preserve">14.4373655319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6984233856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6114053726196</t>
   </si>
   <si>
     <t xml:space="preserve">14.4136323928833</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6272268295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1097917556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0939683914185</t>
+    <t xml:space="preserve">14.6272277832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1097898483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0939693450928</t>
   </si>
   <si>
     <t xml:space="preserve">14.9911289215088</t>
@@ -1937,13 +1940,13 @@
     <t xml:space="preserve">14.9436635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9120178222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.872465133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8645553588867</t>
+    <t xml:space="preserve">14.9120187759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.872462272644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8645544052124</t>
   </si>
   <si>
     <t xml:space="preserve">14.6430492401123</t>
@@ -1952,16 +1955,16 @@
     <t xml:space="preserve">14.2870588302612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3266134262085</t>
+    <t xml:space="preserve">14.3266143798828</t>
   </si>
   <si>
     <t xml:space="preserve">14.2158603668213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.247504234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0260000228882</t>
+    <t xml:space="preserve">14.2475051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0259981155396</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576438903809</t>
@@ -1970,7 +1973,7 @@
     <t xml:space="preserve">13.6067237854004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8677825927734</t>
+    <t xml:space="preserve">13.8677835464478</t>
   </si>
   <si>
     <t xml:space="preserve">14.2000398635864</t>
@@ -1982,22 +1985,22 @@
     <t xml:space="preserve">14.2079496383667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6304559707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5671682357788</t>
+    <t xml:space="preserve">13.6304550170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5671691894531</t>
   </si>
   <si>
     <t xml:space="preserve">13.6700096130371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5197048187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3693952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8203153610229</t>
+    <t xml:space="preserve">13.519702911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3693962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8203163146973</t>
   </si>
   <si>
     <t xml:space="preserve">13.9073371887207</t>
@@ -2006,13 +2009,13 @@
     <t xml:space="preserve">13.8440504074097</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5592565536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7886724472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965850830078</t>
+    <t xml:space="preserve">13.5592575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7886743545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965860366821</t>
   </si>
   <si>
     <t xml:space="preserve">14.1209316253662</t>
@@ -2021,37 +2024,37 @@
     <t xml:space="preserve">13.9310693740845</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0892868041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.302882194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4848308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6588697433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633256912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2316837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1130199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5876722335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.975305557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8566427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9990367889404</t>
+    <t xml:space="preserve">14.0892858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3028812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4848318099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6588726043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633275985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2316827774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1130208969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5876731872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9753046035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8566417694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9990396499634</t>
   </si>
   <si>
     <t xml:space="preserve">14.8329105377197</t>
@@ -2060,124 +2063,124 @@
     <t xml:space="preserve">14.745888710022</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0227718353271</t>
+    <t xml:space="preserve">15.0227708816528</t>
   </si>
   <si>
     <t xml:space="preserve">14.7379779815674</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7854452133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6905136108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6351375579834</t>
+    <t xml:space="preserve">14.7854461669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6905145645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.635139465332</t>
   </si>
   <si>
     <t xml:space="preserve">14.5402069091797</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1525726318359</t>
+    <t xml:space="preserve">14.1525745391846</t>
   </si>
   <si>
     <t xml:space="preserve">14.5164747238159</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4294538497925</t>
+    <t xml:space="preserve">14.4294548034668</t>
   </si>
   <si>
     <t xml:space="preserve">14.1921291351318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0971965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2712364196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2791481018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4057216644287</t>
+    <t xml:space="preserve">14.0971984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2712392807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.279149055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.405722618103</t>
   </si>
   <si>
     <t xml:space="preserve">14.3899021148682</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3424348831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3582572937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4610996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0069484710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9515733718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5322961807251</t>
+    <t xml:space="preserve">14.3424339294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3582563400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4610986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0069494247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9515743255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5322971343994</t>
   </si>
   <si>
     <t xml:space="preserve">14.3345241546631</t>
   </si>
   <si>
-    <t xml:space="preserve">14.374077796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3819894790649</t>
+    <t xml:space="preserve">14.374080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3819904327393</t>
   </si>
   <si>
     <t xml:space="preserve">14.6509609222412</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0860586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8170881271362</t>
+    <t xml:space="preserve">15.0860595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8170900344849</t>
   </si>
   <si>
     <t xml:space="preserve">14.6193170547485</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0544166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4895124435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.869236946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7189311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3075647354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3471193313599</t>
+    <t xml:space="preserve">15.0544157028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4895143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8692350387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7189302444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.307562828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3471183776855</t>
   </si>
   <si>
     <t xml:space="preserve">15.6081781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2284545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572542190552</t>
+    <t xml:space="preserve">15.2284564971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572561264038</t>
   </si>
   <si>
     <t xml:space="preserve">15.1889009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1414356231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3866748809814</t>
+    <t xml:space="preserve">15.1414337158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3866710662842</t>
   </si>
   <si>
     <t xml:space="preserve">15.2838315963745</t>
@@ -2189,13 +2192,13 @@
     <t xml:space="preserve">15.7505731582642</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7110185623169</t>
+    <t xml:space="preserve">15.7110195159912</t>
   </si>
   <si>
     <t xml:space="preserve">15.6160869598389</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4420490264893</t>
+    <t xml:space="preserve">15.4420471191406</t>
   </si>
   <si>
     <t xml:space="preserve">15.2047214508057</t>
@@ -2207,25 +2210,25 @@
     <t xml:space="preserve">15.1651678085327</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4024925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6240005493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7743053436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2173137664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5179271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2964210510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5653953552246</t>
+    <t xml:space="preserve">15.402491569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6239986419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7743072509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2173156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5179290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.296422958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.565393447876</t>
   </si>
   <si>
     <t xml:space="preserve">17.0400466918945</t>
@@ -2234,22 +2237,22 @@
     <t xml:space="preserve">16.9292945861816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0875148773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0558662414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9609375</t>
+    <t xml:space="preserve">17.0875129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0558681488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9609394073486</t>
   </si>
   <si>
     <t xml:space="preserve">16.6919689178467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8976497650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1982669830322</t>
+    <t xml:space="preserve">16.8976516723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.198263168335</t>
   </si>
   <si>
     <t xml:space="preserve">16.8818302154541</t>
@@ -2261,16 +2264,16 @@
     <t xml:space="preserve">17.3564834594727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4514102935791</t>
+    <t xml:space="preserve">17.4514141082764</t>
   </si>
   <si>
     <t xml:space="preserve">17.6096305847168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4039459228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4355945587158</t>
+    <t xml:space="preserve">17.4039478302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4355907440186</t>
   </si>
   <si>
     <t xml:space="preserve">17.5305213928223</t>
@@ -2285,37 +2288,37 @@
     <t xml:space="preserve">18.1317481994629</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2583255767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3690757751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.289966583252</t>
+    <t xml:space="preserve">18.2583236694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3690776824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2899684906006</t>
   </si>
   <si>
     <t xml:space="preserve">18.2108592987061</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3723011016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4830570220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7045612335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3248386383057</t>
+    <t xml:space="preserve">17.3723030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4830589294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7045574188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.324836730957</t>
   </si>
   <si>
     <t xml:space="preserve">16.5021076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4988822937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1507987976074</t>
+    <t xml:space="preserve">17.4988784790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1508007049561</t>
   </si>
   <si>
     <t xml:space="preserve">11.1701707839966</t>
@@ -2324,16 +2327,16 @@
     <t xml:space="preserve">13.0213174819946</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8267736434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6210908889771</t>
+    <t xml:space="preserve">11.8267726898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6210899353027</t>
   </si>
   <si>
     <t xml:space="preserve">11.6290016174316</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3600301742554</t>
+    <t xml:space="preserve">11.3600311279297</t>
   </si>
   <si>
     <t xml:space="preserve">10.9882202148438</t>
@@ -2348,64 +2351,61 @@
     <t xml:space="preserve">12.0641002655029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631010055542</t>
-  </si>
-  <si>
     <t xml:space="preserve">12.4200897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1748514175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9026546478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6969699859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.219090461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4722394943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3140201568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2349100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1241579055786</t>
+    <t xml:space="preserve">12.1748533248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9026536941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6969709396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2190895080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4722385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.314019203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2349109649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1241588592529</t>
   </si>
   <si>
     <t xml:space="preserve">13.4089517593384</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4564161300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1004266738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0925140380859</t>
+    <t xml:space="preserve">13.4564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1004247665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0925159454346</t>
   </si>
   <si>
     <t xml:space="preserve">13.2507333755493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0687837600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3614864349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4326820373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5038814544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9738521575928</t>
+    <t xml:space="preserve">13.0687847137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3614845275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4326839447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5038795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9738512039185</t>
   </si>
   <si>
     <t xml:space="preserve">12.9342975616455</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">13.0371379852295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1795358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2111787796021</t>
+    <t xml:space="preserve">13.1795349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2111806869507</t>
   </si>
   <si>
     <t xml:space="preserve">13.543436050415</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">13.6225442886353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7095632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2056894302368</t>
+    <t xml:space="preserve">13.7095642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2056903839111</t>
   </si>
   <si>
     <t xml:space="preserve">13.8418645858765</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">14.1560773849487</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2966470718384</t>
+    <t xml:space="preserve">14.2966451644897</t>
   </si>
   <si>
     <t xml:space="preserve">14.2883758544922</t>
@@ -2447,22 +2447,22 @@
     <t xml:space="preserve">15.0491008758545</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2475490570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2971620559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1240348815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4134407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5043983459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1405754089355</t>
+    <t xml:space="preserve">15.2475500106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2971630096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1240367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4134426116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5043964385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1405715942383</t>
   </si>
   <si>
     <t xml:space="preserve">16.0909595489502</t>
@@ -2471,55 +2471,55 @@
     <t xml:space="preserve">16.190185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286874771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2144737243652</t>
+    <t xml:space="preserve">15.5865678787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3467741012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2144746780396</t>
   </si>
   <si>
     <t xml:space="preserve">15.2806253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8346290588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.652717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692552566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5782985687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932872772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8594350814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3633117675781</t>
+    <t xml:space="preserve">15.8346300125122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6527166366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5782995223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932844161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8594360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3633108139038</t>
   </si>
   <si>
     <t xml:space="preserve">15.429461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5617609024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8677043914795</t>
+    <t xml:space="preserve">15.5617599487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8677072525024</t>
   </si>
   <si>
     <t xml:space="preserve">16.330753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0501346588135</t>
+    <t xml:space="preserve">17.0501365661621</t>
   </si>
   <si>
     <t xml:space="preserve">17.2651214599609</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">17.1162853240967</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3312683105469</t>
+    <t xml:space="preserve">17.3312702178955</t>
   </si>
   <si>
     <t xml:space="preserve">17.51318359375</t>
@@ -2543,19 +2543,19 @@
     <t xml:space="preserve">17.7777824401855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2981948852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2816562652588</t>
+    <t xml:space="preserve">17.2981967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2816581726074</t>
   </si>
   <si>
     <t xml:space="preserve">17.314733505249</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4304962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3643474578857</t>
+    <t xml:space="preserve">17.4304943084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3643455505371</t>
   </si>
   <si>
     <t xml:space="preserve">17.3808822631836</t>
@@ -2567,22 +2567,22 @@
     <t xml:space="preserve">16.8186092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9012966156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8516826629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7524604797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0170593261719</t>
+    <t xml:space="preserve">16.9012985229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8516845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.752462387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0170574188232</t>
   </si>
   <si>
     <t xml:space="preserve">17.4635715484619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5958709716797</t>
+    <t xml:space="preserve">17.5958728790283</t>
   </si>
   <si>
     <t xml:space="preserve">17.4801082611084</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">17.9266204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.992769241333</t>
+    <t xml:space="preserve">17.9927711486816</t>
   </si>
   <si>
     <t xml:space="preserve">18.0919933319092</t>
@@ -2603,22 +2603,22 @@
     <t xml:space="preserve">18.4227447509766</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4723567962646</t>
+    <t xml:space="preserve">18.472354888916</t>
   </si>
   <si>
     <t xml:space="preserve">18.1581439971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.025842666626</t>
+    <t xml:space="preserve">18.0258445739746</t>
   </si>
   <si>
     <t xml:space="preserve">18.0754566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5054321289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3896713256836</t>
+    <t xml:space="preserve">18.505428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.389669418335</t>
   </si>
   <si>
     <t xml:space="preserve">18.2739067077637</t>
@@ -2627,10 +2627,10 @@
     <t xml:space="preserve">18.3235187530518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3400573730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.191219329834</t>
+    <t xml:space="preserve">18.3400592803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1912212371826</t>
   </si>
   <si>
     <t xml:space="preserve">18.0589218139648</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">17.910083770752</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2408294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3069820404053</t>
+    <t xml:space="preserve">18.2408313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3069801330566</t>
   </si>
   <si>
     <t xml:space="preserve">17.6620216369629</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7943210601807</t>
+    <t xml:space="preserve">17.794319152832</t>
   </si>
   <si>
     <t xml:space="preserve">17.711633682251</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">17.5793323516846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.347806930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4966430664062</t>
+    <t xml:space="preserve">17.3478088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4966468811035</t>
   </si>
   <si>
     <t xml:space="preserve">17.3974208831787</t>
@@ -2669,16 +2669,16 @@
     <t xml:space="preserve">17.7447071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6046581268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7700309753418</t>
+    <t xml:space="preserve">18.6046562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7700328826904</t>
   </si>
   <si>
     <t xml:space="preserve">18.3731307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6542701721191</t>
+    <t xml:space="preserve">18.6542663574219</t>
   </si>
   <si>
     <t xml:space="preserve">18.7534942626953</t>
@@ -2687,31 +2687,31 @@
     <t xml:space="preserve">18.4062080383301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1416091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9431591033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1085338592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7281684875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.95969581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1989727020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6366958618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2894115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9503936767578</t>
+    <t xml:space="preserve">18.1416072845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9431571960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1085300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7281703948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9596939086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1989707946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.636697769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2894096374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9503908157349</t>
   </si>
   <si>
     <t xml:space="preserve">16.0413494110107</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">17.5627956390381</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0666694641113</t>
+    <t xml:space="preserve">17.06667137146</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155094146729</t>
@@ -2735,61 +2735,61 @@
     <t xml:space="preserve">17.1658973693848</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0005226135254</t>
+    <t xml:space="preserve">17.0005207061768</t>
   </si>
   <si>
     <t xml:space="preserve">16.9178333282471</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7028465270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8847579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7855319976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6201591491699</t>
+    <t xml:space="preserve">16.7028484344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8847599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7855358123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6201610565186</t>
   </si>
   <si>
     <t xml:space="preserve">16.4795913696289</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0335941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1328182220459</t>
+    <t xml:space="preserve">17.0335960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1328201293945</t>
   </si>
   <si>
     <t xml:space="preserve">17.1824340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.546257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1746826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8692569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1669292449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3488445281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0599536895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9607276916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5064659118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6883792877197</t>
+    <t xml:space="preserve">17.5462589263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1746807098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8692531585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1669311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3488426208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0599555969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.960729598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5064640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6883773803711</t>
   </si>
   <si>
     <t xml:space="preserve">20.7049160003662</t>
@@ -2804,10 +2804,10 @@
     <t xml:space="preserve">20.7545299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9364414215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7214546203613</t>
+    <t xml:space="preserve">20.9364376068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7214527130127</t>
   </si>
   <si>
     <t xml:space="preserve">21.0025901794434</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">22.1767501831055</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9948387145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5571136474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2175788879395</t>
+    <t xml:space="preserve">21.994836807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5571117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2175769805908</t>
   </si>
   <si>
     <t xml:space="preserve">20.9033660888672</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">21.5979385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4160270690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8956127166748</t>
+    <t xml:space="preserve">21.4160251617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8956146240234</t>
   </si>
   <si>
     <t xml:space="preserve">21.515251159668</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">21.8460006713867</t>
   </si>
   <si>
-    <t xml:space="preserve">22.160213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5317878723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3664150238037</t>
+    <t xml:space="preserve">22.1602115631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5317897796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3664131164551</t>
   </si>
   <si>
     <t xml:space="preserve">20.7379913330078</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">20.5726146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2506504058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7876033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2584037780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6134395599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1922550201416</t>
+    <t xml:space="preserve">21.2506523132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7876014709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2584056854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6134433746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.192253112793</t>
   </si>
   <si>
     <t xml:space="preserve">19.3323059082031</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">20.2749423980713</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2010383605957</t>
+    <t xml:space="preserve">21.2010402679443</t>
   </si>
   <si>
     <t xml:space="preserve">20.9860515594482</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">20.0103416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465167999268</t>
+    <t xml:space="preserve">19.6465148925781</t>
   </si>
   <si>
     <t xml:space="preserve">20.2253265380859</t>
@@ -2915,7 +2915,7 @@
     <t xml:space="preserve">20.3410911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5560760498047</t>
+    <t xml:space="preserve">20.5560779571533</t>
   </si>
   <si>
     <t xml:space="preserve">20.638765335083</t>
@@ -2924,43 +2924,43 @@
     <t xml:space="preserve">21.035665512085</t>
   </si>
   <si>
-    <t xml:space="preserve">21.34987449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.085277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0191268920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8702907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1018142700195</t>
+    <t xml:space="preserve">21.3498783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0852756500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0191287994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.870288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1018161773682</t>
   </si>
   <si>
     <t xml:space="preserve">20.8868274688721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5230045318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6056900024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0268802642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1095657348633</t>
+    <t xml:space="preserve">20.5230007171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.60569190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0268783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1095676422119</t>
   </si>
   <si>
     <t xml:space="preserve">21.1514282226562</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6222286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3080139160156</t>
+    <t xml:space="preserve">20.6222305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3080158233643</t>
   </si>
   <si>
     <t xml:space="preserve">20.4072399139404</t>
@@ -2981,34 +2981,34 @@
     <t xml:space="preserve">20.2914810180664</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2661552429199</t>
+    <t xml:space="preserve">19.2661533355713</t>
   </si>
   <si>
     <t xml:space="preserve">19.762279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8780422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3484592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3314075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0756340026855</t>
+    <t xml:space="preserve">19.878044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3484573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3314094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0756320953369</t>
   </si>
   <si>
     <t xml:space="preserve">21.2461490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.229097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1779460906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4337158203125</t>
+    <t xml:space="preserve">21.2290992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.177942276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4337139129639</t>
   </si>
   <si>
     <t xml:space="preserve">21.4848709106445</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">21.6042308807373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6212825775146</t>
+    <t xml:space="preserve">21.621280670166</t>
   </si>
   <si>
     <t xml:space="preserve">21.3143539428711</t>
@@ -3029,25 +3029,25 @@
     <t xml:space="preserve">22.388599395752</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9793643951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0646190643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.030517578125</t>
+    <t xml:space="preserve">21.979362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0646171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0305194854736</t>
   </si>
   <si>
     <t xml:space="preserve">21.7235908508301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6553840637207</t>
+    <t xml:space="preserve">21.6553859710693</t>
   </si>
   <si>
     <t xml:space="preserve">21.7406406402588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3655090332031</t>
+    <t xml:space="preserve">21.3655071258545</t>
   </si>
   <si>
     <t xml:space="preserve">21.4507675170898</t>
@@ -3065,16 +3065,16 @@
     <t xml:space="preserve">21.9964141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3825607299805</t>
+    <t xml:space="preserve">21.3825626373291</t>
   </si>
   <si>
     <t xml:space="preserve">20.8369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8710155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.888069152832</t>
+    <t xml:space="preserve">20.8710174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8880672454834</t>
   </si>
   <si>
     <t xml:space="preserve">21.7065391540527</t>
@@ -3086,55 +3086,55 @@
     <t xml:space="preserve">22.1328258514404</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2351341247559</t>
+    <t xml:space="preserve">22.2351360321045</t>
   </si>
   <si>
     <t xml:space="preserve">22.47385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2692375183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7346057891846</t>
+    <t xml:space="preserve">22.2692394256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7346038818359</t>
   </si>
   <si>
     <t xml:space="preserve">20.5470390319824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2632026672363</t>
+    <t xml:space="preserve">21.2632007598877</t>
   </si>
   <si>
     <t xml:space="preserve">21.1097373962402</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1608924865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5530776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7747459411621</t>
+    <t xml:space="preserve">21.1608905792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5530757904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7747478485107</t>
   </si>
   <si>
     <t xml:space="preserve">21.2973022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0926876068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8539619445801</t>
+    <t xml:space="preserve">21.0926856994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8539638519287</t>
   </si>
   <si>
     <t xml:space="preserve">21.0074291229248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2802505493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9282093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8600006103516</t>
+    <t xml:space="preserve">21.280252456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9282073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8600025177002</t>
   </si>
   <si>
     <t xml:space="preserve">21.8088474273682</t>
@@ -3146,13 +3146,13 @@
     <t xml:space="preserve">21.7576942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3996124267578</t>
+    <t xml:space="preserve">21.3996143341064</t>
   </si>
   <si>
     <t xml:space="preserve">21.9111576080322</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5079593658447</t>
+    <t xml:space="preserve">22.5079574584961</t>
   </si>
   <si>
     <t xml:space="preserve">22.1669292449951</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">22.0816707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0134658813477</t>
+    <t xml:space="preserve">22.013463973999</t>
   </si>
   <si>
     <t xml:space="preserve">22.4909076690674</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4227027893066</t>
+    <t xml:space="preserve">22.422700881958</t>
   </si>
   <si>
     <t xml:space="preserve">22.2521858215332</t>
@@ -3185,13 +3185,13 @@
     <t xml:space="preserve">23.172966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7697677612305</t>
+    <t xml:space="preserve">23.7697696685791</t>
   </si>
   <si>
     <t xml:space="preserve">23.4628429412842</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3775863647461</t>
+    <t xml:space="preserve">23.3775844573975</t>
   </si>
   <si>
     <t xml:space="preserve">23.9232330322266</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">25.4749164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8329982757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7818450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1740283966064</t>
+    <t xml:space="preserve">25.8329963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7818431854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1740303039551</t>
   </si>
   <si>
     <t xml:space="preserve">26.3274898529053</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">26.7708282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6855716705322</t>
+    <t xml:space="preserve">26.6855735778809</t>
   </si>
   <si>
     <t xml:space="preserve">25.969409942627</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">26.7196750640869</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3615951538086</t>
+    <t xml:space="preserve">26.3615970611572</t>
   </si>
   <si>
     <t xml:space="preserve">26.3104419708252</t>
@@ -3248,22 +3248,22 @@
     <t xml:space="preserve">25.5431232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0315799713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8269596099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0145263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1679916381836</t>
+    <t xml:space="preserve">25.0315780639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.826961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0145282745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.167989730835</t>
   </si>
   <si>
     <t xml:space="preserve">25.1168346405029</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8099098205566</t>
+    <t xml:space="preserve">24.8099117279053</t>
   </si>
   <si>
     <t xml:space="preserve">24.8440113067627</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">25.3896598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3836212158203</t>
+    <t xml:space="preserve">24.3836231231689</t>
   </si>
   <si>
     <t xml:space="preserve">24.1790046691895</t>
@@ -3296,16 +3296,16 @@
     <t xml:space="preserve">24.1960563659668</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3495178222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9402828216553</t>
+    <t xml:space="preserve">24.3495197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9402847290039</t>
   </si>
   <si>
     <t xml:space="preserve">24.1449012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1107978820801</t>
+    <t xml:space="preserve">24.1107997894287</t>
   </si>
   <si>
     <t xml:space="preserve">23.8038711547852</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">24.2813129425049</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0486297607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4347763061523</t>
+    <t xml:space="preserve">25.0486278533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.434778213501</t>
   </si>
   <si>
     <t xml:space="preserve">23.5481014251709</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">23.4969444274902</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9342460632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7978343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6443691253662</t>
+    <t xml:space="preserve">22.9342479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7978324890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6443710327148</t>
   </si>
   <si>
     <t xml:space="preserve">22.3033409118652</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">21.5189723968506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8429508209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1839790344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1949939727783</t>
+    <t xml:space="preserve">21.8429527282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1839809417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.194995880127</t>
   </si>
   <si>
     <t xml:space="preserve">21.6383323669434</t>
@@ -3380,16 +3380,16 @@
     <t xml:space="preserve">20.6663990020752</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4678173065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0244770050049</t>
+    <t xml:space="preserve">21.4678192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0244789123535</t>
   </si>
   <si>
     <t xml:space="preserve">20.5640907287598</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9221725463867</t>
+    <t xml:space="preserve">20.9221706390381</t>
   </si>
   <si>
     <t xml:space="preserve">20.5129356384277</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">24.0937480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6163063049316</t>
+    <t xml:space="preserve">23.616304397583</t>
   </si>
   <si>
     <t xml:space="preserve">22.7637329101562</t>
@@ -3416,67 +3416,67 @@
     <t xml:space="preserve">22.8148860931396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6102676391602</t>
+    <t xml:space="preserve">22.6102695465088</t>
   </si>
   <si>
     <t xml:space="preserve">24.1619529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">25.560173034668</t>
+    <t xml:space="preserve">25.5601749420166</t>
   </si>
   <si>
     <t xml:space="preserve">24.9292697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8951683044434</t>
+    <t xml:space="preserve">24.8951663970947</t>
   </si>
   <si>
     <t xml:space="preserve">24.3154163360596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2873497009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7136363983154</t>
+    <t xml:space="preserve">25.2873516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7136383056641</t>
   </si>
   <si>
     <t xml:space="preserve">24.6564464569092</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1850414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9804248809814</t>
+    <t xml:space="preserve">25.1850433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9804229736328</t>
   </si>
   <si>
     <t xml:space="preserve">25.662483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3786468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2933902740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8049335479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7537803649902</t>
+    <t xml:space="preserve">26.3786449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2933883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8049354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7537784576416</t>
   </si>
   <si>
     <t xml:space="preserve">26.9413452148438</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0436534881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0948085784912</t>
+    <t xml:space="preserve">27.0436515808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0948066711426</t>
   </si>
   <si>
     <t xml:space="preserve">26.8219833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9924983978271</t>
+    <t xml:space="preserve">26.9925003051758</t>
   </si>
   <si>
     <t xml:space="preserve">27.1459617614746</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">27.7086620330811</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5040435791016</t>
+    <t xml:space="preserve">27.5040416717529</t>
   </si>
   <si>
     <t xml:space="preserve">27.4699420928955</t>
@@ -3500,22 +3500,22 @@
     <t xml:space="preserve">27.8621253967285</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0496921539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5893001556396</t>
+    <t xml:space="preserve">28.0496940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5893020629883</t>
   </si>
   <si>
     <t xml:space="preserve">27.1800651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2823753356934</t>
+    <t xml:space="preserve">27.2823734283447</t>
   </si>
   <si>
     <t xml:space="preserve">26.856086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6514701843262</t>
+    <t xml:space="preserve">26.6514682769775</t>
   </si>
   <si>
     <t xml:space="preserve">25.3555564880371</t>
@@ -3524,19 +3524,19 @@
     <t xml:space="preserve">25.3214550018311</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9864597320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3385066986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8901901245117</t>
+    <t xml:space="preserve">25.9864616394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3385047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8901920318604</t>
   </si>
   <si>
     <t xml:space="preserve">27.7598152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4759788513184</t>
+    <t xml:space="preserve">28.475980758667</t>
   </si>
   <si>
     <t xml:space="preserve">28.5100803375244</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">29.4604301452637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4954605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.055944442749</t>
+    <t xml:space="preserve">29.4954624176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0559463500977</t>
   </si>
   <si>
     <t xml:space="preserve">29.5655193328857</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">28.3044338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9524936676025</t>
+    <t xml:space="preserve">28.9524955749512</t>
   </si>
   <si>
     <t xml:space="preserve">28.8824329376221</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">29.0575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1451568603516</t>
+    <t xml:space="preserve">29.1451587677002</t>
   </si>
   <si>
     <t xml:space="preserve">27.043342590332</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">25.9924392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.957405090332</t>
+    <t xml:space="preserve">25.9574069976807</t>
   </si>
   <si>
     <t xml:space="preserve">25.607105255127</t>
@@ -3617,13 +3617,13 @@
     <t xml:space="preserve">26.255163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6054649353027</t>
+    <t xml:space="preserve">26.6054668426514</t>
   </si>
   <si>
     <t xml:space="preserve">25.8873462677002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4653453826904</t>
+    <t xml:space="preserve">26.4653434753418</t>
   </si>
   <si>
     <t xml:space="preserve">26.3252239227295</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">26.9382553100586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9732837677002</t>
+    <t xml:space="preserve">26.9732856750488</t>
   </si>
   <si>
     <t xml:space="preserve">27.1309204101562</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">27.4286785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">27.341100692749</t>
+    <t xml:space="preserve">27.3411026000977</t>
   </si>
   <si>
     <t xml:space="preserve">26.7455902099609</t>
@@ -3671,22 +3671,22 @@
     <t xml:space="preserve">26.6930408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5879516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1834678649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.884069442749</t>
+    <t xml:space="preserve">26.5879535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1834659576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8840713500977</t>
   </si>
   <si>
     <t xml:space="preserve">28.1467971801758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4445552825928</t>
+    <t xml:space="preserve">28.4445533752441</t>
   </si>
   <si>
     <t xml:space="preserve">28.8999481201172</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">29.2327365875244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4062480926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1260070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3186702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8632755279541</t>
+    <t xml:space="preserve">30.40625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1260051727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3186721801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8632774353027</t>
   </si>
   <si>
     <t xml:space="preserve">29.950855255127</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">30.4412784576416</t>
   </si>
   <si>
-    <t xml:space="preserve">31.15940284729</t>
+    <t xml:space="preserve">31.1593990325928</t>
   </si>
   <si>
     <t xml:space="preserve">30.3361873626709</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">29.7406730651855</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7089195251465</t>
+    <t xml:space="preserve">27.7089214324951</t>
   </si>
   <si>
     <t xml:space="preserve">27.4987373352051</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">27.8490409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2694034576416</t>
+    <t xml:space="preserve">28.269401550293</t>
   </si>
   <si>
     <t xml:space="preserve">28.1643142700195</t>
@@ -3773,13 +3773,13 @@
     <t xml:space="preserve">29.0926151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7598285675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1801910400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8665542602539</t>
+    <t xml:space="preserve">28.7598266601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1801891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8665561676025</t>
   </si>
   <si>
     <t xml:space="preserve">25.169225692749</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">25.064136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5912284851074</t>
+    <t xml:space="preserve">24.5912303924561</t>
   </si>
   <si>
     <t xml:space="preserve">24.7488651275635</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">24.9415302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4335918426514</t>
+    <t xml:space="preserve">24.4335899353027</t>
   </si>
   <si>
     <t xml:space="preserve">24.1708660125732</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">24.9065017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5545616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7472267150879</t>
+    <t xml:space="preserve">25.5545597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7472248077393</t>
   </si>
   <si>
     <t xml:space="preserve">25.6946811676025</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">26.7806186676025</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6738910675049</t>
+    <t xml:space="preserve">27.6738891601562</t>
   </si>
   <si>
     <t xml:space="preserve">27.7964954376221</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">26.7631034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9032230377197</t>
+    <t xml:space="preserve">26.9032249450684</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274677276611</t>
@@ -3872,13 +3872,13 @@
     <t xml:space="preserve">26.3952865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8331642150879</t>
+    <t xml:space="preserve">26.8331623077393</t>
   </si>
   <si>
     <t xml:space="preserve">26.307710647583</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9223785400391</t>
+    <t xml:space="preserve">25.9223766326904</t>
   </si>
   <si>
     <t xml:space="preserve">26.3777713775635</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">26.5003757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1325569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0975284576416</t>
+    <t xml:space="preserve">26.1325588226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">26.5354061126709</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">26.2376499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7647399902344</t>
+    <t xml:space="preserve">25.764741897583</t>
   </si>
   <si>
     <t xml:space="preserve">25.8348026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2201347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4144382476807</t>
+    <t xml:space="preserve">26.2201366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4144401550293</t>
   </si>
   <si>
     <t xml:space="preserve">25.466983795166</t>
@@ -3923,10 +3923,10 @@
     <t xml:space="preserve">25.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5895881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8714694976807</t>
+    <t xml:space="preserve">25.5895900726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8714714050293</t>
   </si>
   <si>
     <t xml:space="preserve">24.4686241149902</t>
@@ -3935,52 +3935,52 @@
     <t xml:space="preserve">24.5737133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1183223724365</t>
+    <t xml:space="preserve">24.1183204650879</t>
   </si>
   <si>
     <t xml:space="preserve">24.2409267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3285007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7838935852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8539562225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3109874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.22340965271</t>
+    <t xml:space="preserve">24.3285026550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7838954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8539543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3109855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2234115600586</t>
   </si>
   <si>
     <t xml:space="preserve">24.3460159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4160766601562</t>
+    <t xml:space="preserve">24.4160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">24.3985633850098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6788024902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9590454101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0466194152832</t>
+    <t xml:space="preserve">24.678804397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9590473175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0466213226318</t>
   </si>
   <si>
     <t xml:space="preserve">24.7138328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5036506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6612892150879</t>
+    <t xml:space="preserve">24.5036525726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6612873077393</t>
   </si>
   <si>
     <t xml:space="preserve">24.2759552001953</t>
@@ -4007,10 +4007,10 @@
     <t xml:space="preserve">23.8731079101562</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3476543426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7154731750488</t>
+    <t xml:space="preserve">23.3476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7154712677002</t>
   </si>
   <si>
     <t xml:space="preserve">23.7680168151855</t>
@@ -4025,13 +4025,13 @@
     <t xml:space="preserve">23.049898147583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8747463226318</t>
+    <t xml:space="preserve">22.8747482299805</t>
   </si>
   <si>
     <t xml:space="preserve">23.1900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2425632476807</t>
+    <t xml:space="preserve">23.2425651550293</t>
   </si>
   <si>
     <t xml:space="preserve">23.6979560852051</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">23.9256534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7505035400391</t>
+    <t xml:space="preserve">23.7505016326904</t>
   </si>
   <si>
     <t xml:space="preserve">23.435230255127</t>
@@ -4058,10 +4058,10 @@
     <t xml:space="preserve">23.5228061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9606838226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4861373901367</t>
+    <t xml:space="preserve">23.9606857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4861354827881</t>
   </si>
   <si>
     <t xml:space="preserve">24.2584400177002</t>
@@ -4073,10 +4073,10 @@
     <t xml:space="preserve">25.2217712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2042598724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1341972351074</t>
+    <t xml:space="preserve">25.2042579650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1341991424561</t>
   </si>
   <si>
     <t xml:space="preserve">24.6262588500977</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">24.3635330200195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7855319976807</t>
+    <t xml:space="preserve">23.7855339050293</t>
   </si>
   <si>
     <t xml:space="preserve">23.2250499725342</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">23.2775955200195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.295108795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0657749176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.76637840271</t>
+    <t xml:space="preserve">23.2951107025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0657730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7663803100586</t>
   </si>
   <si>
     <t xml:space="preserve">24.7313499450684</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">23.6418628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4965953826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334342956543</t>
+    <t xml:space="preserve">23.4965972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334362030029</t>
   </si>
   <si>
     <t xml:space="preserve">23.5329132080078</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">24.2955551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5679264068604</t>
+    <t xml:space="preserve">24.5679244995117</t>
   </si>
   <si>
     <t xml:space="preserve">24.4771347045898</t>
@@ -4163,13 +4163,13 @@
     <t xml:space="preserve">24.5134525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3318710327148</t>
+    <t xml:space="preserve">24.3318691253662</t>
   </si>
   <si>
     <t xml:space="preserve">23.9868659973145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5510711669922</t>
+    <t xml:space="preserve">23.5510730743408</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058074951172</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">23.4602813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8234424591064</t>
+    <t xml:space="preserve">23.8234443664551</t>
   </si>
   <si>
     <t xml:space="preserve">23.6237049102783</t>
@@ -4196,13 +4196,13 @@
     <t xml:space="preserve">24.8221397399902</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0413398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3863468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1321296691895</t>
+    <t xml:space="preserve">24.0413417816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.386344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1321315765381</t>
   </si>
   <si>
     <t xml:space="preserve">24.4589786529541</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">24.6768760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6042442321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5497703552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7858238220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2397766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8039817810059</t>
+    <t xml:space="preserve">24.6042423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.549768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7858219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2397747039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8039798736572</t>
   </si>
   <si>
     <t xml:space="preserve">24.9674053192139</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">22.2618465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2981624603271</t>
+    <t xml:space="preserve">22.2981605529785</t>
   </si>
   <si>
     <t xml:space="preserve">22.388952255249</t>
@@ -4271,25 +4271,25 @@
     <t xml:space="preserve">22.2073707580566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0621070861816</t>
+    <t xml:space="preserve">22.062105178833</t>
   </si>
   <si>
     <t xml:space="preserve">21.6807861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6263122558594</t>
+    <t xml:space="preserve">21.6263103485107</t>
   </si>
   <si>
     <t xml:space="preserve">22.6431674957275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6794815063477</t>
+    <t xml:space="preserve">22.6794834136963</t>
   </si>
   <si>
     <t xml:space="preserve">22.5886917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1515922546387</t>
+    <t xml:space="preserve">23.1515941619873</t>
   </si>
   <si>
     <t xml:space="preserve">22.9700107574463</t>
@@ -4310,28 +4310,28 @@
     <t xml:space="preserve">23.024486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9155368804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.86106300354</t>
+    <t xml:space="preserve">22.9155387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8610649108887</t>
   </si>
   <si>
     <t xml:space="preserve">23.2060661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5342178344727</t>
+    <t xml:space="preserve">22.534215927124</t>
   </si>
   <si>
     <t xml:space="preserve">21.9349994659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8442096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2631511688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8999881744385</t>
+    <t xml:space="preserve">21.8442077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2631492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8999862670898</t>
   </si>
   <si>
     <t xml:space="preserve">20.482349395752</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">20.7365646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1010284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6833934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7378673553467</t>
+    <t xml:space="preserve">20.1010303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6833953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7378692626953</t>
   </si>
   <si>
     <t xml:space="preserve">20.0102405548096</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">19.9376068115234</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3915576934814</t>
+    <t xml:space="preserve">20.3915596008301</t>
   </si>
   <si>
     <t xml:space="preserve">20.6094589233398</t>
@@ -4373,19 +4373,19 @@
     <t xml:space="preserve">20.6820907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1542015075684</t>
+    <t xml:space="preserve">21.1541996002197</t>
   </si>
   <si>
     <t xml:space="preserve">21.0997276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1723594665527</t>
+    <t xml:space="preserve">21.1723575592041</t>
   </si>
   <si>
     <t xml:space="preserve">21.0634117126465</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8091983795166</t>
+    <t xml:space="preserve">20.809196472168</t>
   </si>
   <si>
     <t xml:space="preserve">21.0089359283447</t>
@@ -4397,16 +4397,16 @@
     <t xml:space="preserve">21.0270938873291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.608154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7715759277344</t>
+    <t xml:space="preserve">21.6081523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.771577835083</t>
   </si>
   <si>
     <t xml:space="preserve">21.4628887176514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9181480407715</t>
+    <t xml:space="preserve">20.9181461334229</t>
   </si>
   <si>
     <t xml:space="preserve">21.2449913024902</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">22.7884311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0971183776855</t>
+    <t xml:space="preserve">23.0971202850342</t>
   </si>
   <si>
     <t xml:space="preserve">23.2605419158936</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">23.1152763366699</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3694896697998</t>
+    <t xml:space="preserve">23.3694915771484</t>
   </si>
   <si>
     <t xml:space="preserve">23.8960742950439</t>
@@ -4445,13 +4445,13 @@
     <t xml:space="preserve">24.3681869506836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7689685821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4408206939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2216186523438</t>
+    <t xml:space="preserve">23.768970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4408187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2216205596924</t>
   </si>
   <si>
     <t xml:space="preserve">25.493989944458</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">25.966100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">25.984260559082</t>
+    <t xml:space="preserve">25.9842586517334</t>
   </si>
   <si>
     <t xml:space="preserve">26.0932083129883</t>
@@ -4478,31 +4478,31 @@
     <t xml:space="preserve">26.2021560668945</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4758319854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8947734832764</t>
+    <t xml:space="preserve">25.475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8947715759277</t>
   </si>
   <si>
     <t xml:space="preserve">25.0945110321045</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2942523956299</t>
+    <t xml:space="preserve">25.2942504882812</t>
   </si>
   <si>
     <t xml:space="preserve">24.9129314422607</t>
   </si>
   <si>
-    <t xml:space="preserve">24.713191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0763549804688</t>
+    <t xml:space="preserve">24.7131900787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0763530731201</t>
   </si>
   <si>
     <t xml:space="preserve">24.6405582427979</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6587181091309</t>
+    <t xml:space="preserve">24.6587162017822</t>
   </si>
   <si>
     <t xml:space="preserve">24.3137130737305</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">21.5718383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4447326660156</t>
+    <t xml:space="preserve">21.444730758667</t>
   </si>
   <si>
     <t xml:space="preserve">21.1905174255371</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">21.136043548584</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9363040924072</t>
+    <t xml:space="preserve">20.9363021850586</t>
   </si>
   <si>
     <t xml:space="preserve">21.3176250457764</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">22.6976413726807</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7871265411377</t>
+    <t xml:space="preserve">23.7871284484863</t>
   </si>
   <si>
     <t xml:space="preserve">24.0231819152832</t>
@@ -25921,7 +25921,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G773" t="s">
-        <v>430</v>
+        <v>565</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25973,7 +25973,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G775" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -26025,7 +26025,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G777" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -26051,7 +26051,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G778" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -26077,7 +26077,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G779" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -26103,7 +26103,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G780" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -26155,7 +26155,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G782" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -26181,7 +26181,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G783" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -26207,7 +26207,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G784" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -26285,7 +26285,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G787" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -26311,7 +26311,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G788" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -26337,7 +26337,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G789" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -26363,7 +26363,7 @@
         <v>17.5</v>
       </c>
       <c r="G790" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -26467,7 +26467,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G794" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -26493,7 +26493,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G795" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -26571,7 +26571,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G798" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -26623,7 +26623,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G800" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -26649,7 +26649,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G801" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -26675,7 +26675,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G802" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26727,7 +26727,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G804" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26753,7 +26753,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G805" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26779,7 +26779,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G806" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26805,7 +26805,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G807" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26831,7 +26831,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G808" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26857,7 +26857,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G809" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26883,7 +26883,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G810" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26909,7 +26909,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G811" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26935,7 +26935,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G812" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26961,7 +26961,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G813" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26987,7 +26987,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G814" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -27039,7 +27039,7 @@
         <v>16.75</v>
       </c>
       <c r="G816" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -27065,7 +27065,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G817" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -27117,7 +27117,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G819" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -27143,7 +27143,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G820" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -27195,7 +27195,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G822" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -27377,7 +27377,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G829" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -27429,7 +27429,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G831" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -27455,7 +27455,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G832" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -27585,7 +27585,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G837" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -27689,7 +27689,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G841" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27741,7 +27741,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G843" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27767,7 +27767,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G844" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27793,7 +27793,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G845" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27845,7 +27845,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G847" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27923,7 +27923,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G850" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27949,7 +27949,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G851" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -28001,7 +28001,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G853" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -28027,7 +28027,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G854" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -28053,7 +28053,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G855" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -28079,7 +28079,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G856" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -28105,7 +28105,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G857" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -28131,7 +28131,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G858" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -28157,7 +28157,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G859" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -28183,7 +28183,7 @@
         <v>17</v>
       </c>
       <c r="G860" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -28209,7 +28209,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G861" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -28235,7 +28235,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G862" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -28261,7 +28261,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G863" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -28287,7 +28287,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G864" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -28313,7 +28313,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G865" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -28339,7 +28339,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G866" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -28365,7 +28365,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G867" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -28391,7 +28391,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G868" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -28417,7 +28417,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G869" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -28443,7 +28443,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G870" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -28469,7 +28469,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G871" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28495,7 +28495,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G872" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -28521,7 +28521,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G873" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -28547,7 +28547,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G874" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -28573,7 +28573,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G875" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -28599,7 +28599,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G876" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -28625,7 +28625,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G877" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -28651,7 +28651,7 @@
         <v>18</v>
       </c>
       <c r="G878" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -28677,7 +28677,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G879" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -28703,7 +28703,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G880" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -28729,7 +28729,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G881" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -28755,7 +28755,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G882" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -28781,7 +28781,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G883" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -28807,7 +28807,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G884" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -28833,7 +28833,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G885" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -28859,7 +28859,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G886" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -28885,7 +28885,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G887" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -28911,7 +28911,7 @@
         <v>18</v>
       </c>
       <c r="G888" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -28937,7 +28937,7 @@
         <v>18</v>
       </c>
       <c r="G889" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -28963,7 +28963,7 @@
         <v>18.25</v>
       </c>
       <c r="G890" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -28989,7 +28989,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G891" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -29015,7 +29015,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G892" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -29041,7 +29041,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G893" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -29067,7 +29067,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G894" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29093,7 +29093,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G895" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29119,7 +29119,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G896" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29145,7 +29145,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G897" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29171,7 +29171,7 @@
         <v>18.8899993896484</v>
       </c>
       <c r="G898" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29197,7 +29197,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G899" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29223,7 +29223,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G900" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29249,7 +29249,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G901" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29275,7 +29275,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G902" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29301,7 +29301,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G903" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29327,7 +29327,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G904" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29353,7 +29353,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G905" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -29379,7 +29379,7 @@
         <v>18.0100002288818</v>
       </c>
       <c r="G906" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29405,7 +29405,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G907" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29431,7 +29431,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G908" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29457,7 +29457,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G909" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29483,7 +29483,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G910" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29509,7 +29509,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G911" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29535,7 +29535,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G912" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29561,7 +29561,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G913" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29587,7 +29587,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G914" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29613,7 +29613,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G915" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29639,7 +29639,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G916" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29665,7 +29665,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G917" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29691,7 +29691,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G918" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29717,7 +29717,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G919" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29743,7 +29743,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G920" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29769,7 +29769,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G921" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -29795,7 +29795,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G922" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -29821,7 +29821,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G923" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -29847,7 +29847,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G924" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -29873,7 +29873,7 @@
         <v>17.5</v>
       </c>
       <c r="G925" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -29899,7 +29899,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G926" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -29925,7 +29925,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G927" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -29951,7 +29951,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G928" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -29977,7 +29977,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G929" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30003,7 +30003,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G930" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30029,7 +30029,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G931" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30055,7 +30055,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G932" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30081,7 +30081,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G933" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30107,7 +30107,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G934" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30133,7 +30133,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G935" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30159,7 +30159,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G936" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30185,7 +30185,7 @@
         <v>18.25</v>
       </c>
       <c r="G937" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30211,7 +30211,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G938" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30237,7 +30237,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G939" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30263,7 +30263,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G940" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30289,7 +30289,7 @@
         <v>18</v>
       </c>
       <c r="G941" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30315,7 +30315,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G942" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30341,7 +30341,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G943" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30367,7 +30367,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G944" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30393,7 +30393,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G945" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30419,7 +30419,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G946" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30445,7 +30445,7 @@
         <v>18.75</v>
       </c>
       <c r="G947" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30471,7 +30471,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G948" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -30497,7 +30497,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G949" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -30523,7 +30523,7 @@
         <v>18.6299991607666</v>
       </c>
       <c r="G950" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30549,7 +30549,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G951" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30575,7 +30575,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G952" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -30601,7 +30601,7 @@
         <v>18.5</v>
       </c>
       <c r="G953" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30627,7 +30627,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G954" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30653,7 +30653,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G955" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -30679,7 +30679,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G956" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -30705,7 +30705,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G957" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30731,7 +30731,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G958" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30757,7 +30757,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G959" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -30783,7 +30783,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G960" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -30809,7 +30809,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G961" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -30835,7 +30835,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G962" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -30861,7 +30861,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G963" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -30887,7 +30887,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G964" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -30913,7 +30913,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G965" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -30939,7 +30939,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G966" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -30965,7 +30965,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G967" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -30991,7 +30991,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G968" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31017,7 +31017,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G969" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31043,7 +31043,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G970" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31069,7 +31069,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G971" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31095,7 +31095,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G972" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31121,7 +31121,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G973" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31147,7 +31147,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G974" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31173,7 +31173,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G975" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31199,7 +31199,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G976" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31225,7 +31225,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31251,7 +31251,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31277,7 +31277,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G979" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31303,7 +31303,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G980" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31329,7 +31329,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G981" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31355,7 +31355,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G982" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31381,7 +31381,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G983" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31407,7 +31407,7 @@
         <v>18.5200004577637</v>
       </c>
       <c r="G984" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31433,7 +31433,7 @@
         <v>18.75</v>
       </c>
       <c r="G985" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -31459,7 +31459,7 @@
         <v>19.0699996948242</v>
       </c>
       <c r="G986" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -31485,7 +31485,7 @@
         <v>18.9699993133545</v>
       </c>
       <c r="G987" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -31511,7 +31511,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G988" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31537,7 +31537,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G989" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -31563,7 +31563,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G990" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -31589,7 +31589,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G991" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -31615,7 +31615,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G992" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31641,7 +31641,7 @@
         <v>18.3500003814697</v>
       </c>
       <c r="G993" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -31667,7 +31667,7 @@
         <v>19.0300006866455</v>
       </c>
       <c r="G994" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31693,7 +31693,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G995" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -31719,7 +31719,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G996" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -31745,7 +31745,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G997" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -31771,7 +31771,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G998" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -31797,7 +31797,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G999" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -31823,7 +31823,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1000" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -31849,7 +31849,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1001" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -31875,7 +31875,7 @@
         <v>19.25</v>
       </c>
       <c r="G1002" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -31901,7 +31901,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1003" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -31927,7 +31927,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1004" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -31953,7 +31953,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1005" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31979,7 +31979,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1006" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -32005,7 +32005,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1007" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32031,7 +32031,7 @@
         <v>19.3500003814697</v>
       </c>
       <c r="G1008" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32057,7 +32057,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32083,7 +32083,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1010" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32109,7 +32109,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G1011" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32135,7 +32135,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1012" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32161,7 +32161,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1013" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32187,7 +32187,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1014" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32213,7 +32213,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1015" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32239,7 +32239,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1016" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32265,7 +32265,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1017" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -32291,7 +32291,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G1018" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32317,7 +32317,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1019" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32343,7 +32343,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G1020" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32369,7 +32369,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1021" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32395,7 +32395,7 @@
         <v>19.75</v>
       </c>
       <c r="G1022" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32421,7 +32421,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1023" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32447,7 +32447,7 @@
         <v>20.5</v>
       </c>
       <c r="G1024" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -32473,7 +32473,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1025" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -32499,7 +32499,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1026" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -32525,7 +32525,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1027" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -32551,7 +32551,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1028" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -32577,7 +32577,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1029" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -32603,7 +32603,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1030" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -32629,7 +32629,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1031" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32655,7 +32655,7 @@
         <v>21.4400005340576</v>
       </c>
       <c r="G1032" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -32681,7 +32681,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1033" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -32707,7 +32707,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1034" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -32733,7 +32733,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1035" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -32759,7 +32759,7 @@
         <v>21.7399997711182</v>
       </c>
       <c r="G1036" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -32785,7 +32785,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G1037" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -32811,7 +32811,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1038" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -32837,7 +32837,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1039" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -32863,7 +32863,7 @@
         <v>21.9400005340576</v>
       </c>
       <c r="G1040" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -32889,7 +32889,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1041" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -32915,7 +32915,7 @@
         <v>22.2600002288818</v>
       </c>
       <c r="G1042" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -32941,7 +32941,7 @@
         <v>22</v>
       </c>
       <c r="G1043" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -32967,7 +32967,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1044" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -32993,7 +32993,7 @@
         <v>22.1599998474121</v>
       </c>
       <c r="G1045" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -33019,7 +33019,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1046" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -33045,7 +33045,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1047" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -33071,7 +33071,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1048" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -33097,7 +33097,7 @@
         <v>23.0799999237061</v>
       </c>
       <c r="G1049" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -33123,7 +33123,7 @@
         <v>23.2199993133545</v>
       </c>
       <c r="G1050" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -33149,7 +33149,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G1051" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -33175,7 +33175,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1052" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -33201,7 +33201,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1053" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -33227,7 +33227,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1054" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -33253,7 +33253,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G1055" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -33279,7 +33279,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1056" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -33305,7 +33305,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1057" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -33331,7 +33331,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1058" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -33357,7 +33357,7 @@
         <v>21.5599994659424</v>
       </c>
       <c r="G1059" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -33383,7 +33383,7 @@
         <v>22.1200008392334</v>
       </c>
       <c r="G1060" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -33409,7 +33409,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1061" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -33435,7 +33435,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1062" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -33461,7 +33461,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1063" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33487,7 +33487,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1064" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -33513,7 +33513,7 @@
         <v>17.4699993133545</v>
       </c>
       <c r="G1065" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -33539,7 +33539,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1066" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -33565,7 +33565,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1067" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -33591,7 +33591,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1068" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -33617,7 +33617,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G1069" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -33643,7 +33643,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1070" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -33669,7 +33669,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1071" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -33695,7 +33695,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1072" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -33721,7 +33721,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1073" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -33747,7 +33747,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1074" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -33773,7 +33773,7 @@
         <v>15.25</v>
       </c>
       <c r="G1075" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -33799,7 +33799,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1076" t="s">
-        <v>778</v>
+        <v>606</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -34137,7 +34137,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1089" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -34267,7 +34267,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1094" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -34345,7 +34345,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1097" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -34449,7 +34449,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G1101" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34527,7 +34527,7 @@
         <v>17</v>
       </c>
       <c r="G1104" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -34631,7 +34631,7 @@
         <v>17.1900005340576</v>
       </c>
       <c r="G1108" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -71377,7 +71377,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6911805556</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>191963</v>
@@ -71398,6 +71398,32 @@
         <v>1823</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.6910648148</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>224949</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>21.8999996185303</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>21.6599998474121</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>21.7199993133545</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>21.7800006866455</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>1797</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ERG.MI.xlsx
+++ b/data/ERG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="1827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="1828">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,85 +38,85 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4875545501709</t>
+    <t xml:space="preserve">7.48755407333374</t>
   </si>
   <si>
     <t xml:space="preserve">ERG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43893384933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23837471008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04389333724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99527215957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06212472915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25053071975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22014284133911</t>
+    <t xml:space="preserve">7.43893337249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23837327957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04389238357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99527168273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06212520599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25053024291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22014141082764</t>
   </si>
   <si>
     <t xml:space="preserve">7.17152214050293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07428026199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84941101074219</t>
+    <t xml:space="preserve">7.07428169250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84941148757935</t>
   </si>
   <si>
     <t xml:space="preserve">7.01350450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75216960906982</t>
+    <t xml:space="preserve">6.75216913223267</t>
   </si>
   <si>
     <t xml:space="preserve">6.83725500106812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97096252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09251356124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00742673873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00134944915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98919486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92841911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86156558990479</t>
+    <t xml:space="preserve">6.9709620475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09251260757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00742626190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00134992599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98919439315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92841768264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86156511306763</t>
   </si>
   <si>
     <t xml:space="preserve">6.5333776473999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47867918014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61238574981689</t>
+    <t xml:space="preserve">6.47867965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61238527297974</t>
   </si>
   <si>
     <t xml:space="preserve">6.5516095161438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77647876739502</t>
+    <t xml:space="preserve">6.77647972106934</t>
   </si>
   <si>
     <t xml:space="preserve">6.94057369232178</t>
@@ -128,40 +128,40 @@
     <t xml:space="preserve">6.63061809539795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78863525390625</t>
+    <t xml:space="preserve">6.78863430023193</t>
   </si>
   <si>
     <t xml:space="preserve">6.58199834823608</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70354843139648</t>
+    <t xml:space="preserve">6.70354747772217</t>
   </si>
   <si>
     <t xml:space="preserve">6.71570491790771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80686712265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91626358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84333324432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83117723464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70962619781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74609279632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85548830032349</t>
+    <t xml:space="preserve">6.8068675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91626405715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84333229064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8311767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87979745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7096266746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74609184265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85548686981201</t>
   </si>
   <si>
     <t xml:space="preserve">6.8676438331604</t>
@@ -170,46 +170,46 @@
     <t xml:space="preserve">6.95272922515869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0499701499939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27484035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35992574691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34777069091797</t>
+    <t xml:space="preserve">7.04996967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27483987808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35992527008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34777116775513</t>
   </si>
   <si>
     <t xml:space="preserve">7.26876211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22621965408325</t>
+    <t xml:space="preserve">7.22622013092041</t>
   </si>
   <si>
     <t xml:space="preserve">7.11074590682983</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03173685073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08035755157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05604648590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18975448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23229598999023</t>
+    <t xml:space="preserve">7.03173637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08035707473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05604696273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18975400924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23229742050171</t>
   </si>
   <si>
     <t xml:space="preserve">7.1532883644104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11682367324829</t>
+    <t xml:space="preserve">7.11682224273682</t>
   </si>
   <si>
     <t xml:space="preserve">7.16544389724731</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">6.89803123474121</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90410900115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96488428115845</t>
+    <t xml:space="preserve">6.90410757064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96488285064697</t>
   </si>
   <si>
     <t xml:space="preserve">6.79471254348755</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76432371139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14113283157349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02566051483154</t>
+    <t xml:space="preserve">6.76432514190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14113330841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02566003799438</t>
   </si>
   <si>
     <t xml:space="preserve">7.15738725662231</t>
@@ -248,52 +248,52 @@
     <t xml:space="preserve">7.13741207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31052160263062</t>
+    <t xml:space="preserve">7.31051969528198</t>
   </si>
   <si>
     <t xml:space="preserve">7.25725698471069</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34381151199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38375854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29720544815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2505989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21730947494507</t>
+    <t xml:space="preserve">7.34381103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38376045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29720640182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25059986114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21730804443359</t>
   </si>
   <si>
     <t xml:space="preserve">7.23062562942505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23728275299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27723169326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22396802902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10412311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85777425765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.658034324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60476970672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47493839263916</t>
+    <t xml:space="preserve">7.23728370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27723121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22396755218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10412263870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85777473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65803337097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60477113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47493886947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.50822877883911</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">6.93767166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82448625564575</t>
+    <t xml:space="preserve">6.82448434829712</t>
   </si>
   <si>
     <t xml:space="preserve">6.88440799713135</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">6.47826671600342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3218035697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56149244308472</t>
+    <t xml:space="preserve">6.32180309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5614914894104</t>
   </si>
   <si>
     <t xml:space="preserve">6.69132423400879</t>
@@ -326,91 +326,91 @@
     <t xml:space="preserve">6.81782722473145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9176983833313</t>
+    <t xml:space="preserve">6.91769647598267</t>
   </si>
   <si>
     <t xml:space="preserve">7.03754234313965</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78453636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50490045547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6180853843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71795654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68466711044312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73793172836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87774896621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.81116819381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75124597549438</t>
+    <t xml:space="preserve">6.78453731536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5048999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61808586120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71795606613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68466663360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73793125152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8777494430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8111686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7512469291687</t>
   </si>
   <si>
     <t xml:space="preserve">6.79119396209717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76456260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86443376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77122020721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89106512069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73127222061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64471769332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63806056976318</t>
+    <t xml:space="preserve">6.76456212997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86443424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77122163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89106559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73127174377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64471864700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63806009292603</t>
   </si>
   <si>
     <t xml:space="preserve">6.75790452957153</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83114337921143</t>
+    <t xml:space="preserve">6.83114290237427</t>
   </si>
   <si>
     <t xml:space="preserve">6.80451059341431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101406097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96430397033691</t>
+    <t xml:space="preserve">6.9310131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96430349349976</t>
   </si>
   <si>
     <t xml:space="preserve">6.74458885192871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7112979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65137577056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62807321548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64138889312744</t>
+    <t xml:space="preserve">6.71129941940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65137624740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62807369232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64139032363892</t>
   </si>
   <si>
     <t xml:space="preserve">6.62141418457031</t>
@@ -419,232 +419,232 @@
     <t xml:space="preserve">7.01756811141968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98427820205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.010910987854</t>
+    <t xml:space="preserve">6.98427724838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01091051101685</t>
   </si>
   <si>
     <t xml:space="preserve">7.04419994354248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17070341110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87109041213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92435598373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83780193328857</t>
+    <t xml:space="preserve">7.17070150375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87108945846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92435646057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97761869430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83780097961426</t>
   </si>
   <si>
     <t xml:space="preserve">6.84445953369141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79785251617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7778787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59811162948608</t>
+    <t xml:space="preserve">6.79785203933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77787923812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59811210632324</t>
   </si>
   <si>
     <t xml:space="preserve">6.55150556564331</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72461462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67135143280029</t>
+    <t xml:space="preserve">6.7246150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67135000228882</t>
   </si>
   <si>
     <t xml:space="preserve">6.66469287872314</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60809993743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54484748840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45829296112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65470457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67800855636597</t>
+    <t xml:space="preserve">6.60809898376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54484796524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45829391479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65470409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67800807952881</t>
   </si>
   <si>
     <t xml:space="preserve">6.46495151519775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13870763778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22859144210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19197177886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17865610122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24856519699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13537883758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06546878814697</t>
+    <t xml:space="preserve">6.13870716094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.228590965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19197225570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17865562438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24856472015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13537836074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06546974182129</t>
   </si>
   <si>
     <t xml:space="preserve">6.16866874694824</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15868186950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14203691482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06214046478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03883695602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10874700546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05881118774414</t>
+    <t xml:space="preserve">6.15868139266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1420373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06213998794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03883647918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10874605178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0588116645813</t>
   </si>
   <si>
     <t xml:space="preserve">6.02219200134277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0188627243042</t>
+    <t xml:space="preserve">6.01886320114136</t>
   </si>
   <si>
     <t xml:space="preserve">6.11873340606689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23191928863525</t>
+    <t xml:space="preserve">6.23191976547241</t>
   </si>
   <si>
     <t xml:space="preserve">6.12206220626831</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22193336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21860313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35842275619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37839651107788</t>
+    <t xml:space="preserve">6.22193288803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21860456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35842323303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37839603424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62474346160889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70463991165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85111713409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69798278808594</t>
+    <t xml:space="preserve">6.70463943481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8511176109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69798231124878</t>
   </si>
   <si>
     <t xml:space="preserve">6.90438175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89772272109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99093532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07749128341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91103982925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07083225250244</t>
+    <t xml:space="preserve">6.89772319793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99093627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07749080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91104078292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07083177566528</t>
   </si>
   <si>
     <t xml:space="preserve">7.13075494766235</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15072822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18401908874512</t>
+    <t xml:space="preserve">7.15072774887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1840181350708</t>
   </si>
   <si>
     <t xml:space="preserve">7.0974645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05085849761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35046863555908</t>
+    <t xml:space="preserve">7.05085897445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35047006607056</t>
   </si>
   <si>
     <t xml:space="preserve">7.27057409286499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28388929367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30386304855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53023672103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32383823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31718015670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36378574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51692056655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59015893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60347557067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71000289916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76992607116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77658367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73663520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78989934921265</t>
+    <t xml:space="preserve">7.2838888168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30386400222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53023719787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32383632659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31717967987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3637866973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51691961288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59015846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60347414016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71000242233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76992654800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77658414840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73663568496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78990030288696</t>
   </si>
   <si>
     <t xml:space="preserve">7.75660943984985</t>
@@ -653,82 +653,82 @@
     <t xml:space="preserve">7.82319021224976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85648107528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86979675292969</t>
+    <t xml:space="preserve">7.85648250579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86979579925537</t>
   </si>
   <si>
     <t xml:space="preserve">7.87645435333252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90308570861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96966648101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9496922492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92305898666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96300983428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88311243057251</t>
+    <t xml:space="preserve">7.9030876159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96966695785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94969272613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92306041717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96300888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88311195373535</t>
   </si>
   <si>
     <t xml:space="preserve">7.72331953048706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62344980239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54355192184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47031497955322</t>
+    <t xml:space="preserve">7.62344932556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54355335235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47031545639038</t>
   </si>
   <si>
     <t xml:space="preserve">7.63676595687866</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56352663040161</t>
+    <t xml:space="preserve">7.56352519989014</t>
   </si>
   <si>
     <t xml:space="preserve">7.5701847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74329280853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8032169342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89642810821533</t>
+    <t xml:space="preserve">7.74329423904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80321550369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89642715454102</t>
   </si>
   <si>
     <t xml:space="preserve">7.94303417205811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84982347488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06953716278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20842838287354</t>
+    <t xml:space="preserve">7.84982204437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06953620910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20842742919922</t>
   </si>
   <si>
     <t xml:space="preserve">8.25009441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22926139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31954097747803</t>
+    <t xml:space="preserve">8.22926235198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31954002380371</t>
   </si>
   <si>
     <t xml:space="preserve">8.35426235198975</t>
@@ -737,64 +737,64 @@
     <t xml:space="preserve">8.28481674194336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29870700836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37509632110596</t>
+    <t xml:space="preserve">8.29870510101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37509822845459</t>
   </si>
   <si>
     <t xml:space="preserve">8.34731769561768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38898372650146</t>
+    <t xml:space="preserve">8.3889856338501</t>
   </si>
   <si>
     <t xml:space="preserve">8.43759727478027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45148658752441</t>
+    <t xml:space="preserve">8.45148468017578</t>
   </si>
   <si>
     <t xml:space="preserve">8.68760108947754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73621082305908</t>
+    <t xml:space="preserve">8.73621273040771</t>
   </si>
   <si>
     <t xml:space="preserve">8.62509918212891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63898754119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6667652130127</t>
+    <t xml:space="preserve">8.63898849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66676712036133</t>
   </si>
   <si>
     <t xml:space="preserve">8.68065547943115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59732151031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72926712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69454479217529</t>
+    <t xml:space="preserve">8.59732055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72926807403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69454288482666</t>
   </si>
   <si>
     <t xml:space="preserve">8.61120891571045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50704193115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59037780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52787590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54870891571045</t>
+    <t xml:space="preserve">8.50704288482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59037685394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52787494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54870986938477</t>
   </si>
   <si>
     <t xml:space="preserve">8.4931526184082</t>
@@ -809,40 +809,40 @@
     <t xml:space="preserve">8.47231960296631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61815357208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65982055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64593315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40981769561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4306526184082</t>
+    <t xml:space="preserve">8.61815452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65982151031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6459321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40981864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43065357208252</t>
   </si>
   <si>
     <t xml:space="preserve">8.42370796203613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30565071105957</t>
+    <t xml:space="preserve">8.30565166473389</t>
   </si>
   <si>
     <t xml:space="preserve">8.5417652130127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57648849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60426712036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71537780761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88204669952393</t>
+    <t xml:space="preserve">8.57648754119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60426616668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71537971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88204765319824</t>
   </si>
   <si>
     <t xml:space="preserve">9.00010395050049</t>
@@ -857,13 +857,13 @@
     <t xml:space="preserve">9.06954956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09038352966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00704765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95843696594238</t>
+    <t xml:space="preserve">9.09038257598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00704860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95843601226807</t>
   </si>
   <si>
     <t xml:space="preserve">9.06260395050049</t>
@@ -872,16 +872,16 @@
     <t xml:space="preserve">9.12510585784912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20843982696533</t>
+    <t xml:space="preserve">9.20843887329102</t>
   </si>
   <si>
     <t xml:space="preserve">9.24316215515137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2987174987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3681640625</t>
+    <t xml:space="preserve">9.29871940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36816310882568</t>
   </si>
   <si>
     <t xml:space="preserve">9.40983104705811</t>
@@ -890,16 +890,16 @@
     <t xml:space="preserve">9.41677474975586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32649517059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29177284240723</t>
+    <t xml:space="preserve">9.32649612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29177379608154</t>
   </si>
   <si>
     <t xml:space="preserve">9.31260776519775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45149803161621</t>
+    <t xml:space="preserve">9.45149707794189</t>
   </si>
   <si>
     <t xml:space="preserve">9.47233200073242</t>
@@ -908,49 +908,49 @@
     <t xml:space="preserve">9.43760871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44455242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4028844833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38899707794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38205146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3403844833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34732913970947</t>
+    <t xml:space="preserve">9.44455337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40288639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38899612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38205242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34038543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34733009338379</t>
   </si>
   <si>
     <t xml:space="preserve">9.31955146789551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48622131347656</t>
+    <t xml:space="preserve">9.48622035980225</t>
   </si>
   <si>
     <t xml:space="preserve">9.75011253356934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79177951812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7778902053833</t>
+    <t xml:space="preserve">9.79177856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77788925170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.80566883087158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72927856445312</t>
+    <t xml:space="preserve">9.72927761077881</t>
   </si>
   <si>
     <t xml:space="preserve">9.77094554901123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76400184631348</t>
+    <t xml:space="preserve">9.76400089263916</t>
   </si>
   <si>
     <t xml:space="preserve">9.74316787719727</t>
@@ -962,28 +962,28 @@
     <t xml:space="preserve">10.0278930664062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93761444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0834512710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1181726455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1876173019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4445638656616</t>
+    <t xml:space="preserve">9.93761348724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0834493637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1181716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1876163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4445648193359</t>
   </si>
   <si>
     <t xml:space="preserve">10.5001211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5695657730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2292852401733</t>
+    <t xml:space="preserve">10.5695667266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2292833328247</t>
   </si>
   <si>
     <t xml:space="preserve">10.3959522247314</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">10.423731803894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5903997421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4931764602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5626201629639</t>
+    <t xml:space="preserve">10.5903987884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4931755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5626220703125</t>
   </si>
   <si>
     <t xml:space="preserve">10.6251220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6042881011963</t>
+    <t xml:space="preserve">10.6042890548706</t>
   </si>
   <si>
     <t xml:space="preserve">10.7015113830566</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">10.8542919158936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.833456993103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9029035568237</t>
+    <t xml:space="preserve">10.8334579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9029026031494</t>
   </si>
   <si>
     <t xml:space="preserve">11.0904054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1042938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1112394332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667881011963</t>
+    <t xml:space="preserve">11.1042928695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1112384796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667900085449</t>
   </si>
   <si>
     <t xml:space="preserve">10.9723491668701</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">10.9445695877075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0765161514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3473529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3959636688232</t>
+    <t xml:space="preserve">11.0765171051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3473520278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3959627151489</t>
   </si>
   <si>
     <t xml:space="preserve">11.1529054641724</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0626268386841</t>
+    <t xml:space="preserve">11.0626277923584</t>
   </si>
   <si>
     <t xml:space="preserve">11.2154064178467</t>
@@ -1064,16 +1064,16 @@
     <t xml:space="preserve">11.2362403869629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2084608078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9098491668701</t>
+    <t xml:space="preserve">11.2084627151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9098472595215</t>
   </si>
   <si>
     <t xml:space="preserve">10.736234664917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8751239776611</t>
+    <t xml:space="preserve">10.8751249313354</t>
   </si>
   <si>
     <t xml:space="preserve">10.6945667266846</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">10.8612365722656</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0695705413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1876287460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9306802749634</t>
+    <t xml:space="preserve">11.0695714950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.187629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9306812286377</t>
   </si>
   <si>
     <t xml:space="preserve">11.1598510742188</t>
@@ -1106,16 +1106,16 @@
     <t xml:space="preserve">11.5001316070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4931879043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6251344680786</t>
+    <t xml:space="preserve">11.4931869506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6251335144043</t>
   </si>
   <si>
     <t xml:space="preserve">11.7223558425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7709703445435</t>
+    <t xml:space="preserve">11.7709693908691</t>
   </si>
   <si>
     <t xml:space="preserve">11.7015237808228</t>
@@ -1124,16 +1124,16 @@
     <t xml:space="preserve">11.729302406311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7154121398926</t>
+    <t xml:space="preserve">11.7154130935669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6112442016602</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4862442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5765218734741</t>
+    <t xml:space="preserve">11.4862451553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5765209197998</t>
   </si>
   <si>
     <t xml:space="preserve">11.6806888580322</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">10.8959589004517</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9862365722656</t>
+    <t xml:space="preserve">10.9862375259399</t>
   </si>
   <si>
     <t xml:space="preserve">11.0834608078003</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2292966842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2848529815674</t>
+    <t xml:space="preserve">11.2292947769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2848520278931</t>
   </si>
   <si>
     <t xml:space="preserve">11.3265190124512</t>
@@ -1169,79 +1169,79 @@
     <t xml:space="preserve">11.5973558425903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7501363754272</t>
+    <t xml:space="preserve">11.7501354217529</t>
   </si>
   <si>
     <t xml:space="preserve">11.6181888580322</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7987461090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6320772171021</t>
+    <t xml:space="preserve">11.7987470626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6320781707764</t>
   </si>
   <si>
     <t xml:space="preserve">11.8334703445435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1251392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9168043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6668109893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1529293060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3820991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3195962905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3682098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5765447616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5209884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2362632751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1668167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0487623214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4237632751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0070953369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.354320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4584875106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7154359817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7918243408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6807117462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9168272018433</t>
+    <t xml:space="preserve">12.1251382827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.916802406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6668119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1529302597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.382098197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3195972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3682079315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.576545715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5209875106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2362613677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1668157577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0487613677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4237661361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0070924758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3543214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4584865570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7154369354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7918252944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6807146072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9168262481689</t>
   </si>
   <si>
     <t xml:space="preserve">13.9307155609131</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">13.2987623214722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3751544952393</t>
+    <t xml:space="preserve">13.3751554489136</t>
   </si>
   <si>
     <t xml:space="preserve">13.416820526123</t>
@@ -1262,505 +1262,505 @@
     <t xml:space="preserve">13.4723777770996</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4862661361694</t>
+    <t xml:space="preserve">13.4862670898438</t>
   </si>
   <si>
     <t xml:space="preserve">13.6112680435181</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7362718582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7223806381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8196048736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.889048576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8543272018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9029378890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0834970474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7987699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0279378890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057203292847</t>
+    <t xml:space="preserve">13.7362689971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7223796844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8196020126343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8890466690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8543281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9029397964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0834951400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.798770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0279397964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057193756104</t>
   </si>
   <si>
     <t xml:space="preserve">13.1945962905884</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1112623214722</t>
+    <t xml:space="preserve">13.1112613677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1807060241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0200977325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1486539840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8083591461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6571178436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5361261367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2563285827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1277742385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3092622756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4605045318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4983148574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4680662155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.573935508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7327404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7478628158569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4075698852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4889459609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4738235473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6704387664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3755159378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6175031661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.723370552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9351110458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7460584640503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8292417526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2167129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2998962402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2091512680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0654716491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1637763977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0427846908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1713390350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2847709655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6250638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7536211013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6779985427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.791431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8443660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8746128082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8368034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7611827850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.655312538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5494441986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6099405288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6401882171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5721302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5191965103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2393989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.004976272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9217901229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9142293930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2696475982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3982048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9898490905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.664680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6722440719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5814962387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705488204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6268701553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5210008621216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6495552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.551248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4907531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4756269454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5058765411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3470735549927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3924436569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4831895828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8310480117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6344308853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5663738250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5436859130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3773212432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1958322525024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2714519500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3395118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3546342849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2638902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4529438018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3319473266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9311580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0219020843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8101654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5530548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7421064376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6513614654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3848838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1202116012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9614057540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5681791305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.439624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6211137771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4018135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4925584793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4698715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1371393203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2883825302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1522645950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6286754608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.643798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.825288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7723560333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.847975730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.757230758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8177280426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7799167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4471845626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4244995117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2581329345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1673889160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4169368743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1447019577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.031270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2505722045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1068916320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2278852462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0463953018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.099328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7968454360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8800287246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5379295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2656946182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7950410842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2941398620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1126480102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9538450241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5833015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4774341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5757398605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8555383682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0143404006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8328523635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9084720611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">13.1807069778442</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0200996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1486549377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8083600997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6571178436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5361242294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2563276290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1277713775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3092622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4605045318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4983148574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4680671691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5739364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.732738494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7478637695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4075689315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4889459609985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4738235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6704368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158098220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3755178451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6175012588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7233715057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9351091384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.746057510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8292417526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2167110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2998933792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2091503143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0654706954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1637763977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0427846908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1713399887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2847709655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6250629425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7536201477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6779985427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7914304733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8443651199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8746128082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8368034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7611827850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6553134918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5494432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6099405288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.640191078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5721302032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5191955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2393999099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0049743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9217910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9142293930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2696475982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3982028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9898471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6646795272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6722421646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5814981460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7705497741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6268701553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5210008621216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6495580673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5512495040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4907512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4756298065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.505877494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3470726013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3924436569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4831895828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8310480117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6344327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5663738250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5436868667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3773231506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1958322525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2714519500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3395109176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3546342849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2638912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4529428482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3319492340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9311599731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0219030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8101654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5530548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7421073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6513614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3848848342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.120210647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9614067077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5681800842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4396228790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6211137771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4018125534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4925584793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4698724746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1371393203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2883815765381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1522645950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6286754608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.643798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.825288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7723550796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8479747772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.757230758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8177270889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7799158096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4471855163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4245004653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2581329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1673879623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.416937828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1447010040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0312700271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2505712509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1068935394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2278852462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0463943481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0993299484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7968463897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.880030632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5379295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2656955718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7950420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2941389083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1126489639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9538440704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5833024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4774332046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5757398605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8555364608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0143423080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8328514099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9084720611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.052152633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1807088851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9160356521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0975227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0067796707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2260789871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2185163497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9009094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0370264053345</t>
+    <t xml:space="preserve">12.9160346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0975246429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0067806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2260808944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2185173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9009113311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0370292663574</t>
   </si>
   <si>
     <t xml:space="preserve">12.7647924423218</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0294647216797</t>
+    <t xml:space="preserve">13.029465675354</t>
   </si>
   <si>
     <t xml:space="preserve">13.2109546661377</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2336416244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9235963821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.870662689209</t>
+    <t xml:space="preserve">13.233642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9235973358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8706617355347</t>
   </si>
   <si>
     <t xml:space="preserve">12.893346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1882705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1353349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9689693450928</t>
+    <t xml:space="preserve">13.1882696151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1353340148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9689683914185</t>
   </si>
   <si>
     <t xml:space="preserve">13.1050863265991</t>
@@ -1769,46 +1769,46 @@
     <t xml:space="preserve">13.3016996383667</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8857879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6891717910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6967363357544</t>
+    <t xml:space="preserve">12.8857870101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.689172744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6967334747314</t>
   </si>
   <si>
     <t xml:space="preserve">12.6362371444702</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6664848327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5152444839478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3110685348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2430105209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0388336181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6589250564575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7269821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7496700286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3186321258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1900758743286</t>
+    <t xml:space="preserve">12.666485786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5152435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3110666275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2430095672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0388317108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6589241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7269830703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7496690750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3186311721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.19007396698</t>
   </si>
   <si>
     <t xml:space="preserve">12.1976366043091</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">12.1749515533447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2732572555542</t>
+    <t xml:space="preserve">12.2732563018799</t>
   </si>
   <si>
     <t xml:space="preserve">12.1598262786865</t>
@@ -1826,40 +1826,40 @@
     <t xml:space="preserve">12.2203226089478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2808198928833</t>
+    <t xml:space="preserve">12.280818939209</t>
   </si>
   <si>
     <t xml:space="preserve">12.303505897522</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8631010055542</t>
+    <t xml:space="preserve">12.8631000518799</t>
   </si>
   <si>
     <t xml:space="preserve">13.2902870178223</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4485063552856</t>
+    <t xml:space="preserve">13.4485054016113</t>
   </si>
   <si>
     <t xml:space="preserve">13.5988121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6146335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9548034667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.978533744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8598709106445</t>
+    <t xml:space="preserve">13.6146326065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9548025131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9785356521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8598728179932</t>
   </si>
   <si>
     <t xml:space="preserve">13.7491188049316</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7332992553711</t>
+    <t xml:space="preserve">13.7332983016968</t>
   </si>
   <si>
     <t xml:space="preserve">13.7728519439697</t>
@@ -1868,46 +1868,46 @@
     <t xml:space="preserve">13.8124046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7174758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6383657455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6620988845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5750799179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1446647644043</t>
+    <t xml:space="preserve">13.717474937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6383676528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6620998382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5750780105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1446628570557</t>
   </si>
   <si>
     <t xml:space="preserve">14.2395944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">14.508563041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.469012260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5955829620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7221574783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6746940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1763048171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1604833602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.081374168396</t>
+    <t xml:space="preserve">14.5085639953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4690113067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7221584320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6746892929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.176305770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1604862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0813760757446</t>
   </si>
   <si>
     <t xml:space="preserve">14.0339097976685</t>
@@ -1916,55 +1916,55 @@
     <t xml:space="preserve">14.4373655319214</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6984233856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6114053726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4136323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6272277832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1097898483276</t>
+    <t xml:space="preserve">14.6984252929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6114044189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4136333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6272268295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1097917556763</t>
   </si>
   <si>
     <t xml:space="preserve">15.0939693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9911289215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9436635971069</t>
+    <t xml:space="preserve">14.9911279678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9436626434326</t>
   </si>
   <si>
     <t xml:space="preserve">14.9120187759399</t>
   </si>
   <si>
-    <t xml:space="preserve">14.872462272644</t>
+    <t xml:space="preserve">14.872465133667</t>
   </si>
   <si>
     <t xml:space="preserve">14.8645544052124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6430492401123</t>
+    <t xml:space="preserve">14.6430501937866</t>
   </si>
   <si>
     <t xml:space="preserve">14.2870588302612</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3266143798828</t>
+    <t xml:space="preserve">14.3266134262085</t>
   </si>
   <si>
     <t xml:space="preserve">14.2158603668213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2475051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0259981155396</t>
+    <t xml:space="preserve">14.247504234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0260000228882</t>
   </si>
   <si>
     <t xml:space="preserve">14.0576438903809</t>
@@ -1973,28 +1973,28 @@
     <t xml:space="preserve">13.6067237854004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8677835464478</t>
+    <t xml:space="preserve">13.8677825927734</t>
   </si>
   <si>
     <t xml:space="preserve">14.2000398635864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2949695587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2079496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6304550170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5671691894531</t>
+    <t xml:space="preserve">14.2949705123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2079486846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6304559707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5671682357788</t>
   </si>
   <si>
     <t xml:space="preserve">13.6700096130371</t>
   </si>
   <si>
-    <t xml:space="preserve">13.519702911377</t>
+    <t xml:space="preserve">13.5197038650513</t>
   </si>
   <si>
     <t xml:space="preserve">13.3693962097168</t>
@@ -2003,64 +2003,64 @@
     <t xml:space="preserve">13.8203163146973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9073371887207</t>
+    <t xml:space="preserve">13.907338142395</t>
   </si>
   <si>
     <t xml:space="preserve">13.8440504074097</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5592575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7886743545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7965860366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1209316253662</t>
+    <t xml:space="preserve">13.5592565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7886734008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7965841293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1209306716919</t>
   </si>
   <si>
     <t xml:space="preserve">13.9310693740845</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0892858505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3028812408447</t>
+    <t xml:space="preserve">14.0892868041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.302882194519</t>
   </si>
   <si>
     <t xml:space="preserve">14.4848318099976</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6588726043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2633275985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2316827774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1130208969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5876731872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9753046035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8566417694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9990396499634</t>
+    <t xml:space="preserve">14.6588706970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2633247375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2316846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1130199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5876722335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.975305557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8566427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9990367889404</t>
   </si>
   <si>
     <t xml:space="preserve">14.8329105377197</t>
   </si>
   <si>
-    <t xml:space="preserve">14.745888710022</t>
+    <t xml:space="preserve">14.7458877563477</t>
   </si>
   <si>
     <t xml:space="preserve">15.0227708816528</t>
@@ -2069,19 +2069,19 @@
     <t xml:space="preserve">14.7379779815674</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7854461669922</t>
+    <t xml:space="preserve">14.7854452133179</t>
   </si>
   <si>
     <t xml:space="preserve">14.6905145645142</t>
   </si>
   <si>
-    <t xml:space="preserve">14.635139465332</t>
+    <t xml:space="preserve">14.6351375579834</t>
   </si>
   <si>
     <t xml:space="preserve">14.5402069091797</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1525745391846</t>
+    <t xml:space="preserve">14.1525726318359</t>
   </si>
   <si>
     <t xml:space="preserve">14.5164747238159</t>
@@ -2093,133 +2093,133 @@
     <t xml:space="preserve">14.1921291351318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0971984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2712392807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.279149055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.405722618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3899021148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3424339294434</t>
+    <t xml:space="preserve">14.0971965789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2712373733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2791471481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4057216644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3899011611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3424348831177</t>
   </si>
   <si>
     <t xml:space="preserve">14.3582563400269</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4610986709595</t>
+    <t xml:space="preserve">14.4610996246338</t>
   </si>
   <si>
     <t xml:space="preserve">15.0069494247437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9515743255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5322971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3345241546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.374080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3819904327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6509609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0860595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8170900344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6193170547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0544157028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4895143508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8692350387573</t>
+    <t xml:space="preserve">14.9515733718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5322961807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3345232009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3740797042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3819894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6509618759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0860576629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8170871734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6193161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0544185638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4895133972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8692359924316</t>
   </si>
   <si>
     <t xml:space="preserve">15.7189302444458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.307562828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3471183776855</t>
+    <t xml:space="preserve">15.3075647354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3471193313599</t>
   </si>
   <si>
     <t xml:space="preserve">15.6081781387329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2284564971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1572561264038</t>
+    <t xml:space="preserve">15.2284526824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1572551727295</t>
   </si>
   <si>
     <t xml:space="preserve">15.1889009475708</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1414337158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3866710662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2838315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3154745101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7505731582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7110195159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6160869598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4420471191406</t>
+    <t xml:space="preserve">15.1414356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3866739273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2838306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3154735565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7505741119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7110185623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6160879135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4420490264893</t>
   </si>
   <si>
     <t xml:space="preserve">15.2047214508057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2363662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1651678085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.402491569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6239986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7743072509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2173156738281</t>
+    <t xml:space="preserve">15.236367225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.165168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4024925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6239995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7743053436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2173137664795</t>
   </si>
   <si>
     <t xml:space="preserve">16.5179290771484</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">16.296422958374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.565393447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0400466918945</t>
+    <t xml:space="preserve">16.5653953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0400447845459</t>
   </si>
   <si>
     <t xml:space="preserve">16.9292945861816</t>
@@ -2243,16 +2243,16 @@
     <t xml:space="preserve">17.0558681488037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9609394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6919689178467</t>
+    <t xml:space="preserve">16.9609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.691967010498</t>
   </si>
   <si>
     <t xml:space="preserve">16.8976516723633</t>
   </si>
   <si>
-    <t xml:space="preserve">17.198263168335</t>
+    <t xml:space="preserve">17.1982669830322</t>
   </si>
   <si>
     <t xml:space="preserve">16.8818302154541</t>
@@ -2264,16 +2264,16 @@
     <t xml:space="preserve">17.3564834594727</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4514141082764</t>
+    <t xml:space="preserve">17.4514122009277</t>
   </si>
   <si>
     <t xml:space="preserve">17.6096305847168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4039478302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4355907440186</t>
+    <t xml:space="preserve">17.4039459228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4355926513672</t>
   </si>
   <si>
     <t xml:space="preserve">17.5305213928223</t>
@@ -2285,13 +2285,13 @@
     <t xml:space="preserve">18.1792144775391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1317481994629</t>
+    <t xml:space="preserve">18.1317501068115</t>
   </si>
   <si>
     <t xml:space="preserve">18.2583236694336</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3690776824951</t>
+    <t xml:space="preserve">18.3690757751465</t>
   </si>
   <si>
     <t xml:space="preserve">18.2899684906006</t>
@@ -2300,40 +2300,40 @@
     <t xml:space="preserve">18.2108592987061</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3723030090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4830589294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7045574188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.324836730957</t>
+    <t xml:space="preserve">17.3723011016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4830570220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7045612335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3248386383057</t>
   </si>
   <si>
     <t xml:space="preserve">16.5021076202393</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4988784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1508007049561</t>
+    <t xml:space="preserve">17.4988803863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1507968902588</t>
   </si>
   <si>
     <t xml:space="preserve">11.1701707839966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0213174819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8267726898193</t>
+    <t xml:space="preserve">13.0213165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8267736434937</t>
   </si>
   <si>
     <t xml:space="preserve">11.6210899353027</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6290016174316</t>
+    <t xml:space="preserve">11.629002571106</t>
   </si>
   <si>
     <t xml:space="preserve">11.3600311279297</t>
@@ -2348,28 +2348,28 @@
     <t xml:space="preserve">12.0245456695557</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0641002655029</t>
+    <t xml:space="preserve">12.0640993118286</t>
   </si>
   <si>
     <t xml:space="preserve">12.4200897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1748533248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9026536941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6969709396362</t>
+    <t xml:space="preserve">12.1748523712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9026546478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6969699859619</t>
   </si>
   <si>
     <t xml:space="preserve">13.2190895080566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4722385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.314019203186</t>
+    <t xml:space="preserve">13.4722394943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3140211105347</t>
   </si>
   <si>
     <t xml:space="preserve">13.2349109649658</t>
@@ -2381,88 +2381,88 @@
     <t xml:space="preserve">13.4089517593384</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4564151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1004247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0925159454346</t>
+    <t xml:space="preserve">13.4564161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1004257202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0925149917603</t>
   </si>
   <si>
     <t xml:space="preserve">13.2507333755493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0687847137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3614845275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4326839447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5038795471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9738512039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9342975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0371379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1795349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2111806869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.543436050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6225442886353</t>
+    <t xml:space="preserve">13.0687837600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3614864349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4326829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5038814544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9738531112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9342966079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0371389389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1795358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2111787796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5434370040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6225433349609</t>
   </si>
   <si>
     <t xml:space="preserve">13.7095642089844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2056903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8418645858765</t>
+    <t xml:space="preserve">14.2056894302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8418636322021</t>
   </si>
   <si>
     <t xml:space="preserve">14.1560773849487</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2966451644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2883758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0491008758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2475500106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2971630096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1240367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4134426116943</t>
+    <t xml:space="preserve">14.2966461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2883768081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0491018295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2475481033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2971620559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1240348815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4134407043457</t>
   </si>
   <si>
     <t xml:space="preserve">16.5043964385986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1405715942383</t>
+    <t xml:space="preserve">16.1405754089355</t>
   </si>
   <si>
     <t xml:space="preserve">16.0909595489502</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">16.190185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5865678787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3467741012573</t>
+    <t xml:space="preserve">15.5865659713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.346773147583</t>
   </si>
   <si>
     <t xml:space="preserve">15.2144746780396</t>
@@ -2486,37 +2486,37 @@
     <t xml:space="preserve">15.2806253433228</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8346300125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6527166366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6692562103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5782995223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7932844161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8594360351562</t>
+    <t xml:space="preserve">15.8346290588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6527185440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6692543029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5782985687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7932872772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8594379425049</t>
   </si>
   <si>
     <t xml:space="preserve">15.3633108139038</t>
   </si>
   <si>
-    <t xml:space="preserve">15.429461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5617599487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8677072525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.330753326416</t>
+    <t xml:space="preserve">15.4294605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5617609024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8677043914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3307552337646</t>
   </si>
   <si>
     <t xml:space="preserve">17.0501365661621</t>
@@ -2543,16 +2543,16 @@
     <t xml:space="preserve">17.7777824401855</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2981967926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2816581726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.314733505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4304943084717</t>
+    <t xml:space="preserve">17.2981948852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2816600799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3147354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4304962158203</t>
   </si>
   <si>
     <t xml:space="preserve">17.3643455505371</t>
@@ -2561,28 +2561,28 @@
     <t xml:space="preserve">17.3808822631836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9839839935303</t>
+    <t xml:space="preserve">16.9839859008789</t>
   </si>
   <si>
     <t xml:space="preserve">16.8186092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9012985229492</t>
+    <t xml:space="preserve">16.9012966156006</t>
   </si>
   <si>
     <t xml:space="preserve">16.8516845703125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.752462387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0170574188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4635715484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5958728790283</t>
+    <t xml:space="preserve">16.7524585723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0170593261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4635696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5958690643311</t>
   </si>
   <si>
     <t xml:space="preserve">17.4801082611084</t>
@@ -2594,31 +2594,31 @@
     <t xml:space="preserve">17.9266204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9927711486816</t>
+    <t xml:space="preserve">17.992769241333</t>
   </si>
   <si>
     <t xml:space="preserve">18.0919933319092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4227447509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.472354888916</t>
+    <t xml:space="preserve">18.4227428436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4723567962646</t>
   </si>
   <si>
     <t xml:space="preserve">18.1581439971924</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0258445739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0754566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.505428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.389669418335</t>
+    <t xml:space="preserve">18.025842666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0754585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5054302215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3896713256836</t>
   </si>
   <si>
     <t xml:space="preserve">18.2739067077637</t>
@@ -2627,28 +2627,28 @@
     <t xml:space="preserve">18.3235187530518</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3400592803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1912212371826</t>
+    <t xml:space="preserve">18.3400573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.191219329834</t>
   </si>
   <si>
     <t xml:space="preserve">18.0589218139648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.910083770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2408313751221</t>
+    <t xml:space="preserve">17.9100818634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2408294677734</t>
   </si>
   <si>
     <t xml:space="preserve">18.3069801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620216369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.794319152832</t>
+    <t xml:space="preserve">17.6620197296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7943210601807</t>
   </si>
   <si>
     <t xml:space="preserve">17.711633682251</t>
@@ -2657,10 +2657,10 @@
     <t xml:space="preserve">17.5793323516846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3478088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4966468811035</t>
+    <t xml:space="preserve">17.347806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4966449737549</t>
   </si>
   <si>
     <t xml:space="preserve">17.3974208831787</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">17.7447071075439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6046562194824</t>
+    <t xml:space="preserve">18.6046581268311</t>
   </si>
   <si>
     <t xml:space="preserve">18.7700328826904</t>
@@ -2678,28 +2678,28 @@
     <t xml:space="preserve">18.3731307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6542663574219</t>
+    <t xml:space="preserve">18.6542682647705</t>
   </si>
   <si>
     <t xml:space="preserve">18.7534942626953</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4062080383301</t>
+    <t xml:space="preserve">18.4062061309814</t>
   </si>
   <si>
     <t xml:space="preserve">18.1416072845459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9431571960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1085300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7281703948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9596939086914</t>
+    <t xml:space="preserve">17.9431591033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1085319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7281723022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9596977233887</t>
   </si>
   <si>
     <t xml:space="preserve">17.1989707946777</t>
@@ -2708,10 +2708,10 @@
     <t xml:space="preserve">16.636697769165</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2894096374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9503908157349</t>
+    <t xml:space="preserve">16.2894115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9503927230835</t>
   </si>
   <si>
     <t xml:space="preserve">16.0413494110107</t>
@@ -2720,13 +2720,13 @@
     <t xml:space="preserve">16.5374717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0832080841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5627956390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.06667137146</t>
+    <t xml:space="preserve">17.0832099914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5627937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0666694641113</t>
   </si>
   <si>
     <t xml:space="preserve">17.2155094146729</t>
@@ -2738,19 +2738,19 @@
     <t xml:space="preserve">17.0005207061768</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9178333282471</t>
+    <t xml:space="preserve">16.9178352355957</t>
   </si>
   <si>
     <t xml:space="preserve">16.7028484344482</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8847599029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7855358123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6201610565186</t>
+    <t xml:space="preserve">16.8847618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7855319976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6201591491699</t>
   </si>
   <si>
     <t xml:space="preserve">16.4795913696289</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">17.5462589263916</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1746807098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8692531585693</t>
+    <t xml:space="preserve">18.1746826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8692569732666</t>
   </si>
   <si>
     <t xml:space="preserve">19.1669311523438</t>
@@ -2780,16 +2780,16 @@
     <t xml:space="preserve">19.3488426208496</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0599555969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.960729598999</t>
+    <t xml:space="preserve">20.0599536895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9607257843018</t>
   </si>
   <si>
     <t xml:space="preserve">20.5064640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6883773803711</t>
+    <t xml:space="preserve">20.6883792877197</t>
   </si>
   <si>
     <t xml:space="preserve">20.7049160003662</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">20.8206768035889</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7545299530029</t>
+    <t xml:space="preserve">20.7545280456543</t>
   </si>
   <si>
     <t xml:space="preserve">20.9364376068115</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">20.7214527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0025901794434</t>
+    <t xml:space="preserve">21.0025882720947</t>
   </si>
   <si>
     <t xml:space="preserve">21.1845016479492</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">21.6806240081787</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1767501831055</t>
+    <t xml:space="preserve">22.1767520904541</t>
   </si>
   <si>
     <t xml:space="preserve">21.994836807251</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5571117401123</t>
+    <t xml:space="preserve">22.5571136474609</t>
   </si>
   <si>
     <t xml:space="preserve">21.2175769805908</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">20.9529781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3002643585205</t>
+    <t xml:space="preserve">21.3002662658691</t>
   </si>
   <si>
     <t xml:space="preserve">21.5979385375977</t>
@@ -2846,25 +2846,25 @@
     <t xml:space="preserve">21.4160251617432</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8956146240234</t>
+    <t xml:space="preserve">21.8956127166748</t>
   </si>
   <si>
     <t xml:space="preserve">21.515251159668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8460006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1602115631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5317897796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3664131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7379913330078</t>
+    <t xml:space="preserve">21.8459987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.160213470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5317916870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3664150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7379894256592</t>
   </si>
   <si>
     <t xml:space="preserve">20.5726146697998</t>
@@ -2873,19 +2873,19 @@
     <t xml:space="preserve">21.2506523132324</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7876014709473</t>
+    <t xml:space="preserve">20.7876033782959</t>
   </si>
   <si>
     <t xml:space="preserve">20.2584056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6134433746338</t>
+    <t xml:space="preserve">19.6134414672852</t>
   </si>
   <si>
     <t xml:space="preserve">20.192253112793</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3323059082031</t>
+    <t xml:space="preserve">19.3323040008545</t>
   </si>
   <si>
     <t xml:space="preserve">18.9354038238525</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">21.2010402679443</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9860515594482</t>
+    <t xml:space="preserve">20.9860496520996</t>
   </si>
   <si>
     <t xml:space="preserve">21.4656391143799</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">20.0103416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6465148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2253265380859</t>
+    <t xml:space="preserve">19.6465187072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2253284454346</t>
   </si>
   <si>
     <t xml:space="preserve">20.3410911560059</t>
@@ -2918,16 +2918,16 @@
     <t xml:space="preserve">20.5560779571533</t>
   </si>
   <si>
-    <t xml:space="preserve">20.638765335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.035665512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3498783111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0852756500244</t>
+    <t xml:space="preserve">20.6387634277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0356636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.34987449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.085277557373</t>
   </si>
   <si>
     <t xml:space="preserve">21.0191287994385</t>
@@ -2939,13 +2939,13 @@
     <t xml:space="preserve">21.1018161773682</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8868274688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5230007171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.60569190979</t>
+    <t xml:space="preserve">20.8868293762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5230026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6056900024414</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268783569336</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">20.1095676422119</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1514282226562</t>
+    <t xml:space="preserve">21.1514263153076</t>
   </si>
   <si>
     <t xml:space="preserve">20.6222305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3080158233643</t>
+    <t xml:space="preserve">20.3080139160156</t>
   </si>
   <si>
     <t xml:space="preserve">20.4072399139404</t>
@@ -2972,43 +2972,43 @@
     <t xml:space="preserve">20.3907032012939</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1261024475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0764904022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2914810180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2661533355713</t>
+    <t xml:space="preserve">20.1261005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0764923095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2914791107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2661552429199</t>
   </si>
   <si>
     <t xml:space="preserve">19.762279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.878044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3484573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3314094543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0756320953369</t>
+    <t xml:space="preserve">19.8780422210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3484592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3314075469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0756340026855</t>
   </si>
   <si>
     <t xml:space="preserve">21.2461490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2290992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.177942276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4337139129639</t>
+    <t xml:space="preserve">21.229097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1779441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4337158203125</t>
   </si>
   <si>
     <t xml:space="preserve">21.4848709106445</t>
@@ -3017,10 +3017,10 @@
     <t xml:space="preserve">21.6042308807373</t>
   </si>
   <si>
-    <t xml:space="preserve">21.621280670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3143539428711</t>
+    <t xml:space="preserve">21.6212825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3143558502197</t>
   </si>
   <si>
     <t xml:space="preserve">21.570125579834</t>
@@ -3029,25 +3029,25 @@
     <t xml:space="preserve">22.388599395752</t>
   </si>
   <si>
-    <t xml:space="preserve">21.979362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0646171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0305194854736</t>
+    <t xml:space="preserve">21.9793643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0646190643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.030517578125</t>
   </si>
   <si>
     <t xml:space="preserve">21.7235908508301</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6553859710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7406406402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3655071258545</t>
+    <t xml:space="preserve">21.6553840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7406425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3655090332031</t>
   </si>
   <si>
     <t xml:space="preserve">21.4507675170898</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">21.6724376678467</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0987243652344</t>
+    <t xml:space="preserve">22.0987224578857</t>
   </si>
   <si>
     <t xml:space="preserve">21.7917957305908</t>
@@ -3065,16 +3065,16 @@
     <t xml:space="preserve">21.9964141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3825626373291</t>
+    <t xml:space="preserve">21.3825607299805</t>
   </si>
   <si>
     <t xml:space="preserve">20.8369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8710174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8880672454834</t>
+    <t xml:space="preserve">20.8710155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.888069152832</t>
   </si>
   <si>
     <t xml:space="preserve">21.7065391540527</t>
@@ -3086,22 +3086,22 @@
     <t xml:space="preserve">22.1328258514404</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2351360321045</t>
+    <t xml:space="preserve">22.2351341247559</t>
   </si>
   <si>
     <t xml:space="preserve">22.47385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2692394256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7346038818359</t>
+    <t xml:space="preserve">22.2692375183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7346057891846</t>
   </si>
   <si>
     <t xml:space="preserve">20.5470390319824</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2632007598877</t>
+    <t xml:space="preserve">21.2632026672363</t>
   </si>
   <si>
     <t xml:space="preserve">21.1097373962402</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">21.1608905792236</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5530757904053</t>
+    <t xml:space="preserve">21.5530776977539</t>
   </si>
   <si>
     <t xml:space="preserve">21.7747478485107</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">21.2973022460938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0926856994629</t>
+    <t xml:space="preserve">21.0926876068115</t>
   </si>
   <si>
     <t xml:space="preserve">20.8539638519287</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">21.0074291229248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.280252456665</t>
+    <t xml:space="preserve">21.2802505493164</t>
   </si>
   <si>
     <t xml:space="preserve">21.9282073974609</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">21.8088474273682</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8941059112549</t>
+    <t xml:space="preserve">21.8941078186035</t>
   </si>
   <si>
     <t xml:space="preserve">21.7576942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3996143341064</t>
+    <t xml:space="preserve">21.3996124267578</t>
   </si>
   <si>
     <t xml:space="preserve">21.9111576080322</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">22.4909076690674</t>
   </si>
   <si>
-    <t xml:space="preserve">22.422700881958</t>
+    <t xml:space="preserve">22.4227027893066</t>
   </si>
   <si>
     <t xml:space="preserve">22.2521858215332</t>
@@ -3179,37 +3179,37 @@
     <t xml:space="preserve">22.6614227294922</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7296257019043</t>
+    <t xml:space="preserve">22.7296276092529</t>
   </si>
   <si>
     <t xml:space="preserve">23.172966003418</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7697696685791</t>
+    <t xml:space="preserve">23.7697677612305</t>
   </si>
   <si>
     <t xml:space="preserve">23.4628429412842</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3775844573975</t>
+    <t xml:space="preserve">23.3775863647461</t>
   </si>
   <si>
     <t xml:space="preserve">23.9232330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2191429138184</t>
+    <t xml:space="preserve">25.219144821167</t>
   </si>
   <si>
     <t xml:space="preserve">25.4749164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8329963684082</t>
+    <t xml:space="preserve">25.8329982757568</t>
   </si>
   <si>
     <t xml:space="preserve">25.7818431854248</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1740303039551</t>
+    <t xml:space="preserve">26.1740283966064</t>
   </si>
   <si>
     <t xml:space="preserve">26.3274898529053</t>
@@ -3218,13 +3218,13 @@
     <t xml:space="preserve">26.6003150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6173667907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7708282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6855735778809</t>
+    <t xml:space="preserve">26.6173648834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7708301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6855716705322</t>
   </si>
   <si>
     <t xml:space="preserve">25.969409942627</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">26.7196750640869</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3615970611572</t>
+    <t xml:space="preserve">26.3615951538086</t>
   </si>
   <si>
     <t xml:space="preserve">26.3104419708252</t>
@@ -3248,16 +3248,16 @@
     <t xml:space="preserve">25.5431232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0315780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.826961517334</t>
+    <t xml:space="preserve">25.0315799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8269596099854</t>
   </si>
   <si>
     <t xml:space="preserve">25.0145282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">25.167989730835</t>
+    <t xml:space="preserve">25.1679916381836</t>
   </si>
   <si>
     <t xml:space="preserve">25.1168346405029</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">25.1338882446289</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7246513366699</t>
+    <t xml:space="preserve">24.7246532440186</t>
   </si>
   <si>
     <t xml:space="preserve">24.7587566375732</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">25.3896598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3836231231689</t>
+    <t xml:space="preserve">24.3836212158203</t>
   </si>
   <si>
     <t xml:space="preserve">24.1790046691895</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">24.3324680328369</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6223430633545</t>
+    <t xml:space="preserve">24.6223411560059</t>
   </si>
   <si>
     <t xml:space="preserve">24.1960563659668</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">24.1449012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1107997894287</t>
+    <t xml:space="preserve">24.1107978820801</t>
   </si>
   <si>
     <t xml:space="preserve">23.8038711547852</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">24.4518280029297</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2131080627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3665714263916</t>
+    <t xml:space="preserve">24.2131061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3665733337402</t>
   </si>
   <si>
     <t xml:space="preserve">24.2472114562988</t>
@@ -3332,16 +3332,16 @@
     <t xml:space="preserve">25.0486278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">24.434778213501</t>
+    <t xml:space="preserve">24.4347763061523</t>
   </si>
   <si>
     <t xml:space="preserve">23.5481014251709</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4969444274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9342479705811</t>
+    <t xml:space="preserve">23.4969463348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9342460632324</t>
   </si>
   <si>
     <t xml:space="preserve">22.7978324890137</t>
@@ -3359,34 +3359,34 @@
     <t xml:space="preserve">21.5189723968506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8429527282715</t>
+    <t xml:space="preserve">21.8429508209229</t>
   </si>
   <si>
     <t xml:space="preserve">22.1839809417725</t>
   </si>
   <si>
-    <t xml:space="preserve">21.194995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6383323669434</t>
+    <t xml:space="preserve">21.1949939727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6383304595947</t>
   </si>
   <si>
     <t xml:space="preserve">21.2120456695557</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9051189422607</t>
+    <t xml:space="preserve">20.9051208496094</t>
   </si>
   <si>
     <t xml:space="preserve">20.6663990020752</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4678192138672</t>
+    <t xml:space="preserve">21.4678173065186</t>
   </si>
   <si>
     <t xml:space="preserve">21.0244789123535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5640907287598</t>
+    <t xml:space="preserve">20.5640926361084</t>
   </si>
   <si>
     <t xml:space="preserve">20.9221706390381</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">20.5129356384277</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2912673950195</t>
+    <t xml:space="preserve">20.2912654876709</t>
   </si>
   <si>
     <t xml:space="preserve">20.1378021240234</t>
@@ -3422,22 +3422,22 @@
     <t xml:space="preserve">24.1619529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5601749420166</t>
+    <t xml:space="preserve">25.560173034668</t>
   </si>
   <si>
     <t xml:space="preserve">24.9292697906494</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8951663970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3154163360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2873516082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7136383056641</t>
+    <t xml:space="preserve">24.8951683044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3154182434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2873497009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7136363983154</t>
   </si>
   <si>
     <t xml:space="preserve">24.6564464569092</t>
@@ -3446,37 +3446,37 @@
     <t xml:space="preserve">25.1850433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9804229736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.662483215332</t>
+    <t xml:space="preserve">24.9804248809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6624851226807</t>
   </si>
   <si>
     <t xml:space="preserve">26.3786449432373</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2933883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8049354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7537784576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9413452148438</t>
+    <t xml:space="preserve">26.2933902740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8049335479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7537803649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9413471221924</t>
   </si>
   <si>
     <t xml:space="preserve">27.0436515808105</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0948066711426</t>
+    <t xml:space="preserve">27.0948085784912</t>
   </si>
   <si>
     <t xml:space="preserve">26.8219833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9925003051758</t>
+    <t xml:space="preserve">26.9924983978271</t>
   </si>
   <si>
     <t xml:space="preserve">27.1459617614746</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">27.7939186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8621253967285</t>
+    <t xml:space="preserve">27.8621234893799</t>
   </si>
   <si>
     <t xml:space="preserve">28.0496940612793</t>
@@ -3506,25 +3506,25 @@
     <t xml:space="preserve">27.5893020629883</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2823734283447</t>
+    <t xml:space="preserve">27.1800670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2823753356934</t>
   </si>
   <si>
     <t xml:space="preserve">26.856086730957</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6514682769775</t>
+    <t xml:space="preserve">26.6514701843262</t>
   </si>
   <si>
     <t xml:space="preserve">25.3555564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3214550018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9864616394043</t>
+    <t xml:space="preserve">25.3214530944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9864597320557</t>
   </si>
   <si>
     <t xml:space="preserve">25.3385047912598</t>
@@ -3533,16 +3533,16 @@
     <t xml:space="preserve">26.8901920318604</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7598152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.475980758667</t>
+    <t xml:space="preserve">27.7598171234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4759788513184</t>
   </si>
   <si>
     <t xml:space="preserve">28.5100803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6976490020752</t>
+    <t xml:space="preserve">28.6976509094238</t>
   </si>
   <si>
     <t xml:space="preserve">28.9875240325928</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">29.4604301452637</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4954624176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0559463500977</t>
+    <t xml:space="preserve">29.4954605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.055944442749</t>
   </si>
   <si>
     <t xml:space="preserve">29.5655193328857</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">28.3044338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9524955749512</t>
+    <t xml:space="preserve">28.9524936676025</t>
   </si>
   <si>
     <t xml:space="preserve">28.8824329376221</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">29.0575828552246</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1451587677002</t>
+    <t xml:space="preserve">29.1451568603516</t>
   </si>
   <si>
     <t xml:space="preserve">27.043342590332</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">25.9924392700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9574069976807</t>
+    <t xml:space="preserve">25.957405090332</t>
   </si>
   <si>
     <t xml:space="preserve">25.607105255127</t>
@@ -3617,13 +3617,13 @@
     <t xml:space="preserve">26.255163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6054668426514</t>
+    <t xml:space="preserve">26.6054649353027</t>
   </si>
   <si>
     <t xml:space="preserve">25.8873462677002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4653434753418</t>
+    <t xml:space="preserve">26.4653453826904</t>
   </si>
   <si>
     <t xml:space="preserve">26.3252239227295</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">26.9382553100586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9732856750488</t>
+    <t xml:space="preserve">26.9732837677002</t>
   </si>
   <si>
     <t xml:space="preserve">27.1309204101562</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">27.4286785125732</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3411026000977</t>
+    <t xml:space="preserve">27.341100692749</t>
   </si>
   <si>
     <t xml:space="preserve">26.7455902099609</t>
@@ -3671,22 +3671,22 @@
     <t xml:space="preserve">26.6930408477783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5879535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1834659576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5512809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8840713500977</t>
+    <t xml:space="preserve">26.5879516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1834678649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5512828826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.884069442749</t>
   </si>
   <si>
     <t xml:space="preserve">28.1467971801758</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4445533752441</t>
+    <t xml:space="preserve">28.4445552825928</t>
   </si>
   <si>
     <t xml:space="preserve">28.8999481201172</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">29.2327365875244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.40625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1260051727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3186721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8632774353027</t>
+    <t xml:space="preserve">30.4062480926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1260070800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3186702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8632755279541</t>
   </si>
   <si>
     <t xml:space="preserve">29.950855255127</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">30.4412784576416</t>
   </si>
   <si>
-    <t xml:space="preserve">31.1593990325928</t>
+    <t xml:space="preserve">31.15940284729</t>
   </si>
   <si>
     <t xml:space="preserve">30.3361873626709</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">29.7406730651855</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7089214324951</t>
+    <t xml:space="preserve">27.7089195251465</t>
   </si>
   <si>
     <t xml:space="preserve">27.4987373352051</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">27.8490409851074</t>
   </si>
   <si>
-    <t xml:space="preserve">28.269401550293</t>
+    <t xml:space="preserve">28.2694034576416</t>
   </si>
   <si>
     <t xml:space="preserve">28.1643142700195</t>
@@ -3773,13 +3773,13 @@
     <t xml:space="preserve">29.0926151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7598266601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1801891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8665561676025</t>
+    <t xml:space="preserve">28.7598285675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1801910400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8665542602539</t>
   </si>
   <si>
     <t xml:space="preserve">25.169225692749</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">25.064136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5912303924561</t>
+    <t xml:space="preserve">24.5912284851074</t>
   </si>
   <si>
     <t xml:space="preserve">24.7488651275635</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">24.9415302276611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4335899353027</t>
+    <t xml:space="preserve">24.4335918426514</t>
   </si>
   <si>
     <t xml:space="preserve">24.1708660125732</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">24.9065017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5545597076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7472248077393</t>
+    <t xml:space="preserve">25.5545616149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7472267150879</t>
   </si>
   <si>
     <t xml:space="preserve">25.6946811676025</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">26.7806186676025</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6738891601562</t>
+    <t xml:space="preserve">27.6738910675049</t>
   </si>
   <si>
     <t xml:space="preserve">27.7964954376221</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">26.7631034851074</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9032249450684</t>
+    <t xml:space="preserve">26.9032230377197</t>
   </si>
   <si>
     <t xml:space="preserve">26.0274677276611</t>
@@ -3872,13 +3872,13 @@
     <t xml:space="preserve">26.3952865600586</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8331623077393</t>
+    <t xml:space="preserve">26.8331642150879</t>
   </si>
   <si>
     <t xml:space="preserve">26.307710647583</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9223766326904</t>
+    <t xml:space="preserve">25.9223785400391</t>
   </si>
   <si>
     <t xml:space="preserve">26.3777713775635</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">26.5003757476807</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1325588226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.097526550293</t>
+    <t xml:space="preserve">26.1325569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0975284576416</t>
   </si>
   <si>
     <t xml:space="preserve">26.5354061126709</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">26.2376499176025</t>
   </si>
   <si>
-    <t xml:space="preserve">25.764741897583</t>
+    <t xml:space="preserve">25.7647399902344</t>
   </si>
   <si>
     <t xml:space="preserve">25.8348026275635</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2201366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4144401550293</t>
+    <t xml:space="preserve">26.2201347351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4144382476807</t>
   </si>
   <si>
     <t xml:space="preserve">25.466983795166</t>
@@ -3923,10 +3923,10 @@
     <t xml:space="preserve">25.3618927001953</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5895900726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8714714050293</t>
+    <t xml:space="preserve">25.5895881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8714694976807</t>
   </si>
   <si>
     <t xml:space="preserve">24.4686241149902</t>
@@ -3935,52 +3935,52 @@
     <t xml:space="preserve">24.5737133026123</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1183204650879</t>
+    <t xml:space="preserve">24.1183223724365</t>
   </si>
   <si>
     <t xml:space="preserve">24.2409267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3285026550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7838954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8539543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3109855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2234115600586</t>
+    <t xml:space="preserve">24.3285007476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7838935852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8539562225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3109874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.22340965271</t>
   </si>
   <si>
     <t xml:space="preserve">24.3460159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4160785675049</t>
+    <t xml:space="preserve">24.4160766601562</t>
   </si>
   <si>
     <t xml:space="preserve">24.3985633850098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.678804397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9590473175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0466213226318</t>
+    <t xml:space="preserve">24.6788024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9590454101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0466194152832</t>
   </si>
   <si>
     <t xml:space="preserve">24.7138328552246</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5036525726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6612873077393</t>
+    <t xml:space="preserve">24.5036506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6612892150879</t>
   </si>
   <si>
     <t xml:space="preserve">24.2759552001953</t>
@@ -4007,10 +4007,10 @@
     <t xml:space="preserve">23.8731079101562</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3476524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7154712677002</t>
+    <t xml:space="preserve">23.3476543426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7154731750488</t>
   </si>
   <si>
     <t xml:space="preserve">23.7680168151855</t>
@@ -4025,13 +4025,13 @@
     <t xml:space="preserve">23.049898147583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8747482299805</t>
+    <t xml:space="preserve">22.8747463226318</t>
   </si>
   <si>
     <t xml:space="preserve">23.1900177001953</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2425651550293</t>
+    <t xml:space="preserve">23.2425632476807</t>
   </si>
   <si>
     <t xml:space="preserve">23.6979560852051</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">23.9256534576416</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7505016326904</t>
+    <t xml:space="preserve">23.7505035400391</t>
   </si>
   <si>
     <t xml:space="preserve">23.435230255127</t>
@@ -4058,10 +4058,10 @@
     <t xml:space="preserve">23.5228061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9606857299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4861354827881</t>
+    <t xml:space="preserve">23.9606838226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4861373901367</t>
   </si>
   <si>
     <t xml:space="preserve">24.2584400177002</t>
@@ -4073,10 +4073,10 @@
     <t xml:space="preserve">25.2217712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2042579650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1341991424561</t>
+    <t xml:space="preserve">25.2042598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1341972351074</t>
   </si>
   <si>
     <t xml:space="preserve">24.6262588500977</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">24.3635330200195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7855339050293</t>
+    <t xml:space="preserve">23.7855319976807</t>
   </si>
   <si>
     <t xml:space="preserve">23.2250499725342</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">23.2775955200195</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2951107025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0657730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7663803100586</t>
+    <t xml:space="preserve">23.295108795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0657749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.76637840271</t>
   </si>
   <si>
     <t xml:space="preserve">24.7313499450684</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">23.6418628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4965972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1334362030029</t>
+    <t xml:space="preserve">23.4965953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1334342956543</t>
   </si>
   <si>
     <t xml:space="preserve">23.5329132080078</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">24.2955551147461</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5679244995117</t>
+    <t xml:space="preserve">24.5679264068604</t>
   </si>
   <si>
     <t xml:space="preserve">24.4771347045898</t>
@@ -4163,13 +4163,13 @@
     <t xml:space="preserve">24.5134525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3318691253662</t>
+    <t xml:space="preserve">24.3318710327148</t>
   </si>
   <si>
     <t xml:space="preserve">23.9868659973145</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5510730743408</t>
+    <t xml:space="preserve">23.5510711669922</t>
   </si>
   <si>
     <t xml:space="preserve">23.4058074951172</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">23.4602813720703</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8234443664551</t>
+    <t xml:space="preserve">23.8234424591064</t>
   </si>
   <si>
     <t xml:space="preserve">23.6237049102783</t>
@@ -4196,13 +4196,13 @@
     <t xml:space="preserve">24.8221397399902</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0413417816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.386344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1321315765381</t>
+    <t xml:space="preserve">24.0413398742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3863468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1321296691895</t>
   </si>
   <si>
     <t xml:space="preserve">24.4589786529541</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">24.6768760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6042423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.549768447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7858219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2397747039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8039798736572</t>
+    <t xml:space="preserve">24.6042442321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5497703552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7858238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2397766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8039817810059</t>
   </si>
   <si>
     <t xml:space="preserve">24.9674053192139</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">22.2618465423584</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2981605529785</t>
+    <t xml:space="preserve">22.2981624603271</t>
   </si>
   <si>
     <t xml:space="preserve">22.388952255249</t>
@@ -4271,25 +4271,25 @@
     <t xml:space="preserve">22.2073707580566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.062105178833</t>
+    <t xml:space="preserve">22.0621070861816</t>
   </si>
   <si>
     <t xml:space="preserve">21.6807861328125</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6263103485107</t>
+    <t xml:space="preserve">21.6263122558594</t>
   </si>
   <si>
     <t xml:space="preserve">22.6431674957275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6794834136963</t>
+    <t xml:space="preserve">22.6794815063477</t>
   </si>
   <si>
     <t xml:space="preserve">22.5886917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1515941619873</t>
+    <t xml:space="preserve">23.1515922546387</t>
   </si>
   <si>
     <t xml:space="preserve">22.9700107574463</t>
@@ -4310,28 +4310,28 @@
     <t xml:space="preserve">23.024486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9155387878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8610649108887</t>
+    <t xml:space="preserve">22.9155368804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.86106300354</t>
   </si>
   <si>
     <t xml:space="preserve">23.2060661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">22.534215927124</t>
+    <t xml:space="preserve">22.5342178344727</t>
   </si>
   <si>
     <t xml:space="preserve">21.9349994659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8442077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2631492614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8999862670898</t>
+    <t xml:space="preserve">21.8442096710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2631511688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8999881744385</t>
   </si>
   <si>
     <t xml:space="preserve">20.482349395752</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">20.7365646362305</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1010303497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6833953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7378692626953</t>
+    <t xml:space="preserve">20.1010284423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6833934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7378673553467</t>
   </si>
   <si>
     <t xml:space="preserve">20.0102405548096</t>
@@ -4361,7 +4361,7 @@
     <t xml:space="preserve">19.9376068115234</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3915596008301</t>
+    <t xml:space="preserve">20.3915576934814</t>
   </si>
   <si>
     <t xml:space="preserve">20.6094589233398</t>
@@ -4373,19 +4373,19 @@
     <t xml:space="preserve">20.6820907592773</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1541996002197</t>
+    <t xml:space="preserve">21.1542015075684</t>
   </si>
   <si>
     <t xml:space="preserve">21.0997276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1723575592041</t>
+    <t xml:space="preserve">21.1723594665527</t>
   </si>
   <si>
     <t xml:space="preserve">21.0634117126465</t>
   </si>
   <si>
-    <t xml:space="preserve">20.809196472168</t>
+    <t xml:space="preserve">20.8091983795166</t>
   </si>
   <si>
     <t xml:space="preserve">21.0089359283447</t>
@@ -4397,16 +4397,16 @@
     <t xml:space="preserve">21.0270938873291</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6081523895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.771577835083</t>
+    <t xml:space="preserve">21.608154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7715759277344</t>
   </si>
   <si>
     <t xml:space="preserve">21.4628887176514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9181461334229</t>
+    <t xml:space="preserve">20.9181480407715</t>
   </si>
   <si>
     <t xml:space="preserve">21.2449913024902</t>
@@ -4418,7 +4